--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Dashboard" sheetId="1" r:id="R925b89e073564e03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Precedent Transactions" sheetId="2" r:id="R87c46caacbb54fdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Card" sheetId="3" r:id="Rdbebe619fd724037"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; QA" sheetId="4" r:id="R2e51e29854c74032"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Dashboard" sheetId="1" r:id="Rdd12d12ff2da4122"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Precedent Transactions" sheetId="2" r:id="R328d3bbdd89c4d60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Card" sheetId="3" r:id="R62e5697d724f4edb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; QA" sheetId="4" r:id="Rcd48572823e84eb1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,12 +16,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="3">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="#,##0;[Red](#,##0);-"/>
-    <x:numFmt numFmtId="201" formatCode="dd-mmm-yyyy"/>
-    <x:numFmt numFmtId="202" formatCode="0.0%;[Red](0.0%);-"/>
+    <x:numFmt numFmtId="201" formatCode="0.0x"/>
+    <x:numFmt numFmtId="202" formatCode="dd-mmm-yyyy"/>
+    <x:numFmt numFmtId="203" formatCode="0.0%;[Red](0.0%);-"/>
   </x:numFmts>
-  <x:fonts count="10">
+  <x:fonts count="11">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -66,6 +67,11 @@
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FF10243E"/>
@@ -77,7 +83,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -102,6 +108,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -156,7 +167,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="77">
+  <x:cellXfs count="66">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -201,25 +212,13 @@
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:alignment horizontal="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -227,84 +226,61 @@
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="200" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="202" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="201" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -342,8 +318,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PrecedentTransactionsTable" displayName="PrecedentTransactionsTable" ref="A6:T7" headerRowCount="1">
-  <x:tableColumns count="20">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PrecedentTransactionsTable" displayName="PrecedentTransactionsTable" ref="A6:AC43" headerRowCount="1">
+  <x:tableColumns count="29">
     <x:tableColumn id="1" name="Deal ID"/>
     <x:tableColumn id="2" name="Announced Date"/>
     <x:tableColumn id="3" name="Type"/>
@@ -353,17 +329,26 @@
     <x:tableColumn id="7" name="Sector"/>
     <x:tableColumn id="8" name="Geography"/>
     <x:tableColumn id="9" name="Transaction Value"/>
-    <x:tableColumn id="10" name="Currency"/>
-    <x:tableColumn id="11" name="Stake %"/>
-    <x:tableColumn id="12" name="Instrument"/>
-    <x:tableColumn id="13" name="Rationale / Use of Proceeds"/>
-    <x:tableColumn id="14" name="Score"/>
-    <x:tableColumn id="15" name="Evidence"/>
-    <x:tableColumn id="16" name="Coverage"/>
-    <x:tableColumn id="17" name="Source"/>
-    <x:tableColumn id="18" name="Source URL"/>
-    <x:tableColumn id="19" name="Headline"/>
-    <x:tableColumn id="20" name="Notes"/>
+    <x:tableColumn id="10" name="Enterprise Value"/>
+    <x:tableColumn id="11" name="Currency"/>
+    <x:tableColumn id="12" name="Stake %"/>
+    <x:tableColumn id="13" name="Payment Form"/>
+    <x:tableColumn id="14" name="Advisors"/>
+    <x:tableColumn id="15" name="Revenue LTM"/>
+    <x:tableColumn id="16" name="EBITDA LTM"/>
+    <x:tableColumn id="17" name="Financials As Of"/>
+    <x:tableColumn id="18" name="Financials Currency"/>
+    <x:tableColumn id="19" name="EV / Revenue"/>
+    <x:tableColumn id="20" name="EV / EBITDA"/>
+    <x:tableColumn id="21" name="Instrument"/>
+    <x:tableColumn id="22" name="Rationale / Use of Proceeds"/>
+    <x:tableColumn id="23" name="Score"/>
+    <x:tableColumn id="24" name="Evidence"/>
+    <x:tableColumn id="25" name="Coverage"/>
+    <x:tableColumn id="26" name="Source"/>
+    <x:tableColumn id="27" name="Source URL"/>
+    <x:tableColumn id="28" name="Headline"/>
+    <x:tableColumn id="29" name="Notes"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </x:table>
@@ -564,14 +549,14 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="15" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="24" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="17" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="25" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -588,7 +573,7 @@
     </x:row>
     <x:row r="2" ht="25" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Screening-grade database | As of 2026-06-27 | Verify primary documents before use</x:v>
+        <x:v>Screening-grade database | As of 2026-06-28 | N/M means insufficient disclosed data</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -610,69 +595,69 @@
       <x:c r="G4" s="9"/>
       <x:c r="H4" s="9"/>
     </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="29" t="str">
+    <x:row r="6" ht="32" customHeight="1">
+      <x:c r="A6" s="17" t="str">
         <x:v>Total deals</x:v>
       </x:c>
-      <x:c r="B6" s="30" t="str">
+      <x:c r="B6" s="18" t="str">
         <x:v>M&amp;A</x:v>
       </x:c>
-      <x:c r="C6" s="30" t="str">
+      <x:c r="C6" s="18" t="str">
         <x:v>ECM</x:v>
       </x:c>
-      <x:c r="D6" s="30" t="str">
+      <x:c r="D6" s="18" t="str">
         <x:v>DCM</x:v>
       </x:c>
-      <x:c r="E6" s="30" t="str">
+      <x:c r="E6" s="18" t="str">
         <x:v>Disclosed value</x:v>
       </x:c>
-      <x:c r="F6" s="30" t="str">
+      <x:c r="F6" s="18" t="str">
         <x:v>High score (≥7)</x:v>
       </x:c>
-      <x:c r="G6" s="30" t="str">
+      <x:c r="G6" s="18" t="str">
         <x:v>Missing value</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="19" t="str">
         <x:v>QA status</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="32" customHeight="1">
-      <x:c r="A7" s="32" t="n">
+      <x:c r="A7" s="28" t="n">
         <x:f>COUNTA('Precedent Transactions'!$A$7:$A$506)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B7" s="33" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B7" s="29" t="n">
         <x:f>COUNTIF('Precedent Transactions'!$C$7:$C$506,"M&amp;A")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C7" s="29" t="n">
         <x:f>COUNTIF('Precedent Transactions'!$C$7:$C$506,"ECM")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D7" s="33" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="29" t="n">
         <x:f>COUNTIF('Precedent Transactions'!$C$7:$C$506,"DCM")</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E7" s="34" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E7" s="31" t="n">
         <x:f>SUM('Precedent Transactions'!$I$7:$I$506)</x:f>
-        <x:v>5000000000</x:v>
-      </x:c>
-      <x:c r="F7" s="33" t="n">
-        <x:f>COUNTIF('Precedent Transactions'!$N$7:$N$506,"&gt;=7")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="33" t="n">
+        <x:v>252300000000</x:v>
+      </x:c>
+      <x:c r="F7" s="29" t="n">
+        <x:f>COUNTIF('Precedent Transactions'!$W$7:$W$506,"&gt;=7")</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G7" s="29" t="n">
         <x:f>COUNTBLANK('Precedent Transactions'!$I$7:$I$506)-COUNTBLANK('Precedent Transactions'!$A$7:$A$506)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="35" t="str">
-        <x:f>'Sources &amp; QA'!$F$29</x:f>
-        <x:v>OK</x:v>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="H7" s="30" t="str">
+        <x:f>'Sources &amp; QA'!$F$31</x:f>
+        <x:v>REVIEW</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="9" t="str">
-        <x:v>LATEST TRANSACTIONS</x:v>
+        <x:v>PRECEDENT VALUATION — VALID M&amp;A OBSERVATIONS ONLY</x:v>
       </x:c>
       <x:c r="B10" s="9"/>
       <x:c r="C10" s="9"/>
@@ -682,147 +667,321 @@
       <x:c r="G10" s="9"/>
       <x:c r="H10" s="9"/>
     </x:row>
-    <x:row r="12" ht="30" customHeight="1">
+    <x:row r="12" ht="32" customHeight="1">
       <x:c r="A12" s="17" t="str">
+        <x:v>Median EV / Revenue</x:v>
+      </x:c>
+      <x:c r="B12" s="18" t="str">
+        <x:v>Median EV / EBITDA</x:v>
+      </x:c>
+      <x:c r="C12" s="18" t="str">
+        <x:v>EV / Revenue coverage</x:v>
+      </x:c>
+      <x:c r="D12" s="19" t="str">
+        <x:v>EV / EBITDA coverage</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="32" customHeight="1">
+      <x:c r="A13" s="35" t="str">
+        <x:f>IFERROR(MEDIAN(FILTER('Precedent Transactions'!$S$7:$S$506,('Precedent Transactions'!$C$7:$C$506="M&amp;A")*('Precedent Transactions'!$S$7:$S$506&gt;0))),"N/M")</x:f>
+        <x:v>N/M</x:v>
+      </x:c>
+      <x:c r="B13" s="35" t="str">
+        <x:f>IFERROR(MEDIAN(FILTER('Precedent Transactions'!$T$7:$T$506,('Precedent Transactions'!$C$7:$C$506="M&amp;A")*('Precedent Transactions'!$T$7:$T$506&gt;0))),"N/M")</x:f>
+        <x:v>N/M</x:v>
+      </x:c>
+      <x:c r="C13" s="34" t="n">
+        <x:f>COUNTIFS('Precedent Transactions'!$C$7:$C$506,"M&amp;A",'Precedent Transactions'!$S$7:$S$506,"&gt;0")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="34" t="n">
+        <x:f>COUNTIFS('Precedent Transactions'!$C$7:$C$506,"M&amp;A",'Precedent Transactions'!$T$7:$T$506,"&gt;0")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16" s="9" t="str">
+        <x:v>LATEST TRANSACTIONS</x:v>
+      </x:c>
+      <x:c r="B16" s="9"/>
+      <x:c r="C16" s="9"/>
+      <x:c r="D16" s="9"/>
+      <x:c r="E16" s="9"/>
+      <x:c r="F16" s="9"/>
+      <x:c r="G16" s="9"/>
+      <x:c r="H16" s="9"/>
+    </x:row>
+    <x:row r="18" ht="32" customHeight="1">
+      <x:c r="A18" s="17" t="str">
         <x:v>Date</x:v>
       </x:c>
-      <x:c r="B12" s="18" t="str">
+      <x:c r="B18" s="18" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="C12" s="18" t="str">
+      <x:c r="C18" s="18" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="D12" s="18" t="str">
+      <x:c r="D18" s="18" t="str">
         <x:v>Target / Issuer</x:v>
       </x:c>
-      <x:c r="E12" s="18" t="str">
+      <x:c r="E18" s="18" t="str">
         <x:v>Acquirer</x:v>
       </x:c>
-      <x:c r="F12" s="18" t="str">
+      <x:c r="F18" s="18" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="G12" s="18" t="str">
+      <x:c r="G18" s="18" t="str">
         <x:v>Currency</x:v>
       </x:c>
-      <x:c r="H12" s="18" t="str">
+      <x:c r="H18" s="19" t="str">
         <x:v>Source</x:v>
       </x:c>
     </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="40" t="n">
+    <x:row r="19">
+      <x:c r="A19" s="36" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="C19" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="D19" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="E19" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="F19" s="37"/>
+      <x:c r="G19" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="36" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="D20" t="str">
+        <x:v>О регистрации проспекта биржевых облигаций</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="F20" s="37"/>
+      <x:c r="G20" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="36" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>О регистрации изменений в эмиссионные документы</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="F21" s="37"/>
+      <x:c r="G21" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="36" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="F22" s="37"/>
+      <x:c r="G22" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="36" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="C23" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="D23" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="E23" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="F23" s="37"/>
+      <x:c r="G23" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="H23" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="36" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="C24" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="D24" t="str">
+        <x:v>О проведении выкупа облигаций с 29 июня по 03 июля 2026 года</x:v>
+      </x:c>
+      <x:c r="E24" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="F24" s="37"/>
+      <x:c r="G24" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="H24" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="36" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="C25" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="D25" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="E25" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="F25" s="37"/>
+      <x:c r="G25" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="H25" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="36" t="n">
         <x:v>46197</x:v>
       </x:c>
-      <x:c r="B13" s="41" t="str">
+      <x:c r="B26" t="str">
         <x:v>DCM</x:v>
       </x:c>
-      <x:c r="C13" s="41" t="str">
+      <x:c r="C26" t="str">
         <x:v>Announced</x:v>
       </x:c>
-      <x:c r="D13" s="42" t="str">
+      <x:c r="D26" t="str">
         <x:v>Selectel</x:v>
       </x:c>
-      <x:c r="E13" s="42" t="str">
-        <x:v>Not applicable</x:v>
-      </x:c>
-      <x:c r="F13" s="43" t="n">
+      <x:c r="E26" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="F26" s="37" t="n">
         <x:v>5000000000</x:v>
       </x:c>
-      <x:c r="G13" s="42" t="str">
+      <x:c r="G26" t="str">
         <x:v>RUB</x:v>
       </x:c>
-      <x:c r="H13" s="42" t="str">
+      <x:c r="H26" t="str">
         <x:v>ComNews.ru</x:v>
       </x:c>
     </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="44"/>
-      <x:c r="B14" s="42"/>
-      <x:c r="C14" s="42"/>
-      <x:c r="D14" s="42"/>
-      <x:c r="E14" s="42"/>
-      <x:c r="F14" s="42"/>
-      <x:c r="G14" s="42"/>
-      <x:c r="H14" s="42"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="44"/>
-      <x:c r="B15" s="42"/>
-      <x:c r="C15" s="42"/>
-      <x:c r="D15" s="42"/>
-      <x:c r="E15" s="42"/>
-      <x:c r="F15" s="42"/>
-      <x:c r="G15" s="42"/>
-      <x:c r="H15" s="42"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="44"/>
-      <x:c r="B16" s="42"/>
-      <x:c r="C16" s="42"/>
-      <x:c r="D16" s="42"/>
-      <x:c r="E16" s="42"/>
-      <x:c r="F16" s="42"/>
-      <x:c r="G16" s="42"/>
-      <x:c r="H16" s="42"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="44"/>
-      <x:c r="B17" s="42"/>
-      <x:c r="C17" s="42"/>
-      <x:c r="D17" s="42"/>
-      <x:c r="E17" s="42"/>
-      <x:c r="F17" s="42"/>
-      <x:c r="G17" s="42"/>
-      <x:c r="H17" s="42"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="44"/>
-      <x:c r="B18" s="42"/>
-      <x:c r="C18" s="42"/>
-      <x:c r="D18" s="42"/>
-      <x:c r="E18" s="42"/>
-      <x:c r="F18" s="42"/>
-      <x:c r="G18" s="42"/>
-      <x:c r="H18" s="42"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="44"/>
-      <x:c r="B19" s="42"/>
-      <x:c r="C19" s="42"/>
-      <x:c r="D19" s="42"/>
-      <x:c r="E19" s="42"/>
-      <x:c r="F19" s="42"/>
-      <x:c r="G19" s="42"/>
-      <x:c r="H19" s="42"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="44"/>
-      <x:c r="B20" s="42"/>
-      <x:c r="C20" s="42"/>
-      <x:c r="D20" s="42"/>
-      <x:c r="E20" s="42"/>
-      <x:c r="F20" s="42"/>
-      <x:c r="G20" s="42"/>
-      <x:c r="H20" s="42"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="44"/>
-      <x:c r="B21" s="42"/>
-      <x:c r="C21" s="42"/>
-      <x:c r="D21" s="42"/>
-      <x:c r="E21" s="42"/>
-      <x:c r="F21" s="42"/>
-      <x:c r="G21" s="42"/>
-      <x:c r="H21" s="42"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="44"/>
-      <x:c r="B22" s="42"/>
-      <x:c r="C22" s="42"/>
-      <x:c r="D22" s="42"/>
-      <x:c r="E22" s="42"/>
-      <x:c r="F22" s="42"/>
-      <x:c r="G22" s="42"/>
-      <x:c r="H22" s="42"/>
+    <x:row r="27">
+      <x:c r="A27" s="36" t="n">
+        <x:v>46192</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>Issued</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>Yandex</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="F27" s="37" t="n">
+        <x:v>60000000000</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>Yandex Investor Relations</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="36" t="n">
+        <x:v>46183</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="C28" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="D28" t="str">
+        <x:v>Норникель</x:v>
+      </x:c>
+      <x:c r="E28" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="F28" s="37" t="n">
+        <x:v>3000000000</x:v>
+      </x:c>
+      <x:c r="G28" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="H28" t="str">
+        <x:v>Интерфакс</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -830,6 +989,7 @@
     <x:mergeCell ref="A2:H2"/>
     <x:mergeCell ref="A4:H4"/>
     <x:mergeCell ref="A10:H10"/>
+    <x:mergeCell ref="A16:H16"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -848,17 +1008,26 @@
     <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="16" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="10" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="11" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="22" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="34" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="9" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="13" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="14" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="20" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="42" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="52" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="44" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="11" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="30" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="16" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="14" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="14" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="22" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="34" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="9" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="13" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="14" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="22" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="42" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="52" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="44" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -884,10 +1053,19 @@
       <x:c r="R1" s="3"/>
       <x:c r="S1" s="3"/>
       <x:c r="T1" s="3"/>
+      <x:c r="U1" s="3"/>
+      <x:c r="V1" s="3"/>
+      <x:c r="W1" s="3"/>
+      <x:c r="X1" s="3"/>
+      <x:c r="Y1" s="3"/>
+      <x:c r="Z1" s="3"/>
+      <x:c r="AA1" s="3"/>
+      <x:c r="AB1" s="3"/>
+      <x:c r="AC1" s="3"/>
     </x:row>
     <x:row r="2" ht="25" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>One row per source-backed transaction signal; blank economics mean not publicly disclosed, not zero</x:v>
+        <x:v>Blank economics mean not publicly disclosed, not zero; valuation multiples require aligned EV and financial currencies</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -896,32 +1074,62 @@
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
       <x:c r="H2" s="6"/>
+      <x:c r="I2" s="6"/>
+      <x:c r="J2" s="6"/>
+      <x:c r="K2" s="6"/>
+      <x:c r="L2" s="6"/>
+      <x:c r="M2" s="6"/>
+      <x:c r="N2" s="6"/>
+      <x:c r="O2" s="6"/>
+      <x:c r="P2" s="6"/>
+      <x:c r="Q2" s="6"/>
+      <x:c r="R2" s="6"/>
+      <x:c r="S2" s="6"/>
+      <x:c r="T2" s="6"/>
+      <x:c r="U2" s="6"/>
+      <x:c r="V2" s="6"/>
+      <x:c r="W2" s="6"/>
+      <x:c r="X2" s="6"/>
+      <x:c r="Y2" s="6"/>
+      <x:c r="Z2" s="6"/>
+      <x:c r="AA2" s="6"/>
+      <x:c r="AB2" s="6"/>
+      <x:c r="AC2" s="6"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="47" t="str">
-        <x:v>Legend: source/imported fields in green text · calculated dashboard outputs in black · screening limitations highlighted in notes</x:v>
-      </x:c>
-      <x:c r="B4" s="47"/>
-      <x:c r="C4" s="47"/>
-      <x:c r="D4" s="47"/>
-      <x:c r="E4" s="47"/>
-      <x:c r="F4" s="47"/>
-      <x:c r="G4" s="47"/>
-      <x:c r="H4" s="47"/>
-      <x:c r="I4" s="47"/>
-      <x:c r="J4" s="47"/>
-      <x:c r="K4" s="47"/>
-      <x:c r="L4" s="47"/>
-      <x:c r="M4" s="47"/>
-      <x:c r="N4" s="47"/>
-      <x:c r="O4" s="47"/>
-      <x:c r="P4" s="47"/>
-      <x:c r="Q4" s="47"/>
-      <x:c r="R4" s="47"/>
-      <x:c r="S4" s="47"/>
-      <x:c r="T4" s="47"/>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A4" s="40" t="str">
+        <x:v>Green text = sourced/imported field · black formula cells = calculated output · verify primary transaction documents before use</x:v>
+      </x:c>
+      <x:c r="B4" s="40"/>
+      <x:c r="C4" s="40"/>
+      <x:c r="D4" s="40"/>
+      <x:c r="E4" s="40"/>
+      <x:c r="F4" s="40"/>
+      <x:c r="G4" s="40"/>
+      <x:c r="H4" s="40"/>
+      <x:c r="I4" s="40"/>
+      <x:c r="J4" s="40"/>
+      <x:c r="K4" s="40"/>
+      <x:c r="L4" s="40"/>
+      <x:c r="M4" s="40"/>
+      <x:c r="N4" s="40"/>
+      <x:c r="O4" s="40"/>
+      <x:c r="P4" s="40"/>
+      <x:c r="Q4" s="40"/>
+      <x:c r="R4" s="40"/>
+      <x:c r="S4" s="40"/>
+      <x:c r="T4" s="40"/>
+      <x:c r="U4" s="40"/>
+      <x:c r="V4" s="40"/>
+      <x:c r="W4" s="40"/>
+      <x:c r="X4" s="40"/>
+      <x:c r="Y4" s="40"/>
+      <x:c r="Z4" s="40"/>
+      <x:c r="AA4" s="40"/>
+      <x:c r="AB4" s="40"/>
+      <x:c r="AC4" s="40"/>
+    </x:row>
+    <x:row r="6" ht="32" customHeight="1">
       <x:c r="A6" s="17" t="str">
         <x:v>Deal ID</x:v>
       </x:c>
@@ -950,104 +1158,2992 @@
         <x:v>Transaction Value</x:v>
       </x:c>
       <x:c r="J6" s="18" t="str">
+        <x:v>Enterprise Value</x:v>
+      </x:c>
+      <x:c r="K6" s="18" t="str">
         <x:v>Currency</x:v>
       </x:c>
-      <x:c r="K6" s="18" t="str">
+      <x:c r="L6" s="18" t="str">
         <x:v>Stake %</x:v>
       </x:c>
-      <x:c r="L6" s="18" t="str">
+      <x:c r="M6" s="18" t="str">
+        <x:v>Payment Form</x:v>
+      </x:c>
+      <x:c r="N6" s="18" t="str">
+        <x:v>Advisors</x:v>
+      </x:c>
+      <x:c r="O6" s="18" t="str">
+        <x:v>Revenue LTM</x:v>
+      </x:c>
+      <x:c r="P6" s="18" t="str">
+        <x:v>EBITDA LTM</x:v>
+      </x:c>
+      <x:c r="Q6" s="18" t="str">
+        <x:v>Financials As Of</x:v>
+      </x:c>
+      <x:c r="R6" s="18" t="str">
+        <x:v>Financials Currency</x:v>
+      </x:c>
+      <x:c r="S6" s="18" t="str">
+        <x:v>EV / Revenue</x:v>
+      </x:c>
+      <x:c r="T6" s="18" t="str">
+        <x:v>EV / EBITDA</x:v>
+      </x:c>
+      <x:c r="U6" s="18" t="str">
         <x:v>Instrument</x:v>
       </x:c>
-      <x:c r="M6" s="18" t="str">
+      <x:c r="V6" s="18" t="str">
         <x:v>Rationale / Use of Proceeds</x:v>
       </x:c>
-      <x:c r="N6" s="18" t="str">
+      <x:c r="W6" s="18" t="str">
         <x:v>Score</x:v>
       </x:c>
-      <x:c r="O6" s="18" t="str">
+      <x:c r="X6" s="18" t="str">
         <x:v>Evidence</x:v>
       </x:c>
-      <x:c r="P6" s="18" t="str">
+      <x:c r="Y6" s="18" t="str">
         <x:v>Coverage</x:v>
       </x:c>
-      <x:c r="Q6" s="18" t="str">
+      <x:c r="Z6" s="18" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="R6" s="18" t="str">
+      <x:c r="AA6" s="18" t="str">
         <x:v>Source URL</x:v>
       </x:c>
-      <x:c r="S6" s="18" t="str">
+      <x:c r="AB6" s="18" t="str">
         <x:v>Headline</x:v>
       </x:c>
-      <x:c r="T6" s="19" t="str">
+      <x:c r="AC6" s="19" t="str">
         <x:v>Notes</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="48" t="str">
+      <x:c r="A7" s="41" t="str">
+        <x:v>DL-moex-101492</x:v>
+      </x:c>
+      <x:c r="B7" s="43" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="C7" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D7" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E7" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F7" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G7" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H7" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I7" s="44"/>
+      <x:c r="J7" s="44"/>
+      <x:c r="K7" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L7" s="45"/>
+      <x:c r="M7" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N7" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O7" s="44"/>
+      <x:c r="P7" s="44"/>
+      <x:c r="Q7" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R7" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S7" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J7&gt;0,$O7&gt;0,$K7=$R7),$J7/$O7,""),"")</x:f>
+      </x:c>
+      <x:c r="T7" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J7&gt;0,$P7&gt;0,$K7=$R7),$J7/$P7,""),"")</x:f>
+      </x:c>
+      <x:c r="U7" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V7" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W7" s="41" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="X7" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y7" s="41" t="str"/>
+      <x:c r="Z7" s="41" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+      <x:c r="AA7" s="41" t="str">
+        <x:v>https://www.moex.com/n101492</x:v>
+      </x:c>
+      <x:c r="AB7" s="41" t="str">
+        <x:v>О регистрации выпуска биржевых облигаций, о включении его в Список ценных бумаг, допущенных к торгам, и о присвоении указанным биржевым облигациям регистрационного номера</x:v>
+      </x:c>
+      <x:c r="AC7" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="41" t="str">
+        <x:v>DL-moex-101473</x:v>
+      </x:c>
+      <x:c r="B8" s="43" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="C8" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D8" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E8" s="41" t="str">
+        <x:v>О регистрации проспекта биржевых облигаций</x:v>
+      </x:c>
+      <x:c r="F8" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G8" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H8" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I8" s="44"/>
+      <x:c r="J8" s="44"/>
+      <x:c r="K8" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L8" s="45"/>
+      <x:c r="M8" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N8" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O8" s="44"/>
+      <x:c r="P8" s="44"/>
+      <x:c r="Q8" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R8" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S8" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J8&gt;0,$O8&gt;0,$K8=$R8),$J8/$O8,""),"")</x:f>
+      </x:c>
+      <x:c r="T8" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J8&gt;0,$P8&gt;0,$K8=$R8),$J8/$P8,""),"")</x:f>
+      </x:c>
+      <x:c r="U8" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V8" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W8" s="41" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="X8" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y8" s="41" t="str"/>
+      <x:c r="Z8" s="41" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+      <x:c r="AA8" s="41" t="str">
+        <x:v>https://www.moex.com/n101473</x:v>
+      </x:c>
+      <x:c r="AB8" s="41" t="str">
+        <x:v>О регистрации проспекта биржевых облигаций</x:v>
+      </x:c>
+      <x:c r="AC8" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="41" t="str">
+        <x:v>DL-moex-101468</x:v>
+      </x:c>
+      <x:c r="B9" s="43" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="C9" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D9" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E9" s="41" t="str">
+        <x:v>О регистрации изменений в эмиссионные документы</x:v>
+      </x:c>
+      <x:c r="F9" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G9" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H9" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I9" s="44"/>
+      <x:c r="J9" s="44"/>
+      <x:c r="K9" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L9" s="45"/>
+      <x:c r="M9" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N9" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O9" s="44"/>
+      <x:c r="P9" s="44"/>
+      <x:c r="Q9" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R9" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S9" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J9&gt;0,$O9&gt;0,$K9=$R9),$J9/$O9,""),"")</x:f>
+      </x:c>
+      <x:c r="T9" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J9&gt;0,$P9&gt;0,$K9=$R9),$J9/$P9,""),"")</x:f>
+      </x:c>
+      <x:c r="U9" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V9" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W9" s="41" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="X9" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y9" s="41" t="str"/>
+      <x:c r="Z9" s="41" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+      <x:c r="AA9" s="41" t="str">
+        <x:v>https://www.moex.com/n101468</x:v>
+      </x:c>
+      <x:c r="AB9" s="41" t="str">
+        <x:v>О регистрации изменений в эмиссионные документы</x:v>
+      </x:c>
+      <x:c r="AC9" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="41" t="str">
+        <x:v>DL-moex-101457</x:v>
+      </x:c>
+      <x:c r="B10" s="43" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="C10" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D10" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E10" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F10" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G10" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H10" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I10" s="44"/>
+      <x:c r="J10" s="44"/>
+      <x:c r="K10" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L10" s="45"/>
+      <x:c r="M10" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N10" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O10" s="44"/>
+      <x:c r="P10" s="44"/>
+      <x:c r="Q10" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R10" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S10" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J10&gt;0,$O10&gt;0,$K10=$R10),$J10/$O10,""),"")</x:f>
+      </x:c>
+      <x:c r="T10" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J10&gt;0,$P10&gt;0,$K10=$R10),$J10/$P10,""),"")</x:f>
+      </x:c>
+      <x:c r="U10" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V10" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W10" s="41" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="X10" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y10" s="41" t="str"/>
+      <x:c r="Z10" s="41" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+      <x:c r="AA10" s="41" t="str">
+        <x:v>https://www.moex.com/n101457</x:v>
+      </x:c>
+      <x:c r="AB10" s="41" t="str">
+        <x:v>О порядке сбора заявок и заключения сделок при размещении облигаций серии Б-1-403 Банк ВТБ (публичное акционерное общество) с 29 июня 2026 года</x:v>
+      </x:c>
+      <x:c r="AC10" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="41" t="str">
+        <x:v>DL-moex-101454</x:v>
+      </x:c>
+      <x:c r="B11" s="43" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="C11" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D11" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E11" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F11" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G11" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H11" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I11" s="44"/>
+      <x:c r="J11" s="44"/>
+      <x:c r="K11" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L11" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M11" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N11" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O11" s="44"/>
+      <x:c r="P11" s="44"/>
+      <x:c r="Q11" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R11" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S11" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J11&gt;0,$O11&gt;0,$K11=$R11),$J11/$O11,""),"")</x:f>
+      </x:c>
+      <x:c r="T11" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J11&gt;0,$P11&gt;0,$K11=$R11),$J11/$P11,""),"")</x:f>
+      </x:c>
+      <x:c r="U11" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V11" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W11" s="41" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="X11" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y11" s="41" t="str"/>
+      <x:c r="Z11" s="41" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+      <x:c r="AA11" s="41" t="str">
+        <x:v>https://www.moex.com/n101454</x:v>
+      </x:c>
+      <x:c r="AB11" s="41" t="str">
+        <x:v>О порядке приобретения облигаций серии 001P-04 ООО "АРЕНЗА-ПРО" с 29 июня 2026 год</x:v>
+      </x:c>
+      <x:c r="AC11" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="41" t="str">
+        <x:v>DL-moex-101451</x:v>
+      </x:c>
+      <x:c r="B12" s="43" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="C12" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D12" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E12" s="41" t="str">
+        <x:v>О проведении выкупа облигаций с 29 июня по 03 июля 2026 года</x:v>
+      </x:c>
+      <x:c r="F12" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G12" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H12" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I12" s="44"/>
+      <x:c r="J12" s="44"/>
+      <x:c r="K12" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L12" s="45"/>
+      <x:c r="M12" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N12" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O12" s="44"/>
+      <x:c r="P12" s="44"/>
+      <x:c r="Q12" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R12" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S12" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J12&gt;0,$O12&gt;0,$K12=$R12),$J12/$O12,""),"")</x:f>
+      </x:c>
+      <x:c r="T12" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J12&gt;0,$P12&gt;0,$K12=$R12),$J12/$P12,""),"")</x:f>
+      </x:c>
+      <x:c r="U12" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V12" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W12" s="41" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="X12" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y12" s="41" t="str"/>
+      <x:c r="Z12" s="41" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+      <x:c r="AA12" s="41" t="str">
+        <x:v>https://www.moex.com/n101451</x:v>
+      </x:c>
+      <x:c r="AB12" s="41" t="str">
+        <x:v>О проведении выкупа облигаций с 29 июня по 03 июля 2026 года</x:v>
+      </x:c>
+      <x:c r="AC12" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="41" t="str">
+        <x:v>DL-moex-101450</x:v>
+      </x:c>
+      <x:c r="B13" s="43" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="C13" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D13" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E13" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F13" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G13" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H13" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I13" s="44"/>
+      <x:c r="J13" s="44"/>
+      <x:c r="K13" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L13" s="45"/>
+      <x:c r="M13" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N13" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O13" s="44"/>
+      <x:c r="P13" s="44"/>
+      <x:c r="Q13" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R13" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S13" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J13&gt;0,$O13&gt;0,$K13=$R13),$J13/$O13,""),"")</x:f>
+      </x:c>
+      <x:c r="T13" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J13&gt;0,$P13&gt;0,$K13=$R13),$J13/$P13,""),"")</x:f>
+      </x:c>
+      <x:c r="U13" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V13" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W13" s="41" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="X13" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y13" s="41" t="str"/>
+      <x:c r="Z13" s="41" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+      <x:c r="AA13" s="41" t="str">
+        <x:v>https://www.moex.com/n101450</x:v>
+      </x:c>
+      <x:c r="AB13" s="41" t="str">
+        <x:v>Дополнительные условия проведения торгов по выкупу облигаций серии 003Р-02 ООО "Концерн "РОССИУМ" 26 июня 2026 года</x:v>
+      </x:c>
+      <x:c r="AC13" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="41" t="str">
         <x:v>DL-bec65812ff9fcfae</x:v>
       </x:c>
-      <x:c r="B7" s="49" t="n">
+      <x:c r="B14" s="43" t="n">
         <x:v>46197</x:v>
       </x:c>
-      <x:c r="C7" s="48" t="str">
+      <x:c r="C14" s="41" t="str">
         <x:v>DCM</x:v>
       </x:c>
-      <x:c r="D7" s="48" t="str">
+      <x:c r="D14" s="41" t="str">
         <x:v>Announced</x:v>
       </x:c>
-      <x:c r="E7" s="48" t="str">
+      <x:c r="E14" s="41" t="str">
         <x:v>Selectel</x:v>
       </x:c>
-      <x:c r="F7" s="48" t="str">
-        <x:v>Not applicable</x:v>
-      </x:c>
-      <x:c r="G7" s="48" t="str">
+      <x:c r="F14" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G14" s="41" t="str">
         <x:v>Not classified</x:v>
       </x:c>
-      <x:c r="H7" s="48" t="str">
+      <x:c r="H14" s="41" t="str">
         <x:v>Russia</x:v>
       </x:c>
-      <x:c r="I7" s="50" t="n">
+      <x:c r="I14" s="44" t="n">
         <x:v>5000000000</x:v>
       </x:c>
-      <x:c r="J7" s="48" t="str">
+      <x:c r="J14" s="44"/>
+      <x:c r="K14" s="41" t="str">
         <x:v>RUB</x:v>
       </x:c>
-      <x:c r="K7" s="51"/>
-      <x:c r="L7" s="48" t="str">
+      <x:c r="L14" s="45"/>
+      <x:c r="M14" s="41"/>
+      <x:c r="N14" s="41"/>
+      <x:c r="O14" s="44"/>
+      <x:c r="P14" s="44"/>
+      <x:c r="Q14" s="41"/>
+      <x:c r="R14" s="41"/>
+      <x:c r="S14" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J14&gt;0,$O14&gt;0,$K14=$R14),$J14/$O14,""),"")</x:f>
+      </x:c>
+      <x:c r="T14" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J14&gt;0,$P14&gt;0,$K14=$R14),$J14/$P14,""),"")</x:f>
+      </x:c>
+      <x:c r="U14" s="41" t="str">
         <x:v>Bonds</x:v>
       </x:c>
-      <x:c r="M7" s="52" t="str">
+      <x:c r="V14" s="41" t="str">
         <x:v>рефинансирования и инвестиций</x:v>
       </x:c>
-      <x:c r="N7" s="48" t="n">
+      <x:c r="W14" s="41" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="O7" s="48" t="str">
+      <x:c r="X14" s="41" t="str">
         <x:v>unverified</x:v>
       </x:c>
-      <x:c r="P7" s="48" t="str"/>
-      <x:c r="Q7" s="48" t="str">
+      <x:c r="Y14" s="41" t="str"/>
+      <x:c r="Z14" s="41" t="str">
         <x:v>ComNews.ru</x:v>
       </x:c>
-      <x:c r="R7" s="48" t="str">
+      <x:c r="AA14" s="41" t="str">
         <x:v>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZ0FzQTE1TUJkMGFCVjZuNTBGY0JwNTZBaS16Wnl0NW9XSXBmNFlTRUJacXFlV0tYdUxpUTZTWVhNWk4wYll4a3dZZEU2ZFYzZ2d6T2YwUl85bGlXZGRpN3NiTXJwcnExdzBVVkx6YWV1eExnOFJlcmlDb21UTG5KQWozVTNhX0VwNDVmdnFYTEQwcFpENjdHMjhEX01fTERSUHpsNkE2a3FESkdwbzEzbGRsXzB6MWFlVW80Ri1fa0JYdDVKNEhMZml2WmtiSWYyV2tuZA?oc=5</x:v>
       </x:c>
-      <x:c r="S7" s="52" t="str">
+      <x:c r="AB14" s="41" t="str">
         <x:v>Selectel разместит облигации на 5 млрд руб. для рефинансирования и инвестиций - ComNews.ru</x:v>
       </x:c>
-      <x:c r="T7" s="52" t="str">
+      <x:c r="AC14" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="41" t="str">
+        <x:v>DL-48bd4fc3fa031e6c</x:v>
+      </x:c>
+      <x:c r="B15" s="43" t="n">
+        <x:v>46192</x:v>
+      </x:c>
+      <x:c r="C15" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D15" s="41" t="str">
+        <x:v>Issued</x:v>
+      </x:c>
+      <x:c r="E15" s="41" t="str">
+        <x:v>Yandex</x:v>
+      </x:c>
+      <x:c r="F15" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G15" s="41" t="str">
+        <x:v>Technology</x:v>
+      </x:c>
+      <x:c r="H15" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I15" s="44" t="n">
+        <x:v>60000000000</x:v>
+      </x:c>
+      <x:c r="J15" s="44"/>
+      <x:c r="K15" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L15" s="45"/>
+      <x:c r="M15" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N15" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O15" s="44"/>
+      <x:c r="P15" s="44"/>
+      <x:c r="Q15" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R15" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S15" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J15&gt;0,$O15&gt;0,$K15=$R15),$J15/$O15,""),"")</x:f>
+      </x:c>
+      <x:c r="T15" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J15&gt;0,$P15&gt;0,$K15=$R15),$J15/$P15,""),"")</x:f>
+      </x:c>
+      <x:c r="U15" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V15" s="41" t="str">
+        <x:v>частных инвесторов Яндекса содержит информацию про бизнесы и технологии компании, а также географию присутствия, финансовые результаты, важные новости и многое другое о компании и её рынках</x:v>
+      </x:c>
+      <x:c r="W15" s="41" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="X15" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y15" s="41" t="str">
+        <x:v>YDEX</x:v>
+      </x:c>
+      <x:c r="Z15" s="41" t="str">
+        <x:v>Yandex Investor Relations</x:v>
+      </x:c>
+      <x:c r="AA15" s="41" t="str">
+        <x:v>https://ir.yandex.ru/press-releases?year=2026&amp;id=19-06-2026-03</x:v>
+      </x:c>
+      <x:c r="AB15" s="41" t="str">
+        <x:v>Яндекс разместил два выпуска биржевых облигаций на общую сумму 60 млрд рублей</x:v>
+      </x:c>
+      <x:c r="AC15" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="41" t="str">
+        <x:v>DL-9092ffd6a36a0a81</x:v>
+      </x:c>
+      <x:c r="B16" s="43" t="n">
+        <x:v>46183</x:v>
+      </x:c>
+      <x:c r="C16" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D16" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E16" s="41" t="str">
+        <x:v>Норникель</x:v>
+      </x:c>
+      <x:c r="F16" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G16" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H16" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I16" s="44" t="n">
+        <x:v>3000000000</x:v>
+      </x:c>
+      <x:c r="J16" s="44"/>
+      <x:c r="K16" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L16" s="45"/>
+      <x:c r="M16" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N16" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O16" s="44"/>
+      <x:c r="P16" s="44"/>
+      <x:c r="Q16" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R16" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S16" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J16&gt;0,$O16&gt;0,$K16=$R16),$J16/$O16,""),"")</x:f>
+      </x:c>
+      <x:c r="T16" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J16&gt;0,$P16&gt;0,$K16=$R16),$J16/$P16,""),"")</x:f>
+      </x:c>
+      <x:c r="U16" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V16" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W16" s="41" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="X16" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y16" s="41" t="str"/>
+      <x:c r="Z16" s="41" t="str">
+        <x:v>Интерфакс</x:v>
+      </x:c>
+      <x:c r="AA16" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1YcWRJT1pJS3JQYUlDcVBxQmRrd2JFXzdidEJQMkRoTFVIRlBDUnQ5ZjNSMFZGamhRQ1hoTXFwaUVQMW1PZldFWWhvSzdOdmtSQnfSAUtBVV95cUxQWkQ5UHd5NFJieHBKUTVCZURpX1dEWmM4a2FnOXJ3aUREYi04ZGFUclFMNUxBdU1EMFVYWUU4MlhCaXJfTy1NZlVNXzg?oc=5</x:v>
+      </x:c>
+      <x:c r="AB16" s="41" t="str">
+        <x:v>"Норникель" зафиксировал объем размещения облигаций на уровне 3 млрд юаней - Интерфакс</x:v>
+      </x:c>
+      <x:c r="AC16" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="41" t="str">
+        <x:v>DL-f71ff729dc9f5af4</x:v>
+      </x:c>
+      <x:c r="B17" s="43" t="n">
+        <x:v>46181</x:v>
+      </x:c>
+      <x:c r="C17" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D17" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E17" s="41" t="str">
+        <x:v>Yandex</x:v>
+      </x:c>
+      <x:c r="F17" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G17" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H17" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I17" s="44"/>
+      <x:c r="J17" s="44"/>
+      <x:c r="K17" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L17" s="45"/>
+      <x:c r="M17" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N17" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O17" s="44"/>
+      <x:c r="P17" s="44"/>
+      <x:c r="Q17" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R17" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S17" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J17&gt;0,$O17&gt;0,$K17=$R17),$J17/$O17,""),"")</x:f>
+      </x:c>
+      <x:c r="T17" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J17&gt;0,$P17&gt;0,$K17=$R17),$J17/$P17,""),"")</x:f>
+      </x:c>
+      <x:c r="U17" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V17" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W17" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X17" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y17" s="41" t="str">
+        <x:v>YDEX</x:v>
+      </x:c>
+      <x:c r="Z17" s="41" t="str">
+        <x:v>Финам</x:v>
+      </x:c>
+      <x:c r="AA17" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOSmlOMWRURDFvUlZqYktKazJXOFhWR1ZMamNuTGF2QlJ0YmIxTmF6RDMtSHF1Y2RTRkc5QWlnZXQ3WUdUMTB4QUNzUy0zT3I2eGJZSW1DWUxaVDlvR1lrNVhZZ3kybDNrb0tXd0FqMkxHQXNWRFhjcFp0MUI3alRKN1BWdlBSN2V2VWphOUxBQkNjc0l1UDF4WTRKZXkxNHlzSmhIRkhmR2pXc1pKLVV4MzJIN0pLZlVkQ3JvZ2d4aFphcXJkd0F3Z1VKYmdPUUdJ?oc=5</x:v>
+      </x:c>
+      <x:c r="AB17" s="41" t="str">
+        <x:v>«Яндекс» вновь выходит на долговой рынок: разбор двойного размещения облигаций - Финам</x:v>
+      </x:c>
+      <x:c r="AC17" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="41" t="str">
+        <x:v>DL-c0e4b0469b5eb473</x:v>
+      </x:c>
+      <x:c r="B18" s="43" t="n">
+        <x:v>46177</x:v>
+      </x:c>
+      <x:c r="C18" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D18" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E18" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F18" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="G18" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H18" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I18" s="44"/>
+      <x:c r="J18" s="44"/>
+      <x:c r="K18" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L18" s="45"/>
+      <x:c r="M18" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="N18" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O18" s="44"/>
+      <x:c r="P18" s="44"/>
+      <x:c r="Q18" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R18" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S18" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J18&gt;0,$O18&gt;0,$K18=$R18),$J18/$O18,""),"")</x:f>
+      </x:c>
+      <x:c r="T18" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J18&gt;0,$P18&gt;0,$K18=$R18),$J18/$P18,""),"")</x:f>
+      </x:c>
+      <x:c r="U18" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V18" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W18" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X18" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y18" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z18" s="41" t="str">
+        <x:v>БКС Экспресс</x:v>
+      </x:c>
+      <x:c r="AA18" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMioAFBVV95cUxQM0RKYTRnLW8xX0tVdnh1S3RBQ25IUTNrRGtWSTRudTJVU3A3UXpmZjZCR2ItX2NQNmN1aXdPYUpDN0paWHBfUjBNd2xrWWl6Mk9Zel9MREpqcXl1RUpoUXB2MWNPdFBoYV94Mm0zNkVtcVZFM050R2Jqc2ZKQVdlbkVhVmhuNXZpQWd5STAzOW9fYndtQTBpM0JLTWJmMjlq?oc=5</x:v>
+      </x:c>
+      <x:c r="AB18" s="41" t="str">
+        <x:v>Греф опроверг договоренность Сбера о покупке доли в Озоне - БКС Экспресс</x:v>
+      </x:c>
+      <x:c r="AC18" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="41" t="str">
+        <x:v>DL-2e27ebc506e38656</x:v>
+      </x:c>
+      <x:c r="B19" s="43" t="n">
+        <x:v>46176</x:v>
+      </x:c>
+      <x:c r="C19" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D19" s="41" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="E19" s="41" t="str">
+        <x:v>Авто.ру</x:v>
+      </x:c>
+      <x:c r="F19" s="41" t="str">
+        <x:v>Т-Технологии</x:v>
+      </x:c>
+      <x:c r="G19" s="41" t="str">
+        <x:v>Technology</x:v>
+      </x:c>
+      <x:c r="H19" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I19" s="44"/>
+      <x:c r="J19" s="44"/>
+      <x:c r="K19" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L19" s="45"/>
+      <x:c r="M19" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="N19" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O19" s="44"/>
+      <x:c r="P19" s="44"/>
+      <x:c r="Q19" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R19" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S19" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J19&gt;0,$O19&gt;0,$K19=$R19),$J19/$O19,""),"")</x:f>
+      </x:c>
+      <x:c r="T19" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J19&gt;0,$P19&gt;0,$K19=$R19),$J19/$P19,""),"")</x:f>
+      </x:c>
+      <x:c r="U19" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V19" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W19" s="41" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="X19" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y19" s="41" t="str">
+        <x:v>YDEX</x:v>
+      </x:c>
+      <x:c r="Z19" s="41" t="str">
+        <x:v>БКС Экспресс</x:v>
+      </x:c>
+      <x:c r="AA19" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMiowFBVV95cUxNQ0ZvSEhWU1BqUzkyWi1YOWNOR0lab1kxRldxMFV5YllQQWp4Y0xFcjNLTXpHMUFJcnhicWI2RGNuUWRpUndBS0ZlQ2U0c05yWDlTeWZnWG05QjhZR0VWVW5IV19aSkdwa0d1UWpMWC1tLWdicjNtUVk4M2QtbFhsQkFxejdjZ2lLNDYxWTlwUWwyMzhqZ20zelY5SkZpZjBjYzZv?oc=5</x:v>
+      </x:c>
+      <x:c r="AB19" s="41" t="str">
+        <x:v>Т-Технологии закрыли сделку по покупке Авто.ру у Яндекса - БКС Экспресс</x:v>
+      </x:c>
+      <x:c r="AC19" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="41" t="str">
+        <x:v>DL-360af9a222272dcf</x:v>
+      </x:c>
+      <x:c r="B20" s="43" t="n">
+        <x:v>46175</x:v>
+      </x:c>
+      <x:c r="C20" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D20" s="41" t="str">
+        <x:v>Completed</x:v>
+      </x:c>
+      <x:c r="E20" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F20" s="41" t="str">
+        <x:v>Yandex</x:v>
+      </x:c>
+      <x:c r="G20" s="41" t="str">
+        <x:v>Technology</x:v>
+      </x:c>
+      <x:c r="H20" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I20" s="44"/>
+      <x:c r="J20" s="44"/>
+      <x:c r="K20" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L20" s="45"/>
+      <x:c r="M20" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="N20" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O20" s="44"/>
+      <x:c r="P20" s="44"/>
+      <x:c r="Q20" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R20" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S20" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J20&gt;0,$O20&gt;0,$K20=$R20),$J20/$O20,""),"")</x:f>
+      </x:c>
+      <x:c r="T20" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J20&gt;0,$P20&gt;0,$K20=$R20),$J20/$P20,""),"")</x:f>
+      </x:c>
+      <x:c r="U20" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V20" s="41" t="str">
+        <x:v>частных инвесторов Яндекса содержит информацию про бизнесы и технологии компании, а также географию присутствия, финансовые результаты, важные новости и многое другое о компании и её рынках</x:v>
+      </x:c>
+      <x:c r="W20" s="41" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="X20" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y20" s="41" t="str">
+        <x:v>YDEX</x:v>
+      </x:c>
+      <x:c r="Z20" s="41" t="str">
+        <x:v>Yandex Investor Relations</x:v>
+      </x:c>
+      <x:c r="AA20" s="41" t="str">
+        <x:v>https://ir.yandex.ru/press-releases?year=2026&amp;id=02-06-2026-04</x:v>
+      </x:c>
+      <x:c r="AB20" s="41" t="str">
+        <x:v>Яндекс закрыл сделку по продаже Авто.ру</x:v>
+      </x:c>
+      <x:c r="AC20" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="41" t="str">
+        <x:v>DL-a78cf0af94927306</x:v>
+      </x:c>
+      <x:c r="B21" s="43" t="n">
+        <x:v>46175</x:v>
+      </x:c>
+      <x:c r="C21" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D21" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E21" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F21" s="41" t="str">
+        <x:v>Yandex</x:v>
+      </x:c>
+      <x:c r="G21" s="41" t="str">
+        <x:v>Technology</x:v>
+      </x:c>
+      <x:c r="H21" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I21" s="44" t="n">
+        <x:v>35000000000</x:v>
+      </x:c>
+      <x:c r="J21" s="44"/>
+      <x:c r="K21" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L21" s="45"/>
+      <x:c r="M21" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="N21" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O21" s="44"/>
+      <x:c r="P21" s="44"/>
+      <x:c r="Q21" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R21" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S21" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J21&gt;0,$O21&gt;0,$K21=$R21),$J21/$O21,""),"")</x:f>
+      </x:c>
+      <x:c r="T21" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J21&gt;0,$P21&gt;0,$K21=$R21),$J21/$P21,""),"")</x:f>
+      </x:c>
+      <x:c r="U21" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V21" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W21" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X21" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y21" s="41" t="str">
+        <x:v>YDEX</x:v>
+      </x:c>
+      <x:c r="Z21" s="41" t="str">
+        <x:v>Финам</x:v>
+      </x:c>
+      <x:c r="AA21" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMilgFBVV95cUxQWFk5YjhpaHc0S3BiTEpUVzFndHdkTDVmY0EtRDhFQ0pYcjBvWUF3V3FZUFhaUjhEQ1FXT0FDdWU1dGdtVmJ1Z1l5bmhGcVBwdjhsWTZVNG10dWhmTlNGbGZqV2cwRUoyaEdZS3c0dEx1MV8ySGpfX2ljQnhfemFELThnSDc3T09JZ1lOZW45Yk93YmYyb3c?oc=5</x:v>
+      </x:c>
+      <x:c r="AB21" s="41" t="str">
+        <x:v>"Яндекс" продал "Авто.ру" "Т-Технологиям" за 35 млрд рублей - Финам</x:v>
+      </x:c>
+      <x:c r="AC21" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="41" t="str">
+        <x:v>DL-a4f6a4524ddca358</x:v>
+      </x:c>
+      <x:c r="B22" s="43" t="n">
+        <x:v>46170</x:v>
+      </x:c>
+      <x:c r="C22" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D22" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E22" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F22" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="G22" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H22" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I22" s="44"/>
+      <x:c r="J22" s="44"/>
+      <x:c r="K22" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L22" s="45"/>
+      <x:c r="M22" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="N22" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O22" s="44"/>
+      <x:c r="P22" s="44"/>
+      <x:c r="Q22" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R22" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S22" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J22&gt;0,$O22&gt;0,$K22=$R22),$J22/$O22,""),"")</x:f>
+      </x:c>
+      <x:c r="T22" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J22&gt;0,$P22&gt;0,$K22=$R22),$J22/$P22,""),"")</x:f>
+      </x:c>
+      <x:c r="U22" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V22" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W22" s="41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="X22" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y22" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z22" s="41" t="str">
+        <x:v>Интерфакс</x:v>
+      </x:c>
+      <x:c r="AA22" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE9GMUxsS2ZKR2JaU2ZhY1hRSmoteVVNM1V6U2pJQnFGblRETXk1b0pLLXl3VXNvREgwdVg4dmNyc3VBVWxFZ1ZjUmxILXlrWU80VVHSAUtBVV95cUxPM21YSmF3aGRJQThYblp1MEEyNGNLSnR0SzlnTG1ITWtJWXY5bU1Jdm9kWU5nRjRYOUoxRlFscTB5X2NHVUlWYmtDX0k?oc=5</x:v>
+      </x:c>
+      <x:c r="AB22" s="41" t="str">
+        <x:v>"Ъ" сообщил о переговорах структур Сбера с АФК "Система" о покупке доли в Ozon - Интерфакс</x:v>
+      </x:c>
+      <x:c r="AC22" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="41" t="str">
+        <x:v>DL-e08040bba3b952c1</x:v>
+      </x:c>
+      <x:c r="B23" s="43" t="n">
+        <x:v>46170</x:v>
+      </x:c>
+      <x:c r="C23" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D23" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E23" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F23" s="41" t="str">
+        <x:v>Yandex</x:v>
+      </x:c>
+      <x:c r="G23" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H23" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I23" s="44"/>
+      <x:c r="J23" s="44"/>
+      <x:c r="K23" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L23" s="45"/>
+      <x:c r="M23" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="N23" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O23" s="44"/>
+      <x:c r="P23" s="44"/>
+      <x:c r="Q23" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R23" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S23" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J23&gt;0,$O23&gt;0,$K23=$R23),$J23/$O23,""),"")</x:f>
+      </x:c>
+      <x:c r="T23" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J23&gt;0,$P23&gt;0,$K23=$R23),$J23/$P23,""),"")</x:f>
+      </x:c>
+      <x:c r="U23" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V23" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W23" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X23" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y23" s="41" t="str">
+        <x:v>YDEX</x:v>
+      </x:c>
+      <x:c r="Z23" s="41" t="str">
+        <x:v>Финам</x:v>
+      </x:c>
+      <x:c r="AA23" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSlk2WU9xYjNqM1AwRkNGOV9BYnhzQVg3VlRaaWJlT01VVDNrYklwUjY4SFZfdjZQLVlHZEpxYm0tVmpDUFN5a190bUU0MnFnb2VFMFMyQ2E1OWlyQ2djRWwtdWMyN3F5NXRYamZkUmFhMkk4UlFZQXFDOVB2RE9uNjZkdFFMbGZFT0dWOTN4MjZDbXZmMzNSOUNlOXVaZjJGcmM4QnZiM0I3QUhM?oc=5</x:v>
+      </x:c>
+      <x:c r="AB23" s="41" t="str">
+        <x:v>"Яндекс" стал основным претендентом на покупку "Островка" - Финам</x:v>
+      </x:c>
+      <x:c r="AC23" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="41" t="str">
+        <x:v>DL-4ffd21b67b0042b7</x:v>
+      </x:c>
+      <x:c r="B24" s="43" t="n">
+        <x:v>46170</x:v>
+      </x:c>
+      <x:c r="C24" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D24" s="41" t="str">
+        <x:v>Potential</x:v>
+      </x:c>
+      <x:c r="E24" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F24" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="G24" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H24" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I24" s="44" t="n">
+        <x:v>30000000000</x:v>
+      </x:c>
+      <x:c r="J24" s="44"/>
+      <x:c r="K24" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L24" s="45"/>
+      <x:c r="M24" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="N24" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O24" s="44"/>
+      <x:c r="P24" s="44"/>
+      <x:c r="Q24" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R24" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S24" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J24&gt;0,$O24&gt;0,$K24=$R24),$J24/$O24,""),"")</x:f>
+      </x:c>
+      <x:c r="T24" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J24&gt;0,$P24&gt;0,$K24=$R24),$J24/$P24,""),"")</x:f>
+      </x:c>
+      <x:c r="U24" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V24" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W24" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X24" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y24" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z24" s="41" t="str">
+        <x:v>RB.ru</x:v>
+      </x:c>
+      <x:c r="AA24" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMixAFBVV95cUxOZGNTQll0aVZOSDFubmt0bU5BdWNXNVA0WFZaOFdKa3B1VkctYXdkU25tLVdQSlNjNjFBYzA0ZzFYbVZKRnNKMk9Cb3RkSFYtaVFUR0JVc0pMNkNFUnFaeUdJX1JKRWlqMUZKeHo3UTZNaDU3LUc2RWxDd2FMYTUyUTEtY1dhcHFUVlJ4ZDlDS19SVkF5a0tqS0duRkljSWNNN0NLajJrSDZVdDNNR2ZfNVlyTVBvb0xFOXdFYmtpb2ZjTXRi?oc=5</x:v>
+      </x:c>
+      <x:c r="AB24" s="41" t="str">
+        <x:v>Сбер может купить долю инвесткомпании АФК «Система» в Ozon за 30 млрд рублей - RB.ru</x:v>
+      </x:c>
+      <x:c r="AC24" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="41" t="str">
+        <x:v>DL-ca53a880a58471a3</x:v>
+      </x:c>
+      <x:c r="B25" s="43" t="n">
+        <x:v>46170</x:v>
+      </x:c>
+      <x:c r="C25" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D25" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E25" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F25" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="G25" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H25" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I25" s="44"/>
+      <x:c r="J25" s="44"/>
+      <x:c r="K25" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L25" s="45"/>
+      <x:c r="M25" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="N25" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O25" s="44"/>
+      <x:c r="P25" s="44"/>
+      <x:c r="Q25" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R25" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S25" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J25&gt;0,$O25&gt;0,$K25=$R25),$J25/$O25,""),"")</x:f>
+      </x:c>
+      <x:c r="T25" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J25&gt;0,$P25&gt;0,$K25=$R25),$J25/$P25,""),"")</x:f>
+      </x:c>
+      <x:c r="U25" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V25" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W25" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X25" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y25" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z25" s="41" t="str">
+        <x:v>Альфа-Банк</x:v>
+      </x:c>
+      <x:c r="AA25" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMihgFBVV95cUxOVVc5b2xRd2dWREJQMEVGcEVKSlhNdFFmTjNGYWVnRkRNbHlmZ29zRGdzUjlrS2VQQjJxM0RhUTh4bnhIWnhNb3ZnQ2VhYmJqdEI1Q0dpVHZOWlNCLXNUanVlYTdhNmQ2TkpGZ1hFVG0xclRWNWZvZUhmeXdua1BtUDNpMm9LZw?oc=5</x:v>
+      </x:c>
+      <x:c r="AB25" s="41" t="str">
+        <x:v>Сбер забирает Ozon. Инсайд или вброс? Кто выиграет от сделки? - Альфа-Банк</x:v>
+      </x:c>
+      <x:c r="AC25" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="41" t="str">
+        <x:v>DL-eee2cc5f0b30c3ba</x:v>
+      </x:c>
+      <x:c r="B26" s="43" t="n">
+        <x:v>46170</x:v>
+      </x:c>
+      <x:c r="C26" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D26" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E26" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F26" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="G26" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H26" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I26" s="44"/>
+      <x:c r="J26" s="44"/>
+      <x:c r="K26" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L26" s="45"/>
+      <x:c r="M26" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="N26" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O26" s="44"/>
+      <x:c r="P26" s="44"/>
+      <x:c r="Q26" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R26" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S26" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J26&gt;0,$O26&gt;0,$K26=$R26),$J26/$O26,""),"")</x:f>
+      </x:c>
+      <x:c r="T26" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J26&gt;0,$P26&gt;0,$K26=$R26),$J26/$P26,""),"")</x:f>
+      </x:c>
+      <x:c r="U26" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V26" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W26" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X26" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y26" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z26" s="41" t="str">
+        <x:v>Альфа-Банк</x:v>
+      </x:c>
+      <x:c r="AA26" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMihgFBVV95cUxPa1Utd0tlY3RsT1JNSUZEcGdEdG84bFBJYlc0eDVEand3UnppVTduOUZPMUo2UHJ6SmxSSGgwekt6cDFyS3ByZDRxR1RrQjNJWk5VUlB4U2UyM0pSa3FiNnRscllQT19fZ2pEb0xQTU4xdXNXTi1PbWxNTF9LRTg2RTh3VHoyZw?oc=5</x:v>
+      </x:c>
+      <x:c r="AB26" s="41" t="str">
+        <x:v>Озон и Сбер, сделки не будет? - Альфа-Банк</x:v>
+      </x:c>
+      <x:c r="AC26" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="41" t="str">
+        <x:v>DL-54c26c1e05d520bd</x:v>
+      </x:c>
+      <x:c r="B27" s="43" t="n">
+        <x:v>46167</x:v>
+      </x:c>
+      <x:c r="C27" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D27" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E27" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F27" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="G27" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H27" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I27" s="44"/>
+      <x:c r="J27" s="44"/>
+      <x:c r="K27" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L27" s="45"/>
+      <x:c r="M27" s="41" t="str">
+        <x:v>Shares</x:v>
+      </x:c>
+      <x:c r="N27" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O27" s="44"/>
+      <x:c r="P27" s="44"/>
+      <x:c r="Q27" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R27" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S27" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J27&gt;0,$O27&gt;0,$K27=$R27),$J27/$O27,""),"")</x:f>
+      </x:c>
+      <x:c r="T27" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J27&gt;0,$P27&gt;0,$K27=$R27),$J27/$P27,""),"")</x:f>
+      </x:c>
+      <x:c r="U27" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V27" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W27" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X27" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y27" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z27" s="41" t="str">
+        <x:v>Финам</x:v>
+      </x:c>
+      <x:c r="AA27" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMirwFBVV95cUxNckFiOGoyLVd2REpiUVVDaWp6NzF5Y1laekdUZnhnWUJYS3ZteHpxSGd6OElyTUwyZXVFWjgwWmRFclVXbV9FR2xKS2dHZDdoZEZsUEMycy01ZUxUMU03eTBybC1NQlZ5dDVtZHp4NTdVdEhzak9jVlgwZ2ZXTVA0SnIyM0RUTG5saEdQWG5FTDIwUmE1MHllN2xOek1HeXlRS2RtSDhCeFZfaElpRy1F?oc=5</x:v>
+      </x:c>
+      <x:c r="AB27" s="41" t="str">
+        <x:v>25.05.26 Последний день покупки акций “Озона” под дивиденды - 25 мая - Финам</x:v>
+      </x:c>
+      <x:c r="AC27" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="41" t="str">
+        <x:v>DL-38b5154e2b53df8c</x:v>
+      </x:c>
+      <x:c r="B28" s="43" t="n">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="C28" s="41" t="str">
+        <x:v>ECM</x:v>
+      </x:c>
+      <x:c r="D28" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E28" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="F28" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G28" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H28" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I28" s="44"/>
+      <x:c r="J28" s="44"/>
+      <x:c r="K28" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L28" s="45"/>
+      <x:c r="M28" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N28" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O28" s="44"/>
+      <x:c r="P28" s="44"/>
+      <x:c r="Q28" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R28" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S28" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J28&gt;0,$O28&gt;0,$K28=$R28),$J28/$O28,""),"")</x:f>
+      </x:c>
+      <x:c r="T28" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J28&gt;0,$P28&gt;0,$K28=$R28),$J28/$P28,""),"")</x:f>
+      </x:c>
+      <x:c r="U28" s="41" t="str">
+        <x:v>Equity issuance</x:v>
+      </x:c>
+      <x:c r="V28" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W28" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X28" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y28" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z28" s="41" t="str">
+        <x:v>Финам</x:v>
+      </x:c>
+      <x:c r="AA28" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOVkF3VWdna082MXVoUDVVTnpvUjV1Y2tnMGRwRkYwRlhnUE1RZldyUGVCcklzSWdXQmhMYkRaNi1nZGp5LVdzU3RRWV9kTnpJbFFxU2lCSGR1clk5R3NIaDZHeDRxTUF6VkZHV2F4dTAtS0Jjd1FEM281dU5YZ3lMRWROOVNiT29mVG1EcXRCcmdmaDZ5OFpzTmRHRWpidFMzdjktZHhRMGpxZ0pUZmw0MDRGNjZEMWFPVC1EcFFFa1NFNzJlNk1oUnI1cGFpc2ZDYWk0LUxuaVN1LUdvU25hTXpINjhQZGNHdzJIdElR?oc=5</x:v>
+      </x:c>
+      <x:c r="AB28" s="41" t="str">
+        <x:v>Отчетности «Займера», БСП и «Совкомбанка», дивидендный вопрос у «Озона» и «МД Медикал» - основные события 15 мая 15.05.2026 - Финам</x:v>
+      </x:c>
+      <x:c r="AC28" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="41" t="str">
+        <x:v>DL-32f044efd41bc454</x:v>
+      </x:c>
+      <x:c r="B29" s="43" t="n">
+        <x:v>46157</x:v>
+      </x:c>
+      <x:c r="C29" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D29" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E29" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F29" s="41" t="str">
+        <x:v>VKCO</x:v>
+      </x:c>
+      <x:c r="G29" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H29" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I29" s="44"/>
+      <x:c r="J29" s="44"/>
+      <x:c r="K29" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L29" s="45"/>
+      <x:c r="M29" s="41" t="str">
+        <x:v>Shares</x:v>
+      </x:c>
+      <x:c r="N29" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O29" s="44"/>
+      <x:c r="P29" s="44"/>
+      <x:c r="Q29" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R29" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S29" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J29&gt;0,$O29&gt;0,$K29=$R29),$J29/$O29,""),"")</x:f>
+      </x:c>
+      <x:c r="T29" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J29&gt;0,$P29&gt;0,$K29=$R29),$J29/$P29,""),"")</x:f>
+      </x:c>
+      <x:c r="U29" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V29" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W29" s="41" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="X29" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y29" s="41" t="str"/>
+      <x:c r="Z29" s="41" t="str">
+        <x:v>Интерфакс</x:v>
+      </x:c>
+      <x:c r="AA29" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1SRWp6YUhObThSanNWWnBCQjlnX0xPVW1fQzJPSlJxM3JxcVhVTWlJaWZVcW5VNXFTQjU0RkJ6cC0wem9DTUNLZWlXeXZmMDhyUlHSAUtBVV95cUxPaFhNLWM1eThHQVJpOEg0TEpxT1BjRk5IdTEyYmFOdzNCOEluQmtLU3pmcXViOW5PM1gwR3ZsT2RhZEVCLTkwQ1RMZk0?oc=5</x:v>
+      </x:c>
+      <x:c r="AB29" s="41" t="str">
+        <x:v>Трамп в I квартале совершал сделки с акциями Nvidia и Boeing - Интерфакс</x:v>
+      </x:c>
+      <x:c r="AC29" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="41" t="str">
+        <x:v>DL-71608263fecb5e53</x:v>
+      </x:c>
+      <x:c r="B30" s="43" t="n">
+        <x:v>46150</x:v>
+      </x:c>
+      <x:c r="C30" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D30" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E30" s="41" t="str">
+        <x:v>Делимобиль</x:v>
+      </x:c>
+      <x:c r="F30" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G30" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H30" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I30" s="44" t="n">
+        <x:v>1900000000</x:v>
+      </x:c>
+      <x:c r="J30" s="44"/>
+      <x:c r="K30" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L30" s="45"/>
+      <x:c r="M30" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N30" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O30" s="44"/>
+      <x:c r="P30" s="44"/>
+      <x:c r="Q30" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R30" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S30" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J30&gt;0,$O30&gt;0,$K30=$R30),$J30/$O30,""),"")</x:f>
+      </x:c>
+      <x:c r="T30" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J30&gt;0,$P30&gt;0,$K30=$R30),$J30/$P30,""),"")</x:f>
+      </x:c>
+      <x:c r="U30" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V30" s="41" t="str">
+        <x:v>погашения выпуска облигаций на 1,9 млрд рублей</x:v>
+      </x:c>
+      <x:c r="W30" s="41" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="X30" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y30" s="41" t="str"/>
+      <x:c r="Z30" s="41" t="str">
+        <x:v>Интерфакс</x:v>
+      </x:c>
+      <x:c r="AA30" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE5rRHd6NXMzNkpDcVZDdVR4NXhZN185LXRRSDMzVzZiUGd4cmNqV1BydzRLTnh4cHJnU19qNnQ1X05XMDl6VnBjVlBXY0NUOUZ3VlHSAUtBVV95cUxQOHVvOS00aURkZ3lDUGZ6Sk9kYTVFSDJhcGNJQk1PVVR2ZFJwWnZlRGZ4eW85TS15QUs4bmkxOWUzQW5PbGpDeUVnOVk?oc=5</x:v>
+      </x:c>
+      <x:c r="AB30" s="41" t="str">
+        <x:v>"Делимобиль" перечислил в НРД средства для погашения выпуска облигаций на 1,9 млрд рублей - Интерфакс</x:v>
+      </x:c>
+      <x:c r="AC30" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="41" t="str">
+        <x:v>DL-2848bdd8b067faa2</x:v>
+      </x:c>
+      <x:c r="B31" s="43" t="n">
+        <x:v>46147</x:v>
+      </x:c>
+      <x:c r="C31" s="41" t="str">
+        <x:v>ECM</x:v>
+      </x:c>
+      <x:c r="D31" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E31" s="41" t="str">
+        <x:v>Yandex</x:v>
+      </x:c>
+      <x:c r="F31" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G31" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H31" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I31" s="44" t="n">
+        <x:v>50000000000</x:v>
+      </x:c>
+      <x:c r="J31" s="44"/>
+      <x:c r="K31" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L31" s="45"/>
+      <x:c r="M31" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N31" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O31" s="44"/>
+      <x:c r="P31" s="44"/>
+      <x:c r="Q31" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R31" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S31" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J31&gt;0,$O31&gt;0,$K31=$R31),$J31/$O31,""),"")</x:f>
+      </x:c>
+      <x:c r="T31" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J31&gt;0,$P31&gt;0,$K31=$R31),$J31/$P31,""),"")</x:f>
+      </x:c>
+      <x:c r="U31" s="41" t="str">
+        <x:v>Equity issuance</x:v>
+      </x:c>
+      <x:c r="V31" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W31" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X31" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y31" s="41" t="str">
+        <x:v>YDEX</x:v>
+      </x:c>
+      <x:c r="Z31" s="41" t="str">
+        <x:v>БКС Экспресс</x:v>
+      </x:c>
+      <x:c r="AA31" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMikwFBVV95cUxPbkRNMVpoTFN4cXlrOWRya3A4SW1Dd09IUHIzMUw3emMzY1hZckpPRWtMclI2aTllZTRQTlRwUmNGNVp4X1hPV041elJSWGhtVS1kM0VGMFpWdmZIcDRmTS04MjBSb3FoVG5xZWdhY0REZkxLMTMxTE1PeF92VW5SRkxDYVNrVGVuNVFTSlRfaFFFeWc?oc=5</x:v>
+      </x:c>
+      <x:c r="AB31" s="41" t="str">
+        <x:v>Яндекс одобрил выкуп акций на 50 млрд рублей - БКС Экспресс</x:v>
+      </x:c>
+      <x:c r="AC31" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="41" t="str">
+        <x:v>DL-3d4a31cc3b7936d0</x:v>
+      </x:c>
+      <x:c r="B32" s="43" t="n">
+        <x:v>46146</x:v>
+      </x:c>
+      <x:c r="C32" s="41" t="str">
+        <x:v>ECM</x:v>
+      </x:c>
+      <x:c r="D32" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E32" s="41" t="str">
+        <x:v>Yandex</x:v>
+      </x:c>
+      <x:c r="F32" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G32" s="41" t="str">
+        <x:v>Energy</x:v>
+      </x:c>
+      <x:c r="H32" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I32" s="44"/>
+      <x:c r="J32" s="44"/>
+      <x:c r="K32" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L32" s="45"/>
+      <x:c r="M32" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N32" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O32" s="44"/>
+      <x:c r="P32" s="44"/>
+      <x:c r="Q32" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R32" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S32" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J32&gt;0,$O32&gt;0,$K32=$R32),$J32/$O32,""),"")</x:f>
+      </x:c>
+      <x:c r="T32" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J32&gt;0,$P32&gt;0,$K32=$R32),$J32/$P32,""),"")</x:f>
+      </x:c>
+      <x:c r="U32" s="41" t="str">
+        <x:v>Equity issuance</x:v>
+      </x:c>
+      <x:c r="V32" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W32" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X32" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y32" s="41" t="str">
+        <x:v>YDEX, OZON</x:v>
+      </x:c>
+      <x:c r="Z32" s="41" t="str">
+        <x:v>SberCIB</x:v>
+      </x:c>
+      <x:c r="AA32" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQZEltanhoOVlVS2FSRnNObHRXRkJnUEpjZ1VRXzB4czdNUFJOVzVxNU1XcGdxX1gxNmhYcHVrWFh1bXZMRTA5UUZHczhJNlJLYl8wVzdtZmdWYjRQZVB4TDVRNHNURVI1UkhkeVFpNXN4WnhUekFURDhiSlFyZDAtUFMtNW1VR3JEZFUwMEktbmFIYk52Uy02ay1IQTdYZHE2Zm10Vkw1LVBLdw?oc=5</x:v>
+      </x:c>
+      <x:c r="AB32" s="41" t="str">
+        <x:v>Результаты Ozon, ДОМ. РФ, дивиденды Яндекса и Татнефти и другие новости недели - SberCIB</x:v>
+      </x:c>
+      <x:c r="AC32" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="41" t="str">
+        <x:v>DL-6bc0569f7ac374fe</x:v>
+      </x:c>
+      <x:c r="B33" s="43" t="n">
+        <x:v>46139</x:v>
+      </x:c>
+      <x:c r="C33" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D33" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E33" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F33" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="G33" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H33" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I33" s="44"/>
+      <x:c r="J33" s="44"/>
+      <x:c r="K33" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L33" s="45"/>
+      <x:c r="M33" s="41" t="str">
+        <x:v>Shares</x:v>
+      </x:c>
+      <x:c r="N33" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O33" s="44"/>
+      <x:c r="P33" s="44"/>
+      <x:c r="Q33" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R33" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S33" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J33&gt;0,$O33&gt;0,$K33=$R33),$J33/$O33,""),"")</x:f>
+      </x:c>
+      <x:c r="T33" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J33&gt;0,$P33&gt;0,$K33=$R33),$J33/$P33,""),"")</x:f>
+      </x:c>
+      <x:c r="U33" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V33" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W33" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X33" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y33" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z33" s="41" t="str">
+        <x:v>Ведомости</x:v>
+      </x:c>
+      <x:c r="AA33" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMifkFVX3lxTE5wcVN1bk9QeWE3N3kxMkdGdndraERVOGhyUndZcTkwSVVWdlhXUkVldXUtRWR5QTlCR3owOHN1QzFPZVVDR0JWMGkweTM2ekRobml3MzJqT3ZyTGFCSTZtTk0yZ3FxOG52ZjA3c203bEJ4UGVIN18xQUJxenBLQQ?oc=5</x:v>
+      </x:c>
+      <x:c r="AB33" s="41" t="str">
+        <x:v>Путин исключил «Озон банк» из списка с запретом на сделки с акциями и долями - Ведомости</x:v>
+      </x:c>
+      <x:c r="AC33" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="41" t="str">
+        <x:v>DL-cc671fa6b14f8f28</x:v>
+      </x:c>
+      <x:c r="B34" s="43" t="n">
+        <x:v>46139</x:v>
+      </x:c>
+      <x:c r="C34" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D34" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E34" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F34" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="G34" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H34" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I34" s="44"/>
+      <x:c r="J34" s="44"/>
+      <x:c r="K34" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L34" s="45"/>
+      <x:c r="M34" s="41" t="str">
+        <x:v>Shares</x:v>
+      </x:c>
+      <x:c r="N34" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O34" s="44"/>
+      <x:c r="P34" s="44"/>
+      <x:c r="Q34" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R34" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S34" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J34&gt;0,$O34&gt;0,$K34=$R34),$J34/$O34,""),"")</x:f>
+      </x:c>
+      <x:c r="T34" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J34&gt;0,$P34&gt;0,$K34=$R34),$J34/$P34,""),"")</x:f>
+      </x:c>
+      <x:c r="U34" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V34" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W34" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X34" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y34" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z34" s="41" t="str">
+        <x:v>БКС Экспресс</x:v>
+      </x:c>
+      <x:c r="AA34" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMiwgFBVV95cUxORlpPNHotYkNzQVpwd2ptLTRIVmJmelQwVHY5Vjc2Rmd1YzFnMW52R3h3aXlFYkpzc0NfY0NPdWk3RnhUSXhudGhZUWxXeE90WlNpVmRkYlhxSlNHLXFkZ1pLMllFY3VBQUx6bDJUcG13VEVINVlKOTFMUkRkUUx0bllTQ2NQdzBaMENTM3FrN2dMNVFjQ2NKRTVUNG92QWlpcEdtWVFuMWx1dnJRTTFWS1paVllydW9oeUU0NjNUVjhCUQ?oc=5</x:v>
+      </x:c>
+      <x:c r="AB34" s="41" t="str">
+        <x:v>Ozon Банк исключен из перечня банков, с акциями которых запрещены сделки - БКС Экспресс</x:v>
+      </x:c>
+      <x:c r="AC34" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="41" t="str">
+        <x:v>DL-2d1ef3023240f32a</x:v>
+      </x:c>
+      <x:c r="B35" s="43" t="n">
+        <x:v>46139</x:v>
+      </x:c>
+      <x:c r="C35" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D35" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E35" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F35" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="G35" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H35" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I35" s="44"/>
+      <x:c r="J35" s="44"/>
+      <x:c r="K35" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L35" s="45"/>
+      <x:c r="M35" s="41" t="str">
+        <x:v>Shares</x:v>
+      </x:c>
+      <x:c r="N35" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O35" s="44"/>
+      <x:c r="P35" s="44"/>
+      <x:c r="Q35" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R35" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S35" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J35&gt;0,$O35&gt;0,$K35=$R35),$J35/$O35,""),"")</x:f>
+      </x:c>
+      <x:c r="T35" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J35&gt;0,$P35&gt;0,$K35=$R35),$J35/$P35,""),"")</x:f>
+      </x:c>
+      <x:c r="U35" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V35" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W35" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X35" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y35" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z35" s="41" t="str">
+        <x:v>Главпортал</x:v>
+      </x:c>
+      <x:c r="AA35" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMifEFVX3lxTE5vODZHWnJJX1RoLWU3X2RfSGpCZFZrN2xZeGtyOVVzSENxQzlaQTEwV3pCNXBuOG9JRnVfTkdxOGl5N3RJTGhDVVh0YXdBbTY5dnlZYWRjVkJ5MTFROHhTQUVvdjEwS3BpYUtmSG12YmVocnBnVmVpVmN0ZzQ?oc=5</x:v>
+      </x:c>
+      <x:c r="AB35" s="41" t="str">
+        <x:v>Путин разрешил сделки с акциями «Озон банка» - Главпортал</x:v>
+      </x:c>
+      <x:c r="AC35" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="41" t="str">
+        <x:v>DL-0bceebeca9933dc3</x:v>
+      </x:c>
+      <x:c r="B36" s="43" t="n">
+        <x:v>46132</x:v>
+      </x:c>
+      <x:c r="C36" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D36" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E36" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="F36" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G36" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H36" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I36" s="44"/>
+      <x:c r="J36" s="44"/>
+      <x:c r="K36" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L36" s="45"/>
+      <x:c r="M36" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N36" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O36" s="44"/>
+      <x:c r="P36" s="44"/>
+      <x:c r="Q36" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R36" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S36" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J36&gt;0,$O36&gt;0,$K36=$R36),$J36/$O36,""),"")</x:f>
+      </x:c>
+      <x:c r="T36" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J36&gt;0,$P36&gt;0,$K36=$R36),$J36/$P36,""),"")</x:f>
+      </x:c>
+      <x:c r="U36" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V36" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W36" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X36" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y36" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z36" s="41" t="str">
+        <x:v>Альфа-Банк</x:v>
+      </x:c>
+      <x:c r="AA36" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMihgFBVV95cUxOR21Vd1RCOGpSRktSR2g3Mm11emdNTHVpLTlESXFfUVc5SFZFYkZYTWcwZ1kxc2ZUU1lPVWo3UmRjQXl4SFREaElpVTZvZktVMW43QXhNU2ZHal9hSHQ0bkttRV8xa1BVbHRHSENoSE5GblYwZElISUxNbG1fSG1uWUJ0QVgtZw?oc=5</x:v>
+      </x:c>
+      <x:c r="AB36" s="41" t="str">
+        <x:v>Облигации Озона: заработай на маркетплейсе - Альфа-Банк</x:v>
+      </x:c>
+      <x:c r="AC36" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="41" t="str">
+        <x:v>DL-c10daba8af8e67d8</x:v>
+      </x:c>
+      <x:c r="B37" s="43" t="n">
+        <x:v>46128</x:v>
+      </x:c>
+      <x:c r="C37" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D37" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E37" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F37" s="41" t="str">
+        <x:v>VK</x:v>
+      </x:c>
+      <x:c r="G37" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H37" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I37" s="44" t="n">
+        <x:v>21200000000</x:v>
+      </x:c>
+      <x:c r="J37" s="44"/>
+      <x:c r="K37" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L37" s="45" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="M37" s="41" t="str">
+        <x:v>Shares</x:v>
+      </x:c>
+      <x:c r="N37" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O37" s="44"/>
+      <x:c r="P37" s="44"/>
+      <x:c r="Q37" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R37" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S37" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J37&gt;0,$O37&gt;0,$K37=$R37),$J37/$O37,""),"")</x:f>
+      </x:c>
+      <x:c r="T37" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J37&gt;0,$P37&gt;0,$K37=$R37),$J37/$P37,""),"")</x:f>
+      </x:c>
+      <x:c r="U37" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V37" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W37" s="41" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="X37" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y37" s="41" t="str">
+        <x:v>VKCO</x:v>
+      </x:c>
+      <x:c r="Z37" s="41" t="str">
+        <x:v>RB.ru</x:v>
+      </x:c>
+      <x:c r="AA37" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNQlJkLWo5eXZTSkZxSWU5NjF5TVJ0N1lYdXJqSzlFUGFMdk5jVEZMak1HeDE2SDZNcDduc3hENHkzaW8wWTVfWjN1QmpodGdYdDRLVXpua0pBUUs0MzVBX3lnOHlkVkJhVGdLNDlESDNRYmNmaDFaamJZVHdJRGhpX25lSkNmcmZ2dWZhZnhja2NwcXVnelJZVjg0Z1Flakd2VGl0MGRwUVdTTGtYYlNFcUYxSXdYaGY5?oc=5</x:v>
+      </x:c>
+      <x:c r="AB37" s="41" t="str">
+        <x:v>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.ru</x:v>
+      </x:c>
+      <x:c r="AC37" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="41" t="str">
+        <x:v>DL-4d20ecb8f5c75dad</x:v>
+      </x:c>
+      <x:c r="B38" s="43" t="n">
+        <x:v>46128</x:v>
+      </x:c>
+      <x:c r="C38" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D38" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E38" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F38" s="41" t="str">
+        <x:v>VK</x:v>
+      </x:c>
+      <x:c r="G38" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H38" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I38" s="44" t="n">
+        <x:v>21200000000</x:v>
+      </x:c>
+      <x:c r="J38" s="44"/>
+      <x:c r="K38" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L38" s="45"/>
+      <x:c r="M38" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="N38" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O38" s="44"/>
+      <x:c r="P38" s="44"/>
+      <x:c r="Q38" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R38" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S38" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J38&gt;0,$O38&gt;0,$K38=$R38),$J38/$O38,""),"")</x:f>
+      </x:c>
+      <x:c r="T38" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J38&gt;0,$P38&gt;0,$K38=$R38),$J38/$P38,""),"")</x:f>
+      </x:c>
+      <x:c r="U38" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V38" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W38" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X38" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y38" s="41" t="str">
+        <x:v>VKCO</x:v>
+      </x:c>
+      <x:c r="Z38" s="41" t="str">
+        <x:v>Ведомости</x:v>
+      </x:c>
+      <x:c r="AA38" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMifkFVX3lxTE1vSUlEOTl2cU5jckxzemNzN2oyNVZaX203N1VWRkpuZXNwYV9sdUNGMTZPTHhiNm5LWFBmdFM0QkFTRjFPczd4VEFlTEZpRzhiakF2ZGh5UU5kamRvbnFRTDE5dG8zOF9HRkk5MDUwVzBWbU9qWEN0MDhIdTJNUQ?oc=5</x:v>
+      </x:c>
+      <x:c r="AB38" s="41" t="str">
+        <x:v>VK продала долю в «Точка банке» по цене не менее 21,2 млрд рублей - Ведомости</x:v>
+      </x:c>
+      <x:c r="AC38" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="41" t="str">
+        <x:v>DL-dfc59ea0a0794532</x:v>
+      </x:c>
+      <x:c r="B39" s="43" t="n">
+        <x:v>46128</x:v>
+      </x:c>
+      <x:c r="C39" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D39" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E39" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F39" s="41" t="str">
+        <x:v>VK</x:v>
+      </x:c>
+      <x:c r="G39" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H39" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I39" s="44"/>
+      <x:c r="J39" s="44"/>
+      <x:c r="K39" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L39" s="45"/>
+      <x:c r="M39" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="N39" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O39" s="44"/>
+      <x:c r="P39" s="44"/>
+      <x:c r="Q39" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R39" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S39" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J39&gt;0,$O39&gt;0,$K39=$R39),$J39/$O39,""),"")</x:f>
+      </x:c>
+      <x:c r="T39" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J39&gt;0,$P39&gt;0,$K39=$R39),$J39/$P39,""),"")</x:f>
+      </x:c>
+      <x:c r="U39" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V39" s="41" t="str">
+        <x:v>предпринимателей</x:v>
+      </x:c>
+      <x:c r="W39" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X39" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y39" s="41" t="str">
+        <x:v>VKCO</x:v>
+      </x:c>
+      <x:c r="Z39" s="41" t="str">
+        <x:v>CNews.ru</x:v>
+      </x:c>
+      <x:c r="AA39" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMigAFBVV95cUxOeU1NOHJNay1uUm9TdlpGcWh4YkNXN3J0clFCT2JrM0t5T3hwTmtTRlJXUWpyeVBYbnltZlB0dnpqLWxhTUxQNW9wQU1LeG5sTjVzT1NNQlFlY0Jpb1REMGhyWG1wSUM0STZXbFFaNndzQ1A1MlVvMFN3RmlmOW4tXw?oc=5</x:v>
+      </x:c>
+      <x:c r="AB39" s="41" t="str">
+        <x:v>VK продал свою долю в виртуальном банке для предпринимателей - CNews.ru</x:v>
+      </x:c>
+      <x:c r="AC39" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="41" t="str">
+        <x:v>DL-1363a495ec14164a</x:v>
+      </x:c>
+      <x:c r="B40" s="43" t="n">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="C40" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D40" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E40" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="F40" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G40" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H40" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I40" s="44" t="n">
+        <x:v>15000000000</x:v>
+      </x:c>
+      <x:c r="J40" s="44"/>
+      <x:c r="K40" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L40" s="45"/>
+      <x:c r="M40" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N40" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O40" s="44"/>
+      <x:c r="P40" s="44"/>
+      <x:c r="Q40" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R40" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S40" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J40&gt;0,$O40&gt;0,$K40=$R40),$J40/$O40,""),"")</x:f>
+      </x:c>
+      <x:c r="T40" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J40&gt;0,$P40&gt;0,$K40=$R40),$J40/$P40,""),"")</x:f>
+      </x:c>
+      <x:c r="U40" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V40" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W40" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X40" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y40" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z40" s="41" t="str">
+        <x:v>https://expert.ru</x:v>
+      </x:c>
+      <x:c r="AA40" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMiigFBVV95cUxNVmVRdkQ4RElHdURKbmVDQU9NbVRmZTd0Z3NiM3JzMjFhZzNzQzVPMnhzNHFER2VsYVAyWEpwVlg4c24zZUozY1ZNUFQxNDMxakR1Q1J0RFhhbkRxbUZYTmgtc3N3UzhsckljT1lpZTFvaXJKeGlTblNyNlNWb2JhOWFSVXZJWjZ0Rmc?oc=5</x:v>
+      </x:c>
+      <x:c r="AB40" s="41" t="str">
+        <x:v>Ozon анонсировал размещение облигаций на 15 млрд рублей - https://expert.ru</x:v>
+      </x:c>
+      <x:c r="AC40" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="41" t="str">
+        <x:v>DL-12855c6275c496fe</x:v>
+      </x:c>
+      <x:c r="B41" s="43" t="n">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="C41" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D41" s="41" t="str">
+        <x:v>Announced</x:v>
+      </x:c>
+      <x:c r="E41" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="F41" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G41" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H41" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I41" s="44"/>
+      <x:c r="J41" s="44"/>
+      <x:c r="K41" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L41" s="45"/>
+      <x:c r="M41" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N41" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O41" s="44"/>
+      <x:c r="P41" s="44"/>
+      <x:c r="Q41" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R41" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S41" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J41&gt;0,$O41&gt;0,$K41=$R41),$J41/$O41,""),"")</x:f>
+      </x:c>
+      <x:c r="T41" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J41&gt;0,$P41&gt;0,$K41=$R41),$J41/$P41,""),"")</x:f>
+      </x:c>
+      <x:c r="U41" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V41" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W41" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X41" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y41" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z41" s="41" t="str">
+        <x:v>БКС Экспресс</x:v>
+      </x:c>
+      <x:c r="AA41" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMipgFBVV95cUxNTmtrN3N0YVN0c0NuVnBscUJvbzdVbWZ5OXczRTkySkx1T1hKdWJvZlFWNEFqbkxhRmpXVEVQZUdIcjdOZkNFRnJhX1huRGRmelhla1RRTURfejMzd2FIMU9ZcmQ4REtOWWEyZ3JhLUgwSmI2UDhJM2s4TkNRekY0T3ZtcEJNbUYzNTQzOXRITGxsN1A0N1duQ3FKeE5fTXIxMUVJTlh3?oc=5</x:v>
+      </x:c>
+      <x:c r="AB41" s="41" t="str">
+        <x:v>Озон планирует дебютное размещение биржевых облигаций - БКС Экспресс</x:v>
+      </x:c>
+      <x:c r="AC41" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="41" t="str">
+        <x:v>DL-d39c99c4c2dfa45c</x:v>
+      </x:c>
+      <x:c r="B42" s="43" t="n">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="C42" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D42" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E42" s="41" t="str">
+        <x:v>VK</x:v>
+      </x:c>
+      <x:c r="F42" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G42" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H42" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I42" s="44" t="n">
+        <x:v>10000000000</x:v>
+      </x:c>
+      <x:c r="J42" s="44"/>
+      <x:c r="K42" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L42" s="45"/>
+      <x:c r="M42" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N42" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O42" s="44"/>
+      <x:c r="P42" s="44"/>
+      <x:c r="Q42" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R42" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S42" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J42&gt;0,$O42&gt;0,$K42=$R42),$J42/$O42,""),"")</x:f>
+      </x:c>
+      <x:c r="T42" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J42&gt;0,$P42&gt;0,$K42=$R42),$J42/$P42,""),"")</x:f>
+      </x:c>
+      <x:c r="U42" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V42" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W42" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X42" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y42" s="41" t="str">
+        <x:v>VKCO</x:v>
+      </x:c>
+      <x:c r="Z42" s="41" t="str">
+        <x:v>vk.company</x:v>
+      </x:c>
+      <x:c r="AA42" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1WcXUxeUFkWFdQQUk3U0o0RDBfeTdxa3IxV0dWLXRZZXRjWWo1M0NBOUJfeVUwNHRuMUxaOVBKVXdjSWstd1paRHFfX2lpT1VpV0E?oc=5</x:v>
+      </x:c>
+      <x:c r="AB42" s="41" t="str">
+        <x:v>VK объявляет о планах по размещению биржевых облигаций объемом 10 млрд рублей - vk.company</x:v>
+      </x:c>
+      <x:c r="AC42" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="41" t="str">
+        <x:v>DL-b9babb23f2c4462c</x:v>
+      </x:c>
+      <x:c r="B43" s="43" t="n">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="C43" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D43" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E43" s="41" t="str">
+        <x:v>VK</x:v>
+      </x:c>
+      <x:c r="F43" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G43" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H43" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I43" s="44"/>
+      <x:c r="J43" s="44"/>
+      <x:c r="K43" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L43" s="45"/>
+      <x:c r="M43" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N43" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O43" s="44"/>
+      <x:c r="P43" s="44"/>
+      <x:c r="Q43" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R43" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S43" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J43&gt;0,$O43&gt;0,$K43=$R43),$J43/$O43,""),"")</x:f>
+      </x:c>
+      <x:c r="T43" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J43&gt;0,$P43&gt;0,$K43=$R43),$J43/$P43,""),"")</x:f>
+      </x:c>
+      <x:c r="U43" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V43" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W43" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X43" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y43" s="41" t="str">
+        <x:v>VKCO</x:v>
+      </x:c>
+      <x:c r="Z43" s="41" t="str">
+        <x:v>Финам</x:v>
+      </x:c>
+      <x:c r="AA43" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPR3ZFSWgwcm9TTW9rSTlBM0VaYncwM3dBZ0N0OUhwWFBnYVZLc3EtZkNrOE5RLUFjczJ5b25yNURHX0RvYkNPbUFfTlhiSkU3U185NFM0b3R3ZVJVbVEweXI4Q1hRVDBwN3dlcHpocDFYTmRYalh4d1Q1RVU3M1JHZ18ydXdQc2s0OUJGQTJwOFRydlNZOTNJbkItdEtZQVRyb3BMWU5fY082ZHZzbDdNbmNRZWJHRUVhd0FIUkhtX28?oc=5</x:v>
+      </x:c>
+      <x:c r="AB43" s="41" t="str">
+        <x:v>VK размещает облигации: как это отразится на инвесторах в акции 30.03.2026 - Финам</x:v>
+      </x:c>
+      <x:c r="AC43" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:T1"/>
-    <x:mergeCell ref="A2:H2"/>
-    <x:mergeCell ref="A4:T4"/>
+    <x:mergeCell ref="A1:AC1"/>
+    <x:mergeCell ref="A2:AC2"/>
+    <x:mergeCell ref="A4:AC4"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="N7:N7">
+  <x:conditionalFormatting sqref="W7:W43">
     <x:cfRule type="colorScale" priority="1">
       <x:colorScale>
         <x:cfvo type="min"/>
@@ -1061,7 +4157,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd427b9c5e0b4b36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R486e431c6e5f49cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1070,8 +4166,8 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="27" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="78" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -1088,7 +4184,7 @@
     </x:row>
     <x:row r="2" ht="25" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Latest highest-priority transaction from the database; blanks are explicitly labelled</x:v>
+        <x:v>Latest transaction; N/M and Not disclosed are deliberate, not missing-data errors</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -1100,7 +4196,7 @@
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
       <x:c r="A4" s="9" t="str">
-        <x:v>DCM | Announced</x:v>
+        <x:v>DCM | Reported</x:v>
       </x:c>
       <x:c r="B4" s="9"/>
       <x:c r="C4" s="9"/>
@@ -1110,114 +4206,146 @@
       <x:c r="G4" s="9"/>
       <x:c r="H4" s="9"/>
     </x:row>
-    <x:row r="6" ht="25" customHeight="1">
-      <x:c r="A6" s="54" t="str">
+    <x:row r="6">
+      <x:c r="A6" s="48" t="str">
         <x:v>Headline</x:v>
       </x:c>
-      <x:c r="B6" s="67" t="str">
-        <x:v>Selectel разместит облигации на 5 млрд руб. для рефинансирования и инвестиций - ComNews.ru</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="25" customHeight="1">
-      <x:c r="A7" s="55" t="str">
+      <x:c r="B6" s="55" t="str">
+        <x:v>О регистрации выпуска биржевых облигаций, о включении его в Список ценных бумаг, допущенных к торгам, и о присвоении указанным биржевым облигациям регистрационного номера</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="49" t="str">
         <x:v>Announced date</x:v>
       </x:c>
-      <x:c r="B7" s="68" t="n">
-        <x:v>46197</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="25" customHeight="1">
-      <x:c r="A8" s="55" t="str">
+      <x:c r="B7" s="58" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="49" t="str">
         <x:v>Target / Issuer</x:v>
       </x:c>
-      <x:c r="B8" s="69" t="str">
-        <x:v>Selectel</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="25" customHeight="1">
-      <x:c r="A9" s="55" t="str">
+      <x:c r="B8" s="56" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="49" t="str">
         <x:v>Acquirer / Investor</x:v>
       </x:c>
-      <x:c r="B9" s="69" t="str">
-        <x:v>Not applicable</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="25" customHeight="1">
-      <x:c r="A10" s="55" t="str">
+      <x:c r="B9" s="56" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="49" t="str">
         <x:v>Transaction value</x:v>
       </x:c>
-      <x:c r="B10" s="70" t="n">
-        <x:v>5000000000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="25" customHeight="1">
-      <x:c r="A11" s="55" t="str">
+      <x:c r="B10" s="59"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="49" t="str">
+        <x:v>Enterprise value</x:v>
+      </x:c>
+      <x:c r="B11" s="59"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="49" t="str">
         <x:v>Currency</x:v>
       </x:c>
-      <x:c r="B11" s="69" t="str">
-        <x:v>RUB</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="25" customHeight="1">
-      <x:c r="A12" s="55" t="str">
+      <x:c r="B12" s="56" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="49" t="str">
         <x:v>Stake</x:v>
       </x:c>
-      <x:c r="B12" s="71"/>
-    </x:row>
-    <x:row r="13" ht="25" customHeight="1">
-      <x:c r="A13" s="55" t="str">
+      <x:c r="B13" s="60"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="49" t="str">
+        <x:v>Payment form</x:v>
+      </x:c>
+      <x:c r="B14" s="56" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="49" t="str">
+        <x:v>Advisors</x:v>
+      </x:c>
+      <x:c r="B15" s="56" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="49" t="str">
+        <x:v>Revenue LTM</x:v>
+      </x:c>
+      <x:c r="B16" s="59"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="49" t="str">
+        <x:v>EBITDA LTM</x:v>
+      </x:c>
+      <x:c r="B17" s="59"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="49" t="str">
+        <x:v>EV / Revenue</x:v>
+      </x:c>
+      <x:c r="B18" s="61" t="str">
+        <x:v>N/M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="49" t="str">
+        <x:v>EV / EBITDA</x:v>
+      </x:c>
+      <x:c r="B19" s="61" t="str">
+        <x:v>N/M</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="49" t="str">
         <x:v>Instrument</x:v>
       </x:c>
-      <x:c r="B13" s="69" t="str">
+      <x:c r="B20" s="56" t="str">
         <x:v>Bonds</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="25" customHeight="1">
-      <x:c r="A14" s="55" t="str">
-        <x:v>Sector / geography</x:v>
-      </x:c>
-      <x:c r="B14" s="69" t="str">
-        <x:v>Not classified / Russia</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="25" customHeight="1">
-      <x:c r="A15" s="55" t="str">
-        <x:v>Rationale / use of proceeds</x:v>
-      </x:c>
-      <x:c r="B15" s="69" t="str">
-        <x:v>рефинансирования и инвестиций</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="25" customHeight="1">
-      <x:c r="A16" s="55" t="str">
+    <x:row r="21">
+      <x:c r="A21" s="49" t="str">
+        <x:v>Rationale</x:v>
+      </x:c>
+      <x:c r="B21" s="56" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="49" t="str">
         <x:v>Evidence / score</x:v>
       </x:c>
-      <x:c r="B16" s="69" t="str">
-        <x:v>unverified / 4 out of 10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="25" customHeight="1">
-      <x:c r="A17" s="55" t="str">
+      <x:c r="B22" s="56" t="str">
+        <x:v>confirmed / 7 out of 10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="49" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B17" s="69" t="str">
-        <x:v>ComNews.ru</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="25" customHeight="1">
-      <x:c r="A18" s="55" t="str">
+      <x:c r="B23" s="56" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="50" t="str">
         <x:v>Source URL</x:v>
       </x:c>
-      <x:c r="B18" s="69" t="str">
+      <x:c r="B24" s="57" t="str">
         <x:v>See Precedent Transactions → Source URL</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="25" customHeight="1">
-      <x:c r="A19" s="56" t="str">
-        <x:v>Analyst note</x:v>
-      </x:c>
-      <x:c r="B19" s="72" t="str">
-        <x:v>Screening only. Confirm parties, status, consideration and deal perimeter in primary documents.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1234,12 +4362,12 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="55" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="46" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="52" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -1256,7 +4384,7 @@
     </x:row>
     <x:row r="2" ht="25" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>Visible audit checks for completeness, uniqueness and safe source links</x:v>
+        <x:v>Completeness, uniqueness, URL safety and valuation-input checks</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -1278,7 +4406,7 @@
       <x:c r="G4" s="9"/>
       <x:c r="H4" s="9"/>
     </x:row>
-    <x:row r="6" ht="30" customHeight="1">
+    <x:row r="6" ht="32" customHeight="1">
       <x:c r="A6" s="17" t="str">
         <x:v>Deal ID</x:v>
       </x:c>
@@ -1298,24 +4426,204 @@
         <x:v>Headline</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="28" customHeight="1">
-      <x:c r="A7" s="48" t="str">
+    <x:row r="7">
+      <x:c r="A7" s="41" t="str">
+        <x:v>DL-moex-101492</x:v>
+      </x:c>
+      <x:c r="B7" s="43" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="C7" s="41" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+      <x:c r="D7" s="41" t="str">
+        <x:v>See Precedent Transactions → Source URL</x:v>
+      </x:c>
+      <x:c r="E7" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="F7" s="41" t="str">
+        <x:v>О регистрации выпуска биржевых облигаций, о включении его в Список ценных бумаг, допущенных к торгам, и о присвоении указанным биржевым облигациям регистрационного номера</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="41" t="str">
+        <x:v>DL-moex-101473</x:v>
+      </x:c>
+      <x:c r="B8" s="43" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="C8" s="41" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+      <x:c r="D8" s="41" t="str">
+        <x:v>See Precedent Transactions → Source URL</x:v>
+      </x:c>
+      <x:c r="E8" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="F8" s="41" t="str">
+        <x:v>О регистрации проспекта биржевых облигаций</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="41" t="str">
+        <x:v>DL-moex-101468</x:v>
+      </x:c>
+      <x:c r="B9" s="43" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="C9" s="41" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+      <x:c r="D9" s="41" t="str">
+        <x:v>See Precedent Transactions → Source URL</x:v>
+      </x:c>
+      <x:c r="E9" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="F9" s="41" t="str">
+        <x:v>О регистрации изменений в эмиссионные документы</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="41" t="str">
+        <x:v>DL-moex-101457</x:v>
+      </x:c>
+      <x:c r="B10" s="43" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="C10" s="41" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+      <x:c r="D10" s="41" t="str">
+        <x:v>See Precedent Transactions → Source URL</x:v>
+      </x:c>
+      <x:c r="E10" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="F10" s="41" t="str">
+        <x:v>О порядке сбора заявок и заключения сделок при размещении облигаций серии Б-1-403 Банк ВТБ (публичное акционерное общество) с 29 июня 2026 года</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="41" t="str">
+        <x:v>DL-moex-101454</x:v>
+      </x:c>
+      <x:c r="B11" s="43" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="C11" s="41" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+      <x:c r="D11" s="41" t="str">
+        <x:v>See Precedent Transactions → Source URL</x:v>
+      </x:c>
+      <x:c r="E11" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="F11" s="41" t="str">
+        <x:v>О порядке приобретения облигаций серии 001P-04 ООО "АРЕНЗА-ПРО" с 29 июня 2026 год</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="41" t="str">
+        <x:v>DL-moex-101451</x:v>
+      </x:c>
+      <x:c r="B12" s="43" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="C12" s="41" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+      <x:c r="D12" s="41" t="str">
+        <x:v>See Precedent Transactions → Source URL</x:v>
+      </x:c>
+      <x:c r="E12" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="F12" s="41" t="str">
+        <x:v>О проведении выкупа облигаций с 29 июня по 03 июля 2026 года</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="41" t="str">
+        <x:v>DL-moex-101450</x:v>
+      </x:c>
+      <x:c r="B13" s="43" t="n">
+        <x:v>46199</x:v>
+      </x:c>
+      <x:c r="C13" s="41" t="str">
+        <x:v>MOEX disclosure</x:v>
+      </x:c>
+      <x:c r="D13" s="41" t="str">
+        <x:v>See Precedent Transactions → Source URL</x:v>
+      </x:c>
+      <x:c r="E13" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="F13" s="41" t="str">
+        <x:v>Дополнительные условия проведения торгов по выкупу облигаций серии 003Р-02 ООО "Концерн "РОССИУМ" 26 июня 2026 года</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="41" t="str">
         <x:v>DL-bec65812ff9fcfae</x:v>
       </x:c>
-      <x:c r="B7" s="49" t="n">
+      <x:c r="B14" s="43" t="n">
         <x:v>46197</x:v>
       </x:c>
-      <x:c r="C7" s="48" t="str">
+      <x:c r="C14" s="41" t="str">
         <x:v>ComNews.ru</x:v>
       </x:c>
-      <x:c r="D7" s="52" t="str">
+      <x:c r="D14" s="41" t="str">
         <x:v>See Precedent Transactions → Source URL</x:v>
       </x:c>
-      <x:c r="E7" s="52" t="str">
+      <x:c r="E14" s="41" t="str">
         <x:v>unverified</x:v>
       </x:c>
-      <x:c r="F7" s="52" t="str">
+      <x:c r="F14" s="41" t="str">
         <x:v>Selectel разместит облигации на 5 млрд руб. для рефинансирования и инвестиций - ComNews.ru</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="41" t="str">
+        <x:v>DL-48bd4fc3fa031e6c</x:v>
+      </x:c>
+      <x:c r="B15" s="43" t="n">
+        <x:v>46192</x:v>
+      </x:c>
+      <x:c r="C15" s="41" t="str">
+        <x:v>Yandex Investor Relations</x:v>
+      </x:c>
+      <x:c r="D15" s="41" t="str">
+        <x:v>See Precedent Transactions → Source URL</x:v>
+      </x:c>
+      <x:c r="E15" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="F15" s="41" t="str">
+        <x:v>Яндекс разместил два выпуска биржевых облигаций на общую сумму 60 млрд рублей</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="41" t="str">
+        <x:v>DL-9092ffd6a36a0a81</x:v>
+      </x:c>
+      <x:c r="B16" s="43" t="n">
+        <x:v>46183</x:v>
+      </x:c>
+      <x:c r="C16" s="41" t="str">
+        <x:v>Интерфакс</x:v>
+      </x:c>
+      <x:c r="D16" s="41" t="str">
+        <x:v>See Precedent Transactions → Source URL</x:v>
+      </x:c>
+      <x:c r="E16" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="F16" s="41" t="str">
+        <x:v>"Норникель" зафиксировал объем размещения облигаций на уровне 3 млрд юаней - Интерфакс</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
@@ -1330,7 +4638,7 @@
       <x:c r="G20" s="9"/>
       <x:c r="H20" s="9"/>
     </x:row>
-    <x:row r="22" ht="30" customHeight="1">
+    <x:row r="22" ht="32" customHeight="1">
       <x:c r="A22" s="17" t="str">
         <x:v>Check</x:v>
       </x:c>
@@ -1355,7 +4663,7 @@
         <x:v>Duplicate deal IDs</x:v>
       </x:c>
       <x:c r="B23" t="n">
-        <x:f>SUMPRODUCT(--(COUNTIF('Precedent Transactions'!$A$7:$A$7,'Precedent Transactions'!$A$7:$A$7)&gt;1))/2</x:f>
+        <x:f>SUMPRODUCT(--(COUNTIF('Precedent Transactions'!$A$7:$A$43,'Precedent Transactions'!$A$7:$A$43)&gt;1))/2</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C23" t="n">
@@ -1378,7 +4686,7 @@
         <x:v>Missing source URLs</x:v>
       </x:c>
       <x:c r="B24" t="n">
-        <x:f>COUNTBLANK('Precedent Transactions'!$R$7:$R$7)</x:f>
+        <x:f>COUNTBLANK('Precedent Transactions'!$AA$7:$AA$43)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C24" t="n">
@@ -1401,7 +4709,7 @@
         <x:v>Missing announced dates</x:v>
       </x:c>
       <x:c r="B25" t="n">
-        <x:f>COUNTBLANK('Precedent Transactions'!$B$7:$B$7)</x:f>
+        <x:f>COUNTBLANK('Precedent Transactions'!$B$7:$B$43)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C25" t="n">
@@ -1424,7 +4732,7 @@
         <x:v>Unsafe / non-HTTP URLs</x:v>
       </x:c>
       <x:c r="B26" t="n">
-        <x:f>SUMPRODUCT(--(LEFT('Precedent Transactions'!$R$7:$R$7,4)&lt;&gt;"http"),--('Precedent Transactions'!$A$7:$A$7&lt;&gt;""))</x:f>
+        <x:f>SUMPRODUCT(--(LEFT('Precedent Transactions'!$AA$7:$AA$43,4)&lt;&gt;"http"),--('Precedent Transactions'!$A$7:$A$43&lt;&gt;""))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C26" t="n">
@@ -1447,35 +4755,81 @@
         <x:v>Missing target / issuer</x:v>
       </x:c>
       <x:c r="B27" t="n">
-        <x:f>COUNTIF('Precedent Transactions'!$E$7:$E$7,"Not disclosed")</x:f>
-        <x:v>0</x:v>
+        <x:f>COUNTIF('Precedent Transactions'!$E$7:$E$43,"Not disclosed")</x:f>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C27" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" t="n">
         <x:f>B27-C27</x:f>
-        <x:v>0</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E27" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F27" t="str">
         <x:f>IF(ABS(D27)&lt;=E27,"OK","REVIEW")</x:f>
+        <x:v>REVIEW</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>EV without revenue/EBITDA</x:v>
+      </x:c>
+      <x:c r="B28" t="n">
+        <x:f>SUMPRODUCT(--('Precedent Transactions'!$J$7:$J$43&gt;0),--('Precedent Transactions'!$O$7:$O$43=""),--('Precedent Transactions'!$P$7:$P$43=""))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D28" t="n">
+        <x:f>B28-C28</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:f>IF(ABS(D28)&lt;=E28,"OK","REVIEW")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="74" t="str">
+      <x:c r="A29" t="str">
+        <x:v>Multiple without enterprise value</x:v>
+      </x:c>
+      <x:c r="B29" t="n">
+        <x:f>SUMPRODUCT(--('Precedent Transactions'!$J$7:$J$43=""),--((('Precedent Transactions'!$S$7:$S$43&gt;0)+('Precedent Transactions'!$T$7:$T$43&gt;0))&gt;0))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D29" t="n">
+        <x:f>B29-C29</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:f>IF(ABS(D29)&lt;=E29,"OK","REVIEW")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="63" t="str">
         <x:v>Overall model status</x:v>
       </x:c>
-      <x:c r="B29" s="75"/>
-      <x:c r="C29" s="75"/>
-      <x:c r="D29" s="75"/>
-      <x:c r="E29" s="75"/>
-      <x:c r="F29" s="76" t="str">
-        <x:f>IF(COUNTIF(F23:F27,"REVIEW")=0,"OK","REVIEW")</x:f>
-        <x:v>OK</x:v>
+      <x:c r="B31" s="64"/>
+      <x:c r="C31" s="64"/>
+      <x:c r="D31" s="64"/>
+      <x:c r="E31" s="64"/>
+      <x:c r="F31" s="65" t="str">
+        <x:f>IF(COUNTIF(F23:F29,"REVIEW")=0,"OK","REVIEW")</x:f>
+        <x:v>REVIEW</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1484,9 +4838,9 @@
     <x:mergeCell ref="A2:H2"/>
     <x:mergeCell ref="A4:H4"/>
     <x:mergeCell ref="A20:H20"/>
-    <x:mergeCell ref="A29:E29"/>
+    <x:mergeCell ref="A31:E31"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="F23:F29">
+  <x:conditionalFormatting sqref="F23:F31">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="OK"/>
     <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="REVIEW"/>
   </x:conditionalFormatting>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Dashboard" sheetId="1" r:id="Rdd12d12ff2da4122"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Precedent Transactions" sheetId="2" r:id="R328d3bbdd89c4d60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Card" sheetId="3" r:id="R62e5697d724f4edb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; QA" sheetId="4" r:id="Rcd48572823e84eb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Dashboard" sheetId="1" r:id="R209f00ac58ba4bfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Precedent Transactions" sheetId="2" r:id="Rf51a889b1a7f4027"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal Card" sheetId="3" r:id="R6b6d26b547cf48c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; QA" sheetId="4" r:id="R9e0c98700761402c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PrecedentTransactionsTable" displayName="PrecedentTransactionsTable" ref="A6:AC43" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PrecedentTransactionsTable" displayName="PrecedentTransactionsTable" ref="A6:AC56" headerRowCount="1">
   <x:tableColumns count="29">
     <x:tableColumn id="1" name="Deal ID"/>
     <x:tableColumn id="2" name="Announced Date"/>
@@ -624,31 +624,31 @@
     <x:row r="7" ht="32" customHeight="1">
       <x:c r="A7" s="28" t="n">
         <x:f>COUNTA('Precedent Transactions'!$A$7:$A$506)</x:f>
-        <x:v>37</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B7" s="29" t="n">
         <x:f>COUNTIF('Precedent Transactions'!$C$7:$C$506,"M&amp;A")</x:f>
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C7" s="29" t="n">
         <x:f>COUNTIF('Precedent Transactions'!$C$7:$C$506,"ECM")</x:f>
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D7" s="29" t="n">
         <x:f>COUNTIF('Precedent Transactions'!$C$7:$C$506,"DCM")</x:f>
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E7" s="31" t="n">
         <x:f>SUM('Precedent Transactions'!$I$7:$I$506)</x:f>
-        <x:v>252300000000</x:v>
+        <x:v>589300000000</x:v>
       </x:c>
       <x:c r="F7" s="29" t="n">
         <x:f>COUNTIF('Precedent Transactions'!$W$7:$W$506,"&gt;=7")</x:f>
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G7" s="29" t="n">
         <x:f>COUNTBLANK('Precedent Transactions'!$I$7:$I$506)-COUNTBLANK('Precedent Transactions'!$A$7:$A$506)</x:f>
-        <x:v>26</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H7" s="30" t="str">
         <x:f>'Sources &amp; QA'!$F$31</x:f>
@@ -739,26 +739,28 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="36" t="n">
-        <x:v>46199</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="B19" t="str">
         <x:v>DCM</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>Reported</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="D19" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>MTSS</x:v>
       </x:c>
       <x:c r="E19" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
-      <x:c r="F19" s="37"/>
+      <x:c r="F19" s="37" t="n">
+        <x:v>20000000000</x:v>
+      </x:c>
       <x:c r="G19" t="str">
-        <x:v>NOT DISCLOSED</x:v>
+        <x:v>RUB</x:v>
       </x:c>
       <x:c r="H19" t="str">
-        <x:v>MOEX disclosure</x:v>
+        <x:v>MTS Investor Relations</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -772,7 +774,7 @@
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="D20" t="str">
-        <x:v>О регистрации проспекта биржевых облигаций</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="E20" t="str">
         <x:v>Not applicable</x:v>
@@ -796,7 +798,7 @@
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="D21" t="str">
-        <x:v>О регистрации изменений в эмиссионные документы</x:v>
+        <x:v>О регистрации проспекта биржевых облигаций</x:v>
       </x:c>
       <x:c r="E21" t="str">
         <x:v>Not applicable</x:v>
@@ -820,7 +822,7 @@
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="D22" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>О регистрации изменений в эмиссионные документы</x:v>
       </x:c>
       <x:c r="E22" t="str">
         <x:v>Not applicable</x:v>
@@ -868,7 +870,7 @@
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="D24" t="str">
-        <x:v>О проведении выкупа облигаций с 29 июня по 03 июля 2026 года</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="E24" t="str">
         <x:v>Not applicable</x:v>
@@ -892,7 +894,7 @@
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="D25" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>О проведении выкупа облигаций с 29 июня по 03 июля 2026 года</x:v>
       </x:c>
       <x:c r="E25" t="str">
         <x:v>Not applicable</x:v>
@@ -907,80 +909,78 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="36" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="B26" t="str">
         <x:v>DCM</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>Announced</x:v>
+        <x:v>Reported</x:v>
       </x:c>
       <x:c r="D26" t="str">
-        <x:v>Selectel</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="E26" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
-      <x:c r="F26" s="37" t="n">
-        <x:v>5000000000</x:v>
-      </x:c>
+      <x:c r="F26" s="37"/>
       <x:c r="G26" t="str">
-        <x:v>RUB</x:v>
+        <x:v>NOT DISCLOSED</x:v>
       </x:c>
       <x:c r="H26" t="str">
-        <x:v>ComNews.ru</x:v>
+        <x:v>MOEX disclosure</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="36" t="n">
-        <x:v>46192</x:v>
+        <x:v>46197</x:v>
       </x:c>
       <x:c r="B27" t="str">
         <x:v>DCM</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>Issued</x:v>
+        <x:v>Announced</x:v>
       </x:c>
       <x:c r="D27" t="str">
-        <x:v>Yandex</x:v>
+        <x:v>Selectel</x:v>
       </x:c>
       <x:c r="E27" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="F27" s="37" t="n">
-        <x:v>60000000000</x:v>
+        <x:v>5000000000</x:v>
       </x:c>
       <x:c r="G27" t="str">
         <x:v>RUB</x:v>
       </x:c>
       <x:c r="H27" t="str">
-        <x:v>Yandex Investor Relations</x:v>
+        <x:v>ComNews.ru</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="36" t="n">
-        <x:v>46183</x:v>
+        <x:v>46192</x:v>
       </x:c>
       <x:c r="B28" t="str">
         <x:v>DCM</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>Reported</x:v>
+        <x:v>Issued</x:v>
       </x:c>
       <x:c r="D28" t="str">
-        <x:v>Норникель</x:v>
+        <x:v>Yandex</x:v>
       </x:c>
       <x:c r="E28" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="F28" s="37" t="n">
-        <x:v>3000000000</x:v>
+        <x:v>60000000000</x:v>
       </x:c>
       <x:c r="G28" t="str">
         <x:v>RUB</x:v>
       </x:c>
       <x:c r="H28" t="str">
-        <x:v>Интерфакс</x:v>
+        <x:v>Yandex Investor Relations</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1220,19 +1220,19 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="41" t="str">
-        <x:v>DL-moex-101492</x:v>
+        <x:v>DL-4d8f7bcb385b1c88</x:v>
       </x:c>
       <x:c r="B7" s="43" t="n">
-        <x:v>46199</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="C7" s="41" t="str">
         <x:v>DCM</x:v>
       </x:c>
       <x:c r="D7" s="41" t="str">
-        <x:v>Reported</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E7" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>MTSS</x:v>
       </x:c>
       <x:c r="F7" s="41" t="str">
         <x:v>Not applicable</x:v>
@@ -1243,10 +1243,12 @@
       <x:c r="H7" s="41" t="str">
         <x:v>Russia</x:v>
       </x:c>
-      <x:c r="I7" s="44"/>
+      <x:c r="I7" s="44" t="n">
+        <x:v>20000000000</x:v>
+      </x:c>
       <x:c r="J7" s="44"/>
       <x:c r="K7" s="41" t="str">
-        <x:v>NOT DISCLOSED</x:v>
+        <x:v>RUB</x:v>
       </x:c>
       <x:c r="L7" s="45"/>
       <x:c r="M7" s="41" t="str">
@@ -1276,20 +1278,20 @@
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="W7" s="41" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="X7" s="41" t="str">
         <x:v>confirmed</x:v>
       </x:c>
       <x:c r="Y7" s="41" t="str"/>
       <x:c r="Z7" s="41" t="str">
-        <x:v>MOEX disclosure</x:v>
+        <x:v>MTS Investor Relations</x:v>
       </x:c>
       <x:c r="AA7" s="41" t="str">
-        <x:v>https://www.moex.com/n101492</x:v>
+        <x:v>https://ir.mts.ru/news_and_events/corporate_releases/details/742414</x:v>
       </x:c>
       <x:c r="AB7" s="41" t="str">
-        <x:v>О регистрации выпуска биржевых облигаций, о включении его в Список ценных бумаг, допущенных к торгам, и о присвоении указанным биржевым облигациям регистрационного номера</x:v>
+        <x:v>МТС успешно закрыла книгу биржевых облигаций 003Р-03 на 20 млрд руб.</x:v>
       </x:c>
       <x:c r="AC7" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -1297,7 +1299,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="41" t="str">
-        <x:v>DL-moex-101473</x:v>
+        <x:v>DL-moex-101492</x:v>
       </x:c>
       <x:c r="B8" s="43" t="n">
         <x:v>46199</x:v>
@@ -1309,7 +1311,7 @@
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E8" s="41" t="str">
-        <x:v>О регистрации проспекта биржевых облигаций</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="F8" s="41" t="str">
         <x:v>Not applicable</x:v>
@@ -1363,10 +1365,10 @@
         <x:v>MOEX disclosure</x:v>
       </x:c>
       <x:c r="AA8" s="41" t="str">
-        <x:v>https://www.moex.com/n101473</x:v>
+        <x:v>https://www.moex.com/n101492</x:v>
       </x:c>
       <x:c r="AB8" s="41" t="str">
-        <x:v>О регистрации проспекта биржевых облигаций</x:v>
+        <x:v>О регистрации выпуска биржевых облигаций, о включении его в Список ценных бумаг, допущенных к торгам, и о присвоении указанным биржевым облигациям регистрационного номера</x:v>
       </x:c>
       <x:c r="AC8" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -1374,7 +1376,7 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="41" t="str">
-        <x:v>DL-moex-101468</x:v>
+        <x:v>DL-moex-101473</x:v>
       </x:c>
       <x:c r="B9" s="43" t="n">
         <x:v>46199</x:v>
@@ -1386,7 +1388,7 @@
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E9" s="41" t="str">
-        <x:v>О регистрации изменений в эмиссионные документы</x:v>
+        <x:v>О регистрации проспекта биржевых облигаций</x:v>
       </x:c>
       <x:c r="F9" s="41" t="str">
         <x:v>Not applicable</x:v>
@@ -1440,10 +1442,10 @@
         <x:v>MOEX disclosure</x:v>
       </x:c>
       <x:c r="AA9" s="41" t="str">
-        <x:v>https://www.moex.com/n101468</x:v>
+        <x:v>https://www.moex.com/n101473</x:v>
       </x:c>
       <x:c r="AB9" s="41" t="str">
-        <x:v>О регистрации изменений в эмиссионные документы</x:v>
+        <x:v>О регистрации проспекта биржевых облигаций</x:v>
       </x:c>
       <x:c r="AC9" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -1451,7 +1453,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="41" t="str">
-        <x:v>DL-moex-101457</x:v>
+        <x:v>DL-moex-101468</x:v>
       </x:c>
       <x:c r="B10" s="43" t="n">
         <x:v>46199</x:v>
@@ -1463,16 +1465,16 @@
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E10" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>О регистрации изменений в эмиссионные документы</x:v>
       </x:c>
       <x:c r="F10" s="41" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="G10" s="41" t="str">
-        <x:v>Financials</x:v>
+        <x:v>Not classified</x:v>
       </x:c>
       <x:c r="H10" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>Russia</x:v>
       </x:c>
       <x:c r="I10" s="44"/>
       <x:c r="J10" s="44"/>
@@ -1517,10 +1519,10 @@
         <x:v>MOEX disclosure</x:v>
       </x:c>
       <x:c r="AA10" s="41" t="str">
-        <x:v>https://www.moex.com/n101457</x:v>
+        <x:v>https://www.moex.com/n101468</x:v>
       </x:c>
       <x:c r="AB10" s="41" t="str">
-        <x:v>О порядке сбора заявок и заключения сделок при размещении облигаций серии Б-1-403 Банк ВТБ (публичное акционерное общество) с 29 июня 2026 года</x:v>
+        <x:v>О регистрации изменений в эмиссионные документы</x:v>
       </x:c>
       <x:c r="AC10" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -1528,7 +1530,7 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="41" t="str">
-        <x:v>DL-moex-101454</x:v>
+        <x:v>DL-moex-101457</x:v>
       </x:c>
       <x:c r="B11" s="43" t="n">
         <x:v>46199</x:v>
@@ -1549,16 +1551,14 @@
         <x:v>Financials</x:v>
       </x:c>
       <x:c r="H11" s="41" t="str">
-        <x:v>Russia</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="I11" s="44"/>
       <x:c r="J11" s="44"/>
       <x:c r="K11" s="41" t="str">
         <x:v>NOT DISCLOSED</x:v>
       </x:c>
-      <x:c r="L11" s="45" t="n">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="L11" s="45"/>
       <x:c r="M11" s="41" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
@@ -1596,10 +1596,10 @@
         <x:v>MOEX disclosure</x:v>
       </x:c>
       <x:c r="AA11" s="41" t="str">
-        <x:v>https://www.moex.com/n101454</x:v>
+        <x:v>https://www.moex.com/n101457</x:v>
       </x:c>
       <x:c r="AB11" s="41" t="str">
-        <x:v>О порядке приобретения облигаций серии 001P-04 ООО "АРЕНЗА-ПРО" с 29 июня 2026 год</x:v>
+        <x:v>О порядке сбора заявок и заключения сделок при размещении облигаций серии Б-1-403 Банк ВТБ (публичное акционерное общество) с 29 июня 2026 года</x:v>
       </x:c>
       <x:c r="AC11" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -1607,7 +1607,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="41" t="str">
-        <x:v>DL-moex-101451</x:v>
+        <x:v>DL-moex-101454</x:v>
       </x:c>
       <x:c r="B12" s="43" t="n">
         <x:v>46199</x:v>
@@ -1619,23 +1619,25 @@
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E12" s="41" t="str">
-        <x:v>О проведении выкупа облигаций с 29 июня по 03 июля 2026 года</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="F12" s="41" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="G12" s="41" t="str">
-        <x:v>Not classified</x:v>
+        <x:v>Financials</x:v>
       </x:c>
       <x:c r="H12" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>Russia</x:v>
       </x:c>
       <x:c r="I12" s="44"/>
       <x:c r="J12" s="44"/>
       <x:c r="K12" s="41" t="str">
         <x:v>NOT DISCLOSED</x:v>
       </x:c>
-      <x:c r="L12" s="45"/>
+      <x:c r="L12" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="M12" s="41" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
@@ -1673,10 +1675,10 @@
         <x:v>MOEX disclosure</x:v>
       </x:c>
       <x:c r="AA12" s="41" t="str">
-        <x:v>https://www.moex.com/n101451</x:v>
+        <x:v>https://www.moex.com/n101454</x:v>
       </x:c>
       <x:c r="AB12" s="41" t="str">
-        <x:v>О проведении выкупа облигаций с 29 июня по 03 июля 2026 года</x:v>
+        <x:v>О порядке приобретения облигаций серии 001P-04 ООО "АРЕНЗА-ПРО" с 29 июня 2026 год</x:v>
       </x:c>
       <x:c r="AC12" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -1684,7 +1686,7 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="41" t="str">
-        <x:v>DL-moex-101450</x:v>
+        <x:v>DL-moex-101451</x:v>
       </x:c>
       <x:c r="B13" s="43" t="n">
         <x:v>46199</x:v>
@@ -1696,7 +1698,7 @@
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E13" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>О проведении выкупа облигаций с 29 июня по 03 июля 2026 года</x:v>
       </x:c>
       <x:c r="F13" s="41" t="str">
         <x:v>Not applicable</x:v>
@@ -1705,7 +1707,7 @@
         <x:v>Not classified</x:v>
       </x:c>
       <x:c r="H13" s="41" t="str">
-        <x:v>Russia</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="I13" s="44"/>
       <x:c r="J13" s="44"/>
@@ -1750,10 +1752,10 @@
         <x:v>MOEX disclosure</x:v>
       </x:c>
       <x:c r="AA13" s="41" t="str">
-        <x:v>https://www.moex.com/n101450</x:v>
+        <x:v>https://www.moex.com/n101451</x:v>
       </x:c>
       <x:c r="AB13" s="41" t="str">
-        <x:v>Дополнительные условия проведения торгов по выкупу облигаций серии 003Р-02 ООО "Концерн "РОССИУМ" 26 июня 2026 года</x:v>
+        <x:v>О проведении выкупа облигаций с 29 июня по 03 июля 2026 года</x:v>
       </x:c>
       <x:c r="AC13" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -1761,19 +1763,19 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="41" t="str">
-        <x:v>DL-bec65812ff9fcfae</x:v>
+        <x:v>DL-moex-101450</x:v>
       </x:c>
       <x:c r="B14" s="43" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="C14" s="41" t="str">
         <x:v>DCM</x:v>
       </x:c>
       <x:c r="D14" s="41" t="str">
-        <x:v>Announced</x:v>
+        <x:v>Reported</x:v>
       </x:c>
       <x:c r="E14" s="41" t="str">
-        <x:v>Selectel</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="F14" s="41" t="str">
         <x:v>Not applicable</x:v>
@@ -1784,20 +1786,26 @@
       <x:c r="H14" s="41" t="str">
         <x:v>Russia</x:v>
       </x:c>
-      <x:c r="I14" s="44" t="n">
-        <x:v>5000000000</x:v>
-      </x:c>
+      <x:c r="I14" s="44"/>
       <x:c r="J14" s="44"/>
       <x:c r="K14" s="41" t="str">
-        <x:v>RUB</x:v>
+        <x:v>NOT DISCLOSED</x:v>
       </x:c>
       <x:c r="L14" s="45"/>
-      <x:c r="M14" s="41"/>
-      <x:c r="N14" s="41"/>
+      <x:c r="M14" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N14" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
       <x:c r="O14" s="44"/>
       <x:c r="P14" s="44"/>
-      <x:c r="Q14" s="41"/>
-      <x:c r="R14" s="41"/>
+      <x:c r="Q14" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R14" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
       <x:c r="S14" s="46" t="str">
         <x:f>IFERROR(IF(AND($J14&gt;0,$O14&gt;0,$K14=$R14),$J14/$O14,""),"")</x:f>
       </x:c>
@@ -1808,23 +1816,23 @@
         <x:v>Bonds</x:v>
       </x:c>
       <x:c r="V14" s="41" t="str">
-        <x:v>рефинансирования и инвестиций</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="W14" s="41" t="n">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="X14" s="41" t="str">
-        <x:v>unverified</x:v>
+        <x:v>confirmed</x:v>
       </x:c>
       <x:c r="Y14" s="41" t="str"/>
       <x:c r="Z14" s="41" t="str">
-        <x:v>ComNews.ru</x:v>
+        <x:v>MOEX disclosure</x:v>
       </x:c>
       <x:c r="AA14" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOZ0FzQTE1TUJkMGFCVjZuNTBGY0JwNTZBaS16Wnl0NW9XSXBmNFlTRUJacXFlV0tYdUxpUTZTWVhNWk4wYll4a3dZZEU2ZFYzZ2d6T2YwUl85bGlXZGRpN3NiTXJwcnExdzBVVkx6YWV1eExnOFJlcmlDb21UTG5KQWozVTNhX0VwNDVmdnFYTEQwcFpENjdHMjhEX01fTERSUHpsNkE2a3FESkdwbzEzbGRsXzB6MWFlVW80Ri1fa0JYdDVKNEhMZml2WmtiSWYyV2tuZA?oc=5</x:v>
+        <x:v>https://www.moex.com/n101450</x:v>
       </x:c>
       <x:c r="AB14" s="41" t="str">
-        <x:v>Selectel разместит облигации на 5 млрд руб. для рефинансирования и инвестиций - ComNews.ru</x:v>
+        <x:v>Дополнительные условия проведения торгов по выкупу облигаций серии 003Р-02 ООО "Концерн "РОССИУМ" 26 июня 2026 года</x:v>
       </x:c>
       <x:c r="AC14" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -1832,51 +1840,43 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="41" t="str">
-        <x:v>DL-48bd4fc3fa031e6c</x:v>
+        <x:v>DL-bec65812ff9fcfae</x:v>
       </x:c>
       <x:c r="B15" s="43" t="n">
-        <x:v>46192</x:v>
+        <x:v>46197</x:v>
       </x:c>
       <x:c r="C15" s="41" t="str">
         <x:v>DCM</x:v>
       </x:c>
       <x:c r="D15" s="41" t="str">
-        <x:v>Issued</x:v>
+        <x:v>Announced</x:v>
       </x:c>
       <x:c r="E15" s="41" t="str">
-        <x:v>Yandex</x:v>
+        <x:v>Selectel</x:v>
       </x:c>
       <x:c r="F15" s="41" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="G15" s="41" t="str">
-        <x:v>Technology</x:v>
+        <x:v>Not classified</x:v>
       </x:c>
       <x:c r="H15" s="41" t="str">
         <x:v>Russia</x:v>
       </x:c>
       <x:c r="I15" s="44" t="n">
-        <x:v>60000000000</x:v>
+        <x:v>5000000000</x:v>
       </x:c>
       <x:c r="J15" s="44"/>
       <x:c r="K15" s="41" t="str">
         <x:v>RUB</x:v>
       </x:c>
       <x:c r="L15" s="45"/>
-      <x:c r="M15" s="41" t="str">
-        <x:v>Not applicable</x:v>
-      </x:c>
-      <x:c r="N15" s="41" t="str">
-        <x:v>Not disclosed</x:v>
-      </x:c>
+      <x:c r="M15" s="41"/>
+      <x:c r="N15" s="41"/>
       <x:c r="O15" s="44"/>
       <x:c r="P15" s="44"/>
-      <x:c r="Q15" s="41" t="str">
-        <x:v>Not disclosed</x:v>
-      </x:c>
-      <x:c r="R15" s="41" t="str">
-        <x:v>Not disclosed</x:v>
-      </x:c>
+      <x:c r="Q15" s="41"/>
+      <x:c r="R15" s="41"/>
       <x:c r="S15" s="46" t="str">
         <x:f>IFERROR(IF(AND($J15&gt;0,$O15&gt;0,$K15=$R15),$J15/$O15,""),"")</x:f>
       </x:c>
@@ -1887,25 +1887,23 @@
         <x:v>Bonds</x:v>
       </x:c>
       <x:c r="V15" s="41" t="str">
-        <x:v>частных инвесторов Яндекса содержит информацию про бизнесы и технологии компании, а также географию присутствия, финансовые результаты, важные новости и многое другое о компании и её рынках</x:v>
+        <x:v>рефинансирования и инвестиций</x:v>
       </x:c>
       <x:c r="W15" s="41" t="n">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X15" s="41" t="str">
-        <x:v>confirmed</x:v>
-      </x:c>
-      <x:c r="Y15" s="41" t="str">
-        <x:v>YDEX</x:v>
-      </x:c>
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y15" s="41" t="str"/>
       <x:c r="Z15" s="41" t="str">
-        <x:v>Yandex Investor Relations</x:v>
+        <x:v>ComNews.ru</x:v>
       </x:c>
       <x:c r="AA15" s="41" t="str">
-        <x:v>https://ir.yandex.ru/press-releases?year=2026&amp;id=19-06-2026-03</x:v>
+        <x:v>https://www.comnews.ru/content/246003/2026-06-25/2026-w26/1008/selectel-razmestit-obligacii-5-mlrd-rub-dlya-refinansirovaniya-i-investiciy</x:v>
       </x:c>
       <x:c r="AB15" s="41" t="str">
-        <x:v>Яндекс разместил два выпуска биржевых облигаций на общую сумму 60 млрд рублей</x:v>
+        <x:v>Selectel разместит облигации на 5 млрд руб. для рефинансирования и инвестиций - ComNews.ru</x:v>
       </x:c>
       <x:c r="AC15" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -1913,31 +1911,31 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="41" t="str">
-        <x:v>DL-9092ffd6a36a0a81</x:v>
+        <x:v>DL-7a721642a53e0f1d</x:v>
       </x:c>
       <x:c r="B16" s="43" t="n">
-        <x:v>46183</x:v>
+        <x:v>46192</x:v>
       </x:c>
       <x:c r="C16" s="41" t="str">
         <x:v>DCM</x:v>
       </x:c>
       <x:c r="D16" s="41" t="str">
-        <x:v>Reported</x:v>
+        <x:v>Issued</x:v>
       </x:c>
       <x:c r="E16" s="41" t="str">
-        <x:v>Норникель</x:v>
+        <x:v>Yandex</x:v>
       </x:c>
       <x:c r="F16" s="41" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="G16" s="41" t="str">
-        <x:v>Not classified</x:v>
+        <x:v>Technology</x:v>
       </x:c>
       <x:c r="H16" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>Russia</x:v>
       </x:c>
       <x:c r="I16" s="44" t="n">
-        <x:v>3000000000</x:v>
+        <x:v>60000000000</x:v>
       </x:c>
       <x:c r="J16" s="44"/>
       <x:c r="K16" s="41" t="str">
@@ -1968,23 +1966,25 @@
         <x:v>Bonds</x:v>
       </x:c>
       <x:c r="V16" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>частных инвесторов Яндекса содержит информацию про бизнесы и технологии компании, а также географию присутствия, финансовые результаты, важные новости и многое другое о компании и её рынках</x:v>
       </x:c>
       <x:c r="W16" s="41" t="n">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="X16" s="41" t="str">
-        <x:v>unverified</x:v>
-      </x:c>
-      <x:c r="Y16" s="41" t="str"/>
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y16" s="41" t="str">
+        <x:v>YDEX</x:v>
+      </x:c>
       <x:c r="Z16" s="41" t="str">
-        <x:v>Интерфакс</x:v>
+        <x:v>Yandex Investor Relations</x:v>
       </x:c>
       <x:c r="AA16" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1YcWRJT1pJS3JQYUlDcVBxQmRrd2JFXzdidEJQMkRoTFVIRlBDUnQ5ZjNSMFZGamhRQ1hoTXFwaUVQMW1PZldFWWhvSzdOdmtSQnfSAUtBVV95cUxQWkQ5UHd5NFJieHBKUTVCZURpX1dEWmM4a2FnOXJ3aUREYi04ZGFUclFMNUxBdU1EMFVYWUU4MlhCaXJfTy1NZlVNXzg?oc=5</x:v>
+        <x:v>https://ir.yandex.ru/press-releases?year=2026&amp;id=19-06-2026-03</x:v>
       </x:c>
       <x:c r="AB16" s="41" t="str">
-        <x:v>"Норникель" зафиксировал объем размещения облигаций на уровне 3 млрд юаней - Интерфакс</x:v>
+        <x:v>Яндекс разместил два выпуска биржевых облигаций на общую сумму 60 млрд рублей</x:v>
       </x:c>
       <x:c r="AC16" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -1992,10 +1992,10 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="41" t="str">
-        <x:v>DL-f71ff729dc9f5af4</x:v>
+        <x:v>DL-9092ffd6a36a0a81</x:v>
       </x:c>
       <x:c r="B17" s="43" t="n">
-        <x:v>46181</x:v>
+        <x:v>46183</x:v>
       </x:c>
       <x:c r="C17" s="41" t="str">
         <x:v>DCM</x:v>
@@ -2004,7 +2004,7 @@
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E17" s="41" t="str">
-        <x:v>Yandex</x:v>
+        <x:v>Норникель</x:v>
       </x:c>
       <x:c r="F17" s="41" t="str">
         <x:v>Not applicable</x:v>
@@ -2015,10 +2015,12 @@
       <x:c r="H17" s="41" t="str">
         <x:v>Not disclosed</x:v>
       </x:c>
-      <x:c r="I17" s="44"/>
+      <x:c r="I17" s="44" t="n">
+        <x:v>3000000000</x:v>
+      </x:c>
       <x:c r="J17" s="44"/>
       <x:c r="K17" s="41" t="str">
-        <x:v>NOT DISCLOSED</x:v>
+        <x:v>RUB</x:v>
       </x:c>
       <x:c r="L17" s="45"/>
       <x:c r="M17" s="41" t="str">
@@ -2048,22 +2050,20 @@
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="W17" s="41" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="X17" s="41" t="str">
         <x:v>unverified</x:v>
       </x:c>
-      <x:c r="Y17" s="41" t="str">
-        <x:v>YDEX</x:v>
-      </x:c>
+      <x:c r="Y17" s="41" t="str"/>
       <x:c r="Z17" s="41" t="str">
-        <x:v>Финам</x:v>
+        <x:v>Интерфакс</x:v>
       </x:c>
       <x:c r="AA17" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMi0AFBVV95cUxOSmlOMWRURDFvUlZqYktKazJXOFhWR1ZMamNuTGF2QlJ0YmIxTmF6RDMtSHF1Y2RTRkc5QWlnZXQ3WUdUMTB4QUNzUy0zT3I2eGJZSW1DWUxaVDlvR1lrNVhZZ3kybDNrb0tXd0FqMkxHQXNWRFhjcFp0MUI3alRKN1BWdlBSN2V2VWphOUxBQkNjc0l1UDF4WTRKZXkxNHlzSmhIRkhmR2pXc1pKLVV4MzJIN0pLZlVkQ3JvZ2d4aFphcXJkd0F3Z1VKYmdPUUdJ?oc=5</x:v>
+        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1YcWRJT1pJS3JQYUlDcVBxQmRrd2JFXzdidEJQMkRoTFVIRlBDUnQ5ZjNSMFZGamhRQ1hoTXFwaUVQMW1PZldFWWhvSzdOdmtSQnfSAUtBVV95cUxQWkQ5UHd5NFJieHBKUTVCZURpX1dEWmM4a2FnOXJ3aUREYi04ZGFUclFMNUxBdU1EMFVYWUU4MlhCaXJfTy1NZlVNXzg?oc=5</x:v>
       </x:c>
       <x:c r="AB17" s="41" t="str">
-        <x:v>«Яндекс» вновь выходит на долговой рынок: разбор двойного размещения облигаций - Финам</x:v>
+        <x:v>"Норникель" зафиксировал объем размещения облигаций на уровне 3 млрд юаней - Интерфакс</x:v>
       </x:c>
       <x:c r="AC17" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -2071,22 +2071,22 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="41" t="str">
-        <x:v>DL-c0e4b0469b5eb473</x:v>
+        <x:v>DL-f71ff729dc9f5af4</x:v>
       </x:c>
       <x:c r="B18" s="43" t="n">
-        <x:v>46177</x:v>
+        <x:v>46181</x:v>
       </x:c>
       <x:c r="C18" s="41" t="str">
-        <x:v>M&amp;A</x:v>
+        <x:v>DCM</x:v>
       </x:c>
       <x:c r="D18" s="41" t="str">
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E18" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>Yandex</x:v>
       </x:c>
       <x:c r="F18" s="41" t="str">
-        <x:v>Ozon</x:v>
+        <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="G18" s="41" t="str">
         <x:v>Not classified</x:v>
@@ -2101,7 +2101,7 @@
       </x:c>
       <x:c r="L18" s="45"/>
       <x:c r="M18" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="N18" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -2121,7 +2121,7 @@
         <x:f>IFERROR(IF(AND($J18&gt;0,$P18&gt;0,$K18=$R18),$J18/$P18,""),"")</x:f>
       </x:c>
       <x:c r="U18" s="41" t="str">
-        <x:v>Acquisition / disposal</x:v>
+        <x:v>Bonds</x:v>
       </x:c>
       <x:c r="V18" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -2133,16 +2133,16 @@
         <x:v>unverified</x:v>
       </x:c>
       <x:c r="Y18" s="41" t="str">
-        <x:v>OZON</x:v>
+        <x:v>YDEX</x:v>
       </x:c>
       <x:c r="Z18" s="41" t="str">
-        <x:v>БКС Экспресс</x:v>
+        <x:v>Финам</x:v>
       </x:c>
       <x:c r="AA18" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMioAFBVV95cUxQM0RKYTRnLW8xX0tVdnh1S3RBQ25IUTNrRGtWSTRudTJVU3A3UXpmZjZCR2ItX2NQNmN1aXdPYUpDN0paWHBfUjBNd2xrWWl6Mk9Zel9MREpqcXl1RUpoUXB2MWNPdFBoYV94Mm0zNkVtcVZFM050R2Jqc2ZKQVdlbkVhVmhuNXZpQWd5STAzOW9fYndtQTBpM0JLTWJmMjlq?oc=5</x:v>
+        <x:v>https://www.finam.ru/publications/item/yandeks-vnov-vykhodit-na-dolgovoy-rynok-razbor-dvoynogo-razmeshcheniya-obligatsiy-20260608-1729/</x:v>
       </x:c>
       <x:c r="AB18" s="41" t="str">
-        <x:v>Греф опроверг договоренность Сбера о покупке доли в Озоне - БКС Экспресс</x:v>
+        <x:v>«Яндекс» вновь выходит на долговой рынок: разбор двойного размещения облигаций - Финам</x:v>
       </x:c>
       <x:c r="AC18" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -2150,25 +2150,25 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="41" t="str">
-        <x:v>DL-2e27ebc506e38656</x:v>
+        <x:v>DL-c0e4b0469b5eb473</x:v>
       </x:c>
       <x:c r="B19" s="43" t="n">
-        <x:v>46176</x:v>
+        <x:v>46177</x:v>
       </x:c>
       <x:c r="C19" s="41" t="str">
         <x:v>M&amp;A</x:v>
       </x:c>
       <x:c r="D19" s="41" t="str">
-        <x:v>Completed</x:v>
+        <x:v>Reported</x:v>
       </x:c>
       <x:c r="E19" s="41" t="str">
-        <x:v>Авто.ру</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="F19" s="41" t="str">
-        <x:v>Т-Технологии</x:v>
+        <x:v>Ozon</x:v>
       </x:c>
       <x:c r="G19" s="41" t="str">
-        <x:v>Technology</x:v>
+        <x:v>Not classified</x:v>
       </x:c>
       <x:c r="H19" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -2206,22 +2206,22 @@
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="W19" s="41" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X19" s="41" t="str">
         <x:v>unverified</x:v>
       </x:c>
       <x:c r="Y19" s="41" t="str">
-        <x:v>YDEX</x:v>
+        <x:v>OZON</x:v>
       </x:c>
       <x:c r="Z19" s="41" t="str">
         <x:v>БКС Экспресс</x:v>
       </x:c>
       <x:c r="AA19" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMiowFBVV95cUxNQ0ZvSEhWU1BqUzkyWi1YOWNOR0lab1kxRldxMFV5YllQQWp4Y0xFcjNLTXpHMUFJcnhicWI2RGNuUWRpUndBS0ZlQ2U0c05yWDlTeWZnWG05QjhZR0VWVW5IV19aSkdwa0d1UWpMWC1tLWdicjNtUVk4M2QtbFhsQkFxejdjZ2lLNDYxWTlwUWwyMzhqZ20zelY5SkZpZjBjYzZv?oc=5</x:v>
+        <x:v>https://bcs-express.ru/novosti-i-analitika/gref-oproverg-dogovorennost-sbera-o-pokupke-doli-v-ozone</x:v>
       </x:c>
       <x:c r="AB19" s="41" t="str">
-        <x:v>Т-Технологии закрыли сделку по покупке Авто.ру у Яндекса - БКС Экспресс</x:v>
+        <x:v>Греф опроверг договоренность Сбера о покупке доли в Озоне - БКС Экспресс</x:v>
       </x:c>
       <x:c r="AC19" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -2229,10 +2229,10 @@
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="41" t="str">
-        <x:v>DL-360af9a222272dcf</x:v>
+        <x:v>DL-2e27ebc506e38656</x:v>
       </x:c>
       <x:c r="B20" s="43" t="n">
-        <x:v>46175</x:v>
+        <x:v>46176</x:v>
       </x:c>
       <x:c r="C20" s="41" t="str">
         <x:v>M&amp;A</x:v>
@@ -2241,10 +2241,10 @@
         <x:v>Completed</x:v>
       </x:c>
       <x:c r="E20" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>Авто.ру</x:v>
       </x:c>
       <x:c r="F20" s="41" t="str">
-        <x:v>Yandex</x:v>
+        <x:v>Т-Технологии</x:v>
       </x:c>
       <x:c r="G20" s="41" t="str">
         <x:v>Technology</x:v>
@@ -2282,25 +2282,25 @@
         <x:v>Acquisition / disposal</x:v>
       </x:c>
       <x:c r="V20" s="41" t="str">
-        <x:v>частных инвесторов Яндекса содержит информацию про бизнесы и технологии компании, а также географию присутствия, финансовые результаты, важные новости и многое другое о компании и её рынках</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="W20" s="41" t="n">
-        <x:v>9</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="X20" s="41" t="str">
-        <x:v>confirmed</x:v>
+        <x:v>unverified</x:v>
       </x:c>
       <x:c r="Y20" s="41" t="str">
         <x:v>YDEX</x:v>
       </x:c>
       <x:c r="Z20" s="41" t="str">
-        <x:v>Yandex Investor Relations</x:v>
+        <x:v>БКС Экспресс</x:v>
       </x:c>
       <x:c r="AA20" s="41" t="str">
-        <x:v>https://ir.yandex.ru/press-releases?year=2026&amp;id=02-06-2026-04</x:v>
+        <x:v>https://bcs-express.ru/novosti-i-analitika/t-tekhnologii-zakryli-sdelku-po-pokupke-avto-ru-u-iandeksa</x:v>
       </x:c>
       <x:c r="AB20" s="41" t="str">
-        <x:v>Яндекс закрыл сделку по продаже Авто.ру</x:v>
+        <x:v>Т-Технологии закрыли сделку по покупке Авто.ру у Яндекса - БКС Экспресс</x:v>
       </x:c>
       <x:c r="AC20" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -2308,7 +2308,7 @@
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="41" t="str">
-        <x:v>DL-a78cf0af94927306</x:v>
+        <x:v>DL-5eba3b27a4e84dd3</x:v>
       </x:c>
       <x:c r="B21" s="43" t="n">
         <x:v>46175</x:v>
@@ -2317,7 +2317,7 @@
         <x:v>M&amp;A</x:v>
       </x:c>
       <x:c r="D21" s="41" t="str">
-        <x:v>Reported</x:v>
+        <x:v>Completed</x:v>
       </x:c>
       <x:c r="E21" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -2329,14 +2329,12 @@
         <x:v>Technology</x:v>
       </x:c>
       <x:c r="H21" s="41" t="str">
-        <x:v>Russia</x:v>
-      </x:c>
-      <x:c r="I21" s="44" t="n">
-        <x:v>35000000000</x:v>
-      </x:c>
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I21" s="44"/>
       <x:c r="J21" s="44"/>
       <x:c r="K21" s="41" t="str">
-        <x:v>RUB</x:v>
+        <x:v>NOT DISCLOSED</x:v>
       </x:c>
       <x:c r="L21" s="45"/>
       <x:c r="M21" s="41" t="str">
@@ -2363,25 +2361,25 @@
         <x:v>Acquisition / disposal</x:v>
       </x:c>
       <x:c r="V21" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>частных инвесторов Яндекса содержит информацию про бизнесы и технологии компании, а также географию присутствия, финансовые результаты, важные новости и многое другое о компании и её рынках</x:v>
       </x:c>
       <x:c r="W21" s="41" t="n">
-        <x:v>4</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="X21" s="41" t="str">
-        <x:v>unverified</x:v>
+        <x:v>confirmed</x:v>
       </x:c>
       <x:c r="Y21" s="41" t="str">
         <x:v>YDEX</x:v>
       </x:c>
       <x:c r="Z21" s="41" t="str">
-        <x:v>Финам</x:v>
+        <x:v>Yandex Investor Relations</x:v>
       </x:c>
       <x:c r="AA21" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMilgFBVV95cUxQWFk5YjhpaHc0S3BiTEpUVzFndHdkTDVmY0EtRDhFQ0pYcjBvWUF3V3FZUFhaUjhEQ1FXT0FDdWU1dGdtVmJ1Z1l5bmhGcVBwdjhsWTZVNG10dWhmTlNGbGZqV2cwRUoyaEdZS3c0dEx1MV8ySGpfX2ljQnhfemFELThnSDc3T09JZ1lOZW45Yk93YmYyb3c?oc=5</x:v>
+        <x:v>https://ir.yandex.ru/press-releases?year=2026&amp;id=02-06-2026-04</x:v>
       </x:c>
       <x:c r="AB21" s="41" t="str">
-        <x:v>"Яндекс" продал "Авто.ру" "Т-Технологиям" за 35 млрд рублей - Финам</x:v>
+        <x:v>Яндекс закрыл сделку по продаже Авто.ру</x:v>
       </x:c>
       <x:c r="AC21" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -2389,10 +2387,10 @@
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="41" t="str">
-        <x:v>DL-a4f6a4524ddca358</x:v>
+        <x:v>DL-a78cf0af94927306</x:v>
       </x:c>
       <x:c r="B22" s="43" t="n">
-        <x:v>46170</x:v>
+        <x:v>46175</x:v>
       </x:c>
       <x:c r="C22" s="41" t="str">
         <x:v>M&amp;A</x:v>
@@ -2404,18 +2402,20 @@
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="F22" s="41" t="str">
-        <x:v>Ozon</x:v>
+        <x:v>Yandex</x:v>
       </x:c>
       <x:c r="G22" s="41" t="str">
-        <x:v>Not classified</x:v>
+        <x:v>Technology</x:v>
       </x:c>
       <x:c r="H22" s="41" t="str">
-        <x:v>Not disclosed</x:v>
-      </x:c>
-      <x:c r="I22" s="44"/>
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I22" s="44" t="n">
+        <x:v>35000000000</x:v>
+      </x:c>
       <x:c r="J22" s="44"/>
       <x:c r="K22" s="41" t="str">
-        <x:v>NOT DISCLOSED</x:v>
+        <x:v>RUB</x:v>
       </x:c>
       <x:c r="L22" s="45"/>
       <x:c r="M22" s="41" t="str">
@@ -2445,22 +2445,22 @@
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="W22" s="41" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X22" s="41" t="str">
         <x:v>unverified</x:v>
       </x:c>
       <x:c r="Y22" s="41" t="str">
-        <x:v>OZON</x:v>
+        <x:v>YDEX</x:v>
       </x:c>
       <x:c r="Z22" s="41" t="str">
-        <x:v>Интерфакс</x:v>
+        <x:v>Финам</x:v>
       </x:c>
       <x:c r="AA22" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE9GMUxsS2ZKR2JaU2ZhY1hRSmoteVVNM1V6U2pJQnFGblRETXk1b0pLLXl3VXNvREgwdVg4dmNyc3VBVWxFZ1ZjUmxILXlrWU80VVHSAUtBVV95cUxPM21YSmF3aGRJQThYblp1MEEyNGNLSnR0SzlnTG1ITWtJWXY5bU1Jdm9kWU5nRjRYOUoxRlFscTB5X2NHVUlWYmtDX0k?oc=5</x:v>
+        <x:v>https://www.finam.ru/publications/item/yandeks-prodal-avtoru-t-tekhnologiyam-20260602-1802/</x:v>
       </x:c>
       <x:c r="AB22" s="41" t="str">
-        <x:v>"Ъ" сообщил о переговорах структур Сбера с АФК "Система" о покупке доли в Ozon - Интерфакс</x:v>
+        <x:v>"Яндекс" продал "Авто.ру" "Т-Технологиям" за 35 млрд рублей - Финам</x:v>
       </x:c>
       <x:c r="AC22" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -2468,33 +2468,35 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="41" t="str">
-        <x:v>DL-e08040bba3b952c1</x:v>
+        <x:v>DL-1f4ea43fab1ad3e7</x:v>
       </x:c>
       <x:c r="B23" s="43" t="n">
-        <x:v>46170</x:v>
+        <x:v>46171</x:v>
       </x:c>
       <x:c r="C23" s="41" t="str">
         <x:v>M&amp;A</x:v>
       </x:c>
       <x:c r="D23" s="41" t="str">
-        <x:v>Reported</x:v>
+        <x:v>Potential</x:v>
       </x:c>
       <x:c r="E23" s="41" t="str">
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="F23" s="41" t="str">
-        <x:v>Yandex</x:v>
+        <x:v>Ozon</x:v>
       </x:c>
       <x:c r="G23" s="41" t="str">
         <x:v>Not classified</x:v>
       </x:c>
       <x:c r="H23" s="41" t="str">
-        <x:v>Not disclosed</x:v>
-      </x:c>
-      <x:c r="I23" s="44"/>
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I23" s="44" t="n">
+        <x:v>300000000000</x:v>
+      </x:c>
       <x:c r="J23" s="44"/>
       <x:c r="K23" s="41" t="str">
-        <x:v>NOT DISCLOSED</x:v>
+        <x:v>RUB</x:v>
       </x:c>
       <x:c r="L23" s="45"/>
       <x:c r="M23" s="41" t="str">
@@ -2530,16 +2532,16 @@
         <x:v>unverified</x:v>
       </x:c>
       <x:c r="Y23" s="41" t="str">
-        <x:v>YDEX</x:v>
+        <x:v>OZON</x:v>
       </x:c>
       <x:c r="Z23" s="41" t="str">
-        <x:v>Финам</x:v>
+        <x:v>Сибирское информационное агентство</x:v>
       </x:c>
       <x:c r="AA23" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMirAFBVV95cUxNSlk2WU9xYjNqM1AwRkNGOV9BYnhzQVg3VlRaaWJlT01VVDNrYklwUjY4SFZfdjZQLVlHZEpxYm0tVmpDUFN5a190bUU0MnFnb2VFMFMyQ2E1OWlyQ2djRWwtdWMyN3F5NXRYamZkUmFhMkk4UlFZQXFDOVB2RE9uNjZkdFFMbGZFT0dWOTN4MjZDbXZmMzNSOUNlOXVaZjJGcmM4QnZiM0I3QUhM?oc=5</x:v>
+        <x:v>https://sia.ru/?section\=484\&amp;action\=show_news\&amp;id\=16828609</x:v>
       </x:c>
       <x:c r="AB23" s="41" t="str">
-        <x:v>"Яндекс" стал основным претендентом на покупку "Островка" - Финам</x:v>
+        <x:v>«Сбер» может стать совладельцем Ozon в сделке на 300 млрд рублей? - Сибирское информационное агентство</x:v>
       </x:c>
       <x:c r="AC23" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -2547,7 +2549,7 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="41" t="str">
-        <x:v>DL-4ffd21b67b0042b7</x:v>
+        <x:v>DL-a4f6a4524ddca358</x:v>
       </x:c>
       <x:c r="B24" s="43" t="n">
         <x:v>46170</x:v>
@@ -2556,7 +2558,7 @@
         <x:v>M&amp;A</x:v>
       </x:c>
       <x:c r="D24" s="41" t="str">
-        <x:v>Potential</x:v>
+        <x:v>Reported</x:v>
       </x:c>
       <x:c r="E24" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -2568,14 +2570,12 @@
         <x:v>Not classified</x:v>
       </x:c>
       <x:c r="H24" s="41" t="str">
-        <x:v>Russia</x:v>
-      </x:c>
-      <x:c r="I24" s="44" t="n">
-        <x:v>30000000000</x:v>
-      </x:c>
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I24" s="44"/>
       <x:c r="J24" s="44"/>
       <x:c r="K24" s="41" t="str">
-        <x:v>RUB</x:v>
+        <x:v>NOT DISCLOSED</x:v>
       </x:c>
       <x:c r="L24" s="45"/>
       <x:c r="M24" s="41" t="str">
@@ -2605,7 +2605,7 @@
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="W24" s="41" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X24" s="41" t="str">
         <x:v>unverified</x:v>
@@ -2614,13 +2614,13 @@
         <x:v>OZON</x:v>
       </x:c>
       <x:c r="Z24" s="41" t="str">
-        <x:v>RB.ru</x:v>
+        <x:v>Интерфакс</x:v>
       </x:c>
       <x:c r="AA24" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMixAFBVV95cUxOZGNTQll0aVZOSDFubmt0bU5BdWNXNVA0WFZaOFdKa3B1VkctYXdkU25tLVdQSlNjNjFBYzA0ZzFYbVZKRnNKMk9Cb3RkSFYtaVFUR0JVc0pMNkNFUnFaeUdJX1JKRWlqMUZKeHo3UTZNaDU3LUc2RWxDd2FMYTUyUTEtY1dhcHFUVlJ4ZDlDS19SVkF5a0tqS0duRkljSWNNN0NLajJrSDZVdDNNR2ZfNVlyTVBvb0xFOXdFYmtpb2ZjTXRi?oc=5</x:v>
+        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE9GMUxsS2ZKR2JaU2ZhY1hRSmoteVVNM1V6U2pJQnFGblRETXk1b0pLLXl3VXNvREgwdVg4dmNyc3VBVWxFZ1ZjUmxILXlrWU80VVHSAUtBVV95cUxPM21YSmF3aGRJQThYblp1MEEyNGNLSnR0SzlnTG1ITWtJWXY5bU1Jdm9kWU5nRjRYOUoxRlFscTB5X2NHVUlWYmtDX0k?oc=5</x:v>
       </x:c>
       <x:c r="AB24" s="41" t="str">
-        <x:v>Сбер может купить долю инвесткомпании АФК «Система» в Ozon за 30 млрд рублей - RB.ru</x:v>
+        <x:v>"Ъ" сообщил о переговорах структур Сбера с АФК "Система" о покупке доли в Ozon - Интерфакс</x:v>
       </x:c>
       <x:c r="AC24" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -2628,7 +2628,7 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="41" t="str">
-        <x:v>DL-ca53a880a58471a3</x:v>
+        <x:v>DL-e08040bba3b952c1</x:v>
       </x:c>
       <x:c r="B25" s="43" t="n">
         <x:v>46170</x:v>
@@ -2643,10 +2643,10 @@
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="F25" s="41" t="str">
-        <x:v>Ozon</x:v>
+        <x:v>Yandex</x:v>
       </x:c>
       <x:c r="G25" s="41" t="str">
-        <x:v>Financials</x:v>
+        <x:v>Not classified</x:v>
       </x:c>
       <x:c r="H25" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -2690,16 +2690,16 @@
         <x:v>unverified</x:v>
       </x:c>
       <x:c r="Y25" s="41" t="str">
-        <x:v>OZON</x:v>
+        <x:v>YDEX</x:v>
       </x:c>
       <x:c r="Z25" s="41" t="str">
-        <x:v>Альфа-Банк</x:v>
+        <x:v>Финам</x:v>
       </x:c>
       <x:c r="AA25" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMihgFBVV95cUxOVVc5b2xRd2dWREJQMEVGcEVKSlhNdFFmTjNGYWVnRkRNbHlmZ29zRGdzUjlrS2VQQjJxM0RhUTh4bnhIWnhNb3ZnQ2VhYmJqdEI1Q0dpVHZOWlNCLXNUanVlYTdhNmQ2TkpGZ1hFVG0xclRWNWZvZUhmeXdua1BtUDNpMm9LZw?oc=5</x:v>
+        <x:v>https://www.finam.ru/publications/item/yandeks-stal-osnovnym-pretendentom-na-pokupku-ostrovka-20260528-0928/</x:v>
       </x:c>
       <x:c r="AB25" s="41" t="str">
-        <x:v>Сбер забирает Ozon. Инсайд или вброс? Кто выиграет от сделки? - Альфа-Банк</x:v>
+        <x:v>"Яндекс" стал основным претендентом на покупку "Островка" - Финам</x:v>
       </x:c>
       <x:c r="AC25" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -2707,7 +2707,7 @@
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="41" t="str">
-        <x:v>DL-eee2cc5f0b30c3ba</x:v>
+        <x:v>DL-4ffd21b67b0042b7</x:v>
       </x:c>
       <x:c r="B26" s="43" t="n">
         <x:v>46170</x:v>
@@ -2716,7 +2716,7 @@
         <x:v>M&amp;A</x:v>
       </x:c>
       <x:c r="D26" s="41" t="str">
-        <x:v>Reported</x:v>
+        <x:v>Potential</x:v>
       </x:c>
       <x:c r="E26" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -2725,15 +2725,17 @@
         <x:v>Ozon</x:v>
       </x:c>
       <x:c r="G26" s="41" t="str">
-        <x:v>Financials</x:v>
+        <x:v>Not classified</x:v>
       </x:c>
       <x:c r="H26" s="41" t="str">
-        <x:v>Not disclosed</x:v>
-      </x:c>
-      <x:c r="I26" s="44"/>
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I26" s="44" t="n">
+        <x:v>30000000000</x:v>
+      </x:c>
       <x:c r="J26" s="44"/>
       <x:c r="K26" s="41" t="str">
-        <x:v>NOT DISCLOSED</x:v>
+        <x:v>RUB</x:v>
       </x:c>
       <x:c r="L26" s="45"/>
       <x:c r="M26" s="41" t="str">
@@ -2772,13 +2774,13 @@
         <x:v>OZON</x:v>
       </x:c>
       <x:c r="Z26" s="41" t="str">
-        <x:v>Альфа-Банк</x:v>
+        <x:v>RB.ru</x:v>
       </x:c>
       <x:c r="AA26" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMihgFBVV95cUxPa1Utd0tlY3RsT1JNSUZEcGdEdG84bFBJYlc0eDVEand3UnppVTduOUZPMUo2UHJ6SmxSSGgwekt6cDFyS3ByZDRxR1RrQjNJWk5VUlB4U2UyM0pSa3FiNnRscllQT19fZ2pEb0xQTU4xdXNXTi1PbWxNTF9LRTg2RTh3VHoyZw?oc=5</x:v>
+        <x:v>https://rb.ru/news/sber-mozhet-kupit-akcii-v-ozon-na-30-mlrd-investkompaniya-afk-sistema-otricaet-informaciyu-o-prodazhe-doli/</x:v>
       </x:c>
       <x:c r="AB26" s="41" t="str">
-        <x:v>Озон и Сбер, сделки не будет? - Альфа-Банк</x:v>
+        <x:v>Сбер может купить долю инвесткомпании АФК «Система» в Ozon за 30 млрд рублей - RB.ru</x:v>
       </x:c>
       <x:c r="AC26" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -2786,10 +2788,10 @@
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="41" t="str">
-        <x:v>DL-54c26c1e05d520bd</x:v>
+        <x:v>DL-ca53a880a58471a3</x:v>
       </x:c>
       <x:c r="B27" s="43" t="n">
-        <x:v>46167</x:v>
+        <x:v>46170</x:v>
       </x:c>
       <x:c r="C27" s="41" t="str">
         <x:v>M&amp;A</x:v>
@@ -2804,7 +2806,7 @@
         <x:v>Ozon</x:v>
       </x:c>
       <x:c r="G27" s="41" t="str">
-        <x:v>Not classified</x:v>
+        <x:v>Financials</x:v>
       </x:c>
       <x:c r="H27" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -2816,7 +2818,7 @@
       </x:c>
       <x:c r="L27" s="45"/>
       <x:c r="M27" s="41" t="str">
-        <x:v>Shares</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="N27" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -2851,13 +2853,13 @@
         <x:v>OZON</x:v>
       </x:c>
       <x:c r="Z27" s="41" t="str">
-        <x:v>Финам</x:v>
+        <x:v>Альфа-Банк</x:v>
       </x:c>
       <x:c r="AA27" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMirwFBVV95cUxNckFiOGoyLVd2REpiUVVDaWp6NzF5Y1laekdUZnhnWUJYS3ZteHpxSGd6OElyTUwyZXVFWjgwWmRFclVXbV9FR2xKS2dHZDdoZEZsUEMycy01ZUxUMU03eTBybC1NQlZ5dDVtZHp4NTdVdEhzak9jVlgwZ2ZXTVA0SnIyM0RUTG5saEdQWG5FTDIwUmE1MHllN2xOek1HeXlRS2RtSDhCeFZfaElpRy1F?oc=5</x:v>
+        <x:v>https://alfabank.ru/alfa-investor/posts/t/2af58b47-265b-f111-91c6-0050569e1fd0/</x:v>
       </x:c>
       <x:c r="AB27" s="41" t="str">
-        <x:v>25.05.26 Последний день покупки акций “Озона” под дивиденды - 25 мая - Финам</x:v>
+        <x:v>Сбер забирает Ozon. Инсайд или вброс? Кто выиграет от сделки? - Альфа-Банк</x:v>
       </x:c>
       <x:c r="AC27" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -2865,22 +2867,22 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="41" t="str">
-        <x:v>DL-38b5154e2b53df8c</x:v>
+        <x:v>DL-eee2cc5f0b30c3ba</x:v>
       </x:c>
       <x:c r="B28" s="43" t="n">
-        <x:v>46157</x:v>
+        <x:v>46170</x:v>
       </x:c>
       <x:c r="C28" s="41" t="str">
-        <x:v>ECM</x:v>
+        <x:v>M&amp;A</x:v>
       </x:c>
       <x:c r="D28" s="41" t="str">
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E28" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F28" s="41" t="str">
         <x:v>Ozon</x:v>
-      </x:c>
-      <x:c r="F28" s="41" t="str">
-        <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="G28" s="41" t="str">
         <x:v>Financials</x:v>
@@ -2895,7 +2897,7 @@
       </x:c>
       <x:c r="L28" s="45"/>
       <x:c r="M28" s="41" t="str">
-        <x:v>Not applicable</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="N28" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -2915,7 +2917,7 @@
         <x:f>IFERROR(IF(AND($J28&gt;0,$P28&gt;0,$K28=$R28),$J28/$P28,""),"")</x:f>
       </x:c>
       <x:c r="U28" s="41" t="str">
-        <x:v>Equity issuance</x:v>
+        <x:v>Acquisition / disposal</x:v>
       </x:c>
       <x:c r="V28" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -2930,13 +2932,13 @@
         <x:v>OZON</x:v>
       </x:c>
       <x:c r="Z28" s="41" t="str">
-        <x:v>Финам</x:v>
+        <x:v>Альфа-Банк</x:v>
       </x:c>
       <x:c r="AA28" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMi7gFBVV95cUxOVkF3VWdna082MXVoUDVVTnpvUjV1Y2tnMGRwRkYwRlhnUE1RZldyUGVCcklzSWdXQmhMYkRaNi1nZGp5LVdzU3RRWV9kTnpJbFFxU2lCSGR1clk5R3NIaDZHeDRxTUF6VkZHV2F4dTAtS0Jjd1FEM281dU5YZ3lMRWROOVNiT29mVG1EcXRCcmdmaDZ5OFpzTmRHRWpidFMzdjktZHhRMGpxZ0pUZmw0MDRGNjZEMWFPVC1EcFFFa1NFNzJlNk1oUnI1cGFpc2ZDYWk0LUxuaVN1LUdvU25hTXpINjhQZGNHdzJIdElR?oc=5</x:v>
+        <x:v>https://alfabank.ru/alfa-investor/posts/t/06d3da91-dd5a-f111-91c6-0050569e1fd0/</x:v>
       </x:c>
       <x:c r="AB28" s="41" t="str">
-        <x:v>Отчетности «Займера», БСП и «Совкомбанка», дивидендный вопрос у «Озона» и «МД Медикал» - основные события 15 мая 15.05.2026 - Финам</x:v>
+        <x:v>Озон и Сбер, сделки не будет? - Альфа-Банк</x:v>
       </x:c>
       <x:c r="AC28" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -2944,10 +2946,10 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="41" t="str">
-        <x:v>DL-32f044efd41bc454</x:v>
+        <x:v>DL-4d23d3c416f43c48</x:v>
       </x:c>
       <x:c r="B29" s="43" t="n">
-        <x:v>46157</x:v>
+        <x:v>46170</x:v>
       </x:c>
       <x:c r="C29" s="41" t="str">
         <x:v>M&amp;A</x:v>
@@ -2959,7 +2961,7 @@
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="F29" s="41" t="str">
-        <x:v>VKCO</x:v>
+        <x:v>Ozon</x:v>
       </x:c>
       <x:c r="G29" s="41" t="str">
         <x:v>Not classified</x:v>
@@ -2972,7 +2974,9 @@
       <x:c r="K29" s="41" t="str">
         <x:v>NOT DISCLOSED</x:v>
       </x:c>
-      <x:c r="L29" s="45"/>
+      <x:c r="L29" s="45" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
       <x:c r="M29" s="41" t="str">
         <x:v>Shares</x:v>
       </x:c>
@@ -3000,20 +3004,22 @@
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="W29" s="41" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X29" s="41" t="str">
         <x:v>unverified</x:v>
       </x:c>
-      <x:c r="Y29" s="41" t="str"/>
+      <x:c r="Y29" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
       <x:c r="Z29" s="41" t="str">
-        <x:v>Интерфакс</x:v>
+        <x:v>Финам</x:v>
       </x:c>
       <x:c r="AA29" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1SRWp6YUhObThSanNWWnBCQjlnX0xPVW1fQzJPSlJxM3JxcVhVTWlJaWZVcW5VNXFTQjU0RkJ6cC0wem9DTUNLZWlXeXZmMDhyUlHSAUtBVV95cUxPaFhNLWM1eThHQVJpOEg0TEpxT1BjRk5IdTEyYmFOdzNCOEluQmtLU3pmcXViOW5PM1gwR3ZsT2RhZEVCLTkwQ1RMZk0?oc=5</x:v>
+        <x:v>https://www.finam.ru/publications/item/aktsii-afk-sistema-podskochili-na-7-na-soobshcheniyakh-o-pokupke-doli-ozona-strukturami-sbera-20260528-1910/</x:v>
       </x:c>
       <x:c r="AB29" s="41" t="str">
-        <x:v>Трамп в I квартале совершал сделки с акциями Nvidia и Boeing - Интерфакс</x:v>
+        <x:v>Акции АФК "Система" подскочили на 7% на сообщениях о покупке доли "Озона" структурами "Сбера" - Финам</x:v>
       </x:c>
       <x:c r="AC29" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -3021,39 +3027,37 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="41" t="str">
-        <x:v>DL-71608263fecb5e53</x:v>
+        <x:v>DL-54c26c1e05d520bd</x:v>
       </x:c>
       <x:c r="B30" s="43" t="n">
-        <x:v>46150</x:v>
+        <x:v>46167</x:v>
       </x:c>
       <x:c r="C30" s="41" t="str">
-        <x:v>DCM</x:v>
+        <x:v>M&amp;A</x:v>
       </x:c>
       <x:c r="D30" s="41" t="str">
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E30" s="41" t="str">
-        <x:v>Делимобиль</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="F30" s="41" t="str">
-        <x:v>Not applicable</x:v>
+        <x:v>Ozon</x:v>
       </x:c>
       <x:c r="G30" s="41" t="str">
         <x:v>Not classified</x:v>
       </x:c>
       <x:c r="H30" s="41" t="str">
-        <x:v>Russia</x:v>
-      </x:c>
-      <x:c r="I30" s="44" t="n">
-        <x:v>1900000000</x:v>
-      </x:c>
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I30" s="44"/>
       <x:c r="J30" s="44"/>
       <x:c r="K30" s="41" t="str">
-        <x:v>RUB</x:v>
+        <x:v>NOT DISCLOSED</x:v>
       </x:c>
       <x:c r="L30" s="45"/>
       <x:c r="M30" s="41" t="str">
-        <x:v>Not applicable</x:v>
+        <x:v>Shares</x:v>
       </x:c>
       <x:c r="N30" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3073,26 +3077,28 @@
         <x:f>IFERROR(IF(AND($J30&gt;0,$P30&gt;0,$K30=$R30),$J30/$P30,""),"")</x:f>
       </x:c>
       <x:c r="U30" s="41" t="str">
-        <x:v>Bonds</x:v>
+        <x:v>Acquisition / disposal</x:v>
       </x:c>
       <x:c r="V30" s="41" t="str">
-        <x:v>погашения выпуска облигаций на 1,9 млрд рублей</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="W30" s="41" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X30" s="41" t="str">
         <x:v>unverified</x:v>
       </x:c>
-      <x:c r="Y30" s="41" t="str"/>
+      <x:c r="Y30" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
       <x:c r="Z30" s="41" t="str">
-        <x:v>Интерфакс</x:v>
+        <x:v>Финам</x:v>
       </x:c>
       <x:c r="AA30" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE5rRHd6NXMzNkpDcVZDdVR4NXhZN185LXRRSDMzVzZiUGd4cmNqV1BydzRLTnh4cHJnU19qNnQ1X05XMDl6VnBjVlBXY0NUOUZ3VlHSAUtBVV95cUxQOHVvOS00aURkZ3lDUGZ6Sk9kYTVFSDJhcGNJQk1PVVR2ZFJwWnZlRGZ4eW85TS15QUs4bmkxOWUzQW5PbGpDeUVnOVk?oc=5</x:v>
+        <x:v>https://www.finam.ru/publications/item/posledniy-den-pokupki-aktsiy-ozona-pod-dividendy-25-maya-20260525-0652/</x:v>
       </x:c>
       <x:c r="AB30" s="41" t="str">
-        <x:v>"Делимобиль" перечислил в НРД средства для погашения выпуска облигаций на 1,9 млрд рублей - Интерфакс</x:v>
+        <x:v>25.05.26 Последний день покупки акций “Озона” под дивиденды - 25 мая - Финам</x:v>
       </x:c>
       <x:c r="AC30" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -3100,10 +3106,10 @@
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="41" t="str">
-        <x:v>DL-2848bdd8b067faa2</x:v>
+        <x:v>DL-38b5154e2b53df8c</x:v>
       </x:c>
       <x:c r="B31" s="43" t="n">
-        <x:v>46147</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="C31" s="41" t="str">
         <x:v>ECM</x:v>
@@ -3112,23 +3118,21 @@
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E31" s="41" t="str">
-        <x:v>Yandex</x:v>
+        <x:v>Ozon</x:v>
       </x:c>
       <x:c r="F31" s="41" t="str">
         <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="G31" s="41" t="str">
-        <x:v>Not classified</x:v>
+        <x:v>Financials</x:v>
       </x:c>
       <x:c r="H31" s="41" t="str">
-        <x:v>Russia</x:v>
-      </x:c>
-      <x:c r="I31" s="44" t="n">
-        <x:v>50000000000</x:v>
-      </x:c>
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I31" s="44"/>
       <x:c r="J31" s="44"/>
       <x:c r="K31" s="41" t="str">
-        <x:v>RUB</x:v>
+        <x:v>NOT DISCLOSED</x:v>
       </x:c>
       <x:c r="L31" s="45"/>
       <x:c r="M31" s="41" t="str">
@@ -3164,16 +3168,16 @@
         <x:v>unverified</x:v>
       </x:c>
       <x:c r="Y31" s="41" t="str">
-        <x:v>YDEX</x:v>
+        <x:v>OZON</x:v>
       </x:c>
       <x:c r="Z31" s="41" t="str">
-        <x:v>БКС Экспресс</x:v>
+        <x:v>Финам</x:v>
       </x:c>
       <x:c r="AA31" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMikwFBVV95cUxPbkRNMVpoTFN4cXlrOWRya3A4SW1Dd09IUHIzMUw3emMzY1hZckpPRWtMclI2aTllZTRQTlRwUmNGNVp4X1hPV041elJSWGhtVS1kM0VGMFpWdmZIcDRmTS04MjBSb3FoVG5xZWdhY0REZkxLMTMxTE1PeF92VW5SRkxDYVNrVGVuNVFTSlRfaFFFeWc?oc=5</x:v>
+        <x:v>https://www.finam.ru/publications/item/otchetnosti-zaymera-bsp-i-sovkombanka-dividendnyy-vopros-u-ozona-i-md-medikal-osnovnye-sobytiya-15-maya-20260515-0900/</x:v>
       </x:c>
       <x:c r="AB31" s="41" t="str">
-        <x:v>Яндекс одобрил выкуп акций на 50 млрд рублей - БКС Экспресс</x:v>
+        <x:v>Отчетности «Займера», БСП и «Совкомбанка», дивидендный вопрос у «Озона» и «МД Медикал» - основные события 15 мая 15.05.2026 - Финам</x:v>
       </x:c>
       <x:c r="AC31" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -3181,25 +3185,25 @@
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="41" t="str">
-        <x:v>DL-3d4a31cc3b7936d0</x:v>
+        <x:v>DL-32f044efd41bc454</x:v>
       </x:c>
       <x:c r="B32" s="43" t="n">
-        <x:v>46146</x:v>
+        <x:v>46157</x:v>
       </x:c>
       <x:c r="C32" s="41" t="str">
-        <x:v>ECM</x:v>
+        <x:v>M&amp;A</x:v>
       </x:c>
       <x:c r="D32" s="41" t="str">
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E32" s="41" t="str">
-        <x:v>Yandex</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="F32" s="41" t="str">
-        <x:v>Not applicable</x:v>
+        <x:v>VKCO</x:v>
       </x:c>
       <x:c r="G32" s="41" t="str">
-        <x:v>Energy</x:v>
+        <x:v>Not classified</x:v>
       </x:c>
       <x:c r="H32" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3211,7 +3215,7 @@
       </x:c>
       <x:c r="L32" s="45"/>
       <x:c r="M32" s="41" t="str">
-        <x:v>Not applicable</x:v>
+        <x:v>Shares</x:v>
       </x:c>
       <x:c r="N32" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3231,28 +3235,26 @@
         <x:f>IFERROR(IF(AND($J32&gt;0,$P32&gt;0,$K32=$R32),$J32/$P32,""),"")</x:f>
       </x:c>
       <x:c r="U32" s="41" t="str">
-        <x:v>Equity issuance</x:v>
+        <x:v>Acquisition / disposal</x:v>
       </x:c>
       <x:c r="V32" s="41" t="str">
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="W32" s="41" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="X32" s="41" t="str">
         <x:v>unverified</x:v>
       </x:c>
-      <x:c r="Y32" s="41" t="str">
-        <x:v>YDEX, OZON</x:v>
-      </x:c>
+      <x:c r="Y32" s="41" t="str"/>
       <x:c r="Z32" s="41" t="str">
-        <x:v>SberCIB</x:v>
+        <x:v>Интерфакс</x:v>
       </x:c>
       <x:c r="AA32" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQZEltanhoOVlVS2FSRnNObHRXRkJnUEpjZ1VRXzB4czdNUFJOVzVxNU1XcGdxX1gxNmhYcHVrWFh1bXZMRTA5UUZHczhJNlJLYl8wVzdtZmdWYjRQZVB4TDVRNHNURVI1UkhkeVFpNXN4WnhUekFURDhiSlFyZDAtUFMtNW1VR3JEZFUwMEktbmFIYk52Uy02ay1IQTdYZHE2Zm10Vkw1LVBLdw?oc=5</x:v>
+        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1SRWp6YUhObThSanNWWnBCQjlnX0xPVW1fQzJPSlJxM3JxcVhVTWlJaWZVcW5VNXFTQjU0RkJ6cC0wem9DTUNLZWlXeXZmMDhyUlHSAUtBVV95cUxPaFhNLWM1eThHQVJpOEg0TEpxT1BjRk5IdTEyYmFOdzNCOEluQmtLU3pmcXViOW5PM1gwR3ZsT2RhZEVCLTkwQ1RMZk0?oc=5</x:v>
       </x:c>
       <x:c r="AB32" s="41" t="str">
-        <x:v>Результаты Ozon, ДОМ. РФ, дивиденды Яндекса и Татнефти и другие новости недели - SberCIB</x:v>
+        <x:v>Трамп в I квартале совершал сделки с акциями Nvidia и Boeing - Интерфакс</x:v>
       </x:c>
       <x:c r="AC32" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -3260,37 +3262,39 @@
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="41" t="str">
-        <x:v>DL-6bc0569f7ac374fe</x:v>
+        <x:v>DL-71608263fecb5e53</x:v>
       </x:c>
       <x:c r="B33" s="43" t="n">
-        <x:v>46139</x:v>
+        <x:v>46150</x:v>
       </x:c>
       <x:c r="C33" s="41" t="str">
-        <x:v>M&amp;A</x:v>
+        <x:v>DCM</x:v>
       </x:c>
       <x:c r="D33" s="41" t="str">
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E33" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>Делимобиль</x:v>
       </x:c>
       <x:c r="F33" s="41" t="str">
-        <x:v>Ozon</x:v>
+        <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="G33" s="41" t="str">
-        <x:v>Financials</x:v>
+        <x:v>Not classified</x:v>
       </x:c>
       <x:c r="H33" s="41" t="str">
-        <x:v>Not disclosed</x:v>
-      </x:c>
-      <x:c r="I33" s="44"/>
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I33" s="44" t="n">
+        <x:v>1900000000</x:v>
+      </x:c>
       <x:c r="J33" s="44"/>
       <x:c r="K33" s="41" t="str">
-        <x:v>NOT DISCLOSED</x:v>
+        <x:v>RUB</x:v>
       </x:c>
       <x:c r="L33" s="45"/>
       <x:c r="M33" s="41" t="str">
-        <x:v>Shares</x:v>
+        <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="N33" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3310,28 +3314,26 @@
         <x:f>IFERROR(IF(AND($J33&gt;0,$P33&gt;0,$K33=$R33),$J33/$P33,""),"")</x:f>
       </x:c>
       <x:c r="U33" s="41" t="str">
-        <x:v>Acquisition / disposal</x:v>
+        <x:v>Bonds</x:v>
       </x:c>
       <x:c r="V33" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>погашения выпуска облигаций на 1,9 млрд рублей</x:v>
       </x:c>
       <x:c r="W33" s="41" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="X33" s="41" t="str">
         <x:v>unverified</x:v>
       </x:c>
-      <x:c r="Y33" s="41" t="str">
-        <x:v>OZON</x:v>
-      </x:c>
+      <x:c r="Y33" s="41" t="str"/>
       <x:c r="Z33" s="41" t="str">
-        <x:v>Ведомости</x:v>
+        <x:v>Интерфакс</x:v>
       </x:c>
       <x:c r="AA33" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMifkFVX3lxTE5wcVN1bk9QeWE3N3kxMkdGdndraERVOGhyUndZcTkwSVVWdlhXUkVldXUtRWR5QTlCR3owOHN1QzFPZVVDR0JWMGkweTM2ekRobml3MzJqT3ZyTGFCSTZtTk0yZ3FxOG52ZjA3c203bEJ4UGVIN18xQUJxenBLQQ?oc=5</x:v>
+        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE5rRHd6NXMzNkpDcVZDdVR4NXhZN185LXRRSDMzVzZiUGd4cmNqV1BydzRLTnh4cHJnU19qNnQ1X05XMDl6VnBjVlBXY0NUOUZ3VlHSAUtBVV95cUxQOHVvOS00aURkZ3lDUGZ6Sk9kYTVFSDJhcGNJQk1PVVR2ZFJwWnZlRGZ4eW85TS15QUs4bmkxOWUzQW5PbGpDeUVnOVk?oc=5</x:v>
       </x:c>
       <x:c r="AB33" s="41" t="str">
-        <x:v>Путин исключил «Озон банк» из списка с запретом на сделки с акциями и долями - Ведомости</x:v>
+        <x:v>"Делимобиль" перечислил в НРД средства для погашения выпуска облигаций на 1,9 млрд рублей - Интерфакс</x:v>
       </x:c>
       <x:c r="AC33" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -3339,37 +3341,39 @@
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="41" t="str">
-        <x:v>DL-cc671fa6b14f8f28</x:v>
+        <x:v>DL-2848bdd8b067faa2</x:v>
       </x:c>
       <x:c r="B34" s="43" t="n">
-        <x:v>46139</x:v>
+        <x:v>46147</x:v>
       </x:c>
       <x:c r="C34" s="41" t="str">
-        <x:v>M&amp;A</x:v>
+        <x:v>ECM</x:v>
       </x:c>
       <x:c r="D34" s="41" t="str">
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E34" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>Yandex</x:v>
       </x:c>
       <x:c r="F34" s="41" t="str">
-        <x:v>Ozon</x:v>
+        <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="G34" s="41" t="str">
-        <x:v>Financials</x:v>
+        <x:v>Not classified</x:v>
       </x:c>
       <x:c r="H34" s="41" t="str">
-        <x:v>Not disclosed</x:v>
-      </x:c>
-      <x:c r="I34" s="44"/>
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I34" s="44" t="n">
+        <x:v>50000000000</x:v>
+      </x:c>
       <x:c r="J34" s="44"/>
       <x:c r="K34" s="41" t="str">
-        <x:v>NOT DISCLOSED</x:v>
+        <x:v>RUB</x:v>
       </x:c>
       <x:c r="L34" s="45"/>
       <x:c r="M34" s="41" t="str">
-        <x:v>Shares</x:v>
+        <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="N34" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3389,7 +3393,7 @@
         <x:f>IFERROR(IF(AND($J34&gt;0,$P34&gt;0,$K34=$R34),$J34/$P34,""),"")</x:f>
       </x:c>
       <x:c r="U34" s="41" t="str">
-        <x:v>Acquisition / disposal</x:v>
+        <x:v>Equity issuance</x:v>
       </x:c>
       <x:c r="V34" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3401,16 +3405,16 @@
         <x:v>unverified</x:v>
       </x:c>
       <x:c r="Y34" s="41" t="str">
-        <x:v>OZON</x:v>
+        <x:v>YDEX</x:v>
       </x:c>
       <x:c r="Z34" s="41" t="str">
         <x:v>БКС Экспресс</x:v>
       </x:c>
       <x:c r="AA34" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMiwgFBVV95cUxORlpPNHotYkNzQVpwd2ptLTRIVmJmelQwVHY5Vjc2Rmd1YzFnMW52R3h3aXlFYkpzc0NfY0NPdWk3RnhUSXhudGhZUWxXeE90WlNpVmRkYlhxSlNHLXFkZ1pLMllFY3VBQUx6bDJUcG13VEVINVlKOTFMUkRkUUx0bllTQ2NQdzBaMENTM3FrN2dMNVFjQ2NKRTVUNG92QWlpcEdtWVFuMWx1dnJRTTFWS1paVllydW9oeUU0NjNUVjhCUQ?oc=5</x:v>
+        <x:v>https://bcs-express.ru/novosti-i-analitika/iandeks-odobril-vykup-aktsii-na-50-mlrd-rublei</x:v>
       </x:c>
       <x:c r="AB34" s="41" t="str">
-        <x:v>Ozon Банк исключен из перечня банков, с акциями которых запрещены сделки - БКС Экспресс</x:v>
+        <x:v>Яндекс одобрил выкуп акций на 50 млрд рублей - БКС Экспресс</x:v>
       </x:c>
       <x:c r="AC34" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -3418,25 +3422,25 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="41" t="str">
-        <x:v>DL-2d1ef3023240f32a</x:v>
+        <x:v>DL-3d4a31cc3b7936d0</x:v>
       </x:c>
       <x:c r="B35" s="43" t="n">
-        <x:v>46139</x:v>
+        <x:v>46146</x:v>
       </x:c>
       <x:c r="C35" s="41" t="str">
-        <x:v>M&amp;A</x:v>
+        <x:v>ECM</x:v>
       </x:c>
       <x:c r="D35" s="41" t="str">
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E35" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>Yandex</x:v>
       </x:c>
       <x:c r="F35" s="41" t="str">
-        <x:v>Ozon</x:v>
+        <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="G35" s="41" t="str">
-        <x:v>Financials</x:v>
+        <x:v>Energy</x:v>
       </x:c>
       <x:c r="H35" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3448,7 +3452,7 @@
       </x:c>
       <x:c r="L35" s="45"/>
       <x:c r="M35" s="41" t="str">
-        <x:v>Shares</x:v>
+        <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="N35" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3468,7 +3472,7 @@
         <x:f>IFERROR(IF(AND($J35&gt;0,$P35&gt;0,$K35=$R35),$J35/$P35,""),"")</x:f>
       </x:c>
       <x:c r="U35" s="41" t="str">
-        <x:v>Acquisition / disposal</x:v>
+        <x:v>Equity issuance</x:v>
       </x:c>
       <x:c r="V35" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3480,16 +3484,16 @@
         <x:v>unverified</x:v>
       </x:c>
       <x:c r="Y35" s="41" t="str">
-        <x:v>OZON</x:v>
+        <x:v>YDEX, OZON</x:v>
       </x:c>
       <x:c r="Z35" s="41" t="str">
-        <x:v>Главпортал</x:v>
+        <x:v>SberCIB</x:v>
       </x:c>
       <x:c r="AA35" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMifEFVX3lxTE5vODZHWnJJX1RoLWU3X2RfSGpCZFZrN2xZeGtyOVVzSENxQzlaQTEwV3pCNXBuOG9JRnVfTkdxOGl5N3RJTGhDVVh0YXdBbTY5dnlZYWRjVkJ5MTFROHhTQUVvdjEwS3BpYUtmSG12YmVocnBnVmVpVmN0ZzQ?oc=5</x:v>
+        <x:v>https://sbercib.ru/publication/rezultati-ozon-dom-rf-dividendi-yandeksa-i-tatnefti-i-drugie-novosti-nedeli</x:v>
       </x:c>
       <x:c r="AB35" s="41" t="str">
-        <x:v>Путин разрешил сделки с акциями «Озон банка» - Главпортал</x:v>
+        <x:v>Результаты Ozon, ДОМ. РФ, дивиденды Яндекса и Татнефти и другие новости недели - SberCIB</x:v>
       </x:c>
       <x:c r="AC35" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -3497,22 +3501,22 @@
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="41" t="str">
-        <x:v>DL-0bceebeca9933dc3</x:v>
+        <x:v>DL-6bc0569f7ac374fe</x:v>
       </x:c>
       <x:c r="B36" s="43" t="n">
-        <x:v>46132</x:v>
+        <x:v>46139</x:v>
       </x:c>
       <x:c r="C36" s="41" t="str">
-        <x:v>DCM</x:v>
+        <x:v>M&amp;A</x:v>
       </x:c>
       <x:c r="D36" s="41" t="str">
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E36" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F36" s="41" t="str">
         <x:v>Ozon</x:v>
-      </x:c>
-      <x:c r="F36" s="41" t="str">
-        <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="G36" s="41" t="str">
         <x:v>Financials</x:v>
@@ -3527,7 +3531,7 @@
       </x:c>
       <x:c r="L36" s="45"/>
       <x:c r="M36" s="41" t="str">
-        <x:v>Not applicable</x:v>
+        <x:v>Shares</x:v>
       </x:c>
       <x:c r="N36" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3547,7 +3551,7 @@
         <x:f>IFERROR(IF(AND($J36&gt;0,$P36&gt;0,$K36=$R36),$J36/$P36,""),"")</x:f>
       </x:c>
       <x:c r="U36" s="41" t="str">
-        <x:v>Bonds</x:v>
+        <x:v>Acquisition / disposal</x:v>
       </x:c>
       <x:c r="V36" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3562,13 +3566,13 @@
         <x:v>OZON</x:v>
       </x:c>
       <x:c r="Z36" s="41" t="str">
-        <x:v>Альфа-Банк</x:v>
+        <x:v>Ведомости</x:v>
       </x:c>
       <x:c r="AA36" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMihgFBVV95cUxOR21Vd1RCOGpSRktSR2g3Mm11emdNTHVpLTlESXFfUVc5SFZFYkZYTWcwZ1kxc2ZUU1lPVWo3UmRjQXl4SFREaElpVTZvZktVMW43QXhNU2ZHal9hSHQ0bkttRV8xa1BVbHRHSENoSE5GblYwZElISUxNbG1fSG1uWUJ0QVgtZw?oc=5</x:v>
+        <x:v>https://www.vedomosti.ru/finance/news/2026/04/27/1193355-putin-isklyuchil</x:v>
       </x:c>
       <x:c r="AB36" s="41" t="str">
-        <x:v>Облигации Озона: заработай на маркетплейсе - Альфа-Банк</x:v>
+        <x:v>Путин исключил «Озон банк» из списка с запретом на сделки с акциями и долями - Ведомости</x:v>
       </x:c>
       <x:c r="AC36" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -3576,10 +3580,10 @@
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="41" t="str">
-        <x:v>DL-c10daba8af8e67d8</x:v>
+        <x:v>DL-cc671fa6b14f8f28</x:v>
       </x:c>
       <x:c r="B37" s="43" t="n">
-        <x:v>46128</x:v>
+        <x:v>46139</x:v>
       </x:c>
       <x:c r="C37" s="41" t="str">
         <x:v>M&amp;A</x:v>
@@ -3591,7 +3595,7 @@
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="F37" s="41" t="str">
-        <x:v>VK</x:v>
+        <x:v>Ozon</x:v>
       </x:c>
       <x:c r="G37" s="41" t="str">
         <x:v>Financials</x:v>
@@ -3599,16 +3603,12 @@
       <x:c r="H37" s="41" t="str">
         <x:v>Not disclosed</x:v>
       </x:c>
-      <x:c r="I37" s="44" t="n">
-        <x:v>21200000000</x:v>
-      </x:c>
+      <x:c r="I37" s="44"/>
       <x:c r="J37" s="44"/>
       <x:c r="K37" s="41" t="str">
-        <x:v>RUB</x:v>
-      </x:c>
-      <x:c r="L37" s="45" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L37" s="45"/>
       <x:c r="M37" s="41" t="str">
         <x:v>Shares</x:v>
       </x:c>
@@ -3636,22 +3636,22 @@
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="W37" s="41" t="n">
-        <x:v>6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="X37" s="41" t="str">
         <x:v>unverified</x:v>
       </x:c>
       <x:c r="Y37" s="41" t="str">
-        <x:v>VKCO</x:v>
+        <x:v>OZON</x:v>
       </x:c>
       <x:c r="Z37" s="41" t="str">
-        <x:v>RB.ru</x:v>
+        <x:v>БКС Экспресс</x:v>
       </x:c>
       <x:c r="AA37" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNQlJkLWo5eXZTSkZxSWU5NjF5TVJ0N1lYdXJqSzlFUGFMdk5jVEZMak1HeDE2SDZNcDduc3hENHkzaW8wWTVfWjN1QmpodGdYdDRLVXpua0pBUUs0MzVBX3lnOHlkVkJhVGdLNDlESDNRYmNmaDFaamJZVHdJRGhpX25lSkNmcmZ2dWZhZnhja2NwcXVnelJZVjg0Z1Flakd2VGl0MGRwUVdTTGtYYlNFcUYxSXdYaGY5?oc=5</x:v>
+        <x:v>https://bcs-express.ru/novosti-i-analitika/ozon-bank-iskliuchen-iz-perechnia-bankov-s-aktsiiami-kotorykh-zapreshcheny-sdelki</x:v>
       </x:c>
       <x:c r="AB37" s="41" t="str">
-        <x:v>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.ru</x:v>
+        <x:v>Ozon Банк исключен из перечня банков, с акциями которых запрещены сделки - БКС Экспресс</x:v>
       </x:c>
       <x:c r="AC37" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -3659,10 +3659,10 @@
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="41" t="str">
-        <x:v>DL-4d20ecb8f5c75dad</x:v>
+        <x:v>DL-2d1ef3023240f32a</x:v>
       </x:c>
       <x:c r="B38" s="43" t="n">
-        <x:v>46128</x:v>
+        <x:v>46139</x:v>
       </x:c>
       <x:c r="C38" s="41" t="str">
         <x:v>M&amp;A</x:v>
@@ -3674,24 +3674,22 @@
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="F38" s="41" t="str">
-        <x:v>VK</x:v>
+        <x:v>Ozon</x:v>
       </x:c>
       <x:c r="G38" s="41" t="str">
         <x:v>Financials</x:v>
       </x:c>
       <x:c r="H38" s="41" t="str">
-        <x:v>Russia</x:v>
-      </x:c>
-      <x:c r="I38" s="44" t="n">
-        <x:v>21200000000</x:v>
-      </x:c>
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I38" s="44"/>
       <x:c r="J38" s="44"/>
       <x:c r="K38" s="41" t="str">
-        <x:v>RUB</x:v>
+        <x:v>NOT DISCLOSED</x:v>
       </x:c>
       <x:c r="L38" s="45"/>
       <x:c r="M38" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>Shares</x:v>
       </x:c>
       <x:c r="N38" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3723,16 +3721,16 @@
         <x:v>unverified</x:v>
       </x:c>
       <x:c r="Y38" s="41" t="str">
-        <x:v>VKCO</x:v>
+        <x:v>OZON</x:v>
       </x:c>
       <x:c r="Z38" s="41" t="str">
-        <x:v>Ведомости</x:v>
+        <x:v>Главпортал</x:v>
       </x:c>
       <x:c r="AA38" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMifkFVX3lxTE1vSUlEOTl2cU5jckxzemNzN2oyNVZaX203N1VWRkpuZXNwYV9sdUNGMTZPTHhiNm5LWFBmdFM0QkFTRjFPczd4VEFlTEZpRzhiakF2ZGh5UU5kamRvbnFRTDE5dG8zOF9HRkk5MDUwVzBWbU9qWEN0MDhIdTJNUQ?oc=5</x:v>
+        <x:v>https://glavportal.com/news/putin-razreshil-sdelki-s-akciyami-ozon-banka</x:v>
       </x:c>
       <x:c r="AB38" s="41" t="str">
-        <x:v>VK продала долю в «Точка банке» по цене не менее 21,2 млрд рублей - Ведомости</x:v>
+        <x:v>Путин разрешил сделки с акциями «Озон банка» - Главпортал</x:v>
       </x:c>
       <x:c r="AC38" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -3740,10 +3738,10 @@
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="41" t="str">
-        <x:v>DL-dfc59ea0a0794532</x:v>
+        <x:v>DL-dd21f961f579e55a</x:v>
       </x:c>
       <x:c r="B39" s="43" t="n">
-        <x:v>46128</x:v>
+        <x:v>46139</x:v>
       </x:c>
       <x:c r="C39" s="41" t="str">
         <x:v>M&amp;A</x:v>
@@ -3755,7 +3753,7 @@
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="F39" s="41" t="str">
-        <x:v>VK</x:v>
+        <x:v>Ozon</x:v>
       </x:c>
       <x:c r="G39" s="41" t="str">
         <x:v>Financials</x:v>
@@ -3770,7 +3768,7 @@
       </x:c>
       <x:c r="L39" s="45"/>
       <x:c r="M39" s="41" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>Shares</x:v>
       </x:c>
       <x:c r="N39" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3793,7 +3791,7 @@
         <x:v>Acquisition / disposal</x:v>
       </x:c>
       <x:c r="V39" s="41" t="str">
-        <x:v>предпринимателей</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="W39" s="41" t="n">
         <x:v>4</x:v>
@@ -3802,16 +3800,16 @@
         <x:v>unverified</x:v>
       </x:c>
       <x:c r="Y39" s="41" t="str">
-        <x:v>VKCO</x:v>
+        <x:v>OZON</x:v>
       </x:c>
       <x:c r="Z39" s="41" t="str">
-        <x:v>CNews.ru</x:v>
+        <x:v>Реальное время</x:v>
       </x:c>
       <x:c r="AA39" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMigAFBVV95cUxOeU1NOHJNay1uUm9TdlpGcWh4YkNXN3J0clFCT2JrM0t5T3hwTmtTRlJXUWpyeVBYbnltZlB0dnpqLWxhTUxQNW9wQU1LeG5sTjVzT1NNQlFlY0Jpb1REMGhyWG1wSUM0STZXbFFaNndzQ1A1MlVvMFN3RmlmOW4tXw?oc=5</x:v>
+        <x:v>https://realnoevremya.ru/news/394463-s-ozon-banka-snyali-ogranicheniya-na-sdelki-s-akciyami-rasporyazhenie-putina</x:v>
       </x:c>
       <x:c r="AB39" s="41" t="str">
-        <x:v>VK продал свою долю в виртуальном банке для предпринимателей - CNews.ru</x:v>
+        <x:v>С «Озон банка» сняли ограничения на сделки с акциями — распоряжение Путина - Реальное время</x:v>
       </x:c>
       <x:c r="AC39" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -3819,39 +3817,37 @@
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="41" t="str">
-        <x:v>DL-1363a495ec14164a</x:v>
+        <x:v>DL-09b72d880f67361b</x:v>
       </x:c>
       <x:c r="B40" s="43" t="n">
-        <x:v>46115</x:v>
+        <x:v>46139</x:v>
       </x:c>
       <x:c r="C40" s="41" t="str">
-        <x:v>DCM</x:v>
+        <x:v>M&amp;A</x:v>
       </x:c>
       <x:c r="D40" s="41" t="str">
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E40" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F40" s="41" t="str">
         <x:v>Ozon</x:v>
       </x:c>
-      <x:c r="F40" s="41" t="str">
-        <x:v>Not applicable</x:v>
-      </x:c>
       <x:c r="G40" s="41" t="str">
-        <x:v>Not classified</x:v>
+        <x:v>Financials</x:v>
       </x:c>
       <x:c r="H40" s="41" t="str">
         <x:v>Russia</x:v>
       </x:c>
-      <x:c r="I40" s="44" t="n">
-        <x:v>15000000000</x:v>
-      </x:c>
+      <x:c r="I40" s="44"/>
       <x:c r="J40" s="44"/>
       <x:c r="K40" s="41" t="str">
-        <x:v>RUB</x:v>
+        <x:v>NOT DISCLOSED</x:v>
       </x:c>
       <x:c r="L40" s="45"/>
       <x:c r="M40" s="41" t="str">
-        <x:v>Not applicable</x:v>
+        <x:v>Shares</x:v>
       </x:c>
       <x:c r="N40" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3871,7 +3867,7 @@
         <x:f>IFERROR(IF(AND($J40&gt;0,$P40&gt;0,$K40=$R40),$J40/$P40,""),"")</x:f>
       </x:c>
       <x:c r="U40" s="41" t="str">
-        <x:v>Bonds</x:v>
+        <x:v>Acquisition / disposal</x:v>
       </x:c>
       <x:c r="V40" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3886,13 +3882,13 @@
         <x:v>OZON</x:v>
       </x:c>
       <x:c r="Z40" s="41" t="str">
-        <x:v>https://expert.ru</x:v>
+        <x:v>InvestFuture</x:v>
       </x:c>
       <x:c r="AA40" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMiigFBVV95cUxNVmVRdkQ4RElHdURKbmVDQU9NbVRmZTd0Z3NiM3JzMjFhZzNzQzVPMnhzNHFER2VsYVAyWEpwVlg4c24zZUozY1ZNUFQxNDMxakR1Q1J0RFhhbkRxbUZYTmgtc3N3UzhsckljT1lpZTFvaXJKeGlTblNyNlNWb2JhOWFSVXZJWjZ0Rmc?oc=5</x:v>
+        <x:v>https://investfuture.ru/articles/putin-snyal-zapret-na-sdelki-s-aktsiyami-ozon-banka-v-rossii-1178931397</x:v>
       </x:c>
       <x:c r="AB40" s="41" t="str">
-        <x:v>Ozon анонсировал размещение облигаций на 15 млрд рублей - https://expert.ru</x:v>
+        <x:v>Путин снял запрет на сделки с акциями Озон банка в России | IF | 27.04.2026 - InvestFuture</x:v>
       </x:c>
       <x:c r="AC40" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -3900,16 +3896,16 @@
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="41" t="str">
-        <x:v>DL-12855c6275c496fe</x:v>
+        <x:v>DL-0bceebeca9933dc3</x:v>
       </x:c>
       <x:c r="B41" s="43" t="n">
-        <x:v>46115</x:v>
+        <x:v>46132</x:v>
       </x:c>
       <x:c r="C41" s="41" t="str">
         <x:v>DCM</x:v>
       </x:c>
       <x:c r="D41" s="41" t="str">
-        <x:v>Announced</x:v>
+        <x:v>Reported</x:v>
       </x:c>
       <x:c r="E41" s="41" t="str">
         <x:v>Ozon</x:v>
@@ -3918,7 +3914,7 @@
         <x:v>Not applicable</x:v>
       </x:c>
       <x:c r="G41" s="41" t="str">
-        <x:v>Not classified</x:v>
+        <x:v>Financials</x:v>
       </x:c>
       <x:c r="H41" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -3965,13 +3961,13 @@
         <x:v>OZON</x:v>
       </x:c>
       <x:c r="Z41" s="41" t="str">
-        <x:v>БКС Экспресс</x:v>
+        <x:v>Альфа-Банк</x:v>
       </x:c>
       <x:c r="AA41" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMipgFBVV95cUxNTmtrN3N0YVN0c0NuVnBscUJvbzdVbWZ5OXczRTkySkx1T1hKdWJvZlFWNEFqbkxhRmpXVEVQZUdIcjdOZkNFRnJhX1huRGRmelhla1RRTURfejMzd2FIMU9ZcmQ4REtOWWEyZ3JhLUgwSmI2UDhJM2s4TkNRekY0T3ZtcEJNbUYzNTQzOXRITGxsN1A0N1duQ3FKeE5fTXIxMUVJTlh3?oc=5</x:v>
+        <x:v>https://alfabank.ru/alfa-investor/t/obligatsii-ozona-zarabotay-na-marketpleyse/</x:v>
       </x:c>
       <x:c r="AB41" s="41" t="str">
-        <x:v>Озон планирует дебютное размещение биржевых облигаций - БКС Экспресс</x:v>
+        <x:v>Облигации Озона: заработай на маркетплейсе - Альфа-Банк</x:v>
       </x:c>
       <x:c r="AC41" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -3979,39 +3975,41 @@
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="41" t="str">
-        <x:v>DL-d39c99c4c2dfa45c</x:v>
+        <x:v>DL-c10daba8af8e67d8</x:v>
       </x:c>
       <x:c r="B42" s="43" t="n">
-        <x:v>46111</x:v>
+        <x:v>46128</x:v>
       </x:c>
       <x:c r="C42" s="41" t="str">
-        <x:v>DCM</x:v>
+        <x:v>M&amp;A</x:v>
       </x:c>
       <x:c r="D42" s="41" t="str">
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E42" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F42" s="41" t="str">
         <x:v>VK</x:v>
       </x:c>
-      <x:c r="F42" s="41" t="str">
-        <x:v>Not applicable</x:v>
-      </x:c>
       <x:c r="G42" s="41" t="str">
-        <x:v>Not classified</x:v>
+        <x:v>Financials</x:v>
       </x:c>
       <x:c r="H42" s="41" t="str">
-        <x:v>Russia</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="I42" s="44" t="n">
-        <x:v>10000000000</x:v>
+        <x:v>21200000000</x:v>
       </x:c>
       <x:c r="J42" s="44"/>
       <x:c r="K42" s="41" t="str">
         <x:v>RUB</x:v>
       </x:c>
-      <x:c r="L42" s="45"/>
+      <x:c r="L42" s="45" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
       <x:c r="M42" s="41" t="str">
-        <x:v>Not applicable</x:v>
+        <x:v>Shares</x:v>
       </x:c>
       <x:c r="N42" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -4031,13 +4029,13 @@
         <x:f>IFERROR(IF(AND($J42&gt;0,$P42&gt;0,$K42=$R42),$J42/$P42,""),"")</x:f>
       </x:c>
       <x:c r="U42" s="41" t="str">
-        <x:v>Bonds</x:v>
+        <x:v>Acquisition / disposal</x:v>
       </x:c>
       <x:c r="V42" s="41" t="str">
         <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="W42" s="41" t="n">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="X42" s="41" t="str">
         <x:v>unverified</x:v>
@@ -4046,13 +4044,13 @@
         <x:v>VKCO</x:v>
       </x:c>
       <x:c r="Z42" s="41" t="str">
-        <x:v>vk.company</x:v>
+        <x:v>RB.ru</x:v>
       </x:c>
       <x:c r="AA42" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1WcXUxeUFkWFdQQUk3U0o0RDBfeTdxa3IxV0dWLXRZZXRjWWo1M0NBOUJfeVUwNHRuMUxaOVBKVXdjSWstd1paRHFfX2lpT1VpV0E?oc=5</x:v>
+        <x:v>https://news.google.com/rss/articles/CBMiuAFBVV95cUxNQlJkLWo5eXZTSkZxSWU5NjF5TVJ0N1lYdXJqSzlFUGFMdk5jVEZMak1HeDE2SDZNcDduc3hENHkzaW8wWTVfWjN1QmpodGdYdDRLVXpua0pBUUs0MzVBX3lnOHlkVkJhVGdLNDlESDNRYmNmaDFaamJZVHdJRGhpX25lSkNmcmZ2dWZhZnhja2NwcXVnelJZVjg0Z1Flakd2VGl0MGRwUVdTTGtYYlNFcUYxSXdYaGY5?oc=5</x:v>
       </x:c>
       <x:c r="AB42" s="41" t="str">
-        <x:v>VK объявляет о планах по размещению биржевых облигаций объемом 10 млрд рублей - vk.company</x:v>
+        <x:v>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.ru</x:v>
       </x:c>
       <x:c r="AC42" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
@@ -4060,37 +4058,39 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="41" t="str">
-        <x:v>DL-b9babb23f2c4462c</x:v>
+        <x:v>DL-4d20ecb8f5c75dad</x:v>
       </x:c>
       <x:c r="B43" s="43" t="n">
-        <x:v>46111</x:v>
+        <x:v>46128</x:v>
       </x:c>
       <x:c r="C43" s="41" t="str">
-        <x:v>DCM</x:v>
+        <x:v>M&amp;A</x:v>
       </x:c>
       <x:c r="D43" s="41" t="str">
         <x:v>Reported</x:v>
       </x:c>
       <x:c r="E43" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F43" s="41" t="str">
         <x:v>VK</x:v>
       </x:c>
-      <x:c r="F43" s="41" t="str">
-        <x:v>Not applicable</x:v>
-      </x:c>
       <x:c r="G43" s="41" t="str">
-        <x:v>Not classified</x:v>
+        <x:v>Financials</x:v>
       </x:c>
       <x:c r="H43" s="41" t="str">
-        <x:v>Not disclosed</x:v>
-      </x:c>
-      <x:c r="I43" s="44"/>
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I43" s="44" t="n">
+        <x:v>21200000000</x:v>
+      </x:c>
       <x:c r="J43" s="44"/>
       <x:c r="K43" s="41" t="str">
-        <x:v>NOT DISCLOSED</x:v>
+        <x:v>RUB</x:v>
       </x:c>
       <x:c r="L43" s="45"/>
       <x:c r="M43" s="41" t="str">
-        <x:v>Not applicable</x:v>
+        <x:v>Not disclosed</x:v>
       </x:c>
       <x:c r="N43" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -4110,7 +4110,7 @@
         <x:f>IFERROR(IF(AND($J43&gt;0,$P43&gt;0,$K43=$R43),$J43/$P43,""),"")</x:f>
       </x:c>
       <x:c r="U43" s="41" t="str">
-        <x:v>Bonds</x:v>
+        <x:v>Acquisition / disposal</x:v>
       </x:c>
       <x:c r="V43" s="41" t="str">
         <x:v>Not disclosed</x:v>
@@ -4125,15 +4125,1050 @@
         <x:v>VKCO</x:v>
       </x:c>
       <x:c r="Z43" s="41" t="str">
+        <x:v>Ведомости</x:v>
+      </x:c>
+      <x:c r="AA43" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMifkFVX3lxTE1vSUlEOTl2cU5jckxzemNzN2oyNVZaX203N1VWRkpuZXNwYV9sdUNGMTZPTHhiNm5LWFBmdFM0QkFTRjFPczd4VEFlTEZpRzhiakF2ZGh5UU5kamRvbnFRTDE5dG8zOF9HRkk5MDUwVzBWbU9qWEN0MDhIdTJNUQ?oc=5</x:v>
+      </x:c>
+      <x:c r="AB43" s="41" t="str">
+        <x:v>VK продала долю в «Точка банке» по цене не менее 21,2 млрд рублей - Ведомости</x:v>
+      </x:c>
+      <x:c r="AC43" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="41" t="str">
+        <x:v>DL-dfc59ea0a0794532</x:v>
+      </x:c>
+      <x:c r="B44" s="43" t="n">
+        <x:v>46128</x:v>
+      </x:c>
+      <x:c r="C44" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D44" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E44" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F44" s="41" t="str">
+        <x:v>VK</x:v>
+      </x:c>
+      <x:c r="G44" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H44" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I44" s="44"/>
+      <x:c r="J44" s="44"/>
+      <x:c r="K44" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L44" s="45"/>
+      <x:c r="M44" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="N44" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O44" s="44"/>
+      <x:c r="P44" s="44"/>
+      <x:c r="Q44" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R44" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S44" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J44&gt;0,$O44&gt;0,$K44=$R44),$J44/$O44,""),"")</x:f>
+      </x:c>
+      <x:c r="T44" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J44&gt;0,$P44&gt;0,$K44=$R44),$J44/$P44,""),"")</x:f>
+      </x:c>
+      <x:c r="U44" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V44" s="41" t="str">
+        <x:v>предпринимателей</x:v>
+      </x:c>
+      <x:c r="W44" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X44" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y44" s="41" t="str">
+        <x:v>VKCO</x:v>
+      </x:c>
+      <x:c r="Z44" s="41" t="str">
+        <x:v>CNews.ru</x:v>
+      </x:c>
+      <x:c r="AA44" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMigAFBVV95cUxOeU1NOHJNay1uUm9TdlpGcWh4YkNXN3J0clFCT2JrM0t5T3hwTmtTRlJXUWpyeVBYbnltZlB0dnpqLWxhTUxQNW9wQU1LeG5sTjVzT1NNQlFlY0Jpb1REMGhyWG1wSUM0STZXbFFaNndzQ1A1MlVvMFN3RmlmOW4tXw?oc=5</x:v>
+      </x:c>
+      <x:c r="AB44" s="41" t="str">
+        <x:v>VK продал свою долю в виртуальном банке для предпринимателей - CNews.ru</x:v>
+      </x:c>
+      <x:c r="AC44" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="41" t="str">
+        <x:v>DL-4774de17c61c14e4</x:v>
+      </x:c>
+      <x:c r="B45" s="43" t="n">
+        <x:v>46122</x:v>
+      </x:c>
+      <x:c r="C45" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D45" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E45" s="41" t="str">
+        <x:v>VK</x:v>
+      </x:c>
+      <x:c r="F45" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G45" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H45" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I45" s="44"/>
+      <x:c r="J45" s="44"/>
+      <x:c r="K45" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L45" s="45"/>
+      <x:c r="M45" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N45" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O45" s="44"/>
+      <x:c r="P45" s="44"/>
+      <x:c r="Q45" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R45" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S45" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J45&gt;0,$O45&gt;0,$K45=$R45),$J45/$O45,""),"")</x:f>
+      </x:c>
+      <x:c r="T45" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J45&gt;0,$P45&gt;0,$K45=$R45),$J45/$P45,""),"")</x:f>
+      </x:c>
+      <x:c r="U45" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V45" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W45" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X45" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y45" s="41" t="str">
+        <x:v>VKCO</x:v>
+      </x:c>
+      <x:c r="Z45" s="41" t="str">
         <x:v>Финам</x:v>
       </x:c>
-      <x:c r="AA43" s="41" t="str">
-        <x:v>https://news.google.com/rss/articles/CBMiwAFBVV95cUxPR3ZFSWgwcm9TTW9rSTlBM0VaYncwM3dBZ0N0OUhwWFBnYVZLc3EtZkNrOE5RLUFjczJ5b25yNURHX0RvYkNPbUFfTlhiSkU3U185NFM0b3R3ZVJVbVEweXI4Q1hRVDBwN3dlcHpocDFYTmRYalh4d1Q1RVU3M1JHZ18ydXdQc2s0OUJGQTJwOFRydlNZOTNJbkItdEtZQVRyb3BMWU5fY082ZHZzbDdNbmNRZWJHRUVhd0FIUkhtX28?oc=5</x:v>
-      </x:c>
-      <x:c r="AB43" s="41" t="str">
+      <x:c r="AA45" s="41" t="str">
+        <x:v>https://www.finam.ru/publications/item/dvoynoe-razmeshchenie-obligatsiy-vk-chego-zhdat-chastnym-investoram-20260410-1829/</x:v>
+      </x:c>
+      <x:c r="AB45" s="41" t="str">
+        <x:v>Двойное размещение облигаций VK. Чего ждать частным инвесторам? 10.04.2026 - Финам</x:v>
+      </x:c>
+      <x:c r="AC45" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="41" t="str">
+        <x:v>DL-87f81143148d7276</x:v>
+      </x:c>
+      <x:c r="B46" s="43" t="n">
+        <x:v>46122</x:v>
+      </x:c>
+      <x:c r="C46" s="41" t="str">
+        <x:v>ECM</x:v>
+      </x:c>
+      <x:c r="D46" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E46" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="F46" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G46" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H46" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I46" s="44"/>
+      <x:c r="J46" s="44"/>
+      <x:c r="K46" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L46" s="45"/>
+      <x:c r="M46" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N46" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O46" s="44"/>
+      <x:c r="P46" s="44"/>
+      <x:c r="Q46" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R46" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S46" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J46&gt;0,$O46&gt;0,$K46=$R46),$J46/$O46,""),"")</x:f>
+      </x:c>
+      <x:c r="T46" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J46&gt;0,$P46&gt;0,$K46=$R46),$J46/$P46,""),"")</x:f>
+      </x:c>
+      <x:c r="U46" s="41" t="str">
+        <x:v>Equity issuance</x:v>
+      </x:c>
+      <x:c r="V46" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W46" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X46" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y46" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z46" s="41" t="str">
+        <x:v>Альфа-Банк</x:v>
+      </x:c>
+      <x:c r="AA46" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMihgFBVV95cUxNbVZjUURpZDgxcTE2VG9jRktkMVZHRmpqSG9jclBJZU45SVNzS3VLTUFyYkhnUWdpQl9pb1Jvd1p5Ni12Z1pFQWlKeDQtUDUxY0xCSVA0dno3ZjJzWnZkS3RLVWh3UjNGWVJXd29rbjFBUjdVUnZwa1RGdk9hQTIxMHBCRzFPdw?oc=5</x:v>
+      </x:c>
+      <x:c r="AB46" s="41" t="str">
+        <x:v>Мы держим Ozon в портфеле роста, но не в дивидендном Хотя - Альфа-Банк</x:v>
+      </x:c>
+      <x:c r="AC46" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="41" t="str">
+        <x:v>DL-1363a495ec14164a</x:v>
+      </x:c>
+      <x:c r="B47" s="43" t="n">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="C47" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D47" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E47" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="F47" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G47" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H47" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I47" s="44" t="n">
+        <x:v>15000000000</x:v>
+      </x:c>
+      <x:c r="J47" s="44"/>
+      <x:c r="K47" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L47" s="45"/>
+      <x:c r="M47" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N47" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O47" s="44"/>
+      <x:c r="P47" s="44"/>
+      <x:c r="Q47" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R47" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S47" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J47&gt;0,$O47&gt;0,$K47=$R47),$J47/$O47,""),"")</x:f>
+      </x:c>
+      <x:c r="T47" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J47&gt;0,$P47&gt;0,$K47=$R47),$J47/$P47,""),"")</x:f>
+      </x:c>
+      <x:c r="U47" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V47" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W47" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X47" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y47" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z47" s="41" t="str">
+        <x:v>https://expert.ru</x:v>
+      </x:c>
+      <x:c r="AA47" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMiigFBVV95cUxNVmVRdkQ4RElHdURKbmVDQU9NbVRmZTd0Z3NiM3JzMjFhZzNzQzVPMnhzNHFER2VsYVAyWEpwVlg4c24zZUozY1ZNUFQxNDMxakR1Q1J0RFhhbkRxbUZYTmgtc3N3UzhsckljT1lpZTFvaXJKeGlTblNyNlNWb2JhOWFSVXZJWjZ0Rmc?oc=5</x:v>
+      </x:c>
+      <x:c r="AB47" s="41" t="str">
+        <x:v>Ozon анонсировал размещение облигаций на 15 млрд рублей - https://expert.ru</x:v>
+      </x:c>
+      <x:c r="AC47" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="41" t="str">
+        <x:v>DL-12855c6275c496fe</x:v>
+      </x:c>
+      <x:c r="B48" s="43" t="n">
+        <x:v>46115</x:v>
+      </x:c>
+      <x:c r="C48" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D48" s="41" t="str">
+        <x:v>Announced</x:v>
+      </x:c>
+      <x:c r="E48" s="41" t="str">
+        <x:v>Ozon</x:v>
+      </x:c>
+      <x:c r="F48" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G48" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H48" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I48" s="44"/>
+      <x:c r="J48" s="44"/>
+      <x:c r="K48" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L48" s="45"/>
+      <x:c r="M48" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N48" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O48" s="44"/>
+      <x:c r="P48" s="44"/>
+      <x:c r="Q48" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R48" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S48" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J48&gt;0,$O48&gt;0,$K48=$R48),$J48/$O48,""),"")</x:f>
+      </x:c>
+      <x:c r="T48" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J48&gt;0,$P48&gt;0,$K48=$R48),$J48/$P48,""),"")</x:f>
+      </x:c>
+      <x:c r="U48" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V48" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W48" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X48" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y48" s="41" t="str">
+        <x:v>OZON</x:v>
+      </x:c>
+      <x:c r="Z48" s="41" t="str">
+        <x:v>БКС Экспресс</x:v>
+      </x:c>
+      <x:c r="AA48" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMipgFBVV95cUxNTmtrN3N0YVN0c0NuVnBscUJvbzdVbWZ5OXczRTkySkx1T1hKdWJvZlFWNEFqbkxhRmpXVEVQZUdIcjdOZkNFRnJhX1huRGRmelhla1RRTURfejMzd2FIMU9ZcmQ4REtOWWEyZ3JhLUgwSmI2UDhJM2s4TkNRekY0T3ZtcEJNbUYzNTQzOXRITGxsN1A0N1duQ3FKeE5fTXIxMUVJTlh3?oc=5</x:v>
+      </x:c>
+      <x:c r="AB48" s="41" t="str">
+        <x:v>Озон планирует дебютное размещение биржевых облигаций - БКС Экспресс</x:v>
+      </x:c>
+      <x:c r="AC48" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="41" t="str">
+        <x:v>DL-d39c99c4c2dfa45c</x:v>
+      </x:c>
+      <x:c r="B49" s="43" t="n">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="C49" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D49" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E49" s="41" t="str">
+        <x:v>VK</x:v>
+      </x:c>
+      <x:c r="F49" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G49" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H49" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I49" s="44" t="n">
+        <x:v>10000000000</x:v>
+      </x:c>
+      <x:c r="J49" s="44"/>
+      <x:c r="K49" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L49" s="45"/>
+      <x:c r="M49" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N49" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O49" s="44"/>
+      <x:c r="P49" s="44"/>
+      <x:c r="Q49" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R49" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S49" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J49&gt;0,$O49&gt;0,$K49=$R49),$J49/$O49,""),"")</x:f>
+      </x:c>
+      <x:c r="T49" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J49&gt;0,$P49&gt;0,$K49=$R49),$J49/$P49,""),"")</x:f>
+      </x:c>
+      <x:c r="U49" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V49" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W49" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X49" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y49" s="41" t="str">
+        <x:v>VKCO</x:v>
+      </x:c>
+      <x:c r="Z49" s="41" t="str">
+        <x:v>vk.company</x:v>
+      </x:c>
+      <x:c r="AA49" s="41" t="str">
+        <x:v>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1WcXUxeUFkWFdQQUk3U0o0RDBfeTdxa3IxV0dWLXRZZXRjWWo1M0NBOUJfeVUwNHRuMUxaOVBKVXdjSWstd1paRHFfX2lpT1VpV0E?oc=5</x:v>
+      </x:c>
+      <x:c r="AB49" s="41" t="str">
+        <x:v>VK объявляет о планах по размещению биржевых облигаций объемом 10 млрд рублей - vk.company</x:v>
+      </x:c>
+      <x:c r="AC49" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="41" t="str">
+        <x:v>DL-b9babb23f2c4462c</x:v>
+      </x:c>
+      <x:c r="B50" s="43" t="n">
+        <x:v>46111</x:v>
+      </x:c>
+      <x:c r="C50" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D50" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E50" s="41" t="str">
+        <x:v>VK</x:v>
+      </x:c>
+      <x:c r="F50" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G50" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H50" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I50" s="44"/>
+      <x:c r="J50" s="44"/>
+      <x:c r="K50" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L50" s="45"/>
+      <x:c r="M50" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N50" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O50" s="44"/>
+      <x:c r="P50" s="44"/>
+      <x:c r="Q50" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R50" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S50" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J50&gt;0,$O50&gt;0,$K50=$R50),$J50/$O50,""),"")</x:f>
+      </x:c>
+      <x:c r="T50" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J50&gt;0,$P50&gt;0,$K50=$R50),$J50/$P50,""),"")</x:f>
+      </x:c>
+      <x:c r="U50" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V50" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W50" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="X50" s="41" t="str">
+        <x:v>unverified</x:v>
+      </x:c>
+      <x:c r="Y50" s="41" t="str">
+        <x:v>VKCO</x:v>
+      </x:c>
+      <x:c r="Z50" s="41" t="str">
+        <x:v>Финам</x:v>
+      </x:c>
+      <x:c r="AA50" s="41" t="str">
+        <x:v>https://www.finam.ru/publications/item/vk-razmeshchaet-obligatsii-kak-eto-otrazitsya-na-investorakh-v-aktsii-20260330-1740/</x:v>
+      </x:c>
+      <x:c r="AB50" s="41" t="str">
         <x:v>VK размещает облигации: как это отразится на инвесторах в акции 30.03.2026 - Финам</x:v>
       </x:c>
-      <x:c r="AC43" s="41" t="str">
+      <x:c r="AC50" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="41" t="str">
+        <x:v>DL-238a83afad61e805</x:v>
+      </x:c>
+      <x:c r="B51" s="43" t="n">
+        <x:v>46080</x:v>
+      </x:c>
+      <x:c r="C51" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D51" s="41" t="str">
+        <x:v>Issued</x:v>
+      </x:c>
+      <x:c r="E51" s="41" t="str">
+        <x:v>SELECTEL</x:v>
+      </x:c>
+      <x:c r="F51" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G51" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H51" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I51" s="44" t="n">
+        <x:v>7000000000</x:v>
+      </x:c>
+      <x:c r="J51" s="44"/>
+      <x:c r="K51" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L51" s="45" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="M51" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N51" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O51" s="44"/>
+      <x:c r="P51" s="44"/>
+      <x:c r="Q51" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R51" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S51" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J51&gt;0,$O51&gt;0,$K51=$R51),$J51/$O51,""),"")</x:f>
+      </x:c>
+      <x:c r="T51" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J51&gt;0,$P51&gt;0,$K51=$R51),$J51/$P51,""),"")</x:f>
+      </x:c>
+      <x:c r="U51" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V51" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W51" s="41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="X51" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y51" s="41" t="str"/>
+      <x:c r="Z51" s="41" t="str">
+        <x:v>Selectel Newsroom</x:v>
+      </x:c>
+      <x:c r="AA51" s="41" t="str">
+        <x:v>https://selectel.ru/about/newsroom/news/selectel-razmestil-novyj-vypusk-obligaczij-i-privlek-7-milliardov-rublej-na-razvitie-biznesa/</x:v>
+      </x:c>
+      <x:c r="AB51" s="41" t="str">
+        <x:v>Selectel разместил новый выпуск облигаций и привлек 7 миллиардов рублей на развитие бизнеса Selectel сообщил об успешном закрытии книги заявок в рамках размещения выпуска облигаций серии 001P-07R по ставке купона 15,00% годовых сроком на три года. В ходе формирования книги заявок общий спрос инвесторов превысил первоначальный ориентир по объему выпуска, что позволило увеличить объем выпуска с 5 до 7 млрд рублей и снизить итоговую ставку купона до 15,00% годовых.</x:v>
+      </x:c>
+      <x:c r="AC51" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="41" t="str">
+        <x:v>DL-251bf0d0b7b600c1</x:v>
+      </x:c>
+      <x:c r="B52" s="43" t="n">
+        <x:v>45642</x:v>
+      </x:c>
+      <x:c r="C52" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D52" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E52" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="F52" s="41" t="str">
+        <x:v>SELECTEL</x:v>
+      </x:c>
+      <x:c r="G52" s="41" t="str">
+        <x:v>Technology</x:v>
+      </x:c>
+      <x:c r="H52" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="I52" s="44"/>
+      <x:c r="J52" s="44"/>
+      <x:c r="K52" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L52" s="45" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M52" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="N52" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O52" s="44"/>
+      <x:c r="P52" s="44"/>
+      <x:c r="Q52" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R52" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S52" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J52&gt;0,$O52&gt;0,$K52=$R52),$J52/$O52,""),"")</x:f>
+      </x:c>
+      <x:c r="T52" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J52&gt;0,$P52&gt;0,$K52=$R52),$J52/$P52,""),"")</x:f>
+      </x:c>
+      <x:c r="U52" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V52" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W52" s="41" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="X52" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y52" s="41" t="str"/>
+      <x:c r="Z52" s="41" t="str">
+        <x:v>Selectel Newsroom</x:v>
+      </x:c>
+      <x:c r="AA52" s="41" t="str">
+        <x:v>https://selectel.ru/about/newsroom/news/selectel-soobshchaet-o-priobretenii-oblachnogo-provajdera-servers-ru/</x:v>
+      </x:c>
+      <x:c r="AB52" s="41" t="str">
+        <x:v>Selectel сообщает о приобретении облачного провайдера Servers.ru Selectel сообщает о приобретении 100% компании ООО «Единая сеть», работающей под брендами Servers.ru, Exepto.ru и Fozzy.ru. Сделка позволит ускорить рост бизнеса и усилить лидерские позиции Selectel на рынке облачных инфраструктурных сервисов.</x:v>
+      </x:c>
+      <x:c r="AC52" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="41" t="str">
+        <x:v>DL-aa5a93661389a659</x:v>
+      </x:c>
+      <x:c r="B53" s="43" t="n">
+        <x:v>45611</x:v>
+      </x:c>
+      <x:c r="C53" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D53" s="41" t="str">
+        <x:v>Announced</x:v>
+      </x:c>
+      <x:c r="E53" s="41" t="str">
+        <x:v>SELECTEL</x:v>
+      </x:c>
+      <x:c r="F53" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G53" s="41" t="str">
+        <x:v>Financials</x:v>
+      </x:c>
+      <x:c r="H53" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I53" s="44" t="n">
+        <x:v>3000000000</x:v>
+      </x:c>
+      <x:c r="J53" s="44"/>
+      <x:c r="K53" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L53" s="45"/>
+      <x:c r="M53" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N53" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O53" s="44"/>
+      <x:c r="P53" s="44"/>
+      <x:c r="Q53" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R53" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S53" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J53&gt;0,$O53&gt;0,$K53=$R53),$J53/$O53,""),"")</x:f>
+      </x:c>
+      <x:c r="T53" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J53&gt;0,$P53&gt;0,$K53=$R53),$J53/$P53,""),"")</x:f>
+      </x:c>
+      <x:c r="U53" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V53" s="41" t="str">
+        <x:v>целей финансирования инвестиционной программы</x:v>
+      </x:c>
+      <x:c r="W53" s="41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="X53" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y53" s="41" t="str"/>
+      <x:c r="Z53" s="41" t="str">
+        <x:v>Selectel Newsroom</x:v>
+      </x:c>
+      <x:c r="AA53" s="41" t="str">
+        <x:v>https://selectel.ru/about/newsroom/news/selectel-planiruet-razmeshhenie-obligaczij-obemom-3-milliarda-rublej-2/</x:v>
+      </x:c>
+      <x:c r="AB53" s="41" t="str">
+        <x:v>Selectel планирует размещение облигаций объемом 3 миллиарда рублей Компания Selectel планирует разместить новый выпуск облигаций объемом 3 млрд рублей для целей финансирования инвестиционной программы. Тип купона — переменный и определяется исходя из ключевой ставки Банка России плюс премия не выше 400 базисных пунктов. Срок обращения — 2,5 года с ежемесячной выплатой купона. Сбор заявок планируется провести в конце ноября.</x:v>
+      </x:c>
+      <x:c r="AC53" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="41" t="str">
+        <x:v>DL-c898acc93d60813b</x:v>
+      </x:c>
+      <x:c r="B54" s="43" t="n">
+        <x:v>45391</x:v>
+      </x:c>
+      <x:c r="C54" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D54" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E54" s="41" t="str">
+        <x:v>SELECTEL</x:v>
+      </x:c>
+      <x:c r="F54" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G54" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H54" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I54" s="44" t="n">
+        <x:v>4000000000</x:v>
+      </x:c>
+      <x:c r="J54" s="44"/>
+      <x:c r="K54" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L54" s="45" t="n">
+        <x:v>0.15</x:v>
+      </x:c>
+      <x:c r="M54" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N54" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O54" s="44"/>
+      <x:c r="P54" s="44"/>
+      <x:c r="Q54" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R54" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S54" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J54&gt;0,$O54&gt;0,$K54=$R54),$J54/$O54,""),"")</x:f>
+      </x:c>
+      <x:c r="T54" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J54&gt;0,$P54&gt;0,$K54=$R54),$J54/$P54,""),"")</x:f>
+      </x:c>
+      <x:c r="U54" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V54" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W54" s="41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="X54" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y54" s="41" t="str"/>
+      <x:c r="Z54" s="41" t="str">
+        <x:v>Selectel Newsroom</x:v>
+      </x:c>
+      <x:c r="AA54" s="41" t="str">
+        <x:v>https://selectel.ru/about/newsroom/news/selectel-na-fone-povyshennogo-sprosa-na-obligaczii-chetvertogo-vypuska-uvelichil-obem-razmeshheniya-do-4-mlrd-rublej/</x:v>
+      </x:c>
+      <x:c r="AB54" s="41" t="str">
+        <x:v>Selectel на фоне повышенного спроса на облигации четвертого выпуска увеличил объем размещения до 4 млрд рублей Компания Selectel сообщила об успешном закрытии книги заявок в рамках размещения четвертого выпуска облигаций. Объем выпуска составил 4 млрд рублей, ставка купона установлена на уровне 15% годовых с ежемесячной выплатой, срок обращения 2 года.</x:v>
+      </x:c>
+      <x:c r="AC54" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="41" t="str">
+        <x:v>DL-3b4a4419ab6b81bf</x:v>
+      </x:c>
+      <x:c r="B55" s="43" t="n">
+        <x:v>45357</x:v>
+      </x:c>
+      <x:c r="C55" s="41" t="str">
+        <x:v>DCM</x:v>
+      </x:c>
+      <x:c r="D55" s="41" t="str">
+        <x:v>Announced</x:v>
+      </x:c>
+      <x:c r="E55" s="41" t="str">
+        <x:v>SELECTEL</x:v>
+      </x:c>
+      <x:c r="F55" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="G55" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H55" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I55" s="44" t="n">
+        <x:v>3000000000</x:v>
+      </x:c>
+      <x:c r="J55" s="44"/>
+      <x:c r="K55" s="41" t="str">
+        <x:v>RUB</x:v>
+      </x:c>
+      <x:c r="L55" s="45"/>
+      <x:c r="M55" s="41" t="str">
+        <x:v>Not applicable</x:v>
+      </x:c>
+      <x:c r="N55" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O55" s="44"/>
+      <x:c r="P55" s="44"/>
+      <x:c r="Q55" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R55" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S55" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J55&gt;0,$O55&gt;0,$K55=$R55),$J55/$O55,""),"")</x:f>
+      </x:c>
+      <x:c r="T55" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J55&gt;0,$P55&gt;0,$K55=$R55),$J55/$P55,""),"")</x:f>
+      </x:c>
+      <x:c r="U55" s="41" t="str">
+        <x:v>Bonds</x:v>
+      </x:c>
+      <x:c r="V55" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W55" s="41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="X55" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y55" s="41" t="str"/>
+      <x:c r="Z55" s="41" t="str">
+        <x:v>Selectel Newsroom</x:v>
+      </x:c>
+      <x:c r="AA55" s="41" t="str">
+        <x:v>https://selectel.ru/about/newsroom/news/selectel-planiruet-razmeshhenie-obligaczij-obemom-3-milliarda-rublej/</x:v>
+      </x:c>
+      <x:c r="AB55" s="41" t="str">
+        <x:v>Selectel планирует размещение облигаций объемом 3 миллиарда рублей Selectel планирует разместить выпуск облигаций объемом 3 млрд рублей с фиксированной ставкой купона и сроком обращения 2 года. Ориентир доходности — премия не выше 275 базисных пунктов к значению кривой бескупонной доходности (КБД) Московской биржи на сроке 2 года. Купонные выплаты будут осуществляться ежемесячно. Сбор заявок планируется провести в первой декаде апреля.</x:v>
+      </x:c>
+      <x:c r="AC55" s="41" t="str">
+        <x:v>Screening record; verify against primary transaction documents.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="41" t="str">
+        <x:v>DL-0242cf80b3f97c9c</x:v>
+      </x:c>
+      <x:c r="B56" s="43" t="n">
+        <x:v>45288</x:v>
+      </x:c>
+      <x:c r="C56" s="41" t="str">
+        <x:v>M&amp;A</x:v>
+      </x:c>
+      <x:c r="D56" s="41" t="str">
+        <x:v>Reported</x:v>
+      </x:c>
+      <x:c r="E56" s="41" t="str">
+        <x:v>25% провайдера IT-инфраструктуры Selectel Инвестиционный фонд Tier 5, основанный Геворком Вермишяном</x:v>
+      </x:c>
+      <x:c r="F56" s="41" t="str">
+        <x:v>Инвестиционный фонд Tier 5</x:v>
+      </x:c>
+      <x:c r="G56" s="41" t="str">
+        <x:v>Not classified</x:v>
+      </x:c>
+      <x:c r="H56" s="41" t="str">
+        <x:v>Russia</x:v>
+      </x:c>
+      <x:c r="I56" s="44"/>
+      <x:c r="J56" s="44"/>
+      <x:c r="K56" s="41" t="str">
+        <x:v>NOT DISCLOSED</x:v>
+      </x:c>
+      <x:c r="L56" s="45" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="M56" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="N56" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="O56" s="44"/>
+      <x:c r="P56" s="44"/>
+      <x:c r="Q56" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="R56" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="S56" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J56&gt;0,$O56&gt;0,$K56=$R56),$J56/$O56,""),"")</x:f>
+      </x:c>
+      <x:c r="T56" s="46" t="str">
+        <x:f>IFERROR(IF(AND($J56&gt;0,$P56&gt;0,$K56=$R56),$J56/$P56,""),"")</x:f>
+      </x:c>
+      <x:c r="U56" s="41" t="str">
+        <x:v>Acquisition / disposal</x:v>
+      </x:c>
+      <x:c r="V56" s="41" t="str">
+        <x:v>Not disclosed</x:v>
+      </x:c>
+      <x:c r="W56" s="41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="X56" s="41" t="str">
+        <x:v>confirmed</x:v>
+      </x:c>
+      <x:c r="Y56" s="41" t="str"/>
+      <x:c r="Z56" s="41" t="str">
+        <x:v>Selectel Newsroom</x:v>
+      </x:c>
+      <x:c r="AA56" s="41" t="str">
+        <x:v>https://selectel.ru/about/newsroom/news/investicionnyj-fond-tier-5-priobrel-25-provajdera-it-infrastruktury-selectel/</x:v>
+      </x:c>
+      <x:c r="AB56" s="41" t="str">
+        <x:v>Инвестиционный фонд Tier 5 приобрел 25% провайдера IT-инфраструктуры Selectel Инвестиционный фонд Tier 5, основанный Геворком Вермишяном, ранее возглавлявшим «МегаФон», приобрел 25% провайдера IT-инфраструктуры Selectel, который входит в топ-3 российских IaaS-компаний по выручке. Детали сделки стороны не раскрывают.</x:v>
+      </x:c>
+      <x:c r="AC56" s="41" t="str">
         <x:v>Screening record; verify against primary transaction documents.</x:v>
       </x:c>
     </x:row>
@@ -4143,7 +5178,7 @@
     <x:mergeCell ref="A2:AC2"/>
     <x:mergeCell ref="A4:AC4"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="W7:W43">
+  <x:conditionalFormatting sqref="W7:W56">
     <x:cfRule type="colorScale" priority="1">
       <x:colorScale>
         <x:cfvo type="min"/>
@@ -4157,7 +5192,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R486e431c6e5f49cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84f7c49853e947be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4196,7 +5231,7 @@
     </x:row>
     <x:row r="4" ht="22" customHeight="1">
       <x:c r="A4" s="9" t="str">
-        <x:v>DCM | Reported</x:v>
+        <x:v>DCM | Completed</x:v>
       </x:c>
       <x:c r="B4" s="9"/>
       <x:c r="C4" s="9"/>
@@ -4211,7 +5246,7 @@
         <x:v>Headline</x:v>
       </x:c>
       <x:c r="B6" s="55" t="str">
-        <x:v>О регистрации выпуска биржевых облигаций, о включении его в Список ценных бумаг, допущенных к торгам, и о присвоении указанным биржевым облигациям регистрационного номера</x:v>
+        <x:v>МТС успешно закрыла книгу биржевых облигаций 003Р-03 на 20 млрд руб.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4219,7 +5254,7 @@
         <x:v>Announced date</x:v>
       </x:c>
       <x:c r="B7" s="58" t="n">
-        <x:v>46199</x:v>
+        <x:v>46201</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -4227,7 +5262,7 @@
         <x:v>Target / Issuer</x:v>
       </x:c>
       <x:c r="B8" s="56" t="str">
-        <x:v>Not disclosed</x:v>
+        <x:v>MTSS</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -4242,7 +5277,9 @@
       <x:c r="A10" s="49" t="str">
         <x:v>Transaction value</x:v>
       </x:c>
-      <x:c r="B10" s="59"/>
+      <x:c r="B10" s="59" t="n">
+        <x:v>20000000000</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="49" t="str">
@@ -4255,7 +5292,7 @@
         <x:v>Currency</x:v>
       </x:c>
       <x:c r="B12" s="56" t="str">
-        <x:v>NOT DISCLOSED</x:v>
+        <x:v>RUB</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4329,7 +5366,7 @@
         <x:v>Evidence / score</x:v>
       </x:c>
       <x:c r="B22" s="56" t="str">
-        <x:v>confirmed / 7 out of 10</x:v>
+        <x:v>confirmed / 6 out of 10</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -4337,7 +5374,7 @@
         <x:v>Source</x:v>
       </x:c>
       <x:c r="B23" s="56" t="str">
-        <x:v>MOEX disclosure</x:v>
+        <x:v>MTS Investor Relations</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4428,13 +5465,13 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="41" t="str">
-        <x:v>DL-moex-101492</x:v>
+        <x:v>DL-4d8f7bcb385b1c88</x:v>
       </x:c>
       <x:c r="B7" s="43" t="n">
-        <x:v>46199</x:v>
+        <x:v>46201</x:v>
       </x:c>
       <x:c r="C7" s="41" t="str">
-        <x:v>MOEX disclosure</x:v>
+        <x:v>MTS Investor Relations</x:v>
       </x:c>
       <x:c r="D7" s="41" t="str">
         <x:v>See Precedent Transactions → Source URL</x:v>
@@ -4443,12 +5480,12 @@
         <x:v>confirmed</x:v>
       </x:c>
       <x:c r="F7" s="41" t="str">
-        <x:v>О регистрации выпуска биржевых облигаций, о включении его в Список ценных бумаг, допущенных к торгам, и о присвоении указанным биржевым облигациям регистрационного номера</x:v>
+        <x:v>МТС успешно закрыла книгу биржевых облигаций 003Р-03 на 20 млрд руб.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="41" t="str">
-        <x:v>DL-moex-101473</x:v>
+        <x:v>DL-moex-101492</x:v>
       </x:c>
       <x:c r="B8" s="43" t="n">
         <x:v>46199</x:v>
@@ -4463,12 +5500,12 @@
         <x:v>confirmed</x:v>
       </x:c>
       <x:c r="F8" s="41" t="str">
-        <x:v>О регистрации проспекта биржевых облигаций</x:v>
+        <x:v>О регистрации выпуска биржевых облигаций, о включении его в Список ценных бумаг, допущенных к торгам, и о присвоении указанным биржевым облигациям регистрационного номера</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="41" t="str">
-        <x:v>DL-moex-101468</x:v>
+        <x:v>DL-moex-101473</x:v>
       </x:c>
       <x:c r="B9" s="43" t="n">
         <x:v>46199</x:v>
@@ -4483,12 +5520,12 @@
         <x:v>confirmed</x:v>
       </x:c>
       <x:c r="F9" s="41" t="str">
-        <x:v>О регистрации изменений в эмиссионные документы</x:v>
+        <x:v>О регистрации проспекта биржевых облигаций</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="41" t="str">
-        <x:v>DL-moex-101457</x:v>
+        <x:v>DL-moex-101468</x:v>
       </x:c>
       <x:c r="B10" s="43" t="n">
         <x:v>46199</x:v>
@@ -4503,12 +5540,12 @@
         <x:v>confirmed</x:v>
       </x:c>
       <x:c r="F10" s="41" t="str">
-        <x:v>О порядке сбора заявок и заключения сделок при размещении облигаций серии Б-1-403 Банк ВТБ (публичное акционерное общество) с 29 июня 2026 года</x:v>
+        <x:v>О регистрации изменений в эмиссионные документы</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="41" t="str">
-        <x:v>DL-moex-101454</x:v>
+        <x:v>DL-moex-101457</x:v>
       </x:c>
       <x:c r="B11" s="43" t="n">
         <x:v>46199</x:v>
@@ -4523,12 +5560,12 @@
         <x:v>confirmed</x:v>
       </x:c>
       <x:c r="F11" s="41" t="str">
-        <x:v>О порядке приобретения облигаций серии 001P-04 ООО "АРЕНЗА-ПРО" с 29 июня 2026 год</x:v>
+        <x:v>О порядке сбора заявок и заключения сделок при размещении облигаций серии Б-1-403 Банк ВТБ (публичное акционерное общество) с 29 июня 2026 года</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="41" t="str">
-        <x:v>DL-moex-101451</x:v>
+        <x:v>DL-moex-101454</x:v>
       </x:c>
       <x:c r="B12" s="43" t="n">
         <x:v>46199</x:v>
@@ -4543,12 +5580,12 @@
         <x:v>confirmed</x:v>
       </x:c>
       <x:c r="F12" s="41" t="str">
-        <x:v>О проведении выкупа облигаций с 29 июня по 03 июля 2026 года</x:v>
+        <x:v>О порядке приобретения облигаций серии 001P-04 ООО "АРЕНЗА-ПРО" с 29 июня 2026 год</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="41" t="str">
-        <x:v>DL-moex-101450</x:v>
+        <x:v>DL-moex-101451</x:v>
       </x:c>
       <x:c r="B13" s="43" t="n">
         <x:v>46199</x:v>
@@ -4563,67 +5600,67 @@
         <x:v>confirmed</x:v>
       </x:c>
       <x:c r="F13" s="41" t="str">
-        <x:v>Дополнительные условия проведения торгов по выкупу облигаций серии 003Р-02 ООО "Концерн "РОССИУМ" 26 июня 2026 года</x:v>
+        <x:v>О проведении выкупа облигаций с 29 июня по 03 июля 2026 года</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="41" t="str">
-        <x:v>DL-bec65812ff9fcfae</x:v>
+        <x:v>DL-moex-101450</x:v>
       </x:c>
       <x:c r="B14" s="43" t="n">
-        <x:v>46197</x:v>
+        <x:v>46199</x:v>
       </x:c>
       <x:c r="C14" s="41" t="str">
-        <x:v>ComNews.ru</x:v>
+        <x:v>MOEX disclosure</x:v>
       </x:c>
       <x:c r="D14" s="41" t="str">
         <x:v>See Precedent Transactions → Source URL</x:v>
       </x:c>
       <x:c r="E14" s="41" t="str">
-        <x:v>unverified</x:v>
+        <x:v>confirmed</x:v>
       </x:c>
       <x:c r="F14" s="41" t="str">
-        <x:v>Selectel разместит облигации на 5 млрд руб. для рефинансирования и инвестиций - ComNews.ru</x:v>
+        <x:v>Дополнительные условия проведения торгов по выкупу облигаций серии 003Р-02 ООО "Концерн "РОССИУМ" 26 июня 2026 года</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="41" t="str">
-        <x:v>DL-48bd4fc3fa031e6c</x:v>
+        <x:v>DL-bec65812ff9fcfae</x:v>
       </x:c>
       <x:c r="B15" s="43" t="n">
-        <x:v>46192</x:v>
+        <x:v>46197</x:v>
       </x:c>
       <x:c r="C15" s="41" t="str">
-        <x:v>Yandex Investor Relations</x:v>
+        <x:v>ComNews.ru</x:v>
       </x:c>
       <x:c r="D15" s="41" t="str">
         <x:v>See Precedent Transactions → Source URL</x:v>
       </x:c>
       <x:c r="E15" s="41" t="str">
-        <x:v>confirmed</x:v>
+        <x:v>unverified</x:v>
       </x:c>
       <x:c r="F15" s="41" t="str">
-        <x:v>Яндекс разместил два выпуска биржевых облигаций на общую сумму 60 млрд рублей</x:v>
+        <x:v>Selectel разместит облигации на 5 млрд руб. для рефинансирования и инвестиций - ComNews.ru</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="41" t="str">
-        <x:v>DL-9092ffd6a36a0a81</x:v>
+        <x:v>DL-7a721642a53e0f1d</x:v>
       </x:c>
       <x:c r="B16" s="43" t="n">
-        <x:v>46183</x:v>
+        <x:v>46192</x:v>
       </x:c>
       <x:c r="C16" s="41" t="str">
-        <x:v>Интерфакс</x:v>
+        <x:v>Yandex Investor Relations</x:v>
       </x:c>
       <x:c r="D16" s="41" t="str">
         <x:v>See Precedent Transactions → Source URL</x:v>
       </x:c>
       <x:c r="E16" s="41" t="str">
-        <x:v>unverified</x:v>
+        <x:v>confirmed</x:v>
       </x:c>
       <x:c r="F16" s="41" t="str">
-        <x:v>"Норникель" зафиксировал объем размещения облигаций на уровне 3 млрд юаней - Интерфакс</x:v>
+        <x:v>Яндекс разместил два выпуска биржевых облигаций на общую сумму 60 млрд рублей</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
@@ -4663,7 +5700,7 @@
         <x:v>Duplicate deal IDs</x:v>
       </x:c>
       <x:c r="B23" t="n">
-        <x:f>SUMPRODUCT(--(COUNTIF('Precedent Transactions'!$A$7:$A$43,'Precedent Transactions'!$A$7:$A$43)&gt;1))/2</x:f>
+        <x:f>SUMPRODUCT(--(COUNTIF('Precedent Transactions'!$A$7:$A$56,'Precedent Transactions'!$A$7:$A$56)&gt;1))/2</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C23" t="n">
@@ -4686,7 +5723,7 @@
         <x:v>Missing source URLs</x:v>
       </x:c>
       <x:c r="B24" t="n">
-        <x:f>COUNTBLANK('Precedent Transactions'!$AA$7:$AA$43)</x:f>
+        <x:f>COUNTBLANK('Precedent Transactions'!$AA$7:$AA$56)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C24" t="n">
@@ -4709,7 +5746,7 @@
         <x:v>Missing announced dates</x:v>
       </x:c>
       <x:c r="B25" t="n">
-        <x:f>COUNTBLANK('Precedent Transactions'!$B$7:$B$43)</x:f>
+        <x:f>COUNTBLANK('Precedent Transactions'!$B$7:$B$56)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C25" t="n">
@@ -4732,7 +5769,7 @@
         <x:v>Unsafe / non-HTTP URLs</x:v>
       </x:c>
       <x:c r="B26" t="n">
-        <x:f>SUMPRODUCT(--(LEFT('Precedent Transactions'!$AA$7:$AA$43,4)&lt;&gt;"http"),--('Precedent Transactions'!$A$7:$A$43&lt;&gt;""))</x:f>
+        <x:f>SUMPRODUCT(--(LEFT('Precedent Transactions'!$AA$7:$AA$56,4)&lt;&gt;"http"),--('Precedent Transactions'!$A$7:$A$56&lt;&gt;""))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C26" t="n">
@@ -4755,15 +5792,15 @@
         <x:v>Missing target / issuer</x:v>
       </x:c>
       <x:c r="B27" t="n">
-        <x:f>COUNTIF('Precedent Transactions'!$E$7:$E$43,"Not disclosed")</x:f>
-        <x:v>20</x:v>
+        <x:f>COUNTIF('Precedent Transactions'!$E$7:$E$56,"Not disclosed")</x:f>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C27" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D27" t="n">
         <x:f>B27-C27</x:f>
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E27" t="n">
         <x:v>0</x:v>
@@ -4778,7 +5815,7 @@
         <x:v>EV without revenue/EBITDA</x:v>
       </x:c>
       <x:c r="B28" t="n">
-        <x:f>SUMPRODUCT(--('Precedent Transactions'!$J$7:$J$43&gt;0),--('Precedent Transactions'!$O$7:$O$43=""),--('Precedent Transactions'!$P$7:$P$43=""))</x:f>
+        <x:f>SUMPRODUCT(--('Precedent Transactions'!$J$7:$J$56&gt;0),--('Precedent Transactions'!$O$7:$O$56=""),--('Precedent Transactions'!$P$7:$P$56=""))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C28" t="n">
@@ -4801,7 +5838,7 @@
         <x:v>Multiple without enterprise value</x:v>
       </x:c>
       <x:c r="B29" t="n">
-        <x:f>SUMPRODUCT(--('Precedent Transactions'!$J$7:$J$43=""),--((('Precedent Transactions'!$S$7:$S$43&gt;0)+('Precedent Transactions'!$T$7:$T$43&gt;0))&gt;0))</x:f>
+        <x:f>SUMPRODUCT(--('Precedent Transactions'!$J$7:$J$56=""),--((('Precedent Transactions'!$S$7:$S$56&gt;0)+('Precedent Transactions'!$T$7:$T$56&gt;0))&gt;0))</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C29" t="n">

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-02 | Build a4432f860b74 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-03 | Build a4432f860b74 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-03 | Build a4432f860b74 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-02 | Build a4432f860b74 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-02 | Build a4432f860b74 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-03 | Build a4432f860b74 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -6742,13 +6742,10 @@
         <v>237</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="K49" s="8">
-        <v>35000000000</v>
+        <v>70</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>70</v>
@@ -11567,7 +11564,7 @@
         <v>258</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>70</v>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3790" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3825" uniqueCount="578">
   <si>
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-03 | Build a4432f860b74 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-03 | Build e80bc25a208d | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -998,7 +998,7 @@
     <t>https://rb.ru/news/vk-prodal-25-akcij-tochka-banka-sdelku-ocenili-v-212-mlrd-vdvoe-vyshe-iznachalnoj-stoimosti-bumag/</t>
   </si>
   <si>
-    <t>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.RU</t>
+    <t>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.ru</t>
   </si>
   <si>
     <t>DL-4774de17c61c14e4</t>
@@ -1073,6 +1073,15 @@
     <t>Selectel разместил новый выпуск облигаций и привлек 7 миллиардов рублей на развитие бизнеса</t>
   </si>
   <si>
+    <t>DL-e400cd99f963631a</t>
+  </si>
+  <si>
+    <t>https://ir.yandex.ru/press-releases?year=2025&amp;id=01-13-03-2025</t>
+  </si>
+  <si>
+    <t>Яндекс планирует выпустить биржевые облигации</t>
+  </si>
+  <si>
     <t>DL-251bf0d0b7b600c1</t>
   </si>
   <si>
@@ -1689,6 +1698,9 @@
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNTmtrN3N0YVN0c0NuVnBscUJvbzdVbWZ5OXczRTkySkx1T1hKdWJvZlFWNEFqbkxhRmpXVEVQZUdIcjdOZkNFRnJhX1huRGRmelhla1RRTURfejMzd2FIMU9ZcmQ4REtOWWEyZ3JhLUgwSmI2UDhJM2s4TkNRekY0T3ZtcEJNbUYzNTQzOXRITGxsN1A0N1duQ3FKeE5fTXIxMUVJTlh3?oc=5</t>
+  </si>
+  <si>
+    <t>official_issuer</t>
   </si>
   <si>
     <t>issuer_ir</t>
@@ -1862,8 +1874,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DealsTable" displayName="DealsTable" ref="A6:AT88" totalsRowShown="0">
-  <autoFilter ref="A6:AT88"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DealsTable" displayName="DealsTable" ref="A6:AT89" totalsRowShown="0">
+  <autoFilter ref="A6:AT89"/>
   <tableColumns count="46">
     <tableColumn id="1" name="Deal ID"/>
     <tableColumn id="2" name="Announced Date"/>
@@ -1964,8 +1976,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:I150" totalsRowShown="0">
-  <autoFilter ref="A6:I150"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:I151" totalsRowShown="0">
+  <autoFilter ref="A6:I151"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Deal ID"/>
     <tableColumn id="2" name="Date"/>
@@ -2348,7 +2360,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B7">
         <v>27</v>
@@ -2357,10 +2369,10 @@
         <v>8</v>
       </c>
       <c r="D7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7">
         <v>45</v>
@@ -2433,7 +2445,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT88"/>
+  <dimension ref="A1:AT89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="16.7109375" customWidth="1"/>
@@ -6742,10 +6754,13 @@
         <v>237</v>
       </c>
       <c r="J49" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="K49" s="8">
+        <v>35000000000</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>70</v>
@@ -9117,25 +9132,25 @@
         <v>351</v>
       </c>
       <c r="B74" s="7">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>195</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I74" s="6" t="s">
         <v>237</v>
@@ -9147,25 +9162,25 @@
         <v>70</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>70</v>
       </c>
       <c r="Q74" s="6" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S74" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U74" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="X74" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AB74" s="6" t="s">
         <v>71</v>
@@ -9186,10 +9201,10 @@
         <v>75</v>
       </c>
       <c r="AN74" s="6" t="s">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="AO74" s="6">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AP74" s="6" t="s">
         <v>77</v>
@@ -9198,7 +9213,7 @@
         <v>1</v>
       </c>
       <c r="AR74" s="6" t="s">
-        <v>348</v>
+        <v>238</v>
       </c>
       <c r="AS74" s="6" t="s">
         <v>352</v>
@@ -9212,64 +9227,61 @@
         <v>354</v>
       </c>
       <c r="B75" s="7">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>195</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>347</v>
+        <v>70</v>
       </c>
       <c r="G75" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I75" s="6" t="s">
-        <v>9</v>
+        <v>237</v>
       </c>
       <c r="J75" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="K75" s="8">
-        <v>3000000000</v>
+        <v>70</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P75" s="6" t="s">
         <v>70</v>
       </c>
       <c r="Q75" s="6" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S75" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="U75" s="6" t="s">
-        <v>355</v>
+        <v>71</v>
       </c>
       <c r="X75" s="6" t="s">
-        <v>356</v>
+        <v>71</v>
       </c>
       <c r="AB75" s="6" t="s">
         <v>71</v>
       </c>
       <c r="AD75" s="6" t="s">
-        <v>357</v>
+        <v>70</v>
       </c>
       <c r="AH75" s="6" t="s">
         <v>70</v>
@@ -9284,10 +9296,10 @@
         <v>75</v>
       </c>
       <c r="AN75" s="6" t="s">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="AO75" s="6">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AP75" s="6" t="s">
         <v>77</v>
@@ -9299,18 +9311,18 @@
         <v>348</v>
       </c>
       <c r="AS75" s="6" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="AT75" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="76" spans="1:46">
       <c r="A76" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B76" s="7">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>6</v>
@@ -9319,7 +9331,7 @@
         <v>195</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>347</v>
@@ -9331,13 +9343,13 @@
         <v>71</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="J76" s="6" t="s">
         <v>73</v>
       </c>
       <c r="K76" s="8">
-        <v>4000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="M76" s="6" t="s">
         <v>83</v>
@@ -9357,20 +9369,17 @@
       <c r="S76" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="T76" s="9">
-        <v>0.15</v>
-      </c>
       <c r="U76" s="6" t="s">
-        <v>70</v>
+        <v>358</v>
       </c>
       <c r="X76" s="6" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="AB76" s="6" t="s">
         <v>71</v>
       </c>
       <c r="AD76" s="6" t="s">
-        <v>70</v>
+        <v>360</v>
       </c>
       <c r="AH76" s="6" t="s">
         <v>70</v>
@@ -9400,18 +9409,18 @@
         <v>348</v>
       </c>
       <c r="AS76" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="AT76" s="6" t="s">
         <v>362</v>
-      </c>
-      <c r="AT76" s="6" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="77" spans="1:46">
       <c r="A77" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B77" s="7">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>6</v>
@@ -9420,7 +9429,7 @@
         <v>195</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>347</v>
@@ -9438,7 +9447,7 @@
         <v>73</v>
       </c>
       <c r="K77" s="8">
-        <v>3000000000</v>
+        <v>4000000000</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>83</v>
@@ -9458,11 +9467,14 @@
       <c r="S77" s="6" t="s">
         <v>70</v>
       </c>
+      <c r="T77" s="9">
+        <v>0.15</v>
+      </c>
       <c r="U77" s="6" t="s">
         <v>70</v>
       </c>
       <c r="X77" s="6" t="s">
-        <v>70</v>
+        <v>364</v>
       </c>
       <c r="AB77" s="6" t="s">
         <v>71</v>
@@ -9501,33 +9513,33 @@
         <v>365</v>
       </c>
       <c r="AT77" s="6" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="78" spans="1:46">
       <c r="A78" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B78" s="7">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>195</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>368</v>
+        <v>71</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I78" s="6" t="s">
         <v>72</v>
@@ -9535,29 +9547,32 @@
       <c r="J78" s="6" t="s">
         <v>73</v>
       </c>
+      <c r="K78" s="8">
+        <v>3000000000</v>
+      </c>
       <c r="M78" s="6" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>70</v>
       </c>
       <c r="Q78" s="6" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="R78" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="S78" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="U78" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="X78" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AB78" s="6" t="s">
         <v>71</v>
@@ -9578,10 +9593,10 @@
         <v>75</v>
       </c>
       <c r="AN78" s="6" t="s">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="AO78" s="6">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AP78" s="6" t="s">
         <v>77</v>
@@ -9593,18 +9608,18 @@
         <v>348</v>
       </c>
       <c r="AS78" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AT78" s="6" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
     </row>
     <row r="79" spans="1:46">
       <c r="A79" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B79" s="7">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>4</v>
@@ -9613,38 +9628,35 @@
         <v>195</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G79" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>374</v>
+        <v>70</v>
       </c>
       <c r="I79" s="6" t="s">
-        <v>237</v>
+        <v>72</v>
       </c>
       <c r="J79" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="K79" s="8">
-        <v>28000000000</v>
+        <v>73</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="N79" s="9">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>376</v>
+        <v>70</v>
       </c>
       <c r="P79" s="6" t="s">
         <v>70</v>
       </c>
+      <c r="Q79" s="6" t="s">
+        <v>124</v>
+      </c>
       <c r="R79" s="6" t="s">
         <v>71</v>
       </c>
@@ -9661,54 +9673,48 @@
         <v>71</v>
       </c>
       <c r="AD79" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="AE79" s="8">
-        <v>3653708000</v>
-      </c>
-      <c r="AG79" s="7">
-        <v>44957</v>
+        <v>70</v>
       </c>
       <c r="AH79" s="6" t="s">
-        <v>185</v>
+        <v>70</v>
       </c>
       <c r="AK79" s="6" t="s">
-        <v>378</v>
+        <v>70</v>
       </c>
       <c r="AL79" s="6" t="s">
-        <v>379</v>
+        <v>70</v>
       </c>
       <c r="AM79" s="6" t="s">
-        <v>380</v>
+        <v>75</v>
       </c>
       <c r="AN79" s="6" t="s">
-        <v>197</v>
+        <v>76</v>
       </c>
       <c r="AO79" s="6">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AP79" s="6" t="s">
         <v>77</v>
       </c>
       <c r="AQ79" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR79" s="6" t="s">
-        <v>381</v>
+        <v>348</v>
       </c>
       <c r="AS79" s="6" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="AT79" s="6" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
     </row>
     <row r="80" spans="1:46">
       <c r="A80" s="6" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B80" s="7">
-        <v>44707</v>
+        <v>45190</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>4</v>
@@ -9720,25 +9726,22 @@
         <v>160</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I80" s="6" t="s">
         <v>237</v>
       </c>
       <c r="J80" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K80" s="8">
-        <v>61000000000</v>
-      </c>
-      <c r="L80" s="8">
-        <v>69000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="M80" s="6" t="s">
         <v>185</v>
@@ -9747,13 +9750,10 @@
         <v>1</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q80" s="6" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>71</v>
@@ -9771,34 +9771,25 @@
         <v>71</v>
       </c>
       <c r="AD80" s="6" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="AE80" s="8">
-        <v>12851000000</v>
-      </c>
-      <c r="AF80" s="8">
-        <v>2966000000</v>
+        <v>3653708000</v>
       </c>
       <c r="AG80" s="7">
-        <v>44589</v>
+        <v>44957</v>
       </c>
       <c r="AH80" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="AI80" s="5">
-        <v>5.369231966383939</v>
-      </c>
-      <c r="AJ80" s="5">
-        <v>23.26365475387728</v>
-      </c>
       <c r="AK80" s="6" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="AL80" s="6" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="AM80" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AN80" s="6" t="s">
         <v>197</v>
@@ -9813,21 +9804,21 @@
         <v>2</v>
       </c>
       <c r="AR80" s="6" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="AS80" s="6" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="AT80" s="6" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="81" spans="1:46">
       <c r="A81" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="B81" s="7">
-        <v>44640</v>
+        <v>44707</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>4</v>
@@ -9839,22 +9830,25 @@
         <v>160</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I81" s="6" t="s">
         <v>237</v>
       </c>
       <c r="J81" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K81" s="8">
-        <v>10400000000</v>
+        <v>61000000000</v>
+      </c>
+      <c r="L81" s="8">
+        <v>69000000000</v>
       </c>
       <c r="M81" s="6" t="s">
         <v>185</v>
@@ -9863,10 +9857,13 @@
         <v>1</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>70</v>
+        <v>391</v>
+      </c>
+      <c r="Q81" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>71</v>
@@ -9884,25 +9881,34 @@
         <v>71</v>
       </c>
       <c r="AD81" s="6" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="AE81" s="8">
-        <v>592200000</v>
+        <v>12851000000</v>
+      </c>
+      <c r="AF81" s="8">
+        <v>2966000000</v>
       </c>
       <c r="AG81" s="7">
-        <v>44592</v>
+        <v>44589</v>
       </c>
       <c r="AH81" s="6" t="s">
         <v>185</v>
       </c>
+      <c r="AI81" s="5">
+        <v>5.369231966383939</v>
+      </c>
+      <c r="AJ81" s="5">
+        <v>23.26365475387728</v>
+      </c>
       <c r="AK81" s="6" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="AL81" s="6" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="AM81" s="6" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="AN81" s="6" t="s">
         <v>197</v>
@@ -9917,21 +9923,21 @@
         <v>2</v>
       </c>
       <c r="AR81" s="6" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="AS81" s="6" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="AT81" s="6" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="82" spans="1:46">
       <c r="A82" s="6" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B82" s="7">
-        <v>44592</v>
+        <v>44640</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>4</v>
@@ -9943,25 +9949,22 @@
         <v>160</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I82" s="6" t="s">
         <v>237</v>
       </c>
       <c r="J82" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K82" s="8">
-        <v>16500000000</v>
-      </c>
-      <c r="L82" s="8">
-        <v>16500000000</v>
+        <v>10400000000</v>
       </c>
       <c r="M82" s="6" t="s">
         <v>185</v>
@@ -9970,7 +9973,7 @@
         <v>1</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>70</v>
@@ -9991,28 +9994,25 @@
         <v>71</v>
       </c>
       <c r="AD82" s="6" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="AE82" s="8">
-        <v>3217170000</v>
+        <v>592200000</v>
       </c>
       <c r="AG82" s="7">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="AH82" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="AI82" s="5">
-        <v>5.128731151913017</v>
-      </c>
       <c r="AK82" s="6" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="AL82" s="6" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="AM82" s="6" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AN82" s="6" t="s">
         <v>197</v>
@@ -10027,21 +10027,21 @@
         <v>2</v>
       </c>
       <c r="AR82" s="6" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="AS82" s="6" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="AT82" s="6" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="83" spans="1:46">
       <c r="A83" s="6" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B83" s="7">
-        <v>44579</v>
+        <v>44592</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>4</v>
@@ -10053,25 +10053,25 @@
         <v>160</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="G83" s="6" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I83" s="6" t="s">
         <v>237</v>
       </c>
       <c r="J83" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K83" s="8">
-        <v>68700000000</v>
+        <v>16500000000</v>
       </c>
       <c r="L83" s="8">
-        <v>68700000000</v>
+        <v>16500000000</v>
       </c>
       <c r="M83" s="6" t="s">
         <v>185</v>
@@ -10080,13 +10080,10 @@
         <v>1</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q83" s="6" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>71</v>
@@ -10104,28 +10101,28 @@
         <v>71</v>
       </c>
       <c r="AD83" s="6" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="AE83" s="8">
-        <v>8086000000</v>
+        <v>3217170000</v>
       </c>
       <c r="AG83" s="7">
-        <v>44196</v>
+        <v>44561</v>
       </c>
       <c r="AH83" s="6" t="s">
         <v>185</v>
       </c>
       <c r="AI83" s="5">
-        <v>8.496166213208014</v>
+        <v>5.128731151913017</v>
       </c>
       <c r="AK83" s="6" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="AL83" s="6" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="AM83" s="6" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="AN83" s="6" t="s">
         <v>197</v>
@@ -10140,21 +10137,21 @@
         <v>2</v>
       </c>
       <c r="AR83" s="6" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="AS83" s="6" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="AT83" s="6" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
     </row>
     <row r="84" spans="1:46">
       <c r="A84" s="6" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B84" s="7">
-        <v>44166</v>
+        <v>44579</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>4</v>
@@ -10166,25 +10163,25 @@
         <v>160</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I84" s="6" t="s">
         <v>237</v>
       </c>
       <c r="J84" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K84" s="8">
-        <v>27700000000</v>
+        <v>68700000000</v>
       </c>
       <c r="L84" s="8">
-        <v>27700000000</v>
+        <v>68700000000</v>
       </c>
       <c r="M84" s="6" t="s">
         <v>185</v>
@@ -10193,10 +10190,13 @@
         <v>1</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>70</v>
+        <v>420</v>
+      </c>
+      <c r="Q84" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>71</v>
@@ -10214,28 +10214,28 @@
         <v>71</v>
       </c>
       <c r="AD84" s="6" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="AE84" s="8">
-        <v>630422000</v>
+        <v>8086000000</v>
       </c>
       <c r="AG84" s="7">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="AH84" s="6" t="s">
         <v>185</v>
       </c>
       <c r="AI84" s="5">
-        <v>43.93882193197572</v>
+        <v>8.496166213208014</v>
       </c>
       <c r="AK84" s="6" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="AL84" s="6" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="AM84" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AN84" s="6" t="s">
         <v>197</v>
@@ -10250,21 +10250,21 @@
         <v>2</v>
       </c>
       <c r="AR84" s="6" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="AS84" s="6" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="AT84" s="6" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="85" spans="1:46">
       <c r="A85" s="6" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B85" s="7">
-        <v>44131</v>
+        <v>44166</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>4</v>
@@ -10276,22 +10276,25 @@
         <v>160</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="G85" s="6" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I85" s="6" t="s">
         <v>237</v>
       </c>
       <c r="J85" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K85" s="8">
-        <v>35000000000</v>
+        <v>27700000000</v>
+      </c>
+      <c r="L85" s="8">
+        <v>27700000000</v>
       </c>
       <c r="M85" s="6" t="s">
         <v>185</v>
@@ -10300,7 +10303,7 @@
         <v>1</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>206</v>
+        <v>390</v>
       </c>
       <c r="P85" s="6" t="s">
         <v>70</v>
@@ -10321,25 +10324,28 @@
         <v>71</v>
       </c>
       <c r="AD85" s="6" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="AE85" s="8">
-        <v>3162666000</v>
+        <v>630422000</v>
       </c>
       <c r="AG85" s="7">
-        <v>43918</v>
+        <v>43861</v>
       </c>
       <c r="AH85" s="6" t="s">
         <v>185</v>
       </c>
+      <c r="AI85" s="5">
+        <v>43.93882193197572</v>
+      </c>
       <c r="AK85" s="6" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="AL85" s="6" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="AM85" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AN85" s="6" t="s">
         <v>197</v>
@@ -10354,21 +10360,21 @@
         <v>2</v>
       </c>
       <c r="AR85" s="6" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="AS85" s="6" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="AT85" s="6" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="86" spans="1:46">
       <c r="A86" s="6" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B86" s="7">
-        <v>43626</v>
+        <v>44131</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>4</v>
@@ -10380,25 +10386,22 @@
         <v>160</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I86" s="6" t="s">
         <v>237</v>
       </c>
       <c r="J86" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K86" s="8">
-        <v>15700000000</v>
-      </c>
-      <c r="L86" s="8">
-        <v>15700000000</v>
+        <v>35000000000</v>
       </c>
       <c r="M86" s="6" t="s">
         <v>185</v>
@@ -10428,28 +10431,25 @@
         <v>71</v>
       </c>
       <c r="AD86" s="6" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="AE86" s="8">
-        <v>1159000000</v>
+        <v>3162666000</v>
       </c>
       <c r="AG86" s="7">
-        <v>43465</v>
+        <v>43918</v>
       </c>
       <c r="AH86" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="AI86" s="5">
-        <v>13.54616048317515</v>
-      </c>
       <c r="AK86" s="6" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AL86" s="6" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="AM86" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AN86" s="6" t="s">
         <v>197</v>
@@ -10464,21 +10464,21 @@
         <v>2</v>
       </c>
       <c r="AR86" s="6" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="AS86" s="6" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="AT86" s="6" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="87" spans="1:46">
       <c r="A87" s="6" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B87" s="7">
-        <v>43401</v>
+        <v>43626</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>4</v>
@@ -10490,25 +10490,25 @@
         <v>160</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="G87" s="6" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I87" s="6" t="s">
         <v>237</v>
       </c>
       <c r="J87" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K87" s="8">
-        <v>34000000000</v>
+        <v>15700000000</v>
       </c>
       <c r="L87" s="8">
-        <v>34000000000</v>
+        <v>15700000000</v>
       </c>
       <c r="M87" s="6" t="s">
         <v>185</v>
@@ -10517,7 +10517,7 @@
         <v>1</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>376</v>
+        <v>206</v>
       </c>
       <c r="P87" s="6" t="s">
         <v>70</v>
@@ -10538,28 +10538,28 @@
         <v>71</v>
       </c>
       <c r="AD87" s="6" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="AE87" s="8">
-        <v>2920461000</v>
+        <v>1159000000</v>
       </c>
       <c r="AG87" s="7">
-        <v>43159</v>
+        <v>43465</v>
       </c>
       <c r="AH87" s="6" t="s">
         <v>185</v>
       </c>
       <c r="AI87" s="5">
-        <v>11.64199761612978</v>
+        <v>13.54616048317515</v>
       </c>
       <c r="AK87" s="6" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="AL87" s="6" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="AM87" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AN87" s="6" t="s">
         <v>197</v>
@@ -10574,21 +10574,21 @@
         <v>2</v>
       </c>
       <c r="AR87" s="6" t="s">
-        <v>455</v>
+        <v>433</v>
       </c>
       <c r="AS87" s="6" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="AT87" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
     <row r="88" spans="1:46">
       <c r="A88" s="6" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B88" s="7">
-        <v>42534</v>
+        <v>43401</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>4</v>
@@ -10600,25 +10600,25 @@
         <v>160</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>416</v>
+        <v>454</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I88" s="6" t="s">
         <v>237</v>
       </c>
       <c r="J88" s="6" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K88" s="8">
-        <v>26200000000</v>
+        <v>34000000000</v>
       </c>
       <c r="L88" s="8">
-        <v>26200000000</v>
+        <v>34000000000</v>
       </c>
       <c r="M88" s="6" t="s">
         <v>185</v>
@@ -10627,7 +10627,7 @@
         <v>1</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>70</v>
@@ -10648,34 +10648,28 @@
         <v>71</v>
       </c>
       <c r="AD88" s="6" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="AE88" s="8">
-        <v>2990911000</v>
-      </c>
-      <c r="AF88" s="8">
-        <v>254472000</v>
+        <v>2920461000</v>
       </c>
       <c r="AG88" s="7">
-        <v>42369</v>
+        <v>43159</v>
       </c>
       <c r="AH88" s="6" t="s">
         <v>185</v>
       </c>
       <c r="AI88" s="5">
-        <v>8.759872828044699</v>
-      </c>
-      <c r="AJ88" s="5">
-        <v>102.9582822471628</v>
+        <v>11.64199761612978</v>
       </c>
       <c r="AK88" s="6" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="AL88" s="6" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="AM88" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AN88" s="6" t="s">
         <v>197</v>
@@ -10690,13 +10684,129 @@
         <v>2</v>
       </c>
       <c r="AR88" s="6" t="s">
-        <v>421</v>
+        <v>458</v>
       </c>
       <c r="AS88" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="AT88" s="6" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="89" spans="1:46">
+      <c r="A89" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="B89" s="7">
+        <v>42534</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="I89" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="J89" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="K89" s="8">
+        <v>26200000000</v>
+      </c>
+      <c r="L89" s="8">
+        <v>26200000000</v>
+      </c>
+      <c r="M89" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="N89" s="9">
+        <v>1</v>
+      </c>
+      <c r="O89" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="P89" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="R89" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="S89" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="U89" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="X89" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB89" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AD89" s="6" t="s">
         <v>463</v>
       </c>
-      <c r="AT88" s="6" t="s">
+      <c r="AE89" s="8">
+        <v>2990911000</v>
+      </c>
+      <c r="AF89" s="8">
+        <v>254472000</v>
+      </c>
+      <c r="AG89" s="7">
+        <v>42369</v>
+      </c>
+      <c r="AH89" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="AI89" s="5">
+        <v>8.759872828044699</v>
+      </c>
+      <c r="AJ89" s="5">
+        <v>102.9582822471628</v>
+      </c>
+      <c r="AK89" s="6" t="s">
         <v>464</v>
+      </c>
+      <c r="AL89" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="AM89" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="AN89" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="AO89" s="6">
+        <v>100</v>
+      </c>
+      <c r="AP89" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="AQ89" s="6">
+        <v>2</v>
+      </c>
+      <c r="AR89" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="AS89" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="AT89" s="6" t="s">
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -10789,10 +10899,11 @@
     <hyperlink ref="AS86" r:id="rId82"/>
     <hyperlink ref="AS87" r:id="rId83"/>
     <hyperlink ref="AS88" r:id="rId84"/>
+    <hyperlink ref="AS89" r:id="rId85"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId85"/>
+    <tablePart r:id="rId86"/>
   </tableParts>
 </worksheet>
 </file>
@@ -10808,7 +10919,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -10826,7 +10937,7 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -10847,16 +10958,16 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C6" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D6" t="s">
         <v>53</v>
       </c>
       <c r="E6" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="F6" t="s">
         <v>33</v>
@@ -10865,13 +10976,13 @@
         <v>51</v>
       </c>
       <c r="H6" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="I6" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="J6" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="K6" t="s">
         <v>52</v>
@@ -10880,18 +10991,18 @@
         <v>58</v>
       </c>
       <c r="M6" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="N6" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C7" s="7">
         <v>45190</v>
@@ -10909,21 +11020,21 @@
         <v>3653708000</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="6" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C8" s="7">
         <v>44707</v>
@@ -10953,21 +11064,21 @@
         <v>2966000000</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C9" s="7">
         <v>44640</v>
@@ -10985,21 +11096,21 @@
         <v>592200000</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="C10" s="7">
         <v>44592</v>
@@ -11017,21 +11128,21 @@
         <v>3217170000</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="6" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C11" s="7">
         <v>44579</v>
@@ -11052,21 +11163,21 @@
         <v>2734000000</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" spans="1:14">
       <c r="A12" s="6" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C12" s="7">
         <v>44166</v>
@@ -11084,21 +11195,21 @@
         <v>630422000</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C13" s="7">
         <v>44131</v>
@@ -11116,21 +11227,21 @@
         <v>3162666000</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="6" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C14" s="7">
         <v>43626</v>
@@ -11148,21 +11259,21 @@
         <v>1159000000</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="6" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C15" s="7">
         <v>43401</v>
@@ -11183,21 +11294,21 @@
         <v>472442000</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="6" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C16" s="7">
         <v>42534</v>
@@ -11221,13 +11332,13 @@
         <v>254472000</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -11265,7 +11376,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11284,7 +11395,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11306,16 +11417,16 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C6" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="F6" t="s">
         <v>51</v>
@@ -11330,7 +11441,7 @@
         <v>60</v>
       </c>
       <c r="J6" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="K6" t="s">
         <v>55</v>
@@ -11339,13 +11450,13 @@
         <v>56</v>
       </c>
       <c r="M6" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="N6" t="s">
         <v>57</v>
       </c>
       <c r="O6" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -11368,7 +11479,7 @@
         <v>125</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K7" s="5">
         <f>IFERROR(IF(AND(D7&gt;0,F7&gt;0,E7=H7),D7/F7,""),"")</f>
@@ -11409,7 +11520,7 @@
         <v>125</v>
       </c>
       <c r="J8" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K8" s="5">
         <f>IFERROR(IF(AND(D8&gt;0,F8&gt;0,E8=H8),D8/F8,""),"")</f>
@@ -11450,7 +11561,7 @@
         <v>125</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K9" s="5">
         <f>IFERROR(IF(AND(D9&gt;0,F9&gt;0,E9=H9),D9/F9,""),"")</f>
@@ -11491,7 +11602,7 @@
         <v>125</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K10" s="5">
         <f>IFERROR(IF(AND(D10&gt;0,F10&gt;0,E10=H10),D10/F10,""),"")</f>
@@ -11532,7 +11643,7 @@
         <v>76</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K11" s="5">
         <f>IFERROR(IF(AND(D11&gt;0,F11&gt;0,E11=H11),D11/F11,""),"")</f>
@@ -11564,7 +11675,7 @@
         <v>258</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>70</v>
@@ -11573,7 +11684,7 @@
         <v>76</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K12" s="5">
         <f>IFERROR(IF(AND(D12&gt;0,F12&gt;0,E12=H12),D12/F12,""),"")</f>
@@ -11614,7 +11725,7 @@
         <v>76</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K13" s="5">
         <f>IFERROR(IF(AND(D13&gt;0,F13&gt;0,E13=H13),D13/F13,""),"")</f>
@@ -11655,7 +11766,7 @@
         <v>125</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K14" s="5">
         <f>IFERROR(IF(AND(D14&gt;0,F14&gt;0,E14=H14),D14/F14,""),"")</f>
@@ -11696,7 +11807,7 @@
         <v>125</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K15" s="5">
         <f>IFERROR(IF(AND(D15&gt;0,F15&gt;0,E15=H15),D15/F15,""),"")</f>
@@ -11737,7 +11848,7 @@
         <v>125</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K16" s="5">
         <f>IFERROR(IF(AND(D16&gt;0,F16&gt;0,E16=H16),D16/F16,""),"")</f>
@@ -11778,7 +11889,7 @@
         <v>125</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K17" s="5">
         <f>IFERROR(IF(AND(D17&gt;0,F17&gt;0,E17=H17),D17/F17,""),"")</f>
@@ -11819,7 +11930,7 @@
         <v>125</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K18" s="5">
         <f>IFERROR(IF(AND(D18&gt;0,F18&gt;0,E18=H18),D18/F18,""),"")</f>
@@ -11860,7 +11971,7 @@
         <v>125</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K19" s="5">
         <f>IFERROR(IF(AND(D19&gt;0,F19&gt;0,E19=H19),D19/F19,""),"")</f>
@@ -11901,7 +12012,7 @@
         <v>125</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K20" s="5">
         <f>IFERROR(IF(AND(D20&gt;0,F20&gt;0,E20=H20),D20/F20,""),"")</f>
@@ -11942,7 +12053,7 @@
         <v>76</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K21" s="5">
         <f>IFERROR(IF(AND(D21&gt;0,F21&gt;0,E21=H21),D21/F21,""),"")</f>
@@ -11965,7 +12076,7 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="6" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B22" s="7">
         <v>45642</v>
@@ -11983,7 +12094,7 @@
         <v>76</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K22" s="5">
         <f>IFERROR(IF(AND(D22&gt;0,F22&gt;0,E22=H22),D22/F22,""),"")</f>
@@ -12006,13 +12117,13 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="6" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B23" s="7">
         <v>45288</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>70</v>
@@ -12024,7 +12135,7 @@
         <v>76</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K23" s="5">
         <f>IFERROR(IF(AND(D23&gt;0,F23&gt;0,E23=H23),D23/F23,""),"")</f>
@@ -12047,13 +12158,13 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B24" s="7">
         <v>45190</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>185</v>
@@ -12068,7 +12179,7 @@
         <v>197</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K24" s="5">
         <f>IFERROR(IF(AND(D24&gt;0,F24&gt;0,E24=H24),D24/F24,""),"")</f>
@@ -12083,21 +12194,21 @@
         <v>NO</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="6" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B25" s="7">
         <v>44707</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D25" s="8">
         <v>69000000000</v>
@@ -12118,7 +12229,7 @@
         <v>197</v>
       </c>
       <c r="J25" s="6" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K25" s="5">
         <f>IFERROR(IF(AND(D25&gt;0,F25&gt;0,E25=H25),D25/F25,""),"")</f>
@@ -12133,21 +12244,21 @@
         <v>YES</v>
       </c>
       <c r="N25" s="6" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B26" s="7">
         <v>44640</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>185</v>
@@ -12162,7 +12273,7 @@
         <v>197</v>
       </c>
       <c r="J26" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K26" s="5">
         <f>IFERROR(IF(AND(D26&gt;0,F26&gt;0,E26=H26),D26/F26,""),"")</f>
@@ -12177,21 +12288,21 @@
         <v>NO</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B27" s="7">
         <v>44592</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D27" s="8">
         <v>16500000000</v>
@@ -12209,7 +12320,7 @@
         <v>197</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="K27" s="5">
         <f>IFERROR(IF(AND(D27&gt;0,F27&gt;0,E27=H27),D27/F27,""),"")</f>
@@ -12224,21 +12335,21 @@
         <v>NO</v>
       </c>
       <c r="N27" s="6" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="6" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B28" s="7">
         <v>44579</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D28" s="8">
         <v>68700000000</v>
@@ -12256,7 +12367,7 @@
         <v>197</v>
       </c>
       <c r="J28" s="6" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K28" s="5">
         <f>IFERROR(IF(AND(D28&gt;0,F28&gt;0,E28=H28),D28/F28,""),"")</f>
@@ -12271,21 +12382,21 @@
         <v>YES</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="6" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B29" s="7">
         <v>44166</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D29" s="8">
         <v>27700000000</v>
@@ -12303,7 +12414,7 @@
         <v>197</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K29" s="5">
         <f>IFERROR(IF(AND(D29&gt;0,F29&gt;0,E29=H29),D29/F29,""),"")</f>
@@ -12318,21 +12429,21 @@
         <v>YES</v>
       </c>
       <c r="N29" s="6" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B30" s="7">
         <v>44131</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>185</v>
@@ -12347,7 +12458,7 @@
         <v>197</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K30" s="5">
         <f>IFERROR(IF(AND(D30&gt;0,F30&gt;0,E30=H30),D30/F30,""),"")</f>
@@ -12362,21 +12473,21 @@
         <v>NO</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="6" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B31" s="7">
         <v>43626</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D31" s="8">
         <v>15700000000</v>
@@ -12394,7 +12505,7 @@
         <v>197</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K31" s="5">
         <f>IFERROR(IF(AND(D31&gt;0,F31&gt;0,E31=H31),D31/F31,""),"")</f>
@@ -12409,21 +12520,21 @@
         <v>YES</v>
       </c>
       <c r="N31" s="6" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="6" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B32" s="7">
         <v>43401</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D32" s="8">
         <v>34000000000</v>
@@ -12441,7 +12552,7 @@
         <v>197</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K32" s="5">
         <f>IFERROR(IF(AND(D32&gt;0,F32&gt;0,E32=H32),D32/F32,""),"")</f>
@@ -12456,21 +12567,21 @@
         <v>YES</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="6" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B33" s="7">
         <v>42534</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D33" s="8">
         <v>26200000000</v>
@@ -12491,7 +12602,7 @@
         <v>197</v>
       </c>
       <c r="J33" s="6" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K33" s="5">
         <f>IFERROR(IF(AND(D33&gt;0,F33&gt;0,E33=H33),D33/F33,""),"")</f>
@@ -12506,10 +12617,10 @@
         <v>YES</v>
       </c>
       <c r="N33" s="6" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>
@@ -12526,7 +12637,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P150"/>
+  <dimension ref="A1:P151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="20.7109375" customWidth="1"/>
@@ -12537,7 +12648,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -12557,7 +12668,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -12577,7 +12688,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="K4" s="3" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -12590,13 +12701,13 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C6" t="s">
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E6" t="s">
         <v>23</v>
@@ -12605,28 +12716,28 @@
         <v>62</v>
       </c>
       <c r="G6" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="H6" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="I6" t="s">
         <v>66</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="P6" s="4" t="s">
         <v>25</v>
@@ -12646,7 +12757,7 @@
         <v>78</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>77</v>
@@ -12661,7 +12772,7 @@
         <v>80</v>
       </c>
       <c r="K7" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -12693,7 +12804,7 @@
         <v>78</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>77</v>
@@ -12708,7 +12819,7 @@
         <v>86</v>
       </c>
       <c r="K8" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -12740,7 +12851,7 @@
         <v>78</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>77</v>
@@ -12755,7 +12866,7 @@
         <v>90</v>
       </c>
       <c r="K9" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -12787,7 +12898,7 @@
         <v>78</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>77</v>
@@ -12802,7 +12913,7 @@
         <v>93</v>
       </c>
       <c r="K10" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -12834,7 +12945,7 @@
         <v>78</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>77</v>
@@ -12849,7 +12960,7 @@
         <v>96</v>
       </c>
       <c r="K11" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -12881,7 +12992,7 @@
         <v>78</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>77</v>
@@ -12896,7 +13007,7 @@
         <v>101</v>
       </c>
       <c r="K12" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -12928,7 +13039,7 @@
         <v>78</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>77</v>
@@ -12943,7 +13054,7 @@
         <v>86</v>
       </c>
       <c r="K13" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -12975,7 +13086,7 @@
         <v>78</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>77</v>
@@ -12990,7 +13101,7 @@
         <v>108</v>
       </c>
       <c r="K14" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="L14">
         <v>6</v>
@@ -13022,7 +13133,7 @@
         <v>78</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>77</v>
@@ -13051,7 +13162,7 @@
         <v>78</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>77</v>
@@ -13066,7 +13177,7 @@
         <v>115</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -13090,7 +13201,7 @@
         <v>78</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>77</v>
@@ -13119,7 +13230,7 @@
         <v>127</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>126</v>
@@ -13143,16 +13254,16 @@
         <v>70</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="6" t="s">
@@ -13170,16 +13281,16 @@
         <v>70</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="6" t="s">
@@ -13197,16 +13308,16 @@
         <v>70</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6" t="s">
@@ -13227,7 +13338,7 @@
         <v>131</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>126</v>
@@ -13256,13 +13367,13 @@
         <v>131</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="6" t="s">
@@ -13283,7 +13394,7 @@
         <v>78</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>77</v>
@@ -13312,7 +13423,7 @@
         <v>78</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>77</v>
@@ -13341,7 +13452,7 @@
         <v>78</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>77</v>
@@ -13370,7 +13481,7 @@
         <v>78</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>77</v>
@@ -13399,7 +13510,7 @@
         <v>151</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>126</v>
@@ -13426,13 +13537,13 @@
         <v>151</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="6" t="s">
@@ -13453,7 +13564,7 @@
         <v>156</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>126</v>
@@ -13480,7 +13591,7 @@
         <v>151</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>126</v>
@@ -13509,13 +13620,13 @@
         <v>151</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="6" t="s">
@@ -13536,7 +13647,7 @@
         <v>78</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>77</v>
@@ -13565,7 +13676,7 @@
         <v>78</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>77</v>
@@ -13594,7 +13705,7 @@
         <v>78</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F35" s="6" t="s">
         <v>77</v>
@@ -13623,7 +13734,7 @@
         <v>78</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>77</v>
@@ -13652,7 +13763,7 @@
         <v>78</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F37" s="6" t="s">
         <v>77</v>
@@ -13681,7 +13792,7 @@
         <v>186</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>126</v>
@@ -13710,13 +13821,13 @@
         <v>186</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="6" t="s">
@@ -13737,7 +13848,7 @@
         <v>131</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>126</v>
@@ -13766,13 +13877,13 @@
         <v>131</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="6" t="s">
@@ -13793,7 +13904,7 @@
         <v>198</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>77</v>
@@ -13822,7 +13933,7 @@
         <v>186</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>126</v>
@@ -13851,13 +13962,13 @@
         <v>186</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="6" t="s">
@@ -13878,7 +13989,7 @@
         <v>207</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>126</v>
@@ -13907,7 +14018,7 @@
         <v>78</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>77</v>
@@ -13936,7 +14047,7 @@
         <v>78</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="F47" s="6" t="s">
         <v>77</v>
@@ -13965,7 +14076,7 @@
         <v>78</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>77</v>
@@ -13994,7 +14105,7 @@
         <v>78</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F49" s="6" t="s">
         <v>77</v>
@@ -14023,7 +14134,7 @@
         <v>78</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>77</v>
@@ -14052,7 +14163,7 @@
         <v>78</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F51" s="6" t="s">
         <v>77</v>
@@ -14081,7 +14192,7 @@
         <v>78</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>77</v>
@@ -14110,7 +14221,7 @@
         <v>232</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>126</v>
@@ -14139,7 +14250,7 @@
         <v>238</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>77</v>
@@ -14168,7 +14279,7 @@
         <v>244</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>126</v>
@@ -14197,7 +14308,7 @@
         <v>131</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>126</v>
@@ -14226,13 +14337,13 @@
         <v>131</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G57" s="6" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="H57" s="6"/>
       <c r="I57" s="6" t="s">
@@ -14253,7 +14364,7 @@
         <v>151</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>126</v>
@@ -14279,16 +14390,16 @@
         <v>253</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F59" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="H59" s="6">
         <v>46171</v>
@@ -14308,16 +14419,16 @@
         <v>253</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H60" s="6">
         <v>46170</v>
@@ -14340,13 +14451,13 @@
         <v>311</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G61" s="6" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="H61" s="6">
         <v>46170</v>
@@ -14369,13 +14480,13 @@
         <v>311</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="H62" s="6">
         <v>46170</v>
@@ -14398,13 +14509,13 @@
         <v>131</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F63" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G63" s="6" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="H63" s="6">
         <v>46170</v>
@@ -14427,13 +14538,13 @@
         <v>244</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="H64" s="6">
         <v>46170</v>
@@ -14453,16 +14564,16 @@
         <v>253</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G65" s="6" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="H65" s="6"/>
       <c r="I65" s="6" t="s">
@@ -14483,13 +14594,13 @@
         <v>311</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="H66" s="6"/>
       <c r="I66" s="6" t="s">
@@ -14510,13 +14621,13 @@
         <v>131</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G67" s="6" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="H67" s="6"/>
       <c r="I67" s="6" t="s">
@@ -14537,13 +14648,13 @@
         <v>151</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="H68" s="6"/>
       <c r="I68" s="6" t="s">
@@ -14564,13 +14675,13 @@
         <v>319</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F69" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G69" s="6" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="H69" s="6"/>
       <c r="I69" s="6" t="s">
@@ -14591,7 +14702,7 @@
         <v>238</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>77</v>
@@ -14620,13 +14731,13 @@
         <v>151</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F71" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G71" s="6" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="H71" s="6">
         <v>46176</v>
@@ -14649,13 +14760,13 @@
         <v>131</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="H72" s="6">
         <v>46175</v>
@@ -14678,13 +14789,13 @@
         <v>151</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F73" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G73" s="6" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="H73" s="6"/>
       <c r="I73" s="6" t="s">
@@ -14705,13 +14816,13 @@
         <v>131</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H74" s="6"/>
       <c r="I74" s="6" t="s">
@@ -14732,7 +14843,7 @@
         <v>131</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>126</v>
@@ -14761,13 +14872,13 @@
         <v>131</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="H76" s="6"/>
       <c r="I76" s="6" t="s">
@@ -14788,7 +14899,7 @@
         <v>131</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F77" s="6" t="s">
         <v>126</v>
@@ -14817,13 +14928,13 @@
         <v>131</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="H78" s="6"/>
       <c r="I78" s="6" t="s">
@@ -14844,7 +14955,7 @@
         <v>151</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F79" s="6" t="s">
         <v>126</v>
@@ -14873,13 +14984,13 @@
         <v>151</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="H80" s="6"/>
       <c r="I80" s="6" t="s">
@@ -14900,7 +15011,7 @@
         <v>131</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F81" s="6" t="s">
         <v>126</v>
@@ -14929,13 +15040,13 @@
         <v>131</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="H82" s="6"/>
       <c r="I82" s="6" t="s">
@@ -14956,7 +15067,7 @@
         <v>244</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F83" s="6" t="s">
         <v>126</v>
@@ -14985,7 +15096,7 @@
         <v>244</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>126</v>
@@ -15014,7 +15125,7 @@
         <v>151</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F85" s="6" t="s">
         <v>126</v>
@@ -15043,13 +15154,13 @@
         <v>151</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="H86" s="6"/>
       <c r="I86" s="6" t="s">
@@ -15070,7 +15181,7 @@
         <v>288</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F87" s="6" t="s">
         <v>126</v>
@@ -15099,13 +15210,13 @@
         <v>288</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="H88" s="6"/>
       <c r="I88" s="6" t="s">
@@ -15126,7 +15237,7 @@
         <v>292</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F89" s="6" t="s">
         <v>126</v>
@@ -15155,13 +15266,13 @@
         <v>292</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="H90" s="6"/>
       <c r="I90" s="6" t="s">
@@ -15182,7 +15293,7 @@
         <v>151</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>126</v>
@@ -15211,13 +15322,13 @@
         <v>151</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="H92" s="6"/>
       <c r="I92" s="6" t="s">
@@ -15238,7 +15349,7 @@
         <v>299</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F93" s="6" t="s">
         <v>126</v>
@@ -15264,16 +15375,16 @@
         <v>70</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="H94" s="6">
         <v>46139</v>
@@ -15293,16 +15404,16 @@
         <v>70</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F95" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G95" s="6" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="H95" s="6"/>
       <c r="I95" s="6" t="s">
@@ -15323,13 +15434,13 @@
         <v>299</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="H96" s="6"/>
       <c r="I96" s="6" t="s">
@@ -15350,7 +15461,7 @@
         <v>303</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>126</v>
@@ -15379,13 +15490,13 @@
         <v>303</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="H98" s="6"/>
       <c r="I98" s="6" t="s">
@@ -15406,7 +15517,7 @@
         <v>307</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>126</v>
@@ -15435,13 +15546,13 @@
         <v>307</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="H100" s="6"/>
       <c r="I100" s="6" t="s">
@@ -15462,7 +15573,7 @@
         <v>311</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F101" s="6" t="s">
         <v>126</v>
@@ -15491,13 +15602,13 @@
         <v>311</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="H102" s="6"/>
       <c r="I102" s="6" t="s">
@@ -15518,7 +15629,7 @@
         <v>315</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F103" s="6" t="s">
         <v>126</v>
@@ -15547,13 +15658,13 @@
         <v>315</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H104" s="6"/>
       <c r="I104" s="6" t="s">
@@ -15571,16 +15682,16 @@
         <v>155</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F105" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G105" s="6" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H105" s="6"/>
       <c r="I105" s="6" t="s">
@@ -15601,7 +15712,7 @@
         <v>319</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>126</v>
@@ -15630,13 +15741,13 @@
         <v>319</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G107" s="6" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="H107" s="6"/>
       <c r="I107" s="6" t="s">
@@ -15657,7 +15768,7 @@
         <v>319</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>126</v>
@@ -15686,13 +15797,13 @@
         <v>292</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F109" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G109" s="6" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="H109" s="6">
         <v>46128</v>
@@ -15712,16 +15823,16 @@
         <v>323</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="H110" s="6">
         <v>46128</v>
@@ -15744,13 +15855,13 @@
         <v>319</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F111" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="H111" s="6"/>
       <c r="I111" s="6" t="s">
@@ -15771,13 +15882,13 @@
         <v>292</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H112" s="6"/>
       <c r="I112" s="6" t="s">
@@ -15795,16 +15906,16 @@
         <v>323</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F113" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G113" s="6" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="H113" s="6"/>
       <c r="I113" s="6" t="s">
@@ -15825,7 +15936,7 @@
         <v>131</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>126</v>
@@ -15854,13 +15965,13 @@
         <v>131</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F115" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G115" s="6" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="H115" s="6"/>
       <c r="I115" s="6" t="s">
@@ -15881,7 +15992,7 @@
         <v>311</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>126</v>
@@ -15910,13 +16021,13 @@
         <v>311</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F117" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G117" s="6" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="H117" s="6"/>
       <c r="I117" s="6" t="s">
@@ -15937,7 +16048,7 @@
         <v>315</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>126</v>
@@ -15966,13 +16077,13 @@
         <v>315</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G119" s="6" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H119" s="6"/>
       <c r="I119" s="6" t="s">
@@ -15990,16 +16101,16 @@
         <v>253</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="H120" s="6"/>
       <c r="I120" s="6" t="s">
@@ -16020,7 +16131,7 @@
         <v>151</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F121" s="6" t="s">
         <v>126</v>
@@ -16049,13 +16160,13 @@
         <v>151</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>126</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="H122" s="6"/>
       <c r="I122" s="6" t="s">
@@ -16076,7 +16187,7 @@
         <v>340</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>126</v>
@@ -16105,7 +16216,7 @@
         <v>131</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>126</v>
@@ -16134,7 +16245,7 @@
         <v>348</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F125" s="6" t="s">
         <v>77</v>
@@ -16154,16 +16265,16 @@
         <v>351</v>
       </c>
       <c r="B126" s="7">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>70</v>
+        <v>155</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>348</v>
+        <v>238</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>504</v>
+        <v>560</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>77</v>
@@ -16172,7 +16283,7 @@
         <v>352</v>
       </c>
       <c r="H126" s="6">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="I126" s="6" t="s">
         <v>353</v>
@@ -16183,36 +16294,36 @@
         <v>354</v>
       </c>
       <c r="B127" s="7">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>347</v>
+        <v>70</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>348</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F127" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G127" s="6" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="H127" s="6">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="I127" s="6" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B128" s="7">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>347</v>
@@ -16221,27 +16332,27 @@
         <v>348</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="H128" s="6">
+        <v>45611</v>
+      </c>
+      <c r="I128" s="6" t="s">
         <v>362</v>
-      </c>
-      <c r="H128" s="6">
-        <v>45391</v>
-      </c>
-      <c r="I128" s="6" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B129" s="7">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>347</v>
@@ -16250,7 +16361,7 @@
         <v>348</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>77</v>
@@ -16259,619 +16370,648 @@
         <v>365</v>
       </c>
       <c r="H129" s="6">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="I129" s="6" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B130" s="7">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>348</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H130" s="6">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
     </row>
     <row r="131" spans="1:9">
       <c r="A131" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B131" s="7">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>381</v>
+        <v>348</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>557</v>
+        <v>507</v>
       </c>
       <c r="F131" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G131" s="6" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="H131" s="6">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="I131" s="6" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
     </row>
     <row r="132" spans="1:9">
       <c r="A132" s="6" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B132" s="7">
         <v>45190</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>475</v>
+        <v>385</v>
       </c>
       <c r="H132" s="6">
-        <v>45008</v>
+        <v>45190</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="133" spans="1:9">
       <c r="A133" s="6" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B133" s="7">
-        <v>44707</v>
+        <v>45190</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F133" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G133" s="6" t="s">
-        <v>393</v>
+        <v>478</v>
       </c>
       <c r="H133" s="6">
-        <v>44707</v>
+        <v>45008</v>
       </c>
       <c r="I133" s="6" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" s="6" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B134" s="7">
         <v>44707</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>476</v>
+        <v>396</v>
       </c>
       <c r="H134" s="6">
-        <v>44644</v>
+        <v>44707</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:9">
       <c r="A135" s="6" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="B135" s="7">
-        <v>44640</v>
+        <v>44707</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F135" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G135" s="6" t="s">
-        <v>403</v>
+        <v>479</v>
       </c>
       <c r="H135" s="6">
-        <v>44734</v>
+        <v>44644</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="136" spans="1:9">
       <c r="A136" s="6" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B136" s="7">
         <v>44640</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>477</v>
+        <v>406</v>
       </c>
       <c r="H136" s="6">
-        <v>44643</v>
+        <v>44734</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="6" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B137" s="7">
-        <v>44592</v>
+        <v>44640</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="F137" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G137" s="6" t="s">
-        <v>412</v>
+        <v>480</v>
       </c>
       <c r="H137" s="6">
-        <v>44608</v>
+        <v>44643</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="138" spans="1:9">
       <c r="A138" s="6" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B138" s="7">
         <v>44592</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="H138" s="6">
         <v>44608</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="6" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B139" s="7">
-        <v>44579</v>
+        <v>44592</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F139" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G139" s="6" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="H139" s="6">
-        <v>44579</v>
+        <v>44608</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
     </row>
     <row r="140" spans="1:9">
       <c r="A140" s="6" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="B140" s="7">
         <v>44579</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>478</v>
+        <v>425</v>
       </c>
       <c r="H140" s="6">
-        <v>44250</v>
+        <v>44579</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="6" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="B141" s="7">
-        <v>44166</v>
+        <v>44579</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F141" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>431</v>
+        <v>481</v>
       </c>
       <c r="H141" s="6">
-        <v>44166</v>
+        <v>44250</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="142" spans="1:9">
       <c r="A142" s="6" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B142" s="7">
         <v>44166</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>479</v>
+        <v>434</v>
       </c>
       <c r="H142" s="6">
-        <v>43902</v>
+        <v>44166</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="143" spans="1:9">
       <c r="A143" s="6" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B143" s="7">
-        <v>44131</v>
+        <v>44166</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F143" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G143" s="6" t="s">
-        <v>440</v>
+        <v>482</v>
       </c>
       <c r="H143" s="6">
-        <v>44131</v>
+        <v>43902</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="6" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B144" s="7">
         <v>44131</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>480</v>
+        <v>443</v>
       </c>
       <c r="H144" s="6">
-        <v>43966</v>
+        <v>44131</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="145" spans="1:9">
       <c r="A145" s="6" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="B145" s="7">
-        <v>43626</v>
+        <v>44131</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F145" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G145" s="6" t="s">
-        <v>447</v>
+        <v>483</v>
       </c>
       <c r="H145" s="6">
-        <v>43626</v>
+        <v>43966</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="146" spans="1:9">
       <c r="A146" s="6" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B146" s="7">
         <v>43626</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
       <c r="H146" s="6">
-        <v>43518</v>
+        <v>43626</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="6" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B147" s="7">
-        <v>43401</v>
+        <v>43626</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F147" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G147" s="6" t="s">
-        <v>456</v>
+        <v>484</v>
       </c>
       <c r="H147" s="6">
-        <v>43401</v>
+        <v>43518</v>
       </c>
       <c r="I147" s="6" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="6" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B148" s="7">
         <v>43401</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>482</v>
+        <v>459</v>
       </c>
       <c r="H148" s="6">
-        <v>43215</v>
+        <v>43401</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="6" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="B149" s="7">
-        <v>42534</v>
+        <v>43401</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>421</v>
+        <v>456</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>557</v>
+        <v>562</v>
       </c>
       <c r="F149" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G149" s="6" t="s">
-        <v>463</v>
+        <v>485</v>
       </c>
       <c r="H149" s="6">
-        <v>42534</v>
+        <v>43215</v>
       </c>
       <c r="I149" s="6" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="150" spans="1:9">
       <c r="A150" s="6" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B150" s="7">
         <v>42534</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>461</v>
+        <v>424</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>77</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="H150" s="6">
+        <v>42534</v>
+      </c>
+      <c r="I150" s="6" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="B151" s="7">
+        <v>42534</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G151" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="H151" s="6">
         <v>42412</v>
       </c>
-      <c r="I150" s="6" t="s">
-        <v>464</v>
+      <c r="I151" s="6" t="s">
+        <v>467</v>
       </c>
     </row>
   </sheetData>
@@ -17030,10 +17170,11 @@
     <hyperlink ref="G148" r:id="rId146"/>
     <hyperlink ref="G149" r:id="rId147"/>
     <hyperlink ref="G150" r:id="rId148"/>
+    <hyperlink ref="G151" r:id="rId149"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId149"/>
+    <tablePart r:id="rId150"/>
   </tableParts>
 </worksheet>
 </file>
--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-03 | Build e0b866314927 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-03 | Build 909cb1260792 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-03 | Build 909cb1260792 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-03 | Build 33cbf20bd083 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-04 | Build 80155b04ce0d | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-04 | Build 94a6f42ca0da | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-04 | Build 94a6f42ca0da | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-04 | Build 0941b8f1ae01 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-04 | Build f4a2f07f2871 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-05 | Build ffd22f0532cb | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -1064,7 +1064,7 @@
     <t>https://rb.ru/news/vk-prodal-25-akcij-tochka-banka-sdelku-ocenili-v-212-mlrd-vdvoe-vyshe-iznachalnoj-stoimosti-bumag/</t>
   </si>
   <si>
-    <t>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.RU</t>
+    <t>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.ru</t>
   </si>
   <si>
     <t>DL-4774de17c61c14e4</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-05 | Build ffd22f0532cb | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-05 | Build f92e83d7a516 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4106" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4106" uniqueCount="597">
   <si>
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-05 | Build e9e6aa8bf405 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-05 | Build 0e778eea6737 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -798,9 +798,6 @@
   </si>
   <si>
     <t>Technology</t>
-  </si>
-  <si>
-    <t>001Р-04; 001Р-05</t>
   </si>
   <si>
     <t>Yandex Investor Relations</t>
@@ -6961,7 +6958,7 @@
         <v>92</v>
       </c>
       <c r="R48" s="9" t="s">
-        <v>260</v>
+        <v>90</v>
       </c>
       <c r="S48" s="9" t="s">
         <v>90</v>
@@ -7003,10 +7000,10 @@
         <v>5</v>
       </c>
       <c r="AR48" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="AS48" s="9" t="s">
         <v>261</v>
-      </c>
-      <c r="AS48" s="9" t="s">
-        <v>262</v>
       </c>
       <c r="AT48" s="9" t="s">
         <v>39</v>
@@ -7014,7 +7011,7 @@
     </row>
     <row r="49" spans="1:46">
       <c r="A49" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B49" s="8">
         <v>46183</v>
@@ -7029,7 +7026,7 @@
         <v>108</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G49" s="9" t="s">
         <v>33</v>
@@ -7047,7 +7044,7 @@
         <v>3000000000</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>33</v>
@@ -7101,18 +7098,18 @@
         <v>1</v>
       </c>
       <c r="AR49" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="AS49" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="AS49" s="9" t="s">
+      <c r="AT49" s="9" t="s">
         <v>267</v>
-      </c>
-      <c r="AT49" s="9" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="50" spans="1:46">
       <c r="A50" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B50" s="8">
         <v>46177</v>
@@ -7121,16 +7118,16 @@
         <v>4</v>
       </c>
       <c r="D50" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="E50" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="F50" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="F50" s="9" t="s">
+      <c r="G50" s="9" t="s">
         <v>272</v>
-      </c>
-      <c r="G50" s="9" t="s">
-        <v>273</v>
       </c>
       <c r="H50" s="9" t="s">
         <v>90</v>
@@ -7199,15 +7196,15 @@
         <v>187</v>
       </c>
       <c r="AS50" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="AT50" s="9" t="s">
         <v>274</v>
-      </c>
-      <c r="AT50" s="9" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:46">
       <c r="A51" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B51" s="8">
         <v>46175</v>
@@ -7294,10 +7291,10 @@
         <v>5</v>
       </c>
       <c r="AR51" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AS51" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AT51" s="9" t="s">
         <v>43</v>
@@ -7305,7 +7302,7 @@
     </row>
     <row r="52" spans="1:46">
       <c r="A52" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B52" s="8">
         <v>46170</v>
@@ -7317,10 +7314,10 @@
         <v>107</v>
       </c>
       <c r="E52" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="F52" s="9" t="s">
         <v>279</v>
-      </c>
-      <c r="F52" s="9" t="s">
-        <v>280</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>38</v>
@@ -7392,15 +7389,15 @@
         <v>162</v>
       </c>
       <c r="AS52" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="AT52" s="9" t="s">
         <v>281</v>
-      </c>
-      <c r="AT52" s="9" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="53" spans="1:46">
       <c r="A53" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B53" s="8">
         <v>46167</v>
@@ -7487,15 +7484,15 @@
         <v>162</v>
       </c>
       <c r="AS53" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="AT53" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="AT53" s="9" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="54" spans="1:46">
       <c r="A54" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B54" s="8">
         <v>46162</v>
@@ -7510,7 +7507,7 @@
         <v>108</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>33</v>
@@ -7534,7 +7531,7 @@
         <v>90</v>
       </c>
       <c r="Q54" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="R54" s="9" t="s">
         <v>33</v>
@@ -7582,15 +7579,15 @@
         <v>187</v>
       </c>
       <c r="AS54" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="AT54" s="9" t="s">
         <v>288</v>
-      </c>
-      <c r="AT54" s="9" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="55" spans="1:46">
       <c r="A55" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B55" s="8">
         <v>46157</v>
@@ -7605,7 +7602,7 @@
         <v>108</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>33</v>
@@ -7629,7 +7626,7 @@
         <v>90</v>
       </c>
       <c r="Q55" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="R55" s="9" t="s">
         <v>33</v>
@@ -7677,15 +7674,15 @@
         <v>162</v>
       </c>
       <c r="AS55" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="AT55" s="9" t="s">
         <v>291</v>
-      </c>
-      <c r="AT55" s="9" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="56" spans="1:46">
       <c r="A56" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B56" s="8">
         <v>46157</v>
@@ -7769,18 +7766,18 @@
         <v>1</v>
       </c>
       <c r="AR56" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AS56" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="AT56" s="9" t="s">
         <v>294</v>
-      </c>
-      <c r="AT56" s="9" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="57" spans="1:46">
       <c r="A57" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B57" s="8">
         <v>46150</v>
@@ -7795,7 +7792,7 @@
         <v>108</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>33</v>
@@ -7867,18 +7864,18 @@
         <v>1</v>
       </c>
       <c r="AR57" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AS57" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="AT57" s="9" t="s">
         <v>298</v>
-      </c>
-      <c r="AT57" s="9" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="58" spans="1:46">
       <c r="A58" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B58" s="8">
         <v>46147</v>
@@ -7920,7 +7917,7 @@
         <v>90</v>
       </c>
       <c r="Q58" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="R58" s="9" t="s">
         <v>33</v>
@@ -7968,15 +7965,15 @@
         <v>187</v>
       </c>
       <c r="AS58" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="AT58" s="9" t="s">
         <v>301</v>
-      </c>
-      <c r="AT58" s="9" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="59" spans="1:46">
       <c r="A59" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B59" s="8">
         <v>46146</v>
@@ -8000,7 +7997,7 @@
         <v>33</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J59" s="9" t="s">
         <v>90</v>
@@ -8015,7 +8012,7 @@
         <v>90</v>
       </c>
       <c r="Q59" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="R59" s="9" t="s">
         <v>33</v>
@@ -8060,18 +8057,18 @@
         <v>2</v>
       </c>
       <c r="AR59" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="AS59" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="AS59" s="9" t="s">
+      <c r="AT59" s="9" t="s">
         <v>306</v>
-      </c>
-      <c r="AT59" s="9" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="60" spans="1:46">
       <c r="A60" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B60" s="8">
         <v>46139</v>
@@ -8155,18 +8152,18 @@
         <v>2</v>
       </c>
       <c r="AR60" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="AS60" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="AS60" s="9" t="s">
+      <c r="AT60" s="9" t="s">
         <v>310</v>
-      </c>
-      <c r="AT60" s="9" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="61" spans="1:46">
       <c r="A61" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B61" s="8">
         <v>46139</v>
@@ -8253,15 +8250,15 @@
         <v>187</v>
       </c>
       <c r="AS61" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="AT61" s="9" t="s">
         <v>313</v>
-      </c>
-      <c r="AT61" s="9" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="62" spans="1:46">
       <c r="A62" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B62" s="8">
         <v>46139</v>
@@ -8345,18 +8342,18 @@
         <v>4</v>
       </c>
       <c r="AR62" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="AS62" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="AS62" s="9" t="s">
+      <c r="AT62" s="9" t="s">
         <v>317</v>
-      </c>
-      <c r="AT62" s="9" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="63" spans="1:46">
       <c r="A63" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B63" s="8">
         <v>46139</v>
@@ -8440,18 +8437,18 @@
         <v>2</v>
       </c>
       <c r="AR63" s="9" t="s">
+        <v>319</v>
+      </c>
+      <c r="AS63" s="9" t="s">
         <v>320</v>
       </c>
-      <c r="AS63" s="9" t="s">
+      <c r="AT63" s="9" t="s">
         <v>321</v>
-      </c>
-      <c r="AT63" s="9" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:46">
       <c r="A64" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B64" s="8">
         <v>46139</v>
@@ -8535,18 +8532,18 @@
         <v>2</v>
       </c>
       <c r="AR64" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="AS64" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="AS64" s="9" t="s">
+      <c r="AT64" s="9" t="s">
         <v>325</v>
-      </c>
-      <c r="AT64" s="9" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:46">
       <c r="A65" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B65" s="8">
         <v>46132</v>
@@ -8561,7 +8558,7 @@
         <v>108</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>33</v>
@@ -8633,15 +8630,15 @@
         <v>111</v>
       </c>
       <c r="AS65" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="AT65" s="9" t="s">
         <v>328</v>
-      </c>
-      <c r="AT65" s="9" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:46">
       <c r="A66" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B66" s="8">
         <v>46132</v>
@@ -8680,7 +8677,7 @@
         <v>90</v>
       </c>
       <c r="Q66" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="R66" s="9" t="s">
         <v>33</v>
@@ -8725,18 +8722,18 @@
         <v>2</v>
       </c>
       <c r="AR66" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="AS66" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="AS66" s="9" t="s">
+      <c r="AT66" s="9" t="s">
         <v>332</v>
-      </c>
-      <c r="AT66" s="9" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:46">
       <c r="A67" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B67" s="8">
         <v>46132</v>
@@ -8775,7 +8772,7 @@
         <v>90</v>
       </c>
       <c r="Q67" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="R67" s="9" t="s">
         <v>33</v>
@@ -8820,18 +8817,18 @@
         <v>2</v>
       </c>
       <c r="AR67" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="AS67" s="9" t="s">
         <v>335</v>
       </c>
-      <c r="AS67" s="9" t="s">
+      <c r="AT67" s="9" t="s">
         <v>336</v>
-      </c>
-      <c r="AT67" s="9" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:46">
       <c r="A68" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B68" s="8">
         <v>46128</v>
@@ -8846,13 +8843,13 @@
         <v>108</v>
       </c>
       <c r="F68" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="H68" s="9" t="s">
         <v>339</v>
-      </c>
-      <c r="G68" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>340</v>
       </c>
       <c r="I68" s="9" t="s">
         <v>9</v>
@@ -8921,18 +8918,18 @@
         <v>6</v>
       </c>
       <c r="AR68" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AS68" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="AT68" s="9" t="s">
         <v>341</v>
-      </c>
-      <c r="AT68" s="9" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="69" spans="1:46">
       <c r="A69" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B69" s="8">
         <v>46122</v>
@@ -8947,7 +8944,7 @@
         <v>108</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G69" s="9" t="s">
         <v>33</v>
@@ -9019,15 +9016,15 @@
         <v>162</v>
       </c>
       <c r="AS69" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="AT69" s="9" t="s">
         <v>344</v>
-      </c>
-      <c r="AT69" s="9" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="70" spans="1:46">
       <c r="A70" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B70" s="8">
         <v>46122</v>
@@ -9042,7 +9039,7 @@
         <v>108</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G70" s="9" t="s">
         <v>33</v>
@@ -9066,7 +9063,7 @@
         <v>90</v>
       </c>
       <c r="Q70" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="R70" s="9" t="s">
         <v>33</v>
@@ -9114,15 +9111,15 @@
         <v>111</v>
       </c>
       <c r="AS70" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="AT70" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="AT70" s="9" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="71" spans="1:46">
       <c r="A71" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B71" s="8">
         <v>46115</v>
@@ -9137,7 +9134,7 @@
         <v>115</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G71" s="9" t="s">
         <v>33</v>
@@ -9209,18 +9206,18 @@
         <v>2</v>
       </c>
       <c r="AR71" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AS71" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="AT71" s="9" t="s">
         <v>350</v>
-      </c>
-      <c r="AT71" s="9" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="72" spans="1:46">
       <c r="A72" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B72" s="8">
         <v>46115</v>
@@ -9235,7 +9232,7 @@
         <v>115</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G72" s="9" t="s">
         <v>33</v>
@@ -9307,15 +9304,15 @@
         <v>187</v>
       </c>
       <c r="AS72" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="AT72" s="9" t="s">
         <v>353</v>
-      </c>
-      <c r="AT72" s="9" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="73" spans="1:46">
       <c r="A73" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B73" s="8">
         <v>46111</v>
@@ -9330,7 +9327,7 @@
         <v>108</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G73" s="9" t="s">
         <v>33</v>
@@ -9402,18 +9399,18 @@
         <v>1</v>
       </c>
       <c r="AR73" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="AS73" s="9" t="s">
         <v>356</v>
       </c>
-      <c r="AS73" s="9" t="s">
+      <c r="AT73" s="9" t="s">
         <v>357</v>
-      </c>
-      <c r="AT73" s="9" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="74" spans="1:46">
       <c r="A74" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B74" s="8">
         <v>46111</v>
@@ -9428,7 +9425,7 @@
         <v>108</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G74" s="9" t="s">
         <v>33</v>
@@ -9500,15 +9497,15 @@
         <v>162</v>
       </c>
       <c r="AS74" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="AT74" s="9" t="s">
         <v>360</v>
-      </c>
-      <c r="AT74" s="9" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="75" spans="1:46">
       <c r="A75" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B75" s="8">
         <v>46080</v>
@@ -9598,10 +9595,10 @@
         <v>1</v>
       </c>
       <c r="AR75" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="AS75" s="9" t="s">
         <v>363</v>
-      </c>
-      <c r="AS75" s="9" t="s">
-        <v>364</v>
       </c>
       <c r="AT75" s="9" t="s">
         <v>45</v>
@@ -9609,7 +9606,7 @@
     </row>
     <row r="76" spans="1:46">
       <c r="A76" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B76" s="8">
         <v>45729</v>
@@ -9693,18 +9690,18 @@
         <v>1</v>
       </c>
       <c r="AR76" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AS76" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="AT76" s="9" t="s">
         <v>366</v>
-      </c>
-      <c r="AT76" s="9" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="77" spans="1:46">
       <c r="A77" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B77" s="8">
         <v>45642</v>
@@ -9788,18 +9785,18 @@
         <v>1</v>
       </c>
       <c r="AR77" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AS77" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="AT77" s="9" t="s">
         <v>369</v>
-      </c>
-      <c r="AT77" s="9" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="78" spans="1:46">
       <c r="A78" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B78" s="8">
         <v>45611</v>
@@ -9850,16 +9847,16 @@
         <v>90</v>
       </c>
       <c r="U78" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="X78" s="9" t="s">
         <v>372</v>
       </c>
-      <c r="X78" s="9" t="s">
+      <c r="AB78" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD78" s="9" t="s">
         <v>373</v>
-      </c>
-      <c r="AB78" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD78" s="9" t="s">
-        <v>374</v>
       </c>
       <c r="AH78" s="9" t="s">
         <v>90</v>
@@ -9886,18 +9883,18 @@
         <v>1</v>
       </c>
       <c r="AR78" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AS78" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="AT78" s="9" t="s">
         <v>375</v>
-      </c>
-      <c r="AT78" s="9" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="79" spans="1:46">
       <c r="A79" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B79" s="8">
         <v>45391</v>
@@ -9954,7 +9951,7 @@
         <v>90</v>
       </c>
       <c r="X79" s="9" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AB79" s="9" t="s">
         <v>33</v>
@@ -9987,18 +9984,18 @@
         <v>1</v>
       </c>
       <c r="AR79" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AS79" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="AT79" s="9" t="s">
         <v>379</v>
-      </c>
-      <c r="AT79" s="9" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="80" spans="1:46">
       <c r="A80" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B80" s="8">
         <v>45357</v>
@@ -10085,18 +10082,18 @@
         <v>1</v>
       </c>
       <c r="AR80" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AS80" s="9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AT80" s="9" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="81" spans="1:46">
       <c r="A81" s="9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B81" s="8">
         <v>45288</v>
@@ -10111,10 +10108,10 @@
         <v>89</v>
       </c>
       <c r="F81" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>384</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>385</v>
       </c>
       <c r="H81" s="9" t="s">
         <v>90</v>
@@ -10180,18 +10177,18 @@
         <v>1</v>
       </c>
       <c r="AR81" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AS81" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="AT81" s="9" t="s">
         <v>386</v>
-      </c>
-      <c r="AT81" s="9" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="82" spans="1:46">
       <c r="A82" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B82" s="8">
         <v>45190</v>
@@ -10206,19 +10203,19 @@
         <v>40</v>
       </c>
       <c r="F82" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="G82" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="G82" s="9" t="s">
+      <c r="H82" s="9" t="s">
         <v>390</v>
-      </c>
-      <c r="H82" s="9" t="s">
-        <v>391</v>
       </c>
       <c r="I82" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K82" s="10">
         <v>28000000000</v>
@@ -10230,28 +10227,28 @@
         <v>1</v>
       </c>
       <c r="O82" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="P82" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="R82" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="S82" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="U82" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="X82" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB82" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD82" s="9" t="s">
         <v>393</v>
-      </c>
-      <c r="P82" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="R82" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="S82" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="U82" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="X82" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB82" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD82" s="9" t="s">
-        <v>394</v>
       </c>
       <c r="AE82" s="10">
         <v>3653708000</v>
@@ -10263,13 +10260,13 @@
         <v>211</v>
       </c>
       <c r="AK82" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="AL82" s="9" t="s">
         <v>395</v>
       </c>
-      <c r="AL82" s="9" t="s">
+      <c r="AM82" s="9" t="s">
         <v>396</v>
-      </c>
-      <c r="AM82" s="9" t="s">
-        <v>397</v>
       </c>
       <c r="AN82" s="9" t="s">
         <v>35</v>
@@ -10284,18 +10281,18 @@
         <v>2</v>
       </c>
       <c r="AR82" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="AS82" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="AS82" s="9" t="s">
+      <c r="AT82" s="9" t="s">
         <v>399</v>
-      </c>
-      <c r="AT82" s="9" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="83" spans="1:46">
       <c r="A83" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B83" s="8">
         <v>44707</v>
@@ -10310,19 +10307,19 @@
         <v>40</v>
       </c>
       <c r="F83" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="G83" s="9" t="s">
         <v>402</v>
       </c>
-      <c r="G83" s="9" t="s">
-        <v>403</v>
-      </c>
       <c r="H83" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I83" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J83" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K83" s="10">
         <v>61000000000</v>
@@ -10337,10 +10334,10 @@
         <v>1</v>
       </c>
       <c r="O83" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>404</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>405</v>
       </c>
       <c r="Q83" s="9" t="s">
         <v>109</v>
@@ -10361,7 +10358,7 @@
         <v>33</v>
       </c>
       <c r="AD83" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AE83" s="10">
         <v>12851000000</v>
@@ -10382,13 +10379,13 @@
         <v>23.26365475387728</v>
       </c>
       <c r="AK83" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="AL83" s="9" t="s">
         <v>407</v>
       </c>
-      <c r="AL83" s="9" t="s">
-        <v>408</v>
-      </c>
       <c r="AM83" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN83" s="9" t="s">
         <v>35</v>
@@ -10403,18 +10400,18 @@
         <v>2</v>
       </c>
       <c r="AR83" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="AS83" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="AS83" s="9" t="s">
+      <c r="AT83" s="9" t="s">
         <v>410</v>
-      </c>
-      <c r="AT83" s="9" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="84" spans="1:46">
       <c r="A84" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B84" s="8">
         <v>44640</v>
@@ -10429,19 +10426,19 @@
         <v>40</v>
       </c>
       <c r="F84" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="G84" s="9" t="s">
         <v>413</v>
       </c>
-      <c r="G84" s="9" t="s">
-        <v>414</v>
-      </c>
       <c r="H84" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I84" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J84" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K84" s="10">
         <v>10400000000</v>
@@ -10453,7 +10450,7 @@
         <v>1</v>
       </c>
       <c r="O84" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P84" s="9" t="s">
         <v>90</v>
@@ -10474,7 +10471,7 @@
         <v>33</v>
       </c>
       <c r="AD84" s="9" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AE84" s="10">
         <v>592200000</v>
@@ -10486,13 +10483,13 @@
         <v>211</v>
       </c>
       <c r="AK84" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="AL84" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="AL84" s="9" t="s">
+      <c r="AM84" s="9" t="s">
         <v>417</v>
-      </c>
-      <c r="AM84" s="9" t="s">
-        <v>418</v>
       </c>
       <c r="AN84" s="9" t="s">
         <v>35</v>
@@ -10507,18 +10504,18 @@
         <v>2</v>
       </c>
       <c r="AR84" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="AS84" s="9" t="s">
         <v>419</v>
       </c>
-      <c r="AS84" s="9" t="s">
+      <c r="AT84" s="9" t="s">
         <v>420</v>
-      </c>
-      <c r="AT84" s="9" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="85" spans="1:46">
       <c r="A85" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B85" s="8">
         <v>44592</v>
@@ -10533,19 +10530,19 @@
         <v>40</v>
       </c>
       <c r="F85" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="G85" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="G85" s="9" t="s">
-        <v>424</v>
-      </c>
       <c r="H85" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I85" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J85" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K85" s="10">
         <v>16500000000</v>
@@ -10560,7 +10557,7 @@
         <v>1</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>90</v>
@@ -10581,7 +10578,7 @@
         <v>33</v>
       </c>
       <c r="AD85" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AE85" s="10">
         <v>3217170000</v>
@@ -10596,13 +10593,13 @@
         <v>5.128731151913017</v>
       </c>
       <c r="AK85" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="AL85" s="9" t="s">
         <v>426</v>
       </c>
-      <c r="AL85" s="9" t="s">
-        <v>427</v>
-      </c>
       <c r="AM85" s="9" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="AN85" s="9" t="s">
         <v>35</v>
@@ -10617,18 +10614,18 @@
         <v>1</v>
       </c>
       <c r="AR85" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="AS85" s="9" t="s">
         <v>428</v>
       </c>
-      <c r="AS85" s="9" t="s">
+      <c r="AT85" s="9" t="s">
         <v>429</v>
-      </c>
-      <c r="AT85" s="9" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="86" spans="1:46">
       <c r="A86" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B86" s="8">
         <v>44579</v>
@@ -10643,19 +10640,19 @@
         <v>40</v>
       </c>
       <c r="F86" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="G86" s="9" t="s">
         <v>432</v>
       </c>
-      <c r="G86" s="9" t="s">
-        <v>433</v>
-      </c>
       <c r="H86" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I86" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J86" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K86" s="10">
         <v>68700000000</v>
@@ -10670,10 +10667,10 @@
         <v>1</v>
       </c>
       <c r="O86" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P86" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q86" s="9" t="s">
         <v>109</v>
@@ -10694,7 +10691,7 @@
         <v>33</v>
       </c>
       <c r="AD86" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AE86" s="10">
         <v>8086000000</v>
@@ -10709,13 +10706,13 @@
         <v>8.496166213208014</v>
       </c>
       <c r="AK86" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="AL86" s="9" t="s">
         <v>436</v>
       </c>
-      <c r="AL86" s="9" t="s">
-        <v>437</v>
-      </c>
       <c r="AM86" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN86" s="9" t="s">
         <v>35</v>
@@ -10730,18 +10727,18 @@
         <v>2</v>
       </c>
       <c r="AR86" s="9" t="s">
+        <v>437</v>
+      </c>
+      <c r="AS86" s="9" t="s">
         <v>438</v>
       </c>
-      <c r="AS86" s="9" t="s">
+      <c r="AT86" s="9" t="s">
         <v>439</v>
-      </c>
-      <c r="AT86" s="9" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="87" spans="1:46">
       <c r="A87" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B87" s="8">
         <v>44166</v>
@@ -10756,19 +10753,19 @@
         <v>40</v>
       </c>
       <c r="F87" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="G87" s="9" t="s">
         <v>442</v>
       </c>
-      <c r="G87" s="9" t="s">
-        <v>443</v>
-      </c>
       <c r="H87" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I87" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J87" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K87" s="10">
         <v>27700000000</v>
@@ -10783,7 +10780,7 @@
         <v>1</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>90</v>
@@ -10804,7 +10801,7 @@
         <v>33</v>
       </c>
       <c r="AD87" s="9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AE87" s="10">
         <v>630422000</v>
@@ -10819,13 +10816,13 @@
         <v>43.93882193197572</v>
       </c>
       <c r="AK87" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="AL87" s="9" t="s">
         <v>445</v>
       </c>
-      <c r="AL87" s="9" t="s">
-        <v>446</v>
-      </c>
       <c r="AM87" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN87" s="9" t="s">
         <v>35</v>
@@ -10840,18 +10837,18 @@
         <v>2</v>
       </c>
       <c r="AR87" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="AS87" s="9" t="s">
         <v>447</v>
       </c>
-      <c r="AS87" s="9" t="s">
+      <c r="AT87" s="9" t="s">
         <v>448</v>
-      </c>
-      <c r="AT87" s="9" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="88" spans="1:46">
       <c r="A88" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B88" s="8">
         <v>44131</v>
@@ -10866,19 +10863,19 @@
         <v>40</v>
       </c>
       <c r="F88" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="G88" s="9" t="s">
         <v>451</v>
       </c>
-      <c r="G88" s="9" t="s">
-        <v>452</v>
-      </c>
       <c r="H88" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I88" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J88" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K88" s="10">
         <v>35000000000</v>
@@ -10911,7 +10908,7 @@
         <v>33</v>
       </c>
       <c r="AD88" s="9" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AE88" s="10">
         <v>3162666000</v>
@@ -10923,13 +10920,13 @@
         <v>211</v>
       </c>
       <c r="AK88" s="9" t="s">
+        <v>453</v>
+      </c>
+      <c r="AL88" s="9" t="s">
         <v>454</v>
       </c>
-      <c r="AL88" s="9" t="s">
-        <v>455</v>
-      </c>
       <c r="AM88" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN88" s="9" t="s">
         <v>35</v>
@@ -10944,18 +10941,18 @@
         <v>2</v>
       </c>
       <c r="AR88" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="AS88" s="9" t="s">
         <v>456</v>
       </c>
-      <c r="AS88" s="9" t="s">
+      <c r="AT88" s="9" t="s">
         <v>457</v>
-      </c>
-      <c r="AT88" s="9" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="89" spans="1:46">
       <c r="A89" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B89" s="8">
         <v>43626</v>
@@ -10970,19 +10967,19 @@
         <v>40</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I89" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J89" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K89" s="10">
         <v>15700000000</v>
@@ -11018,7 +11015,7 @@
         <v>33</v>
       </c>
       <c r="AD89" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="AE89" s="10">
         <v>1159000000</v>
@@ -11033,13 +11030,13 @@
         <v>13.54616048317515</v>
       </c>
       <c r="AK89" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="AL89" s="9" t="s">
         <v>462</v>
       </c>
-      <c r="AL89" s="9" t="s">
-        <v>463</v>
-      </c>
       <c r="AM89" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN89" s="9" t="s">
         <v>35</v>
@@ -11054,18 +11051,18 @@
         <v>2</v>
       </c>
       <c r="AR89" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AS89" s="9" t="s">
+        <v>463</v>
+      </c>
+      <c r="AT89" s="9" t="s">
         <v>464</v>
-      </c>
-      <c r="AT89" s="9" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="90" spans="1:46">
       <c r="A90" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B90" s="8">
         <v>43401</v>
@@ -11080,19 +11077,19 @@
         <v>40</v>
       </c>
       <c r="F90" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="G90" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="G90" s="9" t="s">
-        <v>468</v>
-      </c>
       <c r="H90" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I90" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J90" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K90" s="10">
         <v>34000000000</v>
@@ -11107,7 +11104,7 @@
         <v>1</v>
       </c>
       <c r="O90" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P90" s="9" t="s">
         <v>90</v>
@@ -11128,7 +11125,7 @@
         <v>33</v>
       </c>
       <c r="AD90" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AE90" s="10">
         <v>2920461000</v>
@@ -11143,13 +11140,13 @@
         <v>11.64199761612978</v>
       </c>
       <c r="AK90" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="AL90" s="9" t="s">
         <v>470</v>
       </c>
-      <c r="AL90" s="9" t="s">
-        <v>471</v>
-      </c>
       <c r="AM90" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN90" s="9" t="s">
         <v>35</v>
@@ -11164,18 +11161,18 @@
         <v>2</v>
       </c>
       <c r="AR90" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="AS90" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="AS90" s="9" t="s">
+      <c r="AT90" s="9" t="s">
         <v>473</v>
-      </c>
-      <c r="AT90" s="9" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="91" spans="1:46">
       <c r="A91" s="9" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B91" s="8">
         <v>42534</v>
@@ -11190,19 +11187,19 @@
         <v>40</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I91" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J91" s="9" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="K91" s="10">
         <v>26200000000</v>
@@ -11217,7 +11214,7 @@
         <v>1</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>90</v>
@@ -11238,7 +11235,7 @@
         <v>33</v>
       </c>
       <c r="AD91" s="9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AE91" s="10">
         <v>2990911000</v>
@@ -11259,13 +11256,13 @@
         <v>102.9582822471628</v>
       </c>
       <c r="AK91" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="AL91" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="AL91" s="9" t="s">
-        <v>479</v>
-      </c>
       <c r="AM91" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN91" s="9" t="s">
         <v>35</v>
@@ -11280,13 +11277,13 @@
         <v>2</v>
       </c>
       <c r="AR91" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AS91" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="AT91" s="9" t="s">
         <v>480</v>
-      </c>
-      <c r="AT91" s="9" t="s">
-        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -11410,7 +11407,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11428,7 +11425,7 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11449,16 +11446,16 @@
         <v>48</v>
       </c>
       <c r="B6" t="s">
+        <v>483</v>
+      </c>
+      <c r="C6" t="s">
         <v>484</v>
-      </c>
-      <c r="C6" t="s">
-        <v>485</v>
       </c>
       <c r="D6" t="s">
         <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F6" t="s">
         <v>27</v>
@@ -11467,13 +11464,13 @@
         <v>73</v>
       </c>
       <c r="H6" t="s">
+        <v>486</v>
+      </c>
+      <c r="I6" t="s">
         <v>487</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>488</v>
-      </c>
-      <c r="J6" t="s">
-        <v>489</v>
       </c>
       <c r="K6" t="s">
         <v>74</v>
@@ -11482,18 +11479,18 @@
         <v>80</v>
       </c>
       <c r="M6" t="s">
+        <v>489</v>
+      </c>
+      <c r="N6" t="s">
         <v>490</v>
-      </c>
-      <c r="N6" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="42" customHeight="1">
       <c r="A7" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>388</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>389</v>
       </c>
       <c r="C7" s="8">
         <v>45190</v>
@@ -11511,21 +11508,21 @@
         <v>3653708000</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" customHeight="1">
       <c r="A8" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>401</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>402</v>
       </c>
       <c r="C8" s="8">
         <v>44707</v>
@@ -11555,21 +11552,21 @@
         <v>2966000000</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="42" customHeight="1">
       <c r="A9" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>412</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>413</v>
       </c>
       <c r="C9" s="8">
         <v>44640</v>
@@ -11587,21 +11584,21 @@
         <v>592200000</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="42" customHeight="1">
       <c r="A10" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>422</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>423</v>
       </c>
       <c r="C10" s="8">
         <v>44592</v>
@@ -11619,21 +11616,21 @@
         <v>3217170000</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="42" customHeight="1">
       <c r="A11" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>431</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>432</v>
       </c>
       <c r="C11" s="8">
         <v>44579</v>
@@ -11654,21 +11651,21 @@
         <v>2734000000</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="42" customHeight="1">
       <c r="A12" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>441</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>442</v>
       </c>
       <c r="C12" s="8">
         <v>44166</v>
@@ -11686,21 +11683,21 @@
         <v>630422000</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="42" customHeight="1">
       <c r="A13" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>450</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>451</v>
       </c>
       <c r="C13" s="8">
         <v>44131</v>
@@ -11718,21 +11715,21 @@
         <v>3162666000</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="42" customHeight="1">
       <c r="A14" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>459</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>460</v>
       </c>
       <c r="C14" s="8">
         <v>43626</v>
@@ -11750,21 +11747,21 @@
         <v>1159000000</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="42" customHeight="1">
       <c r="A15" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>466</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>467</v>
       </c>
       <c r="C15" s="8">
         <v>43401</v>
@@ -11785,21 +11782,21 @@
         <v>472442000</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="42" customHeight="1">
       <c r="A16" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>475</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>476</v>
       </c>
       <c r="C16" s="8">
         <v>42534</v>
@@ -11823,13 +11820,13 @@
         <v>254472000</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -11877,7 +11874,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11896,7 +11893,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11921,13 +11918,13 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D6" t="s">
         <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F6" t="s">
         <v>73</v>
@@ -11942,7 +11939,7 @@
         <v>28</v>
       </c>
       <c r="J6" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K6" t="s">
         <v>77</v>
@@ -11951,13 +11948,13 @@
         <v>78</v>
       </c>
       <c r="M6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="N6" t="s">
         <v>79</v>
       </c>
       <c r="O6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -11980,7 +11977,7 @@
         <v>94</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K7" s="12">
         <f>IFERROR(IF(AND(D7&gt;0,F7&gt;0,E7=H7),D7/F7,""),"")</f>
@@ -12021,7 +12018,7 @@
         <v>157</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K8" s="12">
         <f>IFERROR(IF(AND(D8&gt;0,F8&gt;0,E8=H8),D8/F8,""),"")</f>
@@ -12062,7 +12059,7 @@
         <v>157</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K9" s="12">
         <f>IFERROR(IF(AND(D9&gt;0,F9&gt;0,E9=H9),D9/F9,""),"")</f>
@@ -12103,7 +12100,7 @@
         <v>157</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K10" s="12">
         <f>IFERROR(IF(AND(D10&gt;0,F10&gt;0,E10=H10),D10/F10,""),"")</f>
@@ -12126,13 +12123,13 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B11" s="8">
         <v>46177</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>90</v>
@@ -12144,7 +12141,7 @@
         <v>94</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K11" s="12">
         <f>IFERROR(IF(AND(D11&gt;0,F11&gt;0,E11=H11),D11/F11,""),"")</f>
@@ -12167,7 +12164,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B12" s="8">
         <v>46175</v>
@@ -12185,7 +12182,7 @@
         <v>35</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K12" s="12">
         <f>IFERROR(IF(AND(D12&gt;0,F12&gt;0,E12=H12),D12/F12,""),"")</f>
@@ -12208,13 +12205,13 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B13" s="8">
         <v>46170</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>90</v>
@@ -12226,7 +12223,7 @@
         <v>94</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K13" s="12">
         <f>IFERROR(IF(AND(D13&gt;0,F13&gt;0,E13=H13),D13/F13,""),"")</f>
@@ -12249,7 +12246,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B14" s="8">
         <v>46167</v>
@@ -12267,7 +12264,7 @@
         <v>157</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K14" s="12">
         <f>IFERROR(IF(AND(D14&gt;0,F14&gt;0,E14=H14),D14/F14,""),"")</f>
@@ -12290,7 +12287,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B15" s="8">
         <v>46157</v>
@@ -12308,7 +12305,7 @@
         <v>157</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K15" s="12">
         <f>IFERROR(IF(AND(D15&gt;0,F15&gt;0,E15=H15),D15/F15,""),"")</f>
@@ -12331,7 +12328,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B16" s="8">
         <v>46139</v>
@@ -12349,7 +12346,7 @@
         <v>157</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K16" s="12">
         <f>IFERROR(IF(AND(D16&gt;0,F16&gt;0,E16=H16),D16/F16,""),"")</f>
@@ -12372,7 +12369,7 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B17" s="8">
         <v>46139</v>
@@ -12390,7 +12387,7 @@
         <v>157</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K17" s="12">
         <f>IFERROR(IF(AND(D17&gt;0,F17&gt;0,E17=H17),D17/F17,""),"")</f>
@@ -12413,7 +12410,7 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B18" s="8">
         <v>46139</v>
@@ -12431,7 +12428,7 @@
         <v>157</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K18" s="12">
         <f>IFERROR(IF(AND(D18&gt;0,F18&gt;0,E18=H18),D18/F18,""),"")</f>
@@ -12454,7 +12451,7 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B19" s="8">
         <v>46139</v>
@@ -12472,7 +12469,7 @@
         <v>157</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K19" s="12">
         <f>IFERROR(IF(AND(D19&gt;0,F19&gt;0,E19=H19),D19/F19,""),"")</f>
@@ -12495,7 +12492,7 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B20" s="8">
         <v>46139</v>
@@ -12513,7 +12510,7 @@
         <v>157</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K20" s="12">
         <f>IFERROR(IF(AND(D20&gt;0,F20&gt;0,E20=H20),D20/F20,""),"")</f>
@@ -12536,13 +12533,13 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B21" s="8">
         <v>46128</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>34</v>
@@ -12554,7 +12551,7 @@
         <v>94</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K21" s="12">
         <f>IFERROR(IF(AND(D21&gt;0,F21&gt;0,E21=H21),D21/F21,""),"")</f>
@@ -12577,7 +12574,7 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B22" s="8">
         <v>45642</v>
@@ -12595,7 +12592,7 @@
         <v>94</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K22" s="12">
         <f>IFERROR(IF(AND(D22&gt;0,F22&gt;0,E22=H22),D22/F22,""),"")</f>
@@ -12618,13 +12615,13 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B23" s="8">
         <v>45288</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>90</v>
@@ -12636,7 +12633,7 @@
         <v>94</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K23" s="12">
         <f>IFERROR(IF(AND(D23&gt;0,F23&gt;0,E23=H23),D23/F23,""),"")</f>
@@ -12659,13 +12656,13 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B24" s="8">
         <v>45190</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>211</v>
@@ -12680,7 +12677,7 @@
         <v>35</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K24" s="12">
         <f>IFERROR(IF(AND(D24&gt;0,F24&gt;0,E24=H24),D24/F24,""),"")</f>
@@ -12695,21 +12692,21 @@
         <v>NO</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B25" s="8">
         <v>44707</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D25" s="10">
         <v>69000000000</v>
@@ -12730,7 +12727,7 @@
         <v>35</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K25" s="12">
         <f>IFERROR(IF(AND(D25&gt;0,F25&gt;0,E25=H25),D25/F25,""),"")</f>
@@ -12745,21 +12742,21 @@
         <v>YES</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B26" s="8">
         <v>44640</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>211</v>
@@ -12774,7 +12771,7 @@
         <v>35</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K26" s="12">
         <f>IFERROR(IF(AND(D26&gt;0,F26&gt;0,E26=H26),D26/F26,""),"")</f>
@@ -12789,21 +12786,21 @@
         <v>NO</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="O26" s="9" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B27" s="8">
         <v>44592</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D27" s="10">
         <v>16500000000</v>
@@ -12821,7 +12818,7 @@
         <v>35</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="K27" s="12">
         <f>IFERROR(IF(AND(D27&gt;0,F27&gt;0,E27=H27),D27/F27,""),"")</f>
@@ -12836,21 +12833,21 @@
         <v>NO</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B28" s="8">
         <v>44579</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D28" s="10">
         <v>68700000000</v>
@@ -12868,7 +12865,7 @@
         <v>35</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K28" s="12">
         <f>IFERROR(IF(AND(D28&gt;0,F28&gt;0,E28=H28),D28/F28,""),"")</f>
@@ -12883,21 +12880,21 @@
         <v>YES</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="O28" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B29" s="8">
         <v>44166</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D29" s="10">
         <v>27700000000</v>
@@ -12915,7 +12912,7 @@
         <v>35</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K29" s="12">
         <f>IFERROR(IF(AND(D29&gt;0,F29&gt;0,E29=H29),D29/F29,""),"")</f>
@@ -12930,21 +12927,21 @@
         <v>YES</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B30" s="8">
         <v>44131</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>211</v>
@@ -12959,7 +12956,7 @@
         <v>35</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K30" s="12">
         <f>IFERROR(IF(AND(D30&gt;0,F30&gt;0,E30=H30),D30/F30,""),"")</f>
@@ -12974,21 +12971,21 @@
         <v>NO</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="O30" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B31" s="8">
         <v>43626</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D31" s="10">
         <v>15700000000</v>
@@ -13006,7 +13003,7 @@
         <v>35</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K31" s="12">
         <f>IFERROR(IF(AND(D31&gt;0,F31&gt;0,E31=H31),D31/F31,""),"")</f>
@@ -13021,21 +13018,21 @@
         <v>YES</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B32" s="8">
         <v>43401</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D32" s="10">
         <v>34000000000</v>
@@ -13053,7 +13050,7 @@
         <v>35</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K32" s="12">
         <f>IFERROR(IF(AND(D32&gt;0,F32&gt;0,E32=H32),D32/F32,""),"")</f>
@@ -13068,21 +13065,21 @@
         <v>YES</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O32" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="9" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B33" s="8">
         <v>42534</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D33" s="10">
         <v>26200000000</v>
@@ -13103,7 +13100,7 @@
         <v>35</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="K33" s="12">
         <f>IFERROR(IF(AND(D33&gt;0,F33&gt;0,E33=H33),D33/F33,""),"")</f>
@@ -13118,10 +13115,10 @@
         <v>YES</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -13156,7 +13153,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13176,7 +13173,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -13196,7 +13193,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="K4" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -13215,7 +13212,7 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E6" t="s">
         <v>22</v>
@@ -13224,28 +13221,28 @@
         <v>83</v>
       </c>
       <c r="G6" t="s">
+        <v>510</v>
+      </c>
+      <c r="H6" t="s">
         <v>511</v>
-      </c>
-      <c r="H6" t="s">
-        <v>512</v>
       </c>
       <c r="I6" t="s">
         <v>30</v>
       </c>
       <c r="K6" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="M6" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="N6" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>587</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>588</v>
       </c>
       <c r="P6" s="4" t="s">
         <v>23</v>
@@ -13265,7 +13262,7 @@
         <v>96</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>95</v>
@@ -13280,7 +13277,7 @@
         <v>98</v>
       </c>
       <c r="K7" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -13312,7 +13309,7 @@
         <v>96</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>95</v>
@@ -13327,7 +13324,7 @@
         <v>102</v>
       </c>
       <c r="K8" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -13359,7 +13356,7 @@
         <v>96</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>95</v>
@@ -13374,7 +13371,7 @@
         <v>105</v>
       </c>
       <c r="K9" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -13406,7 +13403,7 @@
         <v>111</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>110</v>
@@ -13419,7 +13416,7 @@
         <v>113</v>
       </c>
       <c r="K10" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -13451,20 +13448,20 @@
         <v>187</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K11" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -13493,23 +13490,23 @@
         <v>90</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K12" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -13541,20 +13538,20 @@
         <v>187</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K13" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -13583,23 +13580,23 @@
         <v>90</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K14" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="L14">
         <v>6</v>
@@ -13631,7 +13628,7 @@
         <v>96</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>95</v>
@@ -13660,7 +13657,7 @@
         <v>96</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>95</v>
@@ -13675,7 +13672,7 @@
         <v>121</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -13699,7 +13696,7 @@
         <v>96</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>95</v>
@@ -13728,7 +13725,7 @@
         <v>96</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>95</v>
@@ -13757,7 +13754,7 @@
         <v>96</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>95</v>
@@ -13786,7 +13783,7 @@
         <v>96</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>95</v>
@@ -13815,7 +13812,7 @@
         <v>96</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>95</v>
@@ -13844,7 +13841,7 @@
         <v>96</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>95</v>
@@ -13873,7 +13870,7 @@
         <v>96</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>95</v>
@@ -13902,7 +13899,7 @@
         <v>96</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>95</v>
@@ -13931,7 +13928,7 @@
         <v>96</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>95</v>
@@ -13960,7 +13957,7 @@
         <v>158</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>110</v>
@@ -13984,16 +13981,16 @@
         <v>90</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="13" t="s">
@@ -14011,16 +14008,16 @@
         <v>90</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="13" t="s">
@@ -14038,16 +14035,16 @@
         <v>90</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="13" t="s">
@@ -14068,7 +14065,7 @@
         <v>162</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>110</v>
@@ -14097,13 +14094,13 @@
         <v>162</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="13" t="s">
@@ -14124,7 +14121,7 @@
         <v>96</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>95</v>
@@ -14153,7 +14150,7 @@
         <v>96</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>95</v>
@@ -14182,7 +14179,7 @@
         <v>96</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>95</v>
@@ -14211,7 +14208,7 @@
         <v>96</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>95</v>
@@ -14240,7 +14237,7 @@
         <v>182</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>110</v>
@@ -14267,7 +14264,7 @@
         <v>187</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>110</v>
@@ -14296,13 +14293,13 @@
         <v>187</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H38" s="9"/>
       <c r="I38" s="13" t="s">
@@ -14323,7 +14320,7 @@
         <v>96</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>95</v>
@@ -14352,7 +14349,7 @@
         <v>96</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>95</v>
@@ -14381,7 +14378,7 @@
         <v>96</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>95</v>
@@ -14410,7 +14407,7 @@
         <v>96</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>95</v>
@@ -14439,7 +14436,7 @@
         <v>96</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>95</v>
@@ -14468,7 +14465,7 @@
         <v>212</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>110</v>
@@ -14497,13 +14494,13 @@
         <v>212</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="13" t="s">
@@ -14524,7 +14521,7 @@
         <v>162</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>110</v>
@@ -14553,13 +14550,13 @@
         <v>162</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="13" t="s">
@@ -14580,7 +14577,7 @@
         <v>222</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>95</v>
@@ -14609,7 +14606,7 @@
         <v>212</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>110</v>
@@ -14638,13 +14635,13 @@
         <v>212</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H50" s="9"/>
       <c r="I50" s="13" t="s">
@@ -14665,7 +14662,7 @@
         <v>230</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>110</v>
@@ -14694,7 +14691,7 @@
         <v>96</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>95</v>
@@ -14723,7 +14720,7 @@
         <v>96</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>95</v>
@@ -14752,7 +14749,7 @@
         <v>96</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>95</v>
@@ -14781,7 +14778,7 @@
         <v>96</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>95</v>
@@ -14810,7 +14807,7 @@
         <v>96</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>95</v>
@@ -14839,7 +14836,7 @@
         <v>96</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>95</v>
@@ -14868,7 +14865,7 @@
         <v>96</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>95</v>
@@ -14897,7 +14894,7 @@
         <v>255</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>110</v>
@@ -14923,16 +14920,16 @@
         <v>38</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H60" s="8">
         <v>46192</v>
@@ -14955,13 +14952,13 @@
         <v>162</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H61" s="8">
         <v>46181</v>
@@ -14981,16 +14978,16 @@
         <v>38</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H62" s="8">
         <v>46177</v>
@@ -15013,13 +15010,13 @@
         <v>162</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H63" s="9"/>
       <c r="I63" s="13" t="s">
@@ -15037,16 +15034,16 @@
         <v>38</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H64" s="9"/>
       <c r="I64" s="13" t="s">
@@ -15055,374 +15052,374 @@
     </row>
     <row r="65" spans="1:9" ht="28" customHeight="1">
       <c r="A65" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B65" s="8">
         <v>46183</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H65" s="8">
         <v>46183</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="28" customHeight="1">
       <c r="A66" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B66" s="8">
         <v>46177</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D66" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H66" s="8">
         <v>46177</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="28" customHeight="1">
       <c r="A67" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B67" s="8">
         <v>46177</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H67" s="8">
         <v>46171</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="28" customHeight="1">
       <c r="A68" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B68" s="8">
         <v>46177</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H68" s="8">
         <v>46170</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="28" customHeight="1">
       <c r="A69" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B69" s="8">
         <v>46177</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H69" s="8">
         <v>46170</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="28" customHeight="1">
       <c r="A70" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B70" s="8">
         <v>46177</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D70" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H70" s="8">
         <v>46170</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="28" customHeight="1">
       <c r="A71" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B71" s="8">
         <v>46177</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D71" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H71" s="8">
         <v>46170</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="28" customHeight="1">
       <c r="A72" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B72" s="8">
         <v>46177</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H72" s="8">
         <v>46170</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="28" customHeight="1">
       <c r="A73" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B73" s="8">
         <v>46177</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H73" s="9"/>
       <c r="I73" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="28" customHeight="1">
       <c r="A74" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B74" s="8">
         <v>46177</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D74" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H74" s="9"/>
       <c r="I74" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="28" customHeight="1">
       <c r="A75" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B75" s="8">
         <v>46177</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D75" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H75" s="9"/>
       <c r="I75" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="28" customHeight="1">
       <c r="A76" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B76" s="8">
         <v>46177</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D76" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H76" s="9"/>
       <c r="I76" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="28" customHeight="1">
       <c r="A77" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B77" s="8">
         <v>46177</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H77" s="9"/>
       <c r="I77" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="28" customHeight="1">
       <c r="A78" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B78" s="8">
         <v>46175</v>
@@ -15431,16 +15428,16 @@
         <v>41</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H78" s="8">
         <v>46175</v>
@@ -15451,7 +15448,7 @@
     </row>
     <row r="79" spans="1:9" ht="28" customHeight="1">
       <c r="A79" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B79" s="8">
         <v>46175</v>
@@ -15463,13 +15460,13 @@
         <v>187</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H79" s="8">
         <v>46176</v>
@@ -15480,7 +15477,7 @@
     </row>
     <row r="80" spans="1:9" ht="28" customHeight="1">
       <c r="A80" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B80" s="8">
         <v>46175</v>
@@ -15492,13 +15489,13 @@
         <v>162</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H80" s="8">
         <v>46175</v>
@@ -15509,7 +15506,7 @@
     </row>
     <row r="81" spans="1:9" ht="28" customHeight="1">
       <c r="A81" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B81" s="8">
         <v>46175</v>
@@ -15521,13 +15518,13 @@
         <v>187</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H81" s="9"/>
       <c r="I81" s="13" t="s">
@@ -15536,7 +15533,7 @@
     </row>
     <row r="82" spans="1:9" ht="28" customHeight="1">
       <c r="A82" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B82" s="8">
         <v>46175</v>
@@ -15548,13 +15545,13 @@
         <v>162</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H82" s="9"/>
       <c r="I82" s="13" t="s">
@@ -15563,63 +15560,63 @@
     </row>
     <row r="83" spans="1:9" ht="28" customHeight="1">
       <c r="A83" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B83" s="8">
         <v>46170</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D83" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H83" s="8">
         <v>46170</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="28" customHeight="1">
       <c r="A84" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B84" s="8">
         <v>46170</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H84" s="9"/>
       <c r="I84" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="28" customHeight="1">
       <c r="A85" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B85" s="8">
         <v>46167</v>
@@ -15631,24 +15628,24 @@
         <v>162</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H85" s="8">
         <v>46167</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="28" customHeight="1">
       <c r="A86" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B86" s="8">
         <v>46167</v>
@@ -15660,134 +15657,134 @@
         <v>162</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H86" s="9"/>
       <c r="I86" s="13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="28" customHeight="1">
       <c r="A87" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B87" s="8">
         <v>46162</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H87" s="8">
         <v>46162</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="28" customHeight="1">
       <c r="A88" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B88" s="8">
         <v>46162</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H88" s="9"/>
       <c r="I88" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="28" customHeight="1">
       <c r="A89" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B89" s="8">
         <v>46157</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H89" s="8">
         <v>46157</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="28" customHeight="1">
       <c r="A90" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B90" s="8">
         <v>46157</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D90" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H90" s="9"/>
       <c r="I90" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="28" customHeight="1">
       <c r="A91" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B91" s="8">
         <v>46157</v>
@@ -15796,56 +15793,56 @@
         <v>90</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H91" s="8">
         <v>46157</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="28" customHeight="1">
       <c r="A92" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B92" s="8">
         <v>46150</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H92" s="8">
         <v>46150</v>
       </c>
       <c r="I92" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="28" customHeight="1">
       <c r="A93" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B93" s="8">
         <v>46147</v>
@@ -15857,24 +15854,24 @@
         <v>187</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H93" s="8">
         <v>46147</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="28" customHeight="1">
       <c r="A94" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B94" s="8">
         <v>46147</v>
@@ -15886,22 +15883,22 @@
         <v>187</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H94" s="9"/>
       <c r="I94" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="28" customHeight="1">
       <c r="A95" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B95" s="8">
         <v>46146</v>
@@ -15910,27 +15907,27 @@
         <v>38</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H95" s="8">
         <v>46146</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="28" customHeight="1">
       <c r="A96" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B96" s="8">
         <v>46146</v>
@@ -15939,25 +15936,25 @@
         <v>38</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H96" s="9"/>
       <c r="I96" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="28" customHeight="1">
       <c r="A97" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B97" s="8">
         <v>46139</v>
@@ -15966,27 +15963,27 @@
         <v>90</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H97" s="8">
         <v>46139</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="28" customHeight="1">
       <c r="A98" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B98" s="8">
         <v>46139</v>
@@ -15995,25 +15992,25 @@
         <v>90</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H98" s="9"/>
       <c r="I98" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="28" customHeight="1">
       <c r="A99" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B99" s="8">
         <v>46139</v>
@@ -16025,24 +16022,24 @@
         <v>187</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H99" s="8">
         <v>46139</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="28" customHeight="1">
       <c r="A100" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B100" s="8">
         <v>46139</v>
@@ -16054,22 +16051,22 @@
         <v>187</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H100" s="9"/>
       <c r="I100" s="13" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="28" customHeight="1">
       <c r="A101" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B101" s="8">
         <v>46139</v>
@@ -16078,27 +16075,27 @@
         <v>90</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H101" s="8">
         <v>46139</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="28" customHeight="1">
       <c r="A102" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B102" s="8">
         <v>46139</v>
@@ -16107,27 +16104,27 @@
         <v>90</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H102" s="8">
         <v>46139</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="28" customHeight="1">
       <c r="A103" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B103" s="8">
         <v>46139</v>
@@ -16136,25 +16133,25 @@
         <v>90</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H103" s="9"/>
       <c r="I103" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="28" customHeight="1">
       <c r="A104" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B104" s="8">
         <v>46139</v>
@@ -16163,25 +16160,25 @@
         <v>90</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H104" s="9"/>
       <c r="I104" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="28" customHeight="1">
       <c r="A105" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B105" s="8">
         <v>46139</v>
@@ -16190,27 +16187,27 @@
         <v>90</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H105" s="8">
         <v>46139</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="28" customHeight="1">
       <c r="A106" s="9" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B106" s="8">
         <v>46139</v>
@@ -16219,25 +16216,25 @@
         <v>90</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H106" s="9"/>
       <c r="I106" s="13" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="28" customHeight="1">
       <c r="A107" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B107" s="8">
         <v>46139</v>
@@ -16246,27 +16243,27 @@
         <v>90</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H107" s="8">
         <v>46139</v>
       </c>
       <c r="I107" s="13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="28" customHeight="1">
       <c r="A108" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B108" s="8">
         <v>46139</v>
@@ -16275,81 +16272,81 @@
         <v>90</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H108" s="9"/>
       <c r="I108" s="13" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="28" customHeight="1">
       <c r="A109" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B109" s="8">
         <v>46132</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H109" s="8">
         <v>46132</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="28" customHeight="1">
       <c r="A110" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B110" s="8">
         <v>46132</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D110" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H110" s="9"/>
       <c r="I110" s="13" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="28" customHeight="1">
       <c r="A111" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B111" s="8">
         <v>46132</v>
@@ -16358,27 +16355,27 @@
         <v>38</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H111" s="8">
         <v>46132</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="28" customHeight="1">
       <c r="A112" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B112" s="8">
         <v>46132</v>
@@ -16387,25 +16384,25 @@
         <v>38</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H112" s="9"/>
       <c r="I112" s="13" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="28" customHeight="1">
       <c r="A113" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B113" s="8">
         <v>46132</v>
@@ -16414,27 +16411,27 @@
         <v>38</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H113" s="8">
         <v>46132</v>
       </c>
       <c r="I113" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="28" customHeight="1">
       <c r="A114" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B114" s="8">
         <v>46132</v>
@@ -16443,475 +16440,475 @@
         <v>38</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H114" s="9"/>
       <c r="I114" s="13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="28" customHeight="1">
       <c r="A115" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B115" s="8">
         <v>46128</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H115" s="8">
         <v>46128</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="28" customHeight="1">
       <c r="A116" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B116" s="8">
         <v>46128</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H116" s="8">
         <v>46128</v>
       </c>
       <c r="I116" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="28" customHeight="1">
       <c r="A117" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B117" s="8">
         <v>46128</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H117" s="8">
         <v>46128</v>
       </c>
       <c r="I117" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="28" customHeight="1">
       <c r="A118" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B118" s="8">
         <v>46128</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H118" s="9"/>
       <c r="I118" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="28" customHeight="1">
       <c r="A119" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B119" s="8">
         <v>46128</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H119" s="9"/>
       <c r="I119" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="28" customHeight="1">
       <c r="A120" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B120" s="8">
         <v>46128</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H120" s="9"/>
       <c r="I120" s="13" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="28" customHeight="1">
       <c r="A121" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B121" s="8">
         <v>46122</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D121" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H121" s="8">
         <v>46122</v>
       </c>
       <c r="I121" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="28" customHeight="1">
       <c r="A122" s="9" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B122" s="8">
         <v>46122</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D122" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H122" s="9"/>
       <c r="I122" s="13" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="28" customHeight="1">
       <c r="A123" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B123" s="8">
         <v>46122</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D123" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H123" s="8">
         <v>46122</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="28" customHeight="1">
       <c r="A124" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B124" s="8">
         <v>46122</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D124" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H124" s="9"/>
       <c r="I124" s="13" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="28" customHeight="1">
       <c r="A125" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B125" s="8">
         <v>46115</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H125" s="8">
         <v>46115</v>
       </c>
       <c r="I125" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="28" customHeight="1">
       <c r="A126" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B126" s="8">
         <v>46115</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H126" s="9"/>
       <c r="I126" s="13" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="28" customHeight="1">
       <c r="A127" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B127" s="8">
         <v>46115</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D127" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H127" s="8">
         <v>46115</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="28" customHeight="1">
       <c r="A128" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B128" s="8">
         <v>46115</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D128" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H128" s="9"/>
       <c r="I128" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="28" customHeight="1">
       <c r="A129" s="9" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B129" s="8">
         <v>46111</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H129" s="8">
         <v>46111</v>
       </c>
       <c r="I129" s="13" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="28" customHeight="1">
       <c r="A130" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B130" s="8">
         <v>46111</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D130" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H130" s="8">
         <v>46111</v>
       </c>
       <c r="I130" s="13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="28" customHeight="1">
       <c r="A131" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B131" s="8">
         <v>46080</v>
@@ -16920,16 +16917,16 @@
         <v>44</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H131" s="8">
         <v>46080</v>
@@ -16940,7 +16937,7 @@
     </row>
     <row r="132" spans="1:9" ht="28" customHeight="1">
       <c r="A132" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B132" s="8">
         <v>45729</v>
@@ -16949,27 +16946,27 @@
         <v>38</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H132" s="8">
         <v>45729</v>
       </c>
       <c r="I132" s="13" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="28" customHeight="1">
       <c r="A133" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B133" s="8">
         <v>45642</v>
@@ -16978,27 +16975,27 @@
         <v>90</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H133" s="8">
         <v>45642</v>
       </c>
       <c r="I133" s="13" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="28" customHeight="1">
       <c r="A134" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B134" s="8">
         <v>45611</v>
@@ -17007,27 +17004,27 @@
         <v>44</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H134" s="8">
         <v>45611</v>
       </c>
       <c r="I134" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="28" customHeight="1">
       <c r="A135" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B135" s="8">
         <v>45391</v>
@@ -17036,27 +17033,27 @@
         <v>44</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H135" s="8">
         <v>45391</v>
       </c>
       <c r="I135" s="13" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="28" customHeight="1">
       <c r="A136" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B136" s="8">
         <v>45357</v>
@@ -17065,602 +17062,602 @@
         <v>44</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E136" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H136" s="8">
         <v>45357</v>
       </c>
       <c r="I136" s="13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="28" customHeight="1">
       <c r="A137" s="9" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B137" s="8">
         <v>45288</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H137" s="8">
         <v>45288</v>
       </c>
       <c r="I137" s="13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="28" customHeight="1">
       <c r="A138" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B138" s="8">
         <v>45190</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E138" s="9" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H138" s="8">
         <v>45190</v>
       </c>
       <c r="I138" s="13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="28" customHeight="1">
       <c r="A139" s="9" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B139" s="8">
         <v>45190</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H139" s="8">
         <v>45008</v>
       </c>
       <c r="I139" s="13" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="28" customHeight="1">
       <c r="A140" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B140" s="8">
         <v>44707</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E140" s="9" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G140" s="9" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H140" s="8">
         <v>44707</v>
       </c>
       <c r="I140" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="28" customHeight="1">
       <c r="A141" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B141" s="8">
         <v>44707</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H141" s="8">
         <v>44644</v>
       </c>
       <c r="I141" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="28" customHeight="1">
       <c r="A142" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B142" s="8">
         <v>44640</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G142" s="9" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H142" s="8">
         <v>44734</v>
       </c>
       <c r="I142" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="28" customHeight="1">
       <c r="A143" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B143" s="8">
         <v>44640</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H143" s="8">
         <v>44643</v>
       </c>
       <c r="I143" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="28" customHeight="1">
       <c r="A144" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B144" s="8">
         <v>44592</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E144" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G144" s="9" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H144" s="8">
         <v>44608</v>
       </c>
       <c r="I144" s="13" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="28" customHeight="1">
       <c r="A145" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B145" s="8">
         <v>44579</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H145" s="8">
         <v>44579</v>
       </c>
       <c r="I145" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="28" customHeight="1">
       <c r="A146" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B146" s="8">
         <v>44579</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E146" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G146" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H146" s="8">
         <v>44250</v>
       </c>
       <c r="I146" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="28" customHeight="1">
       <c r="A147" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B147" s="8">
         <v>44166</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H147" s="8">
         <v>44166</v>
       </c>
       <c r="I147" s="13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="28" customHeight="1">
       <c r="A148" s="9" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B148" s="8">
         <v>44166</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E148" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G148" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H148" s="8">
         <v>43902</v>
       </c>
       <c r="I148" s="13" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="28" customHeight="1">
       <c r="A149" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B149" s="8">
         <v>44131</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H149" s="8">
         <v>44131</v>
       </c>
       <c r="I149" s="13" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="28" customHeight="1">
       <c r="A150" s="9" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B150" s="8">
         <v>44131</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E150" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G150" s="9" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H150" s="8">
         <v>43966</v>
       </c>
       <c r="I150" s="13" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="28" customHeight="1">
       <c r="A151" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B151" s="8">
         <v>43626</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H151" s="8">
         <v>43626</v>
       </c>
       <c r="I151" s="13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="28" customHeight="1">
       <c r="A152" s="9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B152" s="8">
         <v>43626</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E152" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G152" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H152" s="8">
         <v>43518</v>
       </c>
       <c r="I152" s="13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="28" customHeight="1">
       <c r="A153" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B153" s="8">
         <v>43401</v>
       </c>
       <c r="C153" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H153" s="8">
         <v>43401</v>
       </c>
       <c r="I153" s="13" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="28" customHeight="1">
       <c r="A154" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B154" s="8">
         <v>43401</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E154" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G154" s="9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H154" s="8">
         <v>43215</v>
       </c>
       <c r="I154" s="13" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="28" customHeight="1">
       <c r="A155" s="9" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B155" s="8">
         <v>42534</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H155" s="8">
         <v>42534</v>
       </c>
       <c r="I155" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="28" customHeight="1">
       <c r="A156" s="9" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B156" s="8">
         <v>42534</v>
       </c>
       <c r="C156" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D156" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E156" s="9" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G156" s="9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H156" s="8">
         <v>42412</v>
       </c>
       <c r="I156" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
   </sheetData>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4106" uniqueCount="597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4106" uniqueCount="598">
   <si>
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-05 | Build 0e778eea6737 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-05 | Build d2f69d819e75 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -798,6 +798,9 @@
   </si>
   <si>
     <t>Technology</t>
+  </si>
+  <si>
+    <t>001Р-04; 001Р-05</t>
   </si>
   <si>
     <t>Yandex Investor Relations</t>
@@ -6958,7 +6961,7 @@
         <v>92</v>
       </c>
       <c r="R48" s="9" t="s">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="S48" s="9" t="s">
         <v>90</v>
@@ -7000,10 +7003,10 @@
         <v>5</v>
       </c>
       <c r="AR48" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AS48" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AT48" s="9" t="s">
         <v>39</v>
@@ -7011,7 +7014,7 @@
     </row>
     <row r="49" spans="1:46">
       <c r="A49" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B49" s="8">
         <v>46183</v>
@@ -7026,7 +7029,7 @@
         <v>108</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G49" s="9" t="s">
         <v>33</v>
@@ -7044,7 +7047,7 @@
         <v>3000000000</v>
       </c>
       <c r="M49" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>33</v>
@@ -7098,18 +7101,18 @@
         <v>1</v>
       </c>
       <c r="AR49" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AS49" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AT49" s="9" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="50" spans="1:46">
       <c r="A50" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B50" s="8">
         <v>46177</v>
@@ -7118,16 +7121,16 @@
         <v>4</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H50" s="9" t="s">
         <v>90</v>
@@ -7196,15 +7199,15 @@
         <v>187</v>
       </c>
       <c r="AS50" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AT50" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:46">
       <c r="A51" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B51" s="8">
         <v>46175</v>
@@ -7291,10 +7294,10 @@
         <v>5</v>
       </c>
       <c r="AR51" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AS51" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AT51" s="9" t="s">
         <v>43</v>
@@ -7302,7 +7305,7 @@
     </row>
     <row r="52" spans="1:46">
       <c r="A52" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B52" s="8">
         <v>46170</v>
@@ -7314,10 +7317,10 @@
         <v>107</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>38</v>
@@ -7389,15 +7392,15 @@
         <v>162</v>
       </c>
       <c r="AS52" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AT52" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="53" spans="1:46">
       <c r="A53" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B53" s="8">
         <v>46167</v>
@@ -7484,15 +7487,15 @@
         <v>162</v>
       </c>
       <c r="AS53" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AT53" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="54" spans="1:46">
       <c r="A54" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B54" s="8">
         <v>46162</v>
@@ -7507,7 +7510,7 @@
         <v>108</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>33</v>
@@ -7531,7 +7534,7 @@
         <v>90</v>
       </c>
       <c r="Q54" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R54" s="9" t="s">
         <v>33</v>
@@ -7579,15 +7582,15 @@
         <v>187</v>
       </c>
       <c r="AS54" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AT54" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55" spans="1:46">
       <c r="A55" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B55" s="8">
         <v>46157</v>
@@ -7602,7 +7605,7 @@
         <v>108</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>33</v>
@@ -7626,7 +7629,7 @@
         <v>90</v>
       </c>
       <c r="Q55" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R55" s="9" t="s">
         <v>33</v>
@@ -7674,15 +7677,15 @@
         <v>162</v>
       </c>
       <c r="AS55" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AT55" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="56" spans="1:46">
       <c r="A56" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B56" s="8">
         <v>46157</v>
@@ -7766,18 +7769,18 @@
         <v>1</v>
       </c>
       <c r="AR56" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AS56" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AT56" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="57" spans="1:46">
       <c r="A57" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B57" s="8">
         <v>46150</v>
@@ -7792,7 +7795,7 @@
         <v>108</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>33</v>
@@ -7864,18 +7867,18 @@
         <v>1</v>
       </c>
       <c r="AR57" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AS57" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AT57" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="58" spans="1:46">
       <c r="A58" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B58" s="8">
         <v>46147</v>
@@ -7917,7 +7920,7 @@
         <v>90</v>
       </c>
       <c r="Q58" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R58" s="9" t="s">
         <v>33</v>
@@ -7965,15 +7968,15 @@
         <v>187</v>
       </c>
       <c r="AS58" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AT58" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="59" spans="1:46">
       <c r="A59" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B59" s="8">
         <v>46146</v>
@@ -7997,7 +8000,7 @@
         <v>33</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J59" s="9" t="s">
         <v>90</v>
@@ -8012,7 +8015,7 @@
         <v>90</v>
       </c>
       <c r="Q59" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R59" s="9" t="s">
         <v>33</v>
@@ -8057,18 +8060,18 @@
         <v>2</v>
       </c>
       <c r="AR59" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AS59" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AT59" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="60" spans="1:46">
       <c r="A60" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B60" s="8">
         <v>46139</v>
@@ -8152,18 +8155,18 @@
         <v>2</v>
       </c>
       <c r="AR60" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AS60" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AT60" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="61" spans="1:46">
       <c r="A61" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B61" s="8">
         <v>46139</v>
@@ -8250,15 +8253,15 @@
         <v>187</v>
       </c>
       <c r="AS61" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AT61" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="62" spans="1:46">
       <c r="A62" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B62" s="8">
         <v>46139</v>
@@ -8342,18 +8345,18 @@
         <v>4</v>
       </c>
       <c r="AR62" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AS62" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AT62" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="63" spans="1:46">
       <c r="A63" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B63" s="8">
         <v>46139</v>
@@ -8437,18 +8440,18 @@
         <v>2</v>
       </c>
       <c r="AR63" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AS63" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AT63" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:46">
       <c r="A64" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B64" s="8">
         <v>46139</v>
@@ -8532,18 +8535,18 @@
         <v>2</v>
       </c>
       <c r="AR64" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AS64" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AT64" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="65" spans="1:46">
       <c r="A65" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B65" s="8">
         <v>46132</v>
@@ -8558,7 +8561,7 @@
         <v>108</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>33</v>
@@ -8630,15 +8633,15 @@
         <v>111</v>
       </c>
       <c r="AS65" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AT65" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:46">
       <c r="A66" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B66" s="8">
         <v>46132</v>
@@ -8677,7 +8680,7 @@
         <v>90</v>
       </c>
       <c r="Q66" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R66" s="9" t="s">
         <v>33</v>
@@ -8722,18 +8725,18 @@
         <v>2</v>
       </c>
       <c r="AR66" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AS66" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AT66" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:46">
       <c r="A67" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B67" s="8">
         <v>46132</v>
@@ -8772,7 +8775,7 @@
         <v>90</v>
       </c>
       <c r="Q67" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R67" s="9" t="s">
         <v>33</v>
@@ -8817,18 +8820,18 @@
         <v>2</v>
       </c>
       <c r="AR67" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AS67" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AT67" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:46">
       <c r="A68" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B68" s="8">
         <v>46128</v>
@@ -8843,13 +8846,13 @@
         <v>108</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G68" s="9" t="s">
         <v>90</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="I68" s="9" t="s">
         <v>9</v>
@@ -8918,18 +8921,18 @@
         <v>6</v>
       </c>
       <c r="AR68" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AS68" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AT68" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="69" spans="1:46">
       <c r="A69" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B69" s="8">
         <v>46122</v>
@@ -8944,7 +8947,7 @@
         <v>108</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G69" s="9" t="s">
         <v>33</v>
@@ -9016,15 +9019,15 @@
         <v>162</v>
       </c>
       <c r="AS69" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AT69" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="70" spans="1:46">
       <c r="A70" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B70" s="8">
         <v>46122</v>
@@ -9039,7 +9042,7 @@
         <v>108</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G70" s="9" t="s">
         <v>33</v>
@@ -9063,7 +9066,7 @@
         <v>90</v>
       </c>
       <c r="Q70" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="R70" s="9" t="s">
         <v>33</v>
@@ -9111,15 +9114,15 @@
         <v>111</v>
       </c>
       <c r="AS70" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AT70" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="71" spans="1:46">
       <c r="A71" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B71" s="8">
         <v>46115</v>
@@ -9134,7 +9137,7 @@
         <v>115</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G71" s="9" t="s">
         <v>33</v>
@@ -9206,18 +9209,18 @@
         <v>2</v>
       </c>
       <c r="AR71" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AS71" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AT71" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="72" spans="1:46">
       <c r="A72" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B72" s="8">
         <v>46115</v>
@@ -9232,7 +9235,7 @@
         <v>115</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G72" s="9" t="s">
         <v>33</v>
@@ -9304,15 +9307,15 @@
         <v>187</v>
       </c>
       <c r="AS72" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AT72" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="73" spans="1:46">
       <c r="A73" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B73" s="8">
         <v>46111</v>
@@ -9327,7 +9330,7 @@
         <v>108</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G73" s="9" t="s">
         <v>33</v>
@@ -9399,18 +9402,18 @@
         <v>1</v>
       </c>
       <c r="AR73" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AS73" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AT73" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="74" spans="1:46">
       <c r="A74" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B74" s="8">
         <v>46111</v>
@@ -9425,7 +9428,7 @@
         <v>108</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G74" s="9" t="s">
         <v>33</v>
@@ -9497,15 +9500,15 @@
         <v>162</v>
       </c>
       <c r="AS74" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AT74" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="75" spans="1:46">
       <c r="A75" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B75" s="8">
         <v>46080</v>
@@ -9595,10 +9598,10 @@
         <v>1</v>
       </c>
       <c r="AR75" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AS75" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AT75" s="9" t="s">
         <v>45</v>
@@ -9606,7 +9609,7 @@
     </row>
     <row r="76" spans="1:46">
       <c r="A76" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B76" s="8">
         <v>45729</v>
@@ -9690,18 +9693,18 @@
         <v>1</v>
       </c>
       <c r="AR76" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AS76" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AT76" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="77" spans="1:46">
       <c r="A77" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B77" s="8">
         <v>45642</v>
@@ -9785,18 +9788,18 @@
         <v>1</v>
       </c>
       <c r="AR77" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AS77" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AT77" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="78" spans="1:46">
       <c r="A78" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B78" s="8">
         <v>45611</v>
@@ -9847,16 +9850,16 @@
         <v>90</v>
       </c>
       <c r="U78" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="X78" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AB78" s="9" t="s">
         <v>33</v>
       </c>
       <c r="AD78" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AH78" s="9" t="s">
         <v>90</v>
@@ -9883,18 +9886,18 @@
         <v>1</v>
       </c>
       <c r="AR78" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AS78" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AT78" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="79" spans="1:46">
       <c r="A79" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B79" s="8">
         <v>45391</v>
@@ -9951,7 +9954,7 @@
         <v>90</v>
       </c>
       <c r="X79" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AB79" s="9" t="s">
         <v>33</v>
@@ -9984,18 +9987,18 @@
         <v>1</v>
       </c>
       <c r="AR79" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AS79" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AT79" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="80" spans="1:46">
       <c r="A80" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B80" s="8">
         <v>45357</v>
@@ -10082,18 +10085,18 @@
         <v>1</v>
       </c>
       <c r="AR80" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AS80" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AT80" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="81" spans="1:46">
       <c r="A81" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B81" s="8">
         <v>45288</v>
@@ -10108,10 +10111,10 @@
         <v>89</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H81" s="9" t="s">
         <v>90</v>
@@ -10177,18 +10180,18 @@
         <v>1</v>
       </c>
       <c r="AR81" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AS81" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AT81" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="82" spans="1:46">
       <c r="A82" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B82" s="8">
         <v>45190</v>
@@ -10203,19 +10206,19 @@
         <v>40</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I82" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K82" s="10">
         <v>28000000000</v>
@@ -10227,7 +10230,7 @@
         <v>1</v>
       </c>
       <c r="O82" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P82" s="9" t="s">
         <v>90</v>
@@ -10248,7 +10251,7 @@
         <v>33</v>
       </c>
       <c r="AD82" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AE82" s="10">
         <v>3653708000</v>
@@ -10260,13 +10263,13 @@
         <v>211</v>
       </c>
       <c r="AK82" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL82" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM82" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN82" s="9" t="s">
         <v>35</v>
@@ -10281,18 +10284,18 @@
         <v>2</v>
       </c>
       <c r="AR82" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AS82" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AT82" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="83" spans="1:46">
       <c r="A83" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B83" s="8">
         <v>44707</v>
@@ -10307,19 +10310,19 @@
         <v>40</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I83" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J83" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K83" s="10">
         <v>61000000000</v>
@@ -10334,10 +10337,10 @@
         <v>1</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q83" s="9" t="s">
         <v>109</v>
@@ -10358,7 +10361,7 @@
         <v>33</v>
       </c>
       <c r="AD83" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AE83" s="10">
         <v>12851000000</v>
@@ -10379,13 +10382,13 @@
         <v>23.26365475387728</v>
       </c>
       <c r="AK83" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL83" s="9" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM83" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN83" s="9" t="s">
         <v>35</v>
@@ -10400,18 +10403,18 @@
         <v>2</v>
       </c>
       <c r="AR83" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AS83" s="9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AT83" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="84" spans="1:46">
       <c r="A84" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B84" s="8">
         <v>44640</v>
@@ -10426,19 +10429,19 @@
         <v>40</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I84" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J84" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K84" s="10">
         <v>10400000000</v>
@@ -10450,7 +10453,7 @@
         <v>1</v>
       </c>
       <c r="O84" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P84" s="9" t="s">
         <v>90</v>
@@ -10471,7 +10474,7 @@
         <v>33</v>
       </c>
       <c r="AD84" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AE84" s="10">
         <v>592200000</v>
@@ -10483,13 +10486,13 @@
         <v>211</v>
       </c>
       <c r="AK84" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AL84" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AM84" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN84" s="9" t="s">
         <v>35</v>
@@ -10504,18 +10507,18 @@
         <v>2</v>
       </c>
       <c r="AR84" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS84" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AT84" s="9" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="85" spans="1:46">
       <c r="A85" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B85" s="8">
         <v>44592</v>
@@ -10530,19 +10533,19 @@
         <v>40</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I85" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J85" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K85" s="10">
         <v>16500000000</v>
@@ -10557,7 +10560,7 @@
         <v>1</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>90</v>
@@ -10578,7 +10581,7 @@
         <v>33</v>
       </c>
       <c r="AD85" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AE85" s="10">
         <v>3217170000</v>
@@ -10593,13 +10596,13 @@
         <v>5.128731151913017</v>
       </c>
       <c r="AK85" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL85" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM85" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN85" s="9" t="s">
         <v>35</v>
@@ -10614,18 +10617,18 @@
         <v>1</v>
       </c>
       <c r="AR85" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AS85" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AT85" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="86" spans="1:46">
       <c r="A86" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B86" s="8">
         <v>44579</v>
@@ -10640,19 +10643,19 @@
         <v>40</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H86" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I86" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J86" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K86" s="10">
         <v>68700000000</v>
@@ -10667,10 +10670,10 @@
         <v>1</v>
       </c>
       <c r="O86" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P86" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q86" s="9" t="s">
         <v>109</v>
@@ -10691,7 +10694,7 @@
         <v>33</v>
       </c>
       <c r="AD86" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AE86" s="10">
         <v>8086000000</v>
@@ -10706,13 +10709,13 @@
         <v>8.496166213208014</v>
       </c>
       <c r="AK86" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AL86" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM86" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN86" s="9" t="s">
         <v>35</v>
@@ -10727,18 +10730,18 @@
         <v>2</v>
       </c>
       <c r="AR86" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AS86" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AT86" s="9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="87" spans="1:46">
       <c r="A87" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B87" s="8">
         <v>44166</v>
@@ -10753,19 +10756,19 @@
         <v>40</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I87" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J87" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K87" s="10">
         <v>27700000000</v>
@@ -10780,7 +10783,7 @@
         <v>1</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>90</v>
@@ -10801,7 +10804,7 @@
         <v>33</v>
       </c>
       <c r="AD87" s="9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AE87" s="10">
         <v>630422000</v>
@@ -10816,13 +10819,13 @@
         <v>43.93882193197572</v>
       </c>
       <c r="AK87" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AL87" s="9" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM87" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN87" s="9" t="s">
         <v>35</v>
@@ -10837,18 +10840,18 @@
         <v>2</v>
       </c>
       <c r="AR87" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AS87" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AT87" s="9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="88" spans="1:46">
       <c r="A88" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B88" s="8">
         <v>44131</v>
@@ -10863,19 +10866,19 @@
         <v>40</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H88" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I88" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J88" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K88" s="10">
         <v>35000000000</v>
@@ -10908,7 +10911,7 @@
         <v>33</v>
       </c>
       <c r="AD88" s="9" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AE88" s="10">
         <v>3162666000</v>
@@ -10920,13 +10923,13 @@
         <v>211</v>
       </c>
       <c r="AK88" s="9" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL88" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AM88" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN88" s="9" t="s">
         <v>35</v>
@@ -10941,18 +10944,18 @@
         <v>2</v>
       </c>
       <c r="AR88" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AS88" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AT88" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="89" spans="1:46">
       <c r="A89" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B89" s="8">
         <v>43626</v>
@@ -10967,19 +10970,19 @@
         <v>40</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I89" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J89" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K89" s="10">
         <v>15700000000</v>
@@ -11015,7 +11018,7 @@
         <v>33</v>
       </c>
       <c r="AD89" s="9" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AE89" s="10">
         <v>1159000000</v>
@@ -11030,13 +11033,13 @@
         <v>13.54616048317515</v>
       </c>
       <c r="AK89" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AL89" s="9" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AM89" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN89" s="9" t="s">
         <v>35</v>
@@ -11051,18 +11054,18 @@
         <v>2</v>
       </c>
       <c r="AR89" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AS89" s="9" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AT89" s="9" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="90" spans="1:46">
       <c r="A90" s="9" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B90" s="8">
         <v>43401</v>
@@ -11077,19 +11080,19 @@
         <v>40</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H90" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I90" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J90" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K90" s="10">
         <v>34000000000</v>
@@ -11104,7 +11107,7 @@
         <v>1</v>
       </c>
       <c r="O90" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P90" s="9" t="s">
         <v>90</v>
@@ -11125,7 +11128,7 @@
         <v>33</v>
       </c>
       <c r="AD90" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AE90" s="10">
         <v>2920461000</v>
@@ -11140,13 +11143,13 @@
         <v>11.64199761612978</v>
       </c>
       <c r="AK90" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AL90" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM90" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN90" s="9" t="s">
         <v>35</v>
@@ -11161,18 +11164,18 @@
         <v>2</v>
       </c>
       <c r="AR90" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AS90" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AT90" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="91" spans="1:46">
       <c r="A91" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B91" s="8">
         <v>42534</v>
@@ -11187,19 +11190,19 @@
         <v>40</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="I91" s="9" t="s">
         <v>259</v>
       </c>
       <c r="J91" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K91" s="10">
         <v>26200000000</v>
@@ -11214,7 +11217,7 @@
         <v>1</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>90</v>
@@ -11235,7 +11238,7 @@
         <v>33</v>
       </c>
       <c r="AD91" s="9" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AE91" s="10">
         <v>2990911000</v>
@@ -11256,13 +11259,13 @@
         <v>102.9582822471628</v>
       </c>
       <c r="AK91" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AL91" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AM91" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN91" s="9" t="s">
         <v>35</v>
@@ -11277,13 +11280,13 @@
         <v>2</v>
       </c>
       <c r="AR91" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AS91" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AT91" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -11407,7 +11410,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11425,7 +11428,7 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11446,16 +11449,16 @@
         <v>48</v>
       </c>
       <c r="B6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C6" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D6" t="s">
         <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F6" t="s">
         <v>27</v>
@@ -11464,13 +11467,13 @@
         <v>73</v>
       </c>
       <c r="H6" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="J6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="K6" t="s">
         <v>74</v>
@@ -11479,18 +11482,18 @@
         <v>80</v>
       </c>
       <c r="M6" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N6" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="42" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C7" s="8">
         <v>45190</v>
@@ -11508,21 +11511,21 @@
         <v>3653708000</v>
       </c>
       <c r="L7" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="M7" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="M7" s="13" t="s">
-        <v>394</v>
-      </c>
       <c r="N7" s="13" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C8" s="8">
         <v>44707</v>
@@ -11552,21 +11555,21 @@
         <v>2966000000</v>
       </c>
       <c r="L8" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="M8" s="13" t="s">
         <v>407</v>
       </c>
-      <c r="M8" s="13" t="s">
-        <v>406</v>
-      </c>
       <c r="N8" s="13" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="42" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C9" s="8">
         <v>44640</v>
@@ -11584,21 +11587,21 @@
         <v>592200000</v>
       </c>
       <c r="L9" s="13" t="s">
+        <v>417</v>
+      </c>
+      <c r="M9" s="13" t="s">
         <v>416</v>
       </c>
-      <c r="M9" s="13" t="s">
-        <v>415</v>
-      </c>
       <c r="N9" s="13" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="42" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C10" s="8">
         <v>44592</v>
@@ -11616,21 +11619,21 @@
         <v>3217170000</v>
       </c>
       <c r="L10" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="M10" s="13" t="s">
         <v>426</v>
       </c>
-      <c r="M10" s="13" t="s">
-        <v>425</v>
-      </c>
       <c r="N10" s="13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="42" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C11" s="8">
         <v>44579</v>
@@ -11651,21 +11654,21 @@
         <v>2734000000</v>
       </c>
       <c r="L11" s="13" t="s">
+        <v>437</v>
+      </c>
+      <c r="M11" s="13" t="s">
         <v>436</v>
       </c>
-      <c r="M11" s="13" t="s">
-        <v>435</v>
-      </c>
       <c r="N11" s="13" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="42" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C12" s="8">
         <v>44166</v>
@@ -11683,21 +11686,21 @@
         <v>630422000</v>
       </c>
       <c r="L12" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="M12" s="13" t="s">
         <v>445</v>
       </c>
-      <c r="M12" s="13" t="s">
-        <v>444</v>
-      </c>
       <c r="N12" s="13" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="42" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C13" s="8">
         <v>44131</v>
@@ -11715,21 +11718,21 @@
         <v>3162666000</v>
       </c>
       <c r="L13" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="M13" s="13" t="s">
         <v>454</v>
       </c>
-      <c r="M13" s="13" t="s">
-        <v>453</v>
-      </c>
       <c r="N13" s="13" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="42" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C14" s="8">
         <v>43626</v>
@@ -11747,21 +11750,21 @@
         <v>1159000000</v>
       </c>
       <c r="L14" s="13" t="s">
+        <v>463</v>
+      </c>
+      <c r="M14" s="13" t="s">
         <v>462</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>461</v>
-      </c>
       <c r="N14" s="13" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="42" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C15" s="8">
         <v>43401</v>
@@ -11782,21 +11785,21 @@
         <v>472442000</v>
       </c>
       <c r="L15" s="13" t="s">
+        <v>471</v>
+      </c>
+      <c r="M15" s="13" t="s">
         <v>470</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>469</v>
-      </c>
       <c r="N15" s="13" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="42" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C16" s="8">
         <v>42534</v>
@@ -11820,13 +11823,13 @@
         <v>254472000</v>
       </c>
       <c r="L16" s="13" t="s">
+        <v>479</v>
+      </c>
+      <c r="M16" s="13" t="s">
         <v>478</v>
       </c>
-      <c r="M16" s="13" t="s">
-        <v>477</v>
-      </c>
       <c r="N16" s="13" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -11874,7 +11877,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11893,7 +11896,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11918,13 +11921,13 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D6" t="s">
         <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F6" t="s">
         <v>73</v>
@@ -11939,7 +11942,7 @@
         <v>28</v>
       </c>
       <c r="J6" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K6" t="s">
         <v>77</v>
@@ -11948,13 +11951,13 @@
         <v>78</v>
       </c>
       <c r="M6" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N6" t="s">
         <v>79</v>
       </c>
       <c r="O6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -11977,7 +11980,7 @@
         <v>94</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K7" s="12">
         <f>IFERROR(IF(AND(D7&gt;0,F7&gt;0,E7=H7),D7/F7,""),"")</f>
@@ -12018,7 +12021,7 @@
         <v>157</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K8" s="12">
         <f>IFERROR(IF(AND(D8&gt;0,F8&gt;0,E8=H8),D8/F8,""),"")</f>
@@ -12059,7 +12062,7 @@
         <v>157</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K9" s="12">
         <f>IFERROR(IF(AND(D9&gt;0,F9&gt;0,E9=H9),D9/F9,""),"")</f>
@@ -12100,7 +12103,7 @@
         <v>157</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K10" s="12">
         <f>IFERROR(IF(AND(D10&gt;0,F10&gt;0,E10=H10),D10/F10,""),"")</f>
@@ -12123,13 +12126,13 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B11" s="8">
         <v>46177</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>90</v>
@@ -12141,7 +12144,7 @@
         <v>94</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K11" s="12">
         <f>IFERROR(IF(AND(D11&gt;0,F11&gt;0,E11=H11),D11/F11,""),"")</f>
@@ -12164,7 +12167,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B12" s="8">
         <v>46175</v>
@@ -12182,7 +12185,7 @@
         <v>35</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K12" s="12">
         <f>IFERROR(IF(AND(D12&gt;0,F12&gt;0,E12=H12),D12/F12,""),"")</f>
@@ -12205,13 +12208,13 @@
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B13" s="8">
         <v>46170</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>90</v>
@@ -12223,7 +12226,7 @@
         <v>94</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K13" s="12">
         <f>IFERROR(IF(AND(D13&gt;0,F13&gt;0,E13=H13),D13/F13,""),"")</f>
@@ -12246,7 +12249,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B14" s="8">
         <v>46167</v>
@@ -12264,7 +12267,7 @@
         <v>157</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K14" s="12">
         <f>IFERROR(IF(AND(D14&gt;0,F14&gt;0,E14=H14),D14/F14,""),"")</f>
@@ -12287,7 +12290,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B15" s="8">
         <v>46157</v>
@@ -12305,7 +12308,7 @@
         <v>157</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K15" s="12">
         <f>IFERROR(IF(AND(D15&gt;0,F15&gt;0,E15=H15),D15/F15,""),"")</f>
@@ -12328,7 +12331,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B16" s="8">
         <v>46139</v>
@@ -12346,7 +12349,7 @@
         <v>157</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K16" s="12">
         <f>IFERROR(IF(AND(D16&gt;0,F16&gt;0,E16=H16),D16/F16,""),"")</f>
@@ -12369,7 +12372,7 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B17" s="8">
         <v>46139</v>
@@ -12387,7 +12390,7 @@
         <v>157</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K17" s="12">
         <f>IFERROR(IF(AND(D17&gt;0,F17&gt;0,E17=H17),D17/F17,""),"")</f>
@@ -12410,7 +12413,7 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B18" s="8">
         <v>46139</v>
@@ -12428,7 +12431,7 @@
         <v>157</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K18" s="12">
         <f>IFERROR(IF(AND(D18&gt;0,F18&gt;0,E18=H18),D18/F18,""),"")</f>
@@ -12451,7 +12454,7 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B19" s="8">
         <v>46139</v>
@@ -12469,7 +12472,7 @@
         <v>157</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K19" s="12">
         <f>IFERROR(IF(AND(D19&gt;0,F19&gt;0,E19=H19),D19/F19,""),"")</f>
@@ -12492,7 +12495,7 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B20" s="8">
         <v>46139</v>
@@ -12510,7 +12513,7 @@
         <v>157</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K20" s="12">
         <f>IFERROR(IF(AND(D20&gt;0,F20&gt;0,E20=H20),D20/F20,""),"")</f>
@@ -12533,13 +12536,13 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B21" s="8">
         <v>46128</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>34</v>
@@ -12551,7 +12554,7 @@
         <v>94</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K21" s="12">
         <f>IFERROR(IF(AND(D21&gt;0,F21&gt;0,E21=H21),D21/F21,""),"")</f>
@@ -12574,7 +12577,7 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B22" s="8">
         <v>45642</v>
@@ -12592,7 +12595,7 @@
         <v>94</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K22" s="12">
         <f>IFERROR(IF(AND(D22&gt;0,F22&gt;0,E22=H22),D22/F22,""),"")</f>
@@ -12615,13 +12618,13 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B23" s="8">
         <v>45288</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>90</v>
@@ -12633,7 +12636,7 @@
         <v>94</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K23" s="12">
         <f>IFERROR(IF(AND(D23&gt;0,F23&gt;0,E23=H23),D23/F23,""),"")</f>
@@ -12656,13 +12659,13 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B24" s="8">
         <v>45190</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>211</v>
@@ -12677,7 +12680,7 @@
         <v>35</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K24" s="12">
         <f>IFERROR(IF(AND(D24&gt;0,F24&gt;0,E24=H24),D24/F24,""),"")</f>
@@ -12692,21 +12695,21 @@
         <v>NO</v>
       </c>
       <c r="N24" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O24" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B25" s="8">
         <v>44707</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D25" s="10">
         <v>69000000000</v>
@@ -12727,7 +12730,7 @@
         <v>35</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K25" s="12">
         <f>IFERROR(IF(AND(D25&gt;0,F25&gt;0,E25=H25),D25/F25,""),"")</f>
@@ -12742,21 +12745,21 @@
         <v>YES</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B26" s="8">
         <v>44640</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>211</v>
@@ -12771,7 +12774,7 @@
         <v>35</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K26" s="12">
         <f>IFERROR(IF(AND(D26&gt;0,F26&gt;0,E26=H26),D26/F26,""),"")</f>
@@ -12786,21 +12789,21 @@
         <v>NO</v>
       </c>
       <c r="N26" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="O26" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B27" s="8">
         <v>44592</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D27" s="10">
         <v>16500000000</v>
@@ -12818,7 +12821,7 @@
         <v>35</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K27" s="12">
         <f>IFERROR(IF(AND(D27&gt;0,F27&gt;0,E27=H27),D27/F27,""),"")</f>
@@ -12833,21 +12836,21 @@
         <v>NO</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B28" s="8">
         <v>44579</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D28" s="10">
         <v>68700000000</v>
@@ -12865,7 +12868,7 @@
         <v>35</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K28" s="12">
         <f>IFERROR(IF(AND(D28&gt;0,F28&gt;0,E28=H28),D28/F28,""),"")</f>
@@ -12880,21 +12883,21 @@
         <v>YES</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O28" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B29" s="8">
         <v>44166</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D29" s="10">
         <v>27700000000</v>
@@ -12912,7 +12915,7 @@
         <v>35</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K29" s="12">
         <f>IFERROR(IF(AND(D29&gt;0,F29&gt;0,E29=H29),D29/F29,""),"")</f>
@@ -12927,21 +12930,21 @@
         <v>YES</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B30" s="8">
         <v>44131</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>211</v>
@@ -12956,7 +12959,7 @@
         <v>35</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K30" s="12">
         <f>IFERROR(IF(AND(D30&gt;0,F30&gt;0,E30=H30),D30/F30,""),"")</f>
@@ -12971,21 +12974,21 @@
         <v>NO</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O30" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B31" s="8">
         <v>43626</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D31" s="10">
         <v>15700000000</v>
@@ -13003,7 +13006,7 @@
         <v>35</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K31" s="12">
         <f>IFERROR(IF(AND(D31&gt;0,F31&gt;0,E31=H31),D31/F31,""),"")</f>
@@ -13018,21 +13021,21 @@
         <v>YES</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="9" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B32" s="8">
         <v>43401</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D32" s="10">
         <v>34000000000</v>
@@ -13050,7 +13053,7 @@
         <v>35</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K32" s="12">
         <f>IFERROR(IF(AND(D32&gt;0,F32&gt;0,E32=H32),D32/F32,""),"")</f>
@@ -13065,21 +13068,21 @@
         <v>YES</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O32" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B33" s="8">
         <v>42534</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D33" s="10">
         <v>26200000000</v>
@@ -13100,7 +13103,7 @@
         <v>35</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="K33" s="12">
         <f>IFERROR(IF(AND(D33&gt;0,F33&gt;0,E33=H33),D33/F33,""),"")</f>
@@ -13115,10 +13118,10 @@
         <v>YES</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
@@ -13153,7 +13156,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13173,7 +13176,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -13193,7 +13196,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="K4" s="3" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -13212,7 +13215,7 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E6" t="s">
         <v>22</v>
@@ -13221,28 +13224,28 @@
         <v>83</v>
       </c>
       <c r="G6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H6" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="I6" t="s">
         <v>30</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P6" s="4" t="s">
         <v>23</v>
@@ -13262,7 +13265,7 @@
         <v>96</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>95</v>
@@ -13277,7 +13280,7 @@
         <v>98</v>
       </c>
       <c r="K7" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -13309,7 +13312,7 @@
         <v>96</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>95</v>
@@ -13324,7 +13327,7 @@
         <v>102</v>
       </c>
       <c r="K8" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -13356,7 +13359,7 @@
         <v>96</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>95</v>
@@ -13371,7 +13374,7 @@
         <v>105</v>
       </c>
       <c r="K9" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -13403,7 +13406,7 @@
         <v>111</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>110</v>
@@ -13416,7 +13419,7 @@
         <v>113</v>
       </c>
       <c r="K10" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -13448,20 +13451,20 @@
         <v>187</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K11" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -13490,23 +13493,23 @@
         <v>90</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K12" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -13538,20 +13541,20 @@
         <v>187</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K13" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -13580,23 +13583,23 @@
         <v>90</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="13" t="s">
         <v>113</v>
       </c>
       <c r="K14" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L14">
         <v>6</v>
@@ -13628,7 +13631,7 @@
         <v>96</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>95</v>
@@ -13657,7 +13660,7 @@
         <v>96</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>95</v>
@@ -13672,7 +13675,7 @@
         <v>121</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -13696,7 +13699,7 @@
         <v>96</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>95</v>
@@ -13725,7 +13728,7 @@
         <v>96</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>95</v>
@@ -13754,7 +13757,7 @@
         <v>96</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>95</v>
@@ -13783,7 +13786,7 @@
         <v>96</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>95</v>
@@ -13812,7 +13815,7 @@
         <v>96</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>95</v>
@@ -13841,7 +13844,7 @@
         <v>96</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>95</v>
@@ -13870,7 +13873,7 @@
         <v>96</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>95</v>
@@ -13899,7 +13902,7 @@
         <v>96</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>95</v>
@@ -13928,7 +13931,7 @@
         <v>96</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>95</v>
@@ -13957,7 +13960,7 @@
         <v>158</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>110</v>
@@ -13981,16 +13984,16 @@
         <v>90</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="13" t="s">
@@ -14008,16 +14011,16 @@
         <v>90</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="13" t="s">
@@ -14035,16 +14038,16 @@
         <v>90</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="13" t="s">
@@ -14065,7 +14068,7 @@
         <v>162</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>110</v>
@@ -14094,13 +14097,13 @@
         <v>162</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="13" t="s">
@@ -14121,7 +14124,7 @@
         <v>96</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>95</v>
@@ -14150,7 +14153,7 @@
         <v>96</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>95</v>
@@ -14179,7 +14182,7 @@
         <v>96</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>95</v>
@@ -14208,7 +14211,7 @@
         <v>96</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>95</v>
@@ -14237,7 +14240,7 @@
         <v>182</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>110</v>
@@ -14264,7 +14267,7 @@
         <v>187</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>110</v>
@@ -14293,13 +14296,13 @@
         <v>187</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H38" s="9"/>
       <c r="I38" s="13" t="s">
@@ -14320,7 +14323,7 @@
         <v>96</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>95</v>
@@ -14349,7 +14352,7 @@
         <v>96</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>95</v>
@@ -14378,7 +14381,7 @@
         <v>96</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>95</v>
@@ -14407,7 +14410,7 @@
         <v>96</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>95</v>
@@ -14436,7 +14439,7 @@
         <v>96</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>95</v>
@@ -14465,7 +14468,7 @@
         <v>212</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>110</v>
@@ -14494,13 +14497,13 @@
         <v>212</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="13" t="s">
@@ -14521,7 +14524,7 @@
         <v>162</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>110</v>
@@ -14550,13 +14553,13 @@
         <v>162</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="13" t="s">
@@ -14577,7 +14580,7 @@
         <v>222</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>95</v>
@@ -14606,7 +14609,7 @@
         <v>212</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>110</v>
@@ -14635,13 +14638,13 @@
         <v>212</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H50" s="9"/>
       <c r="I50" s="13" t="s">
@@ -14662,7 +14665,7 @@
         <v>230</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>110</v>
@@ -14691,7 +14694,7 @@
         <v>96</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>95</v>
@@ -14720,7 +14723,7 @@
         <v>96</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>95</v>
@@ -14749,7 +14752,7 @@
         <v>96</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>95</v>
@@ -14778,7 +14781,7 @@
         <v>96</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>95</v>
@@ -14807,7 +14810,7 @@
         <v>96</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>95</v>
@@ -14836,7 +14839,7 @@
         <v>96</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>95</v>
@@ -14865,7 +14868,7 @@
         <v>96</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>95</v>
@@ -14894,7 +14897,7 @@
         <v>255</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>110</v>
@@ -14920,16 +14923,16 @@
         <v>38</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H60" s="8">
         <v>46192</v>
@@ -14952,13 +14955,13 @@
         <v>162</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H61" s="8">
         <v>46181</v>
@@ -14978,16 +14981,16 @@
         <v>38</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H62" s="8">
         <v>46177</v>
@@ -15010,13 +15013,13 @@
         <v>162</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H63" s="9"/>
       <c r="I63" s="13" t="s">
@@ -15034,16 +15037,16 @@
         <v>38</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H64" s="9"/>
       <c r="I64" s="13" t="s">
@@ -15052,374 +15055,374 @@
     </row>
     <row r="65" spans="1:9" ht="28" customHeight="1">
       <c r="A65" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B65" s="8">
         <v>46183</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H65" s="8">
         <v>46183</v>
       </c>
       <c r="I65" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="28" customHeight="1">
       <c r="A66" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B66" s="8">
         <v>46177</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D66" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H66" s="8">
         <v>46177</v>
       </c>
       <c r="I66" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="28" customHeight="1">
       <c r="A67" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B67" s="8">
         <v>46177</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H67" s="8">
         <v>46171</v>
       </c>
       <c r="I67" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="28" customHeight="1">
       <c r="A68" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B68" s="8">
         <v>46177</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H68" s="8">
         <v>46170</v>
       </c>
       <c r="I68" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="28" customHeight="1">
       <c r="A69" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B69" s="8">
         <v>46177</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H69" s="8">
         <v>46170</v>
       </c>
       <c r="I69" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="28" customHeight="1">
       <c r="A70" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B70" s="8">
         <v>46177</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D70" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H70" s="8">
         <v>46170</v>
       </c>
       <c r="I70" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="28" customHeight="1">
       <c r="A71" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B71" s="8">
         <v>46177</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D71" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H71" s="8">
         <v>46170</v>
       </c>
       <c r="I71" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="28" customHeight="1">
       <c r="A72" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B72" s="8">
         <v>46177</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H72" s="8">
         <v>46170</v>
       </c>
       <c r="I72" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="28" customHeight="1">
       <c r="A73" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B73" s="8">
         <v>46177</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H73" s="9"/>
       <c r="I73" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="28" customHeight="1">
       <c r="A74" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B74" s="8">
         <v>46177</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D74" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H74" s="9"/>
       <c r="I74" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="28" customHeight="1">
       <c r="A75" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B75" s="8">
         <v>46177</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D75" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H75" s="9"/>
       <c r="I75" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="28" customHeight="1">
       <c r="A76" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B76" s="8">
         <v>46177</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D76" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H76" s="9"/>
       <c r="I76" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="28" customHeight="1">
       <c r="A77" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B77" s="8">
         <v>46177</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H77" s="9"/>
       <c r="I77" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="28" customHeight="1">
       <c r="A78" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B78" s="8">
         <v>46175</v>
@@ -15428,16 +15431,16 @@
         <v>41</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H78" s="8">
         <v>46175</v>
@@ -15448,7 +15451,7 @@
     </row>
     <row r="79" spans="1:9" ht="28" customHeight="1">
       <c r="A79" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B79" s="8">
         <v>46175</v>
@@ -15460,13 +15463,13 @@
         <v>187</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H79" s="8">
         <v>46176</v>
@@ -15477,7 +15480,7 @@
     </row>
     <row r="80" spans="1:9" ht="28" customHeight="1">
       <c r="A80" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B80" s="8">
         <v>46175</v>
@@ -15489,13 +15492,13 @@
         <v>162</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H80" s="8">
         <v>46175</v>
@@ -15506,7 +15509,7 @@
     </row>
     <row r="81" spans="1:9" ht="28" customHeight="1">
       <c r="A81" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B81" s="8">
         <v>46175</v>
@@ -15518,13 +15521,13 @@
         <v>187</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H81" s="9"/>
       <c r="I81" s="13" t="s">
@@ -15533,7 +15536,7 @@
     </row>
     <row r="82" spans="1:9" ht="28" customHeight="1">
       <c r="A82" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B82" s="8">
         <v>46175</v>
@@ -15545,13 +15548,13 @@
         <v>162</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H82" s="9"/>
       <c r="I82" s="13" t="s">
@@ -15560,63 +15563,63 @@
     </row>
     <row r="83" spans="1:9" ht="28" customHeight="1">
       <c r="A83" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B83" s="8">
         <v>46170</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D83" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H83" s="8">
         <v>46170</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="28" customHeight="1">
       <c r="A84" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B84" s="8">
         <v>46170</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H84" s="9"/>
       <c r="I84" s="13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="85" spans="1:9" ht="28" customHeight="1">
       <c r="A85" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B85" s="8">
         <v>46167</v>
@@ -15628,24 +15631,24 @@
         <v>162</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H85" s="8">
         <v>46167</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="28" customHeight="1">
       <c r="A86" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B86" s="8">
         <v>46167</v>
@@ -15657,134 +15660,134 @@
         <v>162</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H86" s="9"/>
       <c r="I86" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="28" customHeight="1">
       <c r="A87" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B87" s="8">
         <v>46162</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H87" s="8">
         <v>46162</v>
       </c>
       <c r="I87" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="28" customHeight="1">
       <c r="A88" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B88" s="8">
         <v>46162</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D88" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H88" s="9"/>
       <c r="I88" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="89" spans="1:9" ht="28" customHeight="1">
       <c r="A89" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B89" s="8">
         <v>46157</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H89" s="8">
         <v>46157</v>
       </c>
       <c r="I89" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="90" spans="1:9" ht="28" customHeight="1">
       <c r="A90" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B90" s="8">
         <v>46157</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D90" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H90" s="9"/>
       <c r="I90" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="91" spans="1:9" ht="28" customHeight="1">
       <c r="A91" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B91" s="8">
         <v>46157</v>
@@ -15793,56 +15796,56 @@
         <v>90</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H91" s="8">
         <v>46157</v>
       </c>
       <c r="I91" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="28" customHeight="1">
       <c r="A92" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B92" s="8">
         <v>46150</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H92" s="8">
         <v>46150</v>
       </c>
       <c r="I92" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="93" spans="1:9" ht="28" customHeight="1">
       <c r="A93" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B93" s="8">
         <v>46147</v>
@@ -15854,24 +15857,24 @@
         <v>187</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H93" s="8">
         <v>46147</v>
       </c>
       <c r="I93" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="28" customHeight="1">
       <c r="A94" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B94" s="8">
         <v>46147</v>
@@ -15883,22 +15886,22 @@
         <v>187</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H94" s="9"/>
       <c r="I94" s="13" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="28" customHeight="1">
       <c r="A95" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B95" s="8">
         <v>46146</v>
@@ -15907,27 +15910,27 @@
         <v>38</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H95" s="8">
         <v>46146</v>
       </c>
       <c r="I95" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="28" customHeight="1">
       <c r="A96" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B96" s="8">
         <v>46146</v>
@@ -15936,25 +15939,25 @@
         <v>38</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H96" s="9"/>
       <c r="I96" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="28" customHeight="1">
       <c r="A97" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B97" s="8">
         <v>46139</v>
@@ -15963,27 +15966,27 @@
         <v>90</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H97" s="8">
         <v>46139</v>
       </c>
       <c r="I97" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="98" spans="1:9" ht="28" customHeight="1">
       <c r="A98" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B98" s="8">
         <v>46139</v>
@@ -15992,25 +15995,25 @@
         <v>90</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H98" s="9"/>
       <c r="I98" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="99" spans="1:9" ht="28" customHeight="1">
       <c r="A99" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B99" s="8">
         <v>46139</v>
@@ -16022,24 +16025,24 @@
         <v>187</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H99" s="8">
         <v>46139</v>
       </c>
       <c r="I99" s="13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="100" spans="1:9" ht="28" customHeight="1">
       <c r="A100" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B100" s="8">
         <v>46139</v>
@@ -16051,22 +16054,22 @@
         <v>187</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H100" s="9"/>
       <c r="I100" s="13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="28" customHeight="1">
       <c r="A101" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B101" s="8">
         <v>46139</v>
@@ -16075,27 +16078,27 @@
         <v>90</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H101" s="8">
         <v>46139</v>
       </c>
       <c r="I101" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="28" customHeight="1">
       <c r="A102" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B102" s="8">
         <v>46139</v>
@@ -16104,27 +16107,27 @@
         <v>90</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H102" s="8">
         <v>46139</v>
       </c>
       <c r="I102" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="103" spans="1:9" ht="28" customHeight="1">
       <c r="A103" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B103" s="8">
         <v>46139</v>
@@ -16133,25 +16136,25 @@
         <v>90</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H103" s="9"/>
       <c r="I103" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="104" spans="1:9" ht="28" customHeight="1">
       <c r="A104" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B104" s="8">
         <v>46139</v>
@@ -16160,25 +16163,25 @@
         <v>90</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H104" s="9"/>
       <c r="I104" s="13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="105" spans="1:9" ht="28" customHeight="1">
       <c r="A105" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B105" s="8">
         <v>46139</v>
@@ -16187,27 +16190,27 @@
         <v>90</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H105" s="8">
         <v>46139</v>
       </c>
       <c r="I105" s="13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="28" customHeight="1">
       <c r="A106" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B106" s="8">
         <v>46139</v>
@@ -16216,25 +16219,25 @@
         <v>90</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H106" s="9"/>
       <c r="I106" s="13" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="28" customHeight="1">
       <c r="A107" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B107" s="8">
         <v>46139</v>
@@ -16243,27 +16246,27 @@
         <v>90</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H107" s="8">
         <v>46139</v>
       </c>
       <c r="I107" s="13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="28" customHeight="1">
       <c r="A108" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B108" s="8">
         <v>46139</v>
@@ -16272,81 +16275,81 @@
         <v>90</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H108" s="9"/>
       <c r="I108" s="13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="28" customHeight="1">
       <c r="A109" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B109" s="8">
         <v>46132</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H109" s="8">
         <v>46132</v>
       </c>
       <c r="I109" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="28" customHeight="1">
       <c r="A110" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B110" s="8">
         <v>46132</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D110" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H110" s="9"/>
       <c r="I110" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="28" customHeight="1">
       <c r="A111" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B111" s="8">
         <v>46132</v>
@@ -16355,27 +16358,27 @@
         <v>38</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H111" s="8">
         <v>46132</v>
       </c>
       <c r="I111" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="28" customHeight="1">
       <c r="A112" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B112" s="8">
         <v>46132</v>
@@ -16384,25 +16387,25 @@
         <v>38</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H112" s="9"/>
       <c r="I112" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="28" customHeight="1">
       <c r="A113" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B113" s="8">
         <v>46132</v>
@@ -16411,27 +16414,27 @@
         <v>38</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H113" s="8">
         <v>46132</v>
       </c>
       <c r="I113" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="28" customHeight="1">
       <c r="A114" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B114" s="8">
         <v>46132</v>
@@ -16440,475 +16443,475 @@
         <v>38</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H114" s="9"/>
       <c r="I114" s="13" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="28" customHeight="1">
       <c r="A115" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B115" s="8">
         <v>46128</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H115" s="8">
         <v>46128</v>
       </c>
       <c r="I115" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="28" customHeight="1">
       <c r="A116" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B116" s="8">
         <v>46128</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H116" s="8">
         <v>46128</v>
       </c>
       <c r="I116" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="28" customHeight="1">
       <c r="A117" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B117" s="8">
         <v>46128</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H117" s="8">
         <v>46128</v>
       </c>
       <c r="I117" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="28" customHeight="1">
       <c r="A118" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B118" s="8">
         <v>46128</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H118" s="9"/>
       <c r="I118" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="28" customHeight="1">
       <c r="A119" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B119" s="8">
         <v>46128</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H119" s="9"/>
       <c r="I119" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="28" customHeight="1">
       <c r="A120" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B120" s="8">
         <v>46128</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H120" s="9"/>
       <c r="I120" s="13" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="28" customHeight="1">
       <c r="A121" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B121" s="8">
         <v>46122</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D121" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H121" s="8">
         <v>46122</v>
       </c>
       <c r="I121" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="28" customHeight="1">
       <c r="A122" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B122" s="8">
         <v>46122</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D122" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H122" s="9"/>
       <c r="I122" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="28" customHeight="1">
       <c r="A123" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B123" s="8">
         <v>46122</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D123" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H123" s="8">
         <v>46122</v>
       </c>
       <c r="I123" s="13" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="28" customHeight="1">
       <c r="A124" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B124" s="8">
         <v>46122</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D124" s="9" t="s">
         <v>111</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H124" s="9"/>
       <c r="I124" s="13" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="28" customHeight="1">
       <c r="A125" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B125" s="8">
         <v>46115</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H125" s="8">
         <v>46115</v>
       </c>
       <c r="I125" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="28" customHeight="1">
       <c r="A126" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B126" s="8">
         <v>46115</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H126" s="9"/>
       <c r="I126" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="28" customHeight="1">
       <c r="A127" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B127" s="8">
         <v>46115</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D127" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H127" s="8">
         <v>46115</v>
       </c>
       <c r="I127" s="13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="28" customHeight="1">
       <c r="A128" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B128" s="8">
         <v>46115</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D128" s="9" t="s">
         <v>187</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H128" s="9"/>
       <c r="I128" s="13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="28" customHeight="1">
       <c r="A129" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B129" s="8">
         <v>46111</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H129" s="8">
         <v>46111</v>
       </c>
       <c r="I129" s="13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="28" customHeight="1">
       <c r="A130" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B130" s="8">
         <v>46111</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D130" s="9" t="s">
         <v>162</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H130" s="8">
         <v>46111</v>
       </c>
       <c r="I130" s="13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="28" customHeight="1">
       <c r="A131" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B131" s="8">
         <v>46080</v>
@@ -16917,16 +16920,16 @@
         <v>44</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H131" s="8">
         <v>46080</v>
@@ -16937,7 +16940,7 @@
     </row>
     <row r="132" spans="1:9" ht="28" customHeight="1">
       <c r="A132" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B132" s="8">
         <v>45729</v>
@@ -16946,27 +16949,27 @@
         <v>38</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H132" s="8">
         <v>45729</v>
       </c>
       <c r="I132" s="13" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="28" customHeight="1">
       <c r="A133" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B133" s="8">
         <v>45642</v>
@@ -16975,27 +16978,27 @@
         <v>90</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H133" s="8">
         <v>45642</v>
       </c>
       <c r="I133" s="13" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="28" customHeight="1">
       <c r="A134" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B134" s="8">
         <v>45611</v>
@@ -17004,27 +17007,27 @@
         <v>44</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H134" s="8">
         <v>45611</v>
       </c>
       <c r="I134" s="13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="28" customHeight="1">
       <c r="A135" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B135" s="8">
         <v>45391</v>
@@ -17033,27 +17036,27 @@
         <v>44</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H135" s="8">
         <v>45391</v>
       </c>
       <c r="I135" s="13" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="28" customHeight="1">
       <c r="A136" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B136" s="8">
         <v>45357</v>
@@ -17062,602 +17065,602 @@
         <v>44</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E136" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H136" s="8">
         <v>45357</v>
       </c>
       <c r="I136" s="13" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="28" customHeight="1">
       <c r="A137" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B137" s="8">
         <v>45288</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H137" s="8">
         <v>45288</v>
       </c>
       <c r="I137" s="13" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="28" customHeight="1">
       <c r="A138" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B138" s="8">
         <v>45190</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E138" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H138" s="8">
         <v>45190</v>
       </c>
       <c r="I138" s="13" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="28" customHeight="1">
       <c r="A139" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B139" s="8">
         <v>45190</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H139" s="8">
         <v>45008</v>
       </c>
       <c r="I139" s="13" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="28" customHeight="1">
       <c r="A140" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B140" s="8">
         <v>44707</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E140" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G140" s="9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H140" s="8">
         <v>44707</v>
       </c>
       <c r="I140" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="28" customHeight="1">
       <c r="A141" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B141" s="8">
         <v>44707</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H141" s="8">
         <v>44644</v>
       </c>
       <c r="I141" s="13" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="28" customHeight="1">
       <c r="A142" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B142" s="8">
         <v>44640</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G142" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H142" s="8">
         <v>44734</v>
       </c>
       <c r="I142" s="13" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="28" customHeight="1">
       <c r="A143" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B143" s="8">
         <v>44640</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H143" s="8">
         <v>44643</v>
       </c>
       <c r="I143" s="13" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="28" customHeight="1">
       <c r="A144" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B144" s="8">
         <v>44592</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E144" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G144" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H144" s="8">
         <v>44608</v>
       </c>
       <c r="I144" s="13" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="28" customHeight="1">
       <c r="A145" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B145" s="8">
         <v>44579</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H145" s="8">
         <v>44579</v>
       </c>
       <c r="I145" s="13" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="28" customHeight="1">
       <c r="A146" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B146" s="8">
         <v>44579</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E146" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G146" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H146" s="8">
         <v>44250</v>
       </c>
       <c r="I146" s="13" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="28" customHeight="1">
       <c r="A147" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B147" s="8">
         <v>44166</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H147" s="8">
         <v>44166</v>
       </c>
       <c r="I147" s="13" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="28" customHeight="1">
       <c r="A148" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B148" s="8">
         <v>44166</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E148" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G148" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H148" s="8">
         <v>43902</v>
       </c>
       <c r="I148" s="13" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="28" customHeight="1">
       <c r="A149" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B149" s="8">
         <v>44131</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H149" s="8">
         <v>44131</v>
       </c>
       <c r="I149" s="13" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="28" customHeight="1">
       <c r="A150" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B150" s="8">
         <v>44131</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E150" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G150" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H150" s="8">
         <v>43966</v>
       </c>
       <c r="I150" s="13" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="28" customHeight="1">
       <c r="A151" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B151" s="8">
         <v>43626</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H151" s="8">
         <v>43626</v>
       </c>
       <c r="I151" s="13" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="28" customHeight="1">
       <c r="A152" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B152" s="8">
         <v>43626</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E152" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G152" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H152" s="8">
         <v>43518</v>
       </c>
       <c r="I152" s="13" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="28" customHeight="1">
       <c r="A153" s="9" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B153" s="8">
         <v>43401</v>
       </c>
       <c r="C153" s="9" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H153" s="8">
         <v>43401</v>
       </c>
       <c r="I153" s="13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="28" customHeight="1">
       <c r="A154" s="9" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B154" s="8">
         <v>43401</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E154" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G154" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H154" s="8">
         <v>43215</v>
       </c>
       <c r="I154" s="13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="28" customHeight="1">
       <c r="A155" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B155" s="8">
         <v>42534</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H155" s="8">
         <v>42534</v>
       </c>
       <c r="I155" s="13" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="28" customHeight="1">
       <c r="A156" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B156" s="8">
         <v>42534</v>
       </c>
       <c r="C156" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D156" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E156" s="9" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>95</v>
       </c>
       <c r="G156" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H156" s="8">
         <v>42412</v>
       </c>
       <c r="I156" s="13" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-05 | Build d2f69d819e75 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-05 | Build 98d1ec625779 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -281,36 +281,48 @@
     <t>Primary URL</t>
   </si>
   <si>
+    <t>DL-moex-101768</t>
+  </si>
+  <si>
+    <t>technical_filing</t>
+  </si>
+  <si>
+    <t>Confirmed</t>
+  </si>
+  <si>
+    <t>Not disclosed</t>
+  </si>
+  <si>
+    <t>Not classified</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t>Bonds</t>
+  </si>
+  <si>
+    <t>N/M: EV and aligned-currency financials are required</t>
+  </si>
+  <si>
+    <t>review</t>
+  </si>
+  <si>
+    <t>confirmed</t>
+  </si>
+  <si>
+    <t>MOEX disclosure</t>
+  </si>
+  <si>
+    <t>https://www.moex.com/n101768</t>
+  </si>
+  <si>
+    <t>Операции РЕПО с ЦК / с КСУ и сделки купли-продажи облигаций с расчётами в Специализированной валюте</t>
+  </si>
+  <si>
     <t>DL-moex-101755</t>
   </si>
   <si>
-    <t>technical_filing</t>
-  </si>
-  <si>
-    <t>Confirmed</t>
-  </si>
-  <si>
-    <t>Not disclosed</t>
-  </si>
-  <si>
-    <t>Not classified</t>
-  </si>
-  <si>
-    <t>Bonds</t>
-  </si>
-  <si>
-    <t>N/M: EV and aligned-currency financials are required</t>
-  </si>
-  <si>
-    <t>review</t>
-  </si>
-  <si>
-    <t>confirmed</t>
-  </si>
-  <si>
-    <t>MOEX disclosure</t>
-  </si>
-  <si>
     <t>https://www.moex.com/n101755</t>
   </si>
   <si>
@@ -320,24 +332,12 @@
     <t>DL-moex-101762</t>
   </si>
   <si>
-    <t>Russia</t>
-  </si>
-  <si>
     <t>https://www.moex.com/n101762</t>
   </si>
   <si>
     <t>О признании программы биржевых облигаций несостоявшейся и аннулировании её регистрации</t>
   </si>
   <si>
-    <t>DL-moex-101768</t>
-  </si>
-  <si>
-    <t>https://www.moex.com/n101768</t>
-  </si>
-  <si>
-    <t>Операции РЕПО с ЦК / с КСУ и сделки купли-продажи облигаций с расчётами в Специализированной валюте</t>
-  </si>
-  <si>
     <t>DL-39d2ffe37344900d</t>
   </si>
   <si>
@@ -1046,7 +1046,7 @@
     <t>https://rb.ru/news/vk-prodal-25-akcij-tochka-banka-sdelku-ocenili-v-212-mlrd-vdvoe-vyshe-iznachalnoj-stoimosti-bumag/</t>
   </si>
   <si>
-    <t>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.ru</t>
+    <t>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.RU</t>
   </si>
   <si>
     <t>DL-4774de17c61c14e4</t>
@@ -3015,7 +3015,7 @@
         <v>91</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>90</v>
@@ -3027,7 +3027,7 @@
         <v>90</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R7" s="9" t="s">
         <v>90</v>
@@ -3057,33 +3057,33 @@
         <v>90</v>
       </c>
       <c r="AM7" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN7" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO7" s="9">
         <v>40</v>
       </c>
       <c r="AP7" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ7" s="9">
         <v>1</v>
       </c>
       <c r="AR7" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS7" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AT7" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:46">
       <c r="A8" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B8" s="8">
         <v>46206</v>
@@ -3110,7 +3110,7 @@
         <v>91</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="M8" s="9" t="s">
         <v>90</v>
@@ -3122,7 +3122,7 @@
         <v>90</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R8" s="9" t="s">
         <v>90</v>
@@ -3152,22 +3152,22 @@
         <v>90</v>
       </c>
       <c r="AM8" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN8" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO8" s="9">
         <v>40</v>
       </c>
       <c r="AP8" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ8" s="9">
         <v>1</v>
       </c>
       <c r="AR8" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS8" s="9" t="s">
         <v>101</v>
@@ -3205,7 +3205,7 @@
         <v>91</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>90</v>
@@ -3217,7 +3217,7 @@
         <v>90</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R9" s="9" t="s">
         <v>90</v>
@@ -3247,22 +3247,22 @@
         <v>90</v>
       </c>
       <c r="AM9" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN9" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO9" s="9">
         <v>40</v>
       </c>
       <c r="AP9" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ9" s="9">
         <v>1</v>
       </c>
       <c r="AR9" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS9" s="9" t="s">
         <v>104</v>
@@ -3342,10 +3342,10 @@
         <v>90</v>
       </c>
       <c r="AM10" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN10" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO10" s="9">
         <v>40</v>
@@ -3395,7 +3395,7 @@
         <v>91</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M11" s="9" t="s">
         <v>90</v>
@@ -3407,7 +3407,7 @@
         <v>90</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R11" s="9" t="s">
         <v>90</v>
@@ -3437,22 +3437,22 @@
         <v>90</v>
       </c>
       <c r="AM11" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN11" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO11" s="9">
         <v>40</v>
       </c>
       <c r="AP11" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ11" s="9">
         <v>1</v>
       </c>
       <c r="AR11" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS11" s="9" t="s">
         <v>116</v>
@@ -3490,7 +3490,7 @@
         <v>9</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K12" s="10">
         <v>9148870000</v>
@@ -3505,7 +3505,7 @@
         <v>90</v>
       </c>
       <c r="Q12" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R12" s="9" t="s">
         <v>119</v>
@@ -3538,22 +3538,22 @@
         <v>90</v>
       </c>
       <c r="AM12" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN12" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO12" s="9">
         <v>40</v>
       </c>
       <c r="AP12" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ12" s="9">
         <v>1</v>
       </c>
       <c r="AR12" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS12" s="9" t="s">
         <v>120</v>
@@ -3591,7 +3591,7 @@
         <v>91</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M13" s="9" t="s">
         <v>90</v>
@@ -3603,7 +3603,7 @@
         <v>90</v>
       </c>
       <c r="Q13" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R13" s="9" t="s">
         <v>123</v>
@@ -3633,22 +3633,22 @@
         <v>90</v>
       </c>
       <c r="AM13" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN13" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO13" s="9">
         <v>40</v>
       </c>
       <c r="AP13" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ13" s="9">
         <v>1</v>
       </c>
       <c r="AR13" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS13" s="9" t="s">
         <v>124</v>
@@ -3686,7 +3686,7 @@
         <v>91</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M14" s="9" t="s">
         <v>90</v>
@@ -3698,7 +3698,7 @@
         <v>90</v>
       </c>
       <c r="Q14" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R14" s="9" t="s">
         <v>90</v>
@@ -3728,22 +3728,22 @@
         <v>90</v>
       </c>
       <c r="AM14" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN14" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO14" s="9">
         <v>40</v>
       </c>
       <c r="AP14" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ14" s="9">
         <v>1</v>
       </c>
       <c r="AR14" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS14" s="9" t="s">
         <v>127</v>
@@ -3781,7 +3781,7 @@
         <v>91</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M15" s="9" t="s">
         <v>90</v>
@@ -3793,7 +3793,7 @@
         <v>90</v>
       </c>
       <c r="Q15" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R15" s="9" t="s">
         <v>90</v>
@@ -3823,22 +3823,22 @@
         <v>90</v>
       </c>
       <c r="AM15" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN15" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO15" s="9">
         <v>40</v>
       </c>
       <c r="AP15" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ15" s="9">
         <v>1</v>
       </c>
       <c r="AR15" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS15" s="9" t="s">
         <v>130</v>
@@ -3876,7 +3876,7 @@
         <v>91</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M16" s="9" t="s">
         <v>90</v>
@@ -3888,7 +3888,7 @@
         <v>90</v>
       </c>
       <c r="Q16" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R16" s="9" t="s">
         <v>90</v>
@@ -3918,22 +3918,22 @@
         <v>90</v>
       </c>
       <c r="AM16" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN16" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO16" s="9">
         <v>60</v>
       </c>
       <c r="AP16" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ16" s="9">
         <v>1</v>
       </c>
       <c r="AR16" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS16" s="9" t="s">
         <v>135</v>
@@ -3971,7 +3971,7 @@
         <v>9</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K17" s="10">
         <v>8821850000</v>
@@ -3986,7 +3986,7 @@
         <v>90</v>
       </c>
       <c r="Q17" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R17" s="9" t="s">
         <v>138</v>
@@ -4019,22 +4019,22 @@
         <v>90</v>
       </c>
       <c r="AM17" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN17" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO17" s="9">
         <v>40</v>
       </c>
       <c r="AP17" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ17" s="9">
         <v>1</v>
       </c>
       <c r="AR17" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS17" s="9" t="s">
         <v>139</v>
@@ -4072,7 +4072,7 @@
         <v>9</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M18" s="9" t="s">
         <v>90</v>
@@ -4084,7 +4084,7 @@
         <v>90</v>
       </c>
       <c r="Q18" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R18" s="9" t="s">
         <v>141</v>
@@ -4114,22 +4114,22 @@
         <v>90</v>
       </c>
       <c r="AM18" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN18" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO18" s="9">
         <v>40</v>
       </c>
       <c r="AP18" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ18" s="9">
         <v>1</v>
       </c>
       <c r="AR18" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS18" s="9" t="s">
         <v>142</v>
@@ -4167,7 +4167,7 @@
         <v>91</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M19" s="9" t="s">
         <v>90</v>
@@ -4179,7 +4179,7 @@
         <v>90</v>
       </c>
       <c r="Q19" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R19" s="9" t="s">
         <v>90</v>
@@ -4209,22 +4209,22 @@
         <v>90</v>
       </c>
       <c r="AM19" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN19" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO19" s="9">
         <v>40</v>
       </c>
       <c r="AP19" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ19" s="9">
         <v>1</v>
       </c>
       <c r="AR19" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS19" s="9" t="s">
         <v>145</v>
@@ -4262,7 +4262,7 @@
         <v>9</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M20" s="9" t="s">
         <v>90</v>
@@ -4274,7 +4274,7 @@
         <v>90</v>
       </c>
       <c r="Q20" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R20" s="9" t="s">
         <v>147</v>
@@ -4304,22 +4304,22 @@
         <v>90</v>
       </c>
       <c r="AM20" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN20" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO20" s="9">
         <v>40</v>
       </c>
       <c r="AP20" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ20" s="9">
         <v>1</v>
       </c>
       <c r="AR20" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS20" s="9" t="s">
         <v>149</v>
@@ -4357,7 +4357,7 @@
         <v>9</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M21" s="9" t="s">
         <v>90</v>
@@ -4369,7 +4369,7 @@
         <v>90</v>
       </c>
       <c r="Q21" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R21" s="9" t="s">
         <v>152</v>
@@ -4399,22 +4399,22 @@
         <v>90</v>
       </c>
       <c r="AM21" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN21" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO21" s="9">
         <v>40</v>
       </c>
       <c r="AP21" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ21" s="9">
         <v>1</v>
       </c>
       <c r="AR21" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS21" s="9" t="s">
         <v>154</v>
@@ -4452,7 +4452,7 @@
         <v>91</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K22" s="10">
         <v>300000000000</v>
@@ -4497,7 +4497,7 @@
         <v>90</v>
       </c>
       <c r="AM22" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN22" s="9" t="s">
         <v>157</v>
@@ -4592,7 +4592,7 @@
         <v>90</v>
       </c>
       <c r="AM23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN23" s="9" t="s">
         <v>157</v>
@@ -4645,7 +4645,7 @@
         <v>9</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M24" s="9" t="s">
         <v>90</v>
@@ -4657,7 +4657,7 @@
         <v>90</v>
       </c>
       <c r="Q24" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R24" s="9" t="s">
         <v>90</v>
@@ -4687,22 +4687,22 @@
         <v>90</v>
       </c>
       <c r="AM24" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN24" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO24" s="9">
         <v>40</v>
       </c>
       <c r="AP24" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ24" s="9">
         <v>1</v>
       </c>
       <c r="AR24" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS24" s="9" t="s">
         <v>166</v>
@@ -4740,7 +4740,7 @@
         <v>9</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M25" s="9" t="s">
         <v>90</v>
@@ -4752,7 +4752,7 @@
         <v>90</v>
       </c>
       <c r="Q25" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R25" s="9" t="s">
         <v>169</v>
@@ -4782,22 +4782,22 @@
         <v>90</v>
       </c>
       <c r="AM25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO25" s="9">
         <v>40</v>
       </c>
       <c r="AP25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ25" s="9">
         <v>1</v>
       </c>
       <c r="AR25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS25" s="9" t="s">
         <v>171</v>
@@ -4835,7 +4835,7 @@
         <v>9</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M26" s="9" t="s">
         <v>90</v>
@@ -4847,7 +4847,7 @@
         <v>90</v>
       </c>
       <c r="Q26" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R26" s="9" t="s">
         <v>174</v>
@@ -4877,22 +4877,22 @@
         <v>90</v>
       </c>
       <c r="AM26" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN26" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO26" s="9">
         <v>40</v>
       </c>
       <c r="AP26" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ26" s="9">
         <v>1</v>
       </c>
       <c r="AR26" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS26" s="9" t="s">
         <v>176</v>
@@ -4930,7 +4930,7 @@
         <v>9</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K27" s="10">
         <v>8520970000</v>
@@ -4945,7 +4945,7 @@
         <v>90</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R27" s="9" t="s">
         <v>179</v>
@@ -4978,22 +4978,22 @@
         <v>90</v>
       </c>
       <c r="AM27" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN27" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO27" s="9">
         <v>40</v>
       </c>
       <c r="AP27" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ27" s="9">
         <v>1</v>
       </c>
       <c r="AR27" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS27" s="9" t="s">
         <v>180</v>
@@ -5043,7 +5043,7 @@
         <v>90</v>
       </c>
       <c r="Q28" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R28" s="9" t="s">
         <v>90</v>
@@ -5073,10 +5073,10 @@
         <v>90</v>
       </c>
       <c r="AM28" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN28" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO28" s="9">
         <v>75</v>
@@ -5138,7 +5138,7 @@
         <v>90</v>
       </c>
       <c r="Q29" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R29" s="9" t="s">
         <v>90</v>
@@ -5168,10 +5168,10 @@
         <v>90</v>
       </c>
       <c r="AM29" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN29" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO29" s="9">
         <v>75</v>
@@ -5221,7 +5221,7 @@
         <v>9</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K30" s="10">
         <v>3930247000</v>
@@ -5236,7 +5236,7 @@
         <v>90</v>
       </c>
       <c r="Q30" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R30" s="9" t="s">
         <v>174</v>
@@ -5269,22 +5269,22 @@
         <v>90</v>
       </c>
       <c r="AM30" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN30" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO30" s="9">
         <v>40</v>
       </c>
       <c r="AP30" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ30" s="9">
         <v>1</v>
       </c>
       <c r="AR30" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS30" s="9" t="s">
         <v>191</v>
@@ -5322,7 +5322,7 @@
         <v>91</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M31" s="9" t="s">
         <v>90</v>
@@ -5334,7 +5334,7 @@
         <v>90</v>
       </c>
       <c r="Q31" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R31" s="9" t="s">
         <v>193</v>
@@ -5364,22 +5364,22 @@
         <v>90</v>
       </c>
       <c r="AM31" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN31" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO31" s="9">
         <v>40</v>
       </c>
       <c r="AP31" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ31" s="9">
         <v>1</v>
       </c>
       <c r="AR31" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS31" s="9" t="s">
         <v>194</v>
@@ -5417,7 +5417,7 @@
         <v>91</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M32" s="9" t="s">
         <v>90</v>
@@ -5429,7 +5429,7 @@
         <v>90</v>
       </c>
       <c r="Q32" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R32" s="9" t="s">
         <v>196</v>
@@ -5459,22 +5459,22 @@
         <v>90</v>
       </c>
       <c r="AM32" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN32" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO32" s="9">
         <v>40</v>
       </c>
       <c r="AP32" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ32" s="9">
         <v>1</v>
       </c>
       <c r="AR32" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS32" s="9" t="s">
         <v>197</v>
@@ -5512,7 +5512,7 @@
         <v>91</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M33" s="9" t="s">
         <v>90</v>
@@ -5524,7 +5524,7 @@
         <v>90</v>
       </c>
       <c r="Q33" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R33" s="9" t="s">
         <v>200</v>
@@ -5554,22 +5554,22 @@
         <v>90</v>
       </c>
       <c r="AM33" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN33" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO33" s="9">
         <v>60</v>
       </c>
       <c r="AP33" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ33" s="9">
         <v>1</v>
       </c>
       <c r="AR33" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS33" s="9" t="s">
         <v>202</v>
@@ -5619,7 +5619,7 @@
         <v>90</v>
       </c>
       <c r="Q34" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R34" s="9" t="s">
         <v>206</v>
@@ -5649,22 +5649,22 @@
         <v>90</v>
       </c>
       <c r="AM34" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN34" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO34" s="9">
         <v>60</v>
       </c>
       <c r="AP34" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ34" s="9">
         <v>1</v>
       </c>
       <c r="AR34" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS34" s="9" t="s">
         <v>207</v>
@@ -5717,7 +5717,7 @@
         <v>90</v>
       </c>
       <c r="Q35" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R35" s="9" t="s">
         <v>90</v>
@@ -5747,10 +5747,10 @@
         <v>90</v>
       </c>
       <c r="AM35" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN35" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO35" s="9">
         <v>75</v>
@@ -5845,7 +5845,7 @@
         <v>90</v>
       </c>
       <c r="AM36" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN36" s="9" t="s">
         <v>157</v>
@@ -5898,7 +5898,7 @@
         <v>91</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K37" s="10">
         <v>20000000000</v>
@@ -5913,7 +5913,7 @@
         <v>90</v>
       </c>
       <c r="Q37" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R37" s="9" t="s">
         <v>90</v>
@@ -5943,7 +5943,7 @@
         <v>90</v>
       </c>
       <c r="AM37" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN37" s="9" t="s">
         <v>35</v>
@@ -5952,7 +5952,7 @@
         <v>100</v>
       </c>
       <c r="AP37" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ37" s="9">
         <v>1</v>
@@ -6008,7 +6008,7 @@
         <v>90</v>
       </c>
       <c r="Q38" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R38" s="9" t="s">
         <v>90</v>
@@ -6038,7 +6038,7 @@
         <v>90</v>
       </c>
       <c r="AM38" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN38" s="9" t="s">
         <v>157</v>
@@ -6133,7 +6133,7 @@
         <v>90</v>
       </c>
       <c r="AM39" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN39" s="9" t="s">
         <v>157</v>
@@ -6186,7 +6186,7 @@
         <v>91</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M40" s="9" t="s">
         <v>90</v>
@@ -6198,7 +6198,7 @@
         <v>90</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R40" s="9" t="s">
         <v>90</v>
@@ -6228,22 +6228,22 @@
         <v>90</v>
       </c>
       <c r="AM40" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN40" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO40" s="9">
         <v>40</v>
       </c>
       <c r="AP40" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ40" s="9">
         <v>1</v>
       </c>
       <c r="AR40" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS40" s="9" t="s">
         <v>234</v>
@@ -6281,7 +6281,7 @@
         <v>91</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M41" s="9" t="s">
         <v>90</v>
@@ -6293,7 +6293,7 @@
         <v>90</v>
       </c>
       <c r="Q41" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R41" s="9" t="s">
         <v>90</v>
@@ -6323,22 +6323,22 @@
         <v>90</v>
       </c>
       <c r="AM41" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN41" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO41" s="9">
         <v>40</v>
       </c>
       <c r="AP41" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ41" s="9">
         <v>1</v>
       </c>
       <c r="AR41" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS41" s="9" t="s">
         <v>237</v>
@@ -6376,7 +6376,7 @@
         <v>91</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M42" s="9" t="s">
         <v>90</v>
@@ -6388,7 +6388,7 @@
         <v>90</v>
       </c>
       <c r="Q42" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R42" s="9" t="s">
         <v>90</v>
@@ -6418,22 +6418,22 @@
         <v>90</v>
       </c>
       <c r="AM42" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN42" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO42" s="9">
         <v>40</v>
       </c>
       <c r="AP42" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ42" s="9">
         <v>1</v>
       </c>
       <c r="AR42" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS42" s="9" t="s">
         <v>239</v>
@@ -6483,7 +6483,7 @@
         <v>90</v>
       </c>
       <c r="Q43" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R43" s="9" t="s">
         <v>90</v>
@@ -6513,22 +6513,22 @@
         <v>90</v>
       </c>
       <c r="AM43" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN43" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO43" s="9">
         <v>40</v>
       </c>
       <c r="AP43" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ43" s="9">
         <v>1</v>
       </c>
       <c r="AR43" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS43" s="9" t="s">
         <v>241</v>
@@ -6566,7 +6566,7 @@
         <v>9</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M44" s="9" t="s">
         <v>90</v>
@@ -6578,7 +6578,7 @@
         <v>90</v>
       </c>
       <c r="Q44" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R44" s="9" t="s">
         <v>90</v>
@@ -6608,22 +6608,22 @@
         <v>90</v>
       </c>
       <c r="AM44" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN44" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO44" s="9">
         <v>40</v>
       </c>
       <c r="AP44" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ44" s="9">
         <v>1</v>
       </c>
       <c r="AR44" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS44" s="9" t="s">
         <v>244</v>
@@ -6673,7 +6673,7 @@
         <v>90</v>
       </c>
       <c r="Q45" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R45" s="9" t="s">
         <v>90</v>
@@ -6703,22 +6703,22 @@
         <v>90</v>
       </c>
       <c r="AM45" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN45" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO45" s="9">
         <v>40</v>
       </c>
       <c r="AP45" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ45" s="9">
         <v>1</v>
       </c>
       <c r="AR45" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS45" s="9" t="s">
         <v>247</v>
@@ -6756,7 +6756,7 @@
         <v>91</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M46" s="9" t="s">
         <v>90</v>
@@ -6768,7 +6768,7 @@
         <v>90</v>
       </c>
       <c r="Q46" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R46" s="9" t="s">
         <v>90</v>
@@ -6798,22 +6798,22 @@
         <v>90</v>
       </c>
       <c r="AM46" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN46" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO46" s="9">
         <v>40</v>
       </c>
       <c r="AP46" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ46" s="9">
         <v>1</v>
       </c>
       <c r="AR46" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AS46" s="9" t="s">
         <v>250</v>
@@ -6851,7 +6851,7 @@
         <v>91</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K47" s="10">
         <v>5000000000</v>
@@ -6863,7 +6863,7 @@
         <v>33</v>
       </c>
       <c r="Q47" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R47" s="9" t="s">
         <v>90</v>
@@ -6890,10 +6890,10 @@
         <v>90</v>
       </c>
       <c r="AM47" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN47" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO47" s="9">
         <v>75</v>
@@ -6943,7 +6943,7 @@
         <v>259</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K48" s="10">
         <v>60000000000</v>
@@ -6958,7 +6958,7 @@
         <v>90</v>
       </c>
       <c r="Q48" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R48" s="9" t="s">
         <v>260</v>
@@ -6988,7 +6988,7 @@
         <v>90</v>
       </c>
       <c r="AM48" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN48" s="9" t="s">
         <v>35</v>
@@ -6997,7 +6997,7 @@
         <v>100</v>
       </c>
       <c r="AP48" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ48" s="9">
         <v>5</v>
@@ -7056,7 +7056,7 @@
         <v>90</v>
       </c>
       <c r="Q49" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R49" s="9" t="s">
         <v>90</v>
@@ -7086,10 +7086,10 @@
         <v>90</v>
       </c>
       <c r="AM49" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN49" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO49" s="9">
         <v>67</v>
@@ -7139,7 +7139,7 @@
         <v>91</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M50" s="9" t="s">
         <v>90</v>
@@ -7181,10 +7181,10 @@
         <v>90</v>
       </c>
       <c r="AM50" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN50" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO50" s="9">
         <v>65</v>
@@ -7234,7 +7234,7 @@
         <v>259</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K51" s="10">
         <v>35000000000</v>
@@ -7279,7 +7279,7 @@
         <v>90</v>
       </c>
       <c r="AM51" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN51" s="9" t="s">
         <v>35</v>
@@ -7288,7 +7288,7 @@
         <v>100</v>
       </c>
       <c r="AP51" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ51" s="9">
         <v>5</v>
@@ -7374,10 +7374,10 @@
         <v>90</v>
       </c>
       <c r="AM52" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN52" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO52" s="9">
         <v>67</v>
@@ -7469,7 +7469,7 @@
         <v>90</v>
       </c>
       <c r="AM53" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN53" s="9" t="s">
         <v>157</v>
@@ -7564,7 +7564,7 @@
         <v>90</v>
       </c>
       <c r="AM54" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN54" s="9" t="s">
         <v>157</v>
@@ -7659,7 +7659,7 @@
         <v>90</v>
       </c>
       <c r="AM55" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN55" s="9" t="s">
         <v>157</v>
@@ -7754,7 +7754,7 @@
         <v>90</v>
       </c>
       <c r="AM56" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN56" s="9" t="s">
         <v>157</v>
@@ -7807,7 +7807,7 @@
         <v>91</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K57" s="10">
         <v>1900000000</v>
@@ -7822,7 +7822,7 @@
         <v>90</v>
       </c>
       <c r="Q57" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R57" s="9" t="s">
         <v>90</v>
@@ -7852,7 +7852,7 @@
         <v>90</v>
       </c>
       <c r="AM57" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN57" s="9" t="s">
         <v>157</v>
@@ -7905,7 +7905,7 @@
         <v>91</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K58" s="10">
         <v>50000000000</v>
@@ -7950,7 +7950,7 @@
         <v>90</v>
       </c>
       <c r="AM58" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN58" s="9" t="s">
         <v>157</v>
@@ -8045,7 +8045,7 @@
         <v>90</v>
       </c>
       <c r="AM59" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN59" s="9" t="s">
         <v>157</v>
@@ -8140,7 +8140,7 @@
         <v>90</v>
       </c>
       <c r="AM60" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN60" s="9" t="s">
         <v>157</v>
@@ -8235,7 +8235,7 @@
         <v>90</v>
       </c>
       <c r="AM61" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN61" s="9" t="s">
         <v>157</v>
@@ -8288,7 +8288,7 @@
         <v>9</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M62" s="9" t="s">
         <v>90</v>
@@ -8330,7 +8330,7 @@
         <v>90</v>
       </c>
       <c r="AM62" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN62" s="9" t="s">
         <v>157</v>
@@ -8425,7 +8425,7 @@
         <v>90</v>
       </c>
       <c r="AM63" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN63" s="9" t="s">
         <v>157</v>
@@ -8520,7 +8520,7 @@
         <v>90</v>
       </c>
       <c r="AM64" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN64" s="9" t="s">
         <v>157</v>
@@ -8585,7 +8585,7 @@
         <v>90</v>
       </c>
       <c r="Q65" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R65" s="9" t="s">
         <v>90</v>
@@ -8615,7 +8615,7 @@
         <v>90</v>
       </c>
       <c r="AM65" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN65" s="9" t="s">
         <v>157</v>
@@ -8668,7 +8668,7 @@
         <v>91</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M66" s="9" t="s">
         <v>90</v>
@@ -8710,7 +8710,7 @@
         <v>90</v>
       </c>
       <c r="AM66" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN66" s="9" t="s">
         <v>157</v>
@@ -8805,7 +8805,7 @@
         <v>90</v>
       </c>
       <c r="AM67" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN67" s="9" t="s">
         <v>157</v>
@@ -8906,10 +8906,10 @@
         <v>90</v>
       </c>
       <c r="AM68" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN68" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO68" s="9">
         <v>60</v>
@@ -8971,7 +8971,7 @@
         <v>90</v>
       </c>
       <c r="Q69" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R69" s="9" t="s">
         <v>90</v>
@@ -9001,10 +9001,10 @@
         <v>90</v>
       </c>
       <c r="AM69" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN69" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO69" s="9">
         <v>75</v>
@@ -9096,7 +9096,7 @@
         <v>90</v>
       </c>
       <c r="AM70" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN70" s="9" t="s">
         <v>157</v>
@@ -9149,7 +9149,7 @@
         <v>91</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K71" s="10">
         <v>15000000000</v>
@@ -9164,7 +9164,7 @@
         <v>90</v>
       </c>
       <c r="Q71" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R71" s="9" t="s">
         <v>90</v>
@@ -9194,10 +9194,10 @@
         <v>90</v>
       </c>
       <c r="AM71" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN71" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO71" s="9">
         <v>75</v>
@@ -9259,7 +9259,7 @@
         <v>90</v>
       </c>
       <c r="Q72" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R72" s="9" t="s">
         <v>90</v>
@@ -9289,10 +9289,10 @@
         <v>90</v>
       </c>
       <c r="AM72" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN72" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO72" s="9">
         <v>75</v>
@@ -9342,7 +9342,7 @@
         <v>91</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K73" s="10">
         <v>10000000000</v>
@@ -9357,7 +9357,7 @@
         <v>90</v>
       </c>
       <c r="Q73" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R73" s="9" t="s">
         <v>90</v>
@@ -9387,10 +9387,10 @@
         <v>90</v>
       </c>
       <c r="AM73" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN73" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO73" s="9">
         <v>75</v>
@@ -9452,7 +9452,7 @@
         <v>90</v>
       </c>
       <c r="Q74" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R74" s="9" t="s">
         <v>90</v>
@@ -9482,10 +9482,10 @@
         <v>90</v>
       </c>
       <c r="AM74" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN74" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO74" s="9">
         <v>75</v>
@@ -9535,7 +9535,7 @@
         <v>91</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K75" s="10">
         <v>7000000000</v>
@@ -9550,7 +9550,7 @@
         <v>90</v>
       </c>
       <c r="Q75" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R75" s="9" t="s">
         <v>90</v>
@@ -9583,7 +9583,7 @@
         <v>90</v>
       </c>
       <c r="AM75" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN75" s="9" t="s">
         <v>35</v>
@@ -9592,7 +9592,7 @@
         <v>100</v>
       </c>
       <c r="AP75" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ75" s="9">
         <v>1</v>
@@ -9648,7 +9648,7 @@
         <v>90</v>
       </c>
       <c r="Q76" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R76" s="9" t="s">
         <v>90</v>
@@ -9678,7 +9678,7 @@
         <v>90</v>
       </c>
       <c r="AM76" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN76" s="9" t="s">
         <v>35</v>
@@ -9687,7 +9687,7 @@
         <v>100</v>
       </c>
       <c r="AP76" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ76" s="9">
         <v>1</v>
@@ -9773,16 +9773,16 @@
         <v>90</v>
       </c>
       <c r="AM77" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN77" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO77" s="9">
         <v>65</v>
       </c>
       <c r="AP77" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ77" s="9">
         <v>1</v>
@@ -9826,7 +9826,7 @@
         <v>9</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K78" s="10">
         <v>3000000000</v>
@@ -9841,7 +9841,7 @@
         <v>90</v>
       </c>
       <c r="Q78" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R78" s="9" t="s">
         <v>90</v>
@@ -9871,7 +9871,7 @@
         <v>90</v>
       </c>
       <c r="AM78" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN78" s="9" t="s">
         <v>35</v>
@@ -9880,7 +9880,7 @@
         <v>100</v>
       </c>
       <c r="AP78" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ78" s="9">
         <v>1</v>
@@ -9924,7 +9924,7 @@
         <v>91</v>
       </c>
       <c r="J79" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K79" s="10">
         <v>4000000000</v>
@@ -9939,7 +9939,7 @@
         <v>90</v>
       </c>
       <c r="Q79" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R79" s="9" t="s">
         <v>90</v>
@@ -9972,7 +9972,7 @@
         <v>90</v>
       </c>
       <c r="AM79" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN79" s="9" t="s">
         <v>35</v>
@@ -9981,7 +9981,7 @@
         <v>100</v>
       </c>
       <c r="AP79" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ79" s="9">
         <v>1</v>
@@ -10025,7 +10025,7 @@
         <v>91</v>
       </c>
       <c r="J80" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K80" s="10">
         <v>3000000000</v>
@@ -10040,7 +10040,7 @@
         <v>90</v>
       </c>
       <c r="Q80" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R80" s="9" t="s">
         <v>90</v>
@@ -10070,7 +10070,7 @@
         <v>90</v>
       </c>
       <c r="AM80" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN80" s="9" t="s">
         <v>35</v>
@@ -10079,7 +10079,7 @@
         <v>100</v>
       </c>
       <c r="AP80" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ80" s="9">
         <v>1</v>
@@ -10123,7 +10123,7 @@
         <v>91</v>
       </c>
       <c r="J81" s="9" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="M81" s="9" t="s">
         <v>90</v>
@@ -10165,16 +10165,16 @@
         <v>90</v>
       </c>
       <c r="AM81" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AN81" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AO81" s="9">
         <v>40</v>
       </c>
       <c r="AP81" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ81" s="9">
         <v>1</v>
@@ -10278,7 +10278,7 @@
         <v>100</v>
       </c>
       <c r="AP82" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ82" s="9">
         <v>2</v>
@@ -10397,7 +10397,7 @@
         <v>100</v>
       </c>
       <c r="AP83" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ83" s="9">
         <v>2</v>
@@ -10501,7 +10501,7 @@
         <v>100</v>
       </c>
       <c r="AP84" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ84" s="9">
         <v>2</v>
@@ -10611,7 +10611,7 @@
         <v>100</v>
       </c>
       <c r="AP85" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ85" s="9">
         <v>1</v>
@@ -10724,7 +10724,7 @@
         <v>100</v>
       </c>
       <c r="AP86" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ86" s="9">
         <v>2</v>
@@ -10834,7 +10834,7 @@
         <v>100</v>
       </c>
       <c r="AP87" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ87" s="9">
         <v>2</v>
@@ -10938,7 +10938,7 @@
         <v>100</v>
       </c>
       <c r="AP88" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ88" s="9">
         <v>2</v>
@@ -11048,7 +11048,7 @@
         <v>100</v>
       </c>
       <c r="AP89" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ89" s="9">
         <v>2</v>
@@ -11158,7 +11158,7 @@
         <v>100</v>
       </c>
       <c r="AP90" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ90" s="9">
         <v>2</v>
@@ -11274,7 +11274,7 @@
         <v>100</v>
       </c>
       <c r="AP91" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AQ91" s="9">
         <v>2</v>
@@ -11977,7 +11977,7 @@
         <v>90</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>507</v>
@@ -11998,7 +11998,7 @@
         <v>90</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -12039,7 +12039,7 @@
         <v>90</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:15">
@@ -12080,7 +12080,7 @@
         <v>90</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:15">
@@ -12121,7 +12121,7 @@
         <v>90</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:15">
@@ -12141,7 +12141,7 @@
         <v>90</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>507</v>
@@ -12162,7 +12162,7 @@
         <v>90</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:15">
@@ -12203,7 +12203,7 @@
         <v>90</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -12223,7 +12223,7 @@
         <v>90</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>507</v>
@@ -12244,7 +12244,7 @@
         <v>90</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:15">
@@ -12285,7 +12285,7 @@
         <v>90</v>
       </c>
       <c r="O14" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:15">
@@ -12326,7 +12326,7 @@
         <v>90</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:15">
@@ -12367,7 +12367,7 @@
         <v>90</v>
       </c>
       <c r="O16" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:15">
@@ -12408,7 +12408,7 @@
         <v>90</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" spans="1:15">
@@ -12449,7 +12449,7 @@
         <v>90</v>
       </c>
       <c r="O18" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="19" spans="1:15">
@@ -12490,7 +12490,7 @@
         <v>90</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="20" spans="1:15">
@@ -12531,7 +12531,7 @@
         <v>90</v>
       </c>
       <c r="O20" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:15">
@@ -12551,7 +12551,7 @@
         <v>90</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>507</v>
@@ -12572,7 +12572,7 @@
         <v>90</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:15">
@@ -12592,7 +12592,7 @@
         <v>90</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>507</v>
@@ -12613,7 +12613,7 @@
         <v>90</v>
       </c>
       <c r="O22" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:15">
@@ -12633,7 +12633,7 @@
         <v>90</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>507</v>
@@ -12654,7 +12654,7 @@
         <v>90</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:15">
@@ -13262,22 +13262,22 @@
         <v>90</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H7" s="8">
         <v>46206</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K7" t="s">
         <v>589</v>
@@ -13300,7 +13300,7 @@
     </row>
     <row r="8" spans="1:16" ht="28" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B8" s="8">
         <v>46206</v>
@@ -13309,13 +13309,13 @@
         <v>90</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>101</v>
@@ -13356,13 +13356,13 @@
         <v>90</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>104</v>
@@ -13628,13 +13628,13 @@
         <v>90</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>116</v>
@@ -13657,13 +13657,13 @@
         <v>90</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G16" s="9" t="s">
         <v>120</v>
@@ -13696,13 +13696,13 @@
         <v>90</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>124</v>
@@ -13725,13 +13725,13 @@
         <v>90</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G18" s="9" t="s">
         <v>127</v>
@@ -13754,13 +13754,13 @@
         <v>90</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>130</v>
@@ -13783,13 +13783,13 @@
         <v>133</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G20" s="9" t="s">
         <v>135</v>
@@ -13812,13 +13812,13 @@
         <v>90</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G21" s="9" t="s">
         <v>139</v>
@@ -13841,13 +13841,13 @@
         <v>90</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>142</v>
@@ -13870,13 +13870,13 @@
         <v>90</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>145</v>
@@ -13899,13 +13899,13 @@
         <v>90</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G24" s="9" t="s">
         <v>149</v>
@@ -13928,13 +13928,13 @@
         <v>90</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G25" s="9" t="s">
         <v>154</v>
@@ -14121,13 +14121,13 @@
         <v>90</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G32" s="9" t="s">
         <v>166</v>
@@ -14150,13 +14150,13 @@
         <v>90</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G33" s="9" t="s">
         <v>171</v>
@@ -14179,13 +14179,13 @@
         <v>90</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G34" s="9" t="s">
         <v>176</v>
@@ -14208,13 +14208,13 @@
         <v>90</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G35" s="9" t="s">
         <v>180</v>
@@ -14320,13 +14320,13 @@
         <v>90</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>191</v>
@@ -14349,13 +14349,13 @@
         <v>90</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G40" s="9" t="s">
         <v>194</v>
@@ -14378,13 +14378,13 @@
         <v>90</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G41" s="9" t="s">
         <v>197</v>
@@ -14407,13 +14407,13 @@
         <v>199</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>202</v>
@@ -14436,13 +14436,13 @@
         <v>205</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>207</v>
@@ -14583,7 +14583,7 @@
         <v>526</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G48" s="9" t="s">
         <v>223</v>
@@ -14691,13 +14691,13 @@
         <v>90</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E52" s="9" t="s">
         <v>526</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>234</v>
@@ -14720,13 +14720,13 @@
         <v>90</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>513</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>237</v>
@@ -14749,13 +14749,13 @@
         <v>90</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>526</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G54" s="9" t="s">
         <v>239</v>
@@ -14778,13 +14778,13 @@
         <v>90</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>526</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G55" s="9" t="s">
         <v>241</v>
@@ -14807,13 +14807,13 @@
         <v>90</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>526</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G56" s="9" t="s">
         <v>244</v>
@@ -14836,13 +14836,13 @@
         <v>90</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>526</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>247</v>
@@ -14865,13 +14865,13 @@
         <v>90</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>526</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>250</v>
@@ -14929,7 +14929,7 @@
         <v>526</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G60" s="9" t="s">
         <v>262</v>
@@ -15437,7 +15437,7 @@
         <v>526</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G78" s="9" t="s">
         <v>277</v>
@@ -16926,7 +16926,7 @@
         <v>526</v>
       </c>
       <c r="F131" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G131" s="9" t="s">
         <v>364</v>
@@ -16955,7 +16955,7 @@
         <v>580</v>
       </c>
       <c r="F132" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G132" s="9" t="s">
         <v>366</v>
@@ -16984,7 +16984,7 @@
         <v>526</v>
       </c>
       <c r="F133" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G133" s="9" t="s">
         <v>369</v>
@@ -17013,7 +17013,7 @@
         <v>526</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G134" s="9" t="s">
         <v>375</v>
@@ -17042,7 +17042,7 @@
         <v>526</v>
       </c>
       <c r="F135" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G135" s="9" t="s">
         <v>379</v>
@@ -17071,7 +17071,7 @@
         <v>526</v>
       </c>
       <c r="F136" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G136" s="9" t="s">
         <v>382</v>
@@ -17100,7 +17100,7 @@
         <v>526</v>
       </c>
       <c r="F137" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G137" s="9" t="s">
         <v>386</v>
@@ -17129,7 +17129,7 @@
         <v>581</v>
       </c>
       <c r="F138" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G138" s="9" t="s">
         <v>399</v>
@@ -17158,7 +17158,7 @@
         <v>582</v>
       </c>
       <c r="F139" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G139" s="9" t="s">
         <v>492</v>
@@ -17187,7 +17187,7 @@
         <v>581</v>
       </c>
       <c r="F140" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G140" s="9" t="s">
         <v>410</v>
@@ -17216,7 +17216,7 @@
         <v>582</v>
       </c>
       <c r="F141" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G141" s="9" t="s">
         <v>493</v>
@@ -17245,7 +17245,7 @@
         <v>581</v>
       </c>
       <c r="F142" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G142" s="9" t="s">
         <v>420</v>
@@ -17274,7 +17274,7 @@
         <v>582</v>
       </c>
       <c r="F143" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G143" s="9" t="s">
         <v>494</v>
@@ -17303,7 +17303,7 @@
         <v>582</v>
       </c>
       <c r="F144" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G144" s="9" t="s">
         <v>429</v>
@@ -17332,7 +17332,7 @@
         <v>581</v>
       </c>
       <c r="F145" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G145" s="9" t="s">
         <v>439</v>
@@ -17361,7 +17361,7 @@
         <v>582</v>
       </c>
       <c r="F146" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G146" s="9" t="s">
         <v>495</v>
@@ -17390,7 +17390,7 @@
         <v>581</v>
       </c>
       <c r="F147" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G147" s="9" t="s">
         <v>448</v>
@@ -17419,7 +17419,7 @@
         <v>582</v>
       </c>
       <c r="F148" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G148" s="9" t="s">
         <v>496</v>
@@ -17448,7 +17448,7 @@
         <v>581</v>
       </c>
       <c r="F149" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G149" s="9" t="s">
         <v>457</v>
@@ -17477,7 +17477,7 @@
         <v>582</v>
       </c>
       <c r="F150" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G150" s="9" t="s">
         <v>497</v>
@@ -17506,7 +17506,7 @@
         <v>581</v>
       </c>
       <c r="F151" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G151" s="9" t="s">
         <v>464</v>
@@ -17535,7 +17535,7 @@
         <v>582</v>
       </c>
       <c r="F152" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G152" s="9" t="s">
         <v>498</v>
@@ -17564,7 +17564,7 @@
         <v>581</v>
       </c>
       <c r="F153" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G153" s="9" t="s">
         <v>473</v>
@@ -17593,7 +17593,7 @@
         <v>582</v>
       </c>
       <c r="F154" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G154" s="9" t="s">
         <v>499</v>
@@ -17622,7 +17622,7 @@
         <v>581</v>
       </c>
       <c r="F155" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G155" s="9" t="s">
         <v>480</v>
@@ -17651,7 +17651,7 @@
         <v>582</v>
       </c>
       <c r="F156" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G156" s="9" t="s">
         <v>500</v>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4106" uniqueCount="598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4114" uniqueCount="600">
   <si>
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-05 | Build 98d1ec625779 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-06 | Build 0cfcd7590d68 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -1046,7 +1046,7 @@
     <t>https://rb.ru/news/vk-prodal-25-akcij-tochka-banka-sdelku-ocenili-v-212-mlrd-vdvoe-vyshe-iznachalnoj-stoimosti-bumag/</t>
   </si>
   <si>
-    <t>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.RU</t>
+    <t>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.ru</t>
   </si>
   <si>
     <t>DL-4774de17c61c14e4</t>
@@ -1713,6 +1713,12 @@
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE5vODZHWnJJX1RoLWU3X2RfSGpCZFZrN2xZeGtyOVVzSENxQzlaQTEwV3pCNXBuOG9JRnVfTkdxOGl5N3RJTGhDVVh0YXdBbTY5dnlZYWRjVkJ5MTFROHhTQUVvdjEwS3BpYUtmSG12YmVocnBnVmVpVmN0ZzQ?oc=5</t>
+  </si>
+  <si>
+    <t>URA.RU</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiR0FVX3lxTE8wam05RkhGd2REbmcta2EzYmJUZDZ0YzFCcVVTT2t0YndoN0x0TVVhTG9tSWJyN1RCaUFnU3NVMWh4WVJPUWRV?oc=5</t>
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPdUFBdHZlVG53aElMZ1BtWGh4VzZmSEg1OFU4UzJqTnlOanFmYW5RLUV3OXR3cFFrdmhJalBhZWFPMmFPTjlObnRyY2c4T3dYZTc3MjBfWHFrUU00RVBxMnFreVNkQ19vNVBGbnlDSktCZXJGTmFWUmJtWllmX2xraTRsM093aHdoWGo2QW0zNGg5VkxyRFk5YnU1QWtYOFMxMzhLNTBQbWxLQjNkbXl6cWY3RQ?oc=5</t>
@@ -2083,8 +2089,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:I156" totalsRowShown="0">
-  <autoFilter ref="A6:I156"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:I157" totalsRowShown="0">
+  <autoFilter ref="A6:I157"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Deal ID"/>
     <tableColumn id="2" name="Date"/>
@@ -8342,7 +8348,7 @@
         <v>110</v>
       </c>
       <c r="AQ62" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR62" s="9" t="s">
         <v>316</v>
@@ -13138,7 +13144,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P156"/>
+  <dimension ref="A1:P157"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -13196,7 +13202,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="K4" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -13233,19 +13239,19 @@
         <v>30</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="P6" s="4" t="s">
         <v>23</v>
@@ -13280,7 +13286,7 @@
         <v>99</v>
       </c>
       <c r="K7" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -13327,7 +13333,7 @@
         <v>102</v>
       </c>
       <c r="K8" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -13374,7 +13380,7 @@
         <v>105</v>
       </c>
       <c r="K9" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -13419,7 +13425,7 @@
         <v>113</v>
       </c>
       <c r="K10" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -13464,7 +13470,7 @@
         <v>113</v>
       </c>
       <c r="K11" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -13509,7 +13515,7 @@
         <v>113</v>
       </c>
       <c r="K12" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -13554,7 +13560,7 @@
         <v>113</v>
       </c>
       <c r="K13" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -13599,7 +13605,7 @@
         <v>113</v>
       </c>
       <c r="K14" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L14">
         <v>6</v>
@@ -13675,7 +13681,7 @@
         <v>121</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -16181,7 +16187,7 @@
     </row>
     <row r="105" spans="1:9" ht="28" customHeight="1">
       <c r="A105" s="9" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B105" s="8">
         <v>46139</v>
@@ -16190,22 +16196,20 @@
         <v>90</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>320</v>
+        <v>565</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="H105" s="8">
-        <v>46139</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="H105" s="9"/>
       <c r="I105" s="13" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="28" customHeight="1">
@@ -16222,22 +16226,24 @@
         <v>320</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>565</v>
-      </c>
-      <c r="H106" s="9"/>
+        <v>321</v>
+      </c>
+      <c r="H106" s="8">
+        <v>46139</v>
+      </c>
       <c r="I106" s="13" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="107" spans="1:9" ht="28" customHeight="1">
       <c r="A107" s="9" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B107" s="8">
         <v>46139</v>
@@ -16246,22 +16252,20 @@
         <v>90</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="H107" s="8">
-        <v>46139</v>
-      </c>
+        <v>567</v>
+      </c>
+      <c r="H107" s="9"/>
       <c r="I107" s="13" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="108" spans="1:9" ht="28" customHeight="1">
@@ -16278,46 +16282,46 @@
         <v>324</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>566</v>
-      </c>
-      <c r="H108" s="9"/>
+        <v>325</v>
+      </c>
+      <c r="H108" s="8">
+        <v>46139</v>
+      </c>
       <c r="I108" s="13" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="109" spans="1:9" ht="28" customHeight="1">
       <c r="A109" s="9" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B109" s="8">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>272</v>
+        <v>90</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>111</v>
+        <v>324</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>328</v>
-      </c>
-      <c r="H109" s="8">
-        <v>46132</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="H109" s="9"/>
       <c r="I109" s="13" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="110" spans="1:9" ht="28" customHeight="1">
@@ -16334,46 +16338,46 @@
         <v>111</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>567</v>
-      </c>
-      <c r="H110" s="9"/>
+        <v>328</v>
+      </c>
+      <c r="H110" s="8">
+        <v>46132</v>
+      </c>
       <c r="I110" s="13" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="111" spans="1:9" ht="28" customHeight="1">
       <c r="A111" s="9" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B111" s="8">
         <v>46132</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>38</v>
+        <v>272</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>331</v>
+        <v>111</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="H111" s="8">
-        <v>46132</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="H111" s="9"/>
       <c r="I111" s="13" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="112" spans="1:9" ht="28" customHeight="1">
@@ -16390,22 +16394,24 @@
         <v>331</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>568</v>
-      </c>
-      <c r="H112" s="9"/>
+        <v>332</v>
+      </c>
+      <c r="H112" s="8">
+        <v>46132</v>
+      </c>
       <c r="I112" s="13" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="113" spans="1:9" ht="28" customHeight="1">
       <c r="A113" s="9" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B113" s="8">
         <v>46132</v>
@@ -16414,22 +16420,20 @@
         <v>38</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="H113" s="8">
-        <v>46132</v>
-      </c>
+        <v>570</v>
+      </c>
+      <c r="H113" s="9"/>
       <c r="I113" s="13" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="114" spans="1:9" ht="28" customHeight="1">
@@ -16446,46 +16450,46 @@
         <v>335</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>569</v>
-      </c>
-      <c r="H114" s="9"/>
+        <v>336</v>
+      </c>
+      <c r="H114" s="8">
+        <v>46132</v>
+      </c>
       <c r="I114" s="13" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="115" spans="1:9" ht="28" customHeight="1">
       <c r="A115" s="9" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B115" s="8">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>339</v>
+        <v>38</v>
       </c>
       <c r="D115" s="9" t="s">
         <v>335</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>341</v>
-      </c>
-      <c r="H115" s="8">
-        <v>46128</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="H115" s="9"/>
       <c r="I115" s="13" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="28" customHeight="1">
@@ -16499,7 +16503,7 @@
         <v>339</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="E116" s="9" t="s">
         <v>526</v>
@@ -16508,7 +16512,7 @@
         <v>110</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>570</v>
+        <v>341</v>
       </c>
       <c r="H116" s="8">
         <v>46128</v>
@@ -16528,7 +16532,7 @@
         <v>339</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>571</v>
+        <v>309</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>526</v>
@@ -16557,18 +16561,20 @@
         <v>339</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>335</v>
+        <v>573</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>573</v>
-      </c>
-      <c r="H118" s="9"/>
+        <v>574</v>
+      </c>
+      <c r="H118" s="8">
+        <v>46128</v>
+      </c>
       <c r="I118" s="13" t="s">
         <v>342</v>
       </c>
@@ -16584,7 +16590,7 @@
         <v>339</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>309</v>
+        <v>335</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>518</v>
@@ -16593,7 +16599,7 @@
         <v>110</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H119" s="9"/>
       <c r="I119" s="13" t="s">
@@ -16611,7 +16617,7 @@
         <v>339</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>571</v>
+        <v>309</v>
       </c>
       <c r="E120" s="9" t="s">
         <v>518</v>
@@ -16620,7 +16626,7 @@
         <v>110</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H120" s="9"/>
       <c r="I120" s="13" t="s">
@@ -16629,31 +16635,29 @@
     </row>
     <row r="121" spans="1:9" ht="28" customHeight="1">
       <c r="A121" s="9" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B121" s="8">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>162</v>
+        <v>573</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="H121" s="8">
-        <v>46122</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="H121" s="9"/>
       <c r="I121" s="13" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="28" customHeight="1">
@@ -16670,46 +16674,46 @@
         <v>162</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>576</v>
-      </c>
-      <c r="H122" s="9"/>
+        <v>344</v>
+      </c>
+      <c r="H122" s="8">
+        <v>46122</v>
+      </c>
       <c r="I122" s="13" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="28" customHeight="1">
       <c r="A123" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B123" s="8">
         <v>46122</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>272</v>
+        <v>340</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="H123" s="8">
-        <v>46122</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="H123" s="9"/>
       <c r="I123" s="13" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="28" customHeight="1">
@@ -16726,46 +16730,46 @@
         <v>111</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>577</v>
-      </c>
-      <c r="H124" s="9"/>
+        <v>347</v>
+      </c>
+      <c r="H124" s="8">
+        <v>46122</v>
+      </c>
       <c r="I124" s="13" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="28" customHeight="1">
       <c r="A125" s="9" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B125" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="C125" s="9" t="s">
         <v>272</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>331</v>
+        <v>111</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="H125" s="8">
-        <v>46115</v>
-      </c>
+        <v>579</v>
+      </c>
+      <c r="H125" s="9"/>
       <c r="I125" s="13" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="28" customHeight="1">
@@ -16782,22 +16786,24 @@
         <v>331</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>578</v>
-      </c>
-      <c r="H126" s="9"/>
+        <v>350</v>
+      </c>
+      <c r="H126" s="8">
+        <v>46115</v>
+      </c>
       <c r="I126" s="13" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="28" customHeight="1">
       <c r="A127" s="9" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B127" s="8">
         <v>46115</v>
@@ -16806,22 +16812,20 @@
         <v>272</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>187</v>
+        <v>331</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="H127" s="8">
-        <v>46115</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="H127" s="9"/>
       <c r="I127" s="13" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="28" customHeight="1">
@@ -16838,51 +16842,51 @@
         <v>187</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>518</v>
+        <v>526</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>579</v>
-      </c>
-      <c r="H128" s="9"/>
+        <v>353</v>
+      </c>
+      <c r="H128" s="8">
+        <v>46115</v>
+      </c>
       <c r="I128" s="13" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="28" customHeight="1">
       <c r="A129" s="9" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B129" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>340</v>
+        <v>272</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>356</v>
+        <v>187</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>110</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="H129" s="8">
-        <v>46111</v>
-      </c>
+        <v>581</v>
+      </c>
+      <c r="H129" s="9"/>
       <c r="I129" s="13" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="28" customHeight="1">
       <c r="A130" s="9" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B130" s="8">
         <v>46111</v>
@@ -16891,7 +16895,7 @@
         <v>340</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>162</v>
+        <v>356</v>
       </c>
       <c r="E130" s="9" t="s">
         <v>526</v>
@@ -16900,111 +16904,111 @@
         <v>110</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H130" s="8">
         <v>46111</v>
       </c>
       <c r="I130" s="13" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="28" customHeight="1">
       <c r="A131" s="9" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B131" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>44</v>
+        <v>340</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>363</v>
+        <v>162</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>526</v>
       </c>
       <c r="F131" s="9" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H131" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="I131" s="13" t="s">
-        <v>45</v>
+        <v>361</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="28" customHeight="1">
       <c r="A132" s="9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B132" s="8">
-        <v>45729</v>
+        <v>46080</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>261</v>
+        <v>363</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>580</v>
+        <v>526</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H132" s="8">
-        <v>45729</v>
+        <v>46080</v>
       </c>
       <c r="I132" s="13" t="s">
-        <v>367</v>
+        <v>45</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="28" customHeight="1">
       <c r="A133" s="9" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B133" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>363</v>
+        <v>261</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>526</v>
+        <v>582</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="H133" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="I133" s="13" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="28" customHeight="1">
       <c r="A134" s="9" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B134" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="D134" s="9" t="s">
         <v>363</v>
@@ -17016,21 +17020,21 @@
         <v>96</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="H134" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="I134" s="13" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="28" customHeight="1">
       <c r="A135" s="9" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B135" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="C135" s="9" t="s">
         <v>44</v>
@@ -17045,21 +17049,21 @@
         <v>96</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="H135" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="I135" s="13" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="28" customHeight="1">
       <c r="A136" s="9" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B136" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="C136" s="9" t="s">
         <v>44</v>
@@ -17074,24 +17078,24 @@
         <v>96</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="H136" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="I136" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="28" customHeight="1">
       <c r="A137" s="9" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B137" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>384</v>
+        <v>44</v>
       </c>
       <c r="D137" s="9" t="s">
         <v>363</v>
@@ -17103,42 +17107,42 @@
         <v>96</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="H137" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="I137" s="13" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="28" customHeight="1">
       <c r="A138" s="9" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B138" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="E138" s="9" t="s">
-        <v>581</v>
+        <v>526</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="H138" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="I138" s="13" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="28" customHeight="1">
@@ -17152,19 +17156,19 @@
         <v>389</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>492</v>
+        <v>399</v>
       </c>
       <c r="H139" s="8">
-        <v>45008</v>
+        <v>45190</v>
       </c>
       <c r="I139" s="13" t="s">
         <v>400</v>
@@ -17172,31 +17176,31 @@
     </row>
     <row r="140" spans="1:9" ht="28" customHeight="1">
       <c r="A140" s="9" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="B140" s="8">
-        <v>44707</v>
+        <v>45190</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="E140" s="9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G140" s="9" t="s">
-        <v>410</v>
+        <v>492</v>
       </c>
       <c r="H140" s="8">
-        <v>44707</v>
+        <v>45008</v>
       </c>
       <c r="I140" s="13" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="28" customHeight="1">
@@ -17210,19 +17214,19 @@
         <v>402</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>493</v>
+        <v>410</v>
       </c>
       <c r="H141" s="8">
-        <v>44644</v>
+        <v>44707</v>
       </c>
       <c r="I141" s="13" t="s">
         <v>411</v>
@@ -17230,31 +17234,31 @@
     </row>
     <row r="142" spans="1:9" ht="28" customHeight="1">
       <c r="A142" s="9" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="B142" s="8">
-        <v>44640</v>
+        <v>44707</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G142" s="9" t="s">
-        <v>420</v>
+        <v>493</v>
       </c>
       <c r="H142" s="8">
-        <v>44734</v>
+        <v>44644</v>
       </c>
       <c r="I142" s="13" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="28" customHeight="1">
@@ -17268,19 +17272,19 @@
         <v>413</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>494</v>
+        <v>420</v>
       </c>
       <c r="H143" s="8">
-        <v>44643</v>
+        <v>44734</v>
       </c>
       <c r="I143" s="13" t="s">
         <v>421</v>
@@ -17288,60 +17292,60 @@
     </row>
     <row r="144" spans="1:9" ht="28" customHeight="1">
       <c r="A144" s="9" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="B144" s="8">
-        <v>44592</v>
+        <v>44640</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="E144" s="9" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G144" s="9" t="s">
-        <v>429</v>
+        <v>494</v>
       </c>
       <c r="H144" s="8">
-        <v>44608</v>
+        <v>44643</v>
       </c>
       <c r="I144" s="13" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="28" customHeight="1">
       <c r="A145" s="9" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="B145" s="8">
-        <v>44579</v>
+        <v>44592</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="H145" s="8">
-        <v>44579</v>
+        <v>44608</v>
       </c>
       <c r="I145" s="13" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="28" customHeight="1">
@@ -17355,19 +17359,19 @@
         <v>432</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E146" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G146" s="9" t="s">
-        <v>495</v>
+        <v>439</v>
       </c>
       <c r="H146" s="8">
-        <v>44250</v>
+        <v>44579</v>
       </c>
       <c r="I146" s="13" t="s">
         <v>440</v>
@@ -17375,31 +17379,31 @@
     </row>
     <row r="147" spans="1:9" ht="28" customHeight="1">
       <c r="A147" s="9" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="B147" s="8">
-        <v>44166</v>
+        <v>44579</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>448</v>
+        <v>495</v>
       </c>
       <c r="H147" s="8">
-        <v>44166</v>
+        <v>44250</v>
       </c>
       <c r="I147" s="13" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="28" customHeight="1">
@@ -17413,19 +17417,19 @@
         <v>442</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E148" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G148" s="9" t="s">
-        <v>496</v>
+        <v>448</v>
       </c>
       <c r="H148" s="8">
-        <v>43902</v>
+        <v>44166</v>
       </c>
       <c r="I148" s="13" t="s">
         <v>449</v>
@@ -17433,31 +17437,31 @@
     </row>
     <row r="149" spans="1:9" ht="28" customHeight="1">
       <c r="A149" s="9" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="B149" s="8">
-        <v>44131</v>
+        <v>44166</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>457</v>
+        <v>496</v>
       </c>
       <c r="H149" s="8">
-        <v>44131</v>
+        <v>43902</v>
       </c>
       <c r="I149" s="13" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="28" customHeight="1">
@@ -17471,19 +17475,19 @@
         <v>451</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E150" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G150" s="9" t="s">
-        <v>497</v>
+        <v>457</v>
       </c>
       <c r="H150" s="8">
-        <v>43966</v>
+        <v>44131</v>
       </c>
       <c r="I150" s="13" t="s">
         <v>458</v>
@@ -17491,31 +17495,31 @@
     </row>
     <row r="151" spans="1:9" ht="28" customHeight="1">
       <c r="A151" s="9" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="B151" s="8">
-        <v>43626</v>
+        <v>44131</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>464</v>
+        <v>497</v>
       </c>
       <c r="H151" s="8">
-        <v>43626</v>
+        <v>43966</v>
       </c>
       <c r="I151" s="13" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="28" customHeight="1">
@@ -17529,19 +17533,19 @@
         <v>460</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="E152" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G152" s="9" t="s">
-        <v>498</v>
+        <v>464</v>
       </c>
       <c r="H152" s="8">
-        <v>43518</v>
+        <v>43626</v>
       </c>
       <c r="I152" s="13" t="s">
         <v>465</v>
@@ -17549,31 +17553,31 @@
     </row>
     <row r="153" spans="1:9" ht="28" customHeight="1">
       <c r="A153" s="9" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="B153" s="8">
-        <v>43401</v>
+        <v>43626</v>
       </c>
       <c r="C153" s="9" t="s">
-        <v>467</v>
+        <v>460</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>473</v>
+        <v>498</v>
       </c>
       <c r="H153" s="8">
-        <v>43401</v>
+        <v>43518</v>
       </c>
       <c r="I153" s="13" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="28" customHeight="1">
@@ -17587,19 +17591,19 @@
         <v>467</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E154" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G154" s="9" t="s">
-        <v>499</v>
+        <v>473</v>
       </c>
       <c r="H154" s="8">
-        <v>43215</v>
+        <v>43401</v>
       </c>
       <c r="I154" s="13" t="s">
         <v>474</v>
@@ -17607,31 +17611,31 @@
     </row>
     <row r="155" spans="1:9" ht="28" customHeight="1">
       <c r="A155" s="9" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="B155" s="8">
-        <v>42534</v>
+        <v>43401</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>480</v>
+        <v>499</v>
       </c>
       <c r="H155" s="8">
-        <v>42534</v>
+        <v>43215</v>
       </c>
       <c r="I155" s="13" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="28" customHeight="1">
@@ -17645,21 +17649,50 @@
         <v>476</v>
       </c>
       <c r="D156" s="9" t="s">
-        <v>478</v>
+        <v>438</v>
       </c>
       <c r="E156" s="9" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>96</v>
       </c>
       <c r="G156" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="H156" s="8">
+        <v>42534</v>
+      </c>
+      <c r="I156" s="13" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="28" customHeight="1">
+      <c r="A157" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="B157" s="8">
+        <v>42534</v>
+      </c>
+      <c r="C157" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="E157" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="F157" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G157" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="H156" s="8">
+      <c r="H157" s="8">
         <v>42412</v>
       </c>
-      <c r="I156" s="13" t="s">
+      <c r="I157" s="13" t="s">
         <v>481</v>
       </c>
     </row>
@@ -17775,10 +17808,10 @@
     <hyperlink ref="G108" r:id="rId102"/>
     <hyperlink ref="G109" r:id="rId103"/>
     <hyperlink ref="G110" r:id="rId104"/>
-    <hyperlink ref="D111" r:id="rId105"/>
-    <hyperlink ref="G111" r:id="rId106"/>
-    <hyperlink ref="D112" r:id="rId107"/>
-    <hyperlink ref="G112" r:id="rId108"/>
+    <hyperlink ref="G111" r:id="rId105"/>
+    <hyperlink ref="D112" r:id="rId106"/>
+    <hyperlink ref="G112" r:id="rId107"/>
+    <hyperlink ref="D113" r:id="rId108"/>
     <hyperlink ref="G113" r:id="rId109"/>
     <hyperlink ref="G114" r:id="rId110"/>
     <hyperlink ref="G115" r:id="rId111"/>
@@ -17791,10 +17824,10 @@
     <hyperlink ref="G122" r:id="rId118"/>
     <hyperlink ref="G123" r:id="rId119"/>
     <hyperlink ref="G124" r:id="rId120"/>
-    <hyperlink ref="D125" r:id="rId121"/>
-    <hyperlink ref="G125" r:id="rId122"/>
-    <hyperlink ref="D126" r:id="rId123"/>
-    <hyperlink ref="G126" r:id="rId124"/>
+    <hyperlink ref="G125" r:id="rId121"/>
+    <hyperlink ref="D126" r:id="rId122"/>
+    <hyperlink ref="G126" r:id="rId123"/>
+    <hyperlink ref="D127" r:id="rId124"/>
     <hyperlink ref="G127" r:id="rId125"/>
     <hyperlink ref="G128" r:id="rId126"/>
     <hyperlink ref="G129" r:id="rId127"/>
@@ -17825,10 +17858,11 @@
     <hyperlink ref="G154" r:id="rId152"/>
     <hyperlink ref="G155" r:id="rId153"/>
     <hyperlink ref="G156" r:id="rId154"/>
+    <hyperlink ref="G157" r:id="rId155"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId155"/>
+    <tablePart r:id="rId156"/>
   </tableParts>
 </worksheet>
 </file>
--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4389" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4399" uniqueCount="641">
   <si>
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-08 | Build b8f3588cf68c | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-08 | Build 6e5e3a8d7a54 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -1796,6 +1796,9 @@
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxOVVc5b2xRd2dWREJQMEVGcEVKSlhNdFFmTjNGYWVnRkRNbHlmZ29zRGdzUjlrS2VQQjJxM0RhUTh4bnhIWnhNb3ZnQ2VhYmJqdEI1Q0dpVHZOWlNCLXNUanVlYTdhNmQ2TkpGZ1hFVG0xclRWNWZvZUhmeXdua1BtUDNpMm9LZw?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPa1Utd0tlY3RsT1JNSUZEcGdEdG84bFBJYlc0eDVEand3UnppVTduOUZPMUo2UHJ6SmxSSGgwekt6cDFyS3ByZDRxR1RrQjNJWk5VUlB4U2UyM0pSa3FiNnRscllQT19fZ2pEb0xQTU4xdXNXTi1PbWxNTF9LRTg2RTh3VHoyZw?oc=5</t>
   </si>
   <si>
     <t>https://bcs-express.ru/novosti-i-analitika/t-tekhnologii-zakryli-sdelku-po-pokupke-avto-ru-u-iandeksa</t>
@@ -2247,8 +2250,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:K130" totalsRowShown="0">
-  <autoFilter ref="A6:K130"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:K131" totalsRowShown="0">
+  <autoFilter ref="A6:K131"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Deal ID"/>
     <tableColumn id="2" name="Date"/>
@@ -8154,7 +8157,7 @@
         <v>109</v>
       </c>
       <c r="AQ58" s="9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR58" s="9" t="s">
         <v>224</v>
@@ -14148,7 +14151,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R130"/>
+  <dimension ref="A1:R131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -14211,7 +14214,7 @@
     </row>
     <row r="4" spans="1:18">
       <c r="M4" s="3" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -14254,19 +14257,19 @@
         <v>30</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>23</v>
@@ -14307,7 +14310,7 @@
         <v>101</v>
       </c>
       <c r="M7" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -14358,7 +14361,7 @@
         <v>112</v>
       </c>
       <c r="M8" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -14411,7 +14414,7 @@
         <v>36</v>
       </c>
       <c r="M9" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -14464,7 +14467,7 @@
         <v>119</v>
       </c>
       <c r="M10" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -14517,7 +14520,7 @@
         <v>124</v>
       </c>
       <c r="M11" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -14570,7 +14573,7 @@
         <v>127</v>
       </c>
       <c r="M12" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -14621,7 +14624,7 @@
         <v>133</v>
       </c>
       <c r="M13" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -14672,7 +14675,7 @@
         <v>138</v>
       </c>
       <c r="M14" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -14760,7 +14763,7 @@
         <v>144</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -16747,37 +16750,35 @@
     </row>
     <row r="74" spans="1:11" ht="28" customHeight="1">
       <c r="A74" s="9" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="B74" s="8">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>45</v>
+        <v>305</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>294</v>
+        <v>149</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="H74" s="8">
-        <v>46175</v>
-      </c>
+        <v>588</v>
+      </c>
+      <c r="H74" s="9"/>
       <c r="I74" s="9">
         <v>1</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>310</v>
+        <v>588</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>47</v>
+        <v>308</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="28" customHeight="1">
@@ -16791,25 +16792,25 @@
         <v>45</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>224</v>
+        <v>294</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>564</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>588</v>
+        <v>310</v>
       </c>
       <c r="H75" s="8">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="I75" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J75" s="13" t="s">
-        <v>589</v>
+        <v>310</v>
       </c>
       <c r="K75" s="13" t="s">
         <v>47</v>
@@ -16826,7 +16827,7 @@
         <v>45</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>564</v>
@@ -16835,16 +16836,16 @@
         <v>109</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H76" s="8">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="I76" s="9">
         <v>2</v>
       </c>
       <c r="J76" s="13" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="K76" s="13" t="s">
         <v>47</v>
@@ -16852,13 +16853,13 @@
     </row>
     <row r="77" spans="1:11" ht="28" customHeight="1">
       <c r="A77" s="9" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B77" s="8">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>313</v>
+        <v>45</v>
       </c>
       <c r="D77" s="9" t="s">
         <v>199</v>
@@ -16870,10 +16871,10 @@
         <v>109</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>314</v>
+        <v>591</v>
       </c>
       <c r="H77" s="8">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="I77" s="9">
         <v>2</v>
@@ -16882,18 +16883,18 @@
         <v>592</v>
       </c>
       <c r="K77" s="13" t="s">
-        <v>315</v>
+        <v>47</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="28" customHeight="1">
       <c r="A78" s="9" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="B78" s="8">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>34</v>
+        <v>313</v>
       </c>
       <c r="D78" s="9" t="s">
         <v>199</v>
@@ -16905,10 +16906,10 @@
         <v>109</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="H78" s="8">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="I78" s="9">
         <v>2</v>
@@ -16917,21 +16918,21 @@
         <v>593</v>
       </c>
       <c r="K78" s="13" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="28" customHeight="1">
       <c r="A79" s="9" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B79" s="8">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>305</v>
+        <v>34</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>564</v>
@@ -16940,10 +16941,10 @@
         <v>109</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="H79" s="8">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="I79" s="9">
         <v>2</v>
@@ -16952,21 +16953,21 @@
         <v>594</v>
       </c>
       <c r="K79" s="13" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="28" customHeight="1">
       <c r="A80" s="9" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B80" s="8">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="C80" s="9" t="s">
         <v>305</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>564</v>
@@ -16975,10 +16976,10 @@
         <v>109</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H80" s="8">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="I80" s="9">
         <v>2</v>
@@ -16987,21 +16988,21 @@
         <v>595</v>
       </c>
       <c r="K80" s="13" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="28" customHeight="1">
       <c r="A81" s="9" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B81" s="8">
         <v>46157</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>34</v>
+        <v>305</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>299</v>
+        <v>199</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>564</v>
@@ -17010,30 +17011,30 @@
         <v>109</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="H81" s="8">
         <v>46157</v>
       </c>
       <c r="I81" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" s="13" t="s">
-        <v>327</v>
+        <v>596</v>
       </c>
       <c r="K81" s="13" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="28" customHeight="1">
       <c r="A82" s="9" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B82" s="8">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>330</v>
+        <v>34</v>
       </c>
       <c r="D82" s="9" t="s">
         <v>299</v>
@@ -17045,33 +17046,33 @@
         <v>109</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="H82" s="8">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="I82" s="9">
         <v>1</v>
       </c>
       <c r="J82" s="13" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="28" customHeight="1">
       <c r="A83" s="9" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B83" s="8">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>42</v>
+        <v>330</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>224</v>
+        <v>299</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>564</v>
@@ -17080,33 +17081,33 @@
         <v>109</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="H83" s="8">
-        <v>46147</v>
+        <v>46150</v>
       </c>
       <c r="I83" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J83" s="13" t="s">
-        <v>596</v>
+        <v>331</v>
       </c>
       <c r="K83" s="13" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="28" customHeight="1">
       <c r="A84" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B84" s="8">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C84" s="9" t="s">
         <v>42</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>338</v>
+        <v>224</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>564</v>
@@ -17115,10 +17116,10 @@
         <v>109</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="H84" s="8">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="I84" s="9">
         <v>2</v>
@@ -17127,21 +17128,21 @@
         <v>597</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="28" customHeight="1">
       <c r="A85" s="9" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B85" s="8">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>136</v>
+        <v>338</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>564</v>
@@ -17150,10 +17151,10 @@
         <v>109</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H85" s="8">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="I85" s="9">
         <v>2</v>
@@ -17162,12 +17163,12 @@
         <v>598</v>
       </c>
       <c r="K85" s="13" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="28" customHeight="1">
       <c r="A86" s="9" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B86" s="8">
         <v>46139</v>
@@ -17176,7 +17177,7 @@
         <v>34</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>224</v>
+        <v>136</v>
       </c>
       <c r="E86" s="9" t="s">
         <v>564</v>
@@ -17185,7 +17186,7 @@
         <v>109</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="H86" s="8">
         <v>46139</v>
@@ -17197,12 +17198,12 @@
         <v>599</v>
       </c>
       <c r="K86" s="13" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="28" customHeight="1">
       <c r="A87" s="9" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B87" s="8">
         <v>46139</v>
@@ -17211,7 +17212,7 @@
         <v>34</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>348</v>
+        <v>224</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>564</v>
@@ -17220,7 +17221,7 @@
         <v>109</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="H87" s="8">
         <v>46139</v>
@@ -17232,7 +17233,7 @@
         <v>600</v>
       </c>
       <c r="K87" s="13" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="28" customHeight="1">
@@ -17246,7 +17247,7 @@
         <v>34</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>560</v>
+        <v>348</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>564</v>
@@ -17255,7 +17256,7 @@
         <v>109</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>601</v>
+        <v>349</v>
       </c>
       <c r="H88" s="8">
         <v>46139</v>
@@ -17264,7 +17265,7 @@
         <v>2</v>
       </c>
       <c r="J88" s="13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="K88" s="13" t="s">
         <v>350</v>
@@ -17281,23 +17282,25 @@
         <v>34</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>603</v>
+        <v>560</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>109</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>604</v>
-      </c>
-      <c r="H89" s="9"/>
+        <v>602</v>
+      </c>
+      <c r="H89" s="8">
+        <v>46139</v>
+      </c>
       <c r="I89" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J89" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K89" s="13" t="s">
         <v>350</v>
@@ -17305,7 +17308,7 @@
     </row>
     <row r="90" spans="1:11" ht="28" customHeight="1">
       <c r="A90" s="9" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B90" s="8">
         <v>46139</v>
@@ -17314,33 +17317,31 @@
         <v>34</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>352</v>
+        <v>604</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>109</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="H90" s="8">
-        <v>46139</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="H90" s="9"/>
       <c r="I90" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" s="13" t="s">
         <v>605</v>
       </c>
       <c r="K90" s="13" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="28" customHeight="1">
       <c r="A91" s="9" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B91" s="8">
         <v>46139</v>
@@ -17349,7 +17350,7 @@
         <v>34</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>564</v>
@@ -17358,7 +17359,7 @@
         <v>109</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="H91" s="8">
         <v>46139</v>
@@ -17370,21 +17371,21 @@
         <v>606</v>
       </c>
       <c r="K91" s="13" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="28" customHeight="1">
       <c r="A92" s="9" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B92" s="8">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>305</v>
+        <v>34</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>149</v>
+        <v>356</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>564</v>
@@ -17393,10 +17394,10 @@
         <v>109</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="H92" s="8">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="I92" s="9">
         <v>2</v>
@@ -17405,21 +17406,21 @@
         <v>607</v>
       </c>
       <c r="K92" s="13" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="28" customHeight="1">
       <c r="A93" s="9" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B93" s="8">
         <v>46132</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>42</v>
+        <v>305</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>363</v>
+        <v>149</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>564</v>
@@ -17428,7 +17429,7 @@
         <v>109</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="H93" s="8">
         <v>46132</v>
@@ -17440,7 +17441,7 @@
         <v>608</v>
       </c>
       <c r="K93" s="13" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="28" customHeight="1">
@@ -17454,23 +17455,25 @@
         <v>42</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>609</v>
+        <v>363</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>109</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>610</v>
-      </c>
-      <c r="H94" s="9"/>
+        <v>364</v>
+      </c>
+      <c r="H94" s="8">
+        <v>46132</v>
+      </c>
       <c r="I94" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J94" s="13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="K94" s="13" t="s">
         <v>365</v>
@@ -17478,7 +17481,7 @@
     </row>
     <row r="95" spans="1:11" ht="28" customHeight="1">
       <c r="A95" s="9" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B95" s="8">
         <v>46132</v>
@@ -17487,39 +17490,37 @@
         <v>42</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>367</v>
+        <v>610</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>109</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="H95" s="8">
-        <v>46132</v>
-      </c>
+        <v>611</v>
+      </c>
+      <c r="H95" s="9"/>
       <c r="I95" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J95" s="13" t="s">
         <v>611</v>
       </c>
       <c r="K95" s="13" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="28" customHeight="1">
       <c r="A96" s="9" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B96" s="8">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>371</v>
+        <v>42</v>
       </c>
       <c r="D96" s="9" t="s">
         <v>367</v>
@@ -17531,10 +17532,10 @@
         <v>109</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="H96" s="8">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="I96" s="9">
         <v>2</v>
@@ -17543,7 +17544,7 @@
         <v>612</v>
       </c>
       <c r="K96" s="13" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="28" customHeight="1">
@@ -17557,7 +17558,7 @@
         <v>371</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>136</v>
+        <v>367</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>564</v>
@@ -17566,7 +17567,7 @@
         <v>109</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>613</v>
+        <v>373</v>
       </c>
       <c r="H97" s="8">
         <v>46128</v>
@@ -17575,7 +17576,7 @@
         <v>2</v>
       </c>
       <c r="J97" s="13" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="K97" s="13" t="s">
         <v>374</v>
@@ -17592,7 +17593,7 @@
         <v>371</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>615</v>
+        <v>136</v>
       </c>
       <c r="E98" s="9" t="s">
         <v>564</v>
@@ -17601,7 +17602,7 @@
         <v>109</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="H98" s="8">
         <v>46128</v>
@@ -17610,7 +17611,7 @@
         <v>2</v>
       </c>
       <c r="J98" s="13" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="K98" s="13" t="s">
         <v>374</v>
@@ -17618,16 +17619,16 @@
     </row>
     <row r="99" spans="1:11" ht="28" customHeight="1">
       <c r="A99" s="9" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B99" s="8">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>199</v>
+        <v>616</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>564</v>
@@ -17636,10 +17637,10 @@
         <v>109</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>376</v>
+        <v>617</v>
       </c>
       <c r="H99" s="8">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="I99" s="9">
         <v>2</v>
@@ -17648,21 +17649,21 @@
         <v>618</v>
       </c>
       <c r="K99" s="13" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="28" customHeight="1">
       <c r="A100" s="9" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B100" s="8">
         <v>46122</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>305</v>
+        <v>372</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>564</v>
@@ -17671,7 +17672,7 @@
         <v>109</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="H100" s="8">
         <v>46122</v>
@@ -17683,21 +17684,21 @@
         <v>619</v>
       </c>
       <c r="K100" s="13" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="28" customHeight="1">
       <c r="A101" s="9" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B101" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="C101" s="9" t="s">
         <v>305</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>363</v>
+        <v>149</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>564</v>
@@ -17706,10 +17707,10 @@
         <v>109</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="H101" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="I101" s="9">
         <v>2</v>
@@ -17718,12 +17719,12 @@
         <v>620</v>
       </c>
       <c r="K101" s="13" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="28" customHeight="1">
       <c r="A102" s="9" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B102" s="8">
         <v>46115</v>
@@ -17732,7 +17733,7 @@
         <v>305</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>224</v>
+        <v>363</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>564</v>
@@ -17741,7 +17742,7 @@
         <v>109</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="H102" s="8">
         <v>46115</v>
@@ -17753,21 +17754,21 @@
         <v>621</v>
       </c>
       <c r="K102" s="13" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="28" customHeight="1">
       <c r="A103" s="9" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B103" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>372</v>
+        <v>305</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>388</v>
+        <v>224</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>564</v>
@@ -17776,24 +17777,24 @@
         <v>109</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="H103" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="I103" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J103" s="13" t="s">
-        <v>389</v>
+        <v>622</v>
       </c>
       <c r="K103" s="13" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="28" customHeight="1">
       <c r="A104" s="9" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B104" s="8">
         <v>46111</v>
@@ -17802,7 +17803,7 @@
         <v>372</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>199</v>
+        <v>388</v>
       </c>
       <c r="E104" s="9" t="s">
         <v>564</v>
@@ -17811,7 +17812,7 @@
         <v>109</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H104" s="8">
         <v>46111</v>
@@ -17820,126 +17821,126 @@
         <v>1</v>
       </c>
       <c r="J104" s="13" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="K104" s="13" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="28" customHeight="1">
       <c r="A105" s="9" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B105" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>48</v>
+        <v>372</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>395</v>
+        <v>199</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>564</v>
       </c>
       <c r="F105" s="9" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="H105" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="I105" s="9">
         <v>1</v>
       </c>
       <c r="J105" s="13" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="K105" s="13" t="s">
-        <v>49</v>
+        <v>393</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="28" customHeight="1">
       <c r="A106" s="9" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B106" s="8">
-        <v>45729</v>
+        <v>46080</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>294</v>
+        <v>395</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>622</v>
+        <v>564</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>98</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="H106" s="8">
-        <v>45729</v>
+        <v>46080</v>
       </c>
       <c r="I106" s="9">
         <v>1</v>
       </c>
       <c r="J106" s="13" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="K106" s="13" t="s">
-        <v>399</v>
+        <v>49</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="28" customHeight="1">
       <c r="A107" s="9" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B107" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>395</v>
+        <v>294</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>564</v>
+        <v>623</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>98</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="H107" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="I107" s="9">
         <v>1</v>
       </c>
       <c r="J107" s="13" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="K107" s="13" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="28" customHeight="1">
       <c r="A108" s="9" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B108" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D108" s="9" t="s">
         <v>395</v>
@@ -17951,27 +17952,27 @@
         <v>98</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="H108" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="I108" s="9">
         <v>1</v>
       </c>
       <c r="J108" s="13" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="K108" s="13" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="28" customHeight="1">
       <c r="A109" s="9" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B109" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="C109" s="9" t="s">
         <v>48</v>
@@ -17986,27 +17987,27 @@
         <v>98</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="H109" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="I109" s="9">
         <v>1</v>
       </c>
       <c r="J109" s="13" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="K109" s="13" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="28" customHeight="1">
       <c r="A110" s="9" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B110" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="C110" s="9" t="s">
         <v>48</v>
@@ -18021,30 +18022,30 @@
         <v>98</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="H110" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="I110" s="9">
         <v>1</v>
       </c>
       <c r="J110" s="13" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="K110" s="13" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="28" customHeight="1">
       <c r="A111" s="9" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B111" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>416</v>
+        <v>48</v>
       </c>
       <c r="D111" s="9" t="s">
         <v>395</v>
@@ -18056,54 +18057,54 @@
         <v>98</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="H111" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="I111" s="9">
         <v>1</v>
       </c>
       <c r="J111" s="13" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="K111" s="13" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="28" customHeight="1">
       <c r="A112" s="9" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B112" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>430</v>
+        <v>395</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>623</v>
+        <v>564</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>98</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="H112" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="I112" s="9">
         <v>1</v>
       </c>
       <c r="J112" s="13" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="K112" s="13" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="28" customHeight="1">
@@ -18117,7 +18118,7 @@
         <v>421</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>624</v>
@@ -18126,16 +18127,16 @@
         <v>98</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>524</v>
+        <v>431</v>
       </c>
       <c r="H113" s="8">
-        <v>45008</v>
+        <v>45190</v>
       </c>
       <c r="I113" s="9">
         <v>1</v>
       </c>
       <c r="J113" s="13" t="s">
-        <v>524</v>
+        <v>431</v>
       </c>
       <c r="K113" s="13" t="s">
         <v>432</v>
@@ -18143,37 +18144,37 @@
     </row>
     <row r="114" spans="1:11" ht="28" customHeight="1">
       <c r="A114" s="9" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="B114" s="8">
-        <v>44707</v>
+        <v>45190</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>441</v>
+        <v>427</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>98</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>442</v>
+        <v>524</v>
       </c>
       <c r="H114" s="8">
-        <v>44707</v>
+        <v>45008</v>
       </c>
       <c r="I114" s="9">
         <v>1</v>
       </c>
       <c r="J114" s="13" t="s">
-        <v>442</v>
+        <v>524</v>
       </c>
       <c r="K114" s="13" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="28" customHeight="1">
@@ -18187,7 +18188,7 @@
         <v>434</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>624</v>
@@ -18196,16 +18197,16 @@
         <v>98</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>525</v>
+        <v>442</v>
       </c>
       <c r="H115" s="8">
-        <v>44644</v>
+        <v>44707</v>
       </c>
       <c r="I115" s="9">
         <v>1</v>
       </c>
       <c r="J115" s="13" t="s">
-        <v>525</v>
+        <v>442</v>
       </c>
       <c r="K115" s="13" t="s">
         <v>443</v>
@@ -18213,37 +18214,37 @@
     </row>
     <row r="116" spans="1:11" ht="28" customHeight="1">
       <c r="A116" s="9" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="B116" s="8">
-        <v>44640</v>
+        <v>44707</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>98</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>452</v>
+        <v>525</v>
       </c>
       <c r="H116" s="8">
-        <v>44734</v>
+        <v>44644</v>
       </c>
       <c r="I116" s="9">
         <v>1</v>
       </c>
       <c r="J116" s="13" t="s">
-        <v>452</v>
+        <v>525</v>
       </c>
       <c r="K116" s="13" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="28" customHeight="1">
@@ -18257,7 +18258,7 @@
         <v>445</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>624</v>
@@ -18266,16 +18267,16 @@
         <v>98</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>526</v>
+        <v>452</v>
       </c>
       <c r="H117" s="8">
-        <v>44643</v>
+        <v>44734</v>
       </c>
       <c r="I117" s="9">
         <v>1</v>
       </c>
       <c r="J117" s="13" t="s">
-        <v>526</v>
+        <v>452</v>
       </c>
       <c r="K117" s="13" t="s">
         <v>453</v>
@@ -18283,72 +18284,72 @@
     </row>
     <row r="118" spans="1:11" ht="28" customHeight="1">
       <c r="A118" s="9" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="B118" s="8">
-        <v>44592</v>
+        <v>44640</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>98</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>461</v>
+        <v>526</v>
       </c>
       <c r="H118" s="8">
-        <v>44608</v>
+        <v>44643</v>
       </c>
       <c r="I118" s="9">
         <v>1</v>
       </c>
       <c r="J118" s="13" t="s">
-        <v>461</v>
+        <v>526</v>
       </c>
       <c r="K118" s="13" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="28" customHeight="1">
       <c r="A119" s="9" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B119" s="8">
-        <v>44579</v>
+        <v>44592</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>98</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="H119" s="8">
-        <v>44579</v>
+        <v>44608</v>
       </c>
       <c r="I119" s="9">
         <v>1</v>
       </c>
       <c r="J119" s="13" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="K119" s="13" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="28" customHeight="1">
@@ -18362,7 +18363,7 @@
         <v>464</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E120" s="9" t="s">
         <v>624</v>
@@ -18371,16 +18372,16 @@
         <v>98</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>527</v>
+        <v>471</v>
       </c>
       <c r="H120" s="8">
-        <v>44250</v>
+        <v>44579</v>
       </c>
       <c r="I120" s="9">
         <v>1</v>
       </c>
       <c r="J120" s="13" t="s">
-        <v>527</v>
+        <v>471</v>
       </c>
       <c r="K120" s="13" t="s">
         <v>472</v>
@@ -18388,37 +18389,37 @@
     </row>
     <row r="121" spans="1:11" ht="28" customHeight="1">
       <c r="A121" s="9" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="B121" s="8">
-        <v>44166</v>
+        <v>44579</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>98</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>480</v>
+        <v>527</v>
       </c>
       <c r="H121" s="8">
-        <v>44166</v>
+        <v>44250</v>
       </c>
       <c r="I121" s="9">
         <v>1</v>
       </c>
       <c r="J121" s="13" t="s">
-        <v>480</v>
+        <v>527</v>
       </c>
       <c r="K121" s="13" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="28" customHeight="1">
@@ -18432,7 +18433,7 @@
         <v>474</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E122" s="9" t="s">
         <v>624</v>
@@ -18441,16 +18442,16 @@
         <v>98</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>528</v>
+        <v>480</v>
       </c>
       <c r="H122" s="8">
-        <v>43902</v>
+        <v>44166</v>
       </c>
       <c r="I122" s="9">
         <v>1</v>
       </c>
       <c r="J122" s="13" t="s">
-        <v>528</v>
+        <v>480</v>
       </c>
       <c r="K122" s="13" t="s">
         <v>481</v>
@@ -18458,37 +18459,37 @@
     </row>
     <row r="123" spans="1:11" ht="28" customHeight="1">
       <c r="A123" s="9" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="B123" s="8">
-        <v>44131</v>
+        <v>44166</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>98</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>489</v>
+        <v>528</v>
       </c>
       <c r="H123" s="8">
-        <v>44131</v>
+        <v>43902</v>
       </c>
       <c r="I123" s="9">
         <v>1</v>
       </c>
       <c r="J123" s="13" t="s">
-        <v>489</v>
+        <v>528</v>
       </c>
       <c r="K123" s="13" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="28" customHeight="1">
@@ -18502,7 +18503,7 @@
         <v>483</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E124" s="9" t="s">
         <v>624</v>
@@ -18511,16 +18512,16 @@
         <v>98</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>529</v>
+        <v>489</v>
       </c>
       <c r="H124" s="8">
-        <v>43966</v>
+        <v>44131</v>
       </c>
       <c r="I124" s="9">
         <v>1</v>
       </c>
       <c r="J124" s="13" t="s">
-        <v>529</v>
+        <v>489</v>
       </c>
       <c r="K124" s="13" t="s">
         <v>490</v>
@@ -18528,37 +18529,37 @@
     </row>
     <row r="125" spans="1:11" ht="28" customHeight="1">
       <c r="A125" s="9" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="B125" s="8">
-        <v>43626</v>
+        <v>44131</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>98</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>496</v>
+        <v>529</v>
       </c>
       <c r="H125" s="8">
-        <v>43626</v>
+        <v>43966</v>
       </c>
       <c r="I125" s="9">
         <v>1</v>
       </c>
       <c r="J125" s="13" t="s">
-        <v>496</v>
+        <v>529</v>
       </c>
       <c r="K125" s="13" t="s">
-        <v>497</v>
+        <v>490</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="28" customHeight="1">
@@ -18572,7 +18573,7 @@
         <v>492</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="E126" s="9" t="s">
         <v>624</v>
@@ -18581,16 +18582,16 @@
         <v>98</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>530</v>
+        <v>496</v>
       </c>
       <c r="H126" s="8">
-        <v>43518</v>
+        <v>43626</v>
       </c>
       <c r="I126" s="9">
         <v>1</v>
       </c>
       <c r="J126" s="13" t="s">
-        <v>530</v>
+        <v>496</v>
       </c>
       <c r="K126" s="13" t="s">
         <v>497</v>
@@ -18598,37 +18599,37 @@
     </row>
     <row r="127" spans="1:11" ht="28" customHeight="1">
       <c r="A127" s="9" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="B127" s="8">
-        <v>43401</v>
+        <v>43626</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>98</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>505</v>
+        <v>530</v>
       </c>
       <c r="H127" s="8">
-        <v>43401</v>
+        <v>43518</v>
       </c>
       <c r="I127" s="9">
         <v>1</v>
       </c>
       <c r="J127" s="13" t="s">
-        <v>505</v>
+        <v>530</v>
       </c>
       <c r="K127" s="13" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="28" customHeight="1">
@@ -18642,7 +18643,7 @@
         <v>499</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E128" s="9" t="s">
         <v>624</v>
@@ -18651,16 +18652,16 @@
         <v>98</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>531</v>
+        <v>505</v>
       </c>
       <c r="H128" s="8">
-        <v>43215</v>
+        <v>43401</v>
       </c>
       <c r="I128" s="9">
         <v>1</v>
       </c>
       <c r="J128" s="13" t="s">
-        <v>531</v>
+        <v>505</v>
       </c>
       <c r="K128" s="13" t="s">
         <v>506</v>
@@ -18668,37 +18669,37 @@
     </row>
     <row r="129" spans="1:11" ht="28" customHeight="1">
       <c r="A129" s="9" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="B129" s="8">
-        <v>42534</v>
+        <v>43401</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>98</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="H129" s="8">
-        <v>42534</v>
+        <v>43215</v>
       </c>
       <c r="I129" s="9">
         <v>1</v>
       </c>
       <c r="J129" s="13" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="K129" s="13" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="28" customHeight="1">
@@ -18712,7 +18713,7 @@
         <v>508</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="E130" s="9" t="s">
         <v>624</v>
@@ -18721,18 +18722,53 @@
         <v>98</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="H130" s="8">
-        <v>42412</v>
+        <v>42534</v>
       </c>
       <c r="I130" s="9">
         <v>1</v>
       </c>
       <c r="J130" s="13" t="s">
+        <v>512</v>
+      </c>
+      <c r="K130" s="13" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" ht="28" customHeight="1">
+      <c r="A131" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="B131" s="8">
+        <v>42534</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="D131" s="9" t="s">
+        <v>510</v>
+      </c>
+      <c r="E131" s="9" t="s">
+        <v>625</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="G131" s="9" t="s">
         <v>532</v>
       </c>
-      <c r="K130" s="13" t="s">
+      <c r="H131" s="8">
+        <v>42412</v>
+      </c>
+      <c r="I131" s="9">
+        <v>1</v>
+      </c>
+      <c r="J131" s="13" t="s">
+        <v>532</v>
+      </c>
+      <c r="K131" s="13" t="s">
         <v>513</v>
       </c>
     </row>
@@ -18916,9 +18952,9 @@
     <hyperlink ref="J91" r:id="rId170"/>
     <hyperlink ref="G92" r:id="rId171"/>
     <hyperlink ref="J92" r:id="rId172"/>
-    <hyperlink ref="D93" r:id="rId173"/>
-    <hyperlink ref="G93" r:id="rId174"/>
-    <hyperlink ref="J93" r:id="rId175"/>
+    <hyperlink ref="G93" r:id="rId173"/>
+    <hyperlink ref="J93" r:id="rId174"/>
+    <hyperlink ref="D94" r:id="rId175"/>
     <hyperlink ref="G94" r:id="rId176"/>
     <hyperlink ref="J94" r:id="rId177"/>
     <hyperlink ref="G95" r:id="rId178"/>
@@ -18933,9 +18969,9 @@
     <hyperlink ref="J99" r:id="rId187"/>
     <hyperlink ref="G100" r:id="rId188"/>
     <hyperlink ref="J100" r:id="rId189"/>
-    <hyperlink ref="D101" r:id="rId190"/>
-    <hyperlink ref="G101" r:id="rId191"/>
-    <hyperlink ref="J101" r:id="rId192"/>
+    <hyperlink ref="G101" r:id="rId190"/>
+    <hyperlink ref="J101" r:id="rId191"/>
+    <hyperlink ref="D102" r:id="rId192"/>
     <hyperlink ref="G102" r:id="rId193"/>
     <hyperlink ref="J102" r:id="rId194"/>
     <hyperlink ref="G103" r:id="rId195"/>
@@ -18994,10 +19030,12 @@
     <hyperlink ref="J129" r:id="rId248"/>
     <hyperlink ref="G130" r:id="rId249"/>
     <hyperlink ref="J130" r:id="rId250"/>
+    <hyperlink ref="G131" r:id="rId251"/>
+    <hyperlink ref="J131" r:id="rId252"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId251"/>
+    <tablePart r:id="rId253"/>
   </tableParts>
 </worksheet>
 </file>
--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-08 | Build 6e5e3a8d7a54 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-08 | Build 13804d1ddf41 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-08 | Build 68307f4a2e38 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-08 | Build f40aa48add25 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-09 | Build 81aae75c545a | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-09 | Build dc5ec3b9dad4 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4771" uniqueCount="684">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4809" uniqueCount="689">
   <si>
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-09 | Build 9605c73536cc | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-09 | Build 9eb4a3ae5345 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -1241,6 +1241,18 @@
     <t>Яндекс утвердил дивиденды по итогам 2025 года — выплаты составят 110 ₽ за акцию - RB.RU</t>
   </si>
   <si>
+    <t>DL-ac8ca50a646028ad</t>
+  </si>
+  <si>
+    <t>Агентство Бизнес Новостей</t>
+  </si>
+  <si>
+    <t>https://abn.agency/2026/04/20/ozon-sokratil-obem-obligaczionnogo-razmeshheniya-do-odnogo-vypuska/</t>
+  </si>
+  <si>
+    <t>Ozon сократил объем облигационного размещения до одного выпуска - Агентство Бизнес Новостей</t>
+  </si>
+  <si>
     <t>DL-c10daba8af8e67d8</t>
   </si>
   <si>
@@ -1253,7 +1265,7 @@
     <t>https://rb.ru/news/vk-prodal-25-akcij-tochka-banka-sdelku-ocenili-v-212-mlrd-vdvoe-vyshe-iznachalnoj-stoimosti-bumag/</t>
   </si>
   <si>
-    <t>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.ru</t>
+    <t>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.RU</t>
   </si>
   <si>
     <t>DL-4774de17c61c14e4</t>
@@ -2026,6 +2038,10 @@
   <si>
     <t>https://rb.ru/news/yandeks-odobril-dividendy-po-itogam-2025-go-vyplaty-sostavyat-110-za-akciyu-pochti-na-40-vyshe-chem-v-proshlom-godu/
 https://news.google.com/rss/articles/CBMi0AFBVV95cUxPM0l6REZfX1FWR3FiY1RBQlJUbzdaNDVTZTB5UklOalA3Vk1qYzRsQWhkZDNScTZWOHVaY0hNaTNRdDNHWU1jR1hhUV9GT1dES3daWVFhTFJ3M3lHTmJSSnZzN19ETGtJbExzNk0ybFdHdWs2ZkprOUd5X25HYWFnb29qZTRMMDBidkhaRG01WTNSMGMxUHJQS1k2Y19Za2NLQlExZWFyUk94aUZGcTVKZ2toSWxBVkg2WFFic3hxcHFQNEphVmlFZkpoMXJLQVB1?oc=5</t>
+  </si>
+  <si>
+    <t>https://abn.agency/2026/04/20/ozon-sokratil-obem-obligaczionnogo-razmeshheniya-do-odnogo-vypuska/
+https://news.google.com/rss/articles/CBMingFBVV95cUxNdHA3SkxPWmM3TDVwb3FvMmZ1aFRGMC0xSm9GUmx3aGJqZ0s1eV9MblNDQldVTThJMFFHbXI1RDZ5R0Q2RHEzYjM3ZjhxTnNOSERJTklsdGFLUmd2VzhLUVh6WHMxZGs1MjRRaWxzR3JEcEVmZWs4MURzc25sNmZXU2o5aEJ0VWk5dWdpdWx6dmF1UTRnX2wwMWsteDdPUQ?oc=5</t>
   </si>
   <si>
     <t>https://rb.ru/news/vk-prodal-25-akcij-tochka-banka-sdelku-ocenili-v-212-mlrd-vdvoe-vyshe-iznachalnoj-stoimosti-bumag/
@@ -2283,8 +2299,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DealsTable" displayName="DealsTable" ref="A6:AT108" totalsRowShown="0">
-  <autoFilter ref="A6:AT108"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="DealsTable" displayName="DealsTable" ref="A6:AT109" totalsRowShown="0">
+  <autoFilter ref="A6:AT109"/>
   <tableColumns count="46">
     <tableColumn id="1" name="Deal ID"/>
     <tableColumn id="2" name="Announced Date"/>
@@ -2385,8 +2401,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:K140" totalsRowShown="0">
-  <autoFilter ref="A6:K140"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:K141" totalsRowShown="0">
+  <autoFilter ref="A6:K141"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Deal ID"/>
     <tableColumn id="2" name="Date"/>
@@ -2779,7 +2795,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="5">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B7" s="5">
         <v>30</v>
@@ -2788,13 +2804,13 @@
         <v>8</v>
       </c>
       <c r="D7" s="5">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E7" s="5">
         <v>21</v>
       </c>
       <c r="F7" s="5">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7" s="5">
         <v>10</v>
@@ -3129,7 +3145,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT108"/>
+  <dimension ref="A1:AT109"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="5" width="16.7109375" customWidth="1"/>
@@ -10769,10 +10785,10 @@
         <v>407</v>
       </c>
       <c r="B84" s="8">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D84" s="9" t="s">
         <v>118</v>
@@ -10781,49 +10797,43 @@
         <v>119</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>408</v>
+        <v>338</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H84" s="9" t="s">
-        <v>409</v>
+        <v>33</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="J84" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="K84" s="10">
-        <v>21200000000</v>
-      </c>
       <c r="M84" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="N84" s="11">
-        <v>0.25</v>
+        <v>34</v>
       </c>
       <c r="O84" s="9" t="s">
-        <v>296</v>
+        <v>33</v>
       </c>
       <c r="P84" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q84" s="9" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="R84" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S84" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U84" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X84" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AB84" s="9" t="s">
         <v>33</v>
@@ -10847,33 +10857,33 @@
         <v>102</v>
       </c>
       <c r="AO84" s="9">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AP84" s="9" t="s">
         <v>122</v>
       </c>
       <c r="AQ84" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AR84" s="9" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="AS84" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="AT84" s="9" t="s">
         <v>410</v>
-      </c>
-      <c r="AT84" s="9" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="85" spans="1:46">
       <c r="A85" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B85" s="8">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>118</v>
@@ -10882,43 +10892,49 @@
         <v>119</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>33</v>
+        <v>413</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="J85" s="9" t="s">
         <v>34</v>
       </c>
+      <c r="K85" s="10">
+        <v>21200000000</v>
+      </c>
       <c r="M85" s="9" t="s">
-        <v>34</v>
+        <v>42</v>
+      </c>
+      <c r="N85" s="11">
+        <v>0.25</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>33</v>
+        <v>296</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q85" s="9" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="R85" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S85" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U85" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X85" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AB85" s="9" t="s">
         <v>33</v>
@@ -10942,33 +10958,33 @@
         <v>102</v>
       </c>
       <c r="AO85" s="9">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AP85" s="9" t="s">
         <v>122</v>
       </c>
       <c r="AQ85" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AR85" s="9" t="s">
-        <v>233</v>
+        <v>404</v>
       </c>
       <c r="AS85" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AT85" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="86" spans="1:46">
       <c r="A86" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B86" s="8">
         <v>46122</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D86" s="9" t="s">
         <v>118</v>
@@ -10977,7 +10993,7 @@
         <v>119</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>338</v>
+        <v>413</v>
       </c>
       <c r="G86" s="9" t="s">
         <v>33</v>
@@ -10986,7 +11002,7 @@
         <v>33</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="J86" s="9" t="s">
         <v>34</v>
@@ -11001,22 +11017,22 @@
         <v>34</v>
       </c>
       <c r="Q86" s="9" t="s">
-        <v>353</v>
+        <v>98</v>
       </c>
       <c r="R86" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S86" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U86" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X86" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AB86" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AD86" s="9" t="s">
         <v>34</v>
@@ -11034,10 +11050,10 @@
         <v>101</v>
       </c>
       <c r="AN86" s="9" t="s">
-        <v>164</v>
+        <v>102</v>
       </c>
       <c r="AO86" s="9">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="AP86" s="9" t="s">
         <v>122</v>
@@ -11046,30 +11062,30 @@
         <v>1</v>
       </c>
       <c r="AR86" s="9" t="s">
-        <v>183</v>
+        <v>233</v>
       </c>
       <c r="AS86" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AT86" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="87" spans="1:46">
       <c r="A87" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B87" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>118</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>187</v>
+        <v>119</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>338</v>
@@ -11081,16 +11097,13 @@
         <v>33</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="J87" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="K87" s="10">
-        <v>15000000000</v>
+        <v>34</v>
       </c>
       <c r="M87" s="9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>33</v>
@@ -11099,22 +11112,22 @@
         <v>34</v>
       </c>
       <c r="Q87" s="9" t="s">
-        <v>98</v>
+        <v>353</v>
       </c>
       <c r="R87" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S87" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U87" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X87" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AB87" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AD87" s="9" t="s">
         <v>34</v>
@@ -11132,10 +11145,10 @@
         <v>101</v>
       </c>
       <c r="AN87" s="9" t="s">
-        <v>102</v>
+        <v>164</v>
       </c>
       <c r="AO87" s="9">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="AP87" s="9" t="s">
         <v>122</v>
@@ -11144,18 +11157,18 @@
         <v>1</v>
       </c>
       <c r="AR87" s="9" t="s">
-        <v>400</v>
+        <v>183</v>
       </c>
       <c r="AS87" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AT87" s="9" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="88" spans="1:46">
       <c r="A88" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B88" s="8">
         <v>46115</v>
@@ -11182,10 +11195,13 @@
         <v>96</v>
       </c>
       <c r="J88" s="9" t="s">
-        <v>34</v>
+        <v>97</v>
+      </c>
+      <c r="K88" s="10">
+        <v>15000000000</v>
       </c>
       <c r="M88" s="9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="O88" s="9" t="s">
         <v>33</v>
@@ -11239,21 +11255,21 @@
         <v>1</v>
       </c>
       <c r="AR88" s="9" t="s">
-        <v>258</v>
+        <v>400</v>
       </c>
       <c r="AS88" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AT88" s="9" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="89" spans="1:46">
       <c r="A89" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B89" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="C89" s="9" t="s">
         <v>6</v>
@@ -11262,10 +11278,10 @@
         <v>118</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>409</v>
+        <v>338</v>
       </c>
       <c r="G89" s="9" t="s">
         <v>33</v>
@@ -11277,13 +11293,10 @@
         <v>96</v>
       </c>
       <c r="J89" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="K89" s="10">
-        <v>10000000000</v>
+        <v>34</v>
       </c>
       <c r="M89" s="9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>33</v>
@@ -11337,7 +11350,7 @@
         <v>1</v>
       </c>
       <c r="AR89" s="9" t="s">
-        <v>425</v>
+        <v>258</v>
       </c>
       <c r="AS89" s="9" t="s">
         <v>426</v>
@@ -11363,7 +11376,7 @@
         <v>119</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G90" s="9" t="s">
         <v>33</v>
@@ -11375,10 +11388,13 @@
         <v>96</v>
       </c>
       <c r="J90" s="9" t="s">
-        <v>34</v>
+        <v>97</v>
+      </c>
+      <c r="K90" s="10">
+        <v>10000000000</v>
       </c>
       <c r="M90" s="9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="O90" s="9" t="s">
         <v>33</v>
@@ -11432,33 +11448,33 @@
         <v>1</v>
       </c>
       <c r="AR90" s="9" t="s">
-        <v>233</v>
+        <v>429</v>
       </c>
       <c r="AS90" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AT90" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="91" spans="1:46">
       <c r="A91" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B91" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="C91" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>32</v>
+        <v>413</v>
       </c>
       <c r="G91" s="9" t="s">
         <v>33</v>
@@ -11470,13 +11486,10 @@
         <v>96</v>
       </c>
       <c r="J91" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="K91" s="10">
-        <v>7000000000</v>
+        <v>34</v>
       </c>
       <c r="M91" s="9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>33</v>
@@ -11493,9 +11506,6 @@
       <c r="S91" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="T91" s="11">
-        <v>0.15</v>
-      </c>
       <c r="U91" s="9" t="s">
         <v>34</v>
       </c>
@@ -11521,33 +11531,33 @@
         <v>101</v>
       </c>
       <c r="AN91" s="9" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="AO91" s="9">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AP91" s="9" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="AQ91" s="9">
         <v>1</v>
       </c>
       <c r="AR91" s="9" t="s">
-        <v>115</v>
+        <v>233</v>
       </c>
       <c r="AS91" s="9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AT91" s="9" t="s">
-        <v>50</v>
+        <v>434</v>
       </c>
     </row>
     <row r="92" spans="1:46">
       <c r="A92" s="9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B92" s="8">
-        <v>45923</v>
+        <v>46080</v>
       </c>
       <c r="C92" s="9" t="s">
         <v>6</v>
@@ -11556,7 +11566,7 @@
         <v>108</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>32</v>
@@ -11574,7 +11584,7 @@
         <v>97</v>
       </c>
       <c r="K92" s="10">
-        <v>6000000000</v>
+        <v>7000000000</v>
       </c>
       <c r="M92" s="9" t="s">
         <v>42</v>
@@ -11595,13 +11605,13 @@
         <v>34</v>
       </c>
       <c r="T92" s="11">
-        <v>0.154</v>
+        <v>0.15</v>
       </c>
       <c r="U92" s="9" t="s">
         <v>34</v>
       </c>
       <c r="X92" s="9" t="s">
-        <v>434</v>
+        <v>34</v>
       </c>
       <c r="AB92" s="9" t="s">
         <v>33</v>
@@ -11637,18 +11647,18 @@
         <v>115</v>
       </c>
       <c r="AS92" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AT92" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:46">
       <c r="A93" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B93" s="8">
-        <v>45729</v>
+        <v>45923</v>
       </c>
       <c r="C93" s="9" t="s">
         <v>6</v>
@@ -11657,10 +11667,10 @@
         <v>108</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>187</v>
+        <v>37</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G93" s="9" t="s">
         <v>33</v>
@@ -11669,13 +11679,16 @@
         <v>33</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="J93" s="9" t="s">
-        <v>34</v>
+        <v>97</v>
+      </c>
+      <c r="K93" s="10">
+        <v>6000000000</v>
       </c>
       <c r="M93" s="9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>33</v>
@@ -11692,11 +11705,14 @@
       <c r="S93" s="9" t="s">
         <v>34</v>
       </c>
+      <c r="T93" s="11">
+        <v>0.154</v>
+      </c>
       <c r="U93" s="9" t="s">
         <v>34</v>
       </c>
       <c r="X93" s="9" t="s">
-        <v>34</v>
+        <v>438</v>
       </c>
       <c r="AB93" s="9" t="s">
         <v>33</v>
@@ -11729,39 +11745,39 @@
         <v>1</v>
       </c>
       <c r="AR93" s="9" t="s">
-        <v>327</v>
+        <v>115</v>
       </c>
       <c r="AS93" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AT93" s="9" t="s">
-        <v>438</v>
+        <v>51</v>
       </c>
     </row>
     <row r="94" spans="1:46">
       <c r="A94" s="9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B94" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D94" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>37</v>
+        <v>187</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H94" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I94" s="9" t="s">
         <v>109</v>
@@ -11773,25 +11789,25 @@
         <v>34</v>
       </c>
       <c r="O94" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P94" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q94" s="9" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="R94" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S94" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U94" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X94" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AB94" s="9" t="s">
         <v>33</v>
@@ -11812,10 +11828,10 @@
         <v>101</v>
       </c>
       <c r="AN94" s="9" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="AO94" s="9">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AP94" s="9" t="s">
         <v>103</v>
@@ -11824,78 +11840,75 @@
         <v>1</v>
       </c>
       <c r="AR94" s="9" t="s">
-        <v>115</v>
+        <v>327</v>
       </c>
       <c r="AS94" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AT94" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="95" spans="1:46">
       <c r="A95" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B95" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D95" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>187</v>
+        <v>37</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I95" s="9" t="s">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="J95" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="K95" s="10">
-        <v>3000000000</v>
+        <v>34</v>
       </c>
       <c r="M95" s="9" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P95" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q95" s="9" t="s">
-        <v>98</v>
+        <v>133</v>
       </c>
       <c r="R95" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S95" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="U95" s="9" t="s">
-        <v>443</v>
+        <v>33</v>
       </c>
       <c r="X95" s="9" t="s">
-        <v>434</v>
+        <v>33</v>
       </c>
       <c r="AB95" s="9" t="s">
         <v>33</v>
       </c>
       <c r="AD95" s="9" t="s">
-        <v>444</v>
+        <v>34</v>
       </c>
       <c r="AH95" s="9" t="s">
         <v>34</v>
@@ -11910,10 +11923,10 @@
         <v>101</v>
       </c>
       <c r="AN95" s="9" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="AO95" s="9">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AP95" s="9" t="s">
         <v>103</v>
@@ -11925,18 +11938,18 @@
         <v>115</v>
       </c>
       <c r="AS95" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="AT95" s="9" t="s">
         <v>445</v>
-      </c>
-      <c r="AT95" s="9" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="96" spans="1:46">
       <c r="A96" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B96" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="C96" s="9" t="s">
         <v>6</v>
@@ -11945,7 +11958,7 @@
         <v>108</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>37</v>
+        <v>187</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>32</v>
@@ -11957,13 +11970,13 @@
         <v>33</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="J96" s="9" t="s">
         <v>97</v>
       </c>
       <c r="K96" s="10">
-        <v>4000000000</v>
+        <v>3000000000</v>
       </c>
       <c r="M96" s="9" t="s">
         <v>42</v>
@@ -11983,20 +11996,17 @@
       <c r="S96" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="T96" s="11">
-        <v>0.15</v>
-      </c>
       <c r="U96" s="9" t="s">
-        <v>34</v>
+        <v>447</v>
       </c>
       <c r="X96" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="AB96" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD96" s="9" t="s">
         <v>448</v>
-      </c>
-      <c r="AB96" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="AD96" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="AH96" s="9" t="s">
         <v>34</v>
@@ -12037,7 +12047,7 @@
         <v>451</v>
       </c>
       <c r="B97" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="C97" s="9" t="s">
         <v>6</v>
@@ -12046,7 +12056,7 @@
         <v>108</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>187</v>
+        <v>37</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>32</v>
@@ -12064,7 +12074,7 @@
         <v>97</v>
       </c>
       <c r="K97" s="10">
-        <v>3000000000</v>
+        <v>4000000000</v>
       </c>
       <c r="M97" s="9" t="s">
         <v>42</v>
@@ -12084,11 +12094,14 @@
       <c r="S97" s="9" t="s">
         <v>34</v>
       </c>
+      <c r="T97" s="11">
+        <v>0.15</v>
+      </c>
       <c r="U97" s="9" t="s">
         <v>34</v>
       </c>
       <c r="X97" s="9" t="s">
-        <v>34</v>
+        <v>452</v>
       </c>
       <c r="AB97" s="9" t="s">
         <v>33</v>
@@ -12124,36 +12137,36 @@
         <v>115</v>
       </c>
       <c r="AS97" s="9" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AT97" s="9" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="98" spans="1:46">
       <c r="A98" s="9" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B98" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D98" s="9" t="s">
         <v>108</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>37</v>
+        <v>187</v>
       </c>
       <c r="F98" s="9" t="s">
-        <v>454</v>
+        <v>32</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>455</v>
+        <v>33</v>
       </c>
       <c r="H98" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I98" s="9" t="s">
         <v>96</v>
@@ -12161,29 +12174,32 @@
       <c r="J98" s="9" t="s">
         <v>97</v>
       </c>
+      <c r="K98" s="10">
+        <v>3000000000</v>
+      </c>
       <c r="M98" s="9" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="O98" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P98" s="9" t="s">
         <v>34</v>
       </c>
       <c r="Q98" s="9" t="s">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="R98" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="S98" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U98" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X98" s="9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AB98" s="9" t="s">
         <v>33</v>
@@ -12204,10 +12220,10 @@
         <v>101</v>
       </c>
       <c r="AN98" s="9" t="s">
-        <v>102</v>
+        <v>35</v>
       </c>
       <c r="AO98" s="9">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AP98" s="9" t="s">
         <v>103</v>
@@ -12222,15 +12238,15 @@
         <v>456</v>
       </c>
       <c r="AT98" s="9" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
     </row>
     <row r="99" spans="1:46">
       <c r="A99" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B99" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="C99" s="9" t="s">
         <v>4</v>
@@ -12239,38 +12255,35 @@
         <v>108</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F99" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="G99" s="9" t="s">
         <v>459</v>
       </c>
-      <c r="G99" s="9" t="s">
-        <v>460</v>
-      </c>
       <c r="H99" s="9" t="s">
-        <v>461</v>
+        <v>34</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="J99" s="9" t="s">
-        <v>462</v>
-      </c>
-      <c r="K99" s="10">
-        <v>28000000000</v>
+        <v>97</v>
       </c>
       <c r="M99" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="N99" s="11">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>463</v>
+        <v>34</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>34</v>
       </c>
+      <c r="Q99" s="9" t="s">
+        <v>133</v>
+      </c>
       <c r="R99" s="9" t="s">
         <v>33</v>
       </c>
@@ -12287,54 +12300,48 @@
         <v>33</v>
       </c>
       <c r="AD99" s="9" t="s">
-        <v>464</v>
-      </c>
-      <c r="AE99" s="10">
-        <v>3653708000</v>
-      </c>
-      <c r="AG99" s="8">
-        <v>44957</v>
+        <v>34</v>
       </c>
       <c r="AH99" s="9" t="s">
-        <v>121</v>
+        <v>34</v>
       </c>
       <c r="AK99" s="9" t="s">
-        <v>465</v>
+        <v>34</v>
       </c>
       <c r="AL99" s="9" t="s">
-        <v>466</v>
+        <v>34</v>
       </c>
       <c r="AM99" s="9" t="s">
-        <v>467</v>
+        <v>101</v>
       </c>
       <c r="AN99" s="9" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="AO99" s="9">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AP99" s="9" t="s">
         <v>103</v>
       </c>
       <c r="AQ99" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR99" s="9" t="s">
-        <v>468</v>
+        <v>115</v>
       </c>
       <c r="AS99" s="9" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="AT99" s="9" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
     </row>
     <row r="100" spans="1:46">
       <c r="A100" s="9" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="B100" s="8">
-        <v>44707</v>
+        <v>45190</v>
       </c>
       <c r="C100" s="9" t="s">
         <v>4</v>
@@ -12346,25 +12353,22 @@
         <v>46</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="H100" s="9" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="I100" s="9" t="s">
         <v>109</v>
       </c>
       <c r="J100" s="9" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="K100" s="10">
-        <v>61000000000</v>
-      </c>
-      <c r="L100" s="10">
-        <v>69000000000</v>
+        <v>28000000000</v>
       </c>
       <c r="M100" s="9" t="s">
         <v>121</v>
@@ -12373,13 +12377,10 @@
         <v>1</v>
       </c>
       <c r="O100" s="9" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="P100" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="Q100" s="9" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="R100" s="9" t="s">
         <v>33</v>
@@ -12397,34 +12398,25 @@
         <v>33</v>
       </c>
       <c r="AD100" s="9" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="AE100" s="10">
-        <v>12851000000</v>
-      </c>
-      <c r="AF100" s="10">
-        <v>2966000000</v>
+        <v>3653708000</v>
       </c>
       <c r="AG100" s="8">
-        <v>44589</v>
+        <v>44957</v>
       </c>
       <c r="AH100" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="AI100" s="12">
-        <v>5.369231966383939</v>
-      </c>
-      <c r="AJ100" s="12">
-        <v>23.26365475387728</v>
-      </c>
       <c r="AK100" s="9" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="AL100" s="9" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="AM100" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="AN100" s="9" t="s">
         <v>35</v>
@@ -12439,21 +12431,21 @@
         <v>2</v>
       </c>
       <c r="AR100" s="9" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="AS100" s="9" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="AT100" s="9" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="101" spans="1:46">
       <c r="A101" s="9" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="B101" s="8">
-        <v>44640</v>
+        <v>44707</v>
       </c>
       <c r="C101" s="9" t="s">
         <v>4</v>
@@ -12465,22 +12457,25 @@
         <v>46</v>
       </c>
       <c r="F101" s="9" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="I101" s="9" t="s">
         <v>109</v>
       </c>
       <c r="J101" s="9" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="K101" s="10">
-        <v>10400000000</v>
+        <v>61000000000</v>
+      </c>
+      <c r="L101" s="10">
+        <v>69000000000</v>
       </c>
       <c r="M101" s="9" t="s">
         <v>121</v>
@@ -12489,10 +12484,13 @@
         <v>1</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>463</v>
+        <v>478</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>34</v>
+        <v>479</v>
+      </c>
+      <c r="Q101" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="R101" s="9" t="s">
         <v>33</v>
@@ -12510,25 +12508,34 @@
         <v>33</v>
       </c>
       <c r="AD101" s="9" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AE101" s="10">
-        <v>592200000</v>
+        <v>12851000000</v>
+      </c>
+      <c r="AF101" s="10">
+        <v>2966000000</v>
       </c>
       <c r="AG101" s="8">
-        <v>44592</v>
+        <v>44589</v>
       </c>
       <c r="AH101" s="9" t="s">
         <v>121</v>
       </c>
+      <c r="AI101" s="12">
+        <v>5.369231966383939</v>
+      </c>
+      <c r="AJ101" s="12">
+        <v>23.26365475387728</v>
+      </c>
       <c r="AK101" s="9" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="AL101" s="9" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="AM101" s="9" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
       <c r="AN101" s="9" t="s">
         <v>35</v>
@@ -12543,21 +12550,21 @@
         <v>2</v>
       </c>
       <c r="AR101" s="9" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="AS101" s="9" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="AT101" s="9" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="102" spans="1:46">
       <c r="A102" s="9" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B102" s="8">
-        <v>44592</v>
+        <v>44640</v>
       </c>
       <c r="C102" s="9" t="s">
         <v>4</v>
@@ -12569,25 +12576,22 @@
         <v>46</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="H102" s="9" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="I102" s="9" t="s">
         <v>109</v>
       </c>
       <c r="J102" s="9" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="K102" s="10">
-        <v>16500000000</v>
-      </c>
-      <c r="L102" s="10">
-        <v>16500000000</v>
+        <v>10400000000</v>
       </c>
       <c r="M102" s="9" t="s">
         <v>121</v>
@@ -12596,7 +12600,7 @@
         <v>1</v>
       </c>
       <c r="O102" s="9" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="P102" s="9" t="s">
         <v>34</v>
@@ -12617,28 +12621,25 @@
         <v>33</v>
       </c>
       <c r="AD102" s="9" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="AE102" s="10">
-        <v>3217170000</v>
+        <v>592200000</v>
       </c>
       <c r="AG102" s="8">
-        <v>44561</v>
+        <v>44592</v>
       </c>
       <c r="AH102" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="AI102" s="12">
-        <v>5.128731151913017</v>
-      </c>
       <c r="AK102" s="9" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="AL102" s="9" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="AM102" s="9" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="AN102" s="9" t="s">
         <v>35</v>
@@ -12650,24 +12651,24 @@
         <v>103</v>
       </c>
       <c r="AQ102" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR102" s="9" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="AS102" s="9" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="AT102" s="9" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="103" spans="1:46">
       <c r="A103" s="9" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B103" s="8">
-        <v>44579</v>
+        <v>44592</v>
       </c>
       <c r="C103" s="9" t="s">
         <v>4</v>
@@ -12679,25 +12680,25 @@
         <v>46</v>
       </c>
       <c r="F103" s="9" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="I103" s="9" t="s">
         <v>109</v>
       </c>
       <c r="J103" s="9" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="K103" s="10">
-        <v>68700000000</v>
+        <v>16500000000</v>
       </c>
       <c r="L103" s="10">
-        <v>68700000000</v>
+        <v>16500000000</v>
       </c>
       <c r="M103" s="9" t="s">
         <v>121</v>
@@ -12706,13 +12707,10 @@
         <v>1</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>504</v>
-      </c>
-      <c r="Q103" s="9" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="R103" s="9" t="s">
         <v>33</v>
@@ -12730,28 +12728,28 @@
         <v>33</v>
       </c>
       <c r="AD103" s="9" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="AE103" s="10">
-        <v>8086000000</v>
+        <v>3217170000</v>
       </c>
       <c r="AG103" s="8">
-        <v>44196</v>
+        <v>44561</v>
       </c>
       <c r="AH103" s="9" t="s">
         <v>121</v>
       </c>
       <c r="AI103" s="12">
-        <v>8.496166213208014</v>
+        <v>5.128731151913017</v>
       </c>
       <c r="AK103" s="9" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="AL103" s="9" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="AM103" s="9" t="s">
-        <v>467</v>
+        <v>492</v>
       </c>
       <c r="AN103" s="9" t="s">
         <v>35</v>
@@ -12763,24 +12761,24 @@
         <v>103</v>
       </c>
       <c r="AQ103" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR103" s="9" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="AS103" s="9" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="AT103" s="9" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="104" spans="1:46">
       <c r="A104" s="9" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B104" s="8">
-        <v>44166</v>
+        <v>44579</v>
       </c>
       <c r="C104" s="9" t="s">
         <v>4</v>
@@ -12792,25 +12790,25 @@
         <v>46</v>
       </c>
       <c r="F104" s="9" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="I104" s="9" t="s">
         <v>109</v>
       </c>
       <c r="J104" s="9" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="K104" s="10">
-        <v>27700000000</v>
+        <v>68700000000</v>
       </c>
       <c r="L104" s="10">
-        <v>27700000000</v>
+        <v>68700000000</v>
       </c>
       <c r="M104" s="9" t="s">
         <v>121</v>
@@ -12819,10 +12817,13 @@
         <v>1</v>
       </c>
       <c r="O104" s="9" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="P104" s="9" t="s">
-        <v>34</v>
+        <v>508</v>
+      </c>
+      <c r="Q104" s="9" t="s">
+        <v>133</v>
       </c>
       <c r="R104" s="9" t="s">
         <v>33</v>
@@ -12840,28 +12841,28 @@
         <v>33</v>
       </c>
       <c r="AD104" s="9" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="AE104" s="10">
-        <v>630422000</v>
+        <v>8086000000</v>
       </c>
       <c r="AG104" s="8">
-        <v>43861</v>
+        <v>44196</v>
       </c>
       <c r="AH104" s="9" t="s">
         <v>121</v>
       </c>
       <c r="AI104" s="12">
-        <v>43.93882193197572</v>
+        <v>8.496166213208014</v>
       </c>
       <c r="AK104" s="9" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="AL104" s="9" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="AM104" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="AN104" s="9" t="s">
         <v>35</v>
@@ -12876,21 +12877,21 @@
         <v>2</v>
       </c>
       <c r="AR104" s="9" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="AS104" s="9" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="AT104" s="9" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="105" spans="1:46">
       <c r="A105" s="9" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B105" s="8">
-        <v>44131</v>
+        <v>44166</v>
       </c>
       <c r="C105" s="9" t="s">
         <v>4</v>
@@ -12902,22 +12903,25 @@
         <v>46</v>
       </c>
       <c r="F105" s="9" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="I105" s="9" t="s">
         <v>109</v>
       </c>
       <c r="J105" s="9" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="K105" s="10">
-        <v>35000000000</v>
+        <v>27700000000</v>
+      </c>
+      <c r="L105" s="10">
+        <v>27700000000</v>
       </c>
       <c r="M105" s="9" t="s">
         <v>121</v>
@@ -12926,7 +12930,7 @@
         <v>1</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>296</v>
+        <v>478</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>34</v>
@@ -12947,25 +12951,28 @@
         <v>33</v>
       </c>
       <c r="AD105" s="9" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="AE105" s="10">
-        <v>3162666000</v>
+        <v>630422000</v>
       </c>
       <c r="AG105" s="8">
-        <v>43918</v>
+        <v>43861</v>
       </c>
       <c r="AH105" s="9" t="s">
         <v>121</v>
       </c>
+      <c r="AI105" s="12">
+        <v>43.93882193197572</v>
+      </c>
       <c r="AK105" s="9" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="AL105" s="9" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="AM105" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="AN105" s="9" t="s">
         <v>35</v>
@@ -12980,21 +12987,21 @@
         <v>2</v>
       </c>
       <c r="AR105" s="9" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="AS105" s="9" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="AT105" s="9" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="106" spans="1:46">
       <c r="A106" s="9" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B106" s="8">
-        <v>43626</v>
+        <v>44131</v>
       </c>
       <c r="C106" s="9" t="s">
         <v>4</v>
@@ -13006,25 +13013,22 @@
         <v>46</v>
       </c>
       <c r="F106" s="9" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>513</v>
+        <v>526</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="I106" s="9" t="s">
         <v>109</v>
       </c>
       <c r="J106" s="9" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="K106" s="10">
-        <v>15700000000</v>
-      </c>
-      <c r="L106" s="10">
-        <v>15700000000</v>
+        <v>35000000000</v>
       </c>
       <c r="M106" s="9" t="s">
         <v>121</v>
@@ -13054,28 +13058,25 @@
         <v>33</v>
       </c>
       <c r="AD106" s="9" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="AE106" s="10">
-        <v>1159000000</v>
+        <v>3162666000</v>
       </c>
       <c r="AG106" s="8">
-        <v>43465</v>
+        <v>43918</v>
       </c>
       <c r="AH106" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="AI106" s="12">
-        <v>13.54616048317515</v>
-      </c>
       <c r="AK106" s="9" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="AL106" s="9" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AM106" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="AN106" s="9" t="s">
         <v>35</v>
@@ -13090,21 +13091,21 @@
         <v>2</v>
       </c>
       <c r="AR106" s="9" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c r="AS106" s="9" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="AT106" s="9" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="107" spans="1:46">
       <c r="A107" s="9" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B107" s="8">
-        <v>43401</v>
+        <v>43626</v>
       </c>
       <c r="C107" s="9" t="s">
         <v>4</v>
@@ -13116,25 +13117,25 @@
         <v>46</v>
       </c>
       <c r="F107" s="9" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="I107" s="9" t="s">
         <v>109</v>
       </c>
       <c r="J107" s="9" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="K107" s="10">
-        <v>34000000000</v>
+        <v>15700000000</v>
       </c>
       <c r="L107" s="10">
-        <v>34000000000</v>
+        <v>15700000000</v>
       </c>
       <c r="M107" s="9" t="s">
         <v>121</v>
@@ -13143,7 +13144,7 @@
         <v>1</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>463</v>
+        <v>296</v>
       </c>
       <c r="P107" s="9" t="s">
         <v>34</v>
@@ -13164,28 +13165,28 @@
         <v>33</v>
       </c>
       <c r="AD107" s="9" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="AE107" s="10">
-        <v>2920461000</v>
+        <v>1159000000</v>
       </c>
       <c r="AG107" s="8">
-        <v>43159</v>
+        <v>43465</v>
       </c>
       <c r="AH107" s="9" t="s">
         <v>121</v>
       </c>
       <c r="AI107" s="12">
-        <v>11.64199761612978</v>
+        <v>13.54616048317515</v>
       </c>
       <c r="AK107" s="9" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="AL107" s="9" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="AM107" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="AN107" s="9" t="s">
         <v>35</v>
@@ -13200,21 +13201,21 @@
         <v>2</v>
       </c>
       <c r="AR107" s="9" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="AS107" s="9" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="AT107" s="9" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="108" spans="1:46">
       <c r="A108" s="9" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B108" s="8">
-        <v>42534</v>
+        <v>43401</v>
       </c>
       <c r="C108" s="9" t="s">
         <v>4</v>
@@ -13226,25 +13227,25 @@
         <v>46</v>
       </c>
       <c r="F108" s="9" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>503</v>
+        <v>542</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="I108" s="9" t="s">
         <v>109</v>
       </c>
       <c r="J108" s="9" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="K108" s="10">
-        <v>26200000000</v>
+        <v>34000000000</v>
       </c>
       <c r="L108" s="10">
-        <v>26200000000</v>
+        <v>34000000000</v>
       </c>
       <c r="M108" s="9" t="s">
         <v>121</v>
@@ -13253,7 +13254,7 @@
         <v>1</v>
       </c>
       <c r="O108" s="9" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="P108" s="9" t="s">
         <v>34</v>
@@ -13274,34 +13275,28 @@
         <v>33</v>
       </c>
       <c r="AD108" s="9" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="AE108" s="10">
-        <v>2990911000</v>
-      </c>
-      <c r="AF108" s="10">
-        <v>254472000</v>
+        <v>2920461000</v>
       </c>
       <c r="AG108" s="8">
-        <v>42369</v>
+        <v>43159</v>
       </c>
       <c r="AH108" s="9" t="s">
         <v>121</v>
       </c>
       <c r="AI108" s="12">
-        <v>8.759872828044699</v>
-      </c>
-      <c r="AJ108" s="12">
-        <v>102.9582822471628</v>
+        <v>11.64199761612978</v>
       </c>
       <c r="AK108" s="9" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="AL108" s="9" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="AM108" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="AN108" s="9" t="s">
         <v>35</v>
@@ -13316,13 +13311,129 @@
         <v>2</v>
       </c>
       <c r="AR108" s="9" t="s">
-        <v>508</v>
+        <v>546</v>
       </c>
       <c r="AS108" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="AT108" s="9" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="109" spans="1:46">
+      <c r="A109" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="B109" s="8">
+        <v>42534</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="E109" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F109" s="9" t="s">
         <v>550</v>
       </c>
-      <c r="AT108" s="9" t="s">
+      <c r="G109" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="I109" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="J109" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="K109" s="10">
+        <v>26200000000</v>
+      </c>
+      <c r="L109" s="10">
+        <v>26200000000</v>
+      </c>
+      <c r="M109" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="N109" s="11">
+        <v>1</v>
+      </c>
+      <c r="O109" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="P109" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="R109" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="S109" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="U109" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="X109" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB109" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="AD109" s="9" t="s">
         <v>551</v>
+      </c>
+      <c r="AE109" s="10">
+        <v>2990911000</v>
+      </c>
+      <c r="AF109" s="10">
+        <v>254472000</v>
+      </c>
+      <c r="AG109" s="8">
+        <v>42369</v>
+      </c>
+      <c r="AH109" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="AI109" s="12">
+        <v>8.759872828044699</v>
+      </c>
+      <c r="AJ109" s="12">
+        <v>102.9582822471628</v>
+      </c>
+      <c r="AK109" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="AL109" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="AM109" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="AN109" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO109" s="9">
+        <v>100</v>
+      </c>
+      <c r="AP109" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="AQ109" s="9">
+        <v>2</v>
+      </c>
+      <c r="AR109" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="AS109" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="AT109" s="9" t="s">
+        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -13412,8 +13523,8 @@
     <hyperlink ref="AS84" r:id="rId79"/>
     <hyperlink ref="AS85" r:id="rId80"/>
     <hyperlink ref="AS86" r:id="rId81"/>
-    <hyperlink ref="AR87" r:id="rId82"/>
-    <hyperlink ref="AS87" r:id="rId83"/>
+    <hyperlink ref="AS87" r:id="rId82"/>
+    <hyperlink ref="AR88" r:id="rId83"/>
     <hyperlink ref="AS88" r:id="rId84"/>
     <hyperlink ref="AS89" r:id="rId85"/>
     <hyperlink ref="AS90" r:id="rId86"/>
@@ -13435,10 +13546,11 @@
     <hyperlink ref="AS106" r:id="rId102"/>
     <hyperlink ref="AS107" r:id="rId103"/>
     <hyperlink ref="AS108" r:id="rId104"/>
+    <hyperlink ref="AS109" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId105"/>
+    <tablePart r:id="rId106"/>
   </tableParts>
 </worksheet>
 </file>
@@ -13463,7 +13575,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13481,7 +13593,7 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -13502,16 +13614,16 @@
         <v>54</v>
       </c>
       <c r="B6" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C6" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="D6" t="s">
         <v>81</v>
       </c>
       <c r="E6" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="F6" t="s">
         <v>27</v>
@@ -13520,13 +13632,13 @@
         <v>79</v>
       </c>
       <c r="H6" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="I6" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="J6" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="K6" t="s">
         <v>80</v>
@@ -13535,18 +13647,18 @@
         <v>86</v>
       </c>
       <c r="M6" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="N6" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="42" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C7" s="8">
         <v>45190</v>
@@ -13564,21 +13676,21 @@
         <v>3653708000</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="C8" s="8">
         <v>44707</v>
@@ -13608,21 +13720,21 @@
         <v>2966000000</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="42" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C9" s="8">
         <v>44640</v>
@@ -13640,21 +13752,21 @@
         <v>592200000</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="42" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C10" s="8">
         <v>44592</v>
@@ -13672,21 +13784,21 @@
         <v>3217170000</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="42" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="C11" s="8">
         <v>44579</v>
@@ -13707,21 +13819,21 @@
         <v>2734000000</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="N11" s="13" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="42" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C12" s="8">
         <v>44166</v>
@@ -13739,21 +13851,21 @@
         <v>630422000</v>
       </c>
       <c r="L12" s="13" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="42" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C13" s="8">
         <v>44131</v>
@@ -13771,21 +13883,21 @@
         <v>3162666000</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="N13" s="13" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="42" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="C14" s="8">
         <v>43626</v>
@@ -13803,21 +13915,21 @@
         <v>1159000000</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="42" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C15" s="8">
         <v>43401</v>
@@ -13838,21 +13950,21 @@
         <v>472442000</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="N15" s="13" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="42" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C16" s="8">
         <v>42534</v>
@@ -13876,13 +13988,13 @@
         <v>254472000</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
   </sheetData>
@@ -13930,7 +14042,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -13949,7 +14061,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -13974,13 +14086,13 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D6" t="s">
         <v>61</v>
       </c>
       <c r="E6" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="F6" t="s">
         <v>79</v>
@@ -13995,7 +14107,7 @@
         <v>28</v>
       </c>
       <c r="J6" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="K6" t="s">
         <v>83</v>
@@ -14004,13 +14116,13 @@
         <v>84</v>
       </c>
       <c r="M6" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="N6" t="s">
         <v>85</v>
       </c>
       <c r="O6" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -14033,7 +14145,7 @@
         <v>102</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K7" s="12">
         <f>IFERROR(IF(AND(D7&gt;0,F7&gt;0,E7=H7),D7/F7,""),"")</f>
@@ -14074,7 +14186,7 @@
         <v>164</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K8" s="12">
         <f>IFERROR(IF(AND(D8&gt;0,F8&gt;0,E8=H8),D8/F8,""),"")</f>
@@ -14115,7 +14227,7 @@
         <v>102</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K9" s="12">
         <f>IFERROR(IF(AND(D9&gt;0,F9&gt;0,E9=H9),D9/F9,""),"")</f>
@@ -14156,7 +14268,7 @@
         <v>164</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K10" s="12">
         <f>IFERROR(IF(AND(D10&gt;0,F10&gt;0,E10=H10),D10/F10,""),"")</f>
@@ -14197,7 +14309,7 @@
         <v>164</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K11" s="12">
         <f>IFERROR(IF(AND(D11&gt;0,F11&gt;0,E11=H11),D11/F11,""),"")</f>
@@ -14238,7 +14350,7 @@
         <v>164</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K12" s="12">
         <f>IFERROR(IF(AND(D12&gt;0,F12&gt;0,E12=H12),D12/F12,""),"")</f>
@@ -14279,7 +14391,7 @@
         <v>102</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K13" s="12">
         <f>IFERROR(IF(AND(D13&gt;0,F13&gt;0,E13=H13),D13/F13,""),"")</f>
@@ -14320,7 +14432,7 @@
         <v>35</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K14" s="12">
         <f>IFERROR(IF(AND(D14&gt;0,F14&gt;0,E14=H14),D14/F14,""),"")</f>
@@ -14361,7 +14473,7 @@
         <v>102</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K15" s="12">
         <f>IFERROR(IF(AND(D15&gt;0,F15&gt;0,E15=H15),D15/F15,""),"")</f>
@@ -14402,7 +14514,7 @@
         <v>164</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K16" s="12">
         <f>IFERROR(IF(AND(D16&gt;0,F16&gt;0,E16=H16),D16/F16,""),"")</f>
@@ -14443,7 +14555,7 @@
         <v>164</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K17" s="12">
         <f>IFERROR(IF(AND(D17&gt;0,F17&gt;0,E17=H17),D17/F17,""),"")</f>
@@ -14484,7 +14596,7 @@
         <v>102</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K18" s="12">
         <f>IFERROR(IF(AND(D18&gt;0,F18&gt;0,E18=H18),D18/F18,""),"")</f>
@@ -14525,7 +14637,7 @@
         <v>164</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K19" s="12">
         <f>IFERROR(IF(AND(D19&gt;0,F19&gt;0,E19=H19),D19/F19,""),"")</f>
@@ -14566,7 +14678,7 @@
         <v>164</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K20" s="12">
         <f>IFERROR(IF(AND(D20&gt;0,F20&gt;0,E20=H20),D20/F20,""),"")</f>
@@ -14607,7 +14719,7 @@
         <v>164</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K21" s="12">
         <f>IFERROR(IF(AND(D21&gt;0,F21&gt;0,E21=H21),D21/F21,""),"")</f>
@@ -14648,7 +14760,7 @@
         <v>164</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K22" s="12">
         <f>IFERROR(IF(AND(D22&gt;0,F22&gt;0,E22=H22),D22/F22,""),"")</f>
@@ -14689,7 +14801,7 @@
         <v>164</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K23" s="12">
         <f>IFERROR(IF(AND(D23&gt;0,F23&gt;0,E23=H23),D23/F23,""),"")</f>
@@ -14712,13 +14824,13 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="9" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B24" s="8">
         <v>46128</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>42</v>
@@ -14730,7 +14842,7 @@
         <v>102</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K24" s="12">
         <f>IFERROR(IF(AND(D24&gt;0,F24&gt;0,E24=H24),D24/F24,""),"")</f>
@@ -14753,7 +14865,7 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="9" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B25" s="8">
         <v>45642</v>
@@ -14771,7 +14883,7 @@
         <v>102</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K25" s="12">
         <f>IFERROR(IF(AND(D25&gt;0,F25&gt;0,E25=H25),D25/F25,""),"")</f>
@@ -14794,13 +14906,13 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="9" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="B26" s="8">
         <v>45288</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>34</v>
@@ -14812,7 +14924,7 @@
         <v>102</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K26" s="12">
         <f>IFERROR(IF(AND(D26&gt;0,F26&gt;0,E26=H26),D26/F26,""),"")</f>
@@ -14835,13 +14947,13 @@
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="9" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B27" s="8">
         <v>45190</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>121</v>
@@ -14856,7 +14968,7 @@
         <v>35</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K27" s="12">
         <f>IFERROR(IF(AND(D27&gt;0,F27&gt;0,E27=H27),D27/F27,""),"")</f>
@@ -14871,21 +14983,21 @@
         <v>NO</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="9" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B28" s="8">
         <v>44707</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D28" s="10">
         <v>69000000000</v>
@@ -14906,7 +15018,7 @@
         <v>35</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K28" s="12">
         <f>IFERROR(IF(AND(D28&gt;0,F28&gt;0,E28=H28),D28/F28,""),"")</f>
@@ -14921,21 +15033,21 @@
         <v>YES</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="O28" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="9" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B29" s="8">
         <v>44640</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>121</v>
@@ -14950,7 +15062,7 @@
         <v>35</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K29" s="12">
         <f>IFERROR(IF(AND(D29&gt;0,F29&gt;0,E29=H29),D29/F29,""),"")</f>
@@ -14965,21 +15077,21 @@
         <v>NO</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="9" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B30" s="8">
         <v>44592</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D30" s="10">
         <v>16500000000</v>
@@ -14997,7 +15109,7 @@
         <v>35</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="K30" s="12">
         <f>IFERROR(IF(AND(D30&gt;0,F30&gt;0,E30=H30),D30/F30,""),"")</f>
@@ -15012,21 +15124,21 @@
         <v>NO</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="O30" s="9" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="9" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B31" s="8">
         <v>44579</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D31" s="10">
         <v>68700000000</v>
@@ -15044,7 +15156,7 @@
         <v>35</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K31" s="12">
         <f>IFERROR(IF(AND(D31&gt;0,F31&gt;0,E31=H31),D31/F31,""),"")</f>
@@ -15059,21 +15171,21 @@
         <v>YES</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="9" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B32" s="8">
         <v>44166</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="D32" s="10">
         <v>27700000000</v>
@@ -15091,7 +15203,7 @@
         <v>35</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K32" s="12">
         <f>IFERROR(IF(AND(D32&gt;0,F32&gt;0,E32=H32),D32/F32,""),"")</f>
@@ -15106,21 +15218,21 @@
         <v>YES</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="O32" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="9" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B33" s="8">
         <v>44131</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>121</v>
@@ -15135,7 +15247,7 @@
         <v>35</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K33" s="12">
         <f>IFERROR(IF(AND(D33&gt;0,F33&gt;0,E33=H33),D33/F33,""),"")</f>
@@ -15150,21 +15262,21 @@
         <v>NO</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="9" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B34" s="8">
         <v>43626</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D34" s="10">
         <v>15700000000</v>
@@ -15182,7 +15294,7 @@
         <v>35</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K34" s="12">
         <f>IFERROR(IF(AND(D34&gt;0,F34&gt;0,E34=H34),D34/F34,""),"")</f>
@@ -15197,21 +15309,21 @@
         <v>YES</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="9" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B35" s="8">
         <v>43401</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D35" s="10">
         <v>34000000000</v>
@@ -15229,7 +15341,7 @@
         <v>35</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K35" s="12">
         <f>IFERROR(IF(AND(D35&gt;0,F35&gt;0,E35=H35),D35/F35,""),"")</f>
@@ -15244,21 +15356,21 @@
         <v>YES</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="9" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B36" s="8">
         <v>42534</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="D36" s="10">
         <v>26200000000</v>
@@ -15279,7 +15391,7 @@
         <v>35</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="K36" s="12">
         <f>IFERROR(IF(AND(D36&gt;0,F36&gt;0,E36=H36),D36/F36,""),"")</f>
@@ -15294,10 +15406,10 @@
         <v>YES</v>
       </c>
       <c r="N36" s="9" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -15314,7 +15426,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R140"/>
+  <dimension ref="A1:R141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -15333,7 +15445,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -15355,7 +15467,7 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -15377,7 +15489,7 @@
     </row>
     <row r="4" spans="1:18">
       <c r="M4" s="3" t="s">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -15396,43 +15508,43 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="E6" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="F6" t="s">
         <v>89</v>
       </c>
       <c r="G6" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="H6" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="I6" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="J6" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="K6" t="s">
         <v>30</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>671</v>
+        <v>676</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>23</v>
@@ -15452,7 +15564,7 @@
         <v>104</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>103</v>
@@ -15473,7 +15585,7 @@
         <v>106</v>
       </c>
       <c r="M7" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -15505,7 +15617,7 @@
         <v>104</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>103</v>
@@ -15526,7 +15638,7 @@
         <v>112</v>
       </c>
       <c r="M8" t="s">
-        <v>676</v>
+        <v>681</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -15558,7 +15670,7 @@
         <v>115</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>103</v>
@@ -15579,7 +15691,7 @@
         <v>36</v>
       </c>
       <c r="M9" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -15611,7 +15723,7 @@
         <v>123</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>122</v>
@@ -15624,13 +15736,13 @@
         <v>2</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="K10" s="13" t="s">
         <v>125</v>
       </c>
       <c r="M10" t="s">
-        <v>678</v>
+        <v>683</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -15662,7 +15774,7 @@
         <v>127</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>122</v>
@@ -15675,13 +15787,13 @@
         <v>2</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="K11" s="13" t="s">
         <v>129</v>
       </c>
       <c r="M11" t="s">
-        <v>679</v>
+        <v>684</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -15713,7 +15825,7 @@
         <v>134</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>122</v>
@@ -15726,13 +15838,13 @@
         <v>2</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="K12" s="13" t="s">
         <v>136</v>
       </c>
       <c r="M12" t="s">
-        <v>680</v>
+        <v>685</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -15764,7 +15876,7 @@
         <v>134</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>122</v>
@@ -15777,13 +15889,13 @@
         <v>2</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>140</v>
       </c>
       <c r="M13" t="s">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -15815,7 +15927,7 @@
         <v>127</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>122</v>
@@ -15828,13 +15940,13 @@
         <v>2</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="K14" s="13" t="s">
         <v>144</v>
       </c>
       <c r="M14" t="s">
-        <v>682</v>
+        <v>687</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -15866,7 +15978,7 @@
         <v>146</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>122</v>
@@ -15879,7 +15991,7 @@
         <v>2</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="K15" s="13" t="s">
         <v>148</v>
@@ -15899,7 +16011,7 @@
         <v>104</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>103</v>
@@ -15920,7 +16032,7 @@
         <v>39</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>683</v>
+        <v>688</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -15944,7 +16056,7 @@
         <v>104</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>103</v>
@@ -15979,7 +16091,7 @@
         <v>104</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>103</v>
@@ -16014,7 +16126,7 @@
         <v>104</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>103</v>
@@ -16049,7 +16161,7 @@
         <v>165</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>122</v>
@@ -16082,7 +16194,7 @@
         <v>170</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>122</v>
@@ -16095,7 +16207,7 @@
         <v>2</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="K21" s="13" t="s">
         <v>172</v>
@@ -16115,7 +16227,7 @@
         <v>104</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>103</v>
@@ -16150,7 +16262,7 @@
         <v>104</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>103</v>
@@ -16185,7 +16297,7 @@
         <v>104</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>103</v>
@@ -16220,7 +16332,7 @@
         <v>183</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>122</v>
@@ -16253,20 +16365,20 @@
         <v>258</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="H26" s="9"/>
       <c r="I26" s="9">
         <v>2</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="K26" s="13" t="s">
         <v>185</v>
@@ -16283,23 +16395,23 @@
         <v>34</v>
       </c>
       <c r="D27" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>600</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>596</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9">
         <v>1</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="K27" s="13" t="s">
         <v>185</v>
@@ -16316,23 +16428,23 @@
         <v>34</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="9">
         <v>1</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="K28" s="13" t="s">
         <v>185</v>
@@ -16352,7 +16464,7 @@
         <v>104</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>103</v>
@@ -16387,7 +16499,7 @@
         <v>104</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>103</v>
@@ -16422,7 +16534,7 @@
         <v>104</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>103</v>
@@ -16457,7 +16569,7 @@
         <v>104</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>103</v>
@@ -16492,7 +16604,7 @@
         <v>104</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>103</v>
@@ -16527,7 +16639,7 @@
         <v>104</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>103</v>
@@ -16562,7 +16674,7 @@
         <v>104</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>103</v>
@@ -16597,7 +16709,7 @@
         <v>104</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>103</v>
@@ -16632,7 +16744,7 @@
         <v>104</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>103</v>
@@ -16667,7 +16779,7 @@
         <v>104</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>103</v>
@@ -16702,7 +16814,7 @@
         <v>104</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>103</v>
@@ -16737,7 +16849,7 @@
         <v>229</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>122</v>
@@ -16770,20 +16882,20 @@
         <v>127</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="9">
         <v>1</v>
       </c>
       <c r="J41" s="13" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="K41" s="13" t="s">
         <v>231</v>
@@ -16803,20 +16915,20 @@
         <v>127</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="H42" s="9"/>
       <c r="I42" s="9">
         <v>1</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="K42" s="13" t="s">
         <v>231</v>
@@ -16836,20 +16948,20 @@
         <v>127</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="9">
         <v>1</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="K43" s="13" t="s">
         <v>231</v>
@@ -16869,7 +16981,7 @@
         <v>233</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>122</v>
@@ -16884,7 +16996,7 @@
         <v>2</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="K44" s="13" t="s">
         <v>235</v>
@@ -16904,7 +17016,7 @@
         <v>104</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>103</v>
@@ -16939,7 +17051,7 @@
         <v>104</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>103</v>
@@ -16974,7 +17086,7 @@
         <v>104</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>103</v>
@@ -17009,7 +17121,7 @@
         <v>104</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>103</v>
@@ -17044,7 +17156,7 @@
         <v>253</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>122</v>
@@ -17077,7 +17189,7 @@
         <v>258</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>122</v>
@@ -17092,7 +17204,7 @@
         <v>2</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="K50" s="13" t="s">
         <v>260</v>
@@ -17112,7 +17224,7 @@
         <v>104</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>103</v>
@@ -17147,7 +17259,7 @@
         <v>104</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>103</v>
@@ -17182,7 +17294,7 @@
         <v>104</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>103</v>
@@ -17217,7 +17329,7 @@
         <v>104</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>103</v>
@@ -17252,7 +17364,7 @@
         <v>104</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>103</v>
@@ -17287,7 +17399,7 @@
         <v>134</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>122</v>
@@ -17302,7 +17414,7 @@
         <v>2</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="K56" s="13" t="s">
         <v>283</v>
@@ -17322,7 +17434,7 @@
         <v>233</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>122</v>
@@ -17337,7 +17449,7 @@
         <v>2</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="K57" s="13" t="s">
         <v>288</v>
@@ -17357,7 +17469,7 @@
         <v>290</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>103</v>
@@ -17392,7 +17504,7 @@
         <v>134</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>122</v>
@@ -17407,7 +17519,7 @@
         <v>2</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="K59" s="13" t="s">
         <v>294</v>
@@ -17427,7 +17539,7 @@
         <v>297</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>122</v>
@@ -17462,7 +17574,7 @@
         <v>104</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>103</v>
@@ -17497,7 +17609,7 @@
         <v>104</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>103</v>
@@ -17532,7 +17644,7 @@
         <v>104</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>103</v>
@@ -17567,7 +17679,7 @@
         <v>104</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>103</v>
@@ -17602,7 +17714,7 @@
         <v>104</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>103</v>
@@ -17637,7 +17749,7 @@
         <v>104</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>103</v>
@@ -17672,7 +17784,7 @@
         <v>104</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>103</v>
@@ -17707,7 +17819,7 @@
         <v>322</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>122</v>
@@ -17742,7 +17854,7 @@
         <v>327</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>103</v>
@@ -17777,13 +17889,13 @@
         <v>233</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="H70" s="8">
         <v>46181</v>
@@ -17792,7 +17904,7 @@
         <v>2</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="K70" s="13" t="s">
         <v>45</v>
@@ -17812,13 +17924,13 @@
         <v>127</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="H71" s="8">
         <v>46177</v>
@@ -17827,7 +17939,7 @@
         <v>2</v>
       </c>
       <c r="J71" s="13" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="K71" s="13" t="s">
         <v>45</v>
@@ -17847,7 +17959,7 @@
         <v>332</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>122</v>
@@ -17882,7 +17994,7 @@
         <v>258</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>122</v>
@@ -17897,7 +18009,7 @@
         <v>2</v>
       </c>
       <c r="J73" s="13" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="K73" s="13" t="s">
         <v>341</v>
@@ -17914,16 +18026,16 @@
         <v>338</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="H74" s="8">
         <v>46171</v>
@@ -17932,7 +18044,7 @@
         <v>2</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="K74" s="13" t="s">
         <v>341</v>
@@ -17949,16 +18061,16 @@
         <v>338</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="H75" s="8">
         <v>46170</v>
@@ -17967,7 +18079,7 @@
         <v>2</v>
       </c>
       <c r="J75" s="13" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="K75" s="13" t="s">
         <v>341</v>
@@ -17987,13 +18099,13 @@
         <v>183</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="H76" s="8">
         <v>46170</v>
@@ -18002,7 +18114,7 @@
         <v>1</v>
       </c>
       <c r="J76" s="13" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="K76" s="13" t="s">
         <v>341</v>
@@ -18022,13 +18134,13 @@
         <v>183</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="H77" s="8">
         <v>46170</v>
@@ -18037,7 +18149,7 @@
         <v>1</v>
       </c>
       <c r="J77" s="13" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="K77" s="13" t="s">
         <v>341</v>
@@ -18057,13 +18169,13 @@
         <v>233</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="H78" s="8">
         <v>46170</v>
@@ -18072,7 +18184,7 @@
         <v>2</v>
       </c>
       <c r="J78" s="13" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="K78" s="13" t="s">
         <v>341</v>
@@ -18092,13 +18204,13 @@
         <v>332</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="H79" s="8">
         <v>46170</v>
@@ -18107,7 +18219,7 @@
         <v>1</v>
       </c>
       <c r="J79" s="13" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="K79" s="13" t="s">
         <v>341</v>
@@ -18127,20 +18239,20 @@
         <v>183</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="H80" s="9"/>
       <c r="I80" s="9">
         <v>1</v>
       </c>
       <c r="J80" s="13" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="K80" s="13" t="s">
         <v>341</v>
@@ -18160,20 +18272,20 @@
         <v>183</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="H81" s="9"/>
       <c r="I81" s="9">
         <v>1</v>
       </c>
       <c r="J81" s="13" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="K81" s="13" t="s">
         <v>341</v>
@@ -18193,7 +18305,7 @@
         <v>327</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>103</v>
@@ -18228,13 +18340,13 @@
         <v>258</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="H83" s="8">
         <v>46176</v>
@@ -18243,7 +18355,7 @@
         <v>2</v>
       </c>
       <c r="J83" s="13" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="K83" s="13" t="s">
         <v>49</v>
@@ -18263,13 +18375,13 @@
         <v>233</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="H84" s="8">
         <v>46175</v>
@@ -18278,7 +18390,7 @@
         <v>2</v>
       </c>
       <c r="J84" s="13" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="K84" s="13" t="s">
         <v>49</v>
@@ -18298,7 +18410,7 @@
         <v>233</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>122</v>
@@ -18313,7 +18425,7 @@
         <v>2</v>
       </c>
       <c r="J85" s="13" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="K85" s="13" t="s">
         <v>348</v>
@@ -18333,7 +18445,7 @@
         <v>233</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>122</v>
@@ -18348,7 +18460,7 @@
         <v>2</v>
       </c>
       <c r="J86" s="13" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="K86" s="13" t="s">
         <v>351</v>
@@ -18368,7 +18480,7 @@
         <v>258</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>122</v>
@@ -18383,7 +18495,7 @@
         <v>2</v>
       </c>
       <c r="J87" s="13" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="K87" s="13" t="s">
         <v>355</v>
@@ -18403,7 +18515,7 @@
         <v>233</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>122</v>
@@ -18418,7 +18530,7 @@
         <v>2</v>
       </c>
       <c r="J88" s="13" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="K88" s="13" t="s">
         <v>358</v>
@@ -18438,7 +18550,7 @@
         <v>332</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>122</v>
@@ -18473,7 +18585,7 @@
         <v>332</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>122</v>
@@ -18508,7 +18620,7 @@
         <v>367</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>122</v>
@@ -18521,7 +18633,7 @@
         <v>2</v>
       </c>
       <c r="J91" s="13" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="K91" s="13" t="s">
         <v>369</v>
@@ -18541,7 +18653,7 @@
         <v>258</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>122</v>
@@ -18556,7 +18668,7 @@
         <v>2</v>
       </c>
       <c r="J92" s="13" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="K92" s="13" t="s">
         <v>372</v>
@@ -18576,7 +18688,7 @@
         <v>375</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>122</v>
@@ -18591,7 +18703,7 @@
         <v>2</v>
       </c>
       <c r="J93" s="13" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="K93" s="13" t="s">
         <v>377</v>
@@ -18611,7 +18723,7 @@
         <v>170</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>122</v>
@@ -18626,7 +18738,7 @@
         <v>2</v>
       </c>
       <c r="J94" s="13" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="K94" s="13" t="s">
         <v>380</v>
@@ -18646,7 +18758,7 @@
         <v>258</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>122</v>
@@ -18661,7 +18773,7 @@
         <v>2</v>
       </c>
       <c r="J95" s="13" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="K95" s="13" t="s">
         <v>383</v>
@@ -18681,7 +18793,7 @@
         <v>385</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>122</v>
@@ -18696,7 +18808,7 @@
         <v>2</v>
       </c>
       <c r="J96" s="13" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="K96" s="13" t="s">
         <v>387</v>
@@ -18716,13 +18828,13 @@
         <v>127</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="H97" s="8">
         <v>46139</v>
@@ -18731,7 +18843,7 @@
         <v>2</v>
       </c>
       <c r="J97" s="13" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="K97" s="13" t="s">
         <v>387</v>
@@ -18748,23 +18860,23 @@
         <v>34</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="H98" s="9"/>
       <c r="I98" s="9">
         <v>1</v>
       </c>
       <c r="J98" s="13" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="K98" s="13" t="s">
         <v>387</v>
@@ -18784,7 +18896,7 @@
         <v>389</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>122</v>
@@ -18799,7 +18911,7 @@
         <v>2</v>
       </c>
       <c r="J99" s="13" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="K99" s="13" t="s">
         <v>391</v>
@@ -18819,7 +18931,7 @@
         <v>393</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>122</v>
@@ -18834,7 +18946,7 @@
         <v>2</v>
       </c>
       <c r="J100" s="13" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="K100" s="13" t="s">
         <v>395</v>
@@ -18854,7 +18966,7 @@
         <v>183</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>122</v>
@@ -18869,7 +18981,7 @@
         <v>2</v>
       </c>
       <c r="J101" s="13" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="K101" s="13" t="s">
         <v>398</v>
@@ -18889,7 +19001,7 @@
         <v>400</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>122</v>
@@ -18904,7 +19016,7 @@
         <v>2</v>
       </c>
       <c r="J102" s="13" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="K102" s="13" t="s">
         <v>402</v>
@@ -18921,23 +19033,23 @@
         <v>44</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="H103" s="9"/>
       <c r="I103" s="9">
         <v>1</v>
       </c>
       <c r="J103" s="13" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="K103" s="13" t="s">
         <v>402</v>
@@ -18957,7 +19069,7 @@
         <v>404</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>122</v>
@@ -18972,7 +19084,7 @@
         <v>2</v>
       </c>
       <c r="J104" s="13" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="K104" s="13" t="s">
         <v>406</v>
@@ -18983,57 +19095,55 @@
         <v>407</v>
       </c>
       <c r="B105" s="8">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="C105" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="D105" s="9" t="s">
         <v>408</v>
       </c>
-      <c r="D105" s="9" t="s">
-        <v>404</v>
-      </c>
       <c r="E105" s="9" t="s">
-        <v>607</v>
+        <v>593</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>410</v>
-      </c>
-      <c r="H105" s="8">
-        <v>46128</v>
-      </c>
+        <v>409</v>
+      </c>
+      <c r="H105" s="9"/>
       <c r="I105" s="9">
         <v>2</v>
       </c>
       <c r="J105" s="13" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="K105" s="13" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="28" customHeight="1">
       <c r="A106" s="9" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B106" s="8">
         <v>46128</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>170</v>
+        <v>404</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>658</v>
+        <v>414</v>
       </c>
       <c r="H106" s="8">
         <v>46128</v>
@@ -19042,33 +19152,33 @@
         <v>2</v>
       </c>
       <c r="J106" s="13" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="K106" s="13" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="28" customHeight="1">
       <c r="A107" s="9" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B107" s="8">
         <v>46128</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>660</v>
+        <v>170</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="H107" s="8">
         <v>46128</v>
@@ -19077,68 +19187,68 @@
         <v>2</v>
       </c>
       <c r="J107" s="13" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="K107" s="13" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="28" customHeight="1">
       <c r="A108" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B108" s="8">
+        <v>46128</v>
+      </c>
+      <c r="C108" s="9" t="s">
         <v>412</v>
       </c>
-      <c r="B108" s="8">
-        <v>46122</v>
-      </c>
-      <c r="C108" s="9" t="s">
-        <v>409</v>
-      </c>
       <c r="D108" s="9" t="s">
-        <v>233</v>
+        <v>665</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>413</v>
+        <v>666</v>
       </c>
       <c r="H108" s="8">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="I108" s="9">
         <v>2</v>
       </c>
       <c r="J108" s="13" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="K108" s="13" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="28" customHeight="1">
       <c r="A109" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B109" s="8">
         <v>46122</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>338</v>
+        <v>413</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>183</v>
+        <v>233</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H109" s="8">
         <v>46122</v>
@@ -19147,50 +19257,50 @@
         <v>2</v>
       </c>
       <c r="J109" s="13" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="K109" s="13" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="28" customHeight="1">
       <c r="A110" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B110" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="C110" s="9" t="s">
         <v>338</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>400</v>
+        <v>183</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H110" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="I110" s="9">
         <v>2</v>
       </c>
       <c r="J110" s="13" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="K110" s="13" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="28" customHeight="1">
       <c r="A111" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B111" s="8">
         <v>46115</v>
@@ -19199,16 +19309,16 @@
         <v>338</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>258</v>
+        <v>400</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H111" s="8">
         <v>46115</v>
@@ -19217,27 +19327,27 @@
         <v>2</v>
       </c>
       <c r="J111" s="13" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K111" s="13" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="28" customHeight="1">
       <c r="A112" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B112" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>409</v>
+        <v>338</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>425</v>
+        <v>258</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>122</v>
@@ -19246,13 +19356,13 @@
         <v>426</v>
       </c>
       <c r="H112" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="I112" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J112" s="13" t="s">
-        <v>426</v>
+        <v>671</v>
       </c>
       <c r="K112" s="13" t="s">
         <v>427</v>
@@ -19266,19 +19376,19 @@
         <v>46111</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>233</v>
+        <v>429</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H113" s="8">
         <v>46111</v>
@@ -19287,53 +19397,53 @@
         <v>1</v>
       </c>
       <c r="J113" s="13" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="K113" s="13" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="28" customHeight="1">
       <c r="A114" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B114" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>32</v>
+        <v>413</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>115</v>
+        <v>233</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F114" s="9" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H114" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="I114" s="9">
         <v>1</v>
       </c>
       <c r="J114" s="13" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="K114" s="13" t="s">
-        <v>50</v>
+        <v>434</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="28" customHeight="1">
       <c r="A115" s="9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B115" s="8">
-        <v>45923</v>
+        <v>46080</v>
       </c>
       <c r="C115" s="9" t="s">
         <v>32</v>
@@ -19342,138 +19452,138 @@
         <v>115</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>588</v>
+        <v>611</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H115" s="8">
-        <v>45923</v>
+        <v>46080</v>
       </c>
       <c r="I115" s="9">
         <v>1</v>
       </c>
       <c r="J115" s="13" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K115" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="28" customHeight="1">
       <c r="A116" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B116" s="8">
-        <v>45729</v>
+        <v>45923</v>
       </c>
       <c r="C116" s="9" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>327</v>
+        <v>115</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="H116" s="8">
-        <v>45729</v>
+        <v>45923</v>
       </c>
       <c r="I116" s="9">
         <v>1</v>
       </c>
       <c r="J116" s="13" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="K116" s="13" t="s">
-        <v>438</v>
+        <v>51</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="28" customHeight="1">
       <c r="A117" s="9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B117" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>115</v>
+        <v>327</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>607</v>
+        <v>592</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H117" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="I117" s="9">
         <v>1</v>
       </c>
       <c r="J117" s="13" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K117" s="13" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="28" customHeight="1">
       <c r="A118" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B118" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D118" s="9" t="s">
         <v>115</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H118" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="I118" s="9">
         <v>1</v>
       </c>
       <c r="J118" s="13" t="s">
+        <v>444</v>
+      </c>
+      <c r="K118" s="13" t="s">
         <v>445</v>
-      </c>
-      <c r="K118" s="13" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="28" customHeight="1">
       <c r="A119" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B119" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="C119" s="9" t="s">
         <v>32</v>
@@ -19482,7 +19592,7 @@
         <v>115</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>103</v>
@@ -19491,7 +19601,7 @@
         <v>449</v>
       </c>
       <c r="H119" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="I119" s="9">
         <v>1</v>
@@ -19508,7 +19618,7 @@
         <v>451</v>
       </c>
       <c r="B120" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="C120" s="9" t="s">
         <v>32</v>
@@ -19517,42 +19627,42 @@
         <v>115</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H120" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="I120" s="9">
         <v>1</v>
       </c>
       <c r="J120" s="13" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K120" s="13" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="28" customHeight="1">
       <c r="A121" s="9" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B121" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>454</v>
+        <v>32</v>
       </c>
       <c r="D121" s="9" t="s">
         <v>115</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>103</v>
@@ -19561,7 +19671,7 @@
         <v>456</v>
       </c>
       <c r="H121" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="I121" s="9">
         <v>1</v>
@@ -19570,672 +19680,707 @@
         <v>456</v>
       </c>
       <c r="K121" s="13" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="28" customHeight="1">
       <c r="A122" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="B122" s="8">
+        <v>45288</v>
+      </c>
+      <c r="C122" s="9" t="s">
         <v>458</v>
       </c>
-      <c r="B122" s="8">
-        <v>45190</v>
-      </c>
-      <c r="C122" s="9" t="s">
-        <v>459</v>
-      </c>
       <c r="D122" s="9" t="s">
-        <v>468</v>
+        <v>115</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>667</v>
+        <v>611</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="H122" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="I122" s="9">
         <v>1</v>
       </c>
       <c r="J122" s="13" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="K122" s="13" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="28" customHeight="1">
       <c r="A123" s="9" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B123" s="8">
         <v>45190</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>562</v>
+        <v>473</v>
       </c>
       <c r="H123" s="8">
-        <v>45008</v>
+        <v>45190</v>
       </c>
       <c r="I123" s="9">
         <v>1</v>
       </c>
       <c r="J123" s="13" t="s">
-        <v>562</v>
+        <v>473</v>
       </c>
       <c r="K123" s="13" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="28" customHeight="1">
       <c r="A124" s="9" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="B124" s="8">
-        <v>44707</v>
+        <v>45190</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>480</v>
+        <v>566</v>
       </c>
       <c r="H124" s="8">
-        <v>44707</v>
+        <v>45008</v>
       </c>
       <c r="I124" s="9">
         <v>1</v>
       </c>
       <c r="J124" s="13" t="s">
-        <v>480</v>
+        <v>566</v>
       </c>
       <c r="K124" s="13" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="28" customHeight="1">
       <c r="A125" s="9" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B125" s="8">
         <v>44707</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>563</v>
+        <v>484</v>
       </c>
       <c r="H125" s="8">
-        <v>44644</v>
+        <v>44707</v>
       </c>
       <c r="I125" s="9">
         <v>1</v>
       </c>
       <c r="J125" s="13" t="s">
-        <v>563</v>
+        <v>484</v>
       </c>
       <c r="K125" s="13" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="28" customHeight="1">
       <c r="A126" s="9" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="B126" s="8">
-        <v>44640</v>
+        <v>44707</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>490</v>
+        <v>567</v>
       </c>
       <c r="H126" s="8">
-        <v>44734</v>
+        <v>44644</v>
       </c>
       <c r="I126" s="9">
         <v>1</v>
       </c>
       <c r="J126" s="13" t="s">
-        <v>490</v>
+        <v>567</v>
       </c>
       <c r="K126" s="13" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="28" customHeight="1">
       <c r="A127" s="9" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="B127" s="8">
         <v>44640</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>564</v>
+        <v>494</v>
       </c>
       <c r="H127" s="8">
-        <v>44643</v>
+        <v>44734</v>
       </c>
       <c r="I127" s="9">
         <v>1</v>
       </c>
       <c r="J127" s="13" t="s">
-        <v>564</v>
+        <v>494</v>
       </c>
       <c r="K127" s="13" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="28" customHeight="1">
       <c r="A128" s="9" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B128" s="8">
-        <v>44592</v>
+        <v>44640</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>499</v>
+        <v>568</v>
       </c>
       <c r="H128" s="8">
-        <v>44608</v>
+        <v>44643</v>
       </c>
       <c r="I128" s="9">
         <v>1</v>
       </c>
       <c r="J128" s="13" t="s">
-        <v>499</v>
+        <v>568</v>
       </c>
       <c r="K128" s="13" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="28" customHeight="1">
       <c r="A129" s="9" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B129" s="8">
-        <v>44579</v>
+        <v>44592</v>
       </c>
       <c r="C129" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="D129" s="9" t="s">
         <v>502</v>
       </c>
-      <c r="D129" s="9" t="s">
-        <v>508</v>
-      </c>
       <c r="E129" s="9" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="H129" s="8">
-        <v>44579</v>
+        <v>44608</v>
       </c>
       <c r="I129" s="9">
         <v>1</v>
       </c>
       <c r="J129" s="13" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="K129" s="13" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="28" customHeight="1">
       <c r="A130" s="9" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B130" s="8">
         <v>44579</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>565</v>
+        <v>513</v>
       </c>
       <c r="H130" s="8">
-        <v>44250</v>
+        <v>44579</v>
       </c>
       <c r="I130" s="9">
         <v>1</v>
       </c>
       <c r="J130" s="13" t="s">
-        <v>565</v>
+        <v>513</v>
       </c>
       <c r="K130" s="13" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="28" customHeight="1">
       <c r="A131" s="9" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="B131" s="8">
-        <v>44166</v>
+        <v>44579</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>518</v>
+        <v>569</v>
       </c>
       <c r="H131" s="8">
-        <v>44166</v>
+        <v>44250</v>
       </c>
       <c r="I131" s="9">
         <v>1</v>
       </c>
       <c r="J131" s="13" t="s">
-        <v>518</v>
+        <v>569</v>
       </c>
       <c r="K131" s="13" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="28" customHeight="1">
       <c r="A132" s="9" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B132" s="8">
         <v>44166</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>566</v>
+        <v>522</v>
       </c>
       <c r="H132" s="8">
-        <v>43902</v>
+        <v>44166</v>
       </c>
       <c r="I132" s="9">
         <v>1</v>
       </c>
       <c r="J132" s="13" t="s">
-        <v>566</v>
+        <v>522</v>
       </c>
       <c r="K132" s="13" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="28" customHeight="1">
       <c r="A133" s="9" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B133" s="8">
-        <v>44131</v>
+        <v>44166</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>527</v>
+        <v>570</v>
       </c>
       <c r="H133" s="8">
-        <v>44131</v>
+        <v>43902</v>
       </c>
       <c r="I133" s="9">
         <v>1</v>
       </c>
       <c r="J133" s="13" t="s">
-        <v>527</v>
+        <v>570</v>
       </c>
       <c r="K133" s="13" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="28" customHeight="1">
       <c r="A134" s="9" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B134" s="8">
         <v>44131</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>567</v>
+        <v>531</v>
       </c>
       <c r="H134" s="8">
-        <v>43966</v>
+        <v>44131</v>
       </c>
       <c r="I134" s="9">
         <v>1</v>
       </c>
       <c r="J134" s="13" t="s">
-        <v>567</v>
+        <v>531</v>
       </c>
       <c r="K134" s="13" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="28" customHeight="1">
       <c r="A135" s="9" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B135" s="8">
-        <v>43626</v>
+        <v>44131</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="H135" s="8">
-        <v>43626</v>
+        <v>43966</v>
       </c>
       <c r="I135" s="9">
         <v>1</v>
       </c>
       <c r="J135" s="13" t="s">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="K135" s="13" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="28" customHeight="1">
       <c r="A136" s="9" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B136" s="8">
         <v>43626</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>532</v>
+        <v>521</v>
       </c>
       <c r="E136" s="9" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>568</v>
+        <v>538</v>
       </c>
       <c r="H136" s="8">
-        <v>43518</v>
+        <v>43626</v>
       </c>
       <c r="I136" s="9">
         <v>1</v>
       </c>
       <c r="J136" s="13" t="s">
-        <v>568</v>
+        <v>538</v>
       </c>
       <c r="K136" s="13" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="28" customHeight="1">
       <c r="A137" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B137" s="8">
+        <v>43626</v>
+      </c>
+      <c r="C137" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="D137" s="9" t="s">
         <v>536</v>
       </c>
-      <c r="B137" s="8">
-        <v>43401</v>
-      </c>
-      <c r="C137" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="D137" s="9" t="s">
-        <v>542</v>
-      </c>
       <c r="E137" s="9" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="H137" s="8">
-        <v>43401</v>
+        <v>43518</v>
       </c>
       <c r="I137" s="9">
         <v>1</v>
       </c>
       <c r="J137" s="13" t="s">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="K137" s="13" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="28" customHeight="1">
       <c r="A138" s="9" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B138" s="8">
         <v>43401</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="E138" s="9" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>569</v>
+        <v>547</v>
       </c>
       <c r="H138" s="8">
-        <v>43215</v>
+        <v>43401</v>
       </c>
       <c r="I138" s="9">
         <v>1</v>
       </c>
       <c r="J138" s="13" t="s">
-        <v>569</v>
+        <v>547</v>
       </c>
       <c r="K138" s="13" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="28" customHeight="1">
       <c r="A139" s="9" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B139" s="8">
-        <v>42534</v>
+        <v>43401</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>508</v>
+        <v>544</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>550</v>
+        <v>573</v>
       </c>
       <c r="H139" s="8">
-        <v>42534</v>
+        <v>43215</v>
       </c>
       <c r="I139" s="9">
         <v>1</v>
       </c>
       <c r="J139" s="13" t="s">
-        <v>550</v>
+        <v>573</v>
       </c>
       <c r="K139" s="13" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="28" customHeight="1">
       <c r="A140" s="9" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B140" s="8">
         <v>42534</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>548</v>
+        <v>512</v>
       </c>
       <c r="E140" s="9" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G140" s="9" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="H140" s="8">
-        <v>42412</v>
+        <v>42534</v>
       </c>
       <c r="I140" s="9">
         <v>1</v>
       </c>
       <c r="J140" s="13" t="s">
-        <v>570</v>
+        <v>554</v>
       </c>
       <c r="K140" s="13" t="s">
-        <v>551</v>
+        <v>555</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" ht="28" customHeight="1">
+      <c r="A141" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="B141" s="8">
+        <v>42534</v>
+      </c>
+      <c r="C141" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="E141" s="9" t="s">
+        <v>673</v>
+      </c>
+      <c r="F141" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G141" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="H141" s="8">
+        <v>42412</v>
+      </c>
+      <c r="I141" s="9">
+        <v>1</v>
+      </c>
+      <c r="J141" s="13" t="s">
+        <v>574</v>
+      </c>
+      <c r="K141" s="13" t="s">
+        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -20453,9 +20598,9 @@
     <hyperlink ref="J108" r:id="rId205"/>
     <hyperlink ref="G109" r:id="rId206"/>
     <hyperlink ref="J109" r:id="rId207"/>
-    <hyperlink ref="D110" r:id="rId208"/>
-    <hyperlink ref="G110" r:id="rId209"/>
-    <hyperlink ref="J110" r:id="rId210"/>
+    <hyperlink ref="G110" r:id="rId208"/>
+    <hyperlink ref="J110" r:id="rId209"/>
+    <hyperlink ref="D111" r:id="rId210"/>
     <hyperlink ref="G111" r:id="rId211"/>
     <hyperlink ref="J111" r:id="rId212"/>
     <hyperlink ref="G112" r:id="rId213"/>
@@ -20516,10 +20661,12 @@
     <hyperlink ref="J139" r:id="rId268"/>
     <hyperlink ref="G140" r:id="rId269"/>
     <hyperlink ref="J140" r:id="rId270"/>
+    <hyperlink ref="G141" r:id="rId271"/>
+    <hyperlink ref="J141" r:id="rId272"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId271"/>
+    <tablePart r:id="rId273"/>
   </tableParts>
 </worksheet>
 </file>
--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-10 | Build 128164946846 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-10 | Build a5ffb6ae33e3 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-10 | Build ea47d5865af6 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-11 | Build 607838a99475 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -1286,7 +1286,7 @@
     <t>https://rb.ru/news/vk-prodal-25-akcij-tochka-banka-sdelku-ocenili-v-212-mlrd-vdvoe-vyshe-iznachalnoj-stoimosti-bumag/</t>
   </si>
   <si>
-    <t>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.RU</t>
+    <t>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - rb.ru</t>
   </si>
   <si>
     <t>DL-4774de17c61c14e4</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-12 | Build 15e2be9e0b2f | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-12 | Build 465c30d19a73 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -296,244 +296,244 @@
     <t>DL-43cba0d6484c89d8</t>
   </si>
   <si>
+    <t>technical_filing</t>
+  </si>
+  <si>
+    <t>Russia</t>
+  </si>
+  <si>
+    <t>Bonds</t>
+  </si>
+  <si>
+    <t>4B02-12-55319-E-001P</t>
+  </si>
+  <si>
+    <t>N/M: EV and aligned-currency financials are required</t>
+  </si>
+  <si>
+    <t>review</t>
+  </si>
+  <si>
+    <t>confirmed</t>
+  </si>
+  <si>
+    <t>Банк России</t>
+  </si>
+  <si>
+    <t>https://www.cbr.ru/press/PR/?file=639192135171625735DSD.htm</t>
+  </si>
+  <si>
+    <t>Совет директоров Банка России принял решение о включении ценных бумаг в Ломбардный список (10.07.2026)</t>
+  </si>
+  <si>
+    <t>DL-moex-101938</t>
+  </si>
+  <si>
+    <t>ОАО "РЖД"</t>
+  </si>
+  <si>
+    <t>Not classified</t>
+  </si>
+  <si>
+    <t>4B02-53-65045-D-001P</t>
+  </si>
+  <si>
+    <t>RU000A10F8P9</t>
+  </si>
+  <si>
+    <t>MOEX disclosure</t>
+  </si>
+  <si>
+    <t>https://www.moex.com/n101938</t>
+  </si>
+  <si>
+    <t>О проведении 10 июля 2026 года размещения биржевых облигаций 001Р-53R (дополнительный выпуск №2) ОАО "РЖД"</t>
+  </si>
+  <si>
+    <t>DL-moex-101874</t>
+  </si>
+  <si>
     <t>deal</t>
   </si>
   <si>
-    <t>Russia</t>
-  </si>
-  <si>
-    <t>Bonds</t>
-  </si>
-  <si>
-    <t>4B02-12-55319-E-001P</t>
-  </si>
-  <si>
-    <t>N/M: EV and aligned-currency financials are required</t>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Secondary share placement</t>
+  </si>
+  <si>
+    <t>https://www.moex.com/n101874</t>
+  </si>
+  <si>
+    <t>Частные инвесторы вложили в облигации на Московской бирже более 1,1 трлн рублей по итогам первого полугодия</t>
+  </si>
+  <si>
+    <t>DL-af6397599d020a5f</t>
+  </si>
+  <si>
+    <t>3 года</t>
+  </si>
+  <si>
+    <t>Selectel Newsroom</t>
+  </si>
+  <si>
+    <t>https://selectel.ru/about/newsroom/news/selectel-razmestil-novyj-vypusk-obligacij-obemom-75-milliardov-rublej/</t>
+  </si>
+  <si>
+    <t>DL-7b25965c17ea42d6</t>
+  </si>
+  <si>
+    <t>watchlist</t>
+  </si>
+  <si>
+    <t>Reported</t>
+  </si>
+  <si>
+    <t>Amazon намерена привлечь $25 млрд путем размещения облигаций</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>unverified</t>
+  </si>
+  <si>
+    <t>FashionNetwork Россия</t>
+  </si>
+  <si>
+    <t>https://ru.fashionnetwork.com/news/Amazon-namerena-privlech%CA%B9-25-mlrd-putem-razmeshcheniya-obligatsiy,1850796.html</t>
+  </si>
+  <si>
+    <t>Amazon намерена привлечь $25 млрд путем размещения облигаций - FashionNetwork Россия</t>
+  </si>
+  <si>
+    <t>DL-a347aba98fed2480</t>
+  </si>
+  <si>
+    <t>InvestFuture</t>
+  </si>
+  <si>
+    <t>https://investfuture.ru/articles/rosseti-sibir-zapuskayut-razmeschenie-obligatsiy-na-10-0-mlrd-s-plavayuschim-kuponom-1182772325</t>
+  </si>
+  <si>
+    <t>Россети Сибирь запускают размещение облигаций на 10,0 млрд с плавающим купоном | IF | 08.07.2026 - InvestFuture</t>
+  </si>
+  <si>
+    <t>DL-3c0392914bb7d450</t>
+  </si>
+  <si>
+    <t>Arm Holdings для фиксации прибыли</t>
+  </si>
+  <si>
+    <t>Траст Джима Крамера полностью</t>
+  </si>
+  <si>
+    <t>Acquisition / disposal</t>
+  </si>
+  <si>
+    <t>Финансы Mail</t>
+  </si>
+  <si>
+    <t>https://finance.mail.ru/article/trast-dzhima-kramera-polnostyu-prodal-aktsii-arm-holdings-dlya-fiksatsii-pribyili-69216903/</t>
+  </si>
+  <si>
+    <t>Траст Джима Крамера полностью продал акции Arm Holdings для фиксации прибыли - Финансы Mail</t>
+  </si>
+  <si>
+    <t>DL-32fe42111a2c1256</t>
+  </si>
+  <si>
+    <t>Избыток новых акций и облигаций угрожает росту американского фондового рынка</t>
+  </si>
+  <si>
+    <t>https://finance.mail.ru/article/izbyitok-novyih-aktsij-i-obligatsij-ugrozhaet-rostu-amerikanskogo-fondovogo-ryinka-69216922/</t>
+  </si>
+  <si>
+    <t>Избыток новых акций и облигаций угрожает росту американского фондового рынка - Финансы Mail</t>
+  </si>
+  <si>
+    <t>DL-f9b80a44749650ae</t>
+  </si>
+  <si>
+    <t>Selectel увеличивает объем размещения облигаций до 7,5 млрд руб</t>
+  </si>
+  <si>
+    <t>https://investfuture.ru/articles/selectel-uvelichivaet-obyem-razmescheniya-obligatsiy-do-7-5-mlrd-rub-i-uderzhivaet-dokhodnost-17-2-1182781875</t>
+  </si>
+  <si>
+    <t>Selectel увеличивает объем размещения облигаций до 7,5 млрд руб.</t>
+  </si>
+  <si>
+    <t>DL-622d99b994e527ab</t>
+  </si>
+  <si>
+    <t>Oninvest</t>
+  </si>
+  <si>
+    <t>https://oninvest.com/article/spros-na-obligacii-giperskejlerov-slabeet-eto-pokazalo-razmesenie-amazon-na-25-mlrd</t>
+  </si>
+  <si>
+    <t>Спрос на облигации гиперскейлеров слабеет: это показало размещение Amazon на $25 млрд - Oninvest</t>
+  </si>
+  <si>
+    <t>DL-ec890718ba131f71</t>
+  </si>
+  <si>
+    <t>VKCO</t>
+  </si>
+  <si>
+    <t>https://finance.mail.ru/article/izbyitok-novyih-aktsij-i-obligatsij-ugrozhaet-rostu-amerikanskogo-fondovogo-ryinka-69216922/?from\=swap\&amp;swap\=2</t>
+  </si>
+  <si>
+    <t>DL-moex-101851</t>
+  </si>
+  <si>
+    <t>https://www.moex.com/n101851</t>
+  </si>
+  <si>
+    <t>О регистрации дополнительного выпуска биржевых облигаций</t>
+  </si>
+  <si>
+    <t>DL-moex-101830</t>
+  </si>
+  <si>
+    <t>RU000A104RC6</t>
+  </si>
+  <si>
+    <t>https://www.moex.com/n101830</t>
+  </si>
+  <si>
+    <t>Дополнительные условия проведения торгов облигациями серии CIB-СО-213 АО "Сбербанк КИБ" с 07 июля 2026 года</t>
+  </si>
+  <si>
+    <t>DL-moex-101798</t>
+  </si>
+  <si>
+    <t>004Р-07</t>
+  </si>
+  <si>
+    <t>RU000A10FJQ4</t>
+  </si>
+  <si>
+    <t>https://www.moex.com/n101798</t>
+  </si>
+  <si>
+    <t>Дополнительные условия проведения торгов облигациями серии 004P-07 ПАО "Банк ПСБ"</t>
+  </si>
+  <si>
+    <t>DL-moex-101795</t>
+  </si>
+  <si>
+    <t>https://www.moex.com/n101795</t>
+  </si>
+  <si>
+    <t>О внесении изменений в решение о выпуске биржевых облигаций в части сведений о представителе владельцев биржевых облигаций</t>
+  </si>
+  <si>
+    <t>DL-faccb2ab896ed1d5</t>
   </si>
   <si>
     <t>rejected</t>
-  </si>
-  <si>
-    <t>confirmed</t>
-  </si>
-  <si>
-    <t>Банк России</t>
-  </si>
-  <si>
-    <t>https://www.cbr.ru/press/PR/?file=639192135171625735DSD.htm</t>
-  </si>
-  <si>
-    <t>Совет директоров Банка России принял решение о включении ценных бумаг в Ломбардный список (10.07.2026)</t>
-  </si>
-  <si>
-    <t>DL-moex-101938</t>
-  </si>
-  <si>
-    <t>technical_filing</t>
-  </si>
-  <si>
-    <t>ОАО "РЖД"</t>
-  </si>
-  <si>
-    <t>Not classified</t>
-  </si>
-  <si>
-    <t>4B02-53-65045-D-001P</t>
-  </si>
-  <si>
-    <t>RU000A10F8P9</t>
-  </si>
-  <si>
-    <t>review</t>
-  </si>
-  <si>
-    <t>MOEX disclosure</t>
-  </si>
-  <si>
-    <t>https://www.moex.com/n101938</t>
-  </si>
-  <si>
-    <t>О проведении 10 июля 2026 года размещения биржевых облигаций 001Р-53R (дополнительный выпуск №2) ОАО "РЖД"</t>
-  </si>
-  <si>
-    <t>DL-moex-101874</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Secondary share placement</t>
-  </si>
-  <si>
-    <t>https://www.moex.com/n101874</t>
-  </si>
-  <si>
-    <t>Частные инвесторы вложили в облигации на Московской бирже более 1,1 трлн рублей по итогам первого полугодия</t>
-  </si>
-  <si>
-    <t>DL-af6397599d020a5f</t>
-  </si>
-  <si>
-    <t>3 года</t>
-  </si>
-  <si>
-    <t>Selectel Newsroom</t>
-  </si>
-  <si>
-    <t>https://selectel.ru/about/newsroom/news/selectel-razmestil-novyj-vypusk-obligacij-obemom-75-milliardov-rublej/</t>
-  </si>
-  <si>
-    <t>DL-7b25965c17ea42d6</t>
-  </si>
-  <si>
-    <t>watchlist</t>
-  </si>
-  <si>
-    <t>Reported</t>
-  </si>
-  <si>
-    <t>Amazon намерена привлечь $25 млрд путем размещения облигаций</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>unverified</t>
-  </si>
-  <si>
-    <t>FashionNetwork Россия</t>
-  </si>
-  <si>
-    <t>https://ru.fashionnetwork.com/news/Amazon-namerena-privlech%CA%B9-25-mlrd-putem-razmeshcheniya-obligatsiy,1850796.html</t>
-  </si>
-  <si>
-    <t>Amazon намерена привлечь $25 млрд путем размещения облигаций - FashionNetwork Россия</t>
-  </si>
-  <si>
-    <t>DL-a347aba98fed2480</t>
-  </si>
-  <si>
-    <t>InvestFuture</t>
-  </si>
-  <si>
-    <t>https://investfuture.ru/articles/rosseti-sibir-zapuskayut-razmeschenie-obligatsiy-na-10-0-mlrd-s-plavayuschim-kuponom-1182772325</t>
-  </si>
-  <si>
-    <t>Россети Сибирь запускают размещение облигаций на 10,0 млрд с плавающим купоном | IF | 08.07.2026 - InvestFuture</t>
-  </si>
-  <si>
-    <t>DL-3c0392914bb7d450</t>
-  </si>
-  <si>
-    <t>Arm Holdings для фиксации прибыли</t>
-  </si>
-  <si>
-    <t>Траст Джима Крамера полностью</t>
-  </si>
-  <si>
-    <t>Acquisition / disposal</t>
-  </si>
-  <si>
-    <t>Финансы Mail</t>
-  </si>
-  <si>
-    <t>https://finance.mail.ru/article/trast-dzhima-kramera-polnostyu-prodal-aktsii-arm-holdings-dlya-fiksatsii-pribyili-69216903/</t>
-  </si>
-  <si>
-    <t>Траст Джима Крамера полностью продал акции Arm Holdings для фиксации прибыли - Финансы Mail</t>
-  </si>
-  <si>
-    <t>DL-32fe42111a2c1256</t>
-  </si>
-  <si>
-    <t>Избыток новых акций и облигаций угрожает росту американского фондового рынка</t>
-  </si>
-  <si>
-    <t>https://finance.mail.ru/article/izbyitok-novyih-aktsij-i-obligatsij-ugrozhaet-rostu-amerikanskogo-fondovogo-ryinka-69216922/</t>
-  </si>
-  <si>
-    <t>Избыток новых акций и облигаций угрожает росту американского фондового рынка - Финансы Mail</t>
-  </si>
-  <si>
-    <t>DL-f9b80a44749650ae</t>
-  </si>
-  <si>
-    <t>Selectel увеличивает объем размещения облигаций до 7,5 млрд руб</t>
-  </si>
-  <si>
-    <t>https://investfuture.ru/articles/selectel-uvelichivaet-obyem-razmescheniya-obligatsiy-do-7-5-mlrd-rub-i-uderzhivaet-dokhodnost-17-2-1182781875</t>
-  </si>
-  <si>
-    <t>Selectel увеличивает объем размещения облигаций до 7,5 млрд руб.</t>
-  </si>
-  <si>
-    <t>DL-622d99b994e527ab</t>
-  </si>
-  <si>
-    <t>Oninvest</t>
-  </si>
-  <si>
-    <t>https://oninvest.com/article/spros-na-obligacii-giperskejlerov-slabeet-eto-pokazalo-razmesenie-amazon-na-25-mlrd</t>
-  </si>
-  <si>
-    <t>Спрос на облигации гиперскейлеров слабеет: это показало размещение Amazon на $25 млрд - Oninvest</t>
-  </si>
-  <si>
-    <t>DL-ec890718ba131f71</t>
-  </si>
-  <si>
-    <t>VKCO</t>
-  </si>
-  <si>
-    <t>https://finance.mail.ru/article/izbyitok-novyih-aktsij-i-obligatsij-ugrozhaet-rostu-amerikanskogo-fondovogo-ryinka-69216922/?from\=swap\&amp;swap\=2</t>
-  </si>
-  <si>
-    <t>DL-moex-101851</t>
-  </si>
-  <si>
-    <t>https://www.moex.com/n101851</t>
-  </si>
-  <si>
-    <t>О регистрации дополнительного выпуска биржевых облигаций</t>
-  </si>
-  <si>
-    <t>DL-moex-101830</t>
-  </si>
-  <si>
-    <t>RU000A104RC6</t>
-  </si>
-  <si>
-    <t>https://www.moex.com/n101830</t>
-  </si>
-  <si>
-    <t>Дополнительные условия проведения торгов облигациями серии CIB-СО-213 АО "Сбербанк КИБ" с 07 июля 2026 года</t>
-  </si>
-  <si>
-    <t>DL-moex-101798</t>
-  </si>
-  <si>
-    <t>004Р-07</t>
-  </si>
-  <si>
-    <t>RU000A10FJQ4</t>
-  </si>
-  <si>
-    <t>https://www.moex.com/n101798</t>
-  </si>
-  <si>
-    <t>Дополнительные условия проведения торгов облигациями серии 004P-07 ПАО "Банк ПСБ"</t>
-  </si>
-  <si>
-    <t>DL-moex-101795</t>
-  </si>
-  <si>
-    <t>https://www.moex.com/n101795</t>
-  </si>
-  <si>
-    <t>О внесении изменений в решение о выпуске биржевых облигаций в части сведений о представителе владельцев биржевых облигаций</t>
-  </si>
-  <si>
-    <t>DL-faccb2ab896ed1d5</t>
   </si>
   <si>
     <t>M O N D I A R A</t>
@@ -2835,7 +2835,7 @@
         <v>20</v>
       </c>
       <c r="F7" s="5">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G7" s="5">
         <v>10</v>
@@ -3469,7 +3469,7 @@
         <v>97</v>
       </c>
       <c r="AO7" s="9">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AP7" s="9" t="s">
         <v>98</v>
@@ -3498,22 +3498,22 @@
         <v>6</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>48</v>
       </c>
       <c r="F8" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="9" t="s">
         <v>104</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>105</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>93</v>
@@ -3531,10 +3531,10 @@
         <v>94</v>
       </c>
       <c r="R8" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="S8" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="S8" s="9" t="s">
-        <v>107</v>
       </c>
       <c r="U8" s="9" t="s">
         <v>34</v>
@@ -3561,7 +3561,7 @@
         <v>96</v>
       </c>
       <c r="AN8" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO8" s="9">
         <v>60</v>
@@ -3573,18 +3573,18 @@
         <v>1</v>
       </c>
       <c r="AR8" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="AS8" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="AT8" s="9" t="s">
         <v>109</v>
-      </c>
-      <c r="AS8" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="AT8" s="9" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:46">
       <c r="A9" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B9" s="8">
         <v>46211</v>
@@ -3593,7 +3593,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>48</v>
@@ -3608,7 +3608,7 @@
         <v>33</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>93</v>
@@ -3626,7 +3626,7 @@
         <v>34</v>
       </c>
       <c r="Q9" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R9" s="9" t="s">
         <v>34</v>
@@ -3659,7 +3659,7 @@
         <v>96</v>
       </c>
       <c r="AN9" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO9" s="9">
         <v>75</v>
@@ -3671,18 +3671,18 @@
         <v>1</v>
       </c>
       <c r="AR9" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS9" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="AT9" s="9" t="s">
         <v>115</v>
-      </c>
-      <c r="AT9" s="9" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:46">
       <c r="A10" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B10" s="8">
         <v>46211</v>
@@ -3691,7 +3691,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>31</v>
@@ -3706,7 +3706,7 @@
         <v>33</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>93</v>
@@ -3736,7 +3736,7 @@
         <v>34</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AB10" s="9" t="s">
         <v>33</v>
@@ -3769,10 +3769,10 @@
         <v>1</v>
       </c>
       <c r="AR10" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="AS10" s="9" t="s">
         <v>119</v>
-      </c>
-      <c r="AS10" s="9" t="s">
-        <v>120</v>
       </c>
       <c r="AT10" s="9" t="s">
         <v>36</v>
@@ -3780,7 +3780,7 @@
     </row>
     <row r="11" spans="1:46">
       <c r="A11" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11" s="8">
         <v>46211</v>
@@ -3789,14 +3789,14 @@
         <v>6</v>
       </c>
       <c r="D11" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="F11" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>124</v>
-      </c>
       <c r="G11" s="9" t="s">
         <v>33</v>
       </c>
@@ -3804,7 +3804,7 @@
         <v>33</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>93</v>
@@ -3813,7 +3813,7 @@
         <v>25000000000</v>
       </c>
       <c r="M11" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>33</v>
@@ -3855,30 +3855,30 @@
         <v>96</v>
       </c>
       <c r="AN11" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO11" s="9">
         <v>75</v>
       </c>
       <c r="AP11" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ11" s="9">
         <v>1</v>
       </c>
       <c r="AR11" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="AS11" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="AS11" s="9" t="s">
+      <c r="AT11" s="9" t="s">
         <v>128</v>
-      </c>
-      <c r="AT11" s="9" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:46">
       <c r="A12" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B12" s="8">
         <v>46211</v>
@@ -3887,11 +3887,11 @@
         <v>6</v>
       </c>
       <c r="D12" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F12" s="9" t="s">
         <v>34</v>
       </c>
@@ -3902,7 +3902,7 @@
         <v>33</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>34</v>
@@ -3953,30 +3953,30 @@
         <v>96</v>
       </c>
       <c r="AN12" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO12" s="9">
         <v>50</v>
       </c>
       <c r="AP12" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ12" s="9">
         <v>1</v>
       </c>
       <c r="AR12" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="AS12" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="AS12" s="9" t="s">
+      <c r="AT12" s="9" t="s">
         <v>132</v>
-      </c>
-      <c r="AT12" s="9" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:46">
       <c r="A13" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B13" s="8">
         <v>46211</v>
@@ -3985,37 +3985,37 @@
         <v>4</v>
       </c>
       <c r="D13" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E13" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F13" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="9" t="s">
+      <c r="I13" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="P13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q13" s="9" t="s">
         <v>136</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="M13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="O13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="P13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q13" s="9" t="s">
-        <v>137</v>
       </c>
       <c r="R13" s="9" t="s">
         <v>33</v>
@@ -4048,30 +4048,30 @@
         <v>96</v>
       </c>
       <c r="AN13" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO13" s="9">
         <v>60</v>
       </c>
       <c r="AP13" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ13" s="9">
         <v>1</v>
       </c>
       <c r="AR13" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="AS13" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="AS13" s="9" t="s">
+      <c r="AT13" s="9" t="s">
         <v>139</v>
-      </c>
-      <c r="AT13" s="9" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:46">
       <c r="A14" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B14" s="8">
         <v>46211</v>
@@ -4080,13 +4080,13 @@
         <v>6</v>
       </c>
       <c r="D14" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E14" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F14" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G14" s="9" t="s">
         <v>33</v>
@@ -4095,7 +4095,7 @@
         <v>33</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J14" s="9" t="s">
         <v>34</v>
@@ -4143,30 +4143,30 @@
         <v>96</v>
       </c>
       <c r="AN14" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO14" s="9">
         <v>75</v>
       </c>
       <c r="AP14" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ14" s="9">
         <v>1</v>
       </c>
       <c r="AR14" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AS14" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="AT14" s="9" t="s">
         <v>143</v>
-      </c>
-      <c r="AT14" s="9" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:46">
       <c r="A15" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B15" s="8">
         <v>46211</v>
@@ -4175,13 +4175,13 @@
         <v>6</v>
       </c>
       <c r="D15" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F15" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>33</v>
@@ -4190,7 +4190,7 @@
         <v>33</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>93</v>
@@ -4244,30 +4244,30 @@
         <v>96</v>
       </c>
       <c r="AN15" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO15" s="9">
         <v>75</v>
       </c>
       <c r="AP15" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ15" s="9">
         <v>1</v>
       </c>
       <c r="AR15" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AS15" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="AT15" s="9" t="s">
         <v>147</v>
-      </c>
-      <c r="AT15" s="9" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:46">
       <c r="A16" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B16" s="8">
         <v>46211</v>
@@ -4276,11 +4276,11 @@
         <v>6</v>
       </c>
       <c r="D16" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E16" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E16" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F16" s="9" t="s">
         <v>34</v>
       </c>
@@ -4291,7 +4291,7 @@
         <v>33</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>34</v>
@@ -4300,7 +4300,7 @@
         <v>25000000000</v>
       </c>
       <c r="M16" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O16" s="9" t="s">
         <v>33</v>
@@ -4342,30 +4342,30 @@
         <v>96</v>
       </c>
       <c r="AN16" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO16" s="9">
         <v>50</v>
       </c>
       <c r="AP16" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ16" s="9">
         <v>1</v>
       </c>
       <c r="AR16" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="AS16" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="AS16" s="9" t="s">
+      <c r="AT16" s="9" t="s">
         <v>151</v>
-      </c>
-      <c r="AT16" s="9" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:46">
       <c r="A17" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B17" s="8">
         <v>46211</v>
@@ -4374,13 +4374,13 @@
         <v>6</v>
       </c>
       <c r="D17" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E17" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F17" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G17" s="9" t="s">
         <v>33</v>
@@ -4389,7 +4389,7 @@
         <v>33</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>34</v>
@@ -4437,30 +4437,30 @@
         <v>96</v>
       </c>
       <c r="AN17" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO17" s="9">
         <v>75</v>
       </c>
       <c r="AP17" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ17" s="9">
         <v>1</v>
       </c>
       <c r="AR17" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AS17" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AT17" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:46">
       <c r="A18" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B18" s="8">
         <v>46210</v>
@@ -4469,7 +4469,7 @@
         <v>6</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>48</v>
@@ -4484,7 +4484,7 @@
         <v>33</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>93</v>
@@ -4532,7 +4532,7 @@
         <v>96</v>
       </c>
       <c r="AN18" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO18" s="9">
         <v>40</v>
@@ -4544,18 +4544,18 @@
         <v>1</v>
       </c>
       <c r="AR18" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS18" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="AT18" s="9" t="s">
         <v>157</v>
-      </c>
-      <c r="AT18" s="9" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:46">
       <c r="A19" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B19" s="8">
         <v>46210</v>
@@ -4564,7 +4564,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>48</v>
@@ -4600,7 +4600,7 @@
         <v>34</v>
       </c>
       <c r="S19" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="U19" s="9" t="s">
         <v>34</v>
@@ -4627,7 +4627,7 @@
         <v>96</v>
       </c>
       <c r="AN19" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO19" s="9">
         <v>40</v>
@@ -4639,18 +4639,18 @@
         <v>1</v>
       </c>
       <c r="AR19" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS19" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="AT19" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="AT19" s="9" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:46">
       <c r="A20" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B20" s="8">
         <v>46209</v>
@@ -4659,7 +4659,7 @@
         <v>6</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>48</v>
@@ -4692,10 +4692,10 @@
         <v>94</v>
       </c>
       <c r="R20" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="S20" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="S20" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="U20" s="9" t="s">
         <v>34</v>
@@ -4722,7 +4722,7 @@
         <v>96</v>
       </c>
       <c r="AN20" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO20" s="9">
         <v>40</v>
@@ -4734,18 +4734,18 @@
         <v>1</v>
       </c>
       <c r="AR20" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS20" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="AT20" s="9" t="s">
         <v>166</v>
-      </c>
-      <c r="AT20" s="9" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:46">
       <c r="A21" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B21" s="8">
         <v>46209</v>
@@ -4754,7 +4754,7 @@
         <v>6</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>48</v>
@@ -4769,7 +4769,7 @@
         <v>33</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>93</v>
@@ -4817,7 +4817,7 @@
         <v>96</v>
       </c>
       <c r="AN21" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO21" s="9">
         <v>40</v>
@@ -4829,18 +4829,18 @@
         <v>1</v>
       </c>
       <c r="AR21" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS21" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="AT21" s="9" t="s">
         <v>169</v>
-      </c>
-      <c r="AT21" s="9" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:46">
       <c r="A22" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B22" s="8">
         <v>46209</v>
@@ -4849,11 +4849,11 @@
         <v>4</v>
       </c>
       <c r="D22" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E22" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E22" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F22" s="9" t="s">
         <v>34</v>
       </c>
@@ -4864,7 +4864,7 @@
         <v>34</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>34</v>
@@ -4879,7 +4879,7 @@
         <v>34</v>
       </c>
       <c r="Q22" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R22" s="9" t="s">
         <v>33</v>
@@ -4912,13 +4912,13 @@
         <v>96</v>
       </c>
       <c r="AN22" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO22" s="9">
         <v>0</v>
       </c>
       <c r="AP22" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ22" s="9">
         <v>1</v>
@@ -4944,10 +4944,10 @@
         <v>6</v>
       </c>
       <c r="D23" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>176</v>
@@ -4959,7 +4959,7 @@
         <v>33</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>34</v>
@@ -5007,13 +5007,13 @@
         <v>96</v>
       </c>
       <c r="AN23" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO23" s="9">
         <v>75</v>
       </c>
       <c r="AP23" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ23" s="9">
         <v>1</v>
@@ -5039,7 +5039,7 @@
         <v>6</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>48</v>
@@ -5054,7 +5054,7 @@
         <v>33</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>93</v>
@@ -5102,7 +5102,7 @@
         <v>96</v>
       </c>
       <c r="AN24" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO24" s="9">
         <v>40</v>
@@ -5114,7 +5114,7 @@
         <v>1</v>
       </c>
       <c r="AR24" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS24" s="9" t="s">
         <v>181</v>
@@ -5134,7 +5134,7 @@
         <v>6</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>48</v>
@@ -5149,7 +5149,7 @@
         <v>33</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>34</v>
@@ -5197,7 +5197,7 @@
         <v>96</v>
       </c>
       <c r="AN25" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO25" s="9">
         <v>40</v>
@@ -5209,7 +5209,7 @@
         <v>1</v>
       </c>
       <c r="AR25" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS25" s="9" t="s">
         <v>184</v>
@@ -5229,7 +5229,7 @@
         <v>6</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>48</v>
@@ -5244,7 +5244,7 @@
         <v>33</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>93</v>
@@ -5292,7 +5292,7 @@
         <v>96</v>
       </c>
       <c r="AN26" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO26" s="9">
         <v>40</v>
@@ -5304,7 +5304,7 @@
         <v>1</v>
       </c>
       <c r="AR26" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS26" s="9" t="s">
         <v>187</v>
@@ -5324,10 +5324,10 @@
         <v>4</v>
       </c>
       <c r="D27" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E27" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>34</v>
@@ -5354,7 +5354,7 @@
         <v>34</v>
       </c>
       <c r="Q27" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R27" s="9" t="s">
         <v>33</v>
@@ -5387,13 +5387,13 @@
         <v>96</v>
       </c>
       <c r="AN27" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO27" s="9">
         <v>40</v>
       </c>
       <c r="AP27" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ27" s="9">
         <v>4</v>
@@ -5419,7 +5419,7 @@
         <v>6</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>194</v>
@@ -5434,7 +5434,7 @@
         <v>33</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J28" s="9" t="s">
         <v>93</v>
@@ -5482,7 +5482,7 @@
         <v>96</v>
       </c>
       <c r="AN28" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO28" s="9">
         <v>40</v>
@@ -5494,7 +5494,7 @@
         <v>1</v>
       </c>
       <c r="AR28" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS28" s="9" t="s">
         <v>195</v>
@@ -5514,7 +5514,7 @@
         <v>6</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>48</v>
@@ -5583,7 +5583,7 @@
         <v>96</v>
       </c>
       <c r="AN29" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO29" s="9">
         <v>40</v>
@@ -5595,7 +5595,7 @@
         <v>1</v>
       </c>
       <c r="AR29" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS29" s="9" t="s">
         <v>199</v>
@@ -5615,7 +5615,7 @@
         <v>6</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>48</v>
@@ -5630,7 +5630,7 @@
         <v>33</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J30" s="9" t="s">
         <v>93</v>
@@ -5678,7 +5678,7 @@
         <v>96</v>
       </c>
       <c r="AN30" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO30" s="9">
         <v>40</v>
@@ -5690,7 +5690,7 @@
         <v>1</v>
       </c>
       <c r="AR30" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS30" s="9" t="s">
         <v>203</v>
@@ -5710,7 +5710,7 @@
         <v>6</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>48</v>
@@ -5725,7 +5725,7 @@
         <v>33</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>93</v>
@@ -5773,7 +5773,7 @@
         <v>96</v>
       </c>
       <c r="AN31" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO31" s="9">
         <v>40</v>
@@ -5785,7 +5785,7 @@
         <v>1</v>
       </c>
       <c r="AR31" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS31" s="9" t="s">
         <v>206</v>
@@ -5805,7 +5805,7 @@
         <v>6</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>48</v>
@@ -5820,7 +5820,7 @@
         <v>33</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J32" s="9" t="s">
         <v>93</v>
@@ -5868,7 +5868,7 @@
         <v>96</v>
       </c>
       <c r="AN32" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO32" s="9">
         <v>40</v>
@@ -5880,7 +5880,7 @@
         <v>1</v>
       </c>
       <c r="AR32" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS32" s="9" t="s">
         <v>209</v>
@@ -5900,7 +5900,7 @@
         <v>6</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>48</v>
@@ -5915,7 +5915,7 @@
         <v>33</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>93</v>
@@ -5963,7 +5963,7 @@
         <v>96</v>
       </c>
       <c r="AN33" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO33" s="9">
         <v>60</v>
@@ -5975,7 +5975,7 @@
         <v>1</v>
       </c>
       <c r="AR33" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS33" s="9" t="s">
         <v>214</v>
@@ -5995,7 +5995,7 @@
         <v>6</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>48</v>
@@ -6064,7 +6064,7 @@
         <v>96</v>
       </c>
       <c r="AN34" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO34" s="9">
         <v>40</v>
@@ -6076,7 +6076,7 @@
         <v>1</v>
       </c>
       <c r="AR34" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS34" s="9" t="s">
         <v>218</v>
@@ -6096,7 +6096,7 @@
         <v>6</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>48</v>
@@ -6159,7 +6159,7 @@
         <v>96</v>
       </c>
       <c r="AN35" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO35" s="9">
         <v>40</v>
@@ -6171,7 +6171,7 @@
         <v>1</v>
       </c>
       <c r="AR35" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS35" s="9" t="s">
         <v>221</v>
@@ -6191,7 +6191,7 @@
         <v>6</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>48</v>
@@ -6206,7 +6206,7 @@
         <v>33</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>93</v>
@@ -6254,7 +6254,7 @@
         <v>96</v>
       </c>
       <c r="AN36" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO36" s="9">
         <v>40</v>
@@ -6266,7 +6266,7 @@
         <v>1</v>
       </c>
       <c r="AR36" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS36" s="9" t="s">
         <v>224</v>
@@ -6286,7 +6286,7 @@
         <v>6</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>48</v>
@@ -6349,7 +6349,7 @@
         <v>96</v>
       </c>
       <c r="AN37" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO37" s="9">
         <v>40</v>
@@ -6361,7 +6361,7 @@
         <v>1</v>
       </c>
       <c r="AR37" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS37" s="9" t="s">
         <v>228</v>
@@ -6381,7 +6381,7 @@
         <v>6</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>48</v>
@@ -6444,7 +6444,7 @@
         <v>96</v>
       </c>
       <c r="AN38" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO38" s="9">
         <v>40</v>
@@ -6456,7 +6456,7 @@
         <v>1</v>
       </c>
       <c r="AR38" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS38" s="9" t="s">
         <v>233</v>
@@ -6476,11 +6476,11 @@
         <v>4</v>
       </c>
       <c r="D39" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E39" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E39" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F39" s="9" t="s">
         <v>34</v>
       </c>
@@ -6491,7 +6491,7 @@
         <v>34</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>93</v>
@@ -6509,7 +6509,7 @@
         <v>34</v>
       </c>
       <c r="Q39" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R39" s="9" t="s">
         <v>33</v>
@@ -6542,13 +6542,13 @@
         <v>96</v>
       </c>
       <c r="AN39" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO39" s="9">
         <v>0</v>
       </c>
       <c r="AP39" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ39" s="9">
         <v>4</v>
@@ -6574,11 +6574,11 @@
         <v>4</v>
       </c>
       <c r="D40" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E40" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E40" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F40" s="9" t="s">
         <v>34</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>34</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J40" s="9" t="s">
         <v>34</v>
@@ -6604,7 +6604,7 @@
         <v>34</v>
       </c>
       <c r="Q40" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R40" s="9" t="s">
         <v>33</v>
@@ -6637,13 +6637,13 @@
         <v>96</v>
       </c>
       <c r="AN40" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO40" s="9">
         <v>0</v>
       </c>
       <c r="AP40" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ40" s="9">
         <v>1</v>
@@ -6669,7 +6669,7 @@
         <v>6</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>48</v>
@@ -6732,7 +6732,7 @@
         <v>96</v>
       </c>
       <c r="AN41" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO41" s="9">
         <v>40</v>
@@ -6744,7 +6744,7 @@
         <v>1</v>
       </c>
       <c r="AR41" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS41" s="9" t="s">
         <v>244</v>
@@ -6764,7 +6764,7 @@
         <v>6</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E42" s="9" t="s">
         <v>48</v>
@@ -6827,7 +6827,7 @@
         <v>96</v>
       </c>
       <c r="AN42" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO42" s="9">
         <v>40</v>
@@ -6839,7 +6839,7 @@
         <v>1</v>
       </c>
       <c r="AR42" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS42" s="9" t="s">
         <v>249</v>
@@ -6859,7 +6859,7 @@
         <v>6</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>48</v>
@@ -6922,7 +6922,7 @@
         <v>96</v>
       </c>
       <c r="AN43" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO43" s="9">
         <v>40</v>
@@ -6934,7 +6934,7 @@
         <v>1</v>
       </c>
       <c r="AR43" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS43" s="9" t="s">
         <v>254</v>
@@ -6954,7 +6954,7 @@
         <v>6</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>48</v>
@@ -7023,7 +7023,7 @@
         <v>96</v>
       </c>
       <c r="AN44" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO44" s="9">
         <v>40</v>
@@ -7035,7 +7035,7 @@
         <v>1</v>
       </c>
       <c r="AR44" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS44" s="9" t="s">
         <v>258</v>
@@ -7055,10 +7055,10 @@
         <v>6</v>
       </c>
       <c r="D45" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E45" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>41</v>
@@ -7118,13 +7118,13 @@
         <v>96</v>
       </c>
       <c r="AN45" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO45" s="9">
         <v>75</v>
       </c>
       <c r="AP45" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ45" s="9">
         <v>1</v>
@@ -7150,7 +7150,7 @@
         <v>6</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>31</v>
@@ -7165,7 +7165,7 @@
         <v>33</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J46" s="9" t="s">
         <v>34</v>
@@ -7213,13 +7213,13 @@
         <v>96</v>
       </c>
       <c r="AN46" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO46" s="9">
         <v>75</v>
       </c>
       <c r="AP46" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ46" s="9">
         <v>1</v>
@@ -7245,7 +7245,7 @@
         <v>6</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>48</v>
@@ -7314,7 +7314,7 @@
         <v>96</v>
       </c>
       <c r="AN47" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO47" s="9">
         <v>40</v>
@@ -7326,7 +7326,7 @@
         <v>1</v>
       </c>
       <c r="AR47" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS47" s="9" t="s">
         <v>269</v>
@@ -7346,7 +7346,7 @@
         <v>6</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>48</v>
@@ -7361,7 +7361,7 @@
         <v>33</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J48" s="9" t="s">
         <v>93</v>
@@ -7409,7 +7409,7 @@
         <v>96</v>
       </c>
       <c r="AN48" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO48" s="9">
         <v>40</v>
@@ -7421,7 +7421,7 @@
         <v>1</v>
       </c>
       <c r="AR48" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS48" s="9" t="s">
         <v>272</v>
@@ -7441,7 +7441,7 @@
         <v>6</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>48</v>
@@ -7456,7 +7456,7 @@
         <v>33</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J49" s="9" t="s">
         <v>93</v>
@@ -7504,7 +7504,7 @@
         <v>96</v>
       </c>
       <c r="AN49" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO49" s="9">
         <v>40</v>
@@ -7516,7 +7516,7 @@
         <v>1</v>
       </c>
       <c r="AR49" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS49" s="9" t="s">
         <v>275</v>
@@ -7536,7 +7536,7 @@
         <v>6</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>48</v>
@@ -7551,7 +7551,7 @@
         <v>33</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J50" s="9" t="s">
         <v>93</v>
@@ -7599,7 +7599,7 @@
         <v>96</v>
       </c>
       <c r="AN50" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO50" s="9">
         <v>60</v>
@@ -7611,7 +7611,7 @@
         <v>1</v>
       </c>
       <c r="AR50" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS50" s="9" t="s">
         <v>280</v>
@@ -7631,7 +7631,7 @@
         <v>6</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>48</v>
@@ -7694,7 +7694,7 @@
         <v>96</v>
       </c>
       <c r="AN51" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO51" s="9">
         <v>60</v>
@@ -7706,7 +7706,7 @@
         <v>1</v>
       </c>
       <c r="AR51" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS51" s="9" t="s">
         <v>285</v>
@@ -7726,10 +7726,10 @@
         <v>6</v>
       </c>
       <c r="D52" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E52" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>288</v>
@@ -7741,7 +7741,7 @@
         <v>33</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J52" s="9" t="s">
         <v>34</v>
@@ -7750,7 +7750,7 @@
         <v>25000000000</v>
       </c>
       <c r="M52" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O52" s="9" t="s">
         <v>33</v>
@@ -7792,19 +7792,19 @@
         <v>96</v>
       </c>
       <c r="AN52" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO52" s="9">
         <v>75</v>
       </c>
       <c r="AP52" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ52" s="9">
         <v>1</v>
       </c>
       <c r="AR52" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AS52" s="9" t="s">
         <v>289</v>
@@ -7824,13 +7824,13 @@
         <v>5</v>
       </c>
       <c r="D53" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E53" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E53" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F53" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>33</v>
@@ -7839,7 +7839,7 @@
         <v>33</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J53" s="9" t="s">
         <v>34</v>
@@ -7848,7 +7848,7 @@
         <v>251000000000</v>
       </c>
       <c r="M53" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>33</v>
@@ -7890,13 +7890,13 @@
         <v>96</v>
       </c>
       <c r="AN53" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO53" s="9">
         <v>15</v>
       </c>
       <c r="AP53" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ53" s="9">
         <v>1</v>
@@ -7922,7 +7922,7 @@
         <v>6</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>37</v>
@@ -7937,7 +7937,7 @@
         <v>33</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J54" s="9" t="s">
         <v>93</v>
@@ -8020,10 +8020,10 @@
         <v>6</v>
       </c>
       <c r="D55" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E55" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E55" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>176</v>
@@ -8035,7 +8035,7 @@
         <v>33</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J55" s="9" t="s">
         <v>34</v>
@@ -8083,19 +8083,19 @@
         <v>96</v>
       </c>
       <c r="AN55" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO55" s="9">
         <v>15</v>
       </c>
       <c r="AP55" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ55" s="9">
         <v>1</v>
       </c>
       <c r="AR55" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AS55" s="9" t="s">
         <v>299</v>
@@ -8115,11 +8115,11 @@
         <v>4</v>
       </c>
       <c r="D56" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E56" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E56" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F56" s="9" t="s">
         <v>34</v>
       </c>
@@ -8130,7 +8130,7 @@
         <v>34</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>34</v>
@@ -8145,7 +8145,7 @@
         <v>34</v>
       </c>
       <c r="Q56" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R56" s="9" t="s">
         <v>33</v>
@@ -8178,13 +8178,13 @@
         <v>96</v>
       </c>
       <c r="AN56" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO56" s="9">
         <v>0</v>
       </c>
       <c r="AP56" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ56" s="9">
         <v>1</v>
@@ -8210,7 +8210,7 @@
         <v>6</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>48</v>
@@ -8225,7 +8225,7 @@
         <v>33</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J57" s="9" t="s">
         <v>93</v>
@@ -8273,7 +8273,7 @@
         <v>96</v>
       </c>
       <c r="AN57" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO57" s="9">
         <v>40</v>
@@ -8285,7 +8285,7 @@
         <v>1</v>
       </c>
       <c r="AR57" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS57" s="9" t="s">
         <v>307</v>
@@ -8305,7 +8305,7 @@
         <v>6</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>48</v>
@@ -8320,7 +8320,7 @@
         <v>33</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J58" s="9" t="s">
         <v>93</v>
@@ -8368,7 +8368,7 @@
         <v>96</v>
       </c>
       <c r="AN58" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO58" s="9">
         <v>40</v>
@@ -8380,7 +8380,7 @@
         <v>1</v>
       </c>
       <c r="AR58" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS58" s="9" t="s">
         <v>310</v>
@@ -8400,7 +8400,7 @@
         <v>6</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>48</v>
@@ -8415,7 +8415,7 @@
         <v>33</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J59" s="9" t="s">
         <v>93</v>
@@ -8463,7 +8463,7 @@
         <v>96</v>
       </c>
       <c r="AN59" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO59" s="9">
         <v>40</v>
@@ -8475,7 +8475,7 @@
         <v>1</v>
       </c>
       <c r="AR59" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS59" s="9" t="s">
         <v>312</v>
@@ -8495,7 +8495,7 @@
         <v>6</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E60" s="9" t="s">
         <v>48</v>
@@ -8558,7 +8558,7 @@
         <v>96</v>
       </c>
       <c r="AN60" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO60" s="9">
         <v>40</v>
@@ -8570,7 +8570,7 @@
         <v>1</v>
       </c>
       <c r="AR60" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS60" s="9" t="s">
         <v>314</v>
@@ -8590,7 +8590,7 @@
         <v>6</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>48</v>
@@ -8653,7 +8653,7 @@
         <v>96</v>
       </c>
       <c r="AN61" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO61" s="9">
         <v>40</v>
@@ -8665,7 +8665,7 @@
         <v>1</v>
       </c>
       <c r="AR61" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS61" s="9" t="s">
         <v>317</v>
@@ -8685,7 +8685,7 @@
         <v>6</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E62" s="9" t="s">
         <v>48</v>
@@ -8700,7 +8700,7 @@
         <v>33</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J62" s="9" t="s">
         <v>34</v>
@@ -8748,7 +8748,7 @@
         <v>96</v>
       </c>
       <c r="AN62" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO62" s="9">
         <v>40</v>
@@ -8760,7 +8760,7 @@
         <v>1</v>
       </c>
       <c r="AR62" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS62" s="9" t="s">
         <v>320</v>
@@ -8780,7 +8780,7 @@
         <v>6</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>48</v>
@@ -8795,7 +8795,7 @@
         <v>33</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J63" s="9" t="s">
         <v>93</v>
@@ -8843,7 +8843,7 @@
         <v>96</v>
       </c>
       <c r="AN63" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO63" s="9">
         <v>40</v>
@@ -8855,7 +8855,7 @@
         <v>1</v>
       </c>
       <c r="AR63" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AS63" s="9" t="s">
         <v>323</v>
@@ -8875,7 +8875,7 @@
         <v>6</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>194</v>
@@ -8890,7 +8890,7 @@
         <v>33</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J64" s="9" t="s">
         <v>93</v>
@@ -8935,13 +8935,13 @@
         <v>96</v>
       </c>
       <c r="AN64" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO64" s="9">
         <v>75</v>
       </c>
       <c r="AP64" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ64" s="9">
         <v>1</v>
@@ -8967,7 +8967,7 @@
         <v>6</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>31</v>
@@ -8982,7 +8982,7 @@
         <v>33</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J65" s="9" t="s">
         <v>93</v>
@@ -9065,10 +9065,10 @@
         <v>6</v>
       </c>
       <c r="D66" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E66" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E66" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>336</v>
@@ -9080,7 +9080,7 @@
         <v>33</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J66" s="9" t="s">
         <v>34</v>
@@ -9131,13 +9131,13 @@
         <v>96</v>
       </c>
       <c r="AN66" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO66" s="9">
         <v>67</v>
       </c>
       <c r="AP66" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ66" s="9">
         <v>1</v>
@@ -9178,7 +9178,7 @@
         <v>34</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J67" s="9" t="s">
         <v>93</v>
@@ -9193,7 +9193,7 @@
         <v>34</v>
       </c>
       <c r="Q67" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R67" s="9" t="s">
         <v>33</v>
@@ -9226,13 +9226,13 @@
         <v>96</v>
       </c>
       <c r="AN67" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO67" s="9">
         <v>65</v>
       </c>
       <c r="AP67" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ67" s="9">
         <v>9</v>
@@ -9258,7 +9258,7 @@
         <v>4</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>43</v>
@@ -9273,7 +9273,7 @@
         <v>41</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J68" s="9" t="s">
         <v>93</v>
@@ -9291,7 +9291,7 @@
         <v>34</v>
       </c>
       <c r="Q68" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R68" s="9" t="s">
         <v>33</v>
@@ -9356,7 +9356,7 @@
         <v>4</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>351</v>
@@ -9371,7 +9371,7 @@
         <v>34</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J69" s="9" t="s">
         <v>34</v>
@@ -9386,7 +9386,7 @@
         <v>34</v>
       </c>
       <c r="Q69" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R69" s="9" t="s">
         <v>33</v>
@@ -9419,13 +9419,13 @@
         <v>96</v>
       </c>
       <c r="AN69" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO69" s="9">
         <v>67</v>
       </c>
       <c r="AP69" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ69" s="9">
         <v>1</v>
@@ -9451,11 +9451,11 @@
         <v>4</v>
       </c>
       <c r="D70" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E70" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E70" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F70" s="9" t="s">
         <v>34</v>
       </c>
@@ -9466,7 +9466,7 @@
         <v>34</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J70" s="9" t="s">
         <v>34</v>
@@ -9481,7 +9481,7 @@
         <v>34</v>
       </c>
       <c r="Q70" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R70" s="9" t="s">
         <v>33</v>
@@ -9514,13 +9514,13 @@
         <v>96</v>
       </c>
       <c r="AN70" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO70" s="9">
         <v>0</v>
       </c>
       <c r="AP70" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ70" s="9">
         <v>1</v>
@@ -9546,10 +9546,10 @@
         <v>5</v>
       </c>
       <c r="D71" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E71" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>344</v>
@@ -9561,7 +9561,7 @@
         <v>33</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J71" s="9" t="s">
         <v>34</v>
@@ -9609,13 +9609,13 @@
         <v>96</v>
       </c>
       <c r="AN71" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO71" s="9">
         <v>15</v>
       </c>
       <c r="AP71" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ71" s="9">
         <v>1</v>
@@ -9641,10 +9641,10 @@
         <v>5</v>
       </c>
       <c r="D72" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E72" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E72" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>344</v>
@@ -9704,13 +9704,13 @@
         <v>96</v>
       </c>
       <c r="AN72" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO72" s="9">
         <v>15</v>
       </c>
       <c r="AP72" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ72" s="9">
         <v>1</v>
@@ -9736,11 +9736,11 @@
         <v>4</v>
       </c>
       <c r="D73" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E73" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E73" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F73" s="9" t="s">
         <v>34</v>
       </c>
@@ -9751,7 +9751,7 @@
         <v>34</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J73" s="9" t="s">
         <v>34</v>
@@ -9766,7 +9766,7 @@
         <v>34</v>
       </c>
       <c r="Q73" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R73" s="9" t="s">
         <v>33</v>
@@ -9799,13 +9799,13 @@
         <v>96</v>
       </c>
       <c r="AN73" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO73" s="9">
         <v>0</v>
       </c>
       <c r="AP73" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ73" s="9">
         <v>1</v>
@@ -9831,10 +9831,10 @@
         <v>6</v>
       </c>
       <c r="D74" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E74" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>369</v>
@@ -9846,7 +9846,7 @@
         <v>33</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J74" s="9" t="s">
         <v>93</v>
@@ -9897,13 +9897,13 @@
         <v>96</v>
       </c>
       <c r="AN74" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO74" s="9">
         <v>7</v>
       </c>
       <c r="AP74" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ74" s="9">
         <v>1</v>
@@ -9929,11 +9929,11 @@
         <v>4</v>
       </c>
       <c r="D75" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E75" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="E75" s="9" t="s">
-        <v>123</v>
-      </c>
       <c r="F75" s="9" t="s">
         <v>34</v>
       </c>
@@ -9944,7 +9944,7 @@
         <v>34</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J75" s="9" t="s">
         <v>34</v>
@@ -9959,7 +9959,7 @@
         <v>34</v>
       </c>
       <c r="Q75" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R75" s="9" t="s">
         <v>33</v>
@@ -9992,13 +9992,13 @@
         <v>96</v>
       </c>
       <c r="AN75" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO75" s="9">
         <v>40</v>
       </c>
       <c r="AP75" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ75" s="9">
         <v>1</v>
@@ -10024,10 +10024,10 @@
         <v>5</v>
       </c>
       <c r="D76" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E76" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>41</v>
@@ -10039,7 +10039,7 @@
         <v>33</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J76" s="9" t="s">
         <v>93</v>
@@ -10090,13 +10090,13 @@
         <v>96</v>
       </c>
       <c r="AN76" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO76" s="9">
         <v>15</v>
       </c>
       <c r="AP76" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ76" s="9">
         <v>1</v>
@@ -10122,10 +10122,10 @@
         <v>5</v>
       </c>
       <c r="D77" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E77" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>41</v>
@@ -10185,13 +10185,13 @@
         <v>96</v>
       </c>
       <c r="AN77" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO77" s="9">
         <v>15</v>
       </c>
       <c r="AP77" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ77" s="9">
         <v>1</v>
@@ -10217,10 +10217,10 @@
         <v>4</v>
       </c>
       <c r="D78" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E78" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E78" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>34</v>
@@ -10247,7 +10247,7 @@
         <v>34</v>
       </c>
       <c r="Q78" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R78" s="9" t="s">
         <v>33</v>
@@ -10280,13 +10280,13 @@
         <v>96</v>
       </c>
       <c r="AN78" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO78" s="9">
         <v>0</v>
       </c>
       <c r="AP78" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ78" s="9">
         <v>1</v>
@@ -10312,10 +10312,10 @@
         <v>4</v>
       </c>
       <c r="D79" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E79" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>34</v>
@@ -10342,7 +10342,7 @@
         <v>34</v>
       </c>
       <c r="Q79" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R79" s="9" t="s">
         <v>33</v>
@@ -10375,13 +10375,13 @@
         <v>96</v>
       </c>
       <c r="AN79" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO79" s="9">
         <v>0</v>
       </c>
       <c r="AP79" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ79" s="9">
         <v>1</v>
@@ -10407,10 +10407,10 @@
         <v>4</v>
       </c>
       <c r="D80" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E80" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>34</v>
@@ -10437,7 +10437,7 @@
         <v>34</v>
       </c>
       <c r="Q80" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R80" s="9" t="s">
         <v>33</v>
@@ -10470,13 +10470,13 @@
         <v>96</v>
       </c>
       <c r="AN80" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO80" s="9">
         <v>0</v>
       </c>
       <c r="AP80" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ80" s="9">
         <v>3</v>
@@ -10502,10 +10502,10 @@
         <v>4</v>
       </c>
       <c r="D81" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E81" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>34</v>
@@ -10532,7 +10532,7 @@
         <v>34</v>
       </c>
       <c r="Q81" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R81" s="9" t="s">
         <v>33</v>
@@ -10565,13 +10565,13 @@
         <v>96</v>
       </c>
       <c r="AN81" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO81" s="9">
         <v>0</v>
       </c>
       <c r="AP81" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ81" s="9">
         <v>1</v>
@@ -10597,10 +10597,10 @@
         <v>4</v>
       </c>
       <c r="D82" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E82" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E82" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>34</v>
@@ -10627,7 +10627,7 @@
         <v>34</v>
       </c>
       <c r="Q82" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R82" s="9" t="s">
         <v>33</v>
@@ -10660,13 +10660,13 @@
         <v>96</v>
       </c>
       <c r="AN82" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO82" s="9">
         <v>0</v>
       </c>
       <c r="AP82" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ82" s="9">
         <v>1</v>
@@ -10692,10 +10692,10 @@
         <v>6</v>
       </c>
       <c r="D83" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E83" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E83" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>344</v>
@@ -10755,13 +10755,13 @@
         <v>96</v>
       </c>
       <c r="AN83" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO83" s="9">
         <v>15</v>
       </c>
       <c r="AP83" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ83" s="9">
         <v>1</v>
@@ -10787,10 +10787,10 @@
         <v>5</v>
       </c>
       <c r="D84" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E84" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>41</v>
@@ -10802,7 +10802,7 @@
         <v>33</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J84" s="9" t="s">
         <v>93</v>
@@ -10850,13 +10850,13 @@
         <v>96</v>
       </c>
       <c r="AN84" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO84" s="9">
         <v>15</v>
       </c>
       <c r="AP84" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ84" s="9">
         <v>2</v>
@@ -10882,10 +10882,10 @@
         <v>5</v>
       </c>
       <c r="D85" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E85" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E85" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>41</v>
@@ -10897,7 +10897,7 @@
         <v>33</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J85" s="9" t="s">
         <v>34</v>
@@ -10945,13 +10945,13 @@
         <v>96</v>
       </c>
       <c r="AN85" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO85" s="9">
         <v>15</v>
       </c>
       <c r="AP85" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ85" s="9">
         <v>1</v>
@@ -10977,10 +10977,10 @@
         <v>6</v>
       </c>
       <c r="D86" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E86" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E86" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>344</v>
@@ -10992,7 +10992,7 @@
         <v>33</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J86" s="9" t="s">
         <v>34</v>
@@ -11040,13 +11040,13 @@
         <v>96</v>
       </c>
       <c r="AN86" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO86" s="9">
         <v>75</v>
       </c>
       <c r="AP86" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ86" s="9">
         <v>1</v>
@@ -11072,10 +11072,10 @@
         <v>4</v>
       </c>
       <c r="D87" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E87" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E87" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>418</v>
@@ -11108,7 +11108,7 @@
         <v>34</v>
       </c>
       <c r="Q87" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R87" s="9" t="s">
         <v>33</v>
@@ -11141,13 +11141,13 @@
         <v>96</v>
       </c>
       <c r="AN87" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO87" s="9">
         <v>60</v>
       </c>
       <c r="AP87" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ87" s="9">
         <v>3</v>
@@ -11173,10 +11173,10 @@
         <v>6</v>
       </c>
       <c r="D88" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E88" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E88" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>419</v>
@@ -11188,7 +11188,7 @@
         <v>33</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J88" s="9" t="s">
         <v>34</v>
@@ -11236,13 +11236,13 @@
         <v>96</v>
       </c>
       <c r="AN88" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO88" s="9">
         <v>75</v>
       </c>
       <c r="AP88" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ88" s="9">
         <v>1</v>
@@ -11268,10 +11268,10 @@
         <v>5</v>
       </c>
       <c r="D89" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E89" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E89" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>344</v>
@@ -11331,13 +11331,13 @@
         <v>96</v>
       </c>
       <c r="AN89" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="AO89" s="9">
         <v>15</v>
       </c>
       <c r="AP89" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ89" s="9">
         <v>1</v>
@@ -11363,7 +11363,7 @@
         <v>6</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E90" s="9" t="s">
         <v>194</v>
@@ -11378,7 +11378,7 @@
         <v>33</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J90" s="9" t="s">
         <v>93</v>
@@ -11429,13 +11429,13 @@
         <v>96</v>
       </c>
       <c r="AN90" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO90" s="9">
         <v>75</v>
       </c>
       <c r="AP90" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ90" s="9">
         <v>1</v>
@@ -11461,7 +11461,7 @@
         <v>6</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>194</v>
@@ -11476,7 +11476,7 @@
         <v>33</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J91" s="9" t="s">
         <v>34</v>
@@ -11524,13 +11524,13 @@
         <v>96</v>
       </c>
       <c r="AN91" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO91" s="9">
         <v>75</v>
       </c>
       <c r="AP91" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ91" s="9">
         <v>1</v>
@@ -11556,10 +11556,10 @@
         <v>6</v>
       </c>
       <c r="D92" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E92" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E92" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>419</v>
@@ -11571,7 +11571,7 @@
         <v>33</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J92" s="9" t="s">
         <v>93</v>
@@ -11622,13 +11622,13 @@
         <v>96</v>
       </c>
       <c r="AN92" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO92" s="9">
         <v>75</v>
       </c>
       <c r="AP92" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ92" s="9">
         <v>1</v>
@@ -11654,10 +11654,10 @@
         <v>6</v>
       </c>
       <c r="D93" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="E93" s="9" t="s">
         <v>122</v>
-      </c>
-      <c r="E93" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>419</v>
@@ -11669,7 +11669,7 @@
         <v>33</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J93" s="9" t="s">
         <v>34</v>
@@ -11717,13 +11717,13 @@
         <v>96</v>
       </c>
       <c r="AN93" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO93" s="9">
         <v>75</v>
       </c>
       <c r="AP93" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AQ93" s="9">
         <v>1</v>
@@ -11749,7 +11749,7 @@
         <v>6</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E94" s="9" t="s">
         <v>31</v>
@@ -11764,7 +11764,7 @@
         <v>33</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J94" s="9" t="s">
         <v>93</v>
@@ -11830,7 +11830,7 @@
         <v>1</v>
       </c>
       <c r="AR94" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AS94" s="9" t="s">
         <v>442</v>
@@ -11850,7 +11850,7 @@
         <v>6</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>48</v>
@@ -11865,7 +11865,7 @@
         <v>33</v>
       </c>
       <c r="I95" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J95" s="9" t="s">
         <v>93</v>
@@ -11931,7 +11931,7 @@
         <v>1</v>
       </c>
       <c r="AR95" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AS95" s="9" t="s">
         <v>445</v>
@@ -11951,7 +11951,7 @@
         <v>6</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E96" s="9" t="s">
         <v>194</v>
@@ -11966,7 +11966,7 @@
         <v>33</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J96" s="9" t="s">
         <v>34</v>
@@ -12046,7 +12046,7 @@
         <v>4</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>48</v>
@@ -12061,7 +12061,7 @@
         <v>34</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J97" s="9" t="s">
         <v>34</v>
@@ -12076,7 +12076,7 @@
         <v>34</v>
       </c>
       <c r="Q97" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R97" s="9" t="s">
         <v>33</v>
@@ -12109,7 +12109,7 @@
         <v>96</v>
       </c>
       <c r="AN97" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO97" s="9">
         <v>65</v>
@@ -12121,7 +12121,7 @@
         <v>1</v>
       </c>
       <c r="AR97" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AS97" s="9" t="s">
         <v>450</v>
@@ -12141,7 +12141,7 @@
         <v>6</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E98" s="9" t="s">
         <v>194</v>
@@ -12219,7 +12219,7 @@
         <v>1</v>
       </c>
       <c r="AR98" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AS98" s="9" t="s">
         <v>455</v>
@@ -12239,7 +12239,7 @@
         <v>6</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>48</v>
@@ -12254,7 +12254,7 @@
         <v>33</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J99" s="9" t="s">
         <v>93</v>
@@ -12320,7 +12320,7 @@
         <v>1</v>
       </c>
       <c r="AR99" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AS99" s="9" t="s">
         <v>459</v>
@@ -12340,7 +12340,7 @@
         <v>6</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E100" s="9" t="s">
         <v>194</v>
@@ -12355,7 +12355,7 @@
         <v>33</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J100" s="9" t="s">
         <v>93</v>
@@ -12418,7 +12418,7 @@
         <v>1</v>
       </c>
       <c r="AR100" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AS100" s="9" t="s">
         <v>462</v>
@@ -12438,7 +12438,7 @@
         <v>4</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>48</v>
@@ -12453,7 +12453,7 @@
         <v>34</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J101" s="9" t="s">
         <v>93</v>
@@ -12468,7 +12468,7 @@
         <v>34</v>
       </c>
       <c r="Q101" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R101" s="9" t="s">
         <v>33</v>
@@ -12501,7 +12501,7 @@
         <v>96</v>
       </c>
       <c r="AN101" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="AO101" s="9">
         <v>40</v>
@@ -12513,7 +12513,7 @@
         <v>1</v>
       </c>
       <c r="AR101" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AS101" s="9" t="s">
         <v>466</v>
@@ -12533,7 +12533,7 @@
         <v>4</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>43</v>
@@ -12548,7 +12548,7 @@
         <v>471</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J102" s="9" t="s">
         <v>472</v>
@@ -12557,7 +12557,7 @@
         <v>28000000000</v>
       </c>
       <c r="M102" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N102" s="11">
         <v>1</v>
@@ -12593,7 +12593,7 @@
         <v>44957</v>
       </c>
       <c r="AH102" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AK102" s="9" t="s">
         <v>475</v>
@@ -12637,7 +12637,7 @@
         <v>4</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>43</v>
@@ -12652,7 +12652,7 @@
         <v>471</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J103" s="9" t="s">
         <v>472</v>
@@ -12664,7 +12664,7 @@
         <v>69000000000</v>
       </c>
       <c r="M103" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N103" s="11">
         <v>1</v>
@@ -12676,7 +12676,7 @@
         <v>485</v>
       </c>
       <c r="Q103" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R103" s="9" t="s">
         <v>33</v>
@@ -12706,7 +12706,7 @@
         <v>44589</v>
       </c>
       <c r="AH103" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AI103" s="12">
         <v>5.369231966383939</v>
@@ -12756,7 +12756,7 @@
         <v>4</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E104" s="9" t="s">
         <v>43</v>
@@ -12771,7 +12771,7 @@
         <v>471</v>
       </c>
       <c r="I104" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J104" s="9" t="s">
         <v>472</v>
@@ -12780,7 +12780,7 @@
         <v>10400000000</v>
       </c>
       <c r="M104" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N104" s="11">
         <v>1</v>
@@ -12816,7 +12816,7 @@
         <v>44592</v>
       </c>
       <c r="AH104" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AK104" s="9" t="s">
         <v>496</v>
@@ -12860,7 +12860,7 @@
         <v>4</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>43</v>
@@ -12875,7 +12875,7 @@
         <v>471</v>
       </c>
       <c r="I105" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J105" s="9" t="s">
         <v>472</v>
@@ -12887,7 +12887,7 @@
         <v>16500000000</v>
       </c>
       <c r="M105" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N105" s="11">
         <v>1</v>
@@ -12923,7 +12923,7 @@
         <v>44561</v>
       </c>
       <c r="AH105" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AI105" s="12">
         <v>5.128731151913017</v>
@@ -12970,7 +12970,7 @@
         <v>4</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E106" s="9" t="s">
         <v>43</v>
@@ -12985,7 +12985,7 @@
         <v>471</v>
       </c>
       <c r="I106" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J106" s="9" t="s">
         <v>472</v>
@@ -12997,7 +12997,7 @@
         <v>68700000000</v>
       </c>
       <c r="M106" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N106" s="11">
         <v>1</v>
@@ -13009,7 +13009,7 @@
         <v>514</v>
       </c>
       <c r="Q106" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="R106" s="9" t="s">
         <v>33</v>
@@ -13036,7 +13036,7 @@
         <v>44196</v>
       </c>
       <c r="AH106" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AI106" s="12">
         <v>8.496166213208014</v>
@@ -13083,7 +13083,7 @@
         <v>4</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>43</v>
@@ -13098,7 +13098,7 @@
         <v>471</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J107" s="9" t="s">
         <v>472</v>
@@ -13110,7 +13110,7 @@
         <v>27700000000</v>
       </c>
       <c r="M107" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N107" s="11">
         <v>1</v>
@@ -13146,7 +13146,7 @@
         <v>43861</v>
       </c>
       <c r="AH107" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AI107" s="12">
         <v>43.93882193197572</v>
@@ -13193,7 +13193,7 @@
         <v>4</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>43</v>
@@ -13208,7 +13208,7 @@
         <v>471</v>
       </c>
       <c r="I108" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J108" s="9" t="s">
         <v>472</v>
@@ -13217,7 +13217,7 @@
         <v>35000000000</v>
       </c>
       <c r="M108" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N108" s="11">
         <v>1</v>
@@ -13253,7 +13253,7 @@
         <v>43918</v>
       </c>
       <c r="AH108" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AK108" s="9" t="s">
         <v>534</v>
@@ -13297,7 +13297,7 @@
         <v>4</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>43</v>
@@ -13312,7 +13312,7 @@
         <v>471</v>
       </c>
       <c r="I109" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J109" s="9" t="s">
         <v>472</v>
@@ -13324,7 +13324,7 @@
         <v>15700000000</v>
       </c>
       <c r="M109" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N109" s="11">
         <v>1</v>
@@ -13360,7 +13360,7 @@
         <v>43465</v>
       </c>
       <c r="AH109" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AI109" s="12">
         <v>13.54616048317515</v>
@@ -13407,7 +13407,7 @@
         <v>4</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E110" s="9" t="s">
         <v>43</v>
@@ -13422,7 +13422,7 @@
         <v>471</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J110" s="9" t="s">
         <v>472</v>
@@ -13434,7 +13434,7 @@
         <v>34000000000</v>
       </c>
       <c r="M110" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N110" s="11">
         <v>1</v>
@@ -13470,7 +13470,7 @@
         <v>43159</v>
       </c>
       <c r="AH110" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AI110" s="12">
         <v>11.64199761612978</v>
@@ -13517,7 +13517,7 @@
         <v>4</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>43</v>
@@ -13532,7 +13532,7 @@
         <v>471</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="J111" s="9" t="s">
         <v>472</v>
@@ -13544,7 +13544,7 @@
         <v>26200000000</v>
       </c>
       <c r="M111" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N111" s="11">
         <v>1</v>
@@ -13583,7 +13583,7 @@
         <v>42369</v>
       </c>
       <c r="AH111" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AI111" s="12">
         <v>8.759872828044699</v>
@@ -13858,7 +13858,7 @@
         <v>45008</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G7" s="10">
         <v>3653708000</v>
@@ -13890,7 +13890,7 @@
         <v>44644</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G8" s="10">
         <v>12851000000</v>
@@ -13934,7 +13934,7 @@
         <v>44643</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G9" s="10">
         <v>592200000</v>
@@ -13966,7 +13966,7 @@
         <v>44608</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G10" s="10">
         <v>3217170000</v>
@@ -13998,7 +13998,7 @@
         <v>44250</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G11" s="10">
         <v>8086000000</v>
@@ -14033,7 +14033,7 @@
         <v>43902</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G12" s="10">
         <v>630422000</v>
@@ -14065,7 +14065,7 @@
         <v>43966</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G13" s="10">
         <v>3162666000</v>
@@ -14097,7 +14097,7 @@
         <v>43518</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G14" s="10">
         <v>1159000000</v>
@@ -14129,7 +14129,7 @@
         <v>43215</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G15" s="10">
         <v>2920461000</v>
@@ -14164,7 +14164,7 @@
         <v>42412</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G16" s="10">
         <v>2990911000</v>
@@ -14315,13 +14315,13 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B7" s="8">
         <v>46211</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>34</v>
@@ -14330,7 +14330,7 @@
         <v>34</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>587</v>
@@ -14356,7 +14356,7 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B8" s="8">
         <v>46209</v>
@@ -14371,7 +14371,7 @@
         <v>34</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="J8" s="9" t="s">
         <v>587</v>
@@ -14412,7 +14412,7 @@
         <v>34</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>587</v>
@@ -14453,7 +14453,7 @@
         <v>34</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="J10" s="9" t="s">
         <v>587</v>
@@ -14494,7 +14494,7 @@
         <v>34</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>587</v>
@@ -14535,7 +14535,7 @@
         <v>34</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>587</v>
@@ -14576,7 +14576,7 @@
         <v>34</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>587</v>
@@ -14658,7 +14658,7 @@
         <v>34</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>587</v>
@@ -14699,7 +14699,7 @@
         <v>34</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>587</v>
@@ -14740,7 +14740,7 @@
         <v>34</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>587</v>
@@ -14781,7 +14781,7 @@
         <v>34</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>587</v>
@@ -14822,7 +14822,7 @@
         <v>34</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>587</v>
@@ -14863,7 +14863,7 @@
         <v>34</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>587</v>
@@ -14904,7 +14904,7 @@
         <v>34</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>587</v>
@@ -14945,7 +14945,7 @@
         <v>34</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>587</v>
@@ -14986,7 +14986,7 @@
         <v>34</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>97</v>
+        <v>171</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>587</v>
@@ -15027,7 +15027,7 @@
         <v>34</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>587</v>
@@ -15068,7 +15068,7 @@
         <v>34</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>587</v>
@@ -15109,7 +15109,7 @@
         <v>34</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="J26" s="9" t="s">
         <v>587</v>
@@ -15144,13 +15144,13 @@
         <v>469</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F27" s="10">
         <v>3653708000</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>35</v>
@@ -15191,7 +15191,7 @@
         <v>69000000000</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F28" s="10">
         <v>12851000000</v>
@@ -15200,7 +15200,7 @@
         <v>2966000000</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I28" s="9" t="s">
         <v>35</v>
@@ -15238,13 +15238,13 @@
         <v>493</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F29" s="10">
         <v>592200000</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I29" s="9" t="s">
         <v>35</v>
@@ -15285,13 +15285,13 @@
         <v>16500000000</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F30" s="10">
         <v>3217170000</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I30" s="9" t="s">
         <v>35</v>
@@ -15332,13 +15332,13 @@
         <v>68700000000</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F31" s="10">
         <v>8086000000</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I31" s="9" t="s">
         <v>35</v>
@@ -15379,13 +15379,13 @@
         <v>27700000000</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F32" s="10">
         <v>630422000</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I32" s="9" t="s">
         <v>35</v>
@@ -15423,13 +15423,13 @@
         <v>531</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F33" s="10">
         <v>3162666000</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>35</v>
@@ -15470,13 +15470,13 @@
         <v>15700000000</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F34" s="10">
         <v>1159000000</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I34" s="9" t="s">
         <v>35</v>
@@ -15517,13 +15517,13 @@
         <v>34000000000</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F35" s="10">
         <v>2920461000</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I35" s="9" t="s">
         <v>35</v>
@@ -15564,7 +15564,7 @@
         <v>26200000000</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F36" s="10">
         <v>2990911000</v>
@@ -15573,7 +15573,7 @@
         <v>254472000</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I36" s="9" t="s">
         <v>35</v>
@@ -15797,10 +15797,10 @@
         <v>46212</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>598</v>
@@ -15809,7 +15809,7 @@
         <v>98</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H8" s="8">
         <v>46212</v>
@@ -15818,10 +15818,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K8" s="13" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M8" t="s">
         <v>689</v>
@@ -15844,7 +15844,7 @@
     </row>
     <row r="9" spans="1:18" ht="28" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B9" s="8">
         <v>46211</v>
@@ -15853,7 +15853,7 @@
         <v>34</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>598</v>
@@ -15862,7 +15862,7 @@
         <v>98</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H9" s="8">
         <v>46211</v>
@@ -15871,10 +15871,10 @@
         <v>1</v>
       </c>
       <c r="J9" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="K9" s="13" t="s">
         <v>115</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>116</v>
       </c>
       <c r="M9" t="s">
         <v>690</v>
@@ -15897,7 +15897,7 @@
     </row>
     <row r="10" spans="1:18" ht="28" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B10" s="8">
         <v>46211</v>
@@ -15906,7 +15906,7 @@
         <v>32</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>599</v>
@@ -15915,7 +15915,7 @@
         <v>98</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H10" s="8">
         <v>46211</v>
@@ -15924,7 +15924,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K10" s="13" t="s">
         <v>36</v>
@@ -15950,25 +15950,25 @@
     </row>
     <row r="11" spans="1:18" ht="28" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11" s="8">
         <v>46211</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>600</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="9">
@@ -15978,7 +15978,7 @@
         <v>601</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M11" t="s">
         <v>692</v>
@@ -16001,7 +16001,7 @@
     </row>
     <row r="12" spans="1:18" ht="28" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B12" s="8">
         <v>46211</v>
@@ -16010,16 +16010,16 @@
         <v>34</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>600</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="9">
@@ -16029,7 +16029,7 @@
         <v>602</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M12" t="s">
         <v>693</v>
@@ -16052,25 +16052,25 @@
     </row>
     <row r="13" spans="1:18" ht="28" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B13" s="8">
         <v>46211</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>600</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9">
@@ -16080,7 +16080,7 @@
         <v>603</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M13" t="s">
         <v>694</v>
@@ -16103,25 +16103,25 @@
     </row>
     <row r="14" spans="1:18" ht="28" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B14" s="8">
         <v>46211</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>600</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9">
@@ -16131,7 +16131,7 @@
         <v>604</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M14" t="s">
         <v>695</v>
@@ -16154,25 +16154,25 @@
     </row>
     <row r="15" spans="1:18" ht="28" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B15" s="8">
         <v>46211</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>600</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9">
@@ -16182,12 +16182,12 @@
         <v>605</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="28" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B16" s="8">
         <v>46211</v>
@@ -16196,16 +16196,16 @@
         <v>34</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>600</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="9">
@@ -16215,7 +16215,7 @@
         <v>606</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>696</v>
@@ -16230,25 +16230,25 @@
     </row>
     <row r="17" spans="1:11" ht="28" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B17" s="8">
         <v>46211</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>600</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9">
@@ -16258,12 +16258,12 @@
         <v>607</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="28" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B18" s="8">
         <v>46210</v>
@@ -16272,7 +16272,7 @@
         <v>34</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>598</v>
@@ -16281,7 +16281,7 @@
         <v>98</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H18" s="8">
         <v>46210</v>
@@ -16290,15 +16290,15 @@
         <v>1</v>
       </c>
       <c r="J18" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="K18" s="13" t="s">
         <v>157</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="28" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B19" s="8">
         <v>46210</v>
@@ -16307,7 +16307,7 @@
         <v>34</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>598</v>
@@ -16316,7 +16316,7 @@
         <v>98</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H19" s="8">
         <v>46210</v>
@@ -16325,15 +16325,15 @@
         <v>1</v>
       </c>
       <c r="J19" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="K19" s="13" t="s">
         <v>161</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="28" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B20" s="8">
         <v>46209</v>
@@ -16342,7 +16342,7 @@
         <v>34</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>598</v>
@@ -16351,7 +16351,7 @@
         <v>98</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H20" s="8">
         <v>46209</v>
@@ -16360,15 +16360,15 @@
         <v>1</v>
       </c>
       <c r="J20" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="K20" s="13" t="s">
         <v>166</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="28" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B21" s="8">
         <v>46209</v>
@@ -16377,7 +16377,7 @@
         <v>34</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>598</v>
@@ -16386,7 +16386,7 @@
         <v>98</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H21" s="8">
         <v>46209</v>
@@ -16395,15 +16395,15 @@
         <v>1</v>
       </c>
       <c r="J21" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="K21" s="13" t="s">
         <v>169</v>
-      </c>
-      <c r="K21" s="13" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="28" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B22" s="8">
         <v>46209</v>
@@ -16418,7 +16418,7 @@
         <v>608</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G22" s="9" t="s">
         <v>173</v>
@@ -16451,7 +16451,7 @@
         <v>600</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G23" s="9" t="s">
         <v>178</v>
@@ -16478,7 +16478,7 @@
         <v>34</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>598</v>
@@ -16513,7 +16513,7 @@
         <v>34</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>598</v>
@@ -16548,7 +16548,7 @@
         <v>34</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>598</v>
@@ -16589,7 +16589,7 @@
         <v>608</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>191</v>
@@ -16622,7 +16622,7 @@
         <v>608</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G28" s="9" t="s">
         <v>610</v>
@@ -16655,7 +16655,7 @@
         <v>608</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G29" s="9" t="s">
         <v>613</v>
@@ -16688,7 +16688,7 @@
         <v>600</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G30" s="9" t="s">
         <v>615</v>
@@ -16715,7 +16715,7 @@
         <v>34</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>598</v>
@@ -16750,7 +16750,7 @@
         <v>34</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>598</v>
@@ -16785,7 +16785,7 @@
         <v>34</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>598</v>
@@ -16820,7 +16820,7 @@
         <v>34</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>598</v>
@@ -16855,7 +16855,7 @@
         <v>34</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>598</v>
@@ -16890,7 +16890,7 @@
         <v>212</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>598</v>
@@ -16925,7 +16925,7 @@
         <v>34</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>598</v>
@@ -16960,7 +16960,7 @@
         <v>34</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E38" s="9" t="s">
         <v>598</v>
@@ -16995,7 +16995,7 @@
         <v>34</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>598</v>
@@ -17030,7 +17030,7 @@
         <v>34</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E40" s="9" t="s">
         <v>598</v>
@@ -17065,7 +17065,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>598</v>
@@ -17106,7 +17106,7 @@
         <v>608</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G42" s="9" t="s">
         <v>237</v>
@@ -17133,13 +17133,13 @@
         <v>34</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>608</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>616</v>
@@ -17166,13 +17166,13 @@
         <v>34</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E44" s="9" t="s">
         <v>600</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G44" s="9" t="s">
         <v>617</v>
@@ -17199,13 +17199,13 @@
         <v>34</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>600</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>618</v>
@@ -17238,7 +17238,7 @@
         <v>619</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G46" s="9" t="s">
         <v>241</v>
@@ -17267,7 +17267,7 @@
         <v>34</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>598</v>
@@ -17302,7 +17302,7 @@
         <v>34</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E48" s="9" t="s">
         <v>598</v>
@@ -17337,7 +17337,7 @@
         <v>34</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>598</v>
@@ -17372,7 +17372,7 @@
         <v>34</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E50" s="9" t="s">
         <v>598</v>
@@ -17413,7 +17413,7 @@
         <v>621</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G51" s="9" t="s">
         <v>261</v>
@@ -17446,7 +17446,7 @@
         <v>619</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G52" s="9" t="s">
         <v>266</v>
@@ -17475,7 +17475,7 @@
         <v>34</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>598</v>
@@ -17510,7 +17510,7 @@
         <v>34</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E54" s="9" t="s">
         <v>598</v>
@@ -17545,7 +17545,7 @@
         <v>34</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>598</v>
@@ -17580,7 +17580,7 @@
         <v>277</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E56" s="9" t="s">
         <v>598</v>
@@ -17615,7 +17615,7 @@
         <v>283</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>598</v>
@@ -17650,13 +17650,13 @@
         <v>288</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E58" s="9" t="s">
         <v>619</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G58" s="9" t="s">
         <v>289</v>
@@ -17682,7 +17682,7 @@
         <v>46202</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>240</v>
@@ -17691,7 +17691,7 @@
         <v>619</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G59" s="9" t="s">
         <v>293</v>
@@ -17755,13 +17755,13 @@
         <v>176</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>619</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G61" s="9" t="s">
         <v>299</v>
@@ -17796,7 +17796,7 @@
         <v>619</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G62" s="9" t="s">
         <v>304</v>
@@ -17825,7 +17825,7 @@
         <v>34</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>619</v>
@@ -17860,7 +17860,7 @@
         <v>34</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E64" s="9" t="s">
         <v>598</v>
@@ -17895,7 +17895,7 @@
         <v>34</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>619</v>
@@ -17930,7 +17930,7 @@
         <v>34</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E66" s="9" t="s">
         <v>619</v>
@@ -17965,7 +17965,7 @@
         <v>34</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>619</v>
@@ -18000,7 +18000,7 @@
         <v>34</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E68" s="9" t="s">
         <v>619</v>
@@ -18035,7 +18035,7 @@
         <v>34</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>619</v>
@@ -18076,7 +18076,7 @@
         <v>619</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G70" s="9" t="s">
         <v>329</v>
@@ -18146,7 +18146,7 @@
         <v>619</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G72" s="9" t="s">
         <v>626</v>
@@ -18175,13 +18175,13 @@
         <v>41</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>619</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G73" s="9" t="s">
         <v>628</v>
@@ -18216,7 +18216,7 @@
         <v>619</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G74" s="9" t="s">
         <v>339</v>
@@ -18251,7 +18251,7 @@
         <v>619</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G75" s="9" t="s">
         <v>346</v>
@@ -18286,7 +18286,7 @@
         <v>619</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G76" s="9" t="s">
         <v>632</v>
@@ -18321,7 +18321,7 @@
         <v>619</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G77" s="9" t="s">
         <v>635</v>
@@ -18356,7 +18356,7 @@
         <v>619</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G78" s="9" t="s">
         <v>637</v>
@@ -18391,7 +18391,7 @@
         <v>619</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G79" s="9" t="s">
         <v>638</v>
@@ -18426,7 +18426,7 @@
         <v>619</v>
       </c>
       <c r="F80" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G80" s="9" t="s">
         <v>639</v>
@@ -18461,7 +18461,7 @@
         <v>619</v>
       </c>
       <c r="F81" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G81" s="9" t="s">
         <v>641</v>
@@ -18496,7 +18496,7 @@
         <v>600</v>
       </c>
       <c r="F82" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G82" s="9" t="s">
         <v>642</v>
@@ -18529,7 +18529,7 @@
         <v>600</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G83" s="9" t="s">
         <v>643</v>
@@ -18597,7 +18597,7 @@
         <v>619</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G85" s="9" t="s">
         <v>644</v>
@@ -18632,7 +18632,7 @@
         <v>619</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G86" s="9" t="s">
         <v>646</v>
@@ -18667,7 +18667,7 @@
         <v>619</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G87" s="9" t="s">
         <v>353</v>
@@ -18702,7 +18702,7 @@
         <v>619</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G88" s="9" t="s">
         <v>356</v>
@@ -18737,7 +18737,7 @@
         <v>619</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G89" s="9" t="s">
         <v>360</v>
@@ -18772,7 +18772,7 @@
         <v>619</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G90" s="9" t="s">
         <v>363</v>
@@ -18807,7 +18807,7 @@
         <v>619</v>
       </c>
       <c r="F91" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G91" s="9" t="s">
         <v>366</v>
@@ -18842,7 +18842,7 @@
         <v>619</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G92" s="9" t="s">
         <v>370</v>
@@ -18877,7 +18877,7 @@
         <v>600</v>
       </c>
       <c r="F93" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G93" s="9" t="s">
         <v>374</v>
@@ -18910,7 +18910,7 @@
         <v>619</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G94" s="9" t="s">
         <v>377</v>
@@ -18945,7 +18945,7 @@
         <v>619</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G95" s="9" t="s">
         <v>382</v>
@@ -18980,7 +18980,7 @@
         <v>619</v>
       </c>
       <c r="F96" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G96" s="9" t="s">
         <v>385</v>
@@ -19015,7 +19015,7 @@
         <v>619</v>
       </c>
       <c r="F97" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G97" s="9" t="s">
         <v>388</v>
@@ -19050,7 +19050,7 @@
         <v>619</v>
       </c>
       <c r="F98" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G98" s="9" t="s">
         <v>392</v>
@@ -19079,13 +19079,13 @@
         <v>34</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>619</v>
       </c>
       <c r="F99" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G99" s="9" t="s">
         <v>658</v>
@@ -19120,7 +19120,7 @@
         <v>600</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G100" s="9" t="s">
         <v>661</v>
@@ -19153,7 +19153,7 @@
         <v>619</v>
       </c>
       <c r="F101" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G101" s="9" t="s">
         <v>396</v>
@@ -19188,7 +19188,7 @@
         <v>619</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G102" s="9" t="s">
         <v>400</v>
@@ -19223,7 +19223,7 @@
         <v>619</v>
       </c>
       <c r="F103" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G103" s="9" t="s">
         <v>403</v>
@@ -19258,7 +19258,7 @@
         <v>619</v>
       </c>
       <c r="F104" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G104" s="9" t="s">
         <v>407</v>
@@ -19293,7 +19293,7 @@
         <v>600</v>
       </c>
       <c r="F105" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G105" s="9" t="s">
         <v>667</v>
@@ -19326,7 +19326,7 @@
         <v>619</v>
       </c>
       <c r="F106" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G106" s="9" t="s">
         <v>411</v>
@@ -19361,7 +19361,7 @@
         <v>600</v>
       </c>
       <c r="F107" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G107" s="9" t="s">
         <v>415</v>
@@ -19394,7 +19394,7 @@
         <v>619</v>
       </c>
       <c r="F108" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G108" s="9" t="s">
         <v>420</v>
@@ -19429,7 +19429,7 @@
         <v>619</v>
       </c>
       <c r="F109" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G109" s="9" t="s">
         <v>671</v>
@@ -19464,7 +19464,7 @@
         <v>619</v>
       </c>
       <c r="F110" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G110" s="9" t="s">
         <v>674</v>
@@ -19499,7 +19499,7 @@
         <v>619</v>
       </c>
       <c r="F111" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G111" s="9" t="s">
         <v>423</v>
@@ -19534,7 +19534,7 @@
         <v>619</v>
       </c>
       <c r="F112" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G112" s="9" t="s">
         <v>426</v>
@@ -19569,7 +19569,7 @@
         <v>619</v>
       </c>
       <c r="F113" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G113" s="9" t="s">
         <v>429</v>
@@ -19604,7 +19604,7 @@
         <v>619</v>
       </c>
       <c r="F114" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G114" s="9" t="s">
         <v>432</v>
@@ -19639,7 +19639,7 @@
         <v>619</v>
       </c>
       <c r="F115" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G115" s="9" t="s">
         <v>436</v>
@@ -19674,7 +19674,7 @@
         <v>619</v>
       </c>
       <c r="F116" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G116" s="9" t="s">
         <v>439</v>
@@ -19703,7 +19703,7 @@
         <v>32</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>619</v>
@@ -19738,7 +19738,7 @@
         <v>32</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E118" s="9" t="s">
         <v>599</v>
@@ -19808,7 +19808,7 @@
         <v>34</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E120" s="9" t="s">
         <v>619</v>
@@ -19843,7 +19843,7 @@
         <v>32</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>619</v>
@@ -19878,7 +19878,7 @@
         <v>32</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E122" s="9" t="s">
         <v>619</v>
@@ -19913,7 +19913,7 @@
         <v>32</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>619</v>
@@ -19948,7 +19948,7 @@
         <v>464</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E124" s="9" t="s">
         <v>619</v>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-12 | Build 465c30d19a73 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-12 | Build 0f452755805e | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-12 | Build 0f452755805e | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-12 | Build 5815eb1a3219 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -9068,7 +9068,7 @@
         <v>121</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>122</v>
+        <v>31</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>336</v>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-12 | Build ee02219e0265 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-13 | Build 7458c62de55c | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-13 | Build 7458c62de55c | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-13 | Build bfe7a96f2c11 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -1271,7 +1271,7 @@
     <t>https://rb.ru/news/yandeks-odobril-dividendy-po-itogam-2025-go-vyplaty-sostavyat-110-za-akciyu-pochti-na-40-vyshe-chem-v-proshlom-godu/</t>
   </si>
   <si>
-    <t>Яндекс утвердил дивиденды по итогам 2025 года — выплаты составят 110 ₽ за акцию - RB.RU</t>
+    <t>Яндекс утвердил дивиденды по итогам 2025 года — выплаты составят 110 ₽ за акцию - rb.ru</t>
   </si>
   <si>
     <t>DL-ac8ca50a646028ad</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-13 | Build bfe7a96f2c11 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-13 | Build 8655a9cf3192 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-13 | Build 2c9aa3f4ce3b | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-13 | Build 7eafc4680bda | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4968" uniqueCount="705">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4978" uniqueCount="706">
   <si>
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-13 | Build 7eafc4680bda | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-13 | Build 79146d51dc3c | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -1280,7 +1280,7 @@
     <t>https://rb.ru/news/yandeks-odobril-dividendy-po-itogam-2025-go-vyplaty-sostavyat-110-za-akciyu-pochti-na-40-vyshe-chem-v-proshlom-godu/</t>
   </si>
   <si>
-    <t>Яндекс утвердил дивиденды по итогам 2025 года — выплаты составят 110 ₽ за акцию - rb.ru</t>
+    <t>Яндекс утвердил дивиденды по итогам 2025 года — выплаты составят 110 ₽ за акцию - RB.ru</t>
   </si>
   <si>
     <t>DL-ac8ca50a646028ad</t>
@@ -1307,7 +1307,7 @@
     <t>https://rb.ru/news/vk-prodal-25-akcij-tochka-banka-sdelku-ocenili-v-212-mlrd-vdvoe-vyshe-iznachalnoj-stoimosti-bumag/</t>
   </si>
   <si>
-    <t>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - rb.ru</t>
+    <t>VK продал 25% акций Точка Банка: сделку оценили в 21,2 млрд ₽ — вдвое выше изначальной стоимости бумаг - RB.ru</t>
   </si>
   <si>
     <t>DL-4774de17c61c14e4</t>
@@ -2112,6 +2112,9 @@
   <si>
     <t>https://www.cnews.ru/news/top/2026-04-16_vk_prodal_svoyu_dolyu_v_virtualnom
 https://news.google.com/rss/articles/CBMigAFBVV95cUxOeU1NOHJNay1uUm9TdlpGcWh4YkNXN3J0clFCT2JrM0t5T3hwTmtTRlJXUWpyeVBYbnltZlB0dnpqLWxhTUxQNW9wQU1LeG5sTjVzT1NNQlFlY0Jpb1REMGhyWG1wSUM0STZXbFFaNndzQ1A1MlVvMFN3RmlmOW4tXw?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE9xb1NxV3dEMTloamc3YjNsM2FmenRQM2JRd2dmcjFJV2JlZHFmWTZuMW9naHpvU2o4SEVvSG9oZXlub25zX21jSzRZZklUbjktRmc?oc=5</t>
   </si>
   <si>
     <t>https://www.finam.ru/publications/item/dvoynoe-razmeshchenie-obligatsiy-vk-chego-zhdat-chastnym-investoram-20260410-1829/
@@ -2450,8 +2453,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:K145" totalsRowShown="0">
-  <autoFilter ref="A6:K145"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:K146" totalsRowShown="0">
+  <autoFilter ref="A6:K146"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Deal ID"/>
     <tableColumn id="2" name="Date"/>
@@ -11374,7 +11377,7 @@
         <v>9</v>
       </c>
       <c r="J89" s="9" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="K89" s="10">
         <v>21200000000</v>
@@ -11434,7 +11437,7 @@
         <v>130</v>
       </c>
       <c r="AQ89" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR89" s="9" t="s">
         <v>418</v>
@@ -15900,7 +15903,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R145"/>
+  <dimension ref="A1:R146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -15963,7 +15966,7 @@
     </row>
     <row r="4" spans="1:18">
       <c r="M4" s="3" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -16006,19 +16009,19 @@
         <v>30</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>23</v>
@@ -16059,7 +16062,7 @@
         <v>32</v>
       </c>
       <c r="M7" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -16110,7 +16113,7 @@
         <v>110</v>
       </c>
       <c r="M8" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -16163,7 +16166,7 @@
         <v>117</v>
       </c>
       <c r="M9" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -16216,7 +16219,7 @@
         <v>120</v>
       </c>
       <c r="M10" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -16269,7 +16272,7 @@
         <v>38</v>
       </c>
       <c r="M11" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -16320,7 +16323,7 @@
         <v>133</v>
       </c>
       <c r="M12" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -16371,7 +16374,7 @@
         <v>137</v>
       </c>
       <c r="M13" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -16422,7 +16425,7 @@
         <v>144</v>
       </c>
       <c r="M14" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -16506,7 +16509,7 @@
         <v>152</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -19840,51 +19843,49 @@
     </row>
     <row r="113" spans="1:11" ht="28" customHeight="1">
       <c r="A113" s="9" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="B113" s="8">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>245</v>
+        <v>443</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>627</v>
+        <v>608</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H113" s="8">
-        <v>46122</v>
-      </c>
+        <v>684</v>
+      </c>
+      <c r="H113" s="9"/>
       <c r="I113" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J113" s="13" t="s">
         <v>684</v>
       </c>
       <c r="K113" s="13" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="28" customHeight="1">
       <c r="A114" s="9" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B114" s="8">
         <v>46122</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>352</v>
+        <v>427</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>627</v>
@@ -19893,7 +19894,7 @@
         <v>130</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="H114" s="8">
         <v>46122</v>
@@ -19905,21 +19906,21 @@
         <v>685</v>
       </c>
       <c r="K114" s="13" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="28" customHeight="1">
       <c r="A115" s="9" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B115" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="C115" s="9" t="s">
         <v>352</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>414</v>
+        <v>195</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>627</v>
@@ -19928,10 +19929,10 @@
         <v>130</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="H115" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="I115" s="9">
         <v>2</v>
@@ -19940,12 +19941,12 @@
         <v>686</v>
       </c>
       <c r="K115" s="13" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="28" customHeight="1">
       <c r="A116" s="9" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B116" s="8">
         <v>46115</v>
@@ -19954,7 +19955,7 @@
         <v>352</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>270</v>
+        <v>414</v>
       </c>
       <c r="E116" s="9" t="s">
         <v>627</v>
@@ -19963,7 +19964,7 @@
         <v>130</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="H116" s="8">
         <v>46115</v>
@@ -19975,21 +19976,21 @@
         <v>687</v>
       </c>
       <c r="K116" s="13" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="28" customHeight="1">
       <c r="A117" s="9" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B117" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="C117" s="9" t="s">
-        <v>427</v>
+        <v>352</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>443</v>
+        <v>270</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>627</v>
@@ -19998,24 +19999,24 @@
         <v>130</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="H117" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="I117" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J117" s="13" t="s">
-        <v>444</v>
+        <v>688</v>
       </c>
       <c r="K117" s="13" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="28" customHeight="1">
       <c r="A118" s="9" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B118" s="8">
         <v>46111</v>
@@ -20024,7 +20025,7 @@
         <v>427</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>245</v>
+        <v>443</v>
       </c>
       <c r="E118" s="9" t="s">
         <v>627</v>
@@ -20033,7 +20034,7 @@
         <v>130</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="H118" s="8">
         <v>46111</v>
@@ -20042,53 +20043,53 @@
         <v>1</v>
       </c>
       <c r="J118" s="13" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="K118" s="13" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="28" customHeight="1">
       <c r="A119" s="9" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B119" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>37</v>
+        <v>427</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>123</v>
+        <v>245</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>627</v>
       </c>
       <c r="F119" s="9" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="H119" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="I119" s="9">
         <v>1</v>
       </c>
       <c r="J119" s="13" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="K119" s="13" t="s">
-        <v>52</v>
+        <v>448</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="28" customHeight="1">
       <c r="A120" s="9" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B120" s="8">
-        <v>45923</v>
+        <v>46080</v>
       </c>
       <c r="C120" s="9" t="s">
         <v>37</v>
@@ -20097,39 +20098,39 @@
         <v>123</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="H120" s="8">
-        <v>45923</v>
+        <v>46080</v>
       </c>
       <c r="I120" s="9">
         <v>1</v>
       </c>
       <c r="J120" s="13" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="K120" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="28" customHeight="1">
       <c r="A121" s="9" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B121" s="8">
-        <v>45729</v>
+        <v>45923</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>341</v>
+        <v>123</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>607</v>
@@ -20138,33 +20139,33 @@
         <v>101</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="H121" s="8">
-        <v>45729</v>
+        <v>45923</v>
       </c>
       <c r="I121" s="9">
         <v>1</v>
       </c>
       <c r="J121" s="13" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="K121" s="13" t="s">
-        <v>456</v>
+        <v>53</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="28" customHeight="1">
       <c r="A122" s="9" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B122" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>123</v>
+        <v>341</v>
       </c>
       <c r="E122" s="9" t="s">
         <v>607</v>
@@ -20173,30 +20174,30 @@
         <v>101</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="H122" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="I122" s="9">
         <v>1</v>
       </c>
       <c r="J122" s="13" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="K122" s="13" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="28" customHeight="1">
       <c r="A123" s="9" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B123" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D123" s="9" t="s">
         <v>123</v>
@@ -20208,27 +20209,27 @@
         <v>101</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="H123" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="I123" s="9">
         <v>1</v>
       </c>
       <c r="J123" s="13" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="K123" s="13" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="28" customHeight="1">
       <c r="A124" s="9" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B124" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="C124" s="9" t="s">
         <v>37</v>
@@ -20237,33 +20238,33 @@
         <v>123</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>627</v>
+        <v>607</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="H124" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="I124" s="9">
         <v>1</v>
       </c>
       <c r="J124" s="13" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="K124" s="13" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="28" customHeight="1">
       <c r="A125" s="9" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="B125" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="C125" s="9" t="s">
         <v>37</v>
@@ -20272,36 +20273,36 @@
         <v>123</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>607</v>
+        <v>627</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="H125" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="I125" s="9">
         <v>1</v>
       </c>
       <c r="J125" s="13" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="K125" s="13" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="28" customHeight="1">
       <c r="A126" s="9" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B126" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>472</v>
+        <v>37</v>
       </c>
       <c r="D126" s="9" t="s">
         <v>123</v>
@@ -20313,54 +20314,54 @@
         <v>101</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="H126" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="I126" s="9">
         <v>1</v>
       </c>
       <c r="J126" s="13" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="K126" s="13" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="28" customHeight="1">
       <c r="A127" s="9" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B127" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>486</v>
+        <v>123</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>688</v>
+        <v>607</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="H127" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="I127" s="9">
         <v>1</v>
       </c>
       <c r="J127" s="13" t="s">
-        <v>487</v>
+        <v>474</v>
       </c>
       <c r="K127" s="13" t="s">
-        <v>488</v>
+        <v>475</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="28" customHeight="1">
@@ -20374,7 +20375,7 @@
         <v>477</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="E128" s="9" t="s">
         <v>689</v>
@@ -20383,16 +20384,16 @@
         <v>101</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>580</v>
+        <v>487</v>
       </c>
       <c r="H128" s="8">
-        <v>45008</v>
+        <v>45190</v>
       </c>
       <c r="I128" s="9">
         <v>1</v>
       </c>
       <c r="J128" s="13" t="s">
-        <v>580</v>
+        <v>487</v>
       </c>
       <c r="K128" s="13" t="s">
         <v>488</v>
@@ -20400,37 +20401,37 @@
     </row>
     <row r="129" spans="1:11" ht="28" customHeight="1">
       <c r="A129" s="9" t="s">
-        <v>489</v>
+        <v>476</v>
       </c>
       <c r="B129" s="8">
-        <v>44707</v>
+        <v>45190</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>490</v>
+        <v>477</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>498</v>
+        <v>580</v>
       </c>
       <c r="H129" s="8">
-        <v>44707</v>
+        <v>45008</v>
       </c>
       <c r="I129" s="9">
         <v>1</v>
       </c>
       <c r="J129" s="13" t="s">
-        <v>498</v>
+        <v>580</v>
       </c>
       <c r="K129" s="13" t="s">
-        <v>499</v>
+        <v>488</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="28" customHeight="1">
@@ -20444,7 +20445,7 @@
         <v>490</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E130" s="9" t="s">
         <v>689</v>
@@ -20453,16 +20454,16 @@
         <v>101</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>581</v>
+        <v>498</v>
       </c>
       <c r="H130" s="8">
-        <v>44644</v>
+        <v>44707</v>
       </c>
       <c r="I130" s="9">
         <v>1</v>
       </c>
       <c r="J130" s="13" t="s">
-        <v>581</v>
+        <v>498</v>
       </c>
       <c r="K130" s="13" t="s">
         <v>499</v>
@@ -20470,37 +20471,37 @@
     </row>
     <row r="131" spans="1:11" ht="28" customHeight="1">
       <c r="A131" s="9" t="s">
-        <v>500</v>
+        <v>489</v>
       </c>
       <c r="B131" s="8">
-        <v>44640</v>
+        <v>44707</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>501</v>
+        <v>490</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>508</v>
+        <v>581</v>
       </c>
       <c r="H131" s="8">
-        <v>44734</v>
+        <v>44644</v>
       </c>
       <c r="I131" s="9">
         <v>1</v>
       </c>
       <c r="J131" s="13" t="s">
-        <v>508</v>
+        <v>581</v>
       </c>
       <c r="K131" s="13" t="s">
-        <v>509</v>
+        <v>499</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="28" customHeight="1">
@@ -20514,7 +20515,7 @@
         <v>501</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E132" s="9" t="s">
         <v>689</v>
@@ -20523,16 +20524,16 @@
         <v>101</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>582</v>
+        <v>508</v>
       </c>
       <c r="H132" s="8">
-        <v>44643</v>
+        <v>44734</v>
       </c>
       <c r="I132" s="9">
         <v>1</v>
       </c>
       <c r="J132" s="13" t="s">
-        <v>582</v>
+        <v>508</v>
       </c>
       <c r="K132" s="13" t="s">
         <v>509</v>
@@ -20540,72 +20541,72 @@
     </row>
     <row r="133" spans="1:11" ht="28" customHeight="1">
       <c r="A133" s="9" t="s">
-        <v>510</v>
+        <v>500</v>
       </c>
       <c r="B133" s="8">
-        <v>44592</v>
+        <v>44640</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>511</v>
+        <v>501</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>517</v>
+        <v>582</v>
       </c>
       <c r="H133" s="8">
-        <v>44608</v>
+        <v>44643</v>
       </c>
       <c r="I133" s="9">
         <v>1</v>
       </c>
       <c r="J133" s="13" t="s">
-        <v>517</v>
+        <v>582</v>
       </c>
       <c r="K133" s="13" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="28" customHeight="1">
       <c r="A134" s="9" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="B134" s="8">
-        <v>44579</v>
+        <v>44592</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>526</v>
+        <v>516</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="H134" s="8">
-        <v>44579</v>
+        <v>44608</v>
       </c>
       <c r="I134" s="9">
         <v>1</v>
       </c>
       <c r="J134" s="13" t="s">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="K134" s="13" t="s">
-        <v>528</v>
+        <v>518</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="28" customHeight="1">
@@ -20619,7 +20620,7 @@
         <v>520</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>689</v>
@@ -20628,16 +20629,16 @@
         <v>101</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>583</v>
+        <v>527</v>
       </c>
       <c r="H135" s="8">
-        <v>44250</v>
+        <v>44579</v>
       </c>
       <c r="I135" s="9">
         <v>1</v>
       </c>
       <c r="J135" s="13" t="s">
-        <v>583</v>
+        <v>527</v>
       </c>
       <c r="K135" s="13" t="s">
         <v>528</v>
@@ -20645,37 +20646,37 @@
     </row>
     <row r="136" spans="1:11" ht="28" customHeight="1">
       <c r="A136" s="9" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="B136" s="8">
-        <v>44166</v>
+        <v>44579</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>530</v>
+        <v>520</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>535</v>
+        <v>524</v>
       </c>
       <c r="E136" s="9" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="H136" s="8">
-        <v>44166</v>
+        <v>44250</v>
       </c>
       <c r="I136" s="9">
         <v>1</v>
       </c>
       <c r="J136" s="13" t="s">
-        <v>536</v>
+        <v>583</v>
       </c>
       <c r="K136" s="13" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="28" customHeight="1">
@@ -20689,7 +20690,7 @@
         <v>530</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>689</v>
@@ -20698,16 +20699,16 @@
         <v>101</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>584</v>
+        <v>536</v>
       </c>
       <c r="H137" s="8">
-        <v>43902</v>
+        <v>44166</v>
       </c>
       <c r="I137" s="9">
         <v>1</v>
       </c>
       <c r="J137" s="13" t="s">
-        <v>584</v>
+        <v>536</v>
       </c>
       <c r="K137" s="13" t="s">
         <v>537</v>
@@ -20715,37 +20716,37 @@
     </row>
     <row r="138" spans="1:11" ht="28" customHeight="1">
       <c r="A138" s="9" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="B138" s="8">
-        <v>44131</v>
+        <v>44166</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>544</v>
+        <v>533</v>
       </c>
       <c r="E138" s="9" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>545</v>
+        <v>584</v>
       </c>
       <c r="H138" s="8">
-        <v>44131</v>
+        <v>43902</v>
       </c>
       <c r="I138" s="9">
         <v>1</v>
       </c>
       <c r="J138" s="13" t="s">
-        <v>545</v>
+        <v>584</v>
       </c>
       <c r="K138" s="13" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="28" customHeight="1">
@@ -20759,7 +20760,7 @@
         <v>539</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>689</v>
@@ -20768,16 +20769,16 @@
         <v>101</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>585</v>
+        <v>545</v>
       </c>
       <c r="H139" s="8">
-        <v>43966</v>
+        <v>44131</v>
       </c>
       <c r="I139" s="9">
         <v>1</v>
       </c>
       <c r="J139" s="13" t="s">
-        <v>585</v>
+        <v>545</v>
       </c>
       <c r="K139" s="13" t="s">
         <v>546</v>
@@ -20785,37 +20786,37 @@
     </row>
     <row r="140" spans="1:11" ht="28" customHeight="1">
       <c r="A140" s="9" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="B140" s="8">
-        <v>43626</v>
+        <v>44131</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="E140" s="9" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G140" s="9" t="s">
-        <v>552</v>
+        <v>585</v>
       </c>
       <c r="H140" s="8">
-        <v>43626</v>
+        <v>43966</v>
       </c>
       <c r="I140" s="9">
         <v>1</v>
       </c>
       <c r="J140" s="13" t="s">
-        <v>552</v>
+        <v>585</v>
       </c>
       <c r="K140" s="13" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="28" customHeight="1">
@@ -20829,7 +20830,7 @@
         <v>548</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>689</v>
@@ -20838,16 +20839,16 @@
         <v>101</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>586</v>
+        <v>552</v>
       </c>
       <c r="H141" s="8">
-        <v>43518</v>
+        <v>43626</v>
       </c>
       <c r="I141" s="9">
         <v>1</v>
       </c>
       <c r="J141" s="13" t="s">
-        <v>586</v>
+        <v>552</v>
       </c>
       <c r="K141" s="13" t="s">
         <v>553</v>
@@ -20855,37 +20856,37 @@
     </row>
     <row r="142" spans="1:11" ht="28" customHeight="1">
       <c r="A142" s="9" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="B142" s="8">
-        <v>43401</v>
+        <v>43626</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G142" s="9" t="s">
-        <v>561</v>
+        <v>586</v>
       </c>
       <c r="H142" s="8">
-        <v>43401</v>
+        <v>43518</v>
       </c>
       <c r="I142" s="9">
         <v>1</v>
       </c>
       <c r="J142" s="13" t="s">
-        <v>561</v>
+        <v>586</v>
       </c>
       <c r="K142" s="13" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="28" customHeight="1">
@@ -20899,7 +20900,7 @@
         <v>555</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>689</v>
@@ -20908,16 +20909,16 @@
         <v>101</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>587</v>
+        <v>561</v>
       </c>
       <c r="H143" s="8">
-        <v>43215</v>
+        <v>43401</v>
       </c>
       <c r="I143" s="9">
         <v>1</v>
       </c>
       <c r="J143" s="13" t="s">
-        <v>587</v>
+        <v>561</v>
       </c>
       <c r="K143" s="13" t="s">
         <v>562</v>
@@ -20925,37 +20926,37 @@
     </row>
     <row r="144" spans="1:11" ht="28" customHeight="1">
       <c r="A144" s="9" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
       <c r="B144" s="8">
-        <v>42534</v>
+        <v>43401</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>526</v>
+        <v>558</v>
       </c>
       <c r="E144" s="9" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G144" s="9" t="s">
-        <v>568</v>
+        <v>587</v>
       </c>
       <c r="H144" s="8">
-        <v>42534</v>
+        <v>43215</v>
       </c>
       <c r="I144" s="9">
         <v>1</v>
       </c>
       <c r="J144" s="13" t="s">
-        <v>568</v>
+        <v>587</v>
       </c>
       <c r="K144" s="13" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="28" customHeight="1">
@@ -20969,7 +20970,7 @@
         <v>564</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>566</v>
+        <v>526</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>689</v>
@@ -20978,18 +20979,53 @@
         <v>101</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>588</v>
+        <v>568</v>
       </c>
       <c r="H145" s="8">
-        <v>42412</v>
+        <v>42534</v>
       </c>
       <c r="I145" s="9">
         <v>1</v>
       </c>
       <c r="J145" s="13" t="s">
+        <v>568</v>
+      </c>
+      <c r="K145" s="13" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" ht="28" customHeight="1">
+      <c r="A146" s="9" t="s">
+        <v>563</v>
+      </c>
+      <c r="B146" s="8">
+        <v>42534</v>
+      </c>
+      <c r="C146" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="D146" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="E146" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="F146" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G146" s="9" t="s">
         <v>588</v>
       </c>
-      <c r="K145" s="13" t="s">
+      <c r="H146" s="8">
+        <v>42412</v>
+      </c>
+      <c r="I146" s="9">
+        <v>1</v>
+      </c>
+      <c r="J146" s="13" t="s">
+        <v>588</v>
+      </c>
+      <c r="K146" s="13" t="s">
         <v>569</v>
       </c>
     </row>
@@ -21218,9 +21254,9 @@
     <hyperlink ref="J113" r:id="rId215"/>
     <hyperlink ref="G114" r:id="rId216"/>
     <hyperlink ref="J114" r:id="rId217"/>
-    <hyperlink ref="D115" r:id="rId218"/>
-    <hyperlink ref="G115" r:id="rId219"/>
-    <hyperlink ref="J115" r:id="rId220"/>
+    <hyperlink ref="G115" r:id="rId218"/>
+    <hyperlink ref="J115" r:id="rId219"/>
+    <hyperlink ref="D116" r:id="rId220"/>
     <hyperlink ref="G116" r:id="rId221"/>
     <hyperlink ref="J116" r:id="rId222"/>
     <hyperlink ref="G117" r:id="rId223"/>
@@ -21281,10 +21317,12 @@
     <hyperlink ref="J144" r:id="rId278"/>
     <hyperlink ref="G145" r:id="rId279"/>
     <hyperlink ref="J145" r:id="rId280"/>
+    <hyperlink ref="G146" r:id="rId281"/>
+    <hyperlink ref="J146" r:id="rId282"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId281"/>
+    <tablePart r:id="rId283"/>
   </tableParts>
 </worksheet>
 </file>
--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-13 | Build 79146d51dc3c | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-14 | Build 8224f07c5009 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -2043,6 +2043,7 @@
   </si>
   <si>
     <t>https://bcs-express.ru/novosti-i-analitika/ozon-bank-iskliuchen-iz-perechnia-bankov-s-aktsiiami-kotorykh-zapreshcheny-sdelki
+https://news.google.com/rss/articles/CBMi2AFBVV95cUxONTJqS2ZYODlVb2tia0wzNzZ5eGRfMlpiNk5yeno5YUJScl9VM01kMklaS0d5YXNwVFNfS1Jib2Q1QnpKTkFySVR4NEhIejRjMzRaOW1ZcjJQSWRyLVlqSmxycExQQ1BGZEtxWmV0UHpYdC1uZTUycHRLSm41MFBiTjVJVUFhWW9lRU9CbThVRGRWS1p4MkxqS3NFZFVmeVF2UmdMaHBFX0p5clZFRGJyNVMyVHVKRldCSlRYMUFMdDR6aEhpTlJMOElyeW1leVVobW5WZFlQdTg?oc=5
 https://news.google.com/rss/articles/CBMiwgFBVV95cUxORlpPNHotYkNzQVpwd2ptLTRIVmJmelQwVHY5Vjc2Rmd1YzFnMW52R3h3aXlFYkpzc0NfY0NPdWk3RnhUSXhudGhZUWxXeE90WlNpVmRkYlhxSlNHLXFkZ1pLMllFY3VBQUx6bDJUcG13VEVINVlKOTFMUkRkUUx0bllTQ2NQdzBaMENTM3FrN2dMNVFjQ2NKRTVUNG92QWlpcEdtWVFuMWx1dnJRTTFWS1paVllydW9oeUU0NjNUVjhCUQ?oc=5</t>
   </si>
   <si>
@@ -19383,7 +19384,7 @@
         <v>46139</v>
       </c>
       <c r="I99" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J99" s="13" t="s">
         <v>664</v>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-14 | Build 8224f07c5009 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-14 | Build 46711059d923 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-14 | Build 46711059d923 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-14 | Build 60432dd64893 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4978" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4988" uniqueCount="708">
   <si>
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-14 | Build 60432dd64893 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-14 | Build c6dbc7d2ac7b | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -1080,6 +1080,9 @@
   </si>
   <si>
     <t>Sber</t>
+  </si>
+  <si>
+    <t>АФК «Система</t>
   </si>
   <si>
     <t>https://bcs-express.ru/novosti-i-analitika/gref-oproverg-dogovorennost-sbera-o-pokupke-doli-v-ozone</t>
@@ -1994,6 +1997,9 @@
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMihgFBVV95cUxPa1Utd0tlY3RsT1JNSUZEcGdEdG84bFBJYlc0eDVEand3UnppVTduOUZPMUo2UHJ6SmxSSGgwekt6cDFyS3ByZDRxR1RrQjNJWk5VUlB4U2UyM0pSa3FiNnRscllQT19fZ2pEb0xQTU4xdXNXTi1PbWxNTF9LRTg2RTh3VHoyZw?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxPMVA0ajM0UVNNcXViUVFDc1Y3MXEwcUN2dzBfMGFsYUNOWkVCYUFaeUExMlA3M1BtVEtVNUFiSy15ZWszTjBVRG8xd1o2WUdBeVhtWlFVV0VBZkdUWHc5dlJBVU5VNzhzYldVTDRrVDZxVjliS1hPalB1eUFuTkZzdEtfYldoSS1rT29faUd3cENUUUl1S180OXNMOTBnaDd4?oc=5</t>
   </si>
   <si>
     <t>https://bcs-express.ru/novosti-i-analitika/t-tekhnologii-zakryli-sdelku-po-pokupke-avto-ru-u-iandeksa</t>
@@ -2454,8 +2460,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:K146" totalsRowShown="0">
-  <autoFilter ref="A6:K146"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:K147" totalsRowShown="0">
+  <autoFilter ref="A6:K147"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Deal ID"/>
     <tableColumn id="2" name="Date"/>
@@ -9463,7 +9469,7 @@
         <v>353</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>44</v>
+        <v>354</v>
       </c>
       <c r="I69" s="9" t="s">
         <v>113</v>
@@ -9523,21 +9529,21 @@
         <v>130</v>
       </c>
       <c r="AQ69" s="9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR69" s="9" t="s">
         <v>270</v>
       </c>
       <c r="AS69" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AT69" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="70" spans="1:46">
       <c r="A70" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B70" s="8">
         <v>46175</v>
@@ -9627,7 +9633,7 @@
         <v>341</v>
       </c>
       <c r="AS70" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AT70" s="9" t="s">
         <v>51</v>
@@ -9635,7 +9641,7 @@
     </row>
     <row r="71" spans="1:46">
       <c r="A71" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B71" s="8">
         <v>46170</v>
@@ -9647,10 +9653,10 @@
         <v>126</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G71" s="9" t="s">
         <v>46</v>
@@ -9722,15 +9728,15 @@
         <v>245</v>
       </c>
       <c r="AS71" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AT71" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="72" spans="1:46">
       <c r="A72" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B72" s="8">
         <v>46167</v>
@@ -9817,15 +9823,15 @@
         <v>245</v>
       </c>
       <c r="AS72" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AT72" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="73" spans="1:46">
       <c r="A73" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B73" s="8">
         <v>46162</v>
@@ -9864,7 +9870,7 @@
         <v>44</v>
       </c>
       <c r="Q73" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R73" s="9" t="s">
         <v>33</v>
@@ -9912,15 +9918,15 @@
         <v>270</v>
       </c>
       <c r="AS73" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AT73" s="9" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="74" spans="1:46">
       <c r="A74" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B74" s="8">
         <v>46157</v>
@@ -9959,7 +9965,7 @@
         <v>44</v>
       </c>
       <c r="Q74" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R74" s="9" t="s">
         <v>33</v>
@@ -10007,15 +10013,15 @@
         <v>245</v>
       </c>
       <c r="AS74" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AT74" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="75" spans="1:46">
       <c r="A75" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B75" s="8">
         <v>46157</v>
@@ -10102,15 +10108,15 @@
         <v>346</v>
       </c>
       <c r="AS75" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AT75" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="76" spans="1:46">
       <c r="A76" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B76" s="8">
         <v>46150</v>
@@ -10125,7 +10131,7 @@
         <v>127</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G76" s="9" t="s">
         <v>33</v>
@@ -10200,15 +10206,15 @@
         <v>346</v>
       </c>
       <c r="AS76" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AT76" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="77" spans="1:46">
       <c r="A77" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B77" s="8">
         <v>46149</v>
@@ -10292,18 +10298,18 @@
         <v>1</v>
       </c>
       <c r="AR77" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AS77" s="9" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AT77" s="9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="78" spans="1:46">
       <c r="A78" s="9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B78" s="8">
         <v>46147</v>
@@ -10345,7 +10351,7 @@
         <v>44</v>
       </c>
       <c r="Q78" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R78" s="9" t="s">
         <v>33</v>
@@ -10393,15 +10399,15 @@
         <v>270</v>
       </c>
       <c r="AS78" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AT78" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="79" spans="1:46">
       <c r="A79" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B79" s="8">
         <v>46146</v>
@@ -10425,7 +10431,7 @@
         <v>33</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J79" s="9" t="s">
         <v>44</v>
@@ -10440,7 +10446,7 @@
         <v>44</v>
       </c>
       <c r="Q79" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R79" s="9" t="s">
         <v>33</v>
@@ -10485,18 +10491,18 @@
         <v>1</v>
       </c>
       <c r="AR79" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AS79" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AT79" s="9" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="80" spans="1:46">
       <c r="A80" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B80" s="8">
         <v>46139</v>
@@ -10583,15 +10589,15 @@
         <v>182</v>
       </c>
       <c r="AS80" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AT80" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="81" spans="1:46">
       <c r="A81" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B81" s="8">
         <v>46139</v>
@@ -10678,15 +10684,15 @@
         <v>270</v>
       </c>
       <c r="AS81" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AT81" s="9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="82" spans="1:46">
       <c r="A82" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B82" s="8">
         <v>46139</v>
@@ -10770,18 +10776,18 @@
         <v>3</v>
       </c>
       <c r="AR82" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AS82" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AT82" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="83" spans="1:46">
       <c r="A83" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B83" s="8">
         <v>46139</v>
@@ -10865,18 +10871,18 @@
         <v>1</v>
       </c>
       <c r="AR83" s="9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AS83" s="9" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AT83" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="84" spans="1:46">
       <c r="A84" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B84" s="8">
         <v>46139</v>
@@ -10960,18 +10966,18 @@
         <v>1</v>
       </c>
       <c r="AR84" s="9" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AS84" s="9" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AT84" s="9" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="85" spans="1:46">
       <c r="A85" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B85" s="8">
         <v>46132</v>
@@ -11058,15 +11064,15 @@
         <v>195</v>
       </c>
       <c r="AS85" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AT85" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="86" spans="1:46">
       <c r="A86" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B86" s="8">
         <v>46132</v>
@@ -11105,7 +11111,7 @@
         <v>44</v>
       </c>
       <c r="Q86" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R86" s="9" t="s">
         <v>33</v>
@@ -11150,18 +11156,18 @@
         <v>2</v>
       </c>
       <c r="AR86" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AS86" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AT86" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="87" spans="1:46">
       <c r="A87" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B87" s="8">
         <v>46132</v>
@@ -11200,7 +11206,7 @@
         <v>44</v>
       </c>
       <c r="Q87" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R87" s="9" t="s">
         <v>33</v>
@@ -11245,18 +11251,18 @@
         <v>1</v>
       </c>
       <c r="AR87" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS87" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AT87" s="9" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="88" spans="1:46">
       <c r="A88" s="9" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B88" s="8">
         <v>46132</v>
@@ -11340,18 +11346,18 @@
         <v>1</v>
       </c>
       <c r="AR88" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AS88" s="9" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AT88" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="89" spans="1:46">
       <c r="A89" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B89" s="8">
         <v>46128</v>
@@ -11366,13 +11372,13 @@
         <v>127</v>
       </c>
       <c r="F89" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G89" s="9" t="s">
         <v>44</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I89" s="9" t="s">
         <v>9</v>
@@ -11441,18 +11447,18 @@
         <v>4</v>
       </c>
       <c r="AR89" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AS89" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AT89" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="90" spans="1:46">
       <c r="A90" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B90" s="8">
         <v>46122</v>
@@ -11467,7 +11473,7 @@
         <v>127</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G90" s="9" t="s">
         <v>33</v>
@@ -11539,15 +11545,15 @@
         <v>245</v>
       </c>
       <c r="AS90" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AT90" s="9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="91" spans="1:46">
       <c r="A91" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B91" s="8">
         <v>46122</v>
@@ -11586,7 +11592,7 @@
         <v>44</v>
       </c>
       <c r="Q91" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="R91" s="9" t="s">
         <v>33</v>
@@ -11634,15 +11640,15 @@
         <v>195</v>
       </c>
       <c r="AS91" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AT91" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="92" spans="1:46">
       <c r="A92" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B92" s="8">
         <v>46115</v>
@@ -11729,18 +11735,18 @@
         <v>1</v>
       </c>
       <c r="AR92" s="9" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AS92" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AT92" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="93" spans="1:46">
       <c r="A93" s="9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B93" s="8">
         <v>46115</v>
@@ -11827,15 +11833,15 @@
         <v>270</v>
       </c>
       <c r="AS93" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AT93" s="9" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="94" spans="1:46">
       <c r="A94" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B94" s="8">
         <v>46111</v>
@@ -11850,7 +11856,7 @@
         <v>127</v>
       </c>
       <c r="F94" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G94" s="9" t="s">
         <v>33</v>
@@ -11922,18 +11928,18 @@
         <v>1</v>
       </c>
       <c r="AR94" s="9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AS94" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AT94" s="9" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="95" spans="1:46">
       <c r="A95" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B95" s="8">
         <v>46111</v>
@@ -11948,7 +11954,7 @@
         <v>127</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G95" s="9" t="s">
         <v>33</v>
@@ -12020,15 +12026,15 @@
         <v>245</v>
       </c>
       <c r="AS95" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AT95" s="9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="96" spans="1:46">
       <c r="A96" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B96" s="8">
         <v>46080</v>
@@ -12121,7 +12127,7 @@
         <v>123</v>
       </c>
       <c r="AS96" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AT96" s="9" t="s">
         <v>52</v>
@@ -12129,7 +12135,7 @@
     </row>
     <row r="97" spans="1:46">
       <c r="A97" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B97" s="8">
         <v>45923</v>
@@ -12186,7 +12192,7 @@
         <v>44</v>
       </c>
       <c r="X97" s="9" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AB97" s="9" t="s">
         <v>33</v>
@@ -12222,7 +12228,7 @@
         <v>123</v>
       </c>
       <c r="AS97" s="9" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AT97" s="9" t="s">
         <v>53</v>
@@ -12230,7 +12236,7 @@
     </row>
     <row r="98" spans="1:46">
       <c r="A98" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B98" s="8">
         <v>45729</v>
@@ -12317,15 +12323,15 @@
         <v>341</v>
       </c>
       <c r="AS98" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AT98" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="99" spans="1:46">
       <c r="A99" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B99" s="8">
         <v>45642</v>
@@ -12412,15 +12418,15 @@
         <v>123</v>
       </c>
       <c r="AS99" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AT99" s="9" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="100" spans="1:46">
       <c r="A100" s="9" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B100" s="8">
         <v>45611</v>
@@ -12471,16 +12477,16 @@
         <v>44</v>
       </c>
       <c r="U100" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="X100" s="9" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AB100" s="9" t="s">
         <v>33</v>
       </c>
       <c r="AD100" s="9" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AH100" s="9" t="s">
         <v>44</v>
@@ -12510,15 +12516,15 @@
         <v>123</v>
       </c>
       <c r="AS100" s="9" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AT100" s="9" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="101" spans="1:46">
       <c r="A101" s="9" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B101" s="8">
         <v>45391</v>
@@ -12575,7 +12581,7 @@
         <v>44</v>
       </c>
       <c r="X101" s="9" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AB101" s="9" t="s">
         <v>33</v>
@@ -12611,15 +12617,15 @@
         <v>123</v>
       </c>
       <c r="AS101" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AT101" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="102" spans="1:46">
       <c r="A102" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B102" s="8">
         <v>45357</v>
@@ -12709,15 +12715,15 @@
         <v>123</v>
       </c>
       <c r="AS102" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AT102" s="9" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="103" spans="1:46">
       <c r="A103" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B103" s="8">
         <v>45288</v>
@@ -12732,10 +12738,10 @@
         <v>31</v>
       </c>
       <c r="F103" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H103" s="9" t="s">
         <v>44</v>
@@ -12804,15 +12810,15 @@
         <v>123</v>
       </c>
       <c r="AS103" s="9" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AT103" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="104" spans="1:46">
       <c r="A104" s="9" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B104" s="8">
         <v>45190</v>
@@ -12827,19 +12833,19 @@
         <v>48</v>
       </c>
       <c r="F104" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H104" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I104" s="9" t="s">
         <v>97</v>
       </c>
       <c r="J104" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K104" s="10">
         <v>28000000000</v>
@@ -12851,7 +12857,7 @@
         <v>1</v>
       </c>
       <c r="O104" s="9" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P104" s="9" t="s">
         <v>44</v>
@@ -12872,7 +12878,7 @@
         <v>33</v>
       </c>
       <c r="AD104" s="9" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AE104" s="10">
         <v>3653708000</v>
@@ -12884,13 +12890,13 @@
         <v>129</v>
       </c>
       <c r="AK104" s="9" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AL104" s="9" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM104" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN104" s="9" t="s">
         <v>35</v>
@@ -12905,18 +12911,18 @@
         <v>2</v>
       </c>
       <c r="AR104" s="9" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AS104" s="9" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AT104" s="9" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="105" spans="1:46">
       <c r="A105" s="9" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B105" s="8">
         <v>44707</v>
@@ -12931,19 +12937,19 @@
         <v>48</v>
       </c>
       <c r="F105" s="9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I105" s="9" t="s">
         <v>97</v>
       </c>
       <c r="J105" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K105" s="10">
         <v>61000000000</v>
@@ -12958,10 +12964,10 @@
         <v>1</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Q105" s="9" t="s">
         <v>141</v>
@@ -12982,7 +12988,7 @@
         <v>33</v>
       </c>
       <c r="AD105" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AE105" s="10">
         <v>12851000000</v>
@@ -13003,13 +13009,13 @@
         <v>23.26365475387728</v>
       </c>
       <c r="AK105" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AL105" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AM105" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN105" s="9" t="s">
         <v>35</v>
@@ -13024,18 +13030,18 @@
         <v>2</v>
       </c>
       <c r="AR105" s="9" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AS105" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AT105" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="106" spans="1:46">
       <c r="A106" s="9" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B106" s="8">
         <v>44640</v>
@@ -13050,19 +13056,19 @@
         <v>48</v>
       </c>
       <c r="F106" s="9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H106" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I106" s="9" t="s">
         <v>97</v>
       </c>
       <c r="J106" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K106" s="10">
         <v>10400000000</v>
@@ -13074,7 +13080,7 @@
         <v>1</v>
       </c>
       <c r="O106" s="9" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P106" s="9" t="s">
         <v>44</v>
@@ -13095,7 +13101,7 @@
         <v>33</v>
       </c>
       <c r="AD106" s="9" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AE106" s="10">
         <v>592200000</v>
@@ -13107,13 +13113,13 @@
         <v>129</v>
       </c>
       <c r="AK106" s="9" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AL106" s="9" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AM106" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AN106" s="9" t="s">
         <v>35</v>
@@ -13128,18 +13134,18 @@
         <v>2</v>
       </c>
       <c r="AR106" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AS106" s="9" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AT106" s="9" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="107" spans="1:46">
       <c r="A107" s="9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B107" s="8">
         <v>44592</v>
@@ -13154,19 +13160,19 @@
         <v>48</v>
       </c>
       <c r="F107" s="9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I107" s="9" t="s">
         <v>97</v>
       </c>
       <c r="J107" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K107" s="10">
         <v>16500000000</v>
@@ -13181,7 +13187,7 @@
         <v>1</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P107" s="9" t="s">
         <v>44</v>
@@ -13202,7 +13208,7 @@
         <v>33</v>
       </c>
       <c r="AD107" s="9" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AE107" s="10">
         <v>3217170000</v>
@@ -13217,13 +13223,13 @@
         <v>5.128731151913017</v>
       </c>
       <c r="AK107" s="9" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AL107" s="9" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM107" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AN107" s="9" t="s">
         <v>35</v>
@@ -13238,18 +13244,18 @@
         <v>1</v>
       </c>
       <c r="AR107" s="9" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AS107" s="9" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AT107" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="108" spans="1:46">
       <c r="A108" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B108" s="8">
         <v>44579</v>
@@ -13264,19 +13270,19 @@
         <v>48</v>
       </c>
       <c r="F108" s="9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H108" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I108" s="9" t="s">
         <v>97</v>
       </c>
       <c r="J108" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K108" s="10">
         <v>68700000000</v>
@@ -13291,10 +13297,10 @@
         <v>1</v>
       </c>
       <c r="O108" s="9" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P108" s="9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="Q108" s="9" t="s">
         <v>141</v>
@@ -13315,7 +13321,7 @@
         <v>33</v>
       </c>
       <c r="AD108" s="9" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AE108" s="10">
         <v>8086000000</v>
@@ -13330,13 +13336,13 @@
         <v>8.496166213208014</v>
       </c>
       <c r="AK108" s="9" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AL108" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AM108" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN108" s="9" t="s">
         <v>35</v>
@@ -13351,18 +13357,18 @@
         <v>2</v>
       </c>
       <c r="AR108" s="9" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AS108" s="9" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AT108" s="9" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="109" spans="1:46">
       <c r="A109" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B109" s="8">
         <v>44166</v>
@@ -13377,19 +13383,19 @@
         <v>48</v>
       </c>
       <c r="F109" s="9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I109" s="9" t="s">
         <v>97</v>
       </c>
       <c r="J109" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K109" s="10">
         <v>27700000000</v>
@@ -13404,7 +13410,7 @@
         <v>1</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>44</v>
@@ -13425,7 +13431,7 @@
         <v>33</v>
       </c>
       <c r="AD109" s="9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AE109" s="10">
         <v>630422000</v>
@@ -13440,13 +13446,13 @@
         <v>43.93882193197572</v>
       </c>
       <c r="AK109" s="9" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AL109" s="9" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AM109" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN109" s="9" t="s">
         <v>35</v>
@@ -13461,18 +13467,18 @@
         <v>2</v>
       </c>
       <c r="AR109" s="9" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AS109" s="9" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AT109" s="9" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="110" spans="1:46">
       <c r="A110" s="9" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B110" s="8">
         <v>44131</v>
@@ -13487,19 +13493,19 @@
         <v>48</v>
       </c>
       <c r="F110" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H110" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I110" s="9" t="s">
         <v>97</v>
       </c>
       <c r="J110" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K110" s="10">
         <v>35000000000</v>
@@ -13532,7 +13538,7 @@
         <v>33</v>
       </c>
       <c r="AD110" s="9" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AE110" s="10">
         <v>3162666000</v>
@@ -13544,13 +13550,13 @@
         <v>129</v>
       </c>
       <c r="AK110" s="9" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AL110" s="9" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM110" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN110" s="9" t="s">
         <v>35</v>
@@ -13565,18 +13571,18 @@
         <v>2</v>
       </c>
       <c r="AR110" s="9" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AS110" s="9" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AT110" s="9" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="111" spans="1:46">
       <c r="A111" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B111" s="8">
         <v>43626</v>
@@ -13591,19 +13597,19 @@
         <v>48</v>
       </c>
       <c r="F111" s="9" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I111" s="9" t="s">
         <v>97</v>
       </c>
       <c r="J111" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K111" s="10">
         <v>15700000000</v>
@@ -13639,7 +13645,7 @@
         <v>33</v>
       </c>
       <c r="AD111" s="9" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AE111" s="10">
         <v>1159000000</v>
@@ -13654,13 +13660,13 @@
         <v>13.54616048317515</v>
       </c>
       <c r="AK111" s="9" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AL111" s="9" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM111" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN111" s="9" t="s">
         <v>35</v>
@@ -13675,18 +13681,18 @@
         <v>2</v>
       </c>
       <c r="AR111" s="9" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AS111" s="9" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AT111" s="9" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="112" spans="1:46">
       <c r="A112" s="9" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B112" s="8">
         <v>43401</v>
@@ -13701,19 +13707,19 @@
         <v>48</v>
       </c>
       <c r="F112" s="9" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H112" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I112" s="9" t="s">
         <v>97</v>
       </c>
       <c r="J112" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K112" s="10">
         <v>34000000000</v>
@@ -13728,7 +13734,7 @@
         <v>1</v>
       </c>
       <c r="O112" s="9" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P112" s="9" t="s">
         <v>44</v>
@@ -13749,7 +13755,7 @@
         <v>33</v>
       </c>
       <c r="AD112" s="9" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AE112" s="10">
         <v>2920461000</v>
@@ -13764,13 +13770,13 @@
         <v>11.64199761612978</v>
       </c>
       <c r="AK112" s="9" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AL112" s="9" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AM112" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN112" s="9" t="s">
         <v>35</v>
@@ -13785,18 +13791,18 @@
         <v>2</v>
       </c>
       <c r="AR112" s="9" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AS112" s="9" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AT112" s="9" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="113" spans="1:46">
       <c r="A113" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B113" s="8">
         <v>42534</v>
@@ -13811,19 +13817,19 @@
         <v>48</v>
       </c>
       <c r="F113" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I113" s="9" t="s">
         <v>97</v>
       </c>
       <c r="J113" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="K113" s="10">
         <v>26200000000</v>
@@ -13838,7 +13844,7 @@
         <v>1</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>44</v>
@@ -13859,7 +13865,7 @@
         <v>33</v>
       </c>
       <c r="AD113" s="9" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AE113" s="10">
         <v>2990911000</v>
@@ -13880,13 +13886,13 @@
         <v>102.9582822471628</v>
       </c>
       <c r="AK113" s="9" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AL113" s="9" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AM113" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN113" s="9" t="s">
         <v>35</v>
@@ -13901,13 +13907,13 @@
         <v>2</v>
       </c>
       <c r="AR113" s="9" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AS113" s="9" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AT113" s="9" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
   </sheetData>
@@ -14053,7 +14059,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14071,7 +14077,7 @@
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -14092,16 +14098,16 @@
         <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C6" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D6" t="s">
         <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F6" t="s">
         <v>27</v>
@@ -14110,13 +14116,13 @@
         <v>81</v>
       </c>
       <c r="H6" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="I6" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="J6" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K6" t="s">
         <v>82</v>
@@ -14125,18 +14131,18 @@
         <v>88</v>
       </c>
       <c r="M6" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N6" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="42" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C7" s="8">
         <v>45190</v>
@@ -14154,21 +14160,21 @@
         <v>3653708000</v>
       </c>
       <c r="L7" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="M7" s="13" t="s">
         <v>484</v>
       </c>
-      <c r="M7" s="13" t="s">
-        <v>483</v>
-      </c>
       <c r="N7" s="13" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C8" s="8">
         <v>44707</v>
@@ -14198,21 +14204,21 @@
         <v>2966000000</v>
       </c>
       <c r="L8" s="13" t="s">
+        <v>497</v>
+      </c>
+      <c r="M8" s="13" t="s">
         <v>496</v>
       </c>
-      <c r="M8" s="13" t="s">
-        <v>495</v>
-      </c>
       <c r="N8" s="13" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="42" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C9" s="8">
         <v>44640</v>
@@ -14230,21 +14236,21 @@
         <v>592200000</v>
       </c>
       <c r="L9" s="13" t="s">
+        <v>506</v>
+      </c>
+      <c r="M9" s="13" t="s">
         <v>505</v>
       </c>
-      <c r="M9" s="13" t="s">
-        <v>504</v>
-      </c>
       <c r="N9" s="13" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="42" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C10" s="8">
         <v>44592</v>
@@ -14262,21 +14268,21 @@
         <v>3217170000</v>
       </c>
       <c r="L10" s="13" t="s">
+        <v>516</v>
+      </c>
+      <c r="M10" s="13" t="s">
         <v>515</v>
       </c>
-      <c r="M10" s="13" t="s">
-        <v>514</v>
-      </c>
       <c r="N10" s="13" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="42" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C11" s="8">
         <v>44579</v>
@@ -14297,21 +14303,21 @@
         <v>2734000000</v>
       </c>
       <c r="L11" s="13" t="s">
+        <v>526</v>
+      </c>
+      <c r="M11" s="13" t="s">
         <v>525</v>
       </c>
-      <c r="M11" s="13" t="s">
-        <v>524</v>
-      </c>
       <c r="N11" s="13" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="42" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C12" s="8">
         <v>44166</v>
@@ -14329,21 +14335,21 @@
         <v>630422000</v>
       </c>
       <c r="L12" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="M12" s="13" t="s">
         <v>534</v>
       </c>
-      <c r="M12" s="13" t="s">
-        <v>533</v>
-      </c>
       <c r="N12" s="13" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="42" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C13" s="8">
         <v>44131</v>
@@ -14361,21 +14367,21 @@
         <v>3162666000</v>
       </c>
       <c r="L13" s="13" t="s">
+        <v>544</v>
+      </c>
+      <c r="M13" s="13" t="s">
         <v>543</v>
       </c>
-      <c r="M13" s="13" t="s">
-        <v>542</v>
-      </c>
       <c r="N13" s="13" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="42" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C14" s="8">
         <v>43626</v>
@@ -14393,21 +14399,21 @@
         <v>1159000000</v>
       </c>
       <c r="L14" s="13" t="s">
+        <v>552</v>
+      </c>
+      <c r="M14" s="13" t="s">
         <v>551</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>550</v>
-      </c>
       <c r="N14" s="13" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="42" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C15" s="8">
         <v>43401</v>
@@ -14428,21 +14434,21 @@
         <v>472442000</v>
       </c>
       <c r="L15" s="13" t="s">
+        <v>560</v>
+      </c>
+      <c r="M15" s="13" t="s">
         <v>559</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>558</v>
-      </c>
       <c r="N15" s="13" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="42" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C16" s="8">
         <v>42534</v>
@@ -14466,13 +14472,13 @@
         <v>254472000</v>
       </c>
       <c r="L16" s="13" t="s">
+        <v>568</v>
+      </c>
+      <c r="M16" s="13" t="s">
         <v>567</v>
       </c>
-      <c r="M16" s="13" t="s">
-        <v>566</v>
-      </c>
       <c r="N16" s="13" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -14520,7 +14526,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -14539,7 +14545,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -14564,13 +14570,13 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D6" t="s">
         <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="F6" t="s">
         <v>81</v>
@@ -14585,7 +14591,7 @@
         <v>28</v>
       </c>
       <c r="J6" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="K6" t="s">
         <v>85</v>
@@ -14594,13 +14600,13 @@
         <v>86</v>
       </c>
       <c r="M6" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N6" t="s">
         <v>87</v>
       </c>
       <c r="O6" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="7" spans="1:15">
@@ -14623,7 +14629,7 @@
         <v>41</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K7" s="12">
         <f>IFERROR(IF(AND(D7&gt;0,F7&gt;0,E7=H7),D7/F7,""),"")</f>
@@ -14664,7 +14670,7 @@
         <v>176</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K8" s="12">
         <f>IFERROR(IF(AND(D8&gt;0,F8&gt;0,E8=H8),D8/F8,""),"")</f>
@@ -14705,7 +14711,7 @@
         <v>41</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K9" s="12">
         <f>IFERROR(IF(AND(D9&gt;0,F9&gt;0,E9=H9),D9/F9,""),"")</f>
@@ -14746,7 +14752,7 @@
         <v>176</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K10" s="12">
         <f>IFERROR(IF(AND(D10&gt;0,F10&gt;0,E10=H10),D10/F10,""),"")</f>
@@ -14787,7 +14793,7 @@
         <v>176</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K11" s="12">
         <f>IFERROR(IF(AND(D11&gt;0,F11&gt;0,E11=H11),D11/F11,""),"")</f>
@@ -14828,7 +14834,7 @@
         <v>176</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K12" s="12">
         <f>IFERROR(IF(AND(D12&gt;0,F12&gt;0,E12=H12),D12/F12,""),"")</f>
@@ -14869,7 +14875,7 @@
         <v>41</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K13" s="12">
         <f>IFERROR(IF(AND(D13&gt;0,F13&gt;0,E13=H13),D13/F13,""),"")</f>
@@ -14892,7 +14898,7 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B14" s="8">
         <v>46175</v>
@@ -14910,7 +14916,7 @@
         <v>35</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K14" s="12">
         <f>IFERROR(IF(AND(D14&gt;0,F14&gt;0,E14=H14),D14/F14,""),"")</f>
@@ -14933,13 +14939,13 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B15" s="8">
         <v>46170</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>44</v>
@@ -14951,7 +14957,7 @@
         <v>41</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K15" s="12">
         <f>IFERROR(IF(AND(D15&gt;0,F15&gt;0,E15=H15),D15/F15,""),"")</f>
@@ -14974,7 +14980,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B16" s="8">
         <v>46167</v>
@@ -14992,7 +14998,7 @@
         <v>176</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K16" s="12">
         <f>IFERROR(IF(AND(D16&gt;0,F16&gt;0,E16=H16),D16/F16,""),"")</f>
@@ -15015,7 +15021,7 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B17" s="8">
         <v>46157</v>
@@ -15033,7 +15039,7 @@
         <v>176</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K17" s="12">
         <f>IFERROR(IF(AND(D17&gt;0,F17&gt;0,E17=H17),D17/F17,""),"")</f>
@@ -15056,7 +15062,7 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B18" s="8">
         <v>46149</v>
@@ -15074,7 +15080,7 @@
         <v>41</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K18" s="12">
         <f>IFERROR(IF(AND(D18&gt;0,F18&gt;0,E18=H18),D18/F18,""),"")</f>
@@ -15097,7 +15103,7 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B19" s="8">
         <v>46139</v>
@@ -15115,7 +15121,7 @@
         <v>176</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K19" s="12">
         <f>IFERROR(IF(AND(D19&gt;0,F19&gt;0,E19=H19),D19/F19,""),"")</f>
@@ -15138,7 +15144,7 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B20" s="8">
         <v>46139</v>
@@ -15156,7 +15162,7 @@
         <v>176</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K20" s="12">
         <f>IFERROR(IF(AND(D20&gt;0,F20&gt;0,E20=H20),D20/F20,""),"")</f>
@@ -15179,7 +15185,7 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B21" s="8">
         <v>46139</v>
@@ -15197,7 +15203,7 @@
         <v>176</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K21" s="12">
         <f>IFERROR(IF(AND(D21&gt;0,F21&gt;0,E21=H21),D21/F21,""),"")</f>
@@ -15220,7 +15226,7 @@
     </row>
     <row r="22" spans="1:15">
       <c r="A22" s="9" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B22" s="8">
         <v>46139</v>
@@ -15238,7 +15244,7 @@
         <v>176</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K22" s="12">
         <f>IFERROR(IF(AND(D22&gt;0,F22&gt;0,E22=H22),D22/F22,""),"")</f>
@@ -15261,7 +15267,7 @@
     </row>
     <row r="23" spans="1:15">
       <c r="A23" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B23" s="8">
         <v>46139</v>
@@ -15279,7 +15285,7 @@
         <v>176</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K23" s="12">
         <f>IFERROR(IF(AND(D23&gt;0,F23&gt;0,E23=H23),D23/F23,""),"")</f>
@@ -15302,13 +15308,13 @@
     </row>
     <row r="24" spans="1:15">
       <c r="A24" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B24" s="8">
         <v>46128</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E24" s="9" t="s">
         <v>34</v>
@@ -15320,7 +15326,7 @@
         <v>41</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K24" s="12">
         <f>IFERROR(IF(AND(D24&gt;0,F24&gt;0,E24=H24),D24/F24,""),"")</f>
@@ -15343,7 +15349,7 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B25" s="8">
         <v>45642</v>
@@ -15361,7 +15367,7 @@
         <v>41</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K25" s="12">
         <f>IFERROR(IF(AND(D25&gt;0,F25&gt;0,E25=H25),D25/F25,""),"")</f>
@@ -15384,13 +15390,13 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B26" s="8">
         <v>45288</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>44</v>
@@ -15402,7 +15408,7 @@
         <v>41</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K26" s="12">
         <f>IFERROR(IF(AND(D26&gt;0,F26&gt;0,E26=H26),D26/F26,""),"")</f>
@@ -15425,13 +15431,13 @@
     </row>
     <row r="27" spans="1:15">
       <c r="A27" s="9" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B27" s="8">
         <v>45190</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>129</v>
@@ -15446,7 +15452,7 @@
         <v>35</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K27" s="12">
         <f>IFERROR(IF(AND(D27&gt;0,F27&gt;0,E27=H27),D27/F27,""),"")</f>
@@ -15461,21 +15467,21 @@
         <v>NO</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="9" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B28" s="8">
         <v>44707</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D28" s="10">
         <v>69000000000</v>
@@ -15496,7 +15502,7 @@
         <v>35</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K28" s="12">
         <f>IFERROR(IF(AND(D28&gt;0,F28&gt;0,E28=H28),D28/F28,""),"")</f>
@@ -15511,21 +15517,21 @@
         <v>YES</v>
       </c>
       <c r="N28" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O28" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="9" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B29" s="8">
         <v>44640</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>129</v>
@@ -15540,7 +15546,7 @@
         <v>35</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K29" s="12">
         <f>IFERROR(IF(AND(D29&gt;0,F29&gt;0,E29=H29),D29/F29,""),"")</f>
@@ -15555,21 +15561,21 @@
         <v>NO</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B30" s="8">
         <v>44592</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D30" s="10">
         <v>16500000000</v>
@@ -15587,7 +15593,7 @@
         <v>35</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="K30" s="12">
         <f>IFERROR(IF(AND(D30&gt;0,F30&gt;0,E30=H30),D30/F30,""),"")</f>
@@ -15602,21 +15608,21 @@
         <v>NO</v>
       </c>
       <c r="N30" s="9" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O30" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B31" s="8">
         <v>44579</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D31" s="10">
         <v>68700000000</v>
@@ -15634,7 +15640,7 @@
         <v>35</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K31" s="12">
         <f>IFERROR(IF(AND(D31&gt;0,F31&gt;0,E31=H31),D31/F31,""),"")</f>
@@ -15649,21 +15655,21 @@
         <v>YES</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B32" s="8">
         <v>44166</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D32" s="10">
         <v>27700000000</v>
@@ -15681,7 +15687,7 @@
         <v>35</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K32" s="12">
         <f>IFERROR(IF(AND(D32&gt;0,F32&gt;0,E32=H32),D32/F32,""),"")</f>
@@ -15696,21 +15702,21 @@
         <v>YES</v>
       </c>
       <c r="N32" s="9" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O32" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="9" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B33" s="8">
         <v>44131</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>129</v>
@@ -15725,7 +15731,7 @@
         <v>35</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K33" s="12">
         <f>IFERROR(IF(AND(D33&gt;0,F33&gt;0,E33=H33),D33/F33,""),"")</f>
@@ -15740,21 +15746,21 @@
         <v>NO</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B34" s="8">
         <v>43626</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D34" s="10">
         <v>15700000000</v>
@@ -15772,7 +15778,7 @@
         <v>35</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K34" s="12">
         <f>IFERROR(IF(AND(D34&gt;0,F34&gt;0,E34=H34),D34/F34,""),"")</f>
@@ -15787,21 +15793,21 @@
         <v>YES</v>
       </c>
       <c r="N34" s="9" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O34" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="9" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B35" s="8">
         <v>43401</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D35" s="10">
         <v>34000000000</v>
@@ -15819,7 +15825,7 @@
         <v>35</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K35" s="12">
         <f>IFERROR(IF(AND(D35&gt;0,F35&gt;0,E35=H35),D35/F35,""),"")</f>
@@ -15834,21 +15840,21 @@
         <v>YES</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B36" s="8">
         <v>42534</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D36" s="10">
         <v>26200000000</v>
@@ -15869,7 +15875,7 @@
         <v>35</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K36" s="12">
         <f>IFERROR(IF(AND(D36&gt;0,F36&gt;0,E36=H36),D36/F36,""),"")</f>
@@ -15884,10 +15890,10 @@
         <v>YES</v>
       </c>
       <c r="N36" s="9" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O36" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -15904,7 +15910,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R146"/>
+  <dimension ref="A1:R147"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -15923,7 +15929,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -15945,7 +15951,7 @@
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -15967,7 +15973,7 @@
     </row>
     <row r="4" spans="1:18">
       <c r="M4" s="3" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -15986,43 +15992,43 @@
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E6" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="F6" t="s">
         <v>91</v>
       </c>
       <c r="G6" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H6" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="I6" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="J6" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="K6" t="s">
         <v>30</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>23</v>
@@ -16042,7 +16048,7 @@
         <v>102</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>101</v>
@@ -16063,7 +16069,7 @@
         <v>32</v>
       </c>
       <c r="M7" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -16095,7 +16101,7 @@
         <v>108</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>101</v>
@@ -16114,7 +16120,7 @@
         <v>110</v>
       </c>
       <c r="M8" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -16146,7 +16152,7 @@
         <v>102</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>101</v>
@@ -16167,7 +16173,7 @@
         <v>117</v>
       </c>
       <c r="M9" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -16199,7 +16205,7 @@
         <v>102</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>101</v>
@@ -16220,7 +16226,7 @@
         <v>120</v>
       </c>
       <c r="M10" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -16252,7 +16258,7 @@
         <v>123</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>101</v>
@@ -16273,7 +16279,7 @@
         <v>38</v>
       </c>
       <c r="M11" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -16305,7 +16311,7 @@
         <v>131</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>130</v>
@@ -16318,13 +16324,13 @@
         <v>2</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K12" s="13" t="s">
         <v>133</v>
       </c>
       <c r="M12" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -16356,7 +16362,7 @@
         <v>135</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>130</v>
@@ -16369,13 +16375,13 @@
         <v>2</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>137</v>
       </c>
       <c r="M13" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -16407,7 +16413,7 @@
         <v>142</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>130</v>
@@ -16420,13 +16426,13 @@
         <v>2</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="K14" s="13" t="s">
         <v>144</v>
       </c>
       <c r="M14" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -16458,7 +16464,7 @@
         <v>142</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>130</v>
@@ -16471,7 +16477,7 @@
         <v>2</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="K15" s="13" t="s">
         <v>148</v>
@@ -16491,7 +16497,7 @@
         <v>135</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>130</v>
@@ -16504,13 +16510,13 @@
         <v>2</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="K16" s="13" t="s">
         <v>152</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -16534,7 +16540,7 @@
         <v>154</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>130</v>
@@ -16547,7 +16553,7 @@
         <v>2</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K17" s="13" t="s">
         <v>156</v>
@@ -16567,7 +16573,7 @@
         <v>142</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>130</v>
@@ -16580,7 +16586,7 @@
         <v>2</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K18" s="13" t="s">
         <v>148</v>
@@ -16600,7 +16606,7 @@
         <v>102</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>101</v>
@@ -16635,7 +16641,7 @@
         <v>102</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>101</v>
@@ -16670,7 +16676,7 @@
         <v>102</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>101</v>
@@ -16705,7 +16711,7 @@
         <v>102</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>101</v>
@@ -16740,7 +16746,7 @@
         <v>177</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>130</v>
@@ -16773,7 +16779,7 @@
         <v>182</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>130</v>
@@ -16786,7 +16792,7 @@
         <v>2</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="K24" s="13" t="s">
         <v>184</v>
@@ -16806,7 +16812,7 @@
         <v>102</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>101</v>
@@ -16841,7 +16847,7 @@
         <v>102</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>101</v>
@@ -16876,7 +16882,7 @@
         <v>102</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>101</v>
@@ -16911,7 +16917,7 @@
         <v>195</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>130</v>
@@ -16944,20 +16950,20 @@
         <v>270</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="9">
         <v>2</v>
       </c>
       <c r="J29" s="13" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="K29" s="13" t="s">
         <v>197</v>
@@ -16974,23 +16980,23 @@
         <v>44</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H30" s="9"/>
       <c r="I30" s="9">
         <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="K30" s="13" t="s">
         <v>197</v>
@@ -17007,23 +17013,23 @@
         <v>44</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="9">
         <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="K31" s="13" t="s">
         <v>197</v>
@@ -17043,7 +17049,7 @@
         <v>102</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>101</v>
@@ -17078,7 +17084,7 @@
         <v>102</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>101</v>
@@ -17113,7 +17119,7 @@
         <v>102</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>101</v>
@@ -17148,7 +17154,7 @@
         <v>102</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>101</v>
@@ -17183,7 +17189,7 @@
         <v>102</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>101</v>
@@ -17218,7 +17224,7 @@
         <v>102</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>101</v>
@@ -17253,7 +17259,7 @@
         <v>102</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>101</v>
@@ -17288,7 +17294,7 @@
         <v>102</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>101</v>
@@ -17323,7 +17329,7 @@
         <v>102</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>101</v>
@@ -17358,7 +17364,7 @@
         <v>102</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>101</v>
@@ -17393,7 +17399,7 @@
         <v>102</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>101</v>
@@ -17428,7 +17434,7 @@
         <v>241</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>130</v>
@@ -17461,20 +17467,20 @@
         <v>135</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9">
         <v>1</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="K44" s="13" t="s">
         <v>243</v>
@@ -17494,20 +17500,20 @@
         <v>135</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="9">
         <v>1</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="K45" s="13" t="s">
         <v>243</v>
@@ -17527,20 +17533,20 @@
         <v>135</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H46" s="9"/>
       <c r="I46" s="9">
         <v>1</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="K46" s="13" t="s">
         <v>243</v>
@@ -17560,7 +17566,7 @@
         <v>245</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>130</v>
@@ -17575,7 +17581,7 @@
         <v>2</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="K47" s="13" t="s">
         <v>247</v>
@@ -17595,7 +17601,7 @@
         <v>102</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>101</v>
@@ -17630,7 +17636,7 @@
         <v>102</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>101</v>
@@ -17665,7 +17671,7 @@
         <v>102</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>101</v>
@@ -17700,7 +17706,7 @@
         <v>102</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>101</v>
@@ -17735,7 +17741,7 @@
         <v>265</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="F52" s="9" t="s">
         <v>130</v>
@@ -17768,7 +17774,7 @@
         <v>270</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>130</v>
@@ -17783,7 +17789,7 @@
         <v>2</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="K53" s="13" t="s">
         <v>272</v>
@@ -17803,7 +17809,7 @@
         <v>102</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>101</v>
@@ -17838,7 +17844,7 @@
         <v>102</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>101</v>
@@ -17873,7 +17879,7 @@
         <v>102</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>101</v>
@@ -17908,7 +17914,7 @@
         <v>102</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>101</v>
@@ -17943,7 +17949,7 @@
         <v>102</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>101</v>
@@ -17978,7 +17984,7 @@
         <v>142</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>130</v>
@@ -17993,7 +17999,7 @@
         <v>2</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K59" s="13" t="s">
         <v>295</v>
@@ -18013,7 +18019,7 @@
         <v>245</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>130</v>
@@ -18028,7 +18034,7 @@
         <v>2</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="K60" s="13" t="s">
         <v>299</v>
@@ -18048,7 +18054,7 @@
         <v>301</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>101</v>
@@ -18083,7 +18089,7 @@
         <v>142</v>
       </c>
       <c r="E62" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>130</v>
@@ -18098,7 +18104,7 @@
         <v>2</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="K62" s="13" t="s">
         <v>305</v>
@@ -18118,7 +18124,7 @@
         <v>308</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>130</v>
@@ -18153,7 +18159,7 @@
         <v>102</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F64" s="9" t="s">
         <v>101</v>
@@ -18188,7 +18194,7 @@
         <v>102</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>101</v>
@@ -18223,7 +18229,7 @@
         <v>102</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>101</v>
@@ -18258,7 +18264,7 @@
         <v>102</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>101</v>
@@ -18293,7 +18299,7 @@
         <v>102</v>
       </c>
       <c r="E68" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>101</v>
@@ -18328,7 +18334,7 @@
         <v>102</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>101</v>
@@ -18363,7 +18369,7 @@
         <v>102</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>101</v>
@@ -18398,7 +18404,7 @@
         <v>333</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>130</v>
@@ -18433,7 +18439,7 @@
         <v>337</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>101</v>
@@ -18468,7 +18474,7 @@
         <v>341</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>101</v>
@@ -18503,13 +18509,13 @@
         <v>245</v>
       </c>
       <c r="E74" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H74" s="8">
         <v>46181</v>
@@ -18518,7 +18524,7 @@
         <v>2</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="K74" s="13" t="s">
         <v>47</v>
@@ -18538,13 +18544,13 @@
         <v>135</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H75" s="8">
         <v>46177</v>
@@ -18553,7 +18559,7 @@
         <v>2</v>
       </c>
       <c r="J75" s="13" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="K75" s="13" t="s">
         <v>47</v>
@@ -18573,7 +18579,7 @@
         <v>346</v>
       </c>
       <c r="E76" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>130</v>
@@ -18608,13 +18614,13 @@
         <v>270</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H77" s="8">
         <v>46177</v>
@@ -18623,10 +18629,10 @@
         <v>2</v>
       </c>
       <c r="J77" s="13" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K77" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="28" customHeight="1">
@@ -18640,16 +18646,16 @@
         <v>352</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H78" s="8">
         <v>46171</v>
@@ -18658,10 +18664,10 @@
         <v>2</v>
       </c>
       <c r="J78" s="13" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K78" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="28" customHeight="1">
@@ -18675,16 +18681,16 @@
         <v>352</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H79" s="8">
         <v>46170</v>
@@ -18693,10 +18699,10 @@
         <v>2</v>
       </c>
       <c r="J79" s="13" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="K79" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="28" customHeight="1">
@@ -18713,13 +18719,13 @@
         <v>195</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H80" s="8">
         <v>46170</v>
@@ -18728,10 +18734,10 @@
         <v>1</v>
       </c>
       <c r="J80" s="13" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K80" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="28" customHeight="1">
@@ -18748,13 +18754,13 @@
         <v>195</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H81" s="8">
         <v>46170</v>
@@ -18763,10 +18769,10 @@
         <v>1</v>
       </c>
       <c r="J81" s="13" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K81" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="28" customHeight="1">
@@ -18783,13 +18789,13 @@
         <v>245</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F82" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H82" s="8">
         <v>46170</v>
@@ -18798,10 +18804,10 @@
         <v>2</v>
       </c>
       <c r="J82" s="13" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="28" customHeight="1">
@@ -18818,13 +18824,13 @@
         <v>346</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H83" s="8">
         <v>46170</v>
@@ -18833,10 +18839,10 @@
         <v>1</v>
       </c>
       <c r="J83" s="13" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="K83" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="28" customHeight="1">
@@ -18853,23 +18859,23 @@
         <v>195</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F84" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H84" s="9"/>
       <c r="I84" s="9">
         <v>1</v>
       </c>
       <c r="J84" s="13" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="28" customHeight="1">
@@ -18886,63 +18892,61 @@
         <v>195</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H85" s="9"/>
       <c r="I85" s="9">
         <v>1</v>
       </c>
       <c r="J85" s="13" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="K85" s="13" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="28" customHeight="1">
       <c r="A86" s="9" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B86" s="8">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>49</v>
+        <v>352</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>341</v>
+        <v>423</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="F86" s="9" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="H86" s="8">
-        <v>46175</v>
-      </c>
+        <v>653</v>
+      </c>
+      <c r="H86" s="9"/>
       <c r="I86" s="9">
         <v>1</v>
       </c>
       <c r="J86" s="13" t="s">
-        <v>357</v>
+        <v>653</v>
       </c>
       <c r="K86" s="13" t="s">
-        <v>51</v>
+        <v>356</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="28" customHeight="1">
       <c r="A87" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B87" s="8">
         <v>46175</v>
@@ -18951,25 +18955,25 @@
         <v>49</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>270</v>
+        <v>341</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>627</v>
+        <v>608</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>652</v>
+        <v>358</v>
       </c>
       <c r="H87" s="8">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="I87" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J87" s="13" t="s">
-        <v>653</v>
+        <v>358</v>
       </c>
       <c r="K87" s="13" t="s">
         <v>51</v>
@@ -18977,7 +18981,7 @@
     </row>
     <row r="88" spans="1:11" ht="28" customHeight="1">
       <c r="A88" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B88" s="8">
         <v>46175</v>
@@ -18986,10 +18990,10 @@
         <v>49</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="E88" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F88" s="9" t="s">
         <v>130</v>
@@ -18998,7 +19002,7 @@
         <v>654</v>
       </c>
       <c r="H88" s="8">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="I88" s="9">
         <v>2</v>
@@ -19012,355 +19016,355 @@
     </row>
     <row r="89" spans="1:11" ht="28" customHeight="1">
       <c r="A89" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B89" s="8">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>360</v>
+        <v>49</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>245</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>361</v>
+        <v>656</v>
       </c>
       <c r="H89" s="8">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="I89" s="9">
         <v>2</v>
       </c>
       <c r="J89" s="13" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="K89" s="13" t="s">
-        <v>362</v>
+        <v>51</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="28" customHeight="1">
       <c r="A90" s="9" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B90" s="8">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>44</v>
+        <v>361</v>
       </c>
       <c r="D90" s="9" t="s">
         <v>245</v>
       </c>
       <c r="E90" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F90" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="H90" s="8">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="I90" s="9">
         <v>2</v>
       </c>
       <c r="J90" s="13" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="K90" s="13" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="28" customHeight="1">
       <c r="A91" s="9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B91" s="8">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>352</v>
+        <v>44</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>270</v>
+        <v>245</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="H91" s="8">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="I91" s="9">
         <v>2</v>
       </c>
       <c r="J91" s="13" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="K91" s="13" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="28" customHeight="1">
       <c r="A92" s="9" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B92" s="8">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="C92" s="9" t="s">
         <v>352</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="E92" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F92" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="H92" s="8">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="I92" s="9">
         <v>2</v>
       </c>
       <c r="J92" s="13" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="K92" s="13" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="28" customHeight="1">
       <c r="A93" s="9" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B93" s="8">
         <v>46157</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>44</v>
+        <v>352</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>346</v>
+        <v>245</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="H93" s="8">
         <v>46157</v>
       </c>
       <c r="I93" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J93" s="13" t="s">
-        <v>374</v>
+        <v>661</v>
       </c>
       <c r="K93" s="13" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="28" customHeight="1">
       <c r="A94" s="9" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B94" s="8">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>377</v>
+        <v>44</v>
       </c>
       <c r="D94" s="9" t="s">
         <v>346</v>
       </c>
       <c r="E94" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F94" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="H94" s="8">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="I94" s="9">
         <v>1</v>
       </c>
       <c r="J94" s="13" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="K94" s="13" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="28" customHeight="1">
       <c r="A95" s="9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B95" s="8">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>44</v>
+        <v>378</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>381</v>
+        <v>346</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="H95" s="9"/>
+        <v>379</v>
+      </c>
+      <c r="H95" s="8">
+        <v>46150</v>
+      </c>
       <c r="I95" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J95" s="13" t="s">
-        <v>660</v>
+        <v>379</v>
       </c>
       <c r="K95" s="13" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="28" customHeight="1">
       <c r="A96" s="9" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B96" s="8">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>270</v>
+        <v>382</v>
       </c>
       <c r="E96" s="9" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="F96" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="H96" s="8">
-        <v>46147</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="H96" s="9"/>
       <c r="I96" s="9">
         <v>2</v>
       </c>
       <c r="J96" s="13" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="K96" s="13" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="28" customHeight="1">
       <c r="A97" s="9" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B97" s="8">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C97" s="9" t="s">
         <v>46</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>389</v>
+        <v>270</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="H97" s="8">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="I97" s="9">
         <v>2</v>
       </c>
       <c r="J97" s="13" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="K97" s="13" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="28" customHeight="1">
       <c r="A98" s="9" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B98" s="8">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>182</v>
+        <v>390</v>
       </c>
       <c r="E98" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F98" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H98" s="8">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="I98" s="9">
         <v>2</v>
       </c>
       <c r="J98" s="13" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="K98" s="13" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="28" customHeight="1">
       <c r="A99" s="9" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B99" s="8">
         <v>46139</v>
@@ -19369,33 +19373,33 @@
         <v>44</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>270</v>
+        <v>182</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="H99" s="8">
         <v>46139</v>
       </c>
       <c r="I99" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J99" s="13" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="K99" s="13" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="28" customHeight="1">
       <c r="A100" s="9" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B100" s="8">
         <v>46139</v>
@@ -19404,33 +19408,33 @@
         <v>44</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>399</v>
+        <v>270</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F100" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="H100" s="8">
         <v>46139</v>
       </c>
       <c r="I100" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J100" s="13" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="K100" s="13" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="28" customHeight="1">
       <c r="A101" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B101" s="8">
         <v>46139</v>
@@ -19439,16 +19443,16 @@
         <v>44</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>135</v>
+        <v>400</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>666</v>
+        <v>401</v>
       </c>
       <c r="H101" s="8">
         <v>46139</v>
@@ -19460,12 +19464,12 @@
         <v>667</v>
       </c>
       <c r="K101" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="28" customHeight="1">
       <c r="A102" s="9" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B102" s="8">
         <v>46139</v>
@@ -19474,31 +19478,33 @@
         <v>44</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>668</v>
+        <v>135</v>
       </c>
       <c r="E102" s="9" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="F102" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>669</v>
-      </c>
-      <c r="H102" s="9"/>
+        <v>668</v>
+      </c>
+      <c r="H102" s="8">
+        <v>46139</v>
+      </c>
       <c r="I102" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J102" s="13" t="s">
         <v>669</v>
       </c>
       <c r="K102" s="13" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="28" customHeight="1">
       <c r="A103" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B103" s="8">
         <v>46139</v>
@@ -19507,33 +19513,31 @@
         <v>44</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>403</v>
+        <v>670</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>404</v>
-      </c>
-      <c r="H103" s="8">
-        <v>46139</v>
-      </c>
+        <v>671</v>
+      </c>
+      <c r="H103" s="9"/>
       <c r="I103" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J103" s="13" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K103" s="13" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="28" customHeight="1">
       <c r="A104" s="9" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B104" s="8">
         <v>46139</v>
@@ -19542,16 +19546,16 @@
         <v>44</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E104" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="H104" s="8">
         <v>46139</v>
@@ -19560,68 +19564,68 @@
         <v>2</v>
       </c>
       <c r="J104" s="13" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="K104" s="13" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="28" customHeight="1">
       <c r="A105" s="9" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B105" s="8">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>352</v>
+        <v>44</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>195</v>
+        <v>408</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="H105" s="8">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="I105" s="9">
         <v>2</v>
       </c>
       <c r="J105" s="13" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K105" s="13" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="28" customHeight="1">
       <c r="A106" s="9" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B106" s="8">
         <v>46132</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>46</v>
+        <v>352</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>414</v>
+        <v>195</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="H106" s="8">
         <v>46132</v>
@@ -19630,15 +19634,15 @@
         <v>2</v>
       </c>
       <c r="J106" s="13" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="K106" s="13" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="28" customHeight="1">
       <c r="A107" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B107" s="8">
         <v>46132</v>
@@ -19647,31 +19651,33 @@
         <v>46</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>674</v>
+        <v>415</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="H107" s="9"/>
+        <v>416</v>
+      </c>
+      <c r="H107" s="8">
+        <v>46132</v>
+      </c>
       <c r="I107" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J107" s="13" t="s">
         <v>675</v>
       </c>
       <c r="K107" s="13" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="28" customHeight="1">
       <c r="A108" s="9" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B108" s="8">
         <v>46132</v>
@@ -19680,119 +19686,117 @@
         <v>46</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>418</v>
+        <v>676</v>
       </c>
       <c r="E108" s="9" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="F108" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>419</v>
-      </c>
-      <c r="H108" s="8">
-        <v>46132</v>
-      </c>
+        <v>677</v>
+      </c>
+      <c r="H108" s="9"/>
       <c r="I108" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J108" s="13" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="K108" s="13" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="28" customHeight="1">
       <c r="A109" s="9" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B109" s="8">
         <v>46132</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>352</v>
+        <v>46</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>423</v>
-      </c>
-      <c r="H109" s="9"/>
+        <v>420</v>
+      </c>
+      <c r="H109" s="8">
+        <v>46132</v>
+      </c>
       <c r="I109" s="9">
         <v>2</v>
       </c>
       <c r="J109" s="13" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="K109" s="13" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="28" customHeight="1">
       <c r="A110" s="9" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B110" s="8">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>426</v>
+        <v>352</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>428</v>
-      </c>
-      <c r="H110" s="8">
-        <v>46128</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="H110" s="9"/>
       <c r="I110" s="9">
         <v>2</v>
       </c>
       <c r="J110" s="13" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="K110" s="13" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="28" customHeight="1">
       <c r="A111" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B111" s="8">
         <v>46128</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>182</v>
+        <v>419</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>679</v>
+        <v>429</v>
       </c>
       <c r="H111" s="8">
         <v>46128</v>
@@ -19804,30 +19808,30 @@
         <v>680</v>
       </c>
       <c r="K111" s="13" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="28" customHeight="1">
       <c r="A112" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B112" s="8">
         <v>46128</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>681</v>
+        <v>182</v>
       </c>
       <c r="E112" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F112" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H112" s="8">
         <v>46128</v>
@@ -19836,27 +19840,27 @@
         <v>2</v>
       </c>
       <c r="J112" s="13" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="K112" s="13" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="28" customHeight="1">
       <c r="A113" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B113" s="8">
         <v>46128</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>443</v>
+        <v>683</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>608</v>
+        <v>628</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>130</v>
@@ -19864,73 +19868,73 @@
       <c r="G113" s="9" t="s">
         <v>684</v>
       </c>
-      <c r="H113" s="9"/>
+      <c r="H113" s="8">
+        <v>46128</v>
+      </c>
       <c r="I113" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J113" s="13" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="K113" s="13" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="28" customHeight="1">
       <c r="A114" s="9" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B114" s="8">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="C114" s="9" t="s">
         <v>427</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>245</v>
+        <v>444</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>627</v>
+        <v>609</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>431</v>
-      </c>
-      <c r="H114" s="8">
-        <v>46122</v>
-      </c>
+        <v>686</v>
+      </c>
+      <c r="H114" s="9"/>
       <c r="I114" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J114" s="13" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="K114" s="13" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="28" customHeight="1">
       <c r="A115" s="9" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B115" s="8">
         <v>46122</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>352</v>
+        <v>428</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>195</v>
+        <v>245</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H115" s="8">
         <v>46122</v>
@@ -19939,50 +19943,50 @@
         <v>2</v>
       </c>
       <c r="J115" s="13" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="K115" s="13" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="28" customHeight="1">
       <c r="A116" s="9" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B116" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="C116" s="9" t="s">
         <v>352</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>414</v>
+        <v>195</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="H116" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="I116" s="9">
         <v>2</v>
       </c>
       <c r="J116" s="13" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="K116" s="13" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="28" customHeight="1">
       <c r="A117" s="9" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B117" s="8">
         <v>46115</v>
@@ -19991,16 +19995,16 @@
         <v>352</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>270</v>
+        <v>415</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="H117" s="8">
         <v>46115</v>
@@ -20009,68 +20013,68 @@
         <v>2</v>
       </c>
       <c r="J117" s="13" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="K117" s="13" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="28" customHeight="1">
       <c r="A118" s="9" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B118" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>427</v>
+        <v>352</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>443</v>
+        <v>270</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="H118" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="I118" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J118" s="13" t="s">
-        <v>444</v>
+        <v>690</v>
       </c>
       <c r="K118" s="13" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="28" customHeight="1">
       <c r="A119" s="9" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B119" s="8">
         <v>46111</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>245</v>
+        <v>444</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>130</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="H119" s="8">
         <v>46111</v>
@@ -20079,53 +20083,53 @@
         <v>1</v>
       </c>
       <c r="J119" s="13" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="K119" s="13" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="28" customHeight="1">
       <c r="A120" s="9" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B120" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>37</v>
+        <v>428</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>123</v>
+        <v>245</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="F120" s="9" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="H120" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="I120" s="9">
         <v>1</v>
       </c>
       <c r="J120" s="13" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="K120" s="13" t="s">
-        <v>52</v>
+        <v>449</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="28" customHeight="1">
       <c r="A121" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B121" s="8">
-        <v>45923</v>
+        <v>46080</v>
       </c>
       <c r="C121" s="9" t="s">
         <v>37</v>
@@ -20134,138 +20138,138 @@
         <v>123</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>607</v>
+        <v>628</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="H121" s="8">
-        <v>45923</v>
+        <v>46080</v>
       </c>
       <c r="I121" s="9">
         <v>1</v>
       </c>
       <c r="J121" s="13" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="K121" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="28" customHeight="1">
       <c r="A122" s="9" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B122" s="8">
-        <v>45729</v>
+        <v>45923</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>341</v>
+        <v>123</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H122" s="8">
-        <v>45729</v>
+        <v>45923</v>
       </c>
       <c r="I122" s="9">
         <v>1</v>
       </c>
       <c r="J122" s="13" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="K122" s="13" t="s">
-        <v>456</v>
+        <v>53</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="28" customHeight="1">
       <c r="A123" s="9" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B123" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>123</v>
+        <v>341</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="H123" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="I123" s="9">
         <v>1</v>
       </c>
       <c r="J123" s="13" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="K123" s="13" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="28" customHeight="1">
       <c r="A124" s="9" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B124" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D124" s="9" t="s">
         <v>123</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="H124" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="I124" s="9">
         <v>1</v>
       </c>
       <c r="J124" s="13" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="K124" s="13" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="28" customHeight="1">
       <c r="A125" s="9" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B125" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="C125" s="9" t="s">
         <v>37</v>
@@ -20274,33 +20278,33 @@
         <v>123</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>627</v>
+        <v>608</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="H125" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="I125" s="9">
         <v>1</v>
       </c>
       <c r="J125" s="13" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="K125" s="13" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="28" customHeight="1">
       <c r="A126" s="9" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B126" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="C126" s="9" t="s">
         <v>37</v>
@@ -20309,725 +20313,760 @@
         <v>123</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>607</v>
+        <v>628</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="H126" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="I126" s="9">
         <v>1</v>
       </c>
       <c r="J126" s="13" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K126" s="13" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="28" customHeight="1">
       <c r="A127" s="9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B127" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>472</v>
+        <v>37</v>
       </c>
       <c r="D127" s="9" t="s">
         <v>123</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="H127" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="I127" s="9">
         <v>1</v>
       </c>
       <c r="J127" s="13" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="K127" s="13" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="28" customHeight="1">
       <c r="A128" s="9" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B128" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>486</v>
+        <v>123</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>689</v>
+        <v>608</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="H128" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="I128" s="9">
         <v>1</v>
       </c>
       <c r="J128" s="13" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="K128" s="13" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="28" customHeight="1">
       <c r="A129" s="9" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B129" s="8">
         <v>45190</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>580</v>
+        <v>488</v>
       </c>
       <c r="H129" s="8">
-        <v>45008</v>
+        <v>45190</v>
       </c>
       <c r="I129" s="9">
         <v>1</v>
       </c>
       <c r="J129" s="13" t="s">
-        <v>580</v>
+        <v>488</v>
       </c>
       <c r="K129" s="13" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="28" customHeight="1">
       <c r="A130" s="9" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="B130" s="8">
-        <v>44707</v>
+        <v>45190</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>497</v>
+        <v>484</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>498</v>
+        <v>581</v>
       </c>
       <c r="H130" s="8">
-        <v>44707</v>
+        <v>45008</v>
       </c>
       <c r="I130" s="9">
         <v>1</v>
       </c>
       <c r="J130" s="13" t="s">
-        <v>498</v>
+        <v>581</v>
       </c>
       <c r="K130" s="13" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="28" customHeight="1">
       <c r="A131" s="9" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B131" s="8">
         <v>44707</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>581</v>
+        <v>499</v>
       </c>
       <c r="H131" s="8">
-        <v>44644</v>
+        <v>44707</v>
       </c>
       <c r="I131" s="9">
         <v>1</v>
       </c>
       <c r="J131" s="13" t="s">
-        <v>581</v>
+        <v>499</v>
       </c>
       <c r="K131" s="13" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="28" customHeight="1">
       <c r="A132" s="9" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
       <c r="B132" s="8">
-        <v>44640</v>
+        <v>44707</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="E132" s="9" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="F132" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>508</v>
+        <v>582</v>
       </c>
       <c r="H132" s="8">
-        <v>44734</v>
+        <v>44644</v>
       </c>
       <c r="I132" s="9">
         <v>1</v>
       </c>
       <c r="J132" s="13" t="s">
-        <v>508</v>
+        <v>582</v>
       </c>
       <c r="K132" s="13" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="28" customHeight="1">
       <c r="A133" s="9" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B133" s="8">
         <v>44640</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>582</v>
+        <v>509</v>
       </c>
       <c r="H133" s="8">
-        <v>44643</v>
+        <v>44734</v>
       </c>
       <c r="I133" s="9">
         <v>1</v>
       </c>
       <c r="J133" s="13" t="s">
-        <v>582</v>
+        <v>509</v>
       </c>
       <c r="K133" s="13" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="28" customHeight="1">
       <c r="A134" s="9" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="B134" s="8">
-        <v>44592</v>
+        <v>44640</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
       <c r="E134" s="9" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="F134" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>517</v>
+        <v>583</v>
       </c>
       <c r="H134" s="8">
-        <v>44608</v>
+        <v>44643</v>
       </c>
       <c r="I134" s="9">
         <v>1</v>
       </c>
       <c r="J134" s="13" t="s">
-        <v>517</v>
+        <v>583</v>
       </c>
       <c r="K134" s="13" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="28" customHeight="1">
       <c r="A135" s="9" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="B135" s="8">
-        <v>44579</v>
+        <v>44592</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="H135" s="8">
-        <v>44579</v>
+        <v>44608</v>
       </c>
       <c r="I135" s="9">
         <v>1</v>
       </c>
       <c r="J135" s="13" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="K135" s="13" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="28" customHeight="1">
       <c r="A136" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B136" s="8">
         <v>44579</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E136" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>583</v>
+        <v>528</v>
       </c>
       <c r="H136" s="8">
-        <v>44250</v>
+        <v>44579</v>
       </c>
       <c r="I136" s="9">
         <v>1</v>
       </c>
       <c r="J136" s="13" t="s">
-        <v>583</v>
+        <v>528</v>
       </c>
       <c r="K136" s="13" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="28" customHeight="1">
       <c r="A137" s="9" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="B137" s="8">
-        <v>44166</v>
+        <v>44579</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>535</v>
+        <v>525</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>536</v>
+        <v>584</v>
       </c>
       <c r="H137" s="8">
-        <v>44166</v>
+        <v>44250</v>
       </c>
       <c r="I137" s="9">
         <v>1</v>
       </c>
       <c r="J137" s="13" t="s">
-        <v>536</v>
+        <v>584</v>
       </c>
       <c r="K137" s="13" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="28" customHeight="1">
       <c r="A138" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B138" s="8">
         <v>44166</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E138" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>584</v>
+        <v>537</v>
       </c>
       <c r="H138" s="8">
-        <v>43902</v>
+        <v>44166</v>
       </c>
       <c r="I138" s="9">
         <v>1</v>
       </c>
       <c r="J138" s="13" t="s">
-        <v>584</v>
+        <v>537</v>
       </c>
       <c r="K138" s="13" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="28" customHeight="1">
       <c r="A139" s="9" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="B139" s="8">
-        <v>44131</v>
+        <v>44166</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>544</v>
+        <v>534</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>545</v>
+        <v>585</v>
       </c>
       <c r="H139" s="8">
-        <v>44131</v>
+        <v>43902</v>
       </c>
       <c r="I139" s="9">
         <v>1</v>
       </c>
       <c r="J139" s="13" t="s">
-        <v>545</v>
+        <v>585</v>
       </c>
       <c r="K139" s="13" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="28" customHeight="1">
       <c r="A140" s="9" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B140" s="8">
         <v>44131</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E140" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G140" s="9" t="s">
-        <v>585</v>
+        <v>546</v>
       </c>
       <c r="H140" s="8">
-        <v>43966</v>
+        <v>44131</v>
       </c>
       <c r="I140" s="9">
         <v>1</v>
       </c>
       <c r="J140" s="13" t="s">
-        <v>585</v>
+        <v>546</v>
       </c>
       <c r="K140" s="13" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="28" customHeight="1">
       <c r="A141" s="9" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="B141" s="8">
-        <v>43626</v>
+        <v>44131</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>535</v>
+        <v>543</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>552</v>
+        <v>586</v>
       </c>
       <c r="H141" s="8">
-        <v>43626</v>
+        <v>43966</v>
       </c>
       <c r="I141" s="9">
         <v>1</v>
       </c>
       <c r="J141" s="13" t="s">
-        <v>552</v>
+        <v>586</v>
       </c>
       <c r="K141" s="13" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="28" customHeight="1">
       <c r="A142" s="9" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B142" s="8">
         <v>43626</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G142" s="9" t="s">
-        <v>586</v>
+        <v>553</v>
       </c>
       <c r="H142" s="8">
-        <v>43518</v>
+        <v>43626</v>
       </c>
       <c r="I142" s="9">
         <v>1</v>
       </c>
       <c r="J142" s="13" t="s">
-        <v>586</v>
+        <v>553</v>
       </c>
       <c r="K142" s="13" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="28" customHeight="1">
       <c r="A143" s="9" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="B143" s="8">
-        <v>43401</v>
+        <v>43626</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>561</v>
+        <v>587</v>
       </c>
       <c r="H143" s="8">
-        <v>43401</v>
+        <v>43518</v>
       </c>
       <c r="I143" s="9">
         <v>1</v>
       </c>
       <c r="J143" s="13" t="s">
-        <v>561</v>
+        <v>587</v>
       </c>
       <c r="K143" s="13" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="28" customHeight="1">
       <c r="A144" s="9" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B144" s="8">
         <v>43401</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="E144" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G144" s="9" t="s">
-        <v>587</v>
+        <v>562</v>
       </c>
       <c r="H144" s="8">
-        <v>43215</v>
+        <v>43401</v>
       </c>
       <c r="I144" s="9">
         <v>1</v>
       </c>
       <c r="J144" s="13" t="s">
-        <v>587</v>
+        <v>562</v>
       </c>
       <c r="K144" s="13" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="28" customHeight="1">
       <c r="A145" s="9" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="B145" s="8">
-        <v>42534</v>
+        <v>43401</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>526</v>
+        <v>559</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="H145" s="8">
-        <v>42534</v>
+        <v>43215</v>
       </c>
       <c r="I145" s="9">
         <v>1</v>
       </c>
       <c r="J145" s="13" t="s">
-        <v>568</v>
+        <v>588</v>
       </c>
       <c r="K145" s="13" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="28" customHeight="1">
       <c r="A146" s="9" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B146" s="8">
         <v>42534</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>566</v>
+        <v>527</v>
       </c>
       <c r="E146" s="9" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>101</v>
       </c>
       <c r="G146" s="9" t="s">
-        <v>588</v>
+        <v>569</v>
       </c>
       <c r="H146" s="8">
-        <v>42412</v>
+        <v>42534</v>
       </c>
       <c r="I146" s="9">
         <v>1</v>
       </c>
       <c r="J146" s="13" t="s">
-        <v>588</v>
+        <v>569</v>
       </c>
       <c r="K146" s="13" t="s">
-        <v>569</v>
+        <v>570</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" ht="28" customHeight="1">
+      <c r="A147" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="B147" s="8">
+        <v>42534</v>
+      </c>
+      <c r="C147" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="D147" s="9" t="s">
+        <v>567</v>
+      </c>
+      <c r="E147" s="9" t="s">
+        <v>692</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="G147" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="H147" s="8">
+        <v>42412</v>
+      </c>
+      <c r="I147" s="9">
+        <v>1</v>
+      </c>
+      <c r="J147" s="13" t="s">
+        <v>589</v>
+      </c>
+      <c r="K147" s="13" t="s">
+        <v>570</v>
       </c>
     </row>
   </sheetData>
@@ -21236,9 +21275,9 @@
     <hyperlink ref="J104" r:id="rId196"/>
     <hyperlink ref="G105" r:id="rId197"/>
     <hyperlink ref="J105" r:id="rId198"/>
-    <hyperlink ref="D106" r:id="rId199"/>
-    <hyperlink ref="G106" r:id="rId200"/>
-    <hyperlink ref="J106" r:id="rId201"/>
+    <hyperlink ref="G106" r:id="rId199"/>
+    <hyperlink ref="J106" r:id="rId200"/>
+    <hyperlink ref="D107" r:id="rId201"/>
     <hyperlink ref="G107" r:id="rId202"/>
     <hyperlink ref="J107" r:id="rId203"/>
     <hyperlink ref="G108" r:id="rId204"/>
@@ -21257,9 +21296,9 @@
     <hyperlink ref="J114" r:id="rId217"/>
     <hyperlink ref="G115" r:id="rId218"/>
     <hyperlink ref="J115" r:id="rId219"/>
-    <hyperlink ref="D116" r:id="rId220"/>
-    <hyperlink ref="G116" r:id="rId221"/>
-    <hyperlink ref="J116" r:id="rId222"/>
+    <hyperlink ref="G116" r:id="rId220"/>
+    <hyperlink ref="J116" r:id="rId221"/>
+    <hyperlink ref="D117" r:id="rId222"/>
     <hyperlink ref="G117" r:id="rId223"/>
     <hyperlink ref="J117" r:id="rId224"/>
     <hyperlink ref="G118" r:id="rId225"/>
@@ -21320,10 +21359,12 @@
     <hyperlink ref="J145" r:id="rId280"/>
     <hyperlink ref="G146" r:id="rId281"/>
     <hyperlink ref="J146" r:id="rId282"/>
+    <hyperlink ref="G147" r:id="rId283"/>
+    <hyperlink ref="J147" r:id="rId284"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId283"/>
+    <tablePart r:id="rId285"/>
   </tableParts>
 </worksheet>
 </file>
--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-14 | Build b0e93efa80f7 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-14 | Build 83c8b15fd6ba | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-14 | Build 83c8b15fd6ba | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-15 | Build bdac40313d81 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -2067,7 +2067,8 @@
   </si>
   <si>
     <t>https://bcs-express.ru/novosti-i-analitika/iandeks-odobril-vykup-aktsii-na-50-mlrd-rublei
-https://news.google.com/rss/articles/CBMikwFBVV95cUxPbkRNMVpoTFN4cXlrOWRya3A4SW1Dd09IUHIzMUw3emMzY1hZckpPRWtMclI2aTllZTRQTlRwUmNGNVp4X1hPV041elJSWGhtVS1kM0VGMFpWdmZIcDRmTS04MjBSb3FoVG5xZWdhY0REZkxLMTMxTE1PeF92VW5SRkxDYVNrVGVuNVFTSlRfaFFFeWc?oc=5</t>
+https://news.google.com/rss/articles/CBMikwFBVV95cUxPbkRNMVpoTFN4cXlrOWRya3A4SW1Dd09IUHIzMUw3emMzY1hZckpPRWtMclI2aTllZTRQTlRwUmNGNVp4X1hPV041elJSWGhtVS1kM0VGMFpWdmZIcDRmTS04MjBSb3FoVG5xZWdhY0REZkxLMTMxTE1PeF92VW5SRkxDYVNrVGVuNVFTSlRfaFFFeWc?oc=5
+https://news.google.com/rss/articles/CBMiqgFBVV95cUxPajdyQVZVYm1JZlFyeHU3bG41dUVvZ2M5eTJ3S1pCUTlXazlZYzFDSjJseGR5M3g2ZmhWT2xrczU5bWJTemJyNmhSRWd1ejAtQm9NcUlDUlhwcjgwbUpFQ2czbjgxX3MxVHhZYlVnUzRjNE9XZnk1LWY0T0tKcDRzOUx1LXNNUEsyOTJ2NWxLajRpenRTM0ZNaHJEemI1aGFyeGQxLVFDREY2Zw?oc=5</t>
   </si>
   <si>
     <t>https://sbercib.ru/publication/rezultati-ozon-dom-rf-dividendi-yandeksa-i-tatnefti-i-drugie-novosti-nedeli
@@ -19639,7 +19640,7 @@
         <v>46147</v>
       </c>
       <c r="I99" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J99" s="13" t="s">
         <v>673</v>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-15 | Build 9aa25a019b95 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-15 | Build 58355f2d6f53 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-15 | Build 58355f2d6f53 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-16 | Build f1789f9b9163 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-16 | Build f1789f9b9163 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-16 | Build 486623b5df39 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-16 | Build f987e52b5b89 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-16 | Build 7433d4b88b95 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-16 | Build 7433d4b88b95 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-16 | Build b7233620e3c0 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-16 | Build b7233620e3c0 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-16 | Build e7804f451064 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5501" uniqueCount="766">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5511" uniqueCount="768">
   <si>
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-17 | Build a88b0b4ba423 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-17 | Build 953af017702e | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -2212,6 +2212,12 @@
     <t>https://bcs-express.ru/novosti-i-analitika/aktsionery-ozon-utverdili-final-nye-dividendy-za-2025
 https://news.google.com/rss/articles/CBMinAFBVV95cUxPUDczZmMzcGh0VmlVbnducmFDWkNiamxLVDdCT29PQXVGSkRDeFN4MGFNbzJFNHo4UlZ6Qjk1bUFXaXJVUDdENXZ4a1ctNWRzcVRiZlE4R19uTXhkNndrc09VaUpfa3R4NkdWM1A2NEdETXdwOUpYeDVLLWF1VHNvNURIUXg0NlRaRVpsTDliNFNjbGlicG9VbWVMaEQ?oc=5
 https://news.google.com/rss/articles/CBMiswFBVV95cUxPWE5xZlBVejF3U1RNV1VHa3hMS2o4eDduOV96LURuZ0JyOE1IRmxhbWNHcDRqR1JKU1Jhc2NIdWdLQTRwdGFJYkxsZlJhcGN1aHNsWWE5STZRX1VEdHhIS1ZTSmxualNXWExYanFGTV9rQmNEYkxBSm45Q1BlbE54emxVTUgyMndoOFpOMEcyUndhWWo3UlBpcXZPREU1cGhMSE9jQ3Q3UGJlSEk5Q1pBUXVhQQ?oc=5</t>
+  </si>
+  <si>
+    <t>Forbes.ru</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPa0plUGNITkFCM0xWY2VENEFjWm5Vc2xldnRMa0hmVDVKT2Rmbmtsa1ZMclNLNS15THZUWVdZNE82MGJYRWhnVG9obWQwblk3SER2blVOcHg4OGx2Q1FVNDhZMnlISWZQTFo5Rk5vM2pVWGdmdkxUX016cW9qLUswRmJya1BsWUlVLVRyTk5PUjRibDJ6ajBfemRERno?oc=5</t>
   </si>
   <si>
     <t>https://www.finam.ru/publications/item/otchetnosti-zaymera-bsp-i-sovkombanka-dividendnyy-vopros-u-ozona-i-md-medikal-osnovnye-sobytiya-15-maya-20260515-0900/
@@ -2644,8 +2650,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:K160" totalsRowShown="0">
-  <autoFilter ref="A6:K160"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:K161" totalsRowShown="0">
+  <autoFilter ref="A6:K161"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Deal ID"/>
     <tableColumn id="2" name="Date"/>
@@ -11277,7 +11283,7 @@
         <v>105</v>
       </c>
       <c r="AQ85" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR85" s="9" t="s">
         <v>321</v>
@@ -17492,7 +17498,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R160"/>
+  <dimension ref="A1:R161"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -17555,7 +17561,7 @@
     </row>
     <row r="4" spans="1:18">
       <c r="M4" s="3" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -17598,19 +17604,19 @@
         <v>30</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>23</v>
@@ -17649,7 +17655,7 @@
         <v>108</v>
       </c>
       <c r="M7" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -17700,7 +17706,7 @@
         <v>114</v>
       </c>
       <c r="M8" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -17751,7 +17757,7 @@
         <v>118</v>
       </c>
       <c r="M9" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -17804,7 +17810,7 @@
         <v>125</v>
       </c>
       <c r="M10" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -17855,7 +17861,7 @@
         <v>131</v>
       </c>
       <c r="M11" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -17906,7 +17912,7 @@
         <v>131</v>
       </c>
       <c r="M12" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -17957,7 +17963,7 @@
         <v>137</v>
       </c>
       <c r="M13" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -18008,7 +18014,7 @@
         <v>142</v>
       </c>
       <c r="M14" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -18092,7 +18098,7 @@
         <v>151</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -21173,51 +21179,49 @@
     </row>
     <row r="106" spans="1:11" ht="28" customHeight="1">
       <c r="A106" s="9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B106" s="8">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="C106" s="9" t="s">
         <v>402</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>296</v>
+        <v>720</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="H106" s="8">
-        <v>46157</v>
-      </c>
+        <v>721</v>
+      </c>
+      <c r="H106" s="9"/>
       <c r="I106" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J106" s="13" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="K106" s="13" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="28" customHeight="1">
       <c r="A107" s="9" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B107" s="8">
         <v>46157</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>34</v>
+        <v>402</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>396</v>
+        <v>296</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>655</v>
@@ -21226,30 +21230,30 @@
         <v>105</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="H107" s="8">
         <v>46157</v>
       </c>
       <c r="I107" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J107" s="13" t="s">
-        <v>424</v>
+        <v>722</v>
       </c>
       <c r="K107" s="13" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="28" customHeight="1">
       <c r="A108" s="9" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B108" s="8">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>427</v>
+        <v>34</v>
       </c>
       <c r="D108" s="9" t="s">
         <v>396</v>
@@ -21261,101 +21265,101 @@
         <v>105</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="H108" s="8">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="I108" s="9">
         <v>1</v>
       </c>
       <c r="J108" s="13" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="K108" s="13" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="28" customHeight="1">
       <c r="A109" s="9" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B109" s="8">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>34</v>
+        <v>427</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>431</v>
+        <v>396</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="H109" s="9"/>
+        <v>428</v>
+      </c>
+      <c r="H109" s="8">
+        <v>46150</v>
+      </c>
       <c r="I109" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J109" s="13" t="s">
-        <v>721</v>
+        <v>428</v>
       </c>
       <c r="K109" s="13" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="28" customHeight="1">
       <c r="A110" s="9" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B110" s="8">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>321</v>
+        <v>431</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="H110" s="8">
-        <v>46147</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="H110" s="9"/>
       <c r="I110" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J110" s="13" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="K110" s="13" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="28" customHeight="1">
       <c r="A111" s="9" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B111" s="8">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C111" s="9" t="s">
         <v>48</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>439</v>
+        <v>321</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>655</v>
@@ -21364,33 +21368,33 @@
         <v>105</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="H111" s="8">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="I111" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J111" s="13" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="K111" s="13" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="28" customHeight="1">
       <c r="A112" s="9" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B112" s="8">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>135</v>
+        <v>439</v>
       </c>
       <c r="E112" s="9" t="s">
         <v>655</v>
@@ -21399,24 +21403,24 @@
         <v>105</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H112" s="8">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="I112" s="9">
         <v>2</v>
       </c>
       <c r="J112" s="13" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="K112" s="13" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="28" customHeight="1">
       <c r="A113" s="9" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B113" s="8">
         <v>46139</v>
@@ -21425,7 +21429,7 @@
         <v>34</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>321</v>
+        <v>135</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>655</v>
@@ -21434,24 +21438,24 @@
         <v>105</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H113" s="8">
         <v>46139</v>
       </c>
       <c r="I113" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J113" s="13" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="K113" s="13" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="28" customHeight="1">
       <c r="A114" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B114" s="8">
         <v>46139</v>
@@ -21460,7 +21464,7 @@
         <v>34</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>449</v>
+        <v>321</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>655</v>
@@ -21469,19 +21473,19 @@
         <v>105</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="H114" s="8">
         <v>46139</v>
       </c>
       <c r="I114" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J114" s="13" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="K114" s="13" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="28" customHeight="1">
@@ -21495,7 +21499,7 @@
         <v>34</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>149</v>
+        <v>449</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>655</v>
@@ -21504,7 +21508,7 @@
         <v>105</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>727</v>
+        <v>450</v>
       </c>
       <c r="H115" s="8">
         <v>46139</v>
@@ -21530,20 +21534,22 @@
         <v>34</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>729</v>
+        <v>149</v>
       </c>
       <c r="E116" s="9" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F116" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>730</v>
-      </c>
-      <c r="H116" s="9"/>
+        <v>729</v>
+      </c>
+      <c r="H116" s="8">
+        <v>46139</v>
+      </c>
       <c r="I116" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J116" s="13" t="s">
         <v>730</v>
@@ -21554,7 +21560,7 @@
     </row>
     <row r="117" spans="1:11" ht="28" customHeight="1">
       <c r="A117" s="9" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B117" s="8">
         <v>46139</v>
@@ -21563,33 +21569,31 @@
         <v>34</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>453</v>
+        <v>731</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="H117" s="8">
-        <v>46139</v>
-      </c>
+        <v>732</v>
+      </c>
+      <c r="H117" s="9"/>
       <c r="I117" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J117" s="13" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="K117" s="13" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="28" customHeight="1">
       <c r="A118" s="9" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B118" s="8">
         <v>46139</v>
@@ -21598,7 +21602,7 @@
         <v>34</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E118" s="9" t="s">
         <v>655</v>
@@ -21607,7 +21611,7 @@
         <v>105</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H118" s="8">
         <v>46139</v>
@@ -21616,24 +21620,24 @@
         <v>2</v>
       </c>
       <c r="J118" s="13" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="K118" s="13" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="28" customHeight="1">
       <c r="A119" s="9" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B119" s="8">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>402</v>
+        <v>34</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>247</v>
+        <v>457</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>655</v>
@@ -21642,33 +21646,33 @@
         <v>105</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="H119" s="8">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="I119" s="9">
         <v>2</v>
       </c>
       <c r="J119" s="13" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="K119" s="13" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="28" customHeight="1">
       <c r="A120" s="9" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B120" s="8">
         <v>46132</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>48</v>
+        <v>402</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>464</v>
+        <v>247</v>
       </c>
       <c r="E120" s="9" t="s">
         <v>655</v>
@@ -21677,7 +21681,7 @@
         <v>105</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="H120" s="8">
         <v>46132</v>
@@ -21686,10 +21690,10 @@
         <v>2</v>
       </c>
       <c r="J120" s="13" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="K120" s="13" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="28" customHeight="1">
@@ -21703,23 +21707,25 @@
         <v>48</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>116</v>
+        <v>464</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="H121" s="9"/>
+        <v>465</v>
+      </c>
+      <c r="H121" s="8">
+        <v>46132</v>
+      </c>
       <c r="I121" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J121" s="13" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="K121" s="13" t="s">
         <v>466</v>
@@ -21727,7 +21733,7 @@
     </row>
     <row r="122" spans="1:11" ht="28" customHeight="1">
       <c r="A122" s="9" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B122" s="8">
         <v>46132</v>
@@ -21736,96 +21742,94 @@
         <v>48</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>468</v>
+        <v>116</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="H122" s="8">
-        <v>46132</v>
-      </c>
+        <v>737</v>
+      </c>
+      <c r="H122" s="9"/>
       <c r="I122" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J122" s="13" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="K122" s="13" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="28" customHeight="1">
       <c r="A123" s="9" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B123" s="8">
         <v>46132</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>402</v>
+        <v>48</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="H123" s="9"/>
+        <v>469</v>
+      </c>
+      <c r="H123" s="8">
+        <v>46132</v>
+      </c>
       <c r="I123" s="9">
         <v>2</v>
       </c>
       <c r="J123" s="13" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="K123" s="13" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="28" customHeight="1">
       <c r="A124" s="9" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B124" s="8">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>476</v>
+        <v>402</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="H124" s="8">
-        <v>46128</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="H124" s="9"/>
       <c r="I124" s="9">
         <v>2</v>
       </c>
       <c r="J124" s="13" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="K124" s="13" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="28" customHeight="1">
@@ -21839,7 +21843,7 @@
         <v>476</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>135</v>
+        <v>468</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>655</v>
@@ -21848,7 +21852,7 @@
         <v>105</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>739</v>
+        <v>478</v>
       </c>
       <c r="H125" s="8">
         <v>46128</v>
@@ -21874,7 +21878,7 @@
         <v>476</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>741</v>
+        <v>135</v>
       </c>
       <c r="E126" s="9" t="s">
         <v>655</v>
@@ -21883,7 +21887,7 @@
         <v>105</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H126" s="8">
         <v>46128</v>
@@ -21892,7 +21896,7 @@
         <v>2</v>
       </c>
       <c r="J126" s="13" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="K126" s="13" t="s">
         <v>479</v>
@@ -21909,10 +21913,10 @@
         <v>476</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>493</v>
+        <v>743</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>105</v>
@@ -21920,12 +21924,14 @@
       <c r="G127" s="9" t="s">
         <v>744</v>
       </c>
-      <c r="H127" s="9"/>
+      <c r="H127" s="8">
+        <v>46128</v>
+      </c>
       <c r="I127" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J127" s="13" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="K127" s="13" t="s">
         <v>479</v>
@@ -21933,51 +21939,49 @@
     </row>
     <row r="128" spans="1:11" ht="28" customHeight="1">
       <c r="A128" s="9" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B128" s="8">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="C128" s="9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>296</v>
+        <v>493</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="H128" s="8">
-        <v>46122</v>
-      </c>
+        <v>746</v>
+      </c>
+      <c r="H128" s="9"/>
       <c r="I128" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J128" s="13" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="K128" s="13" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="129" spans="1:11" ht="28" customHeight="1">
       <c r="A129" s="9" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B129" s="8">
         <v>46122</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>402</v>
+        <v>477</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>655</v>
@@ -21986,7 +21990,7 @@
         <v>105</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="H129" s="8">
         <v>46122</v>
@@ -21995,24 +21999,24 @@
         <v>2</v>
       </c>
       <c r="J129" s="13" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="K129" s="13" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="28" customHeight="1">
       <c r="A130" s="9" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B130" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="C130" s="9" t="s">
         <v>402</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>464</v>
+        <v>247</v>
       </c>
       <c r="E130" s="9" t="s">
         <v>655</v>
@@ -22021,24 +22025,24 @@
         <v>105</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H130" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="I130" s="9">
         <v>2</v>
       </c>
       <c r="J130" s="13" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="K130" s="13" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="28" customHeight="1">
       <c r="A131" s="9" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B131" s="8">
         <v>46115</v>
@@ -22047,7 +22051,7 @@
         <v>402</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>321</v>
+        <v>464</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>655</v>
@@ -22056,7 +22060,7 @@
         <v>105</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="H131" s="8">
         <v>46115</v>
@@ -22065,24 +22069,24 @@
         <v>2</v>
       </c>
       <c r="J131" s="13" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="K131" s="13" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="28" customHeight="1">
       <c r="A132" s="9" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B132" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>477</v>
+        <v>402</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>493</v>
+        <v>321</v>
       </c>
       <c r="E132" s="9" t="s">
         <v>655</v>
@@ -22091,24 +22095,24 @@
         <v>105</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H132" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="I132" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J132" s="13" t="s">
-        <v>494</v>
+        <v>750</v>
       </c>
       <c r="K132" s="13" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="28" customHeight="1">
       <c r="A133" s="9" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B133" s="8">
         <v>46111</v>
@@ -22117,7 +22121,7 @@
         <v>477</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>296</v>
+        <v>493</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>655</v>
@@ -22126,7 +22130,7 @@
         <v>105</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="H133" s="8">
         <v>46111</v>
@@ -22135,53 +22139,53 @@
         <v>1</v>
       </c>
       <c r="J133" s="13" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="K133" s="13" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="28" customHeight="1">
       <c r="A134" s="9" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B134" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="C134" s="9" t="s">
-        <v>41</v>
+        <v>477</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>185</v>
+        <v>296</v>
       </c>
       <c r="E134" s="9" t="s">
         <v>655</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="H134" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="I134" s="9">
         <v>1</v>
       </c>
       <c r="J134" s="13" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K134" s="13" t="s">
-        <v>54</v>
+        <v>498</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="28" customHeight="1">
       <c r="A135" s="9" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B135" s="8">
-        <v>45923</v>
+        <v>46080</v>
       </c>
       <c r="C135" s="9" t="s">
         <v>41</v>
@@ -22190,39 +22194,39 @@
         <v>185</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H135" s="8">
-        <v>45923</v>
+        <v>46080</v>
       </c>
       <c r="I135" s="9">
         <v>1</v>
       </c>
       <c r="J135" s="13" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="K135" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="28" customHeight="1">
       <c r="A136" s="9" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B136" s="8">
-        <v>45729</v>
+        <v>45923</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>391</v>
+        <v>185</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>669</v>
@@ -22231,33 +22235,33 @@
         <v>122</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H136" s="8">
-        <v>45729</v>
+        <v>45923</v>
       </c>
       <c r="I136" s="9">
         <v>1</v>
       </c>
       <c r="J136" s="13" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K136" s="13" t="s">
-        <v>506</v>
+        <v>55</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="28" customHeight="1">
       <c r="A137" s="9" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B137" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>185</v>
+        <v>391</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>669</v>
@@ -22266,30 +22270,30 @@
         <v>122</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H137" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="I137" s="9">
         <v>1</v>
       </c>
       <c r="J137" s="13" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="K137" s="13" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="28" customHeight="1">
       <c r="A138" s="9" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B138" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D138" s="9" t="s">
         <v>185</v>
@@ -22301,27 +22305,27 @@
         <v>122</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="H138" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="I138" s="9">
         <v>1</v>
       </c>
       <c r="J138" s="13" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="K138" s="13" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="28" customHeight="1">
       <c r="A139" s="9" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B139" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="C139" s="9" t="s">
         <v>41</v>
@@ -22330,33 +22334,33 @@
         <v>185</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>655</v>
+        <v>669</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="H139" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="I139" s="9">
         <v>1</v>
       </c>
       <c r="J139" s="13" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="K139" s="13" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="28" customHeight="1">
       <c r="A140" s="9" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B140" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="C140" s="9" t="s">
         <v>41</v>
@@ -22365,36 +22369,36 @@
         <v>185</v>
       </c>
       <c r="E140" s="9" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G140" s="9" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="H140" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="I140" s="9">
         <v>1</v>
       </c>
       <c r="J140" s="13" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="K140" s="13" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="28" customHeight="1">
       <c r="A141" s="9" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B141" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>522</v>
+        <v>41</v>
       </c>
       <c r="D141" s="9" t="s">
         <v>185</v>
@@ -22406,54 +22410,54 @@
         <v>122</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="H141" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="I141" s="9">
         <v>1</v>
       </c>
       <c r="J141" s="13" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="K141" s="13" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="28" customHeight="1">
       <c r="A142" s="9" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B142" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>536</v>
+        <v>185</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>749</v>
+        <v>669</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G142" s="9" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="H142" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="I142" s="9">
         <v>1</v>
       </c>
       <c r="J142" s="13" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="K142" s="13" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="28" customHeight="1">
@@ -22467,25 +22471,25 @@
         <v>527</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>630</v>
+        <v>537</v>
       </c>
       <c r="H143" s="8">
-        <v>45008</v>
+        <v>45190</v>
       </c>
       <c r="I143" s="9">
         <v>1</v>
       </c>
       <c r="J143" s="13" t="s">
-        <v>630</v>
+        <v>537</v>
       </c>
       <c r="K143" s="13" t="s">
         <v>538</v>
@@ -22493,37 +22497,37 @@
     </row>
     <row r="144" spans="1:11" ht="28" customHeight="1">
       <c r="A144" s="9" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="B144" s="8">
-        <v>44707</v>
+        <v>45190</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="E144" s="9" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="F144" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G144" s="9" t="s">
-        <v>548</v>
+        <v>630</v>
       </c>
       <c r="H144" s="8">
-        <v>44707</v>
+        <v>45008</v>
       </c>
       <c r="I144" s="9">
         <v>1</v>
       </c>
       <c r="J144" s="13" t="s">
-        <v>548</v>
+        <v>630</v>
       </c>
       <c r="K144" s="13" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="28" customHeight="1">
@@ -22537,25 +22541,25 @@
         <v>540</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>631</v>
+        <v>548</v>
       </c>
       <c r="H145" s="8">
-        <v>44644</v>
+        <v>44707</v>
       </c>
       <c r="I145" s="9">
         <v>1</v>
       </c>
       <c r="J145" s="13" t="s">
-        <v>631</v>
+        <v>548</v>
       </c>
       <c r="K145" s="13" t="s">
         <v>549</v>
@@ -22563,37 +22567,37 @@
     </row>
     <row r="146" spans="1:11" ht="28" customHeight="1">
       <c r="A146" s="9" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="B146" s="8">
-        <v>44640</v>
+        <v>44707</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="E146" s="9" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="F146" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G146" s="9" t="s">
-        <v>558</v>
+        <v>631</v>
       </c>
       <c r="H146" s="8">
-        <v>44734</v>
+        <v>44644</v>
       </c>
       <c r="I146" s="9">
         <v>1</v>
       </c>
       <c r="J146" s="13" t="s">
-        <v>558</v>
+        <v>631</v>
       </c>
       <c r="K146" s="13" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="28" customHeight="1">
@@ -22607,25 +22611,25 @@
         <v>551</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>632</v>
+        <v>558</v>
       </c>
       <c r="H147" s="8">
-        <v>44643</v>
+        <v>44734</v>
       </c>
       <c r="I147" s="9">
         <v>1</v>
       </c>
       <c r="J147" s="13" t="s">
-        <v>632</v>
+        <v>558</v>
       </c>
       <c r="K147" s="13" t="s">
         <v>559</v>
@@ -22633,72 +22637,72 @@
     </row>
     <row r="148" spans="1:11" ht="28" customHeight="1">
       <c r="A148" s="9" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="B148" s="8">
-        <v>44592</v>
+        <v>44640</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="E148" s="9" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="F148" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G148" s="9" t="s">
-        <v>567</v>
+        <v>632</v>
       </c>
       <c r="H148" s="8">
-        <v>44608</v>
+        <v>44643</v>
       </c>
       <c r="I148" s="9">
         <v>1</v>
       </c>
       <c r="J148" s="13" t="s">
-        <v>567</v>
+        <v>632</v>
       </c>
       <c r="K148" s="13" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="28" customHeight="1">
       <c r="A149" s="9" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="B149" s="8">
-        <v>44579</v>
+        <v>44592</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="H149" s="8">
-        <v>44579</v>
+        <v>44608</v>
       </c>
       <c r="I149" s="9">
         <v>1</v>
       </c>
       <c r="J149" s="13" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="K149" s="13" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="28" customHeight="1">
@@ -22712,25 +22716,25 @@
         <v>570</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E150" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G150" s="9" t="s">
-        <v>633</v>
+        <v>577</v>
       </c>
       <c r="H150" s="8">
-        <v>44250</v>
+        <v>44579</v>
       </c>
       <c r="I150" s="9">
         <v>1</v>
       </c>
       <c r="J150" s="13" t="s">
-        <v>633</v>
+        <v>577</v>
       </c>
       <c r="K150" s="13" t="s">
         <v>578</v>
@@ -22738,37 +22742,37 @@
     </row>
     <row r="151" spans="1:11" ht="28" customHeight="1">
       <c r="A151" s="9" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="B151" s="8">
-        <v>44166</v>
+        <v>44579</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="H151" s="8">
-        <v>44166</v>
+        <v>44250</v>
       </c>
       <c r="I151" s="9">
         <v>1</v>
       </c>
       <c r="J151" s="13" t="s">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="K151" s="13" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="28" customHeight="1">
@@ -22782,25 +22786,25 @@
         <v>580</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E152" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G152" s="9" t="s">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="H152" s="8">
-        <v>43902</v>
+        <v>44166</v>
       </c>
       <c r="I152" s="9">
         <v>1</v>
       </c>
       <c r="J152" s="13" t="s">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="K152" s="13" t="s">
         <v>587</v>
@@ -22808,37 +22812,37 @@
     </row>
     <row r="153" spans="1:11" ht="28" customHeight="1">
       <c r="A153" s="9" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="B153" s="8">
-        <v>44131</v>
+        <v>44166</v>
       </c>
       <c r="C153" s="9" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>595</v>
+        <v>634</v>
       </c>
       <c r="H153" s="8">
-        <v>44131</v>
+        <v>43902</v>
       </c>
       <c r="I153" s="9">
         <v>1</v>
       </c>
       <c r="J153" s="13" t="s">
-        <v>595</v>
+        <v>634</v>
       </c>
       <c r="K153" s="13" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="28" customHeight="1">
@@ -22852,25 +22856,25 @@
         <v>589</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E154" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G154" s="9" t="s">
-        <v>635</v>
+        <v>595</v>
       </c>
       <c r="H154" s="8">
-        <v>43966</v>
+        <v>44131</v>
       </c>
       <c r="I154" s="9">
         <v>1</v>
       </c>
       <c r="J154" s="13" t="s">
-        <v>635</v>
+        <v>595</v>
       </c>
       <c r="K154" s="13" t="s">
         <v>596</v>
@@ -22878,37 +22882,37 @@
     </row>
     <row r="155" spans="1:11" ht="28" customHeight="1">
       <c r="A155" s="9" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="B155" s="8">
-        <v>43626</v>
+        <v>44131</v>
       </c>
       <c r="C155" s="9" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>602</v>
+        <v>635</v>
       </c>
       <c r="H155" s="8">
-        <v>43626</v>
+        <v>43966</v>
       </c>
       <c r="I155" s="9">
         <v>1</v>
       </c>
       <c r="J155" s="13" t="s">
-        <v>602</v>
+        <v>635</v>
       </c>
       <c r="K155" s="13" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="28" customHeight="1">
@@ -22922,25 +22926,25 @@
         <v>598</v>
       </c>
       <c r="D156" s="9" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="E156" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G156" s="9" t="s">
-        <v>636</v>
+        <v>602</v>
       </c>
       <c r="H156" s="8">
-        <v>43518</v>
+        <v>43626</v>
       </c>
       <c r="I156" s="9">
         <v>1</v>
       </c>
       <c r="J156" s="13" t="s">
-        <v>636</v>
+        <v>602</v>
       </c>
       <c r="K156" s="13" t="s">
         <v>603</v>
@@ -22948,37 +22952,37 @@
     </row>
     <row r="157" spans="1:11" ht="28" customHeight="1">
       <c r="A157" s="9" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="B157" s="8">
-        <v>43401</v>
+        <v>43626</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="D157" s="9" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="H157" s="8">
-        <v>43401</v>
+        <v>43518</v>
       </c>
       <c r="I157" s="9">
         <v>1</v>
       </c>
       <c r="J157" s="13" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="K157" s="13" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="28" customHeight="1">
@@ -22992,25 +22996,25 @@
         <v>605</v>
       </c>
       <c r="D158" s="9" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E158" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G158" s="9" t="s">
-        <v>637</v>
+        <v>611</v>
       </c>
       <c r="H158" s="8">
-        <v>43215</v>
+        <v>43401</v>
       </c>
       <c r="I158" s="9">
         <v>1</v>
       </c>
       <c r="J158" s="13" t="s">
-        <v>637</v>
+        <v>611</v>
       </c>
       <c r="K158" s="13" t="s">
         <v>612</v>
@@ -23018,37 +23022,37 @@
     </row>
     <row r="159" spans="1:11" ht="28" customHeight="1">
       <c r="A159" s="9" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="B159" s="8">
-        <v>42534</v>
+        <v>43401</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="D159" s="9" t="s">
-        <v>576</v>
+        <v>608</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>618</v>
+        <v>637</v>
       </c>
       <c r="H159" s="8">
-        <v>42534</v>
+        <v>43215</v>
       </c>
       <c r="I159" s="9">
         <v>1</v>
       </c>
       <c r="J159" s="13" t="s">
-        <v>618</v>
+        <v>637</v>
       </c>
       <c r="K159" s="13" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="28" customHeight="1">
@@ -23062,27 +23066,62 @@
         <v>614</v>
       </c>
       <c r="D160" s="9" t="s">
-        <v>616</v>
+        <v>576</v>
       </c>
       <c r="E160" s="9" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G160" s="9" t="s">
-        <v>638</v>
+        <v>618</v>
       </c>
       <c r="H160" s="8">
-        <v>42412</v>
+        <v>42534</v>
       </c>
       <c r="I160" s="9">
         <v>1</v>
       </c>
       <c r="J160" s="13" t="s">
+        <v>618</v>
+      </c>
+      <c r="K160" s="13" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" ht="28" customHeight="1">
+      <c r="A161" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="B161" s="8">
+        <v>42534</v>
+      </c>
+      <c r="C161" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="D161" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="E161" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="F161" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G161" s="9" t="s">
         <v>638</v>
       </c>
-      <c r="K160" s="13" t="s">
+      <c r="H161" s="8">
+        <v>42412</v>
+      </c>
+      <c r="I161" s="9">
+        <v>1</v>
+      </c>
+      <c r="J161" s="13" t="s">
+        <v>638</v>
+      </c>
+      <c r="K161" s="13" t="s">
         <v>619</v>
       </c>
     </row>
@@ -23320,9 +23359,9 @@
     <hyperlink ref="J118" r:id="rId224"/>
     <hyperlink ref="G119" r:id="rId225"/>
     <hyperlink ref="J119" r:id="rId226"/>
-    <hyperlink ref="D120" r:id="rId227"/>
-    <hyperlink ref="G120" r:id="rId228"/>
-    <hyperlink ref="J120" r:id="rId229"/>
+    <hyperlink ref="G120" r:id="rId227"/>
+    <hyperlink ref="J120" r:id="rId228"/>
+    <hyperlink ref="D121" r:id="rId229"/>
     <hyperlink ref="G121" r:id="rId230"/>
     <hyperlink ref="J121" r:id="rId231"/>
     <hyperlink ref="G122" r:id="rId232"/>
@@ -23341,9 +23380,9 @@
     <hyperlink ref="J128" r:id="rId245"/>
     <hyperlink ref="G129" r:id="rId246"/>
     <hyperlink ref="J129" r:id="rId247"/>
-    <hyperlink ref="D130" r:id="rId248"/>
-    <hyperlink ref="G130" r:id="rId249"/>
-    <hyperlink ref="J130" r:id="rId250"/>
+    <hyperlink ref="G130" r:id="rId248"/>
+    <hyperlink ref="J130" r:id="rId249"/>
+    <hyperlink ref="D131" r:id="rId250"/>
     <hyperlink ref="G131" r:id="rId251"/>
     <hyperlink ref="J131" r:id="rId252"/>
     <hyperlink ref="G132" r:id="rId253"/>
@@ -23404,10 +23443,12 @@
     <hyperlink ref="J159" r:id="rId308"/>
     <hyperlink ref="G160" r:id="rId309"/>
     <hyperlink ref="J160" r:id="rId310"/>
+    <hyperlink ref="G161" r:id="rId311"/>
+    <hyperlink ref="J161" r:id="rId312"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId311"/>
+    <tablePart r:id="rId313"/>
   </tableParts>
 </worksheet>
 </file>
--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5511" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5521" uniqueCount="769">
   <si>
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-17 | Build 953af017702e | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-17 | Build c09294a8cb0d | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -2014,6 +2014,9 @@
   </si>
   <si>
     <t>https://news.google.com/rss/articles/CBMi2gFBVV95cUxNMEV2NGVDZFdXcWt5VDJaTGNBWlNXeTFZdkc0STZoT1JqY0l6MzdGRWMtZXdleEREWjJpQVp2dklQT3dYUUU4SlYtamRpR1RZSkJQX0lBbUM2bFMydjFUei13dVVCY3dyOHdPTW03cTcwY0xDRTgwNTN3TUgyb2M0dXVlT1hhQmViV21UcEJDUWdyb0pIOTdMRk5YY0U1ZXI5a2pOUk1sdm5DVHhWT0lZUEE2a3h6WDdfeUFKUVkzb0FEYUZQRXZyc1NjQUFxS3N1WWVYRjRqWDZTZ9IB3wFBVV95cUxNWENRSTNJX29iYzdUYmFqaC1pSS1hREl6WGlYTEdrN0MwYXphc2tQbmlpMXlKajBGdmhUUW1aUXR6Ylo1alphMHAxNUY4YzBHZnFoOWp1bUVsbkhsbko0eHZtRUZkaDBaelNuMGc2amFMYmtBa2wySGVoODRFUTB1SThiaFFWV1lYODFhS2VDQ0FVV2tVbk1WajgwaGgwaXRrLUdTazJUTGl3U0U1MUtweGdIMHVLVGN5TFE1b3dxdUU4eXlzcTU5eTBHN2kzckV2cGMtMzloSUZ3VmNac3RR?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTFBOYVFhZzFTYUZyRUI3U3lnOUdiREdCYTNlY0NvVEJZYzdwYnRVaUZmUjd4ZWFfdWV2b2V0a3hUbXFLd3hKYnZGbmI1eWtEQ1BDTjJNS2ZIZHctRTkx?oc=5</t>
   </si>
   <si>
     <t>https://www.vedomosti.ru/investments/news/2026/07/15/1213753-v-gazprombanke-nazvali-potentsial
@@ -2650,8 +2653,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:K161" totalsRowShown="0">
-  <autoFilter ref="A6:K161"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:K162" totalsRowShown="0">
+  <autoFilter ref="A6:K162"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Deal ID"/>
     <tableColumn id="2" name="Date"/>
@@ -4178,7 +4181,7 @@
         <v>105</v>
       </c>
       <c r="AQ11" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR11" s="9" t="s">
         <v>129</v>
@@ -17498,7 +17501,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R161"/>
+  <dimension ref="A1:R162"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -17561,7 +17564,7 @@
     </row>
     <row r="4" spans="1:18">
       <c r="M4" s="3" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -17604,19 +17607,19 @@
         <v>30</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>23</v>
@@ -17655,7 +17658,7 @@
         <v>108</v>
       </c>
       <c r="M7" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -17706,7 +17709,7 @@
         <v>114</v>
       </c>
       <c r="M8" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -17757,7 +17760,7 @@
         <v>118</v>
       </c>
       <c r="M9" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -17810,7 +17813,7 @@
         <v>125</v>
       </c>
       <c r="M10" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -17861,7 +17864,7 @@
         <v>131</v>
       </c>
       <c r="M11" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -17912,7 +17915,7 @@
         <v>131</v>
       </c>
       <c r="M12" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -17932,16 +17935,16 @@
     </row>
     <row r="13" spans="1:18" ht="28" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B13" s="8">
         <v>46218</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>657</v>
@@ -17950,20 +17953,20 @@
         <v>105</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>136</v>
+        <v>664</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" s="13" t="s">
         <v>664</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="M13" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -17983,13 +17986,13 @@
     </row>
     <row r="14" spans="1:18" ht="28" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B14" s="8">
         <v>46218</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>135</v>
@@ -18001,7 +18004,7 @@
         <v>105</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="9">
@@ -18011,10 +18014,10 @@
         <v>665</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M14" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -18034,16 +18037,16 @@
     </row>
     <row r="15" spans="1:18" ht="28" customHeight="1">
       <c r="A15" s="9" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B15" s="8">
         <v>46218</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>657</v>
@@ -18052,31 +18055,31 @@
         <v>105</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>145</v>
+        <v>666</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="28" customHeight="1">
       <c r="A16" s="9" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B16" s="8">
         <v>46218</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>148</v>
+        <v>34</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>657</v>
@@ -18085,20 +18088,20 @@
         <v>105</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>666</v>
+        <v>145</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -18110,16 +18113,16 @@
     </row>
     <row r="17" spans="1:11" ht="28" customHeight="1">
       <c r="A17" s="9" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B17" s="8">
         <v>46218</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>657</v>
@@ -18128,7 +18131,7 @@
         <v>105</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="9">
@@ -18138,53 +18141,51 @@
         <v>667</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="28" customHeight="1">
       <c r="A18" s="9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B18" s="8">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="H18" s="8">
-        <v>46217</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="H18" s="9"/>
       <c r="I18" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>158</v>
+        <v>668</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>36</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="28" customHeight="1">
       <c r="A19" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B19" s="8">
         <v>46217</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="D19" s="9" t="s">
         <v>123</v>
@@ -18196,7 +18197,7 @@
         <v>122</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="H19" s="8">
         <v>46217</v>
@@ -18205,21 +18206,21 @@
         <v>1</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>163</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="28" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B20" s="8">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>37</v>
+        <v>160</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>123</v>
@@ -18231,98 +18232,98 @@
         <v>122</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H20" s="8">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="I20" s="9">
         <v>1</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>37</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="28" customHeight="1">
       <c r="A21" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B21" s="8">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="H21" s="9"/>
+        <v>167</v>
+      </c>
+      <c r="H21" s="8">
+        <v>46216</v>
+      </c>
       <c r="I21" s="9">
         <v>1</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>173</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="28" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B22" s="8">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>175</v>
+        <v>34</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="H22" s="8">
-        <v>46212</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="H22" s="9"/>
       <c r="I22" s="9">
         <v>1</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="K22" s="13" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="28" customHeight="1">
       <c r="A23" s="9" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B23" s="8">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>34</v>
+        <v>175</v>
       </c>
       <c r="D23" s="9" t="s">
         <v>123</v>
@@ -18334,42 +18335,42 @@
         <v>122</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H23" s="8">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="I23" s="9">
         <v>1</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K23" s="13" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="28" customHeight="1">
       <c r="A24" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B24" s="8">
         <v>46211</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>185</v>
+        <v>123</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H24" s="8">
         <v>46211</v>
@@ -18378,57 +18379,59 @@
         <v>1</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K24" s="13" t="s">
-        <v>42</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="28" customHeight="1">
       <c r="A25" s="9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B25" s="8">
         <v>46211</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>188</v>
+        <v>41</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>657</v>
+        <v>670</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="H25" s="9"/>
+        <v>186</v>
+      </c>
+      <c r="H25" s="8">
+        <v>46211</v>
+      </c>
       <c r="I25" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>670</v>
+        <v>186</v>
       </c>
       <c r="K25" s="13" t="s">
-        <v>191</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="28" customHeight="1">
       <c r="A26" s="9" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B26" s="8">
         <v>46211</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>657</v>
@@ -18437,7 +18440,7 @@
         <v>105</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H26" s="9"/>
       <c r="I26" s="9">
@@ -18447,21 +18450,21 @@
         <v>671</v>
       </c>
       <c r="K26" s="13" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="28" customHeight="1">
       <c r="A27" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B27" s="8">
         <v>46211</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>196</v>
+        <v>34</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>198</v>
+        <v>149</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>657</v>
@@ -18470,7 +18473,7 @@
         <v>105</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9">
@@ -18480,18 +18483,18 @@
         <v>672</v>
       </c>
       <c r="K27" s="13" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="28" customHeight="1">
       <c r="A28" s="9" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B28" s="8">
         <v>46211</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>198</v>
@@ -18503,7 +18506,7 @@
         <v>105</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="9">
@@ -18513,21 +18516,21 @@
         <v>673</v>
       </c>
       <c r="K28" s="13" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="28" customHeight="1">
       <c r="A29" s="9" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B29" s="8">
         <v>46211</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>149</v>
+        <v>198</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>657</v>
@@ -18536,7 +18539,7 @@
         <v>105</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="9">
@@ -18546,21 +18549,21 @@
         <v>674</v>
       </c>
       <c r="K29" s="13" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="28" customHeight="1">
       <c r="A30" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B30" s="8">
         <v>46211</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>34</v>
+        <v>206</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>210</v>
+        <v>149</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>657</v>
@@ -18569,7 +18572,7 @@
         <v>105</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="H30" s="9"/>
       <c r="I30" s="9">
@@ -18579,21 +18582,21 @@
         <v>675</v>
       </c>
       <c r="K30" s="13" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="28" customHeight="1">
       <c r="A31" s="9" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B31" s="8">
         <v>46211</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>139</v>
+        <v>34</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>657</v>
@@ -18602,7 +18605,7 @@
         <v>105</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="9">
@@ -18612,47 +18615,45 @@
         <v>676</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="28" customHeight="1">
       <c r="A32" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B32" s="8">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>123</v>
+        <v>198</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="H32" s="8">
-        <v>46210</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="H32" s="9"/>
       <c r="I32" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>216</v>
+        <v>677</v>
       </c>
       <c r="K32" s="13" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="28" customHeight="1">
       <c r="A33" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B33" s="8">
         <v>46210</v>
@@ -18670,7 +18671,7 @@
         <v>122</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="H33" s="8">
         <v>46210</v>
@@ -18679,18 +18680,18 @@
         <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="28" customHeight="1">
       <c r="A34" s="9" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B34" s="8">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>34</v>
@@ -18705,24 +18706,24 @@
         <v>122</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H34" s="8">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="I34" s="9">
         <v>1</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="K34" s="13" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="28" customHeight="1">
       <c r="A35" s="9" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B35" s="8">
         <v>46209</v>
@@ -18740,7 +18741,7 @@
         <v>122</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H35" s="8">
         <v>46209</v>
@@ -18749,15 +18750,15 @@
         <v>1</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="K35" s="13" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="28" customHeight="1">
       <c r="A36" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B36" s="8">
         <v>46209</v>
@@ -18766,99 +18767,99 @@
         <v>34</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>231</v>
+        <v>123</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>677</v>
+        <v>660</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G36" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="H36" s="9"/>
+        <v>228</v>
+      </c>
+      <c r="H36" s="8">
+        <v>46209</v>
+      </c>
       <c r="I36" s="9">
         <v>1</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="28" customHeight="1">
       <c r="A37" s="9" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B37" s="8">
         <v>46209</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>135</v>
+        <v>231</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>657</v>
+        <v>678</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>678</v>
+        <v>232</v>
       </c>
       <c r="K37" s="13" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="28" customHeight="1">
       <c r="A38" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B38" s="8">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="G38" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="H38" s="8">
-        <v>46206</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="H38" s="9"/>
       <c r="I38" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>238</v>
+        <v>679</v>
       </c>
       <c r="K38" s="13" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="28" customHeight="1">
       <c r="A39" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B39" s="8">
         <v>46206</v>
@@ -18876,7 +18877,7 @@
         <v>122</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H39" s="8">
         <v>46206</v>
@@ -18885,15 +18886,15 @@
         <v>1</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="K39" s="13" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="28" customHeight="1">
       <c r="A40" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B40" s="8">
         <v>46206</v>
@@ -18911,7 +18912,7 @@
         <v>122</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H40" s="8">
         <v>46206</v>
@@ -18920,15 +18921,15 @@
         <v>1</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="K40" s="13" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="28" customHeight="1">
       <c r="A41" s="9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B41" s="8">
         <v>46206</v>
@@ -18937,26 +18938,28 @@
         <v>34</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>247</v>
+        <v>123</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>677</v>
+        <v>660</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="H41" s="9"/>
+        <v>244</v>
+      </c>
+      <c r="H41" s="8">
+        <v>46206</v>
+      </c>
       <c r="I41" s="9">
         <v>1</v>
       </c>
       <c r="J41" s="13" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="K41" s="13" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="28" customHeight="1">
@@ -18970,23 +18973,23 @@
         <v>34</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>321</v>
+        <v>247</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G42" s="9" t="s">
-        <v>679</v>
+        <v>248</v>
       </c>
       <c r="H42" s="9"/>
       <c r="I42" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>680</v>
+        <v>248</v>
       </c>
       <c r="K42" s="13" t="s">
         <v>249</v>
@@ -19003,23 +19006,23 @@
         <v>34</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>681</v>
+        <v>321</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="K43" s="13" t="s">
         <v>249</v>
@@ -19036,23 +19039,23 @@
         <v>34</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>657</v>
+        <v>678</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9">
         <v>1</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="K44" s="13" t="s">
         <v>249</v>
@@ -19060,42 +19063,40 @@
     </row>
     <row r="45" spans="1:11" ht="28" customHeight="1">
       <c r="A45" s="9" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B45" s="8">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="C45" s="9" t="s">
         <v>34</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>123</v>
+        <v>684</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="H45" s="8">
-        <v>46205</v>
-      </c>
+        <v>685</v>
+      </c>
+      <c r="H45" s="9"/>
       <c r="I45" s="9">
         <v>1</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>252</v>
+        <v>685</v>
       </c>
       <c r="K45" s="13" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="28" customHeight="1">
       <c r="A46" s="9" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B46" s="8">
         <v>46205</v>
@@ -19113,7 +19114,7 @@
         <v>122</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="H46" s="8">
         <v>46205</v>
@@ -19122,15 +19123,15 @@
         <v>1</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="K46" s="13" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="28" customHeight="1">
       <c r="A47" s="9" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B47" s="8">
         <v>46205</v>
@@ -19148,7 +19149,7 @@
         <v>122</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H47" s="8">
         <v>46205</v>
@@ -19157,15 +19158,15 @@
         <v>1</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="K47" s="13" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="28" customHeight="1">
       <c r="A48" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B48" s="8">
         <v>46205</v>
@@ -19183,7 +19184,7 @@
         <v>122</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H48" s="8">
         <v>46205</v>
@@ -19192,15 +19193,15 @@
         <v>1</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="K48" s="13" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="28" customHeight="1">
       <c r="A49" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B49" s="8">
         <v>46205</v>
@@ -19218,7 +19219,7 @@
         <v>122</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H49" s="8">
         <v>46205</v>
@@ -19227,21 +19228,21 @@
         <v>1</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="K49" s="13" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="50" spans="1:11" ht="28" customHeight="1">
       <c r="A50" s="9" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B50" s="8">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>269</v>
+        <v>34</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>123</v>
@@ -19253,30 +19254,30 @@
         <v>122</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="H50" s="8">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="I50" s="9">
         <v>1</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="K50" s="13" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
     </row>
     <row r="51" spans="1:11" ht="28" customHeight="1">
       <c r="A51" s="9" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B51" s="8">
         <v>46204</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>34</v>
+        <v>269</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>123</v>
@@ -19288,7 +19289,7 @@
         <v>122</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H51" s="8">
         <v>46204</v>
@@ -19297,15 +19298,15 @@
         <v>1</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="K51" s="13" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="28" customHeight="1">
       <c r="A52" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B52" s="8">
         <v>46204</v>
@@ -19323,7 +19324,7 @@
         <v>122</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H52" s="8">
         <v>46204</v>
@@ -19332,15 +19333,15 @@
         <v>1</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="K52" s="13" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="28" customHeight="1">
       <c r="A53" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="B53" s="8">
         <v>46204</v>
@@ -19358,7 +19359,7 @@
         <v>122</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H53" s="8">
         <v>46204</v>
@@ -19367,15 +19368,15 @@
         <v>1</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="28" customHeight="1">
       <c r="A54" s="9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B54" s="8">
         <v>46204</v>
@@ -19393,7 +19394,7 @@
         <v>122</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H54" s="8">
         <v>46204</v>
@@ -19402,15 +19403,15 @@
         <v>1</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="K54" s="13" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="28" customHeight="1">
       <c r="A55" s="9" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B55" s="8">
         <v>46204</v>
@@ -19428,7 +19429,7 @@
         <v>122</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="H55" s="8">
         <v>46204</v>
@@ -19437,15 +19438,15 @@
         <v>1</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="K55" s="13" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="28" customHeight="1">
       <c r="A56" s="9" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B56" s="8">
         <v>46204</v>
@@ -19454,26 +19455,28 @@
         <v>34</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>677</v>
+        <v>660</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G56" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="H56" s="9"/>
+        <v>290</v>
+      </c>
+      <c r="H56" s="8">
+        <v>46204</v>
+      </c>
       <c r="I56" s="9">
         <v>1</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="K56" s="13" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="28" customHeight="1">
@@ -19487,23 +19490,23 @@
         <v>34</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>685</v>
+        <v>293</v>
       </c>
       <c r="H57" s="9"/>
       <c r="I57" s="9">
         <v>1</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>685</v>
+        <v>293</v>
       </c>
       <c r="K57" s="13" t="s">
         <v>294</v>
@@ -19523,7 +19526,7 @@
         <v>149</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>657</v>
+        <v>678</v>
       </c>
       <c r="F58" s="9" t="s">
         <v>105</v>
@@ -19577,7 +19580,7 @@
     </row>
     <row r="60" spans="1:11" ht="28" customHeight="1">
       <c r="A60" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B60" s="8">
         <v>46204</v>
@@ -19586,68 +19589,66 @@
         <v>34</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>296</v>
+        <v>149</v>
       </c>
       <c r="E60" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F60" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G60" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="H60" s="8">
-        <v>46204</v>
-      </c>
+        <v>688</v>
+      </c>
+      <c r="H60" s="9"/>
       <c r="I60" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J60" s="13" t="s">
         <v>688</v>
       </c>
       <c r="K60" s="13" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="28" customHeight="1">
       <c r="A61" s="9" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B61" s="8">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="C61" s="9" t="s">
         <v>34</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>123</v>
+        <v>296</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H61" s="8">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="I61" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J61" s="13" t="s">
-        <v>300</v>
+        <v>689</v>
       </c>
       <c r="K61" s="13" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="28" customHeight="1">
       <c r="A62" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B62" s="8">
         <v>46203</v>
@@ -19665,7 +19666,7 @@
         <v>122</v>
       </c>
       <c r="G62" s="9" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="H62" s="8">
         <v>46203</v>
@@ -19674,15 +19675,15 @@
         <v>1</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="K62" s="13" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="28" customHeight="1">
       <c r="A63" s="9" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B63" s="8">
         <v>46203</v>
@@ -19700,7 +19701,7 @@
         <v>122</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="H63" s="8">
         <v>46203</v>
@@ -19709,15 +19710,15 @@
         <v>1</v>
       </c>
       <c r="J63" s="13" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="K63" s="13" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="28" customHeight="1">
       <c r="A64" s="9" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B64" s="8">
         <v>46203</v>
@@ -19735,7 +19736,7 @@
         <v>122</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="H64" s="8">
         <v>46203</v>
@@ -19744,118 +19745,118 @@
         <v>1</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K64" s="13" t="s">
-        <v>257</v>
+        <v>311</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="28" customHeight="1">
       <c r="A65" s="9" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B65" s="8">
         <v>46203</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>316</v>
+        <v>123</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>689</v>
+        <v>660</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>317</v>
-      </c>
-      <c r="H65" s="9"/>
+        <v>314</v>
+      </c>
+      <c r="H65" s="8">
+        <v>46203</v>
+      </c>
       <c r="I65" s="9">
         <v>1</v>
       </c>
       <c r="J65" s="13" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="K65" s="13" t="s">
-        <v>318</v>
+        <v>257</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="28" customHeight="1">
       <c r="A66" s="9" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B66" s="8">
         <v>46203</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>320</v>
+        <v>48</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>655</v>
+        <v>690</v>
       </c>
       <c r="F66" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="H66" s="8">
-        <v>46203</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="H66" s="9"/>
       <c r="I66" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J66" s="13" t="s">
-        <v>690</v>
+        <v>317</v>
       </c>
       <c r="K66" s="13" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="28" customHeight="1">
       <c r="A67" s="9" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B67" s="8">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>34</v>
+        <v>320</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>123</v>
+        <v>321</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="H67" s="8">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="I67" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J67" s="13" t="s">
-        <v>325</v>
+        <v>691</v>
       </c>
       <c r="K67" s="13" t="s">
-        <v>257</v>
+        <v>323</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="28" customHeight="1">
       <c r="A68" s="9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B68" s="8">
         <v>46202</v>
@@ -19873,7 +19874,7 @@
         <v>122</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="H68" s="8">
         <v>46202</v>
@@ -19882,15 +19883,15 @@
         <v>1</v>
       </c>
       <c r="J68" s="13" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="K68" s="13" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="28" customHeight="1">
       <c r="A69" s="9" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B69" s="8">
         <v>46202</v>
@@ -19908,7 +19909,7 @@
         <v>122</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="H69" s="8">
         <v>46202</v>
@@ -19917,21 +19918,21 @@
         <v>1</v>
       </c>
       <c r="J69" s="13" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="K69" s="13" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="28" customHeight="1">
       <c r="A70" s="9" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B70" s="8">
         <v>46202</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>333</v>
+        <v>34</v>
       </c>
       <c r="D70" s="9" t="s">
         <v>123</v>
@@ -19943,7 +19944,7 @@
         <v>122</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="H70" s="8">
         <v>46202</v>
@@ -19952,21 +19953,21 @@
         <v>1</v>
       </c>
       <c r="J70" s="13" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="K70" s="13" t="s">
-        <v>337</v>
+        <v>286</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="28" customHeight="1">
       <c r="A71" s="9" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B71" s="8">
         <v>46202</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="D71" s="9" t="s">
         <v>123</v>
@@ -19978,7 +19979,7 @@
         <v>122</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="H71" s="8">
         <v>46202</v>
@@ -19987,59 +19988,59 @@
         <v>1</v>
       </c>
       <c r="J71" s="13" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="K71" s="13" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="28" customHeight="1">
       <c r="A72" s="9" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B72" s="8">
         <v>46202</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>198</v>
+        <v>123</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="H72" s="8">
         <v>46202</v>
       </c>
       <c r="I72" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J72" s="13" t="s">
-        <v>691</v>
+        <v>341</v>
       </c>
       <c r="K72" s="13" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="28" customHeight="1">
       <c r="A73" s="9" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B73" s="8">
         <v>46202</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>139</v>
+        <v>344</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>296</v>
+        <v>198</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>655</v>
@@ -20048,7 +20049,7 @@
         <v>105</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H73" s="8">
         <v>46202</v>
@@ -20060,91 +20061,91 @@
         <v>692</v>
       </c>
       <c r="K73" s="13" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="28" customHeight="1">
       <c r="A74" s="9" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B74" s="8">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>44</v>
+        <v>139</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>351</v>
+        <v>296</v>
       </c>
       <c r="E74" s="9" t="s">
         <v>655</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="G74" s="9" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="H74" s="8">
-        <v>46201</v>
+        <v>46202</v>
       </c>
       <c r="I74" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J74" s="13" t="s">
-        <v>352</v>
+        <v>693</v>
       </c>
       <c r="K74" s="13" t="s">
-        <v>45</v>
+        <v>349</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="28" customHeight="1">
       <c r="A75" s="9" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B75" s="8">
         <v>46201</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>198</v>
+        <v>351</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>655</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="H75" s="8">
         <v>46201</v>
       </c>
       <c r="I75" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J75" s="13" t="s">
-        <v>693</v>
+        <v>352</v>
       </c>
       <c r="K75" s="13" t="s">
-        <v>355</v>
+        <v>45</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="28" customHeight="1">
       <c r="A76" s="9" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B76" s="8">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>34</v>
+        <v>133</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>358</v>
+        <v>198</v>
       </c>
       <c r="E76" s="9" t="s">
         <v>655</v>
@@ -20153,59 +20154,59 @@
         <v>105</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="H76" s="8">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="I76" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J76" s="13" t="s">
-        <v>359</v>
+        <v>694</v>
       </c>
       <c r="K76" s="13" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="28" customHeight="1">
       <c r="A77" s="9" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B77" s="8">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="C77" s="9" t="s">
         <v>34</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>123</v>
+        <v>358</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>655</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="H77" s="8">
-        <v>46199</v>
+        <v>46200</v>
       </c>
       <c r="I77" s="9">
         <v>1</v>
       </c>
       <c r="J77" s="13" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="K77" s="13" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="28" customHeight="1">
       <c r="A78" s="9" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B78" s="8">
         <v>46199</v>
@@ -20217,13 +20218,13 @@
         <v>123</v>
       </c>
       <c r="E78" s="9" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="H78" s="8">
         <v>46199</v>
@@ -20232,15 +20233,15 @@
         <v>1</v>
       </c>
       <c r="J78" s="13" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="K78" s="13" t="s">
-        <v>279</v>
+        <v>363</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="28" customHeight="1">
       <c r="A79" s="9" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B79" s="8">
         <v>46199</v>
@@ -20252,13 +20253,13 @@
         <v>123</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>655</v>
+        <v>660</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H79" s="8">
         <v>46199</v>
@@ -20267,15 +20268,15 @@
         <v>1</v>
       </c>
       <c r="J79" s="13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="K79" s="13" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="28" customHeight="1">
       <c r="A80" s="9" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B80" s="8">
         <v>46199</v>
@@ -20293,7 +20294,7 @@
         <v>122</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="H80" s="8">
         <v>46199</v>
@@ -20302,15 +20303,15 @@
         <v>1</v>
       </c>
       <c r="J80" s="13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="K80" s="13" t="s">
-        <v>370</v>
+        <v>267</v>
       </c>
     </row>
     <row r="81" spans="1:11" ht="28" customHeight="1">
       <c r="A81" s="9" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B81" s="8">
         <v>46199</v>
@@ -20328,7 +20329,7 @@
         <v>122</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="H81" s="8">
         <v>46199</v>
@@ -20337,15 +20338,15 @@
         <v>1</v>
       </c>
       <c r="J81" s="13" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="K81" s="13" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="82" spans="1:11" ht="28" customHeight="1">
       <c r="A82" s="9" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B82" s="8">
         <v>46199</v>
@@ -20363,7 +20364,7 @@
         <v>122</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="H82" s="8">
         <v>46199</v>
@@ -20372,15 +20373,15 @@
         <v>1</v>
       </c>
       <c r="J82" s="13" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="28" customHeight="1">
       <c r="A83" s="9" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B83" s="8">
         <v>46199</v>
@@ -20398,7 +20399,7 @@
         <v>122</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="H83" s="8">
         <v>46199</v>
@@ -20407,115 +20408,115 @@
         <v>1</v>
       </c>
       <c r="J83" s="13" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="K83" s="13" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="28" customHeight="1">
       <c r="A84" s="9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B84" s="8">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>381</v>
+        <v>34</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>383</v>
+        <v>123</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>655</v>
       </c>
       <c r="F84" s="9" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="H84" s="8">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="I84" s="9">
         <v>1</v>
       </c>
       <c r="J84" s="13" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="28" customHeight="1">
       <c r="A85" s="9" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B85" s="8">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>46</v>
+        <v>381</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="F85" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="H85" s="8">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="I85" s="9">
         <v>1</v>
       </c>
       <c r="J85" s="13" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="K85" s="13" t="s">
-        <v>47</v>
+        <v>385</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="28" customHeight="1">
       <c r="A86" s="9" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B86" s="8">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E86" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="H86" s="8">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="I86" s="9">
         <v>1</v>
       </c>
       <c r="J86" s="13" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="K86" s="13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="87" spans="1:11" ht="28" customHeight="1">
@@ -20529,25 +20530,25 @@
         <v>48</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>296</v>
+        <v>391</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>655</v>
+        <v>670</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>694</v>
+        <v>392</v>
       </c>
       <c r="H87" s="8">
-        <v>46181</v>
+        <v>46192</v>
       </c>
       <c r="I87" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J87" s="13" t="s">
-        <v>695</v>
+        <v>392</v>
       </c>
       <c r="K87" s="13" t="s">
         <v>49</v>
@@ -20564,7 +20565,7 @@
         <v>48</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>149</v>
+        <v>296</v>
       </c>
       <c r="E88" s="9" t="s">
         <v>655</v>
@@ -20573,16 +20574,16 @@
         <v>105</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H88" s="8">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="I88" s="9">
         <v>2</v>
       </c>
       <c r="J88" s="13" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="K88" s="13" t="s">
         <v>49</v>
@@ -20590,16 +20591,16 @@
     </row>
     <row r="89" spans="1:11" ht="28" customHeight="1">
       <c r="A89" s="9" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B89" s="8">
-        <v>46183</v>
+        <v>46192</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>394</v>
+        <v>48</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>396</v>
+        <v>149</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>655</v>
@@ -20608,33 +20609,33 @@
         <v>105</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>397</v>
+        <v>697</v>
       </c>
       <c r="H89" s="8">
-        <v>46183</v>
+        <v>46177</v>
       </c>
       <c r="I89" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J89" s="13" t="s">
-        <v>397</v>
+        <v>698</v>
       </c>
       <c r="K89" s="13" t="s">
-        <v>398</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="28" customHeight="1">
       <c r="A90" s="9" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B90" s="8">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>321</v>
+        <v>396</v>
       </c>
       <c r="E90" s="9" t="s">
         <v>655</v>
@@ -20643,19 +20644,19 @@
         <v>105</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="H90" s="8">
-        <v>46177</v>
+        <v>46183</v>
       </c>
       <c r="I90" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90" s="13" t="s">
-        <v>698</v>
+        <v>397</v>
       </c>
       <c r="K90" s="13" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="28" customHeight="1">
@@ -20669,7 +20670,7 @@
         <v>402</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>699</v>
+        <v>321</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>655</v>
@@ -20678,16 +20679,16 @@
         <v>105</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>700</v>
+        <v>405</v>
       </c>
       <c r="H91" s="8">
-        <v>46171</v>
+        <v>46177</v>
       </c>
       <c r="I91" s="9">
         <v>2</v>
       </c>
       <c r="J91" s="13" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="K91" s="13" t="s">
         <v>406</v>
@@ -20704,7 +20705,7 @@
         <v>402</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="E92" s="9" t="s">
         <v>655</v>
@@ -20713,16 +20714,16 @@
         <v>105</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="H92" s="8">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="I92" s="9">
         <v>2</v>
       </c>
       <c r="J92" s="13" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="K92" s="13" t="s">
         <v>406</v>
@@ -20739,7 +20740,7 @@
         <v>402</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>247</v>
+        <v>703</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>655</v>
@@ -20748,13 +20749,13 @@
         <v>105</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H93" s="8">
         <v>46170</v>
       </c>
       <c r="I93" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J93" s="13" t="s">
         <v>705</v>
@@ -20809,7 +20810,7 @@
         <v>402</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>655</v>
@@ -20824,10 +20825,10 @@
         <v>46170</v>
       </c>
       <c r="I95" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J95" s="13" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="K95" s="13" t="s">
         <v>406</v>
@@ -20844,7 +20845,7 @@
         <v>402</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>396</v>
+        <v>296</v>
       </c>
       <c r="E96" s="9" t="s">
         <v>655</v>
@@ -20853,13 +20854,13 @@
         <v>105</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H96" s="8">
         <v>46170</v>
       </c>
       <c r="I96" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J96" s="13" t="s">
         <v>709</v>
@@ -20879,10 +20880,10 @@
         <v>402</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>247</v>
+        <v>396</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>105</v>
@@ -20890,7 +20891,9 @@
       <c r="G97" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="H97" s="9"/>
+      <c r="H97" s="8">
+        <v>46170</v>
+      </c>
       <c r="I97" s="9">
         <v>1</v>
       </c>
@@ -20945,7 +20948,7 @@
         <v>402</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>472</v>
+        <v>247</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>657</v>
@@ -20969,37 +20972,35 @@
     </row>
     <row r="100" spans="1:11" ht="28" customHeight="1">
       <c r="A100" s="9" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="B100" s="8">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>51</v>
+        <v>402</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>391</v>
+        <v>472</v>
       </c>
       <c r="E100" s="9" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="F100" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>408</v>
-      </c>
-      <c r="H100" s="8">
-        <v>46175</v>
-      </c>
+        <v>713</v>
+      </c>
+      <c r="H100" s="9"/>
       <c r="I100" s="9">
         <v>1</v>
       </c>
       <c r="J100" s="13" t="s">
-        <v>408</v>
+        <v>713</v>
       </c>
       <c r="K100" s="13" t="s">
-        <v>53</v>
+        <v>406</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="28" customHeight="1">
@@ -21013,25 +21014,25 @@
         <v>51</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>321</v>
+        <v>391</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>655</v>
+        <v>670</v>
       </c>
       <c r="F101" s="9" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>713</v>
+        <v>408</v>
       </c>
       <c r="H101" s="8">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="I101" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J101" s="13" t="s">
-        <v>714</v>
+        <v>408</v>
       </c>
       <c r="K101" s="13" t="s">
         <v>53</v>
@@ -21048,7 +21049,7 @@
         <v>51</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>296</v>
+        <v>321</v>
       </c>
       <c r="E102" s="9" t="s">
         <v>655</v>
@@ -21057,16 +21058,16 @@
         <v>105</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H102" s="8">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="I102" s="9">
         <v>2</v>
       </c>
       <c r="J102" s="13" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="K102" s="13" t="s">
         <v>53</v>
@@ -21074,13 +21075,13 @@
     </row>
     <row r="103" spans="1:11" ht="28" customHeight="1">
       <c r="A103" s="9" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B103" s="8">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>411</v>
+        <v>51</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>296</v>
@@ -21092,10 +21093,10 @@
         <v>105</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>412</v>
+        <v>716</v>
       </c>
       <c r="H103" s="8">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="I103" s="9">
         <v>2</v>
@@ -21104,18 +21105,18 @@
         <v>717</v>
       </c>
       <c r="K103" s="13" t="s">
-        <v>413</v>
+        <v>53</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="28" customHeight="1">
       <c r="A104" s="9" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="B104" s="8">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>34</v>
+        <v>411</v>
       </c>
       <c r="D104" s="9" t="s">
         <v>296</v>
@@ -21127,10 +21128,10 @@
         <v>105</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="H104" s="8">
-        <v>46167</v>
+        <v>46170</v>
       </c>
       <c r="I104" s="9">
         <v>2</v>
@@ -21139,21 +21140,21 @@
         <v>718</v>
       </c>
       <c r="K104" s="13" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="28" customHeight="1">
       <c r="A105" s="9" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B105" s="8">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>402</v>
+        <v>34</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>321</v>
+        <v>296</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>655</v>
@@ -21162,19 +21163,19 @@
         <v>105</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="H105" s="8">
-        <v>46162</v>
+        <v>46167</v>
       </c>
       <c r="I105" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J105" s="13" t="s">
         <v>719</v>
       </c>
       <c r="K105" s="13" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="106" spans="1:11" ht="28" customHeight="1">
@@ -21188,23 +21189,25 @@
         <v>402</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>720</v>
+        <v>321</v>
       </c>
       <c r="E106" s="9" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>721</v>
-      </c>
-      <c r="H106" s="9"/>
+        <v>418</v>
+      </c>
+      <c r="H106" s="8">
+        <v>46162</v>
+      </c>
       <c r="I106" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J106" s="13" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="K106" s="13" t="s">
         <v>419</v>
@@ -21212,51 +21215,49 @@
     </row>
     <row r="107" spans="1:11" ht="28" customHeight="1">
       <c r="A107" s="9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B107" s="8">
-        <v>46157</v>
+        <v>46162</v>
       </c>
       <c r="C107" s="9" t="s">
         <v>402</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>296</v>
+        <v>721</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>421</v>
-      </c>
-      <c r="H107" s="8">
-        <v>46157</v>
-      </c>
+        <v>722</v>
+      </c>
+      <c r="H107" s="9"/>
       <c r="I107" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J107" s="13" t="s">
         <v>722</v>
       </c>
       <c r="K107" s="13" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="28" customHeight="1">
       <c r="A108" s="9" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="B108" s="8">
         <v>46157</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>34</v>
+        <v>402</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>396</v>
+        <v>296</v>
       </c>
       <c r="E108" s="9" t="s">
         <v>655</v>
@@ -21265,30 +21266,30 @@
         <v>105</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="H108" s="8">
         <v>46157</v>
       </c>
       <c r="I108" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J108" s="13" t="s">
-        <v>424</v>
+        <v>723</v>
       </c>
       <c r="K108" s="13" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="109" spans="1:11" ht="28" customHeight="1">
       <c r="A109" s="9" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="B109" s="8">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>427</v>
+        <v>34</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>396</v>
@@ -21300,101 +21301,101 @@
         <v>105</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="H109" s="8">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="I109" s="9">
         <v>1</v>
       </c>
       <c r="J109" s="13" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="K109" s="13" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="28" customHeight="1">
       <c r="A110" s="9" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B110" s="8">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>34</v>
+        <v>427</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>431</v>
+        <v>396</v>
       </c>
       <c r="E110" s="9" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F110" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="H110" s="9"/>
+        <v>428</v>
+      </c>
+      <c r="H110" s="8">
+        <v>46150</v>
+      </c>
       <c r="I110" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J110" s="13" t="s">
-        <v>723</v>
+        <v>428</v>
       </c>
       <c r="K110" s="13" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="28" customHeight="1">
       <c r="A111" s="9" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B111" s="8">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>321</v>
+        <v>431</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>435</v>
-      </c>
-      <c r="H111" s="8">
-        <v>46147</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="H111" s="9"/>
       <c r="I111" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J111" s="13" t="s">
         <v>724</v>
       </c>
       <c r="K111" s="13" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
     </row>
     <row r="112" spans="1:11" ht="28" customHeight="1">
       <c r="A112" s="9" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B112" s="8">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C112" s="9" t="s">
         <v>48</v>
       </c>
       <c r="D112" s="9" t="s">
-        <v>439</v>
+        <v>321</v>
       </c>
       <c r="E112" s="9" t="s">
         <v>655</v>
@@ -21403,33 +21404,33 @@
         <v>105</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="H112" s="8">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="I112" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J112" s="13" t="s">
         <v>725</v>
       </c>
       <c r="K112" s="13" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="28" customHeight="1">
       <c r="A113" s="9" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B113" s="8">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>135</v>
+        <v>439</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>655</v>
@@ -21438,10 +21439,10 @@
         <v>105</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="H113" s="8">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="I113" s="9">
         <v>2</v>
@@ -21450,12 +21451,12 @@
         <v>726</v>
       </c>
       <c r="K113" s="13" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="28" customHeight="1">
       <c r="A114" s="9" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B114" s="8">
         <v>46139</v>
@@ -21464,7 +21465,7 @@
         <v>34</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>321</v>
+        <v>135</v>
       </c>
       <c r="E114" s="9" t="s">
         <v>655</v>
@@ -21473,24 +21474,24 @@
         <v>105</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H114" s="8">
         <v>46139</v>
       </c>
       <c r="I114" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J114" s="13" t="s">
         <v>727</v>
       </c>
       <c r="K114" s="13" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="28" customHeight="1">
       <c r="A115" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B115" s="8">
         <v>46139</v>
@@ -21499,7 +21500,7 @@
         <v>34</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>449</v>
+        <v>321</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>655</v>
@@ -21508,19 +21509,19 @@
         <v>105</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="H115" s="8">
         <v>46139</v>
       </c>
       <c r="I115" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J115" s="13" t="s">
         <v>728</v>
       </c>
       <c r="K115" s="13" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="28" customHeight="1">
@@ -21534,7 +21535,7 @@
         <v>34</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>149</v>
+        <v>449</v>
       </c>
       <c r="E116" s="9" t="s">
         <v>655</v>
@@ -21543,7 +21544,7 @@
         <v>105</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>729</v>
+        <v>450</v>
       </c>
       <c r="H116" s="8">
         <v>46139</v>
@@ -21552,7 +21553,7 @@
         <v>2</v>
       </c>
       <c r="J116" s="13" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="K116" s="13" t="s">
         <v>451</v>
@@ -21569,23 +21570,25 @@
         <v>34</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>731</v>
+        <v>149</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>732</v>
-      </c>
-      <c r="H117" s="9"/>
+        <v>730</v>
+      </c>
+      <c r="H117" s="8">
+        <v>46139</v>
+      </c>
       <c r="I117" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J117" s="13" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="K117" s="13" t="s">
         <v>451</v>
@@ -21593,7 +21596,7 @@
     </row>
     <row r="118" spans="1:11" ht="28" customHeight="1">
       <c r="A118" s="9" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B118" s="8">
         <v>46139</v>
@@ -21602,33 +21605,31 @@
         <v>34</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>453</v>
+        <v>732</v>
       </c>
       <c r="E118" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F118" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="H118" s="8">
-        <v>46139</v>
-      </c>
+        <v>733</v>
+      </c>
+      <c r="H118" s="9"/>
       <c r="I118" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J118" s="13" t="s">
         <v>733</v>
       </c>
       <c r="K118" s="13" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="28" customHeight="1">
       <c r="A119" s="9" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B119" s="8">
         <v>46139</v>
@@ -21637,7 +21638,7 @@
         <v>34</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>655</v>
@@ -21646,7 +21647,7 @@
         <v>105</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="H119" s="8">
         <v>46139</v>
@@ -21658,21 +21659,21 @@
         <v>734</v>
       </c>
       <c r="K119" s="13" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="28" customHeight="1">
       <c r="A120" s="9" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B120" s="8">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>402</v>
+        <v>34</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>247</v>
+        <v>457</v>
       </c>
       <c r="E120" s="9" t="s">
         <v>655</v>
@@ -21681,10 +21682,10 @@
         <v>105</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="H120" s="8">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="I120" s="9">
         <v>2</v>
@@ -21693,21 +21694,21 @@
         <v>735</v>
       </c>
       <c r="K120" s="13" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="28" customHeight="1">
       <c r="A121" s="9" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B121" s="8">
         <v>46132</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>48</v>
+        <v>402</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>464</v>
+        <v>247</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>655</v>
@@ -21716,7 +21717,7 @@
         <v>105</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="H121" s="8">
         <v>46132</v>
@@ -21728,7 +21729,7 @@
         <v>736</v>
       </c>
       <c r="K121" s="13" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="28" customHeight="1">
@@ -21742,20 +21743,22 @@
         <v>48</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>116</v>
+        <v>464</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F122" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>737</v>
-      </c>
-      <c r="H122" s="9"/>
+        <v>465</v>
+      </c>
+      <c r="H122" s="8">
+        <v>46132</v>
+      </c>
       <c r="I122" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J122" s="13" t="s">
         <v>737</v>
@@ -21766,7 +21769,7 @@
     </row>
     <row r="123" spans="1:11" ht="28" customHeight="1">
       <c r="A123" s="9" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="B123" s="8">
         <v>46132</v>
@@ -21775,53 +21778,53 @@
         <v>48</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>468</v>
+        <v>116</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>469</v>
-      </c>
-      <c r="H123" s="8">
-        <v>46132</v>
-      </c>
+        <v>738</v>
+      </c>
+      <c r="H123" s="9"/>
       <c r="I123" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J123" s="13" t="s">
         <v>738</v>
       </c>
       <c r="K123" s="13" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="28" customHeight="1">
       <c r="A124" s="9" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="B124" s="8">
         <v>46132</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>402</v>
+        <v>48</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>473</v>
-      </c>
-      <c r="H124" s="9"/>
+        <v>469</v>
+      </c>
+      <c r="H124" s="8">
+        <v>46132</v>
+      </c>
       <c r="I124" s="9">
         <v>2</v>
       </c>
@@ -21829,34 +21832,32 @@
         <v>739</v>
       </c>
       <c r="K124" s="13" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="28" customHeight="1">
       <c r="A125" s="9" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B125" s="8">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>476</v>
+        <v>402</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>478</v>
-      </c>
-      <c r="H125" s="8">
-        <v>46128</v>
-      </c>
+        <v>473</v>
+      </c>
+      <c r="H125" s="9"/>
       <c r="I125" s="9">
         <v>2</v>
       </c>
@@ -21864,7 +21865,7 @@
         <v>740</v>
       </c>
       <c r="K125" s="13" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="28" customHeight="1">
@@ -21878,7 +21879,7 @@
         <v>476</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>135</v>
+        <v>468</v>
       </c>
       <c r="E126" s="9" t="s">
         <v>655</v>
@@ -21887,7 +21888,7 @@
         <v>105</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>741</v>
+        <v>478</v>
       </c>
       <c r="H126" s="8">
         <v>46128</v>
@@ -21896,7 +21897,7 @@
         <v>2</v>
       </c>
       <c r="J126" s="13" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="K126" s="13" t="s">
         <v>479</v>
@@ -21913,7 +21914,7 @@
         <v>476</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>743</v>
+        <v>135</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>655</v>
@@ -21922,7 +21923,7 @@
         <v>105</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="H127" s="8">
         <v>46128</v>
@@ -21931,7 +21932,7 @@
         <v>2</v>
       </c>
       <c r="J127" s="13" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="K127" s="13" t="s">
         <v>479</v>
@@ -21948,20 +21949,22 @@
         <v>476</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>493</v>
+        <v>744</v>
       </c>
       <c r="E128" s="9" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F128" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>746</v>
-      </c>
-      <c r="H128" s="9"/>
+        <v>745</v>
+      </c>
+      <c r="H128" s="8">
+        <v>46128</v>
+      </c>
       <c r="I128" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J128" s="13" t="s">
         <v>746</v>
@@ -21972,51 +21975,49 @@
     </row>
     <row r="129" spans="1:11" ht="28" customHeight="1">
       <c r="A129" s="9" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B129" s="8">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="C129" s="9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>296</v>
+        <v>493</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>105</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="H129" s="8">
-        <v>46122</v>
-      </c>
+        <v>747</v>
+      </c>
+      <c r="H129" s="9"/>
       <c r="I129" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J129" s="13" t="s">
         <v>747</v>
       </c>
       <c r="K129" s="13" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="28" customHeight="1">
       <c r="A130" s="9" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B130" s="8">
         <v>46122</v>
       </c>
       <c r="C130" s="9" t="s">
-        <v>402</v>
+        <v>477</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="E130" s="9" t="s">
         <v>655</v>
@@ -22025,7 +22026,7 @@
         <v>105</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="H130" s="8">
         <v>46122</v>
@@ -22037,21 +22038,21 @@
         <v>748</v>
       </c>
       <c r="K130" s="13" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="131" spans="1:11" ht="28" customHeight="1">
       <c r="A131" s="9" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B131" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="C131" s="9" t="s">
         <v>402</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>464</v>
+        <v>247</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>655</v>
@@ -22060,10 +22061,10 @@
         <v>105</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H131" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="I131" s="9">
         <v>2</v>
@@ -22072,12 +22073,12 @@
         <v>749</v>
       </c>
       <c r="K131" s="13" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="28" customHeight="1">
       <c r="A132" s="9" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B132" s="8">
         <v>46115</v>
@@ -22086,7 +22087,7 @@
         <v>402</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>321</v>
+        <v>464</v>
       </c>
       <c r="E132" s="9" t="s">
         <v>655</v>
@@ -22095,7 +22096,7 @@
         <v>105</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="H132" s="8">
         <v>46115</v>
@@ -22107,21 +22108,21 @@
         <v>750</v>
       </c>
       <c r="K132" s="13" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="28" customHeight="1">
       <c r="A133" s="9" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B133" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>477</v>
+        <v>402</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>493</v>
+        <v>321</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>655</v>
@@ -22130,24 +22131,24 @@
         <v>105</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="H133" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="I133" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J133" s="13" t="s">
-        <v>494</v>
+        <v>751</v>
       </c>
       <c r="K133" s="13" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="28" customHeight="1">
       <c r="A134" s="9" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B134" s="8">
         <v>46111</v>
@@ -22156,7 +22157,7 @@
         <v>477</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>296</v>
+        <v>493</v>
       </c>
       <c r="E134" s="9" t="s">
         <v>655</v>
@@ -22165,7 +22166,7 @@
         <v>105</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="H134" s="8">
         <v>46111</v>
@@ -22174,53 +22175,53 @@
         <v>1</v>
       </c>
       <c r="J134" s="13" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="K134" s="13" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="28" customHeight="1">
       <c r="A135" s="9" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B135" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>41</v>
+        <v>477</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>185</v>
+        <v>296</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>655</v>
       </c>
       <c r="F135" s="9" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="H135" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="I135" s="9">
         <v>1</v>
       </c>
       <c r="J135" s="13" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K135" s="13" t="s">
-        <v>54</v>
+        <v>498</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="28" customHeight="1">
       <c r="A136" s="9" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B136" s="8">
-        <v>45923</v>
+        <v>46080</v>
       </c>
       <c r="C136" s="9" t="s">
         <v>41</v>
@@ -22229,138 +22230,138 @@
         <v>185</v>
       </c>
       <c r="E136" s="9" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="F136" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H136" s="8">
-        <v>45923</v>
+        <v>46080</v>
       </c>
       <c r="I136" s="9">
         <v>1</v>
       </c>
       <c r="J136" s="13" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="K136" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="28" customHeight="1">
       <c r="A137" s="9" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B137" s="8">
-        <v>45729</v>
+        <v>45923</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>391</v>
+        <v>185</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H137" s="8">
-        <v>45729</v>
+        <v>45923</v>
       </c>
       <c r="I137" s="9">
         <v>1</v>
       </c>
       <c r="J137" s="13" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="K137" s="13" t="s">
-        <v>506</v>
+        <v>55</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="28" customHeight="1">
       <c r="A138" s="9" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B138" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D138" s="9" t="s">
-        <v>185</v>
+        <v>391</v>
       </c>
       <c r="E138" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H138" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="I138" s="9">
         <v>1</v>
       </c>
       <c r="J138" s="13" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="K138" s="13" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="28" customHeight="1">
       <c r="A139" s="9" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B139" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D139" s="9" t="s">
         <v>185</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="H139" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="I139" s="9">
         <v>1</v>
       </c>
       <c r="J139" s="13" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="K139" s="13" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="28" customHeight="1">
       <c r="A140" s="9" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B140" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="C140" s="9" t="s">
         <v>41</v>
@@ -22369,33 +22370,33 @@
         <v>185</v>
       </c>
       <c r="E140" s="9" t="s">
-        <v>655</v>
+        <v>670</v>
       </c>
       <c r="F140" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G140" s="9" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="H140" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="I140" s="9">
         <v>1</v>
       </c>
       <c r="J140" s="13" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="K140" s="13" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="28" customHeight="1">
       <c r="A141" s="9" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B141" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="C141" s="9" t="s">
         <v>41</v>
@@ -22404,95 +22405,95 @@
         <v>185</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>669</v>
+        <v>655</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="H141" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="I141" s="9">
         <v>1</v>
       </c>
       <c r="J141" s="13" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="K141" s="13" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="28" customHeight="1">
       <c r="A142" s="9" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B142" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>522</v>
+        <v>41</v>
       </c>
       <c r="D142" s="9" t="s">
         <v>185</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G142" s="9" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="H142" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="I142" s="9">
         <v>1</v>
       </c>
       <c r="J142" s="13" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="K142" s="13" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="28" customHeight="1">
       <c r="A143" s="9" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B143" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="C143" s="9" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>536</v>
+        <v>185</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>751</v>
+        <v>670</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="H143" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="I143" s="9">
         <v>1</v>
       </c>
       <c r="J143" s="13" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="K143" s="13" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="28" customHeight="1">
@@ -22506,7 +22507,7 @@
         <v>527</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E144" s="9" t="s">
         <v>752</v>
@@ -22515,16 +22516,16 @@
         <v>122</v>
       </c>
       <c r="G144" s="9" t="s">
-        <v>630</v>
+        <v>537</v>
       </c>
       <c r="H144" s="8">
-        <v>45008</v>
+        <v>45190</v>
       </c>
       <c r="I144" s="9">
         <v>1</v>
       </c>
       <c r="J144" s="13" t="s">
-        <v>630</v>
+        <v>537</v>
       </c>
       <c r="K144" s="13" t="s">
         <v>538</v>
@@ -22532,37 +22533,37 @@
     </row>
     <row r="145" spans="1:11" ht="28" customHeight="1">
       <c r="A145" s="9" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="B145" s="8">
-        <v>44707</v>
+        <v>45190</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>548</v>
+        <v>630</v>
       </c>
       <c r="H145" s="8">
-        <v>44707</v>
+        <v>45008</v>
       </c>
       <c r="I145" s="9">
         <v>1</v>
       </c>
       <c r="J145" s="13" t="s">
-        <v>548</v>
+        <v>630</v>
       </c>
       <c r="K145" s="13" t="s">
-        <v>549</v>
+        <v>538</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="28" customHeight="1">
@@ -22576,7 +22577,7 @@
         <v>540</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="E146" s="9" t="s">
         <v>752</v>
@@ -22585,16 +22586,16 @@
         <v>122</v>
       </c>
       <c r="G146" s="9" t="s">
-        <v>631</v>
+        <v>548</v>
       </c>
       <c r="H146" s="8">
-        <v>44644</v>
+        <v>44707</v>
       </c>
       <c r="I146" s="9">
         <v>1</v>
       </c>
       <c r="J146" s="13" t="s">
-        <v>631</v>
+        <v>548</v>
       </c>
       <c r="K146" s="13" t="s">
         <v>549</v>
@@ -22602,37 +22603,37 @@
     </row>
     <row r="147" spans="1:11" ht="28" customHeight="1">
       <c r="A147" s="9" t="s">
-        <v>550</v>
+        <v>539</v>
       </c>
       <c r="B147" s="8">
-        <v>44640</v>
+        <v>44707</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>551</v>
+        <v>540</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>557</v>
+        <v>545</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>558</v>
+        <v>631</v>
       </c>
       <c r="H147" s="8">
-        <v>44734</v>
+        <v>44644</v>
       </c>
       <c r="I147" s="9">
         <v>1</v>
       </c>
       <c r="J147" s="13" t="s">
-        <v>558</v>
+        <v>631</v>
       </c>
       <c r="K147" s="13" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="28" customHeight="1">
@@ -22646,7 +22647,7 @@
         <v>551</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E148" s="9" t="s">
         <v>752</v>
@@ -22655,16 +22656,16 @@
         <v>122</v>
       </c>
       <c r="G148" s="9" t="s">
-        <v>632</v>
+        <v>558</v>
       </c>
       <c r="H148" s="8">
-        <v>44643</v>
+        <v>44734</v>
       </c>
       <c r="I148" s="9">
         <v>1</v>
       </c>
       <c r="J148" s="13" t="s">
-        <v>632</v>
+        <v>558</v>
       </c>
       <c r="K148" s="13" t="s">
         <v>559</v>
@@ -22672,72 +22673,72 @@
     </row>
     <row r="149" spans="1:11" ht="28" customHeight="1">
       <c r="A149" s="9" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="B149" s="8">
-        <v>44592</v>
+        <v>44640</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>567</v>
+        <v>632</v>
       </c>
       <c r="H149" s="8">
-        <v>44608</v>
+        <v>44643</v>
       </c>
       <c r="I149" s="9">
         <v>1</v>
       </c>
       <c r="J149" s="13" t="s">
-        <v>567</v>
+        <v>632</v>
       </c>
       <c r="K149" s="13" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="28" customHeight="1">
       <c r="A150" s="9" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="B150" s="8">
-        <v>44579</v>
+        <v>44592</v>
       </c>
       <c r="C150" s="9" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="E150" s="9" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F150" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G150" s="9" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="H150" s="8">
-        <v>44579</v>
+        <v>44608</v>
       </c>
       <c r="I150" s="9">
         <v>1</v>
       </c>
       <c r="J150" s="13" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="K150" s="13" t="s">
-        <v>578</v>
+        <v>568</v>
       </c>
     </row>
     <row r="151" spans="1:11" ht="28" customHeight="1">
@@ -22751,7 +22752,7 @@
         <v>570</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>752</v>
@@ -22760,16 +22761,16 @@
         <v>122</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>633</v>
+        <v>577</v>
       </c>
       <c r="H151" s="8">
-        <v>44250</v>
+        <v>44579</v>
       </c>
       <c r="I151" s="9">
         <v>1</v>
       </c>
       <c r="J151" s="13" t="s">
-        <v>633</v>
+        <v>577</v>
       </c>
       <c r="K151" s="13" t="s">
         <v>578</v>
@@ -22777,37 +22778,37 @@
     </row>
     <row r="152" spans="1:11" ht="28" customHeight="1">
       <c r="A152" s="9" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="B152" s="8">
-        <v>44166</v>
+        <v>44579</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>585</v>
+        <v>574</v>
       </c>
       <c r="E152" s="9" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G152" s="9" t="s">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="H152" s="8">
-        <v>44166</v>
+        <v>44250</v>
       </c>
       <c r="I152" s="9">
         <v>1</v>
       </c>
       <c r="J152" s="13" t="s">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="K152" s="13" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="28" customHeight="1">
@@ -22821,7 +22822,7 @@
         <v>580</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>752</v>
@@ -22830,16 +22831,16 @@
         <v>122</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="H153" s="8">
-        <v>43902</v>
+        <v>44166</v>
       </c>
       <c r="I153" s="9">
         <v>1</v>
       </c>
       <c r="J153" s="13" t="s">
-        <v>634</v>
+        <v>586</v>
       </c>
       <c r="K153" s="13" t="s">
         <v>587</v>
@@ -22847,37 +22848,37 @@
     </row>
     <row r="154" spans="1:11" ht="28" customHeight="1">
       <c r="A154" s="9" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="B154" s="8">
-        <v>44131</v>
+        <v>44166</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>594</v>
+        <v>583</v>
       </c>
       <c r="E154" s="9" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G154" s="9" t="s">
-        <v>595</v>
+        <v>634</v>
       </c>
       <c r="H154" s="8">
-        <v>44131</v>
+        <v>43902</v>
       </c>
       <c r="I154" s="9">
         <v>1</v>
       </c>
       <c r="J154" s="13" t="s">
-        <v>595</v>
+        <v>634</v>
       </c>
       <c r="K154" s="13" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="28" customHeight="1">
@@ -22891,7 +22892,7 @@
         <v>589</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>752</v>
@@ -22900,16 +22901,16 @@
         <v>122</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>635</v>
+        <v>595</v>
       </c>
       <c r="H155" s="8">
-        <v>43966</v>
+        <v>44131</v>
       </c>
       <c r="I155" s="9">
         <v>1</v>
       </c>
       <c r="J155" s="13" t="s">
-        <v>635</v>
+        <v>595</v>
       </c>
       <c r="K155" s="13" t="s">
         <v>596</v>
@@ -22917,37 +22918,37 @@
     </row>
     <row r="156" spans="1:11" ht="28" customHeight="1">
       <c r="A156" s="9" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="B156" s="8">
-        <v>43626</v>
+        <v>44131</v>
       </c>
       <c r="C156" s="9" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="D156" s="9" t="s">
-        <v>585</v>
+        <v>592</v>
       </c>
       <c r="E156" s="9" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G156" s="9" t="s">
-        <v>602</v>
+        <v>635</v>
       </c>
       <c r="H156" s="8">
-        <v>43626</v>
+        <v>43966</v>
       </c>
       <c r="I156" s="9">
         <v>1</v>
       </c>
       <c r="J156" s="13" t="s">
-        <v>602</v>
+        <v>635</v>
       </c>
       <c r="K156" s="13" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="28" customHeight="1">
@@ -22961,7 +22962,7 @@
         <v>598</v>
       </c>
       <c r="D157" s="9" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>752</v>
@@ -22970,16 +22971,16 @@
         <v>122</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>636</v>
+        <v>602</v>
       </c>
       <c r="H157" s="8">
-        <v>43518</v>
+        <v>43626</v>
       </c>
       <c r="I157" s="9">
         <v>1</v>
       </c>
       <c r="J157" s="13" t="s">
-        <v>636</v>
+        <v>602</v>
       </c>
       <c r="K157" s="13" t="s">
         <v>603</v>
@@ -22987,37 +22988,37 @@
     </row>
     <row r="158" spans="1:11" ht="28" customHeight="1">
       <c r="A158" s="9" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="B158" s="8">
-        <v>43401</v>
+        <v>43626</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="D158" s="9" t="s">
-        <v>610</v>
+        <v>600</v>
       </c>
       <c r="E158" s="9" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G158" s="9" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="H158" s="8">
-        <v>43401</v>
+        <v>43518</v>
       </c>
       <c r="I158" s="9">
         <v>1</v>
       </c>
       <c r="J158" s="13" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="K158" s="13" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="28" customHeight="1">
@@ -23031,7 +23032,7 @@
         <v>605</v>
       </c>
       <c r="D159" s="9" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>752</v>
@@ -23040,16 +23041,16 @@
         <v>122</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>637</v>
+        <v>611</v>
       </c>
       <c r="H159" s="8">
-        <v>43215</v>
+        <v>43401</v>
       </c>
       <c r="I159" s="9">
         <v>1</v>
       </c>
       <c r="J159" s="13" t="s">
-        <v>637</v>
+        <v>611</v>
       </c>
       <c r="K159" s="13" t="s">
         <v>612</v>
@@ -23057,37 +23058,37 @@
     </row>
     <row r="160" spans="1:11" ht="28" customHeight="1">
       <c r="A160" s="9" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="B160" s="8">
-        <v>42534</v>
+        <v>43401</v>
       </c>
       <c r="C160" s="9" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="D160" s="9" t="s">
-        <v>576</v>
+        <v>608</v>
       </c>
       <c r="E160" s="9" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>122</v>
       </c>
       <c r="G160" s="9" t="s">
-        <v>618</v>
+        <v>637</v>
       </c>
       <c r="H160" s="8">
-        <v>42534</v>
+        <v>43215</v>
       </c>
       <c r="I160" s="9">
         <v>1</v>
       </c>
       <c r="J160" s="13" t="s">
-        <v>618</v>
+        <v>637</v>
       </c>
       <c r="K160" s="13" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="28" customHeight="1">
@@ -23101,7 +23102,7 @@
         <v>614</v>
       </c>
       <c r="D161" s="9" t="s">
-        <v>616</v>
+        <v>576</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>752</v>
@@ -23110,18 +23111,53 @@
         <v>122</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>638</v>
+        <v>618</v>
       </c>
       <c r="H161" s="8">
-        <v>42412</v>
+        <v>42534</v>
       </c>
       <c r="I161" s="9">
         <v>1</v>
       </c>
       <c r="J161" s="13" t="s">
+        <v>618</v>
+      </c>
+      <c r="K161" s="13" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" ht="28" customHeight="1">
+      <c r="A162" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="B162" s="8">
+        <v>42534</v>
+      </c>
+      <c r="C162" s="9" t="s">
+        <v>614</v>
+      </c>
+      <c r="D162" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="E162" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="F162" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="G162" s="9" t="s">
         <v>638</v>
       </c>
-      <c r="K161" s="13" t="s">
+      <c r="H162" s="8">
+        <v>42412</v>
+      </c>
+      <c r="I162" s="9">
+        <v>1</v>
+      </c>
+      <c r="J162" s="13" t="s">
+        <v>638</v>
+      </c>
+      <c r="K162" s="13" t="s">
         <v>619</v>
       </c>
     </row>
@@ -23361,9 +23397,9 @@
     <hyperlink ref="J119" r:id="rId226"/>
     <hyperlink ref="G120" r:id="rId227"/>
     <hyperlink ref="J120" r:id="rId228"/>
-    <hyperlink ref="D121" r:id="rId229"/>
-    <hyperlink ref="G121" r:id="rId230"/>
-    <hyperlink ref="J121" r:id="rId231"/>
+    <hyperlink ref="G121" r:id="rId229"/>
+    <hyperlink ref="J121" r:id="rId230"/>
+    <hyperlink ref="D122" r:id="rId231"/>
     <hyperlink ref="G122" r:id="rId232"/>
     <hyperlink ref="J122" r:id="rId233"/>
     <hyperlink ref="G123" r:id="rId234"/>
@@ -23382,9 +23418,9 @@
     <hyperlink ref="J129" r:id="rId247"/>
     <hyperlink ref="G130" r:id="rId248"/>
     <hyperlink ref="J130" r:id="rId249"/>
-    <hyperlink ref="D131" r:id="rId250"/>
-    <hyperlink ref="G131" r:id="rId251"/>
-    <hyperlink ref="J131" r:id="rId252"/>
+    <hyperlink ref="G131" r:id="rId250"/>
+    <hyperlink ref="J131" r:id="rId251"/>
+    <hyperlink ref="D132" r:id="rId252"/>
     <hyperlink ref="G132" r:id="rId253"/>
     <hyperlink ref="J132" r:id="rId254"/>
     <hyperlink ref="G133" r:id="rId255"/>
@@ -23445,10 +23481,12 @@
     <hyperlink ref="J160" r:id="rId310"/>
     <hyperlink ref="G161" r:id="rId311"/>
     <hyperlink ref="J161" r:id="rId312"/>
+    <hyperlink ref="G162" r:id="rId313"/>
+    <hyperlink ref="J162" r:id="rId314"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId313"/>
+    <tablePart r:id="rId315"/>
   </tableParts>
 </worksheet>
 </file>
--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-17 | Build c09294a8cb0d | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-17 | Build c8f8520ee2f8 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-17 | Build 84f208c61d13 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-17 | Build a2b4948458ae | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -18,12 +18,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5559" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5569" uniqueCount="774">
   <si>
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-17 | Build a2b4948458ae | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-20 | Build b9ba83f370fc | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -2247,6 +2247,9 @@
     <t>https://bcs-express.ru/novosti-i-analitika/iandeks-odobril-vykup-aktsii-na-50-mlrd-rublei
 https://news.google.com/rss/articles/CBMikwFBVV95cUxPbkRNMVpoTFN4cXlrOWRya3A4SW1Dd09IUHIzMUw3emMzY1hZckpPRWtMclI2aTllZTRQTlRwUmNGNVp4X1hPV041elJSWGhtVS1kM0VGMFpWdmZIcDRmTS04MjBSb3FoVG5xZWdhY0REZkxLMTMxTE1PeF92VW5SRkxDYVNrVGVuNVFTSlRfaFFFeWc?oc=5
 https://news.google.com/rss/articles/CBMiqgFBVV95cUxPajdyQVZVYm1JZlFyeHU3bG41dUVvZ2M5eTJ3S1pCUTlXazlZYzFDSjJseGR5M3g2ZmhWT2xrczU5bWJTemJyNmhSRWd1ejAtQm9NcUlDUlhwcjgwbUpFQ2czbjgxX3MxVHhZYlVnUzRjNE9XZnk1LWY0T0tKcDRzOUx1LXNNUEsyOTJ2NWxLajRpenRTM0ZNaHJEemI1aGFyeGQxLVFDREY2Zw?oc=5</t>
+  </si>
+  <si>
+    <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxOQm1hb0Q1a2UzbENCQzJVQlh0MnJKRkJKMnY5RDBEbDM0alo0VzNNZ1pDVkQySXZ0TXRUYmd6dzJkd0h2T3RVUHB6ZFEwWGwzX1VDel94a0tFbHE3azFZOHVIdHktaU82TlBJelVRSGpqQzJMZ2doS1YwWFVZNmdjTXBfWHRiZmtNT2QxdjVtZWhIQTBTdEE1b1I3ci0?oc=5</t>
   </si>
   <si>
     <t>https://sbercib.ru/publication/rezultati-ozon-dom-rf-dividendi-yandeksa-i-tatnefti-i-drugie-novosti-nedeli
@@ -2666,8 +2669,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:K163" totalsRowShown="0">
-  <autoFilter ref="A6:K163"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SourcesTable" displayName="SourcesTable" ref="A6:K164" totalsRowShown="0">
+  <autoFilter ref="A6:K164"/>
   <tableColumns count="11">
     <tableColumn id="1" name="Deal ID"/>
     <tableColumn id="2" name="Date"/>
@@ -11875,7 +11878,7 @@
         <v>103</v>
       </c>
       <c r="AQ91" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR91" s="9" t="s">
         <v>324</v>
@@ -17610,7 +17613,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R163"/>
+  <dimension ref="A1:R164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -17673,7 +17676,7 @@
     </row>
     <row r="4" spans="1:18">
       <c r="M4" s="3" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -17716,19 +17719,19 @@
         <v>30</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>23</v>
@@ -17767,7 +17770,7 @@
         <v>106</v>
       </c>
       <c r="M7" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -17818,7 +17821,7 @@
         <v>114</v>
       </c>
       <c r="M8" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -17869,7 +17872,7 @@
         <v>119</v>
       </c>
       <c r="M9" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -17920,7 +17923,7 @@
         <v>123</v>
       </c>
       <c r="M10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -17973,7 +17976,7 @@
         <v>130</v>
       </c>
       <c r="M11" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -18024,7 +18027,7 @@
         <v>135</v>
       </c>
       <c r="M12" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -18075,7 +18078,7 @@
         <v>135</v>
       </c>
       <c r="M13" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -18126,7 +18129,7 @@
         <v>135</v>
       </c>
       <c r="M14" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -18210,7 +18213,7 @@
         <v>146</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -21563,51 +21566,49 @@
     </row>
     <row r="114" spans="1:11" ht="28" customHeight="1">
       <c r="A114" s="9" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B114" s="8">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C114" s="9" t="s">
         <v>48</v>
       </c>
       <c r="D114" s="9" t="s">
-        <v>442</v>
+        <v>121</v>
       </c>
       <c r="E114" s="9" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F114" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>443</v>
-      </c>
-      <c r="H114" s="8">
-        <v>46146</v>
-      </c>
+        <v>730</v>
+      </c>
+      <c r="H114" s="9"/>
       <c r="I114" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J114" s="13" t="s">
         <v>730</v>
       </c>
       <c r="K114" s="13" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="28" customHeight="1">
       <c r="A115" s="9" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B115" s="8">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="C115" s="9" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D115" s="9" t="s">
-        <v>139</v>
+        <v>442</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>660</v>
@@ -21616,10 +21617,10 @@
         <v>103</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="H115" s="8">
-        <v>46139</v>
+        <v>46146</v>
       </c>
       <c r="I115" s="9">
         <v>2</v>
@@ -21628,12 +21629,12 @@
         <v>731</v>
       </c>
       <c r="K115" s="13" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="28" customHeight="1">
       <c r="A116" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="B116" s="8">
         <v>46139</v>
@@ -21642,7 +21643,7 @@
         <v>34</v>
       </c>
       <c r="D116" s="9" t="s">
-        <v>324</v>
+        <v>139</v>
       </c>
       <c r="E116" s="9" t="s">
         <v>660</v>
@@ -21651,24 +21652,24 @@
         <v>103</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="H116" s="8">
         <v>46139</v>
       </c>
       <c r="I116" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J116" s="13" t="s">
         <v>732</v>
       </c>
       <c r="K116" s="13" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
     </row>
     <row r="117" spans="1:11" ht="28" customHeight="1">
       <c r="A117" s="9" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B117" s="8">
         <v>46139</v>
@@ -21677,7 +21678,7 @@
         <v>34</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>452</v>
+        <v>324</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>660</v>
@@ -21686,19 +21687,19 @@
         <v>103</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="H117" s="8">
         <v>46139</v>
       </c>
       <c r="I117" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J117" s="13" t="s">
         <v>733</v>
       </c>
       <c r="K117" s="13" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="118" spans="1:11" ht="28" customHeight="1">
@@ -21712,7 +21713,7 @@
         <v>34</v>
       </c>
       <c r="D118" s="9" t="s">
-        <v>104</v>
+        <v>452</v>
       </c>
       <c r="E118" s="9" t="s">
         <v>660</v>
@@ -21721,7 +21722,7 @@
         <v>103</v>
       </c>
       <c r="G118" s="9" t="s">
-        <v>734</v>
+        <v>453</v>
       </c>
       <c r="H118" s="8">
         <v>46139</v>
@@ -21730,7 +21731,7 @@
         <v>2</v>
       </c>
       <c r="J118" s="13" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K118" s="13" t="s">
         <v>454</v>
@@ -21747,23 +21748,25 @@
         <v>34</v>
       </c>
       <c r="D119" s="9" t="s">
-        <v>736</v>
+        <v>104</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>737</v>
-      </c>
-      <c r="H119" s="9"/>
+        <v>735</v>
+      </c>
+      <c r="H119" s="8">
+        <v>46139</v>
+      </c>
       <c r="I119" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J119" s="13" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="K119" s="13" t="s">
         <v>454</v>
@@ -21771,7 +21774,7 @@
     </row>
     <row r="120" spans="1:11" ht="28" customHeight="1">
       <c r="A120" s="9" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B120" s="8">
         <v>46139</v>
@@ -21780,33 +21783,31 @@
         <v>34</v>
       </c>
       <c r="D120" s="9" t="s">
-        <v>456</v>
+        <v>737</v>
       </c>
       <c r="E120" s="9" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F120" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G120" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="H120" s="8">
-        <v>46139</v>
-      </c>
+        <v>738</v>
+      </c>
+      <c r="H120" s="9"/>
       <c r="I120" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J120" s="13" t="s">
         <v>738</v>
       </c>
       <c r="K120" s="13" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="28" customHeight="1">
       <c r="A121" s="9" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B121" s="8">
         <v>46139</v>
@@ -21815,7 +21816,7 @@
         <v>34</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>660</v>
@@ -21824,7 +21825,7 @@
         <v>103</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="H121" s="8">
         <v>46139</v>
@@ -21836,21 +21837,21 @@
         <v>739</v>
       </c>
       <c r="K121" s="13" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="28" customHeight="1">
       <c r="A122" s="9" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B122" s="8">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>405</v>
+        <v>34</v>
       </c>
       <c r="D122" s="9" t="s">
-        <v>250</v>
+        <v>460</v>
       </c>
       <c r="E122" s="9" t="s">
         <v>660</v>
@@ -21859,10 +21860,10 @@
         <v>103</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="H122" s="8">
-        <v>46132</v>
+        <v>46139</v>
       </c>
       <c r="I122" s="9">
         <v>2</v>
@@ -21871,21 +21872,21 @@
         <v>740</v>
       </c>
       <c r="K122" s="13" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="123" spans="1:11" ht="28" customHeight="1">
       <c r="A123" s="9" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="B123" s="8">
         <v>46132</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>48</v>
+        <v>405</v>
       </c>
       <c r="D123" s="9" t="s">
-        <v>467</v>
+        <v>250</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>660</v>
@@ -21894,7 +21895,7 @@
         <v>103</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="H123" s="8">
         <v>46132</v>
@@ -21906,7 +21907,7 @@
         <v>741</v>
       </c>
       <c r="K123" s="13" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="124" spans="1:11" ht="28" customHeight="1">
@@ -21920,20 +21921,22 @@
         <v>48</v>
       </c>
       <c r="D124" s="9" t="s">
-        <v>121</v>
+        <v>467</v>
       </c>
       <c r="E124" s="9" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F124" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G124" s="9" t="s">
-        <v>742</v>
-      </c>
-      <c r="H124" s="9"/>
+        <v>468</v>
+      </c>
+      <c r="H124" s="8">
+        <v>46132</v>
+      </c>
       <c r="I124" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J124" s="13" t="s">
         <v>742</v>
@@ -21944,7 +21947,7 @@
     </row>
     <row r="125" spans="1:11" ht="28" customHeight="1">
       <c r="A125" s="9" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="B125" s="8">
         <v>46132</v>
@@ -21953,53 +21956,53 @@
         <v>48</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>471</v>
+        <v>121</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="H125" s="8">
-        <v>46132</v>
-      </c>
+        <v>743</v>
+      </c>
+      <c r="H125" s="9"/>
       <c r="I125" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J125" s="13" t="s">
         <v>743</v>
       </c>
       <c r="K125" s="13" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="126" spans="1:11" ht="28" customHeight="1">
       <c r="A126" s="9" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B126" s="8">
         <v>46132</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>405</v>
+        <v>48</v>
       </c>
       <c r="D126" s="9" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E126" s="9" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F126" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G126" s="9" t="s">
-        <v>476</v>
-      </c>
-      <c r="H126" s="9"/>
+        <v>472</v>
+      </c>
+      <c r="H126" s="8">
+        <v>46132</v>
+      </c>
       <c r="I126" s="9">
         <v>2</v>
       </c>
@@ -22007,34 +22010,32 @@
         <v>744</v>
       </c>
       <c r="K126" s="13" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="127" spans="1:11" ht="28" customHeight="1">
       <c r="A127" s="9" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B127" s="8">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="C127" s="9" t="s">
-        <v>479</v>
+        <v>405</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="H127" s="8">
-        <v>46128</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="H127" s="9"/>
       <c r="I127" s="9">
         <v>2</v>
       </c>
@@ -22042,7 +22043,7 @@
         <v>745</v>
       </c>
       <c r="K127" s="13" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="128" spans="1:11" ht="28" customHeight="1">
@@ -22056,7 +22057,7 @@
         <v>479</v>
       </c>
       <c r="D128" s="9" t="s">
-        <v>139</v>
+        <v>471</v>
       </c>
       <c r="E128" s="9" t="s">
         <v>660</v>
@@ -22065,7 +22066,7 @@
         <v>103</v>
       </c>
       <c r="G128" s="9" t="s">
-        <v>746</v>
+        <v>481</v>
       </c>
       <c r="H128" s="8">
         <v>46128</v>
@@ -22074,7 +22075,7 @@
         <v>2</v>
       </c>
       <c r="J128" s="13" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="K128" s="13" t="s">
         <v>482</v>
@@ -22091,7 +22092,7 @@
         <v>479</v>
       </c>
       <c r="D129" s="9" t="s">
-        <v>748</v>
+        <v>139</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>660</v>
@@ -22100,7 +22101,7 @@
         <v>103</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="H129" s="8">
         <v>46128</v>
@@ -22109,7 +22110,7 @@
         <v>2</v>
       </c>
       <c r="J129" s="13" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="K129" s="13" t="s">
         <v>482</v>
@@ -22126,20 +22127,22 @@
         <v>479</v>
       </c>
       <c r="D130" s="9" t="s">
-        <v>496</v>
+        <v>749</v>
       </c>
       <c r="E130" s="9" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G130" s="9" t="s">
-        <v>751</v>
-      </c>
-      <c r="H130" s="9"/>
+        <v>750</v>
+      </c>
+      <c r="H130" s="8">
+        <v>46128</v>
+      </c>
       <c r="I130" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J130" s="13" t="s">
         <v>751</v>
@@ -22150,51 +22153,49 @@
     </row>
     <row r="131" spans="1:11" ht="28" customHeight="1">
       <c r="A131" s="9" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B131" s="8">
-        <v>46122</v>
+        <v>46128</v>
       </c>
       <c r="C131" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>299</v>
+        <v>496</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>103</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>484</v>
-      </c>
-      <c r="H131" s="8">
-        <v>46122</v>
-      </c>
+        <v>752</v>
+      </c>
+      <c r="H131" s="9"/>
       <c r="I131" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J131" s="13" t="s">
         <v>752</v>
       </c>
       <c r="K131" s="13" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="132" spans="1:11" ht="28" customHeight="1">
       <c r="A132" s="9" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B132" s="8">
         <v>46122</v>
       </c>
       <c r="C132" s="9" t="s">
-        <v>405</v>
+        <v>480</v>
       </c>
       <c r="D132" s="9" t="s">
-        <v>250</v>
+        <v>299</v>
       </c>
       <c r="E132" s="9" t="s">
         <v>660</v>
@@ -22203,7 +22204,7 @@
         <v>103</v>
       </c>
       <c r="G132" s="9" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="H132" s="8">
         <v>46122</v>
@@ -22215,21 +22216,21 @@
         <v>753</v>
       </c>
       <c r="K132" s="13" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
     </row>
     <row r="133" spans="1:11" ht="28" customHeight="1">
       <c r="A133" s="9" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B133" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="C133" s="9" t="s">
         <v>405</v>
       </c>
       <c r="D133" s="9" t="s">
-        <v>467</v>
+        <v>250</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>660</v>
@@ -22238,10 +22239,10 @@
         <v>103</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="H133" s="8">
-        <v>46115</v>
+        <v>46122</v>
       </c>
       <c r="I133" s="9">
         <v>2</v>
@@ -22250,12 +22251,12 @@
         <v>754</v>
       </c>
       <c r="K133" s="13" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="134" spans="1:11" ht="28" customHeight="1">
       <c r="A134" s="9" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B134" s="8">
         <v>46115</v>
@@ -22264,7 +22265,7 @@
         <v>405</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>324</v>
+        <v>467</v>
       </c>
       <c r="E134" s="9" t="s">
         <v>660</v>
@@ -22273,7 +22274,7 @@
         <v>103</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="H134" s="8">
         <v>46115</v>
@@ -22285,21 +22286,21 @@
         <v>755</v>
       </c>
       <c r="K134" s="13" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
     </row>
     <row r="135" spans="1:11" ht="28" customHeight="1">
       <c r="A135" s="9" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B135" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="C135" s="9" t="s">
-        <v>480</v>
+        <v>405</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>496</v>
+        <v>324</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>660</v>
@@ -22308,24 +22309,24 @@
         <v>103</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="H135" s="8">
-        <v>46111</v>
+        <v>46115</v>
       </c>
       <c r="I135" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J135" s="13" t="s">
-        <v>497</v>
+        <v>756</v>
       </c>
       <c r="K135" s="13" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
     </row>
     <row r="136" spans="1:11" ht="28" customHeight="1">
       <c r="A136" s="9" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B136" s="8">
         <v>46111</v>
@@ -22334,7 +22335,7 @@
         <v>480</v>
       </c>
       <c r="D136" s="9" t="s">
-        <v>299</v>
+        <v>496</v>
       </c>
       <c r="E136" s="9" t="s">
         <v>660</v>
@@ -22343,7 +22344,7 @@
         <v>103</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="H136" s="8">
         <v>46111</v>
@@ -22352,53 +22353,53 @@
         <v>1</v>
       </c>
       <c r="J136" s="13" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K136" s="13" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="137" spans="1:11" ht="28" customHeight="1">
       <c r="A137" s="9" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B137" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="C137" s="9" t="s">
-        <v>41</v>
+        <v>480</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>188</v>
+        <v>299</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>660</v>
       </c>
       <c r="F137" s="9" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="H137" s="8">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="I137" s="9">
         <v>1</v>
       </c>
       <c r="J137" s="13" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="K137" s="13" t="s">
-        <v>54</v>
+        <v>501</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="28" customHeight="1">
       <c r="A138" s="9" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B138" s="8">
-        <v>45923</v>
+        <v>46080</v>
       </c>
       <c r="C138" s="9" t="s">
         <v>41</v>
@@ -22407,39 +22408,39 @@
         <v>188</v>
       </c>
       <c r="E138" s="9" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="F138" s="9" t="s">
         <v>127</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="H138" s="8">
-        <v>45923</v>
+        <v>46080</v>
       </c>
       <c r="I138" s="9">
         <v>1</v>
       </c>
       <c r="J138" s="13" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="K138" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="28" customHeight="1">
       <c r="A139" s="9" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B139" s="8">
-        <v>45729</v>
+        <v>45923</v>
       </c>
       <c r="C139" s="9" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>394</v>
+        <v>188</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>674</v>
@@ -22448,33 +22449,33 @@
         <v>127</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="H139" s="8">
-        <v>45729</v>
+        <v>45923</v>
       </c>
       <c r="I139" s="9">
         <v>1</v>
       </c>
       <c r="J139" s="13" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="K139" s="13" t="s">
-        <v>509</v>
+        <v>55</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="28" customHeight="1">
       <c r="A140" s="9" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B140" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="C140" s="9" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>188</v>
+        <v>394</v>
       </c>
       <c r="E140" s="9" t="s">
         <v>674</v>
@@ -22483,30 +22484,30 @@
         <v>127</v>
       </c>
       <c r="G140" s="9" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="H140" s="8">
-        <v>45642</v>
+        <v>45729</v>
       </c>
       <c r="I140" s="9">
         <v>1</v>
       </c>
       <c r="J140" s="13" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="K140" s="13" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="28" customHeight="1">
       <c r="A141" s="9" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B141" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="C141" s="9" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D141" s="9" t="s">
         <v>188</v>
@@ -22518,27 +22519,27 @@
         <v>127</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="H141" s="8">
-        <v>45611</v>
+        <v>45642</v>
       </c>
       <c r="I141" s="9">
         <v>1</v>
       </c>
       <c r="J141" s="13" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="K141" s="13" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="28" customHeight="1">
       <c r="A142" s="9" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B142" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="C142" s="9" t="s">
         <v>41</v>
@@ -22547,33 +22548,33 @@
         <v>188</v>
       </c>
       <c r="E142" s="9" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="F142" s="9" t="s">
         <v>127</v>
       </c>
       <c r="G142" s="9" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="H142" s="8">
-        <v>45391</v>
+        <v>45611</v>
       </c>
       <c r="I142" s="9">
         <v>1</v>
       </c>
       <c r="J142" s="13" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="K142" s="13" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="28" customHeight="1">
       <c r="A143" s="9" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="B143" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="C143" s="9" t="s">
         <v>41</v>
@@ -22582,36 +22583,36 @@
         <v>188</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>674</v>
+        <v>660</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>127</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="H143" s="8">
-        <v>45357</v>
+        <v>45391</v>
       </c>
       <c r="I143" s="9">
         <v>1</v>
       </c>
       <c r="J143" s="13" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="K143" s="13" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="144" spans="1:11" ht="28" customHeight="1">
       <c r="A144" s="9" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B144" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>525</v>
+        <v>41</v>
       </c>
       <c r="D144" s="9" t="s">
         <v>188</v>
@@ -22623,54 +22624,54 @@
         <v>127</v>
       </c>
       <c r="G144" s="9" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="H144" s="8">
-        <v>45288</v>
+        <v>45357</v>
       </c>
       <c r="I144" s="9">
         <v>1</v>
       </c>
       <c r="J144" s="13" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="K144" s="13" t="s">
-        <v>528</v>
+        <v>517</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="28" customHeight="1">
       <c r="A145" s="9" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B145" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="C145" s="9" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>539</v>
+        <v>188</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>756</v>
+        <v>674</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>127</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="H145" s="8">
-        <v>45190</v>
+        <v>45288</v>
       </c>
       <c r="I145" s="9">
         <v>1</v>
       </c>
       <c r="J145" s="13" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="K145" s="13" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
     </row>
     <row r="146" spans="1:11" ht="28" customHeight="1">
@@ -22684,7 +22685,7 @@
         <v>530</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E146" s="9" t="s">
         <v>757</v>
@@ -22693,16 +22694,16 @@
         <v>127</v>
       </c>
       <c r="G146" s="9" t="s">
-        <v>633</v>
+        <v>540</v>
       </c>
       <c r="H146" s="8">
-        <v>45008</v>
+        <v>45190</v>
       </c>
       <c r="I146" s="9">
         <v>1</v>
       </c>
       <c r="J146" s="13" t="s">
-        <v>633</v>
+        <v>540</v>
       </c>
       <c r="K146" s="13" t="s">
         <v>541</v>
@@ -22710,37 +22711,37 @@
     </row>
     <row r="147" spans="1:11" ht="28" customHeight="1">
       <c r="A147" s="9" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="B147" s="8">
-        <v>44707</v>
+        <v>45190</v>
       </c>
       <c r="C147" s="9" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>127</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>551</v>
+        <v>633</v>
       </c>
       <c r="H147" s="8">
-        <v>44707</v>
+        <v>45008</v>
       </c>
       <c r="I147" s="9">
         <v>1</v>
       </c>
       <c r="J147" s="13" t="s">
-        <v>551</v>
+        <v>633</v>
       </c>
       <c r="K147" s="13" t="s">
-        <v>552</v>
+        <v>541</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="28" customHeight="1">
@@ -22754,7 +22755,7 @@
         <v>543</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E148" s="9" t="s">
         <v>757</v>
@@ -22763,16 +22764,16 @@
         <v>127</v>
       </c>
       <c r="G148" s="9" t="s">
-        <v>634</v>
+        <v>551</v>
       </c>
       <c r="H148" s="8">
-        <v>44644</v>
+        <v>44707</v>
       </c>
       <c r="I148" s="9">
         <v>1</v>
       </c>
       <c r="J148" s="13" t="s">
-        <v>634</v>
+        <v>551</v>
       </c>
       <c r="K148" s="13" t="s">
         <v>552</v>
@@ -22780,37 +22781,37 @@
     </row>
     <row r="149" spans="1:11" ht="28" customHeight="1">
       <c r="A149" s="9" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="B149" s="8">
-        <v>44640</v>
+        <v>44707</v>
       </c>
       <c r="C149" s="9" t="s">
-        <v>554</v>
+        <v>543</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>560</v>
+        <v>548</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>127</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>561</v>
+        <v>634</v>
       </c>
       <c r="H149" s="8">
-        <v>44734</v>
+        <v>44644</v>
       </c>
       <c r="I149" s="9">
         <v>1</v>
       </c>
       <c r="J149" s="13" t="s">
-        <v>561</v>
+        <v>634</v>
       </c>
       <c r="K149" s="13" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="28" customHeight="1">
@@ -22824,7 +22825,7 @@
         <v>554</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="E150" s="9" t="s">
         <v>757</v>
@@ -22833,16 +22834,16 @@
         <v>127</v>
       </c>
       <c r="G150" s="9" t="s">
-        <v>635</v>
+        <v>561</v>
       </c>
       <c r="H150" s="8">
-        <v>44643</v>
+        <v>44734</v>
       </c>
       <c r="I150" s="9">
         <v>1</v>
       </c>
       <c r="J150" s="13" t="s">
-        <v>635</v>
+        <v>561</v>
       </c>
       <c r="K150" s="13" t="s">
         <v>562</v>
@@ -22850,72 +22851,72 @@
     </row>
     <row r="151" spans="1:11" ht="28" customHeight="1">
       <c r="A151" s="9" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="B151" s="8">
-        <v>44592</v>
+        <v>44640</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>127</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>570</v>
+        <v>635</v>
       </c>
       <c r="H151" s="8">
-        <v>44608</v>
+        <v>44643</v>
       </c>
       <c r="I151" s="9">
         <v>1</v>
       </c>
       <c r="J151" s="13" t="s">
-        <v>570</v>
+        <v>635</v>
       </c>
       <c r="K151" s="13" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="28" customHeight="1">
       <c r="A152" s="9" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="B152" s="8">
-        <v>44579</v>
+        <v>44592</v>
       </c>
       <c r="C152" s="9" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="E152" s="9" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F152" s="9" t="s">
         <v>127</v>
       </c>
       <c r="G152" s="9" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="H152" s="8">
-        <v>44579</v>
+        <v>44608</v>
       </c>
       <c r="I152" s="9">
         <v>1</v>
       </c>
       <c r="J152" s="13" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="K152" s="13" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="28" customHeight="1">
@@ -22929,7 +22930,7 @@
         <v>573</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>757</v>
@@ -22938,16 +22939,16 @@
         <v>127</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>636</v>
+        <v>580</v>
       </c>
       <c r="H153" s="8">
-        <v>44250</v>
+        <v>44579</v>
       </c>
       <c r="I153" s="9">
         <v>1</v>
       </c>
       <c r="J153" s="13" t="s">
-        <v>636</v>
+        <v>580</v>
       </c>
       <c r="K153" s="13" t="s">
         <v>581</v>
@@ -22955,37 +22956,37 @@
     </row>
     <row r="154" spans="1:11" ht="28" customHeight="1">
       <c r="A154" s="9" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="B154" s="8">
-        <v>44166</v>
+        <v>44579</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
       <c r="E154" s="9" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F154" s="9" t="s">
         <v>127</v>
       </c>
       <c r="G154" s="9" t="s">
-        <v>589</v>
+        <v>636</v>
       </c>
       <c r="H154" s="8">
-        <v>44166</v>
+        <v>44250</v>
       </c>
       <c r="I154" s="9">
         <v>1</v>
       </c>
       <c r="J154" s="13" t="s">
-        <v>589</v>
+        <v>636</v>
       </c>
       <c r="K154" s="13" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="28" customHeight="1">
@@ -22999,7 +23000,7 @@
         <v>583</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>757</v>
@@ -23008,16 +23009,16 @@
         <v>127</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>637</v>
+        <v>589</v>
       </c>
       <c r="H155" s="8">
-        <v>43902</v>
+        <v>44166</v>
       </c>
       <c r="I155" s="9">
         <v>1</v>
       </c>
       <c r="J155" s="13" t="s">
-        <v>637</v>
+        <v>589</v>
       </c>
       <c r="K155" s="13" t="s">
         <v>590</v>
@@ -23025,37 +23026,37 @@
     </row>
     <row r="156" spans="1:11" ht="28" customHeight="1">
       <c r="A156" s="9" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="B156" s="8">
-        <v>44131</v>
+        <v>44166</v>
       </c>
       <c r="C156" s="9" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="D156" s="9" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="E156" s="9" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F156" s="9" t="s">
         <v>127</v>
       </c>
       <c r="G156" s="9" t="s">
-        <v>598</v>
+        <v>637</v>
       </c>
       <c r="H156" s="8">
-        <v>44131</v>
+        <v>43902</v>
       </c>
       <c r="I156" s="9">
         <v>1</v>
       </c>
       <c r="J156" s="13" t="s">
-        <v>598</v>
+        <v>637</v>
       </c>
       <c r="K156" s="13" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="28" customHeight="1">
@@ -23069,7 +23070,7 @@
         <v>592</v>
       </c>
       <c r="D157" s="9" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>757</v>
@@ -23078,16 +23079,16 @@
         <v>127</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>638</v>
+        <v>598</v>
       </c>
       <c r="H157" s="8">
-        <v>43966</v>
+        <v>44131</v>
       </c>
       <c r="I157" s="9">
         <v>1</v>
       </c>
       <c r="J157" s="13" t="s">
-        <v>638</v>
+        <v>598</v>
       </c>
       <c r="K157" s="13" t="s">
         <v>599</v>
@@ -23095,37 +23096,37 @@
     </row>
     <row r="158" spans="1:11" ht="28" customHeight="1">
       <c r="A158" s="9" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="B158" s="8">
-        <v>43626</v>
+        <v>44131</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="D158" s="9" t="s">
-        <v>588</v>
+        <v>595</v>
       </c>
       <c r="E158" s="9" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F158" s="9" t="s">
         <v>127</v>
       </c>
       <c r="G158" s="9" t="s">
-        <v>605</v>
+        <v>638</v>
       </c>
       <c r="H158" s="8">
-        <v>43626</v>
+        <v>43966</v>
       </c>
       <c r="I158" s="9">
         <v>1</v>
       </c>
       <c r="J158" s="13" t="s">
-        <v>605</v>
+        <v>638</v>
       </c>
       <c r="K158" s="13" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="28" customHeight="1">
@@ -23139,7 +23140,7 @@
         <v>601</v>
       </c>
       <c r="D159" s="9" t="s">
-        <v>603</v>
+        <v>588</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>757</v>
@@ -23148,16 +23149,16 @@
         <v>127</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>639</v>
+        <v>605</v>
       </c>
       <c r="H159" s="8">
-        <v>43518</v>
+        <v>43626</v>
       </c>
       <c r="I159" s="9">
         <v>1</v>
       </c>
       <c r="J159" s="13" t="s">
-        <v>639</v>
+        <v>605</v>
       </c>
       <c r="K159" s="13" t="s">
         <v>606</v>
@@ -23165,37 +23166,37 @@
     </row>
     <row r="160" spans="1:11" ht="28" customHeight="1">
       <c r="A160" s="9" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="B160" s="8">
-        <v>43401</v>
+        <v>43626</v>
       </c>
       <c r="C160" s="9" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="D160" s="9" t="s">
-        <v>613</v>
+        <v>603</v>
       </c>
       <c r="E160" s="9" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F160" s="9" t="s">
         <v>127</v>
       </c>
       <c r="G160" s="9" t="s">
-        <v>614</v>
+        <v>639</v>
       </c>
       <c r="H160" s="8">
-        <v>43401</v>
+        <v>43518</v>
       </c>
       <c r="I160" s="9">
         <v>1</v>
       </c>
       <c r="J160" s="13" t="s">
-        <v>614</v>
+        <v>639</v>
       </c>
       <c r="K160" s="13" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="28" customHeight="1">
@@ -23209,7 +23210,7 @@
         <v>608</v>
       </c>
       <c r="D161" s="9" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>757</v>
@@ -23218,16 +23219,16 @@
         <v>127</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>640</v>
+        <v>614</v>
       </c>
       <c r="H161" s="8">
-        <v>43215</v>
+        <v>43401</v>
       </c>
       <c r="I161" s="9">
         <v>1</v>
       </c>
       <c r="J161" s="13" t="s">
-        <v>640</v>
+        <v>614</v>
       </c>
       <c r="K161" s="13" t="s">
         <v>615</v>
@@ -23235,37 +23236,37 @@
     </row>
     <row r="162" spans="1:11" ht="28" customHeight="1">
       <c r="A162" s="9" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="B162" s="8">
-        <v>42534</v>
+        <v>43401</v>
       </c>
       <c r="C162" s="9" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="D162" s="9" t="s">
-        <v>579</v>
+        <v>611</v>
       </c>
       <c r="E162" s="9" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="F162" s="9" t="s">
         <v>127</v>
       </c>
       <c r="G162" s="9" t="s">
-        <v>621</v>
+        <v>640</v>
       </c>
       <c r="H162" s="8">
-        <v>42534</v>
+        <v>43215</v>
       </c>
       <c r="I162" s="9">
         <v>1</v>
       </c>
       <c r="J162" s="13" t="s">
-        <v>621</v>
+        <v>640</v>
       </c>
       <c r="K162" s="13" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
     </row>
     <row r="163" spans="1:11" ht="28" customHeight="1">
@@ -23279,7 +23280,7 @@
         <v>617</v>
       </c>
       <c r="D163" s="9" t="s">
-        <v>619</v>
+        <v>579</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>757</v>
@@ -23288,18 +23289,53 @@
         <v>127</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>641</v>
+        <v>621</v>
       </c>
       <c r="H163" s="8">
-        <v>42412</v>
+        <v>42534</v>
       </c>
       <c r="I163" s="9">
         <v>1</v>
       </c>
       <c r="J163" s="13" t="s">
+        <v>621</v>
+      </c>
+      <c r="K163" s="13" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" ht="28" customHeight="1">
+      <c r="A164" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="B164" s="8">
+        <v>42534</v>
+      </c>
+      <c r="C164" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="D164" s="9" t="s">
+        <v>619</v>
+      </c>
+      <c r="E164" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="F164" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G164" s="9" t="s">
         <v>641</v>
       </c>
-      <c r="K163" s="13" t="s">
+      <c r="H164" s="8">
+        <v>42412</v>
+      </c>
+      <c r="I164" s="9">
+        <v>1</v>
+      </c>
+      <c r="J164" s="13" t="s">
+        <v>641</v>
+      </c>
+      <c r="K164" s="13" t="s">
         <v>622</v>
       </c>
     </row>
@@ -23543,9 +23579,9 @@
     <hyperlink ref="J121" r:id="rId230"/>
     <hyperlink ref="G122" r:id="rId231"/>
     <hyperlink ref="J122" r:id="rId232"/>
-    <hyperlink ref="D123" r:id="rId233"/>
-    <hyperlink ref="G123" r:id="rId234"/>
-    <hyperlink ref="J123" r:id="rId235"/>
+    <hyperlink ref="G123" r:id="rId233"/>
+    <hyperlink ref="J123" r:id="rId234"/>
+    <hyperlink ref="D124" r:id="rId235"/>
     <hyperlink ref="G124" r:id="rId236"/>
     <hyperlink ref="J124" r:id="rId237"/>
     <hyperlink ref="G125" r:id="rId238"/>
@@ -23564,9 +23600,9 @@
     <hyperlink ref="J131" r:id="rId251"/>
     <hyperlink ref="G132" r:id="rId252"/>
     <hyperlink ref="J132" r:id="rId253"/>
-    <hyperlink ref="D133" r:id="rId254"/>
-    <hyperlink ref="G133" r:id="rId255"/>
-    <hyperlink ref="J133" r:id="rId256"/>
+    <hyperlink ref="G133" r:id="rId254"/>
+    <hyperlink ref="J133" r:id="rId255"/>
+    <hyperlink ref="D134" r:id="rId256"/>
     <hyperlink ref="G134" r:id="rId257"/>
     <hyperlink ref="J134" r:id="rId258"/>
     <hyperlink ref="G135" r:id="rId259"/>
@@ -23627,10 +23663,12 @@
     <hyperlink ref="J162" r:id="rId314"/>
     <hyperlink ref="G163" r:id="rId315"/>
     <hyperlink ref="J163" r:id="rId316"/>
+    <hyperlink ref="G164" r:id="rId317"/>
+    <hyperlink ref="J164" r:id="rId318"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId317"/>
+    <tablePart r:id="rId319"/>
   </tableParts>
 </worksheet>
 </file>
--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-20 | Build b9ba83f370fc | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-20 | Build 7dd51c888995 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-21 | Build d9eba1503b57 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-21 | Build 6c51d67bf890 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
@@ -11223,7 +11223,7 @@
         <v>406</v>
       </c>
       <c r="B84" s="8">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C84" s="9" t="s">
         <v>6</v>
@@ -21602,7 +21602,7 @@
         <v>406</v>
       </c>
       <c r="B92" s="8">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C92" s="9" t="s">
         <v>407</v>
@@ -21635,7 +21635,7 @@
         <v>406</v>
       </c>
       <c r="B93" s="8">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="C93" s="9" t="s">
         <v>407</v>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-22 | Build 099a1017621b | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-22 | Build eca6c0172277 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-22 | Build 5ec8cec17651 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-22 | Build d6eb7fa2d78b | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-22 | Build d6eb7fa2d78b | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-22 | Build 0b5f25754968 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-23 | Build deddb3adcb23 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-23 | Build fa00b9674345 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-23 | Build 2952ddd903c9 | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-24 | Build 06f0ff817a21 | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-24 | Build 3c4fba95709b | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-24 | Build 3fc14f3aa86b | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>

--- a/output/precedent_transactions.xlsx
+++ b/output/precedent_transactions.xlsx
@@ -23,7 +23,7 @@
     <t>DEAL MARKETS COPILOT — SUMMARY</t>
   </si>
   <si>
-    <t>As of 2026-07-24 | Build 3fc14f3aa86b | Quality-controlled transaction monitor</t>
+    <t>As of 2026-07-24 | Build e9bc656ea0dd | Quality-controlled transaction monitor</t>
   </si>
   <si>
     <t>DATABASE SNAPSHOT</t>
